--- a/raw/D3.xlsx
+++ b/raw/D3.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F768A3-B27A-47E9-A67D-636D0CCF8837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7ADCC9-A251-4939-A210-780A803D34BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30-2" sheetId="34" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="15" sheetId="40" r:id="rId7"/>
     <sheet name="15-2" sheetId="41" r:id="rId8"/>
     <sheet name="16" sheetId="42" r:id="rId9"/>
+    <sheet name="17" sheetId="43" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -104,6 +105,62 @@
           </rPr>
           <t>Аслан
 87014988298</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="H17" authorId="0" shapeId="0" xr:uid="{DB11EAC8-E36B-467E-B5F7-A8976A1623C1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Даулет
+87025167087</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H19" authorId="0" shapeId="0" xr:uid="{F786351A-3C6C-434C-B6B8-53861529347C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Аслан
+87014988298</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{D7B936F9-5C1D-4D19-91FE-1CAA3AE7D317}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Алібек
+87012894507</t>
         </r>
       </text>
     </comment>
@@ -807,7 +864,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="245">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -1539,6 +1596,9 @@
   </si>
   <si>
     <t xml:space="preserve">22-H268212  </t>
+  </si>
+  <si>
+    <t>49-Н180112</t>
   </si>
 </sst>
 </file>
@@ -2359,7 +2419,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="265">
+  <cellXfs count="272">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3046,10 +3106,46 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3066,37 +3162,31 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3110,15 +3200,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -4316,21 +4397,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="251" t="s">
+      <c r="A1" s="246" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4385,13 +4466,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="240" t="s">
+      <c r="D3" s="247" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="240" t="s">
+      <c r="F3" s="247" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -4403,24 +4484,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="246" t="s">
+      <c r="J3" s="245" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="247" t="s">
+      <c r="M3" s="248" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="244" t="s">
+      <c r="Q3" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="245"/>
+      <c r="R3" s="257"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="237" t="s">
+      <c r="T3" s="250" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="238"/>
+      <c r="U3" s="251"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -4432,20 +4513,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="240"/>
+      <c r="D4" s="247"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="240"/>
+      <c r="F4" s="247"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="246"/>
+      <c r="J4" s="245"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="247"/>
+      <c r="M4" s="248"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -4484,7 +4565,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="243" t="s">
+      <c r="F5" s="255" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -4492,7 +4573,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="240" t="s">
+      <c r="J5" s="247" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -4537,13 +4618,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="243"/>
+      <c r="F6" s="255"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="240"/>
+      <c r="J6" s="247"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -4589,13 +4670,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="246" t="s">
+      <c r="F7" s="245" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="242" t="s">
+      <c r="J7" s="254" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -4643,11 +4724,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="246"/>
+      <c r="F8" s="245"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="242"/>
+      <c r="J8" s="254"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -4691,7 +4772,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="243" t="s">
+      <c r="F9" s="255" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -4731,7 +4812,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="243"/>
+      <c r="F10" s="255"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -4856,7 +4937,7 @@
         <v>115</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="247" t="s">
+      <c r="H13" s="248" t="s">
         <v>82</v>
       </c>
       <c r="I13" s="30"/>
@@ -4895,7 +4976,7 @@
       <c r="F14" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="247"/>
+      <c r="H14" s="248"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -4930,7 +5011,7 @@
         <v>83</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="247" t="s">
+      <c r="H15" s="248" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="30"/>
@@ -4967,7 +5048,7 @@
         <v>81</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="247"/>
+      <c r="H16" s="248"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -4999,7 +5080,7 @@
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="248" t="s">
+      <c r="H17" s="258" t="s">
         <v>45</v>
       </c>
       <c r="I17" s="30"/>
@@ -5034,7 +5115,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="249"/>
+      <c r="H18" s="259"/>
       <c r="I18" s="30"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
@@ -5051,7 +5132,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="246" t="s">
+      <c r="H19" s="245" t="s">
         <v>85</v>
       </c>
       <c r="I19" s="30"/>
@@ -5076,7 +5157,7 @@
       <c r="E20" s="137"/>
       <c r="F20" s="8"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="246"/>
+      <c r="H20" s="245"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -5095,7 +5176,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="246" t="s">
+      <c r="H21" s="245" t="s">
         <v>84</v>
       </c>
       <c r="I21" s="30"/>
@@ -5112,7 +5193,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="137"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="246"/>
+      <c r="H22" s="245"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -5209,13 +5290,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="252" t="s">
+      <c r="A28" s="249" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="252"/>
-      <c r="C28" s="252"/>
-      <c r="D28" s="252"/>
-      <c r="E28" s="252"/>
+      <c r="B28" s="249"/>
+      <c r="C28" s="249"/>
+      <c r="D28" s="249"/>
+      <c r="E28" s="249"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -5275,7 +5356,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="241" t="s">
+      <c r="E30" s="253" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -5309,7 +5390,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="241"/>
+      <c r="E31" s="253"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -5339,7 +5420,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="241" t="s">
+      <c r="E32" s="253" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="8"/>
@@ -5365,7 +5446,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="241"/>
+      <c r="E33" s="253"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
       <c r="I33" s="30"/>
@@ -5388,7 +5469,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="239" t="s">
+      <c r="E34" s="252" t="s">
         <v>133</v>
       </c>
       <c r="G34" s="8"/>
@@ -5409,7 +5490,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="239"/>
+      <c r="E35" s="252"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
       <c r="I35" s="30"/>
@@ -5428,7 +5509,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="241" t="s">
+      <c r="E36" s="253" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -5448,7 +5529,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="241"/>
+      <c r="E37" s="253"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -5915,7 +5996,7 @@
       <c r="S65"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A66" s="250" t="s">
+      <c r="A66" s="244" t="s">
         <v>139</v>
       </c>
       <c r="L66" s="119" t="s">
@@ -5927,7 +6008,7 @@
       <c r="S66"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A67" s="250"/>
+      <c r="A67" s="244"/>
       <c r="L67" s="119" t="s">
         <v>95</v>
       </c>
@@ -5979,14 +6060,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A28:E28"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="J5:J6"/>
@@ -6002,6 +6075,2619 @@
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="H17:H18"/>
     <mergeCell ref="H19:H20"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A28:E28"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83BEC9BE-4127-4590-88B0-716BDF9EF620}">
+  <dimension ref="A1:W72"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" style="98" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" style="25" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" style="25" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" style="25" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" customWidth="1"/>
+    <col min="14" max="14" width="21.26953125" customWidth="1"/>
+    <col min="15" max="15" width="9.7265625" customWidth="1"/>
+    <col min="16" max="16" width="7.7265625" customWidth="1"/>
+    <col min="17" max="17" width="6.453125" customWidth="1"/>
+    <col min="18" max="18" width="7.81640625" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" style="84" customWidth="1"/>
+    <col min="20" max="20" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="257" max="260" width="14.453125" customWidth="1"/>
+    <col min="261" max="261" width="15.453125" customWidth="1"/>
+    <col min="262" max="262" width="14.54296875" customWidth="1"/>
+    <col min="263" max="263" width="15.26953125" customWidth="1"/>
+    <col min="264" max="265" width="14.453125" customWidth="1"/>
+    <col min="266" max="266" width="13.1796875" customWidth="1"/>
+    <col min="267" max="269" width="14.453125" customWidth="1"/>
+    <col min="270" max="270" width="15.81640625" customWidth="1"/>
+    <col min="271" max="271" width="7.81640625" customWidth="1"/>
+    <col min="272" max="272" width="5.453125" customWidth="1"/>
+    <col min="273" max="273" width="6.453125" customWidth="1"/>
+    <col min="274" max="274" width="7.81640625" customWidth="1"/>
+    <col min="275" max="275" width="3" customWidth="1"/>
+    <col min="276" max="276" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="513" max="516" width="14.453125" customWidth="1"/>
+    <col min="517" max="517" width="15.453125" customWidth="1"/>
+    <col min="518" max="518" width="14.54296875" customWidth="1"/>
+    <col min="519" max="519" width="15.26953125" customWidth="1"/>
+    <col min="520" max="521" width="14.453125" customWidth="1"/>
+    <col min="522" max="522" width="13.1796875" customWidth="1"/>
+    <col min="523" max="525" width="14.453125" customWidth="1"/>
+    <col min="526" max="526" width="15.81640625" customWidth="1"/>
+    <col min="527" max="527" width="7.81640625" customWidth="1"/>
+    <col min="528" max="528" width="5.453125" customWidth="1"/>
+    <col min="529" max="529" width="6.453125" customWidth="1"/>
+    <col min="530" max="530" width="7.81640625" customWidth="1"/>
+    <col min="531" max="531" width="3" customWidth="1"/>
+    <col min="532" max="532" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="769" max="772" width="14.453125" customWidth="1"/>
+    <col min="773" max="773" width="15.453125" customWidth="1"/>
+    <col min="774" max="774" width="14.54296875" customWidth="1"/>
+    <col min="775" max="775" width="15.26953125" customWidth="1"/>
+    <col min="776" max="777" width="14.453125" customWidth="1"/>
+    <col min="778" max="778" width="13.1796875" customWidth="1"/>
+    <col min="779" max="781" width="14.453125" customWidth="1"/>
+    <col min="782" max="782" width="15.81640625" customWidth="1"/>
+    <col min="783" max="783" width="7.81640625" customWidth="1"/>
+    <col min="784" max="784" width="5.453125" customWidth="1"/>
+    <col min="785" max="785" width="6.453125" customWidth="1"/>
+    <col min="786" max="786" width="7.81640625" customWidth="1"/>
+    <col min="787" max="787" width="3" customWidth="1"/>
+    <col min="788" max="788" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1025" max="1028" width="14.453125" customWidth="1"/>
+    <col min="1029" max="1029" width="15.453125" customWidth="1"/>
+    <col min="1030" max="1030" width="14.54296875" customWidth="1"/>
+    <col min="1031" max="1031" width="15.26953125" customWidth="1"/>
+    <col min="1032" max="1033" width="14.453125" customWidth="1"/>
+    <col min="1034" max="1034" width="13.1796875" customWidth="1"/>
+    <col min="1035" max="1037" width="14.453125" customWidth="1"/>
+    <col min="1038" max="1038" width="15.81640625" customWidth="1"/>
+    <col min="1039" max="1039" width="7.81640625" customWidth="1"/>
+    <col min="1040" max="1040" width="5.453125" customWidth="1"/>
+    <col min="1041" max="1041" width="6.453125" customWidth="1"/>
+    <col min="1042" max="1042" width="7.81640625" customWidth="1"/>
+    <col min="1043" max="1043" width="3" customWidth="1"/>
+    <col min="1044" max="1044" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1281" max="1284" width="14.453125" customWidth="1"/>
+    <col min="1285" max="1285" width="15.453125" customWidth="1"/>
+    <col min="1286" max="1286" width="14.54296875" customWidth="1"/>
+    <col min="1287" max="1287" width="15.26953125" customWidth="1"/>
+    <col min="1288" max="1289" width="14.453125" customWidth="1"/>
+    <col min="1290" max="1290" width="13.1796875" customWidth="1"/>
+    <col min="1291" max="1293" width="14.453125" customWidth="1"/>
+    <col min="1294" max="1294" width="15.81640625" customWidth="1"/>
+    <col min="1295" max="1295" width="7.81640625" customWidth="1"/>
+    <col min="1296" max="1296" width="5.453125" customWidth="1"/>
+    <col min="1297" max="1297" width="6.453125" customWidth="1"/>
+    <col min="1298" max="1298" width="7.81640625" customWidth="1"/>
+    <col min="1299" max="1299" width="3" customWidth="1"/>
+    <col min="1300" max="1300" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1537" max="1540" width="14.453125" customWidth="1"/>
+    <col min="1541" max="1541" width="15.453125" customWidth="1"/>
+    <col min="1542" max="1542" width="14.54296875" customWidth="1"/>
+    <col min="1543" max="1543" width="15.26953125" customWidth="1"/>
+    <col min="1544" max="1545" width="14.453125" customWidth="1"/>
+    <col min="1546" max="1546" width="13.1796875" customWidth="1"/>
+    <col min="1547" max="1549" width="14.453125" customWidth="1"/>
+    <col min="1550" max="1550" width="15.81640625" customWidth="1"/>
+    <col min="1551" max="1551" width="7.81640625" customWidth="1"/>
+    <col min="1552" max="1552" width="5.453125" customWidth="1"/>
+    <col min="1553" max="1553" width="6.453125" customWidth="1"/>
+    <col min="1554" max="1554" width="7.81640625" customWidth="1"/>
+    <col min="1555" max="1555" width="3" customWidth="1"/>
+    <col min="1556" max="1556" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1793" max="1796" width="14.453125" customWidth="1"/>
+    <col min="1797" max="1797" width="15.453125" customWidth="1"/>
+    <col min="1798" max="1798" width="14.54296875" customWidth="1"/>
+    <col min="1799" max="1799" width="15.26953125" customWidth="1"/>
+    <col min="1800" max="1801" width="14.453125" customWidth="1"/>
+    <col min="1802" max="1802" width="13.1796875" customWidth="1"/>
+    <col min="1803" max="1805" width="14.453125" customWidth="1"/>
+    <col min="1806" max="1806" width="15.81640625" customWidth="1"/>
+    <col min="1807" max="1807" width="7.81640625" customWidth="1"/>
+    <col min="1808" max="1808" width="5.453125" customWidth="1"/>
+    <col min="1809" max="1809" width="6.453125" customWidth="1"/>
+    <col min="1810" max="1810" width="7.81640625" customWidth="1"/>
+    <col min="1811" max="1811" width="3" customWidth="1"/>
+    <col min="1812" max="1812" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2049" max="2052" width="14.453125" customWidth="1"/>
+    <col min="2053" max="2053" width="15.453125" customWidth="1"/>
+    <col min="2054" max="2054" width="14.54296875" customWidth="1"/>
+    <col min="2055" max="2055" width="15.26953125" customWidth="1"/>
+    <col min="2056" max="2057" width="14.453125" customWidth="1"/>
+    <col min="2058" max="2058" width="13.1796875" customWidth="1"/>
+    <col min="2059" max="2061" width="14.453125" customWidth="1"/>
+    <col min="2062" max="2062" width="15.81640625" customWidth="1"/>
+    <col min="2063" max="2063" width="7.81640625" customWidth="1"/>
+    <col min="2064" max="2064" width="5.453125" customWidth="1"/>
+    <col min="2065" max="2065" width="6.453125" customWidth="1"/>
+    <col min="2066" max="2066" width="7.81640625" customWidth="1"/>
+    <col min="2067" max="2067" width="3" customWidth="1"/>
+    <col min="2068" max="2068" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2305" max="2308" width="14.453125" customWidth="1"/>
+    <col min="2309" max="2309" width="15.453125" customWidth="1"/>
+    <col min="2310" max="2310" width="14.54296875" customWidth="1"/>
+    <col min="2311" max="2311" width="15.26953125" customWidth="1"/>
+    <col min="2312" max="2313" width="14.453125" customWidth="1"/>
+    <col min="2314" max="2314" width="13.1796875" customWidth="1"/>
+    <col min="2315" max="2317" width="14.453125" customWidth="1"/>
+    <col min="2318" max="2318" width="15.81640625" customWidth="1"/>
+    <col min="2319" max="2319" width="7.81640625" customWidth="1"/>
+    <col min="2320" max="2320" width="5.453125" customWidth="1"/>
+    <col min="2321" max="2321" width="6.453125" customWidth="1"/>
+    <col min="2322" max="2322" width="7.81640625" customWidth="1"/>
+    <col min="2323" max="2323" width="3" customWidth="1"/>
+    <col min="2324" max="2324" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2561" max="2564" width="14.453125" customWidth="1"/>
+    <col min="2565" max="2565" width="15.453125" customWidth="1"/>
+    <col min="2566" max="2566" width="14.54296875" customWidth="1"/>
+    <col min="2567" max="2567" width="15.26953125" customWidth="1"/>
+    <col min="2568" max="2569" width="14.453125" customWidth="1"/>
+    <col min="2570" max="2570" width="13.1796875" customWidth="1"/>
+    <col min="2571" max="2573" width="14.453125" customWidth="1"/>
+    <col min="2574" max="2574" width="15.81640625" customWidth="1"/>
+    <col min="2575" max="2575" width="7.81640625" customWidth="1"/>
+    <col min="2576" max="2576" width="5.453125" customWidth="1"/>
+    <col min="2577" max="2577" width="6.453125" customWidth="1"/>
+    <col min="2578" max="2578" width="7.81640625" customWidth="1"/>
+    <col min="2579" max="2579" width="3" customWidth="1"/>
+    <col min="2580" max="2580" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2817" max="2820" width="14.453125" customWidth="1"/>
+    <col min="2821" max="2821" width="15.453125" customWidth="1"/>
+    <col min="2822" max="2822" width="14.54296875" customWidth="1"/>
+    <col min="2823" max="2823" width="15.26953125" customWidth="1"/>
+    <col min="2824" max="2825" width="14.453125" customWidth="1"/>
+    <col min="2826" max="2826" width="13.1796875" customWidth="1"/>
+    <col min="2827" max="2829" width="14.453125" customWidth="1"/>
+    <col min="2830" max="2830" width="15.81640625" customWidth="1"/>
+    <col min="2831" max="2831" width="7.81640625" customWidth="1"/>
+    <col min="2832" max="2832" width="5.453125" customWidth="1"/>
+    <col min="2833" max="2833" width="6.453125" customWidth="1"/>
+    <col min="2834" max="2834" width="7.81640625" customWidth="1"/>
+    <col min="2835" max="2835" width="3" customWidth="1"/>
+    <col min="2836" max="2836" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3073" max="3076" width="14.453125" customWidth="1"/>
+    <col min="3077" max="3077" width="15.453125" customWidth="1"/>
+    <col min="3078" max="3078" width="14.54296875" customWidth="1"/>
+    <col min="3079" max="3079" width="15.26953125" customWidth="1"/>
+    <col min="3080" max="3081" width="14.453125" customWidth="1"/>
+    <col min="3082" max="3082" width="13.1796875" customWidth="1"/>
+    <col min="3083" max="3085" width="14.453125" customWidth="1"/>
+    <col min="3086" max="3086" width="15.81640625" customWidth="1"/>
+    <col min="3087" max="3087" width="7.81640625" customWidth="1"/>
+    <col min="3088" max="3088" width="5.453125" customWidth="1"/>
+    <col min="3089" max="3089" width="6.453125" customWidth="1"/>
+    <col min="3090" max="3090" width="7.81640625" customWidth="1"/>
+    <col min="3091" max="3091" width="3" customWidth="1"/>
+    <col min="3092" max="3092" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3329" max="3332" width="14.453125" customWidth="1"/>
+    <col min="3333" max="3333" width="15.453125" customWidth="1"/>
+    <col min="3334" max="3334" width="14.54296875" customWidth="1"/>
+    <col min="3335" max="3335" width="15.26953125" customWidth="1"/>
+    <col min="3336" max="3337" width="14.453125" customWidth="1"/>
+    <col min="3338" max="3338" width="13.1796875" customWidth="1"/>
+    <col min="3339" max="3341" width="14.453125" customWidth="1"/>
+    <col min="3342" max="3342" width="15.81640625" customWidth="1"/>
+    <col min="3343" max="3343" width="7.81640625" customWidth="1"/>
+    <col min="3344" max="3344" width="5.453125" customWidth="1"/>
+    <col min="3345" max="3345" width="6.453125" customWidth="1"/>
+    <col min="3346" max="3346" width="7.81640625" customWidth="1"/>
+    <col min="3347" max="3347" width="3" customWidth="1"/>
+    <col min="3348" max="3348" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3585" max="3588" width="14.453125" customWidth="1"/>
+    <col min="3589" max="3589" width="15.453125" customWidth="1"/>
+    <col min="3590" max="3590" width="14.54296875" customWidth="1"/>
+    <col min="3591" max="3591" width="15.26953125" customWidth="1"/>
+    <col min="3592" max="3593" width="14.453125" customWidth="1"/>
+    <col min="3594" max="3594" width="13.1796875" customWidth="1"/>
+    <col min="3595" max="3597" width="14.453125" customWidth="1"/>
+    <col min="3598" max="3598" width="15.81640625" customWidth="1"/>
+    <col min="3599" max="3599" width="7.81640625" customWidth="1"/>
+    <col min="3600" max="3600" width="5.453125" customWidth="1"/>
+    <col min="3601" max="3601" width="6.453125" customWidth="1"/>
+    <col min="3602" max="3602" width="7.81640625" customWidth="1"/>
+    <col min="3603" max="3603" width="3" customWidth="1"/>
+    <col min="3604" max="3604" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3841" max="3844" width="14.453125" customWidth="1"/>
+    <col min="3845" max="3845" width="15.453125" customWidth="1"/>
+    <col min="3846" max="3846" width="14.54296875" customWidth="1"/>
+    <col min="3847" max="3847" width="15.26953125" customWidth="1"/>
+    <col min="3848" max="3849" width="14.453125" customWidth="1"/>
+    <col min="3850" max="3850" width="13.1796875" customWidth="1"/>
+    <col min="3851" max="3853" width="14.453125" customWidth="1"/>
+    <col min="3854" max="3854" width="15.81640625" customWidth="1"/>
+    <col min="3855" max="3855" width="7.81640625" customWidth="1"/>
+    <col min="3856" max="3856" width="5.453125" customWidth="1"/>
+    <col min="3857" max="3857" width="6.453125" customWidth="1"/>
+    <col min="3858" max="3858" width="7.81640625" customWidth="1"/>
+    <col min="3859" max="3859" width="3" customWidth="1"/>
+    <col min="3860" max="3860" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4097" max="4100" width="14.453125" customWidth="1"/>
+    <col min="4101" max="4101" width="15.453125" customWidth="1"/>
+    <col min="4102" max="4102" width="14.54296875" customWidth="1"/>
+    <col min="4103" max="4103" width="15.26953125" customWidth="1"/>
+    <col min="4104" max="4105" width="14.453125" customWidth="1"/>
+    <col min="4106" max="4106" width="13.1796875" customWidth="1"/>
+    <col min="4107" max="4109" width="14.453125" customWidth="1"/>
+    <col min="4110" max="4110" width="15.81640625" customWidth="1"/>
+    <col min="4111" max="4111" width="7.81640625" customWidth="1"/>
+    <col min="4112" max="4112" width="5.453125" customWidth="1"/>
+    <col min="4113" max="4113" width="6.453125" customWidth="1"/>
+    <col min="4114" max="4114" width="7.81640625" customWidth="1"/>
+    <col min="4115" max="4115" width="3" customWidth="1"/>
+    <col min="4116" max="4116" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4353" max="4356" width="14.453125" customWidth="1"/>
+    <col min="4357" max="4357" width="15.453125" customWidth="1"/>
+    <col min="4358" max="4358" width="14.54296875" customWidth="1"/>
+    <col min="4359" max="4359" width="15.26953125" customWidth="1"/>
+    <col min="4360" max="4361" width="14.453125" customWidth="1"/>
+    <col min="4362" max="4362" width="13.1796875" customWidth="1"/>
+    <col min="4363" max="4365" width="14.453125" customWidth="1"/>
+    <col min="4366" max="4366" width="15.81640625" customWidth="1"/>
+    <col min="4367" max="4367" width="7.81640625" customWidth="1"/>
+    <col min="4368" max="4368" width="5.453125" customWidth="1"/>
+    <col min="4369" max="4369" width="6.453125" customWidth="1"/>
+    <col min="4370" max="4370" width="7.81640625" customWidth="1"/>
+    <col min="4371" max="4371" width="3" customWidth="1"/>
+    <col min="4372" max="4372" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4609" max="4612" width="14.453125" customWidth="1"/>
+    <col min="4613" max="4613" width="15.453125" customWidth="1"/>
+    <col min="4614" max="4614" width="14.54296875" customWidth="1"/>
+    <col min="4615" max="4615" width="15.26953125" customWidth="1"/>
+    <col min="4616" max="4617" width="14.453125" customWidth="1"/>
+    <col min="4618" max="4618" width="13.1796875" customWidth="1"/>
+    <col min="4619" max="4621" width="14.453125" customWidth="1"/>
+    <col min="4622" max="4622" width="15.81640625" customWidth="1"/>
+    <col min="4623" max="4623" width="7.81640625" customWidth="1"/>
+    <col min="4624" max="4624" width="5.453125" customWidth="1"/>
+    <col min="4625" max="4625" width="6.453125" customWidth="1"/>
+    <col min="4626" max="4626" width="7.81640625" customWidth="1"/>
+    <col min="4627" max="4627" width="3" customWidth="1"/>
+    <col min="4628" max="4628" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4865" max="4868" width="14.453125" customWidth="1"/>
+    <col min="4869" max="4869" width="15.453125" customWidth="1"/>
+    <col min="4870" max="4870" width="14.54296875" customWidth="1"/>
+    <col min="4871" max="4871" width="15.26953125" customWidth="1"/>
+    <col min="4872" max="4873" width="14.453125" customWidth="1"/>
+    <col min="4874" max="4874" width="13.1796875" customWidth="1"/>
+    <col min="4875" max="4877" width="14.453125" customWidth="1"/>
+    <col min="4878" max="4878" width="15.81640625" customWidth="1"/>
+    <col min="4879" max="4879" width="7.81640625" customWidth="1"/>
+    <col min="4880" max="4880" width="5.453125" customWidth="1"/>
+    <col min="4881" max="4881" width="6.453125" customWidth="1"/>
+    <col min="4882" max="4882" width="7.81640625" customWidth="1"/>
+    <col min="4883" max="4883" width="3" customWidth="1"/>
+    <col min="4884" max="4884" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5121" max="5124" width="14.453125" customWidth="1"/>
+    <col min="5125" max="5125" width="15.453125" customWidth="1"/>
+    <col min="5126" max="5126" width="14.54296875" customWidth="1"/>
+    <col min="5127" max="5127" width="15.26953125" customWidth="1"/>
+    <col min="5128" max="5129" width="14.453125" customWidth="1"/>
+    <col min="5130" max="5130" width="13.1796875" customWidth="1"/>
+    <col min="5131" max="5133" width="14.453125" customWidth="1"/>
+    <col min="5134" max="5134" width="15.81640625" customWidth="1"/>
+    <col min="5135" max="5135" width="7.81640625" customWidth="1"/>
+    <col min="5136" max="5136" width="5.453125" customWidth="1"/>
+    <col min="5137" max="5137" width="6.453125" customWidth="1"/>
+    <col min="5138" max="5138" width="7.81640625" customWidth="1"/>
+    <col min="5139" max="5139" width="3" customWidth="1"/>
+    <col min="5140" max="5140" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5377" max="5380" width="14.453125" customWidth="1"/>
+    <col min="5381" max="5381" width="15.453125" customWidth="1"/>
+    <col min="5382" max="5382" width="14.54296875" customWidth="1"/>
+    <col min="5383" max="5383" width="15.26953125" customWidth="1"/>
+    <col min="5384" max="5385" width="14.453125" customWidth="1"/>
+    <col min="5386" max="5386" width="13.1796875" customWidth="1"/>
+    <col min="5387" max="5389" width="14.453125" customWidth="1"/>
+    <col min="5390" max="5390" width="15.81640625" customWidth="1"/>
+    <col min="5391" max="5391" width="7.81640625" customWidth="1"/>
+    <col min="5392" max="5392" width="5.453125" customWidth="1"/>
+    <col min="5393" max="5393" width="6.453125" customWidth="1"/>
+    <col min="5394" max="5394" width="7.81640625" customWidth="1"/>
+    <col min="5395" max="5395" width="3" customWidth="1"/>
+    <col min="5396" max="5396" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5633" max="5636" width="14.453125" customWidth="1"/>
+    <col min="5637" max="5637" width="15.453125" customWidth="1"/>
+    <col min="5638" max="5638" width="14.54296875" customWidth="1"/>
+    <col min="5639" max="5639" width="15.26953125" customWidth="1"/>
+    <col min="5640" max="5641" width="14.453125" customWidth="1"/>
+    <col min="5642" max="5642" width="13.1796875" customWidth="1"/>
+    <col min="5643" max="5645" width="14.453125" customWidth="1"/>
+    <col min="5646" max="5646" width="15.81640625" customWidth="1"/>
+    <col min="5647" max="5647" width="7.81640625" customWidth="1"/>
+    <col min="5648" max="5648" width="5.453125" customWidth="1"/>
+    <col min="5649" max="5649" width="6.453125" customWidth="1"/>
+    <col min="5650" max="5650" width="7.81640625" customWidth="1"/>
+    <col min="5651" max="5651" width="3" customWidth="1"/>
+    <col min="5652" max="5652" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5889" max="5892" width="14.453125" customWidth="1"/>
+    <col min="5893" max="5893" width="15.453125" customWidth="1"/>
+    <col min="5894" max="5894" width="14.54296875" customWidth="1"/>
+    <col min="5895" max="5895" width="15.26953125" customWidth="1"/>
+    <col min="5896" max="5897" width="14.453125" customWidth="1"/>
+    <col min="5898" max="5898" width="13.1796875" customWidth="1"/>
+    <col min="5899" max="5901" width="14.453125" customWidth="1"/>
+    <col min="5902" max="5902" width="15.81640625" customWidth="1"/>
+    <col min="5903" max="5903" width="7.81640625" customWidth="1"/>
+    <col min="5904" max="5904" width="5.453125" customWidth="1"/>
+    <col min="5905" max="5905" width="6.453125" customWidth="1"/>
+    <col min="5906" max="5906" width="7.81640625" customWidth="1"/>
+    <col min="5907" max="5907" width="3" customWidth="1"/>
+    <col min="5908" max="5908" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6145" max="6148" width="14.453125" customWidth="1"/>
+    <col min="6149" max="6149" width="15.453125" customWidth="1"/>
+    <col min="6150" max="6150" width="14.54296875" customWidth="1"/>
+    <col min="6151" max="6151" width="15.26953125" customWidth="1"/>
+    <col min="6152" max="6153" width="14.453125" customWidth="1"/>
+    <col min="6154" max="6154" width="13.1796875" customWidth="1"/>
+    <col min="6155" max="6157" width="14.453125" customWidth="1"/>
+    <col min="6158" max="6158" width="15.81640625" customWidth="1"/>
+    <col min="6159" max="6159" width="7.81640625" customWidth="1"/>
+    <col min="6160" max="6160" width="5.453125" customWidth="1"/>
+    <col min="6161" max="6161" width="6.453125" customWidth="1"/>
+    <col min="6162" max="6162" width="7.81640625" customWidth="1"/>
+    <col min="6163" max="6163" width="3" customWidth="1"/>
+    <col min="6164" max="6164" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6401" max="6404" width="14.453125" customWidth="1"/>
+    <col min="6405" max="6405" width="15.453125" customWidth="1"/>
+    <col min="6406" max="6406" width="14.54296875" customWidth="1"/>
+    <col min="6407" max="6407" width="15.26953125" customWidth="1"/>
+    <col min="6408" max="6409" width="14.453125" customWidth="1"/>
+    <col min="6410" max="6410" width="13.1796875" customWidth="1"/>
+    <col min="6411" max="6413" width="14.453125" customWidth="1"/>
+    <col min="6414" max="6414" width="15.81640625" customWidth="1"/>
+    <col min="6415" max="6415" width="7.81640625" customWidth="1"/>
+    <col min="6416" max="6416" width="5.453125" customWidth="1"/>
+    <col min="6417" max="6417" width="6.453125" customWidth="1"/>
+    <col min="6418" max="6418" width="7.81640625" customWidth="1"/>
+    <col min="6419" max="6419" width="3" customWidth="1"/>
+    <col min="6420" max="6420" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6657" max="6660" width="14.453125" customWidth="1"/>
+    <col min="6661" max="6661" width="15.453125" customWidth="1"/>
+    <col min="6662" max="6662" width="14.54296875" customWidth="1"/>
+    <col min="6663" max="6663" width="15.26953125" customWidth="1"/>
+    <col min="6664" max="6665" width="14.453125" customWidth="1"/>
+    <col min="6666" max="6666" width="13.1796875" customWidth="1"/>
+    <col min="6667" max="6669" width="14.453125" customWidth="1"/>
+    <col min="6670" max="6670" width="15.81640625" customWidth="1"/>
+    <col min="6671" max="6671" width="7.81640625" customWidth="1"/>
+    <col min="6672" max="6672" width="5.453125" customWidth="1"/>
+    <col min="6673" max="6673" width="6.453125" customWidth="1"/>
+    <col min="6674" max="6674" width="7.81640625" customWidth="1"/>
+    <col min="6675" max="6675" width="3" customWidth="1"/>
+    <col min="6676" max="6676" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6913" max="6916" width="14.453125" customWidth="1"/>
+    <col min="6917" max="6917" width="15.453125" customWidth="1"/>
+    <col min="6918" max="6918" width="14.54296875" customWidth="1"/>
+    <col min="6919" max="6919" width="15.26953125" customWidth="1"/>
+    <col min="6920" max="6921" width="14.453125" customWidth="1"/>
+    <col min="6922" max="6922" width="13.1796875" customWidth="1"/>
+    <col min="6923" max="6925" width="14.453125" customWidth="1"/>
+    <col min="6926" max="6926" width="15.81640625" customWidth="1"/>
+    <col min="6927" max="6927" width="7.81640625" customWidth="1"/>
+    <col min="6928" max="6928" width="5.453125" customWidth="1"/>
+    <col min="6929" max="6929" width="6.453125" customWidth="1"/>
+    <col min="6930" max="6930" width="7.81640625" customWidth="1"/>
+    <col min="6931" max="6931" width="3" customWidth="1"/>
+    <col min="6932" max="6932" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7169" max="7172" width="14.453125" customWidth="1"/>
+    <col min="7173" max="7173" width="15.453125" customWidth="1"/>
+    <col min="7174" max="7174" width="14.54296875" customWidth="1"/>
+    <col min="7175" max="7175" width="15.26953125" customWidth="1"/>
+    <col min="7176" max="7177" width="14.453125" customWidth="1"/>
+    <col min="7178" max="7178" width="13.1796875" customWidth="1"/>
+    <col min="7179" max="7181" width="14.453125" customWidth="1"/>
+    <col min="7182" max="7182" width="15.81640625" customWidth="1"/>
+    <col min="7183" max="7183" width="7.81640625" customWidth="1"/>
+    <col min="7184" max="7184" width="5.453125" customWidth="1"/>
+    <col min="7185" max="7185" width="6.453125" customWidth="1"/>
+    <col min="7186" max="7186" width="7.81640625" customWidth="1"/>
+    <col min="7187" max="7187" width="3" customWidth="1"/>
+    <col min="7188" max="7188" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7425" max="7428" width="14.453125" customWidth="1"/>
+    <col min="7429" max="7429" width="15.453125" customWidth="1"/>
+    <col min="7430" max="7430" width="14.54296875" customWidth="1"/>
+    <col min="7431" max="7431" width="15.26953125" customWidth="1"/>
+    <col min="7432" max="7433" width="14.453125" customWidth="1"/>
+    <col min="7434" max="7434" width="13.1796875" customWidth="1"/>
+    <col min="7435" max="7437" width="14.453125" customWidth="1"/>
+    <col min="7438" max="7438" width="15.81640625" customWidth="1"/>
+    <col min="7439" max="7439" width="7.81640625" customWidth="1"/>
+    <col min="7440" max="7440" width="5.453125" customWidth="1"/>
+    <col min="7441" max="7441" width="6.453125" customWidth="1"/>
+    <col min="7442" max="7442" width="7.81640625" customWidth="1"/>
+    <col min="7443" max="7443" width="3" customWidth="1"/>
+    <col min="7444" max="7444" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7681" max="7684" width="14.453125" customWidth="1"/>
+    <col min="7685" max="7685" width="15.453125" customWidth="1"/>
+    <col min="7686" max="7686" width="14.54296875" customWidth="1"/>
+    <col min="7687" max="7687" width="15.26953125" customWidth="1"/>
+    <col min="7688" max="7689" width="14.453125" customWidth="1"/>
+    <col min="7690" max="7690" width="13.1796875" customWidth="1"/>
+    <col min="7691" max="7693" width="14.453125" customWidth="1"/>
+    <col min="7694" max="7694" width="15.81640625" customWidth="1"/>
+    <col min="7695" max="7695" width="7.81640625" customWidth="1"/>
+    <col min="7696" max="7696" width="5.453125" customWidth="1"/>
+    <col min="7697" max="7697" width="6.453125" customWidth="1"/>
+    <col min="7698" max="7698" width="7.81640625" customWidth="1"/>
+    <col min="7699" max="7699" width="3" customWidth="1"/>
+    <col min="7700" max="7700" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7937" max="7940" width="14.453125" customWidth="1"/>
+    <col min="7941" max="7941" width="15.453125" customWidth="1"/>
+    <col min="7942" max="7942" width="14.54296875" customWidth="1"/>
+    <col min="7943" max="7943" width="15.26953125" customWidth="1"/>
+    <col min="7944" max="7945" width="14.453125" customWidth="1"/>
+    <col min="7946" max="7946" width="13.1796875" customWidth="1"/>
+    <col min="7947" max="7949" width="14.453125" customWidth="1"/>
+    <col min="7950" max="7950" width="15.81640625" customWidth="1"/>
+    <col min="7951" max="7951" width="7.81640625" customWidth="1"/>
+    <col min="7952" max="7952" width="5.453125" customWidth="1"/>
+    <col min="7953" max="7953" width="6.453125" customWidth="1"/>
+    <col min="7954" max="7954" width="7.81640625" customWidth="1"/>
+    <col min="7955" max="7955" width="3" customWidth="1"/>
+    <col min="7956" max="7956" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8193" max="8196" width="14.453125" customWidth="1"/>
+    <col min="8197" max="8197" width="15.453125" customWidth="1"/>
+    <col min="8198" max="8198" width="14.54296875" customWidth="1"/>
+    <col min="8199" max="8199" width="15.26953125" customWidth="1"/>
+    <col min="8200" max="8201" width="14.453125" customWidth="1"/>
+    <col min="8202" max="8202" width="13.1796875" customWidth="1"/>
+    <col min="8203" max="8205" width="14.453125" customWidth="1"/>
+    <col min="8206" max="8206" width="15.81640625" customWidth="1"/>
+    <col min="8207" max="8207" width="7.81640625" customWidth="1"/>
+    <col min="8208" max="8208" width="5.453125" customWidth="1"/>
+    <col min="8209" max="8209" width="6.453125" customWidth="1"/>
+    <col min="8210" max="8210" width="7.81640625" customWidth="1"/>
+    <col min="8211" max="8211" width="3" customWidth="1"/>
+    <col min="8212" max="8212" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8449" max="8452" width="14.453125" customWidth="1"/>
+    <col min="8453" max="8453" width="15.453125" customWidth="1"/>
+    <col min="8454" max="8454" width="14.54296875" customWidth="1"/>
+    <col min="8455" max="8455" width="15.26953125" customWidth="1"/>
+    <col min="8456" max="8457" width="14.453125" customWidth="1"/>
+    <col min="8458" max="8458" width="13.1796875" customWidth="1"/>
+    <col min="8459" max="8461" width="14.453125" customWidth="1"/>
+    <col min="8462" max="8462" width="15.81640625" customWidth="1"/>
+    <col min="8463" max="8463" width="7.81640625" customWidth="1"/>
+    <col min="8464" max="8464" width="5.453125" customWidth="1"/>
+    <col min="8465" max="8465" width="6.453125" customWidth="1"/>
+    <col min="8466" max="8466" width="7.81640625" customWidth="1"/>
+    <col min="8467" max="8467" width="3" customWidth="1"/>
+    <col min="8468" max="8468" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8705" max="8708" width="14.453125" customWidth="1"/>
+    <col min="8709" max="8709" width="15.453125" customWidth="1"/>
+    <col min="8710" max="8710" width="14.54296875" customWidth="1"/>
+    <col min="8711" max="8711" width="15.26953125" customWidth="1"/>
+    <col min="8712" max="8713" width="14.453125" customWidth="1"/>
+    <col min="8714" max="8714" width="13.1796875" customWidth="1"/>
+    <col min="8715" max="8717" width="14.453125" customWidth="1"/>
+    <col min="8718" max="8718" width="15.81640625" customWidth="1"/>
+    <col min="8719" max="8719" width="7.81640625" customWidth="1"/>
+    <col min="8720" max="8720" width="5.453125" customWidth="1"/>
+    <col min="8721" max="8721" width="6.453125" customWidth="1"/>
+    <col min="8722" max="8722" width="7.81640625" customWidth="1"/>
+    <col min="8723" max="8723" width="3" customWidth="1"/>
+    <col min="8724" max="8724" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8961" max="8964" width="14.453125" customWidth="1"/>
+    <col min="8965" max="8965" width="15.453125" customWidth="1"/>
+    <col min="8966" max="8966" width="14.54296875" customWidth="1"/>
+    <col min="8967" max="8967" width="15.26953125" customWidth="1"/>
+    <col min="8968" max="8969" width="14.453125" customWidth="1"/>
+    <col min="8970" max="8970" width="13.1796875" customWidth="1"/>
+    <col min="8971" max="8973" width="14.453125" customWidth="1"/>
+    <col min="8974" max="8974" width="15.81640625" customWidth="1"/>
+    <col min="8975" max="8975" width="7.81640625" customWidth="1"/>
+    <col min="8976" max="8976" width="5.453125" customWidth="1"/>
+    <col min="8977" max="8977" width="6.453125" customWidth="1"/>
+    <col min="8978" max="8978" width="7.81640625" customWidth="1"/>
+    <col min="8979" max="8979" width="3" customWidth="1"/>
+    <col min="8980" max="8980" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9217" max="9220" width="14.453125" customWidth="1"/>
+    <col min="9221" max="9221" width="15.453125" customWidth="1"/>
+    <col min="9222" max="9222" width="14.54296875" customWidth="1"/>
+    <col min="9223" max="9223" width="15.26953125" customWidth="1"/>
+    <col min="9224" max="9225" width="14.453125" customWidth="1"/>
+    <col min="9226" max="9226" width="13.1796875" customWidth="1"/>
+    <col min="9227" max="9229" width="14.453125" customWidth="1"/>
+    <col min="9230" max="9230" width="15.81640625" customWidth="1"/>
+    <col min="9231" max="9231" width="7.81640625" customWidth="1"/>
+    <col min="9232" max="9232" width="5.453125" customWidth="1"/>
+    <col min="9233" max="9233" width="6.453125" customWidth="1"/>
+    <col min="9234" max="9234" width="7.81640625" customWidth="1"/>
+    <col min="9235" max="9235" width="3" customWidth="1"/>
+    <col min="9236" max="9236" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9473" max="9476" width="14.453125" customWidth="1"/>
+    <col min="9477" max="9477" width="15.453125" customWidth="1"/>
+    <col min="9478" max="9478" width="14.54296875" customWidth="1"/>
+    <col min="9479" max="9479" width="15.26953125" customWidth="1"/>
+    <col min="9480" max="9481" width="14.453125" customWidth="1"/>
+    <col min="9482" max="9482" width="13.1796875" customWidth="1"/>
+    <col min="9483" max="9485" width="14.453125" customWidth="1"/>
+    <col min="9486" max="9486" width="15.81640625" customWidth="1"/>
+    <col min="9487" max="9487" width="7.81640625" customWidth="1"/>
+    <col min="9488" max="9488" width="5.453125" customWidth="1"/>
+    <col min="9489" max="9489" width="6.453125" customWidth="1"/>
+    <col min="9490" max="9490" width="7.81640625" customWidth="1"/>
+    <col min="9491" max="9491" width="3" customWidth="1"/>
+    <col min="9492" max="9492" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9729" max="9732" width="14.453125" customWidth="1"/>
+    <col min="9733" max="9733" width="15.453125" customWidth="1"/>
+    <col min="9734" max="9734" width="14.54296875" customWidth="1"/>
+    <col min="9735" max="9735" width="15.26953125" customWidth="1"/>
+    <col min="9736" max="9737" width="14.453125" customWidth="1"/>
+    <col min="9738" max="9738" width="13.1796875" customWidth="1"/>
+    <col min="9739" max="9741" width="14.453125" customWidth="1"/>
+    <col min="9742" max="9742" width="15.81640625" customWidth="1"/>
+    <col min="9743" max="9743" width="7.81640625" customWidth="1"/>
+    <col min="9744" max="9744" width="5.453125" customWidth="1"/>
+    <col min="9745" max="9745" width="6.453125" customWidth="1"/>
+    <col min="9746" max="9746" width="7.81640625" customWidth="1"/>
+    <col min="9747" max="9747" width="3" customWidth="1"/>
+    <col min="9748" max="9748" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9985" max="9988" width="14.453125" customWidth="1"/>
+    <col min="9989" max="9989" width="15.453125" customWidth="1"/>
+    <col min="9990" max="9990" width="14.54296875" customWidth="1"/>
+    <col min="9991" max="9991" width="15.26953125" customWidth="1"/>
+    <col min="9992" max="9993" width="14.453125" customWidth="1"/>
+    <col min="9994" max="9994" width="13.1796875" customWidth="1"/>
+    <col min="9995" max="9997" width="14.453125" customWidth="1"/>
+    <col min="9998" max="9998" width="15.81640625" customWidth="1"/>
+    <col min="9999" max="9999" width="7.81640625" customWidth="1"/>
+    <col min="10000" max="10000" width="5.453125" customWidth="1"/>
+    <col min="10001" max="10001" width="6.453125" customWidth="1"/>
+    <col min="10002" max="10002" width="7.81640625" customWidth="1"/>
+    <col min="10003" max="10003" width="3" customWidth="1"/>
+    <col min="10004" max="10004" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10241" max="10244" width="14.453125" customWidth="1"/>
+    <col min="10245" max="10245" width="15.453125" customWidth="1"/>
+    <col min="10246" max="10246" width="14.54296875" customWidth="1"/>
+    <col min="10247" max="10247" width="15.26953125" customWidth="1"/>
+    <col min="10248" max="10249" width="14.453125" customWidth="1"/>
+    <col min="10250" max="10250" width="13.1796875" customWidth="1"/>
+    <col min="10251" max="10253" width="14.453125" customWidth="1"/>
+    <col min="10254" max="10254" width="15.81640625" customWidth="1"/>
+    <col min="10255" max="10255" width="7.81640625" customWidth="1"/>
+    <col min="10256" max="10256" width="5.453125" customWidth="1"/>
+    <col min="10257" max="10257" width="6.453125" customWidth="1"/>
+    <col min="10258" max="10258" width="7.81640625" customWidth="1"/>
+    <col min="10259" max="10259" width="3" customWidth="1"/>
+    <col min="10260" max="10260" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10497" max="10500" width="14.453125" customWidth="1"/>
+    <col min="10501" max="10501" width="15.453125" customWidth="1"/>
+    <col min="10502" max="10502" width="14.54296875" customWidth="1"/>
+    <col min="10503" max="10503" width="15.26953125" customWidth="1"/>
+    <col min="10504" max="10505" width="14.453125" customWidth="1"/>
+    <col min="10506" max="10506" width="13.1796875" customWidth="1"/>
+    <col min="10507" max="10509" width="14.453125" customWidth="1"/>
+    <col min="10510" max="10510" width="15.81640625" customWidth="1"/>
+    <col min="10511" max="10511" width="7.81640625" customWidth="1"/>
+    <col min="10512" max="10512" width="5.453125" customWidth="1"/>
+    <col min="10513" max="10513" width="6.453125" customWidth="1"/>
+    <col min="10514" max="10514" width="7.81640625" customWidth="1"/>
+    <col min="10515" max="10515" width="3" customWidth="1"/>
+    <col min="10516" max="10516" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10753" max="10756" width="14.453125" customWidth="1"/>
+    <col min="10757" max="10757" width="15.453125" customWidth="1"/>
+    <col min="10758" max="10758" width="14.54296875" customWidth="1"/>
+    <col min="10759" max="10759" width="15.26953125" customWidth="1"/>
+    <col min="10760" max="10761" width="14.453125" customWidth="1"/>
+    <col min="10762" max="10762" width="13.1796875" customWidth="1"/>
+    <col min="10763" max="10765" width="14.453125" customWidth="1"/>
+    <col min="10766" max="10766" width="15.81640625" customWidth="1"/>
+    <col min="10767" max="10767" width="7.81640625" customWidth="1"/>
+    <col min="10768" max="10768" width="5.453125" customWidth="1"/>
+    <col min="10769" max="10769" width="6.453125" customWidth="1"/>
+    <col min="10770" max="10770" width="7.81640625" customWidth="1"/>
+    <col min="10771" max="10771" width="3" customWidth="1"/>
+    <col min="10772" max="10772" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11009" max="11012" width="14.453125" customWidth="1"/>
+    <col min="11013" max="11013" width="15.453125" customWidth="1"/>
+    <col min="11014" max="11014" width="14.54296875" customWidth="1"/>
+    <col min="11015" max="11015" width="15.26953125" customWidth="1"/>
+    <col min="11016" max="11017" width="14.453125" customWidth="1"/>
+    <col min="11018" max="11018" width="13.1796875" customWidth="1"/>
+    <col min="11019" max="11021" width="14.453125" customWidth="1"/>
+    <col min="11022" max="11022" width="15.81640625" customWidth="1"/>
+    <col min="11023" max="11023" width="7.81640625" customWidth="1"/>
+    <col min="11024" max="11024" width="5.453125" customWidth="1"/>
+    <col min="11025" max="11025" width="6.453125" customWidth="1"/>
+    <col min="11026" max="11026" width="7.81640625" customWidth="1"/>
+    <col min="11027" max="11027" width="3" customWidth="1"/>
+    <col min="11028" max="11028" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11265" max="11268" width="14.453125" customWidth="1"/>
+    <col min="11269" max="11269" width="15.453125" customWidth="1"/>
+    <col min="11270" max="11270" width="14.54296875" customWidth="1"/>
+    <col min="11271" max="11271" width="15.26953125" customWidth="1"/>
+    <col min="11272" max="11273" width="14.453125" customWidth="1"/>
+    <col min="11274" max="11274" width="13.1796875" customWidth="1"/>
+    <col min="11275" max="11277" width="14.453125" customWidth="1"/>
+    <col min="11278" max="11278" width="15.81640625" customWidth="1"/>
+    <col min="11279" max="11279" width="7.81640625" customWidth="1"/>
+    <col min="11280" max="11280" width="5.453125" customWidth="1"/>
+    <col min="11281" max="11281" width="6.453125" customWidth="1"/>
+    <col min="11282" max="11282" width="7.81640625" customWidth="1"/>
+    <col min="11283" max="11283" width="3" customWidth="1"/>
+    <col min="11284" max="11284" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11521" max="11524" width="14.453125" customWidth="1"/>
+    <col min="11525" max="11525" width="15.453125" customWidth="1"/>
+    <col min="11526" max="11526" width="14.54296875" customWidth="1"/>
+    <col min="11527" max="11527" width="15.26953125" customWidth="1"/>
+    <col min="11528" max="11529" width="14.453125" customWidth="1"/>
+    <col min="11530" max="11530" width="13.1796875" customWidth="1"/>
+    <col min="11531" max="11533" width="14.453125" customWidth="1"/>
+    <col min="11534" max="11534" width="15.81640625" customWidth="1"/>
+    <col min="11535" max="11535" width="7.81640625" customWidth="1"/>
+    <col min="11536" max="11536" width="5.453125" customWidth="1"/>
+    <col min="11537" max="11537" width="6.453125" customWidth="1"/>
+    <col min="11538" max="11538" width="7.81640625" customWidth="1"/>
+    <col min="11539" max="11539" width="3" customWidth="1"/>
+    <col min="11540" max="11540" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11777" max="11780" width="14.453125" customWidth="1"/>
+    <col min="11781" max="11781" width="15.453125" customWidth="1"/>
+    <col min="11782" max="11782" width="14.54296875" customWidth="1"/>
+    <col min="11783" max="11783" width="15.26953125" customWidth="1"/>
+    <col min="11784" max="11785" width="14.453125" customWidth="1"/>
+    <col min="11786" max="11786" width="13.1796875" customWidth="1"/>
+    <col min="11787" max="11789" width="14.453125" customWidth="1"/>
+    <col min="11790" max="11790" width="15.81640625" customWidth="1"/>
+    <col min="11791" max="11791" width="7.81640625" customWidth="1"/>
+    <col min="11792" max="11792" width="5.453125" customWidth="1"/>
+    <col min="11793" max="11793" width="6.453125" customWidth="1"/>
+    <col min="11794" max="11794" width="7.81640625" customWidth="1"/>
+    <col min="11795" max="11795" width="3" customWidth="1"/>
+    <col min="11796" max="11796" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12033" max="12036" width="14.453125" customWidth="1"/>
+    <col min="12037" max="12037" width="15.453125" customWidth="1"/>
+    <col min="12038" max="12038" width="14.54296875" customWidth="1"/>
+    <col min="12039" max="12039" width="15.26953125" customWidth="1"/>
+    <col min="12040" max="12041" width="14.453125" customWidth="1"/>
+    <col min="12042" max="12042" width="13.1796875" customWidth="1"/>
+    <col min="12043" max="12045" width="14.453125" customWidth="1"/>
+    <col min="12046" max="12046" width="15.81640625" customWidth="1"/>
+    <col min="12047" max="12047" width="7.81640625" customWidth="1"/>
+    <col min="12048" max="12048" width="5.453125" customWidth="1"/>
+    <col min="12049" max="12049" width="6.453125" customWidth="1"/>
+    <col min="12050" max="12050" width="7.81640625" customWidth="1"/>
+    <col min="12051" max="12051" width="3" customWidth="1"/>
+    <col min="12052" max="12052" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12289" max="12292" width="14.453125" customWidth="1"/>
+    <col min="12293" max="12293" width="15.453125" customWidth="1"/>
+    <col min="12294" max="12294" width="14.54296875" customWidth="1"/>
+    <col min="12295" max="12295" width="15.26953125" customWidth="1"/>
+    <col min="12296" max="12297" width="14.453125" customWidth="1"/>
+    <col min="12298" max="12298" width="13.1796875" customWidth="1"/>
+    <col min="12299" max="12301" width="14.453125" customWidth="1"/>
+    <col min="12302" max="12302" width="15.81640625" customWidth="1"/>
+    <col min="12303" max="12303" width="7.81640625" customWidth="1"/>
+    <col min="12304" max="12304" width="5.453125" customWidth="1"/>
+    <col min="12305" max="12305" width="6.453125" customWidth="1"/>
+    <col min="12306" max="12306" width="7.81640625" customWidth="1"/>
+    <col min="12307" max="12307" width="3" customWidth="1"/>
+    <col min="12308" max="12308" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12545" max="12548" width="14.453125" customWidth="1"/>
+    <col min="12549" max="12549" width="15.453125" customWidth="1"/>
+    <col min="12550" max="12550" width="14.54296875" customWidth="1"/>
+    <col min="12551" max="12551" width="15.26953125" customWidth="1"/>
+    <col min="12552" max="12553" width="14.453125" customWidth="1"/>
+    <col min="12554" max="12554" width="13.1796875" customWidth="1"/>
+    <col min="12555" max="12557" width="14.453125" customWidth="1"/>
+    <col min="12558" max="12558" width="15.81640625" customWidth="1"/>
+    <col min="12559" max="12559" width="7.81640625" customWidth="1"/>
+    <col min="12560" max="12560" width="5.453125" customWidth="1"/>
+    <col min="12561" max="12561" width="6.453125" customWidth="1"/>
+    <col min="12562" max="12562" width="7.81640625" customWidth="1"/>
+    <col min="12563" max="12563" width="3" customWidth="1"/>
+    <col min="12564" max="12564" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12801" max="12804" width="14.453125" customWidth="1"/>
+    <col min="12805" max="12805" width="15.453125" customWidth="1"/>
+    <col min="12806" max="12806" width="14.54296875" customWidth="1"/>
+    <col min="12807" max="12807" width="15.26953125" customWidth="1"/>
+    <col min="12808" max="12809" width="14.453125" customWidth="1"/>
+    <col min="12810" max="12810" width="13.1796875" customWidth="1"/>
+    <col min="12811" max="12813" width="14.453125" customWidth="1"/>
+    <col min="12814" max="12814" width="15.81640625" customWidth="1"/>
+    <col min="12815" max="12815" width="7.81640625" customWidth="1"/>
+    <col min="12816" max="12816" width="5.453125" customWidth="1"/>
+    <col min="12817" max="12817" width="6.453125" customWidth="1"/>
+    <col min="12818" max="12818" width="7.81640625" customWidth="1"/>
+    <col min="12819" max="12819" width="3" customWidth="1"/>
+    <col min="12820" max="12820" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13057" max="13060" width="14.453125" customWidth="1"/>
+    <col min="13061" max="13061" width="15.453125" customWidth="1"/>
+    <col min="13062" max="13062" width="14.54296875" customWidth="1"/>
+    <col min="13063" max="13063" width="15.26953125" customWidth="1"/>
+    <col min="13064" max="13065" width="14.453125" customWidth="1"/>
+    <col min="13066" max="13066" width="13.1796875" customWidth="1"/>
+    <col min="13067" max="13069" width="14.453125" customWidth="1"/>
+    <col min="13070" max="13070" width="15.81640625" customWidth="1"/>
+    <col min="13071" max="13071" width="7.81640625" customWidth="1"/>
+    <col min="13072" max="13072" width="5.453125" customWidth="1"/>
+    <col min="13073" max="13073" width="6.453125" customWidth="1"/>
+    <col min="13074" max="13074" width="7.81640625" customWidth="1"/>
+    <col min="13075" max="13075" width="3" customWidth="1"/>
+    <col min="13076" max="13076" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13313" max="13316" width="14.453125" customWidth="1"/>
+    <col min="13317" max="13317" width="15.453125" customWidth="1"/>
+    <col min="13318" max="13318" width="14.54296875" customWidth="1"/>
+    <col min="13319" max="13319" width="15.26953125" customWidth="1"/>
+    <col min="13320" max="13321" width="14.453125" customWidth="1"/>
+    <col min="13322" max="13322" width="13.1796875" customWidth="1"/>
+    <col min="13323" max="13325" width="14.453125" customWidth="1"/>
+    <col min="13326" max="13326" width="15.81640625" customWidth="1"/>
+    <col min="13327" max="13327" width="7.81640625" customWidth="1"/>
+    <col min="13328" max="13328" width="5.453125" customWidth="1"/>
+    <col min="13329" max="13329" width="6.453125" customWidth="1"/>
+    <col min="13330" max="13330" width="7.81640625" customWidth="1"/>
+    <col min="13331" max="13331" width="3" customWidth="1"/>
+    <col min="13332" max="13332" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13569" max="13572" width="14.453125" customWidth="1"/>
+    <col min="13573" max="13573" width="15.453125" customWidth="1"/>
+    <col min="13574" max="13574" width="14.54296875" customWidth="1"/>
+    <col min="13575" max="13575" width="15.26953125" customWidth="1"/>
+    <col min="13576" max="13577" width="14.453125" customWidth="1"/>
+    <col min="13578" max="13578" width="13.1796875" customWidth="1"/>
+    <col min="13579" max="13581" width="14.453125" customWidth="1"/>
+    <col min="13582" max="13582" width="15.81640625" customWidth="1"/>
+    <col min="13583" max="13583" width="7.81640625" customWidth="1"/>
+    <col min="13584" max="13584" width="5.453125" customWidth="1"/>
+    <col min="13585" max="13585" width="6.453125" customWidth="1"/>
+    <col min="13586" max="13586" width="7.81640625" customWidth="1"/>
+    <col min="13587" max="13587" width="3" customWidth="1"/>
+    <col min="13588" max="13588" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13825" max="13828" width="14.453125" customWidth="1"/>
+    <col min="13829" max="13829" width="15.453125" customWidth="1"/>
+    <col min="13830" max="13830" width="14.54296875" customWidth="1"/>
+    <col min="13831" max="13831" width="15.26953125" customWidth="1"/>
+    <col min="13832" max="13833" width="14.453125" customWidth="1"/>
+    <col min="13834" max="13834" width="13.1796875" customWidth="1"/>
+    <col min="13835" max="13837" width="14.453125" customWidth="1"/>
+    <col min="13838" max="13838" width="15.81640625" customWidth="1"/>
+    <col min="13839" max="13839" width="7.81640625" customWidth="1"/>
+    <col min="13840" max="13840" width="5.453125" customWidth="1"/>
+    <col min="13841" max="13841" width="6.453125" customWidth="1"/>
+    <col min="13842" max="13842" width="7.81640625" customWidth="1"/>
+    <col min="13843" max="13843" width="3" customWidth="1"/>
+    <col min="13844" max="13844" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14081" max="14084" width="14.453125" customWidth="1"/>
+    <col min="14085" max="14085" width="15.453125" customWidth="1"/>
+    <col min="14086" max="14086" width="14.54296875" customWidth="1"/>
+    <col min="14087" max="14087" width="15.26953125" customWidth="1"/>
+    <col min="14088" max="14089" width="14.453125" customWidth="1"/>
+    <col min="14090" max="14090" width="13.1796875" customWidth="1"/>
+    <col min="14091" max="14093" width="14.453125" customWidth="1"/>
+    <col min="14094" max="14094" width="15.81640625" customWidth="1"/>
+    <col min="14095" max="14095" width="7.81640625" customWidth="1"/>
+    <col min="14096" max="14096" width="5.453125" customWidth="1"/>
+    <col min="14097" max="14097" width="6.453125" customWidth="1"/>
+    <col min="14098" max="14098" width="7.81640625" customWidth="1"/>
+    <col min="14099" max="14099" width="3" customWidth="1"/>
+    <col min="14100" max="14100" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14337" max="14340" width="14.453125" customWidth="1"/>
+    <col min="14341" max="14341" width="15.453125" customWidth="1"/>
+    <col min="14342" max="14342" width="14.54296875" customWidth="1"/>
+    <col min="14343" max="14343" width="15.26953125" customWidth="1"/>
+    <col min="14344" max="14345" width="14.453125" customWidth="1"/>
+    <col min="14346" max="14346" width="13.1796875" customWidth="1"/>
+    <col min="14347" max="14349" width="14.453125" customWidth="1"/>
+    <col min="14350" max="14350" width="15.81640625" customWidth="1"/>
+    <col min="14351" max="14351" width="7.81640625" customWidth="1"/>
+    <col min="14352" max="14352" width="5.453125" customWidth="1"/>
+    <col min="14353" max="14353" width="6.453125" customWidth="1"/>
+    <col min="14354" max="14354" width="7.81640625" customWidth="1"/>
+    <col min="14355" max="14355" width="3" customWidth="1"/>
+    <col min="14356" max="14356" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14593" max="14596" width="14.453125" customWidth="1"/>
+    <col min="14597" max="14597" width="15.453125" customWidth="1"/>
+    <col min="14598" max="14598" width="14.54296875" customWidth="1"/>
+    <col min="14599" max="14599" width="15.26953125" customWidth="1"/>
+    <col min="14600" max="14601" width="14.453125" customWidth="1"/>
+    <col min="14602" max="14602" width="13.1796875" customWidth="1"/>
+    <col min="14603" max="14605" width="14.453125" customWidth="1"/>
+    <col min="14606" max="14606" width="15.81640625" customWidth="1"/>
+    <col min="14607" max="14607" width="7.81640625" customWidth="1"/>
+    <col min="14608" max="14608" width="5.453125" customWidth="1"/>
+    <col min="14609" max="14609" width="6.453125" customWidth="1"/>
+    <col min="14610" max="14610" width="7.81640625" customWidth="1"/>
+    <col min="14611" max="14611" width="3" customWidth="1"/>
+    <col min="14612" max="14612" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14849" max="14852" width="14.453125" customWidth="1"/>
+    <col min="14853" max="14853" width="15.453125" customWidth="1"/>
+    <col min="14854" max="14854" width="14.54296875" customWidth="1"/>
+    <col min="14855" max="14855" width="15.26953125" customWidth="1"/>
+    <col min="14856" max="14857" width="14.453125" customWidth="1"/>
+    <col min="14858" max="14858" width="13.1796875" customWidth="1"/>
+    <col min="14859" max="14861" width="14.453125" customWidth="1"/>
+    <col min="14862" max="14862" width="15.81640625" customWidth="1"/>
+    <col min="14863" max="14863" width="7.81640625" customWidth="1"/>
+    <col min="14864" max="14864" width="5.453125" customWidth="1"/>
+    <col min="14865" max="14865" width="6.453125" customWidth="1"/>
+    <col min="14866" max="14866" width="7.81640625" customWidth="1"/>
+    <col min="14867" max="14867" width="3" customWidth="1"/>
+    <col min="14868" max="14868" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15105" max="15108" width="14.453125" customWidth="1"/>
+    <col min="15109" max="15109" width="15.453125" customWidth="1"/>
+    <col min="15110" max="15110" width="14.54296875" customWidth="1"/>
+    <col min="15111" max="15111" width="15.26953125" customWidth="1"/>
+    <col min="15112" max="15113" width="14.453125" customWidth="1"/>
+    <col min="15114" max="15114" width="13.1796875" customWidth="1"/>
+    <col min="15115" max="15117" width="14.453125" customWidth="1"/>
+    <col min="15118" max="15118" width="15.81640625" customWidth="1"/>
+    <col min="15119" max="15119" width="7.81640625" customWidth="1"/>
+    <col min="15120" max="15120" width="5.453125" customWidth="1"/>
+    <col min="15121" max="15121" width="6.453125" customWidth="1"/>
+    <col min="15122" max="15122" width="7.81640625" customWidth="1"/>
+    <col min="15123" max="15123" width="3" customWidth="1"/>
+    <col min="15124" max="15124" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15361" max="15364" width="14.453125" customWidth="1"/>
+    <col min="15365" max="15365" width="15.453125" customWidth="1"/>
+    <col min="15366" max="15366" width="14.54296875" customWidth="1"/>
+    <col min="15367" max="15367" width="15.26953125" customWidth="1"/>
+    <col min="15368" max="15369" width="14.453125" customWidth="1"/>
+    <col min="15370" max="15370" width="13.1796875" customWidth="1"/>
+    <col min="15371" max="15373" width="14.453125" customWidth="1"/>
+    <col min="15374" max="15374" width="15.81640625" customWidth="1"/>
+    <col min="15375" max="15375" width="7.81640625" customWidth="1"/>
+    <col min="15376" max="15376" width="5.453125" customWidth="1"/>
+    <col min="15377" max="15377" width="6.453125" customWidth="1"/>
+    <col min="15378" max="15378" width="7.81640625" customWidth="1"/>
+    <col min="15379" max="15379" width="3" customWidth="1"/>
+    <col min="15380" max="15380" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15617" max="15620" width="14.453125" customWidth="1"/>
+    <col min="15621" max="15621" width="15.453125" customWidth="1"/>
+    <col min="15622" max="15622" width="14.54296875" customWidth="1"/>
+    <col min="15623" max="15623" width="15.26953125" customWidth="1"/>
+    <col min="15624" max="15625" width="14.453125" customWidth="1"/>
+    <col min="15626" max="15626" width="13.1796875" customWidth="1"/>
+    <col min="15627" max="15629" width="14.453125" customWidth="1"/>
+    <col min="15630" max="15630" width="15.81640625" customWidth="1"/>
+    <col min="15631" max="15631" width="7.81640625" customWidth="1"/>
+    <col min="15632" max="15632" width="5.453125" customWidth="1"/>
+    <col min="15633" max="15633" width="6.453125" customWidth="1"/>
+    <col min="15634" max="15634" width="7.81640625" customWidth="1"/>
+    <col min="15635" max="15635" width="3" customWidth="1"/>
+    <col min="15636" max="15636" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15873" max="15876" width="14.453125" customWidth="1"/>
+    <col min="15877" max="15877" width="15.453125" customWidth="1"/>
+    <col min="15878" max="15878" width="14.54296875" customWidth="1"/>
+    <col min="15879" max="15879" width="15.26953125" customWidth="1"/>
+    <col min="15880" max="15881" width="14.453125" customWidth="1"/>
+    <col min="15882" max="15882" width="13.1796875" customWidth="1"/>
+    <col min="15883" max="15885" width="14.453125" customWidth="1"/>
+    <col min="15886" max="15886" width="15.81640625" customWidth="1"/>
+    <col min="15887" max="15887" width="7.81640625" customWidth="1"/>
+    <col min="15888" max="15888" width="5.453125" customWidth="1"/>
+    <col min="15889" max="15889" width="6.453125" customWidth="1"/>
+    <col min="15890" max="15890" width="7.81640625" customWidth="1"/>
+    <col min="15891" max="15891" width="3" customWidth="1"/>
+    <col min="15892" max="15892" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="16129" max="16132" width="14.453125" customWidth="1"/>
+    <col min="16133" max="16133" width="15.453125" customWidth="1"/>
+    <col min="16134" max="16134" width="14.54296875" customWidth="1"/>
+    <col min="16135" max="16135" width="15.26953125" customWidth="1"/>
+    <col min="16136" max="16137" width="14.453125" customWidth="1"/>
+    <col min="16138" max="16138" width="13.1796875" customWidth="1"/>
+    <col min="16139" max="16141" width="14.453125" customWidth="1"/>
+    <col min="16142" max="16142" width="15.81640625" customWidth="1"/>
+    <col min="16143" max="16143" width="7.81640625" customWidth="1"/>
+    <col min="16144" max="16144" width="5.453125" customWidth="1"/>
+    <col min="16145" max="16145" width="6.453125" customWidth="1"/>
+    <col min="16146" max="16146" width="7.81640625" customWidth="1"/>
+    <col min="16147" max="16147" width="3" customWidth="1"/>
+    <col min="16148" max="16148" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="246" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
+      <c r="S1"/>
+    </row>
+    <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2"/>
+    </row>
+    <row r="3" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" s="61"/>
+      <c r="E3" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F3" s="247" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="129" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="254" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="271" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="26"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="256" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" s="257"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="250" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="251"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="29"/>
+    </row>
+    <row r="4" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="61"/>
+      <c r="E4" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F4" s="247"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="254"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="271"/>
+      <c r="O4" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" s="241" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" s="242" t="s">
+        <v>71</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" s="237" t="s">
+        <v>70</v>
+      </c>
+      <c r="U4" s="238" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" s="37"/>
+      <c r="E5" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="F5" s="255" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="247" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="54"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="38"/>
+      <c r="O5" s="39">
+        <v>31</v>
+      </c>
+      <c r="P5" s="40">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="41">
+        <v>19</v>
+      </c>
+      <c r="R5" s="42">
+        <v>11</v>
+      </c>
+      <c r="S5" s="40">
+        <v>31</v>
+      </c>
+      <c r="T5" s="41">
+        <v>19</v>
+      </c>
+      <c r="U5" s="42">
+        <v>11</v>
+      </c>
+      <c r="V5" s="43">
+        <f t="shared" ref="V5:V17" si="0">-SUM(S5-P5)*-1</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="44"/>
+    </row>
+    <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="255"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="129" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="247"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="126" t="s">
+        <v>215</v>
+      </c>
+      <c r="N6" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" s="47">
+        <v>49</v>
+      </c>
+      <c r="P6" s="48">
+        <f t="shared" ref="P6:P17" si="1">SUM(Q6:R6)</f>
+        <v>12</v>
+      </c>
+      <c r="Q6" s="49">
+        <v>7</v>
+      </c>
+      <c r="R6" s="50">
+        <v>5</v>
+      </c>
+      <c r="S6" s="48">
+        <f t="shared" ref="S6:S17" si="2">SUM(T6:U6)</f>
+        <v>12</v>
+      </c>
+      <c r="T6" s="49">
+        <v>7</v>
+      </c>
+      <c r="U6" s="50">
+        <v>5</v>
+      </c>
+      <c r="V6" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="52"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="53"/>
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="255" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="64"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="47">
+        <v>22</v>
+      </c>
+      <c r="P7" s="48">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Q7" s="49">
+        <v>11</v>
+      </c>
+      <c r="R7" s="50">
+        <v>4</v>
+      </c>
+      <c r="S7" s="48">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="T7" s="49">
+        <v>11</v>
+      </c>
+      <c r="U7" s="50">
+        <v>4</v>
+      </c>
+      <c r="V7" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W7" s="52"/>
+    </row>
+    <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="45"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="255"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="56">
+        <v>46255</v>
+      </c>
+      <c r="O8" s="47">
+        <v>24</v>
+      </c>
+      <c r="P8" s="48">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Q8" s="49">
+        <v>3</v>
+      </c>
+      <c r="R8" s="50">
+        <v>3</v>
+      </c>
+      <c r="S8" s="48">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="T8" s="49">
+        <v>2</v>
+      </c>
+      <c r="U8" s="50">
+        <v>2</v>
+      </c>
+      <c r="V8" s="51">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="W8" s="52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="45"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="58"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="64"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9" s="47"/>
+      <c r="P9" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="49"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W9" s="52"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="45"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="129" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="61"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="64"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="49"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="52"/>
+    </row>
+    <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="64"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="243" t="s">
+        <v>149</v>
+      </c>
+      <c r="G11" s="64"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="66"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="68"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="70"/>
+    </row>
+    <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="71"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="243" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" s="64"/>
+      <c r="H12" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="L12" s="73" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" s="74"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="68"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W12" s="70"/>
+    </row>
+    <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="61"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="128" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="245" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" s="30"/>
+      <c r="J13" s="127" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="128"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="60"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="68"/>
+      <c r="U13" s="69"/>
+      <c r="V13" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="70"/>
+    </row>
+    <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="8"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="240" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="245"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="60"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="68"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="70"/>
+    </row>
+    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="129"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="240"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="245" t="s">
+        <v>84</v>
+      </c>
+      <c r="I15" s="30"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="107"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="68"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="70"/>
+    </row>
+    <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="8"/>
+      <c r="B16" s="245" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="245"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="107"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="68"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="68"/>
+      <c r="U16" s="69"/>
+      <c r="V16" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="70"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="8"/>
+      <c r="B17" s="245"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="248" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="30"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="80"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="82">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="83"/>
+    </row>
+    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="248"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="77"/>
+      <c r="M18" s="77"/>
+      <c r="R18" s="84"/>
+      <c r="S18"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="240"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="248" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" s="30"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="77"/>
+      <c r="R19" s="84"/>
+      <c r="S19"/>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="85" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="240"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="158"/>
+      <c r="H20" s="248"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="R20" s="84"/>
+      <c r="S20"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="D21" s="61"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="248" t="s">
+        <v>82</v>
+      </c>
+      <c r="I21" s="30"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="R21" s="84"/>
+      <c r="S21"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="6"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="240"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="248"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="R22" s="84"/>
+      <c r="S22"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="R23" s="84"/>
+      <c r="S23"/>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="R24" s="84"/>
+      <c r="S24"/>
+    </row>
+    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="30"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="R25" s="84"/>
+      <c r="S25"/>
+    </row>
+    <row r="26" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="240"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="R26" s="84"/>
+      <c r="S26"/>
+    </row>
+    <row r="27" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="R27" s="84"/>
+      <c r="S27"/>
+    </row>
+    <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="249" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="249"/>
+      <c r="C28" s="249"/>
+      <c r="D28" s="249"/>
+      <c r="E28" s="249"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="R28" s="84"/>
+      <c r="S28"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="30"/>
+      <c r="I29" s="240"/>
+      <c r="J29" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K29" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="92" t="s">
+        <v>25</v>
+      </c>
+      <c r="R29" s="84"/>
+      <c r="S29"/>
+    </row>
+    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="B30" s="94"/>
+      <c r="C30" s="93" t="s">
+        <v>231</v>
+      </c>
+      <c r="D30" s="93" t="s">
+        <v>234</v>
+      </c>
+      <c r="E30" s="253" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="8"/>
+      <c r="G30" s="239" t="s">
+        <v>240</v>
+      </c>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="159" t="s">
+        <v>141</v>
+      </c>
+      <c r="K30" s="124" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="224" t="s">
+        <v>242</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="R30" s="84"/>
+      <c r="S30"/>
+    </row>
+    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="93" t="s">
+        <v>232</v>
+      </c>
+      <c r="D31" s="93" t="s">
+        <v>233</v>
+      </c>
+      <c r="E31" s="253"/>
+      <c r="F31" s="8"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="K31" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="L31" s="224" t="s">
+        <v>119</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" s="84"/>
+      <c r="S31"/>
+    </row>
+    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="94"/>
+      <c r="C32" s="93" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="93" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" s="253" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="143"/>
+      <c r="K32" s="110" t="s">
+        <v>150</v>
+      </c>
+      <c r="L32" s="224" t="s">
+        <v>122</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="R32" s="84"/>
+      <c r="S32"/>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="8"/>
+      <c r="C33" s="93" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="93" t="s">
+        <v>236</v>
+      </c>
+      <c r="E33" s="253"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="124" t="s">
+        <v>120</v>
+      </c>
+      <c r="L33" s="224" t="s">
+        <v>243</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="R33" s="84"/>
+      <c r="S33"/>
+    </row>
+    <row r="34" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="94"/>
+      <c r="B34" s="95"/>
+      <c r="D34" s="93" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" s="252" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="224" t="s">
+        <v>81</v>
+      </c>
+      <c r="L34" s="224" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="8"/>
+      <c r="R34" s="84"/>
+      <c r="S34"/>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="94"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="93" t="s">
+        <v>238</v>
+      </c>
+      <c r="E35" s="252"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="224" t="s">
+        <v>244</v>
+      </c>
+      <c r="L35" s="218" t="s">
+        <v>16</v>
+      </c>
+      <c r="M35" s="13"/>
+      <c r="R35" s="84"/>
+      <c r="S35"/>
+    </row>
+    <row r="36" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="94"/>
+      <c r="B36" s="94"/>
+      <c r="D36" s="93" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="253" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="97"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="124" t="s">
+        <v>211</v>
+      </c>
+      <c r="L36" s="218" t="s">
+        <v>38</v>
+      </c>
+      <c r="M36" s="94"/>
+      <c r="R36" s="84"/>
+      <c r="S36"/>
+    </row>
+    <row r="37" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="E37" s="253"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="100"/>
+      <c r="K37" s="124" t="s">
+        <v>212</v>
+      </c>
+      <c r="L37" s="218" t="s">
+        <v>205</v>
+      </c>
+      <c r="M37" s="94"/>
+      <c r="R37" s="84"/>
+      <c r="S37"/>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="77"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="239" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" s="77"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="2"/>
+      <c r="R38" s="84"/>
+      <c r="S38"/>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="74"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="239" t="s">
+        <v>92</v>
+      </c>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="2"/>
+      <c r="S39"/>
+    </row>
+    <row r="40" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="105"/>
+      <c r="S40"/>
+    </row>
+    <row r="41" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="104"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="104"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="93" t="s">
+        <v>152</v>
+      </c>
+      <c r="F41" s="8"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="101"/>
+      <c r="M41" s="106"/>
+      <c r="S41"/>
+    </row>
+    <row r="42" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="104"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="104"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="239" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="106"/>
+      <c r="S42"/>
+    </row>
+    <row r="43" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="104"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="239" t="s">
+        <v>216</v>
+      </c>
+      <c r="F43" s="107"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="106"/>
+      <c r="S43"/>
+    </row>
+    <row r="44" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="104"/>
+      <c r="B44" s="104"/>
+      <c r="C44" s="104"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="109"/>
+      <c r="S44"/>
+    </row>
+    <row r="45" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="104"/>
+      <c r="B45" s="104"/>
+      <c r="C45" s="104"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="110"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="111"/>
+      <c r="S45"/>
+    </row>
+    <row r="46" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="104"/>
+      <c r="B46" s="104"/>
+      <c r="C46" s="104"/>
+      <c r="D46" s="104"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="104"/>
+      <c r="J46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="111"/>
+      <c r="S46"/>
+    </row>
+    <row r="47" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="104"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="104"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="104"/>
+      <c r="H47" s="104"/>
+      <c r="I47" s="240"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="112"/>
+      <c r="S47"/>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="84"/>
+      <c r="S48"/>
+    </row>
+    <row r="49" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="77"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="113"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="104"/>
+      <c r="I49" s="240"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="84"/>
+      <c r="S49"/>
+    </row>
+    <row r="50" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="77"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="84"/>
+      <c r="S50"/>
+    </row>
+    <row r="51" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="77"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="77"/>
+      <c r="D51" s="113"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="77"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="84"/>
+      <c r="S51"/>
+    </row>
+    <row r="52" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="77"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="113"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="77"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="77"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+    </row>
+    <row r="53" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="77"/>
+      <c r="B53" s="77"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="113"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="77"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="114"/>
+      <c r="M53" s="8"/>
+    </row>
+    <row r="54" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="77"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="113"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="77"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="77"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="114"/>
+      <c r="M54" s="8"/>
+    </row>
+    <row r="55" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="77"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="113"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="77"/>
+      <c r="G55" s="77"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="104"/>
+      <c r="J55" s="77"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="114"/>
+      <c r="M55" s="8"/>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="77"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="113"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="77"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="77"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="114"/>
+      <c r="M56" s="8"/>
+    </row>
+    <row r="57" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="77"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="77"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="114"/>
+      <c r="M57" s="8"/>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="77"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="113"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="77"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="115"/>
+      <c r="L58" s="114"/>
+      <c r="M58" s="8"/>
+    </row>
+    <row r="59" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="77"/>
+      <c r="B59" s="77"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="113"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="77"/>
+      <c r="G59" s="77"/>
+      <c r="H59" s="104"/>
+      <c r="I59" s="104"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="115"/>
+      <c r="L59" s="114"/>
+      <c r="M59" s="8"/>
+    </row>
+    <row r="60" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="77"/>
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="77"/>
+      <c r="G60" s="77"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="115"/>
+      <c r="L60" s="114"/>
+      <c r="M60" s="8"/>
+    </row>
+    <row r="61" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="77"/>
+      <c r="B61" s="77"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="113"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="114"/>
+      <c r="M61" s="8"/>
+    </row>
+    <row r="62" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="77"/>
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="77"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="114"/>
+      <c r="M62" s="8"/>
+    </row>
+    <row r="63" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="77"/>
+      <c r="B63" s="77"/>
+      <c r="C63" s="77"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="104"/>
+      <c r="I63" s="104"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="77"/>
+      <c r="M63" s="8"/>
+    </row>
+    <row r="64" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="77"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="77"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="77"/>
+      <c r="H64" s="104"/>
+      <c r="I64" s="104"/>
+      <c r="J64" s="77"/>
+      <c r="K64" s="116">
+        <v>22</v>
+      </c>
+      <c r="L64" s="117">
+        <v>6</v>
+      </c>
+      <c r="M64" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="61"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
+      <c r="S65"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L66" s="119" t="s">
+        <v>94</v>
+      </c>
+      <c r="M66" s="25">
+        <v>97</v>
+      </c>
+      <c r="S66"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L67" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="M67" s="25">
+        <f>SUM(M66-(M68+M69+M70))</f>
+        <v>69</v>
+      </c>
+      <c r="S67"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L68" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" s="25">
+        <v>15</v>
+      </c>
+      <c r="S68"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L69" s="121" t="s">
+        <v>24</v>
+      </c>
+      <c r="M69" s="25">
+        <v>9</v>
+      </c>
+      <c r="S69"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L70" s="122" t="s">
+        <v>25</v>
+      </c>
+      <c r="M70" s="25">
+        <v>4</v>
+      </c>
+      <c r="S70"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L71" t="s">
+        <v>96</v>
+      </c>
+      <c r="M71" s="25">
+        <v>13</v>
+      </c>
+      <c r="S71"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="M72" s="25"/>
+      <c r="S72"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="Q3:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6921,21 +9607,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="251" t="s">
+      <c r="A1" s="246" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -6990,13 +9676,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="240" t="s">
+      <c r="D3" s="247" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="240" t="s">
+      <c r="F3" s="247" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -7005,24 +9691,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="246" t="s">
+      <c r="J3" s="245" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="247" t="s">
+      <c r="M3" s="248" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="244" t="s">
+      <c r="Q3" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="245"/>
+      <c r="R3" s="257"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="237" t="s">
+      <c r="T3" s="250" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="238"/>
+      <c r="U3" s="251"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -7034,20 +9720,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="240"/>
+      <c r="D4" s="247"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="240"/>
+      <c r="F4" s="247"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="246"/>
+      <c r="J4" s="245"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="247"/>
+      <c r="M4" s="248"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -7086,7 +9772,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="243" t="s">
+      <c r="F5" s="255" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -7094,7 +9780,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="240" t="s">
+      <c r="J5" s="247" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -7139,13 +9825,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="243"/>
+      <c r="F6" s="255"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="240"/>
+      <c r="J6" s="247"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -7194,13 +9880,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="246" t="s">
+      <c r="F7" s="245" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="242" t="s">
+      <c r="J7" s="254" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -7248,11 +9934,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="246"/>
+      <c r="F8" s="245"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="242"/>
+      <c r="J8" s="254"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -7296,7 +9982,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="243" t="s">
+      <c r="F9" s="255" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -7336,7 +10022,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="243"/>
+      <c r="F10" s="255"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -7462,7 +10148,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="247" t="s">
+      <c r="I13" s="248" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -7503,7 +10189,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="247"/>
+      <c r="I14" s="248"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -7563,13 +10249,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="246" t="s">
+      <c r="A16" s="245" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="246" t="s">
+      <c r="B16" s="245" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="248" t="s">
+      <c r="C16" s="258" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -7604,9 +10290,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="246"/>
-      <c r="B17" s="246"/>
-      <c r="C17" s="249"/>
+      <c r="A17" s="245"/>
+      <c r="B17" s="245"/>
+      <c r="C17" s="259"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -7639,7 +10325,7 @@
     <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="247" t="s">
+      <c r="C18" s="248" t="s">
         <v>82</v>
       </c>
       <c r="D18" s="61"/>
@@ -7657,7 +10343,7 @@
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="147"/>
-      <c r="C19" s="247"/>
+      <c r="C19" s="248"/>
       <c r="D19" s="125"/>
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
@@ -7816,13 +10502,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="252" t="s">
+      <c r="A28" s="249" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="252"/>
-      <c r="C28" s="252"/>
-      <c r="D28" s="252"/>
-      <c r="E28" s="252"/>
+      <c r="B28" s="249"/>
+      <c r="C28" s="249"/>
+      <c r="D28" s="249"/>
+      <c r="E28" s="249"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -7882,7 +10568,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="241" t="s">
+      <c r="E30" s="253" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -7916,7 +10602,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="241"/>
+      <c r="E31" s="253"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -7946,7 +10632,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="241" t="s">
+      <c r="E32" s="253" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -7976,7 +10662,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="241"/>
+      <c r="E33" s="253"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -8000,7 +10686,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="239" t="s">
+      <c r="E34" s="252" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -8025,7 +10711,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="239"/>
+      <c r="E35" s="252"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -8044,7 +10730,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="241" t="s">
+      <c r="E36" s="253" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -8064,7 +10750,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="241"/>
+      <c r="E37" s="253"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -8592,28 +11278,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="C18:C19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -9534,21 +12220,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="251" t="s">
+      <c r="A1" s="246" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -9603,13 +12289,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="240" t="s">
+      <c r="D3" s="247" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="240" t="s">
+      <c r="F3" s="247" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -9618,24 +12304,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="246" t="s">
+      <c r="J3" s="245" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="247" t="s">
+      <c r="M3" s="248" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="244" t="s">
+      <c r="Q3" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="245"/>
+      <c r="R3" s="257"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="237" t="s">
+      <c r="T3" s="250" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="238"/>
+      <c r="U3" s="251"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -9647,20 +12333,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="240"/>
+      <c r="D4" s="247"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="240"/>
+      <c r="F4" s="247"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="246"/>
+      <c r="J4" s="245"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="247"/>
+      <c r="M4" s="248"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -9699,7 +12385,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="243" t="s">
+      <c r="F5" s="255" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -9707,7 +12393,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="240" t="s">
+      <c r="J5" s="247" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -9752,13 +12438,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="243"/>
+      <c r="F6" s="255"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="240"/>
+      <c r="J6" s="247"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -9802,13 +12488,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="246" t="s">
+      <c r="F7" s="245" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="242" t="s">
+      <c r="J7" s="254" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -9856,11 +12542,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="246"/>
+      <c r="F8" s="245"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="242"/>
+      <c r="J8" s="254"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -9904,7 +12590,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="243" t="s">
+      <c r="F9" s="255" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -9944,7 +12630,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="243"/>
+      <c r="F10" s="255"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -10070,7 +12756,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="247" t="s">
+      <c r="I13" s="248" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -10111,7 +12797,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="247"/>
+      <c r="I14" s="248"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -10146,7 +12832,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="247" t="s">
+      <c r="I15" s="248" t="s">
         <v>82</v>
       </c>
       <c r="J15" s="60"/>
@@ -10173,13 +12859,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="246" t="s">
+      <c r="A16" s="245" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="246" t="s">
+      <c r="B16" s="245" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="248" t="s">
+      <c r="C16" s="258" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -10189,7 +12875,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="247"/>
+      <c r="I16" s="248"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -10214,15 +12900,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="246"/>
-      <c r="B17" s="246"/>
-      <c r="C17" s="249"/>
+      <c r="A17" s="245"/>
+      <c r="B17" s="245"/>
+      <c r="C17" s="259"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="243" t="s">
+      <c r="I17" s="255" t="s">
         <v>139</v>
       </c>
       <c r="J17" s="71"/>
@@ -10257,7 +12943,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="243"/>
+      <c r="I18" s="255"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -10429,13 +13115,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="252" t="s">
+      <c r="A28" s="249" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="252"/>
-      <c r="C28" s="252"/>
-      <c r="D28" s="252"/>
-      <c r="E28" s="252"/>
+      <c r="B28" s="249"/>
+      <c r="C28" s="249"/>
+      <c r="D28" s="249"/>
+      <c r="E28" s="249"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -10495,7 +13181,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="241" t="s">
+      <c r="E30" s="253" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -10529,7 +13215,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="241"/>
+      <c r="E31" s="253"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -10559,7 +13245,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="241" t="s">
+      <c r="E32" s="253" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -10589,7 +13275,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="241"/>
+      <c r="E33" s="253"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -10615,7 +13301,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="239" t="s">
+      <c r="E34" s="252" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -10638,7 +13324,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="239"/>
+      <c r="E35" s="252"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -10658,7 +13344,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="241" t="s">
+      <c r="E36" s="253" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -10675,7 +13361,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="241"/>
+      <c r="E37" s="253"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -11203,29 +13889,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="I13:I14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -12143,21 +14829,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="251" t="s">
+      <c r="A1" s="246" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -12210,13 +14896,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="240" t="s">
+      <c r="D3" s="247" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="240" t="s">
+      <c r="F3" s="247" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -12225,24 +14911,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="246" t="s">
+      <c r="J3" s="245" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="247" t="s">
+      <c r="M3" s="248" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="244" t="s">
+      <c r="Q3" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="245"/>
+      <c r="R3" s="257"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="237" t="s">
+      <c r="T3" s="250" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="238"/>
+      <c r="U3" s="251"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -12254,20 +14940,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="240"/>
+      <c r="D4" s="247"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="240"/>
+      <c r="F4" s="247"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="246"/>
+      <c r="J4" s="245"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="247"/>
+      <c r="M4" s="248"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -12306,7 +14992,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="243" t="s">
+      <c r="F5" s="255" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -12314,7 +15000,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="240" t="s">
+      <c r="J5" s="247" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -12359,13 +15045,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="243"/>
+      <c r="F6" s="255"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="240"/>
+      <c r="J6" s="247"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -12409,13 +15095,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="246" t="s">
+      <c r="F7" s="245" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="242" t="s">
+      <c r="J7" s="254" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -12463,13 +15149,13 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="246"/>
+      <c r="F8" s="245"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="J8" s="242"/>
+      <c r="J8" s="254"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -12513,13 +15199,13 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="243" t="s">
+      <c r="F9" s="255" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
       <c r="H9" s="30"/>
       <c r="I9" s="134"/>
-      <c r="J9" s="247" t="s">
+      <c r="J9" s="248" t="s">
         <v>82</v>
       </c>
       <c r="K9" s="54"/>
@@ -12555,11 +15241,11 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="243"/>
+      <c r="F10" s="255"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
-      <c r="J10" s="247"/>
+      <c r="J10" s="248"/>
       <c r="K10" s="6"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
@@ -12682,7 +15368,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="247" t="s">
+      <c r="I13" s="248" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -12723,7 +15409,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="247"/>
+      <c r="I14" s="248"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -12758,7 +15444,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="253" t="s">
+      <c r="I15" s="260" t="s">
         <v>139</v>
       </c>
       <c r="J15" s="60"/>
@@ -12785,13 +15471,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="246" t="s">
+      <c r="A16" s="245" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="246" t="s">
+      <c r="B16" s="245" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="248" t="s">
+      <c r="C16" s="258" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -12801,7 +15487,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="253"/>
+      <c r="I16" s="260"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -12826,9 +15512,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="246"/>
-      <c r="B17" s="246"/>
-      <c r="C17" s="249"/>
+      <c r="A17" s="245"/>
+      <c r="B17" s="245"/>
+      <c r="C17" s="259"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -13039,13 +15725,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="252" t="s">
+      <c r="A28" s="249" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="252"/>
-      <c r="C28" s="252"/>
-      <c r="D28" s="252"/>
-      <c r="E28" s="252"/>
+      <c r="B28" s="249"/>
+      <c r="C28" s="249"/>
+      <c r="D28" s="249"/>
+      <c r="E28" s="249"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -13105,7 +15791,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="241" t="s">
+      <c r="E30" s="253" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -13139,7 +15825,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="241"/>
+      <c r="E31" s="253"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -13169,7 +15855,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="241" t="s">
+      <c r="E32" s="253" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -13194,7 +15880,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="241"/>
+      <c r="E33" s="253"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -13215,7 +15901,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="239" t="s">
+      <c r="E34" s="252" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -13238,7 +15924,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="239"/>
+      <c r="E35" s="252"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -13258,7 +15944,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="241" t="s">
+      <c r="E36" s="253" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -13278,7 +15964,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="241"/>
+      <c r="E37" s="253"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -13806,17 +16492,11 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="A16:A17"/>
@@ -13824,11 +16504,17 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -14745,21 +17431,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="251" t="s">
+      <c r="A1" s="246" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -14814,13 +17500,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="240" t="s">
+      <c r="D3" s="247" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="240" t="s">
+      <c r="F3" s="247" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -14829,24 +17515,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="246" t="s">
+      <c r="J3" s="245" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="247" t="s">
+      <c r="M3" s="248" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="244" t="s">
+      <c r="Q3" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="245"/>
+      <c r="R3" s="257"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="237" t="s">
+      <c r="T3" s="250" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="238"/>
+      <c r="U3" s="251"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -14858,20 +17544,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="240"/>
+      <c r="D4" s="247"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="240"/>
+      <c r="F4" s="247"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="246"/>
+      <c r="J4" s="245"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="247"/>
+      <c r="M4" s="248"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -14910,7 +17596,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="243" t="s">
+      <c r="F5" s="255" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -14918,7 +17604,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="240" t="s">
+      <c r="J5" s="247" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -14963,13 +17649,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="243"/>
+      <c r="F6" s="255"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="240"/>
+      <c r="J6" s="247"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -15016,7 +17702,7 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="246" t="s">
+      <c r="F7" s="245" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
@@ -15024,7 +17710,7 @@
       <c r="I7" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="242" t="s">
+      <c r="J7" s="254" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -15072,10 +17758,10 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="246"/>
+      <c r="F8" s="245"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
-      <c r="J8" s="242"/>
+      <c r="J8" s="254"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -15119,7 +17805,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="243" t="s">
+      <c r="F9" s="255" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -15159,7 +17845,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="243"/>
+      <c r="F10" s="255"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -15286,7 +17972,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="247" t="s">
+      <c r="I13" s="248" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -15324,7 +18010,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="247"/>
+      <c r="I14" s="248"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -15359,7 +18045,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="247" t="s">
+      <c r="I15" s="248" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -15386,13 +18072,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="246" t="s">
+      <c r="A16" s="245" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="246" t="s">
+      <c r="B16" s="245" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="243" t="s">
+      <c r="C16" s="255" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -15402,7 +18088,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="247"/>
+      <c r="I16" s="248"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -15427,15 +18113,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="246"/>
-      <c r="B17" s="246"/>
-      <c r="C17" s="243"/>
+      <c r="A17" s="245"/>
+      <c r="B17" s="245"/>
+      <c r="C17" s="255"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="247" t="s">
+      <c r="I17" s="248" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -15470,7 +18156,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="247"/>
+      <c r="I18" s="248"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -15640,13 +18326,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="252" t="s">
+      <c r="A28" s="249" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="252"/>
-      <c r="C28" s="252"/>
-      <c r="D28" s="252"/>
-      <c r="E28" s="252"/>
+      <c r="B28" s="249"/>
+      <c r="C28" s="249"/>
+      <c r="D28" s="249"/>
+      <c r="E28" s="249"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -15706,7 +18392,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="241" t="s">
+      <c r="E30" s="253" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -15740,7 +18426,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="241"/>
+      <c r="E31" s="253"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -15770,7 +18456,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="241" t="s">
+      <c r="E32" s="253" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -15796,7 +18482,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="241"/>
+      <c r="E33" s="253"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -15818,7 +18504,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="239" t="s">
+      <c r="E34" s="252" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -15841,7 +18527,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="239"/>
+      <c r="E35" s="252"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -15861,7 +18547,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="241" t="s">
+      <c r="E36" s="253" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -15878,7 +18564,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="241"/>
+      <c r="E37" s="253"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -16406,17 +19092,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="I17:I18"/>
     <mergeCell ref="A1:M1"/>
@@ -16429,6 +19104,17 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="I13:I14"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17348,21 +20034,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="251" t="s">
+      <c r="A1" s="246" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -17417,13 +20103,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="240" t="s">
+      <c r="D3" s="247" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="240" t="s">
+      <c r="F3" s="247" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -17432,24 +20118,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="246" t="s">
+      <c r="J3" s="245" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="247" t="s">
+      <c r="M3" s="248" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="244" t="s">
+      <c r="Q3" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="245"/>
+      <c r="R3" s="257"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="237" t="s">
+      <c r="T3" s="250" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="238"/>
+      <c r="U3" s="251"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -17461,20 +20147,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="240"/>
+      <c r="D4" s="247"/>
       <c r="E4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="240"/>
+      <c r="F4" s="247"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="246"/>
+      <c r="J4" s="245"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="247"/>
+      <c r="M4" s="248"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -17513,7 +20199,7 @@
       <c r="E5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F5" s="243" t="s">
+      <c r="F5" s="255" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -17521,7 +20207,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="240" t="s">
+      <c r="J5" s="247" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -17566,13 +20252,13 @@
       <c r="E6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="243"/>
+      <c r="F6" s="255"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="240"/>
+      <c r="J6" s="247"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -17619,13 +20305,13 @@
       <c r="E7" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="246" t="s">
+      <c r="F7" s="245" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="242" t="s">
+      <c r="J7" s="254" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -17671,11 +20357,11 @@
         <v>17</v>
       </c>
       <c r="E8" s="30"/>
-      <c r="F8" s="246"/>
+      <c r="F8" s="245"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="242"/>
+      <c r="J8" s="254"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -17720,7 +20406,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="243" t="s">
+      <c r="F9" s="255" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -17760,7 +20446,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="243"/>
+      <c r="F10" s="255"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -17887,7 +20573,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="247" t="s">
+      <c r="I13" s="248" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -17928,7 +20614,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="247"/>
+      <c r="I14" s="248"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -17963,7 +20649,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="247" t="s">
+      <c r="I15" s="248" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -17990,13 +20676,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="246" t="s">
+      <c r="A16" s="245" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="246" t="s">
+      <c r="B16" s="245" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="243" t="s">
+      <c r="C16" s="255" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -18006,7 +20692,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="247"/>
+      <c r="I16" s="248"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -18031,15 +20717,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="246"/>
-      <c r="B17" s="246"/>
-      <c r="C17" s="243"/>
+      <c r="A17" s="245"/>
+      <c r="B17" s="245"/>
+      <c r="C17" s="255"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="247" t="s">
+      <c r="I17" s="248" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -18074,7 +20760,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="247"/>
+      <c r="I18" s="248"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -18245,13 +20931,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="252" t="s">
+      <c r="A28" s="249" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="252"/>
-      <c r="C28" s="252"/>
-      <c r="D28" s="252"/>
-      <c r="E28" s="252"/>
+      <c r="B28" s="249"/>
+      <c r="C28" s="249"/>
+      <c r="D28" s="249"/>
+      <c r="E28" s="249"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -18311,7 +20997,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="241" t="s">
+      <c r="E30" s="253" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -18345,7 +21031,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="241"/>
+      <c r="E31" s="253"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -18373,7 +21059,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="241" t="s">
+      <c r="E32" s="253" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -18399,7 +21085,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="241"/>
+      <c r="E33" s="253"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -18421,7 +21107,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="239" t="s">
+      <c r="E34" s="252" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -18444,7 +21130,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="239"/>
+      <c r="E35" s="252"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -18464,7 +21150,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="241" t="s">
+      <c r="E36" s="253" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -18484,7 +21170,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="241"/>
+      <c r="E37" s="253"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -19014,29 +21700,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -19185,22 +21871,22 @@
       <c r="C3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="240" t="s">
+      <c r="D3" s="247" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="201" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="256" t="s">
+      <c r="F3" s="264" t="s">
         <v>160</v>
       </c>
       <c r="H3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="242" t="s">
+      <c r="I3" s="254" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="254" t="s">
+      <c r="K3" s="265" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="2"/>
@@ -19216,16 +21902,16 @@
       <c r="C4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="240"/>
+      <c r="D4" s="247"/>
       <c r="E4" s="201" t="s">
         <v>162</v>
       </c>
-      <c r="F4" s="256"/>
+      <c r="F4" s="264"/>
       <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="242"/>
-      <c r="K4" s="255"/>
+      <c r="I4" s="254"/>
+      <c r="K4" s="266"/>
       <c r="L4" s="203" t="s">
         <v>163</v>
       </c>
@@ -19238,13 +21924,13 @@
       <c r="E5" s="129" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="256" t="s">
+      <c r="F5" s="264" t="s">
         <v>165</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="240" t="s">
+      <c r="I5" s="247" t="s">
         <v>166</v>
       </c>
       <c r="K5" s="2"/>
@@ -19258,11 +21944,11 @@
       <c r="E6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="256"/>
+      <c r="F6" s="264"/>
       <c r="H6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="240"/>
+      <c r="I6" s="247"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -19277,10 +21963,10 @@
       <c r="E7" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F7" s="240" t="s">
+      <c r="F7" s="247" t="s">
         <v>168</v>
       </c>
-      <c r="I7" s="240" t="s">
+      <c r="I7" s="247" t="s">
         <v>15</v>
       </c>
       <c r="K7" s="2"/>
@@ -19294,17 +21980,17 @@
       <c r="E8" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="240"/>
-      <c r="I8" s="240"/>
+      <c r="F8" s="247"/>
+      <c r="I8" s="247"/>
       <c r="K8" s="2"/>
       <c r="L8" s="206"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="248" t="s">
+      <c r="A9" s="258" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="240" t="s">
+      <c r="B9" s="247" t="s">
         <v>171</v>
       </c>
       <c r="C9" s="207" t="s">
@@ -19313,7 +21999,7 @@
       <c r="E9" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="256" t="s">
+      <c r="F9" s="264" t="s">
         <v>173</v>
       </c>
       <c r="K9" s="2"/>
@@ -19323,15 +22009,15 @@
       <c r="P9"/>
     </row>
     <row r="10" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="249"/>
-      <c r="B10" s="240"/>
+      <c r="A10" s="259"/>
+      <c r="B10" s="247"/>
       <c r="C10" s="208" t="s">
         <v>174</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>175</v>
       </c>
-      <c r="F10" s="256"/>
+      <c r="F10" s="264"/>
       <c r="K10" s="209"/>
       <c r="L10" s="2"/>
       <c r="M10" s="206"/>
@@ -19358,7 +22044,7 @@
       <c r="E11" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="F11" s="246" t="s">
+      <c r="F11" s="245" t="s">
         <v>177</v>
       </c>
       <c r="K11" s="209"/>
@@ -19387,7 +22073,7 @@
       <c r="E12" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="246"/>
+      <c r="F12" s="245"/>
       <c r="G12" s="212" t="s">
         <v>179</v>
       </c>
@@ -19426,10 +22112,10 @@
       <c r="E13" s="183" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="257" t="s">
+      <c r="F13" s="267" t="s">
         <v>184</v>
       </c>
-      <c r="H13" s="248" t="s">
+      <c r="H13" s="258" t="s">
         <v>185</v>
       </c>
       <c r="K13" s="2"/>
@@ -19459,8 +22145,8 @@
       <c r="E14" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="F14" s="258"/>
-      <c r="H14" s="249"/>
+      <c r="F14" s="268"/>
+      <c r="H14" s="259"/>
       <c r="K14" s="2"/>
       <c r="L14" s="6"/>
       <c r="M14" s="2"/>
@@ -19487,10 +22173,10 @@
       <c r="E15" s="183" t="s">
         <v>189</v>
       </c>
-      <c r="F15" s="240" t="s">
+      <c r="F15" s="247" t="s">
         <v>190</v>
       </c>
-      <c r="H15" s="254" t="s">
+      <c r="H15" s="265" t="s">
         <v>45</v>
       </c>
       <c r="K15" s="2"/>
@@ -19515,8 +22201,8 @@
       <c r="C16" s="183" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="240"/>
-      <c r="H16" s="255"/>
+      <c r="F16" s="247"/>
+      <c r="H16" s="266"/>
       <c r="K16" s="2"/>
       <c r="L16" s="209"/>
       <c r="M16" s="8"/>
@@ -19543,7 +22229,7 @@
       </c>
       <c r="D17" s="206"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="259" t="s">
+      <c r="F17" s="269" t="s">
         <v>193</v>
       </c>
       <c r="G17" s="2"/>
@@ -19560,7 +22246,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="260"/>
+      <c r="F18" s="270"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="209"/>
@@ -19611,7 +22297,7 @@
       <c r="B20" s="133" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="240" t="s">
+      <c r="C20" s="247" t="s">
         <v>197</v>
       </c>
       <c r="D20" s="2"/>
@@ -19643,7 +22329,7 @@
         <v>199</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="240"/>
+      <c r="C21" s="247"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="219" t="s">
@@ -19651,7 +22337,7 @@
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="254" t="s">
+      <c r="I21" s="265" t="s">
         <v>82</v>
       </c>
       <c r="J21" s="209"/>
@@ -19685,7 +22371,7 @@
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="255"/>
+      <c r="I22" s="266"/>
       <c r="J22" s="209"/>
       <c r="K22" s="101" t="s">
         <v>40</v>
@@ -20415,11 +23101,8 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="I5:I6"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="I7:I8"/>
@@ -20433,8 +23116,11 @@
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="F17:F18"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21354,21 +24040,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="251" t="s">
+      <c r="A1" s="246" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -21423,13 +24109,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="247" t="s">
+      <c r="D3" s="248" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="240" t="s">
+      <c r="F3" s="247" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -21438,24 +24124,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="247" t="s">
+      <c r="J3" s="248" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="264" t="s">
+      <c r="M3" s="271" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="244" t="s">
+      <c r="Q3" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="245"/>
+      <c r="R3" s="257"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="237" t="s">
+      <c r="T3" s="250" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="238"/>
+      <c r="U3" s="251"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -21469,20 +24155,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="247"/>
+      <c r="D4" s="248"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="240"/>
+      <c r="F4" s="247"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="247"/>
+      <c r="J4" s="248"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="264"/>
+      <c r="M4" s="271"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -21521,7 +24207,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="243" t="s">
+      <c r="F5" s="255" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -21529,7 +24215,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="240" t="s">
+      <c r="J5" s="247" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -21574,13 +24260,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="243"/>
+      <c r="F6" s="255"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="240"/>
+      <c r="J6" s="247"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -21624,13 +24310,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="246" t="s">
+      <c r="F7" s="245" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="242" t="s">
+      <c r="J7" s="254" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -21678,11 +24364,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="246"/>
+      <c r="F8" s="245"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="242"/>
+      <c r="J8" s="254"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -21727,7 +24413,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="243" t="s">
+      <c r="F9" s="255" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -21767,7 +24453,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="243"/>
+      <c r="F10" s="255"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -21989,13 +24675,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="246" t="s">
+      <c r="A16" s="245" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="246" t="s">
+      <c r="B16" s="245" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="247" t="s">
+      <c r="C16" s="248" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -22030,9 +24716,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="246"/>
-      <c r="B17" s="246"/>
-      <c r="C17" s="247"/>
+      <c r="A17" s="245"/>
+      <c r="B17" s="245"/>
+      <c r="C17" s="248"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -22242,13 +24928,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="252" t="s">
+      <c r="A28" s="249" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="252"/>
-      <c r="C28" s="252"/>
-      <c r="D28" s="252"/>
-      <c r="E28" s="252"/>
+      <c r="B28" s="249"/>
+      <c r="C28" s="249"/>
+      <c r="D28" s="249"/>
+      <c r="E28" s="249"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -22308,7 +24994,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="241" t="s">
+      <c r="E30" s="253" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -22340,7 +25026,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="241"/>
+      <c r="E31" s="253"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -22368,7 +25054,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="241" t="s">
+      <c r="E32" s="253" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -22396,7 +25082,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="241"/>
+      <c r="E33" s="253"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -22420,7 +25106,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="239" t="s">
+      <c r="E34" s="252" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -22443,7 +25129,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="239"/>
+      <c r="E35" s="252"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -22463,7 +25149,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="241" t="s">
+      <c r="E36" s="253" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -22483,7 +25169,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="241"/>
+      <c r="E37" s="253"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -23011,26 +25697,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -23948,21 +26634,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="251" t="s">
+      <c r="A1" s="246" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -24017,13 +26703,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="247" t="s">
+      <c r="D3" s="248" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="240" t="s">
+      <c r="F3" s="247" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -24032,24 +26718,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="247" t="s">
+      <c r="J3" s="248" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="264" t="s">
+      <c r="M3" s="271" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="244" t="s">
+      <c r="Q3" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="245"/>
+      <c r="R3" s="257"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="237" t="s">
+      <c r="T3" s="250" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="238"/>
+      <c r="U3" s="251"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -24063,20 +26749,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="247"/>
+      <c r="D4" s="248"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="240"/>
+      <c r="F4" s="247"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="247"/>
+      <c r="J4" s="248"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="264"/>
+      <c r="M4" s="271"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -24115,7 +26801,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="243" t="s">
+      <c r="F5" s="255" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -24123,7 +26809,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="240" t="s">
+      <c r="J5" s="247" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -24168,13 +26854,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="243"/>
+      <c r="F6" s="255"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="240"/>
+      <c r="J6" s="247"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -24218,13 +26904,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="246" t="s">
+      <c r="F7" s="245" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="242" t="s">
+      <c r="J7" s="254" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -24272,11 +26958,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="246"/>
+      <c r="F8" s="245"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="242"/>
+      <c r="J8" s="254"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -24321,7 +27007,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="243" t="s">
+      <c r="F9" s="255" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -24361,7 +27047,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="243"/>
+      <c r="F10" s="255"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -24583,13 +27269,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="246" t="s">
+      <c r="A16" s="245" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="246" t="s">
+      <c r="B16" s="245" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="247" t="s">
+      <c r="C16" s="248" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -24624,9 +27310,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="246"/>
-      <c r="B17" s="246"/>
-      <c r="C17" s="247"/>
+      <c r="A17" s="245"/>
+      <c r="B17" s="245"/>
+      <c r="C17" s="248"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -24836,13 +27522,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="252" t="s">
+      <c r="A28" s="249" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="252"/>
-      <c r="C28" s="252"/>
-      <c r="D28" s="252"/>
-      <c r="E28" s="252"/>
+      <c r="B28" s="249"/>
+      <c r="C28" s="249"/>
+      <c r="D28" s="249"/>
+      <c r="E28" s="249"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -24902,7 +27588,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="241" t="s">
+      <c r="E30" s="253" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -24917,8 +27603,8 @@
       <c r="K30" s="124" t="s">
         <v>55</v>
       </c>
-      <c r="L30" s="218" t="s">
-        <v>16</v>
+      <c r="L30" s="224" t="s">
+        <v>242</v>
       </c>
       <c r="M30" s="10" t="s">
         <v>29</v>
@@ -24936,16 +27622,16 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="241"/>
+      <c r="E31" s="253"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
       <c r="J31" s="143"/>
-      <c r="K31" s="224" t="s">
-        <v>242</v>
-      </c>
-      <c r="L31" s="218" t="s">
-        <v>38</v>
+      <c r="K31" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="L31" s="224" t="s">
+        <v>119</v>
       </c>
       <c r="M31" s="10" t="s">
         <v>32</v>
@@ -24964,7 +27650,7 @@
       <c r="D32" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="241" t="s">
+      <c r="E32" s="253" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -24972,11 +27658,11 @@
       <c r="H32" s="30"/>
       <c r="I32" s="30"/>
       <c r="J32" s="143"/>
-      <c r="K32" s="224" t="s">
-        <v>119</v>
-      </c>
-      <c r="L32" s="218" t="s">
-        <v>205</v>
+      <c r="K32" s="110" t="s">
+        <v>141</v>
+      </c>
+      <c r="L32" s="224" t="s">
+        <v>122</v>
       </c>
       <c r="M32" s="20" t="s">
         <v>28</v>
@@ -24992,14 +27678,17 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="241"/>
+      <c r="E33" s="253"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
       <c r="I33" s="30"/>
       <c r="J33" s="143"/>
-      <c r="K33" s="224" t="s">
-        <v>122</v>
+      <c r="K33" s="110" t="s">
+        <v>150</v>
+      </c>
+      <c r="L33" s="224" t="s">
+        <v>243</v>
       </c>
       <c r="M33" s="23" t="s">
         <v>33</v>
@@ -25013,7 +27702,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="239" t="s">
+      <c r="E34" s="252" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -25021,10 +27710,12 @@
       <c r="H34" s="30"/>
       <c r="I34" s="30"/>
       <c r="J34" s="8"/>
-      <c r="K34" s="224" t="s">
-        <v>243</v>
-      </c>
-      <c r="L34" s="62"/>
+      <c r="K34" s="124" t="s">
+        <v>120</v>
+      </c>
+      <c r="L34" s="218" t="s">
+        <v>16</v>
+      </c>
       <c r="M34" s="8"/>
       <c r="R34" s="84"/>
       <c r="S34"/>
@@ -25036,16 +27727,18 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="239"/>
+      <c r="E35" s="252"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
       <c r="I35" s="30"/>
       <c r="J35" s="4"/>
-      <c r="K35" s="110" t="s">
-        <v>201</v>
-      </c>
-      <c r="L35" s="62"/>
+      <c r="K35" s="124" t="s">
+        <v>211</v>
+      </c>
+      <c r="L35" s="218" t="s">
+        <v>38</v>
+      </c>
       <c r="M35" s="13"/>
       <c r="R35" s="84"/>
       <c r="S35"/>
@@ -25056,7 +27749,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="241" t="s">
+      <c r="E36" s="253" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -25064,10 +27757,12 @@
       <c r="H36" s="97"/>
       <c r="I36" s="30"/>
       <c r="J36" s="4"/>
-      <c r="K36" s="110" t="s">
-        <v>141</v>
-      </c>
-      <c r="L36" s="8"/>
+      <c r="K36" s="124" t="s">
+        <v>212</v>
+      </c>
+      <c r="L36" s="218" t="s">
+        <v>205</v>
+      </c>
       <c r="M36" s="94"/>
       <c r="R36" s="84"/>
       <c r="S36"/>
@@ -25076,15 +27771,13 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="241"/>
+      <c r="E37" s="253"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
       <c r="I37" s="30"/>
       <c r="J37" s="100"/>
-      <c r="K37" s="110" t="s">
-        <v>150</v>
-      </c>
+      <c r="K37" s="8"/>
       <c r="L37" s="8"/>
       <c r="M37" s="94"/>
       <c r="R37" s="84"/>
@@ -25103,9 +27796,7 @@
       <c r="H38" s="30"/>
       <c r="I38" s="30"/>
       <c r="J38" s="6"/>
-      <c r="K38" s="124" t="s">
-        <v>120</v>
-      </c>
+      <c r="K38" s="8"/>
       <c r="L38" s="8"/>
       <c r="M38" s="2"/>
       <c r="R38" s="84"/>
@@ -25124,9 +27815,7 @@
       <c r="H39" s="103"/>
       <c r="I39" s="30"/>
       <c r="J39" s="6"/>
-      <c r="K39" s="124" t="s">
-        <v>211</v>
-      </c>
+      <c r="K39" s="8"/>
       <c r="L39" s="16"/>
       <c r="M39" s="2"/>
       <c r="S39"/>
@@ -25144,9 +27833,7 @@
       <c r="H40" s="103"/>
       <c r="I40" s="30"/>
       <c r="J40" s="6"/>
-      <c r="K40" s="124" t="s">
-        <v>212</v>
-      </c>
+      <c r="K40" s="8"/>
       <c r="L40" s="16"/>
       <c r="M40" s="105"/>
       <c r="S40"/>
@@ -25612,6 +28299,18 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="A16:A17"/>
@@ -25620,18 +28319,6 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="Q3:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/raw/D3.xlsx
+++ b/raw/D3.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7ADCC9-A251-4939-A210-780A803D34BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971B6A8C-AC8E-4944-AF4D-C9CB341F7F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30-2" sheetId="34" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="15-2" sheetId="41" r:id="rId8"/>
     <sheet name="16" sheetId="42" r:id="rId9"/>
     <sheet name="17" sheetId="43" r:id="rId10"/>
+    <sheet name="17-2" sheetId="44" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -150,6 +151,62 @@
       </text>
     </comment>
     <comment ref="H21" authorId="0" shapeId="0" xr:uid="{D7B936F9-5C1D-4D19-91FE-1CAA3AE7D317}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Алібек
+87012894507</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="H17" authorId="0" shapeId="0" xr:uid="{9C7CAB6F-AF20-440C-9EBD-CA5B15DEAEAD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Даулет
+87025167087</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H19" authorId="0" shapeId="0" xr:uid="{C8439274-2B6B-4780-92B1-6DA5EFDE26CC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Аслан
+87014988298</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{4D05B01B-D97E-4028-B035-581F1C24A551}">
       <text>
         <r>
           <rPr>
@@ -864,7 +921,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="245">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -2419,7 +2476,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="279">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3120,22 +3177,25 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3146,6 +3206,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3162,22 +3225,28 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3200,6 +3269,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -4397,21 +4475,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="246" t="s">
+      <c r="A1" s="265" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="246"/>
-      <c r="C1" s="246"/>
-      <c r="D1" s="246"/>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
-      <c r="G1" s="246"/>
-      <c r="H1" s="246"/>
-      <c r="I1" s="246"/>
-      <c r="J1" s="246"/>
-      <c r="K1" s="246"/>
-      <c r="L1" s="246"/>
-      <c r="M1" s="246"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4466,13 +4544,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="247" t="s">
+      <c r="D3" s="254" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="247" t="s">
+      <c r="F3" s="254" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -4484,24 +4562,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="245" t="s">
+      <c r="J3" s="260" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="248" t="s">
+      <c r="M3" s="261" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="256" t="s">
+      <c r="Q3" s="258" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="257"/>
+      <c r="R3" s="259"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="250" t="s">
+      <c r="T3" s="251" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="251"/>
+      <c r="U3" s="252"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -4513,20 +4591,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="247"/>
+      <c r="D4" s="254"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="247"/>
+      <c r="F4" s="254"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="245"/>
+      <c r="J4" s="260"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="248"/>
+      <c r="M4" s="261"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -4565,7 +4643,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="255" t="s">
+      <c r="F5" s="257" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -4573,7 +4651,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="247" t="s">
+      <c r="J5" s="254" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -4618,13 +4696,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="255"/>
+      <c r="F6" s="257"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="247"/>
+      <c r="J6" s="254"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -4670,13 +4748,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="245" t="s">
+      <c r="F7" s="260" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="254" t="s">
+      <c r="J7" s="256" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -4724,11 +4802,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="245"/>
+      <c r="F8" s="260"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="254"/>
+      <c r="J8" s="256"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -4772,7 +4850,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="255" t="s">
+      <c r="F9" s="257" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -4812,7 +4890,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="255"/>
+      <c r="F10" s="257"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -4937,7 +5015,7 @@
         <v>115</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="248" t="s">
+      <c r="H13" s="261" t="s">
         <v>82</v>
       </c>
       <c r="I13" s="30"/>
@@ -4976,7 +5054,7 @@
       <c r="F14" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="248"/>
+      <c r="H14" s="261"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -5011,7 +5089,7 @@
         <v>83</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="248" t="s">
+      <c r="H15" s="261" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="30"/>
@@ -5048,7 +5126,7 @@
         <v>81</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="248"/>
+      <c r="H16" s="261"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -5080,7 +5158,7 @@
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="258" t="s">
+      <c r="H17" s="262" t="s">
         <v>45</v>
       </c>
       <c r="I17" s="30"/>
@@ -5115,7 +5193,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="259"/>
+      <c r="H18" s="263"/>
       <c r="I18" s="30"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
@@ -5132,7 +5210,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="245" t="s">
+      <c r="H19" s="260" t="s">
         <v>85</v>
       </c>
       <c r="I19" s="30"/>
@@ -5157,7 +5235,7 @@
       <c r="E20" s="137"/>
       <c r="F20" s="8"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="245"/>
+      <c r="H20" s="260"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -5176,7 +5254,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="245" t="s">
+      <c r="H21" s="260" t="s">
         <v>84</v>
       </c>
       <c r="I21" s="30"/>
@@ -5193,7 +5271,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="137"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="245"/>
+      <c r="H22" s="260"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -5290,13 +5368,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="249" t="s">
+      <c r="A28" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="249"/>
-      <c r="C28" s="249"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
+      <c r="B28" s="266"/>
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
+      <c r="E28" s="266"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -5356,7 +5434,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="253" t="s">
+      <c r="E30" s="255" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -5390,7 +5468,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="253"/>
+      <c r="E31" s="255"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -5420,7 +5498,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="253" t="s">
+      <c r="E32" s="255" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="8"/>
@@ -5446,7 +5524,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="253"/>
+      <c r="E33" s="255"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
       <c r="I33" s="30"/>
@@ -5469,7 +5547,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="252" t="s">
+      <c r="E34" s="253" t="s">
         <v>133</v>
       </c>
       <c r="G34" s="8"/>
@@ -5490,7 +5568,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="252"/>
+      <c r="E35" s="253"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
       <c r="I35" s="30"/>
@@ -5509,7 +5587,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="253" t="s">
+      <c r="E36" s="255" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -5529,7 +5607,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="253"/>
+      <c r="E37" s="255"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -5996,7 +6074,7 @@
       <c r="S65"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A66" s="244" t="s">
+      <c r="A66" s="264" t="s">
         <v>139</v>
       </c>
       <c r="L66" s="119" t="s">
@@ -6008,7 +6086,7 @@
       <c r="S66"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A67" s="244"/>
+      <c r="A67" s="264"/>
       <c r="L67" s="119" t="s">
         <v>95</v>
       </c>
@@ -6060,6 +6138,14 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="J5:J6"/>
@@ -6075,14 +6161,6 @@
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="H17:H18"/>
     <mergeCell ref="H19:H20"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A28:E28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6999,21 +7077,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="246" t="s">
+      <c r="A1" s="265" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="246"/>
-      <c r="C1" s="246"/>
-      <c r="D1" s="246"/>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
-      <c r="G1" s="246"/>
-      <c r="H1" s="246"/>
-      <c r="I1" s="246"/>
-      <c r="J1" s="246"/>
-      <c r="K1" s="246"/>
-      <c r="L1" s="246"/>
-      <c r="M1" s="246"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -7072,7 +7150,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="247" t="s">
+      <c r="F3" s="254" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -7081,24 +7159,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="254" t="s">
+      <c r="J3" s="256" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="271" t="s">
+      <c r="M3" s="278" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="256" t="s">
+      <c r="Q3" s="258" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="257"/>
+      <c r="R3" s="259"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="250" t="s">
+      <c r="T3" s="251" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="251"/>
+      <c r="U3" s="252"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -7116,16 +7194,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="247"/>
+      <c r="F4" s="254"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="254"/>
+      <c r="J4" s="256"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="271"/>
+      <c r="M4" s="278"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -7164,7 +7242,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="255" t="s">
+      <c r="F5" s="257" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -7172,7 +7250,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="247" t="s">
+      <c r="J5" s="254" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -7217,13 +7295,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="255"/>
+      <c r="F6" s="257"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="247"/>
+      <c r="J6" s="254"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -7270,7 +7348,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="255" t="s">
+      <c r="F7" s="257" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -7322,7 +7400,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="255"/>
+      <c r="F8" s="257"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -7538,7 +7616,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="245" t="s">
+      <c r="H13" s="260" t="s">
         <v>121</v>
       </c>
       <c r="I13" s="30"/>
@@ -7574,7 +7652,7 @@
       <c r="F14" s="240" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="245"/>
+      <c r="H14" s="260"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -7607,7 +7685,7 @@
       <c r="E15" s="240"/>
       <c r="F15" s="8"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="245" t="s">
+      <c r="H15" s="260" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="30"/>
@@ -7636,7 +7714,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="245" t="s">
+      <c r="B16" s="260" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="8"/>
@@ -7644,7 +7722,7 @@
       <c r="E16" s="59"/>
       <c r="F16" s="8"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="245"/>
+      <c r="H16" s="260"/>
       <c r="I16" s="30"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
@@ -7671,13 +7749,13 @@
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
-      <c r="B17" s="245"/>
+      <c r="B17" s="260"/>
       <c r="C17" s="8"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="248" t="s">
+      <c r="H17" s="261" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -7712,7 +7790,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="248"/>
+      <c r="H18" s="261"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -7729,7 +7807,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="248" t="s">
+      <c r="H19" s="261" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -7754,7 +7832,7 @@
       <c r="E20" s="240"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="248"/>
+      <c r="H20" s="261"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -7773,7 +7851,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="248" t="s">
+      <c r="H21" s="261" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -7791,7 +7869,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="240"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="248"/>
+      <c r="H22" s="261"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -7888,13 +7966,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="249" t="s">
+      <c r="A28" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="249"/>
-      <c r="C28" s="249"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
+      <c r="B28" s="266"/>
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
+      <c r="E28" s="266"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -7954,7 +8032,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="253" t="s">
+      <c r="E30" s="255" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -7988,7 +8066,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="253"/>
+      <c r="E31" s="255"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -8015,7 +8093,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="253" t="s">
+      <c r="E32" s="255" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -8043,7 +8121,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="253"/>
+      <c r="E33" s="255"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -8067,7 +8145,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="252" t="s">
+      <c r="E34" s="253" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -8092,7 +8170,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="252"/>
+      <c r="E35" s="253"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -8114,7 +8192,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="253" t="s">
+      <c r="E36" s="255" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -8136,7 +8214,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="253"/>
+      <c r="E37" s="255"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -8668,6 +8746,18 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="H15:H16"/>
@@ -8676,18 +8766,2611 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
-    <mergeCell ref="T3:U3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7E415CA-04DB-4992-97B1-F5E37849C194}">
+  <dimension ref="A1:W72"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" style="98" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" style="25" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" style="25" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" style="25" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" customWidth="1"/>
+    <col min="14" max="14" width="21.26953125" customWidth="1"/>
+    <col min="15" max="15" width="9.7265625" customWidth="1"/>
+    <col min="16" max="16" width="7.7265625" customWidth="1"/>
+    <col min="17" max="17" width="6.453125" customWidth="1"/>
+    <col min="18" max="18" width="7.81640625" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" style="84" customWidth="1"/>
+    <col min="20" max="20" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="257" max="260" width="14.453125" customWidth="1"/>
+    <col min="261" max="261" width="15.453125" customWidth="1"/>
+    <col min="262" max="262" width="14.54296875" customWidth="1"/>
+    <col min="263" max="263" width="15.26953125" customWidth="1"/>
+    <col min="264" max="265" width="14.453125" customWidth="1"/>
+    <col min="266" max="266" width="13.1796875" customWidth="1"/>
+    <col min="267" max="269" width="14.453125" customWidth="1"/>
+    <col min="270" max="270" width="15.81640625" customWidth="1"/>
+    <col min="271" max="271" width="7.81640625" customWidth="1"/>
+    <col min="272" max="272" width="5.453125" customWidth="1"/>
+    <col min="273" max="273" width="6.453125" customWidth="1"/>
+    <col min="274" max="274" width="7.81640625" customWidth="1"/>
+    <col min="275" max="275" width="3" customWidth="1"/>
+    <col min="276" max="276" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="513" max="516" width="14.453125" customWidth="1"/>
+    <col min="517" max="517" width="15.453125" customWidth="1"/>
+    <col min="518" max="518" width="14.54296875" customWidth="1"/>
+    <col min="519" max="519" width="15.26953125" customWidth="1"/>
+    <col min="520" max="521" width="14.453125" customWidth="1"/>
+    <col min="522" max="522" width="13.1796875" customWidth="1"/>
+    <col min="523" max="525" width="14.453125" customWidth="1"/>
+    <col min="526" max="526" width="15.81640625" customWidth="1"/>
+    <col min="527" max="527" width="7.81640625" customWidth="1"/>
+    <col min="528" max="528" width="5.453125" customWidth="1"/>
+    <col min="529" max="529" width="6.453125" customWidth="1"/>
+    <col min="530" max="530" width="7.81640625" customWidth="1"/>
+    <col min="531" max="531" width="3" customWidth="1"/>
+    <col min="532" max="532" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="769" max="772" width="14.453125" customWidth="1"/>
+    <col min="773" max="773" width="15.453125" customWidth="1"/>
+    <col min="774" max="774" width="14.54296875" customWidth="1"/>
+    <col min="775" max="775" width="15.26953125" customWidth="1"/>
+    <col min="776" max="777" width="14.453125" customWidth="1"/>
+    <col min="778" max="778" width="13.1796875" customWidth="1"/>
+    <col min="779" max="781" width="14.453125" customWidth="1"/>
+    <col min="782" max="782" width="15.81640625" customWidth="1"/>
+    <col min="783" max="783" width="7.81640625" customWidth="1"/>
+    <col min="784" max="784" width="5.453125" customWidth="1"/>
+    <col min="785" max="785" width="6.453125" customWidth="1"/>
+    <col min="786" max="786" width="7.81640625" customWidth="1"/>
+    <col min="787" max="787" width="3" customWidth="1"/>
+    <col min="788" max="788" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1025" max="1028" width="14.453125" customWidth="1"/>
+    <col min="1029" max="1029" width="15.453125" customWidth="1"/>
+    <col min="1030" max="1030" width="14.54296875" customWidth="1"/>
+    <col min="1031" max="1031" width="15.26953125" customWidth="1"/>
+    <col min="1032" max="1033" width="14.453125" customWidth="1"/>
+    <col min="1034" max="1034" width="13.1796875" customWidth="1"/>
+    <col min="1035" max="1037" width="14.453125" customWidth="1"/>
+    <col min="1038" max="1038" width="15.81640625" customWidth="1"/>
+    <col min="1039" max="1039" width="7.81640625" customWidth="1"/>
+    <col min="1040" max="1040" width="5.453125" customWidth="1"/>
+    <col min="1041" max="1041" width="6.453125" customWidth="1"/>
+    <col min="1042" max="1042" width="7.81640625" customWidth="1"/>
+    <col min="1043" max="1043" width="3" customWidth="1"/>
+    <col min="1044" max="1044" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1281" max="1284" width="14.453125" customWidth="1"/>
+    <col min="1285" max="1285" width="15.453125" customWidth="1"/>
+    <col min="1286" max="1286" width="14.54296875" customWidth="1"/>
+    <col min="1287" max="1287" width="15.26953125" customWidth="1"/>
+    <col min="1288" max="1289" width="14.453125" customWidth="1"/>
+    <col min="1290" max="1290" width="13.1796875" customWidth="1"/>
+    <col min="1291" max="1293" width="14.453125" customWidth="1"/>
+    <col min="1294" max="1294" width="15.81640625" customWidth="1"/>
+    <col min="1295" max="1295" width="7.81640625" customWidth="1"/>
+    <col min="1296" max="1296" width="5.453125" customWidth="1"/>
+    <col min="1297" max="1297" width="6.453125" customWidth="1"/>
+    <col min="1298" max="1298" width="7.81640625" customWidth="1"/>
+    <col min="1299" max="1299" width="3" customWidth="1"/>
+    <col min="1300" max="1300" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1537" max="1540" width="14.453125" customWidth="1"/>
+    <col min="1541" max="1541" width="15.453125" customWidth="1"/>
+    <col min="1542" max="1542" width="14.54296875" customWidth="1"/>
+    <col min="1543" max="1543" width="15.26953125" customWidth="1"/>
+    <col min="1544" max="1545" width="14.453125" customWidth="1"/>
+    <col min="1546" max="1546" width="13.1796875" customWidth="1"/>
+    <col min="1547" max="1549" width="14.453125" customWidth="1"/>
+    <col min="1550" max="1550" width="15.81640625" customWidth="1"/>
+    <col min="1551" max="1551" width="7.81640625" customWidth="1"/>
+    <col min="1552" max="1552" width="5.453125" customWidth="1"/>
+    <col min="1553" max="1553" width="6.453125" customWidth="1"/>
+    <col min="1554" max="1554" width="7.81640625" customWidth="1"/>
+    <col min="1555" max="1555" width="3" customWidth="1"/>
+    <col min="1556" max="1556" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1793" max="1796" width="14.453125" customWidth="1"/>
+    <col min="1797" max="1797" width="15.453125" customWidth="1"/>
+    <col min="1798" max="1798" width="14.54296875" customWidth="1"/>
+    <col min="1799" max="1799" width="15.26953125" customWidth="1"/>
+    <col min="1800" max="1801" width="14.453125" customWidth="1"/>
+    <col min="1802" max="1802" width="13.1796875" customWidth="1"/>
+    <col min="1803" max="1805" width="14.453125" customWidth="1"/>
+    <col min="1806" max="1806" width="15.81640625" customWidth="1"/>
+    <col min="1807" max="1807" width="7.81640625" customWidth="1"/>
+    <col min="1808" max="1808" width="5.453125" customWidth="1"/>
+    <col min="1809" max="1809" width="6.453125" customWidth="1"/>
+    <col min="1810" max="1810" width="7.81640625" customWidth="1"/>
+    <col min="1811" max="1811" width="3" customWidth="1"/>
+    <col min="1812" max="1812" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2049" max="2052" width="14.453125" customWidth="1"/>
+    <col min="2053" max="2053" width="15.453125" customWidth="1"/>
+    <col min="2054" max="2054" width="14.54296875" customWidth="1"/>
+    <col min="2055" max="2055" width="15.26953125" customWidth="1"/>
+    <col min="2056" max="2057" width="14.453125" customWidth="1"/>
+    <col min="2058" max="2058" width="13.1796875" customWidth="1"/>
+    <col min="2059" max="2061" width="14.453125" customWidth="1"/>
+    <col min="2062" max="2062" width="15.81640625" customWidth="1"/>
+    <col min="2063" max="2063" width="7.81640625" customWidth="1"/>
+    <col min="2064" max="2064" width="5.453125" customWidth="1"/>
+    <col min="2065" max="2065" width="6.453125" customWidth="1"/>
+    <col min="2066" max="2066" width="7.81640625" customWidth="1"/>
+    <col min="2067" max="2067" width="3" customWidth="1"/>
+    <col min="2068" max="2068" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2305" max="2308" width="14.453125" customWidth="1"/>
+    <col min="2309" max="2309" width="15.453125" customWidth="1"/>
+    <col min="2310" max="2310" width="14.54296875" customWidth="1"/>
+    <col min="2311" max="2311" width="15.26953125" customWidth="1"/>
+    <col min="2312" max="2313" width="14.453125" customWidth="1"/>
+    <col min="2314" max="2314" width="13.1796875" customWidth="1"/>
+    <col min="2315" max="2317" width="14.453125" customWidth="1"/>
+    <col min="2318" max="2318" width="15.81640625" customWidth="1"/>
+    <col min="2319" max="2319" width="7.81640625" customWidth="1"/>
+    <col min="2320" max="2320" width="5.453125" customWidth="1"/>
+    <col min="2321" max="2321" width="6.453125" customWidth="1"/>
+    <col min="2322" max="2322" width="7.81640625" customWidth="1"/>
+    <col min="2323" max="2323" width="3" customWidth="1"/>
+    <col min="2324" max="2324" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2561" max="2564" width="14.453125" customWidth="1"/>
+    <col min="2565" max="2565" width="15.453125" customWidth="1"/>
+    <col min="2566" max="2566" width="14.54296875" customWidth="1"/>
+    <col min="2567" max="2567" width="15.26953125" customWidth="1"/>
+    <col min="2568" max="2569" width="14.453125" customWidth="1"/>
+    <col min="2570" max="2570" width="13.1796875" customWidth="1"/>
+    <col min="2571" max="2573" width="14.453125" customWidth="1"/>
+    <col min="2574" max="2574" width="15.81640625" customWidth="1"/>
+    <col min="2575" max="2575" width="7.81640625" customWidth="1"/>
+    <col min="2576" max="2576" width="5.453125" customWidth="1"/>
+    <col min="2577" max="2577" width="6.453125" customWidth="1"/>
+    <col min="2578" max="2578" width="7.81640625" customWidth="1"/>
+    <col min="2579" max="2579" width="3" customWidth="1"/>
+    <col min="2580" max="2580" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2817" max="2820" width="14.453125" customWidth="1"/>
+    <col min="2821" max="2821" width="15.453125" customWidth="1"/>
+    <col min="2822" max="2822" width="14.54296875" customWidth="1"/>
+    <col min="2823" max="2823" width="15.26953125" customWidth="1"/>
+    <col min="2824" max="2825" width="14.453125" customWidth="1"/>
+    <col min="2826" max="2826" width="13.1796875" customWidth="1"/>
+    <col min="2827" max="2829" width="14.453125" customWidth="1"/>
+    <col min="2830" max="2830" width="15.81640625" customWidth="1"/>
+    <col min="2831" max="2831" width="7.81640625" customWidth="1"/>
+    <col min="2832" max="2832" width="5.453125" customWidth="1"/>
+    <col min="2833" max="2833" width="6.453125" customWidth="1"/>
+    <col min="2834" max="2834" width="7.81640625" customWidth="1"/>
+    <col min="2835" max="2835" width="3" customWidth="1"/>
+    <col min="2836" max="2836" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3073" max="3076" width="14.453125" customWidth="1"/>
+    <col min="3077" max="3077" width="15.453125" customWidth="1"/>
+    <col min="3078" max="3078" width="14.54296875" customWidth="1"/>
+    <col min="3079" max="3079" width="15.26953125" customWidth="1"/>
+    <col min="3080" max="3081" width="14.453125" customWidth="1"/>
+    <col min="3082" max="3082" width="13.1796875" customWidth="1"/>
+    <col min="3083" max="3085" width="14.453125" customWidth="1"/>
+    <col min="3086" max="3086" width="15.81640625" customWidth="1"/>
+    <col min="3087" max="3087" width="7.81640625" customWidth="1"/>
+    <col min="3088" max="3088" width="5.453125" customWidth="1"/>
+    <col min="3089" max="3089" width="6.453125" customWidth="1"/>
+    <col min="3090" max="3090" width="7.81640625" customWidth="1"/>
+    <col min="3091" max="3091" width="3" customWidth="1"/>
+    <col min="3092" max="3092" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3329" max="3332" width="14.453125" customWidth="1"/>
+    <col min="3333" max="3333" width="15.453125" customWidth="1"/>
+    <col min="3334" max="3334" width="14.54296875" customWidth="1"/>
+    <col min="3335" max="3335" width="15.26953125" customWidth="1"/>
+    <col min="3336" max="3337" width="14.453125" customWidth="1"/>
+    <col min="3338" max="3338" width="13.1796875" customWidth="1"/>
+    <col min="3339" max="3341" width="14.453125" customWidth="1"/>
+    <col min="3342" max="3342" width="15.81640625" customWidth="1"/>
+    <col min="3343" max="3343" width="7.81640625" customWidth="1"/>
+    <col min="3344" max="3344" width="5.453125" customWidth="1"/>
+    <col min="3345" max="3345" width="6.453125" customWidth="1"/>
+    <col min="3346" max="3346" width="7.81640625" customWidth="1"/>
+    <col min="3347" max="3347" width="3" customWidth="1"/>
+    <col min="3348" max="3348" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3585" max="3588" width="14.453125" customWidth="1"/>
+    <col min="3589" max="3589" width="15.453125" customWidth="1"/>
+    <col min="3590" max="3590" width="14.54296875" customWidth="1"/>
+    <col min="3591" max="3591" width="15.26953125" customWidth="1"/>
+    <col min="3592" max="3593" width="14.453125" customWidth="1"/>
+    <col min="3594" max="3594" width="13.1796875" customWidth="1"/>
+    <col min="3595" max="3597" width="14.453125" customWidth="1"/>
+    <col min="3598" max="3598" width="15.81640625" customWidth="1"/>
+    <col min="3599" max="3599" width="7.81640625" customWidth="1"/>
+    <col min="3600" max="3600" width="5.453125" customWidth="1"/>
+    <col min="3601" max="3601" width="6.453125" customWidth="1"/>
+    <col min="3602" max="3602" width="7.81640625" customWidth="1"/>
+    <col min="3603" max="3603" width="3" customWidth="1"/>
+    <col min="3604" max="3604" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3841" max="3844" width="14.453125" customWidth="1"/>
+    <col min="3845" max="3845" width="15.453125" customWidth="1"/>
+    <col min="3846" max="3846" width="14.54296875" customWidth="1"/>
+    <col min="3847" max="3847" width="15.26953125" customWidth="1"/>
+    <col min="3848" max="3849" width="14.453125" customWidth="1"/>
+    <col min="3850" max="3850" width="13.1796875" customWidth="1"/>
+    <col min="3851" max="3853" width="14.453125" customWidth="1"/>
+    <col min="3854" max="3854" width="15.81640625" customWidth="1"/>
+    <col min="3855" max="3855" width="7.81640625" customWidth="1"/>
+    <col min="3856" max="3856" width="5.453125" customWidth="1"/>
+    <col min="3857" max="3857" width="6.453125" customWidth="1"/>
+    <col min="3858" max="3858" width="7.81640625" customWidth="1"/>
+    <col min="3859" max="3859" width="3" customWidth="1"/>
+    <col min="3860" max="3860" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4097" max="4100" width="14.453125" customWidth="1"/>
+    <col min="4101" max="4101" width="15.453125" customWidth="1"/>
+    <col min="4102" max="4102" width="14.54296875" customWidth="1"/>
+    <col min="4103" max="4103" width="15.26953125" customWidth="1"/>
+    <col min="4104" max="4105" width="14.453125" customWidth="1"/>
+    <col min="4106" max="4106" width="13.1796875" customWidth="1"/>
+    <col min="4107" max="4109" width="14.453125" customWidth="1"/>
+    <col min="4110" max="4110" width="15.81640625" customWidth="1"/>
+    <col min="4111" max="4111" width="7.81640625" customWidth="1"/>
+    <col min="4112" max="4112" width="5.453125" customWidth="1"/>
+    <col min="4113" max="4113" width="6.453125" customWidth="1"/>
+    <col min="4114" max="4114" width="7.81640625" customWidth="1"/>
+    <col min="4115" max="4115" width="3" customWidth="1"/>
+    <col min="4116" max="4116" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4353" max="4356" width="14.453125" customWidth="1"/>
+    <col min="4357" max="4357" width="15.453125" customWidth="1"/>
+    <col min="4358" max="4358" width="14.54296875" customWidth="1"/>
+    <col min="4359" max="4359" width="15.26953125" customWidth="1"/>
+    <col min="4360" max="4361" width="14.453125" customWidth="1"/>
+    <col min="4362" max="4362" width="13.1796875" customWidth="1"/>
+    <col min="4363" max="4365" width="14.453125" customWidth="1"/>
+    <col min="4366" max="4366" width="15.81640625" customWidth="1"/>
+    <col min="4367" max="4367" width="7.81640625" customWidth="1"/>
+    <col min="4368" max="4368" width="5.453125" customWidth="1"/>
+    <col min="4369" max="4369" width="6.453125" customWidth="1"/>
+    <col min="4370" max="4370" width="7.81640625" customWidth="1"/>
+    <col min="4371" max="4371" width="3" customWidth="1"/>
+    <col min="4372" max="4372" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4609" max="4612" width="14.453125" customWidth="1"/>
+    <col min="4613" max="4613" width="15.453125" customWidth="1"/>
+    <col min="4614" max="4614" width="14.54296875" customWidth="1"/>
+    <col min="4615" max="4615" width="15.26953125" customWidth="1"/>
+    <col min="4616" max="4617" width="14.453125" customWidth="1"/>
+    <col min="4618" max="4618" width="13.1796875" customWidth="1"/>
+    <col min="4619" max="4621" width="14.453125" customWidth="1"/>
+    <col min="4622" max="4622" width="15.81640625" customWidth="1"/>
+    <col min="4623" max="4623" width="7.81640625" customWidth="1"/>
+    <col min="4624" max="4624" width="5.453125" customWidth="1"/>
+    <col min="4625" max="4625" width="6.453125" customWidth="1"/>
+    <col min="4626" max="4626" width="7.81640625" customWidth="1"/>
+    <col min="4627" max="4627" width="3" customWidth="1"/>
+    <col min="4628" max="4628" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4865" max="4868" width="14.453125" customWidth="1"/>
+    <col min="4869" max="4869" width="15.453125" customWidth="1"/>
+    <col min="4870" max="4870" width="14.54296875" customWidth="1"/>
+    <col min="4871" max="4871" width="15.26953125" customWidth="1"/>
+    <col min="4872" max="4873" width="14.453125" customWidth="1"/>
+    <col min="4874" max="4874" width="13.1796875" customWidth="1"/>
+    <col min="4875" max="4877" width="14.453125" customWidth="1"/>
+    <col min="4878" max="4878" width="15.81640625" customWidth="1"/>
+    <col min="4879" max="4879" width="7.81640625" customWidth="1"/>
+    <col min="4880" max="4880" width="5.453125" customWidth="1"/>
+    <col min="4881" max="4881" width="6.453125" customWidth="1"/>
+    <col min="4882" max="4882" width="7.81640625" customWidth="1"/>
+    <col min="4883" max="4883" width="3" customWidth="1"/>
+    <col min="4884" max="4884" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5121" max="5124" width="14.453125" customWidth="1"/>
+    <col min="5125" max="5125" width="15.453125" customWidth="1"/>
+    <col min="5126" max="5126" width="14.54296875" customWidth="1"/>
+    <col min="5127" max="5127" width="15.26953125" customWidth="1"/>
+    <col min="5128" max="5129" width="14.453125" customWidth="1"/>
+    <col min="5130" max="5130" width="13.1796875" customWidth="1"/>
+    <col min="5131" max="5133" width="14.453125" customWidth="1"/>
+    <col min="5134" max="5134" width="15.81640625" customWidth="1"/>
+    <col min="5135" max="5135" width="7.81640625" customWidth="1"/>
+    <col min="5136" max="5136" width="5.453125" customWidth="1"/>
+    <col min="5137" max="5137" width="6.453125" customWidth="1"/>
+    <col min="5138" max="5138" width="7.81640625" customWidth="1"/>
+    <col min="5139" max="5139" width="3" customWidth="1"/>
+    <col min="5140" max="5140" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5377" max="5380" width="14.453125" customWidth="1"/>
+    <col min="5381" max="5381" width="15.453125" customWidth="1"/>
+    <col min="5382" max="5382" width="14.54296875" customWidth="1"/>
+    <col min="5383" max="5383" width="15.26953125" customWidth="1"/>
+    <col min="5384" max="5385" width="14.453125" customWidth="1"/>
+    <col min="5386" max="5386" width="13.1796875" customWidth="1"/>
+    <col min="5387" max="5389" width="14.453125" customWidth="1"/>
+    <col min="5390" max="5390" width="15.81640625" customWidth="1"/>
+    <col min="5391" max="5391" width="7.81640625" customWidth="1"/>
+    <col min="5392" max="5392" width="5.453125" customWidth="1"/>
+    <col min="5393" max="5393" width="6.453125" customWidth="1"/>
+    <col min="5394" max="5394" width="7.81640625" customWidth="1"/>
+    <col min="5395" max="5395" width="3" customWidth="1"/>
+    <col min="5396" max="5396" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5633" max="5636" width="14.453125" customWidth="1"/>
+    <col min="5637" max="5637" width="15.453125" customWidth="1"/>
+    <col min="5638" max="5638" width="14.54296875" customWidth="1"/>
+    <col min="5639" max="5639" width="15.26953125" customWidth="1"/>
+    <col min="5640" max="5641" width="14.453125" customWidth="1"/>
+    <col min="5642" max="5642" width="13.1796875" customWidth="1"/>
+    <col min="5643" max="5645" width="14.453125" customWidth="1"/>
+    <col min="5646" max="5646" width="15.81640625" customWidth="1"/>
+    <col min="5647" max="5647" width="7.81640625" customWidth="1"/>
+    <col min="5648" max="5648" width="5.453125" customWidth="1"/>
+    <col min="5649" max="5649" width="6.453125" customWidth="1"/>
+    <col min="5650" max="5650" width="7.81640625" customWidth="1"/>
+    <col min="5651" max="5651" width="3" customWidth="1"/>
+    <col min="5652" max="5652" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5889" max="5892" width="14.453125" customWidth="1"/>
+    <col min="5893" max="5893" width="15.453125" customWidth="1"/>
+    <col min="5894" max="5894" width="14.54296875" customWidth="1"/>
+    <col min="5895" max="5895" width="15.26953125" customWidth="1"/>
+    <col min="5896" max="5897" width="14.453125" customWidth="1"/>
+    <col min="5898" max="5898" width="13.1796875" customWidth="1"/>
+    <col min="5899" max="5901" width="14.453125" customWidth="1"/>
+    <col min="5902" max="5902" width="15.81640625" customWidth="1"/>
+    <col min="5903" max="5903" width="7.81640625" customWidth="1"/>
+    <col min="5904" max="5904" width="5.453125" customWidth="1"/>
+    <col min="5905" max="5905" width="6.453125" customWidth="1"/>
+    <col min="5906" max="5906" width="7.81640625" customWidth="1"/>
+    <col min="5907" max="5907" width="3" customWidth="1"/>
+    <col min="5908" max="5908" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6145" max="6148" width="14.453125" customWidth="1"/>
+    <col min="6149" max="6149" width="15.453125" customWidth="1"/>
+    <col min="6150" max="6150" width="14.54296875" customWidth="1"/>
+    <col min="6151" max="6151" width="15.26953125" customWidth="1"/>
+    <col min="6152" max="6153" width="14.453125" customWidth="1"/>
+    <col min="6154" max="6154" width="13.1796875" customWidth="1"/>
+    <col min="6155" max="6157" width="14.453125" customWidth="1"/>
+    <col min="6158" max="6158" width="15.81640625" customWidth="1"/>
+    <col min="6159" max="6159" width="7.81640625" customWidth="1"/>
+    <col min="6160" max="6160" width="5.453125" customWidth="1"/>
+    <col min="6161" max="6161" width="6.453125" customWidth="1"/>
+    <col min="6162" max="6162" width="7.81640625" customWidth="1"/>
+    <col min="6163" max="6163" width="3" customWidth="1"/>
+    <col min="6164" max="6164" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6401" max="6404" width="14.453125" customWidth="1"/>
+    <col min="6405" max="6405" width="15.453125" customWidth="1"/>
+    <col min="6406" max="6406" width="14.54296875" customWidth="1"/>
+    <col min="6407" max="6407" width="15.26953125" customWidth="1"/>
+    <col min="6408" max="6409" width="14.453125" customWidth="1"/>
+    <col min="6410" max="6410" width="13.1796875" customWidth="1"/>
+    <col min="6411" max="6413" width="14.453125" customWidth="1"/>
+    <col min="6414" max="6414" width="15.81640625" customWidth="1"/>
+    <col min="6415" max="6415" width="7.81640625" customWidth="1"/>
+    <col min="6416" max="6416" width="5.453125" customWidth="1"/>
+    <col min="6417" max="6417" width="6.453125" customWidth="1"/>
+    <col min="6418" max="6418" width="7.81640625" customWidth="1"/>
+    <col min="6419" max="6419" width="3" customWidth="1"/>
+    <col min="6420" max="6420" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6657" max="6660" width="14.453125" customWidth="1"/>
+    <col min="6661" max="6661" width="15.453125" customWidth="1"/>
+    <col min="6662" max="6662" width="14.54296875" customWidth="1"/>
+    <col min="6663" max="6663" width="15.26953125" customWidth="1"/>
+    <col min="6664" max="6665" width="14.453125" customWidth="1"/>
+    <col min="6666" max="6666" width="13.1796875" customWidth="1"/>
+    <col min="6667" max="6669" width="14.453125" customWidth="1"/>
+    <col min="6670" max="6670" width="15.81640625" customWidth="1"/>
+    <col min="6671" max="6671" width="7.81640625" customWidth="1"/>
+    <col min="6672" max="6672" width="5.453125" customWidth="1"/>
+    <col min="6673" max="6673" width="6.453125" customWidth="1"/>
+    <col min="6674" max="6674" width="7.81640625" customWidth="1"/>
+    <col min="6675" max="6675" width="3" customWidth="1"/>
+    <col min="6676" max="6676" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6913" max="6916" width="14.453125" customWidth="1"/>
+    <col min="6917" max="6917" width="15.453125" customWidth="1"/>
+    <col min="6918" max="6918" width="14.54296875" customWidth="1"/>
+    <col min="6919" max="6919" width="15.26953125" customWidth="1"/>
+    <col min="6920" max="6921" width="14.453125" customWidth="1"/>
+    <col min="6922" max="6922" width="13.1796875" customWidth="1"/>
+    <col min="6923" max="6925" width="14.453125" customWidth="1"/>
+    <col min="6926" max="6926" width="15.81640625" customWidth="1"/>
+    <col min="6927" max="6927" width="7.81640625" customWidth="1"/>
+    <col min="6928" max="6928" width="5.453125" customWidth="1"/>
+    <col min="6929" max="6929" width="6.453125" customWidth="1"/>
+    <col min="6930" max="6930" width="7.81640625" customWidth="1"/>
+    <col min="6931" max="6931" width="3" customWidth="1"/>
+    <col min="6932" max="6932" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7169" max="7172" width="14.453125" customWidth="1"/>
+    <col min="7173" max="7173" width="15.453125" customWidth="1"/>
+    <col min="7174" max="7174" width="14.54296875" customWidth="1"/>
+    <col min="7175" max="7175" width="15.26953125" customWidth="1"/>
+    <col min="7176" max="7177" width="14.453125" customWidth="1"/>
+    <col min="7178" max="7178" width="13.1796875" customWidth="1"/>
+    <col min="7179" max="7181" width="14.453125" customWidth="1"/>
+    <col min="7182" max="7182" width="15.81640625" customWidth="1"/>
+    <col min="7183" max="7183" width="7.81640625" customWidth="1"/>
+    <col min="7184" max="7184" width="5.453125" customWidth="1"/>
+    <col min="7185" max="7185" width="6.453125" customWidth="1"/>
+    <col min="7186" max="7186" width="7.81640625" customWidth="1"/>
+    <col min="7187" max="7187" width="3" customWidth="1"/>
+    <col min="7188" max="7188" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7425" max="7428" width="14.453125" customWidth="1"/>
+    <col min="7429" max="7429" width="15.453125" customWidth="1"/>
+    <col min="7430" max="7430" width="14.54296875" customWidth="1"/>
+    <col min="7431" max="7431" width="15.26953125" customWidth="1"/>
+    <col min="7432" max="7433" width="14.453125" customWidth="1"/>
+    <col min="7434" max="7434" width="13.1796875" customWidth="1"/>
+    <col min="7435" max="7437" width="14.453125" customWidth="1"/>
+    <col min="7438" max="7438" width="15.81640625" customWidth="1"/>
+    <col min="7439" max="7439" width="7.81640625" customWidth="1"/>
+    <col min="7440" max="7440" width="5.453125" customWidth="1"/>
+    <col min="7441" max="7441" width="6.453125" customWidth="1"/>
+    <col min="7442" max="7442" width="7.81640625" customWidth="1"/>
+    <col min="7443" max="7443" width="3" customWidth="1"/>
+    <col min="7444" max="7444" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7681" max="7684" width="14.453125" customWidth="1"/>
+    <col min="7685" max="7685" width="15.453125" customWidth="1"/>
+    <col min="7686" max="7686" width="14.54296875" customWidth="1"/>
+    <col min="7687" max="7687" width="15.26953125" customWidth="1"/>
+    <col min="7688" max="7689" width="14.453125" customWidth="1"/>
+    <col min="7690" max="7690" width="13.1796875" customWidth="1"/>
+    <col min="7691" max="7693" width="14.453125" customWidth="1"/>
+    <col min="7694" max="7694" width="15.81640625" customWidth="1"/>
+    <col min="7695" max="7695" width="7.81640625" customWidth="1"/>
+    <col min="7696" max="7696" width="5.453125" customWidth="1"/>
+    <col min="7697" max="7697" width="6.453125" customWidth="1"/>
+    <col min="7698" max="7698" width="7.81640625" customWidth="1"/>
+    <col min="7699" max="7699" width="3" customWidth="1"/>
+    <col min="7700" max="7700" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7937" max="7940" width="14.453125" customWidth="1"/>
+    <col min="7941" max="7941" width="15.453125" customWidth="1"/>
+    <col min="7942" max="7942" width="14.54296875" customWidth="1"/>
+    <col min="7943" max="7943" width="15.26953125" customWidth="1"/>
+    <col min="7944" max="7945" width="14.453125" customWidth="1"/>
+    <col min="7946" max="7946" width="13.1796875" customWidth="1"/>
+    <col min="7947" max="7949" width="14.453125" customWidth="1"/>
+    <col min="7950" max="7950" width="15.81640625" customWidth="1"/>
+    <col min="7951" max="7951" width="7.81640625" customWidth="1"/>
+    <col min="7952" max="7952" width="5.453125" customWidth="1"/>
+    <col min="7953" max="7953" width="6.453125" customWidth="1"/>
+    <col min="7954" max="7954" width="7.81640625" customWidth="1"/>
+    <col min="7955" max="7955" width="3" customWidth="1"/>
+    <col min="7956" max="7956" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8193" max="8196" width="14.453125" customWidth="1"/>
+    <col min="8197" max="8197" width="15.453125" customWidth="1"/>
+    <col min="8198" max="8198" width="14.54296875" customWidth="1"/>
+    <col min="8199" max="8199" width="15.26953125" customWidth="1"/>
+    <col min="8200" max="8201" width="14.453125" customWidth="1"/>
+    <col min="8202" max="8202" width="13.1796875" customWidth="1"/>
+    <col min="8203" max="8205" width="14.453125" customWidth="1"/>
+    <col min="8206" max="8206" width="15.81640625" customWidth="1"/>
+    <col min="8207" max="8207" width="7.81640625" customWidth="1"/>
+    <col min="8208" max="8208" width="5.453125" customWidth="1"/>
+    <col min="8209" max="8209" width="6.453125" customWidth="1"/>
+    <col min="8210" max="8210" width="7.81640625" customWidth="1"/>
+    <col min="8211" max="8211" width="3" customWidth="1"/>
+    <col min="8212" max="8212" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8449" max="8452" width="14.453125" customWidth="1"/>
+    <col min="8453" max="8453" width="15.453125" customWidth="1"/>
+    <col min="8454" max="8454" width="14.54296875" customWidth="1"/>
+    <col min="8455" max="8455" width="15.26953125" customWidth="1"/>
+    <col min="8456" max="8457" width="14.453125" customWidth="1"/>
+    <col min="8458" max="8458" width="13.1796875" customWidth="1"/>
+    <col min="8459" max="8461" width="14.453125" customWidth="1"/>
+    <col min="8462" max="8462" width="15.81640625" customWidth="1"/>
+    <col min="8463" max="8463" width="7.81640625" customWidth="1"/>
+    <col min="8464" max="8464" width="5.453125" customWidth="1"/>
+    <col min="8465" max="8465" width="6.453125" customWidth="1"/>
+    <col min="8466" max="8466" width="7.81640625" customWidth="1"/>
+    <col min="8467" max="8467" width="3" customWidth="1"/>
+    <col min="8468" max="8468" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8705" max="8708" width="14.453125" customWidth="1"/>
+    <col min="8709" max="8709" width="15.453125" customWidth="1"/>
+    <col min="8710" max="8710" width="14.54296875" customWidth="1"/>
+    <col min="8711" max="8711" width="15.26953125" customWidth="1"/>
+    <col min="8712" max="8713" width="14.453125" customWidth="1"/>
+    <col min="8714" max="8714" width="13.1796875" customWidth="1"/>
+    <col min="8715" max="8717" width="14.453125" customWidth="1"/>
+    <col min="8718" max="8718" width="15.81640625" customWidth="1"/>
+    <col min="8719" max="8719" width="7.81640625" customWidth="1"/>
+    <col min="8720" max="8720" width="5.453125" customWidth="1"/>
+    <col min="8721" max="8721" width="6.453125" customWidth="1"/>
+    <col min="8722" max="8722" width="7.81640625" customWidth="1"/>
+    <col min="8723" max="8723" width="3" customWidth="1"/>
+    <col min="8724" max="8724" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8961" max="8964" width="14.453125" customWidth="1"/>
+    <col min="8965" max="8965" width="15.453125" customWidth="1"/>
+    <col min="8966" max="8966" width="14.54296875" customWidth="1"/>
+    <col min="8967" max="8967" width="15.26953125" customWidth="1"/>
+    <col min="8968" max="8969" width="14.453125" customWidth="1"/>
+    <col min="8970" max="8970" width="13.1796875" customWidth="1"/>
+    <col min="8971" max="8973" width="14.453125" customWidth="1"/>
+    <col min="8974" max="8974" width="15.81640625" customWidth="1"/>
+    <col min="8975" max="8975" width="7.81640625" customWidth="1"/>
+    <col min="8976" max="8976" width="5.453125" customWidth="1"/>
+    <col min="8977" max="8977" width="6.453125" customWidth="1"/>
+    <col min="8978" max="8978" width="7.81640625" customWidth="1"/>
+    <col min="8979" max="8979" width="3" customWidth="1"/>
+    <col min="8980" max="8980" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9217" max="9220" width="14.453125" customWidth="1"/>
+    <col min="9221" max="9221" width="15.453125" customWidth="1"/>
+    <col min="9222" max="9222" width="14.54296875" customWidth="1"/>
+    <col min="9223" max="9223" width="15.26953125" customWidth="1"/>
+    <col min="9224" max="9225" width="14.453125" customWidth="1"/>
+    <col min="9226" max="9226" width="13.1796875" customWidth="1"/>
+    <col min="9227" max="9229" width="14.453125" customWidth="1"/>
+    <col min="9230" max="9230" width="15.81640625" customWidth="1"/>
+    <col min="9231" max="9231" width="7.81640625" customWidth="1"/>
+    <col min="9232" max="9232" width="5.453125" customWidth="1"/>
+    <col min="9233" max="9233" width="6.453125" customWidth="1"/>
+    <col min="9234" max="9234" width="7.81640625" customWidth="1"/>
+    <col min="9235" max="9235" width="3" customWidth="1"/>
+    <col min="9236" max="9236" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9473" max="9476" width="14.453125" customWidth="1"/>
+    <col min="9477" max="9477" width="15.453125" customWidth="1"/>
+    <col min="9478" max="9478" width="14.54296875" customWidth="1"/>
+    <col min="9479" max="9479" width="15.26953125" customWidth="1"/>
+    <col min="9480" max="9481" width="14.453125" customWidth="1"/>
+    <col min="9482" max="9482" width="13.1796875" customWidth="1"/>
+    <col min="9483" max="9485" width="14.453125" customWidth="1"/>
+    <col min="9486" max="9486" width="15.81640625" customWidth="1"/>
+    <col min="9487" max="9487" width="7.81640625" customWidth="1"/>
+    <col min="9488" max="9488" width="5.453125" customWidth="1"/>
+    <col min="9489" max="9489" width="6.453125" customWidth="1"/>
+    <col min="9490" max="9490" width="7.81640625" customWidth="1"/>
+    <col min="9491" max="9491" width="3" customWidth="1"/>
+    <col min="9492" max="9492" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9729" max="9732" width="14.453125" customWidth="1"/>
+    <col min="9733" max="9733" width="15.453125" customWidth="1"/>
+    <col min="9734" max="9734" width="14.54296875" customWidth="1"/>
+    <col min="9735" max="9735" width="15.26953125" customWidth="1"/>
+    <col min="9736" max="9737" width="14.453125" customWidth="1"/>
+    <col min="9738" max="9738" width="13.1796875" customWidth="1"/>
+    <col min="9739" max="9741" width="14.453125" customWidth="1"/>
+    <col min="9742" max="9742" width="15.81640625" customWidth="1"/>
+    <col min="9743" max="9743" width="7.81640625" customWidth="1"/>
+    <col min="9744" max="9744" width="5.453125" customWidth="1"/>
+    <col min="9745" max="9745" width="6.453125" customWidth="1"/>
+    <col min="9746" max="9746" width="7.81640625" customWidth="1"/>
+    <col min="9747" max="9747" width="3" customWidth="1"/>
+    <col min="9748" max="9748" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9985" max="9988" width="14.453125" customWidth="1"/>
+    <col min="9989" max="9989" width="15.453125" customWidth="1"/>
+    <col min="9990" max="9990" width="14.54296875" customWidth="1"/>
+    <col min="9991" max="9991" width="15.26953125" customWidth="1"/>
+    <col min="9992" max="9993" width="14.453125" customWidth="1"/>
+    <col min="9994" max="9994" width="13.1796875" customWidth="1"/>
+    <col min="9995" max="9997" width="14.453125" customWidth="1"/>
+    <col min="9998" max="9998" width="15.81640625" customWidth="1"/>
+    <col min="9999" max="9999" width="7.81640625" customWidth="1"/>
+    <col min="10000" max="10000" width="5.453125" customWidth="1"/>
+    <col min="10001" max="10001" width="6.453125" customWidth="1"/>
+    <col min="10002" max="10002" width="7.81640625" customWidth="1"/>
+    <col min="10003" max="10003" width="3" customWidth="1"/>
+    <col min="10004" max="10004" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10241" max="10244" width="14.453125" customWidth="1"/>
+    <col min="10245" max="10245" width="15.453125" customWidth="1"/>
+    <col min="10246" max="10246" width="14.54296875" customWidth="1"/>
+    <col min="10247" max="10247" width="15.26953125" customWidth="1"/>
+    <col min="10248" max="10249" width="14.453125" customWidth="1"/>
+    <col min="10250" max="10250" width="13.1796875" customWidth="1"/>
+    <col min="10251" max="10253" width="14.453125" customWidth="1"/>
+    <col min="10254" max="10254" width="15.81640625" customWidth="1"/>
+    <col min="10255" max="10255" width="7.81640625" customWidth="1"/>
+    <col min="10256" max="10256" width="5.453125" customWidth="1"/>
+    <col min="10257" max="10257" width="6.453125" customWidth="1"/>
+    <col min="10258" max="10258" width="7.81640625" customWidth="1"/>
+    <col min="10259" max="10259" width="3" customWidth="1"/>
+    <col min="10260" max="10260" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10497" max="10500" width="14.453125" customWidth="1"/>
+    <col min="10501" max="10501" width="15.453125" customWidth="1"/>
+    <col min="10502" max="10502" width="14.54296875" customWidth="1"/>
+    <col min="10503" max="10503" width="15.26953125" customWidth="1"/>
+    <col min="10504" max="10505" width="14.453125" customWidth="1"/>
+    <col min="10506" max="10506" width="13.1796875" customWidth="1"/>
+    <col min="10507" max="10509" width="14.453125" customWidth="1"/>
+    <col min="10510" max="10510" width="15.81640625" customWidth="1"/>
+    <col min="10511" max="10511" width="7.81640625" customWidth="1"/>
+    <col min="10512" max="10512" width="5.453125" customWidth="1"/>
+    <col min="10513" max="10513" width="6.453125" customWidth="1"/>
+    <col min="10514" max="10514" width="7.81640625" customWidth="1"/>
+    <col min="10515" max="10515" width="3" customWidth="1"/>
+    <col min="10516" max="10516" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10753" max="10756" width="14.453125" customWidth="1"/>
+    <col min="10757" max="10757" width="15.453125" customWidth="1"/>
+    <col min="10758" max="10758" width="14.54296875" customWidth="1"/>
+    <col min="10759" max="10759" width="15.26953125" customWidth="1"/>
+    <col min="10760" max="10761" width="14.453125" customWidth="1"/>
+    <col min="10762" max="10762" width="13.1796875" customWidth="1"/>
+    <col min="10763" max="10765" width="14.453125" customWidth="1"/>
+    <col min="10766" max="10766" width="15.81640625" customWidth="1"/>
+    <col min="10767" max="10767" width="7.81640625" customWidth="1"/>
+    <col min="10768" max="10768" width="5.453125" customWidth="1"/>
+    <col min="10769" max="10769" width="6.453125" customWidth="1"/>
+    <col min="10770" max="10770" width="7.81640625" customWidth="1"/>
+    <col min="10771" max="10771" width="3" customWidth="1"/>
+    <col min="10772" max="10772" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11009" max="11012" width="14.453125" customWidth="1"/>
+    <col min="11013" max="11013" width="15.453125" customWidth="1"/>
+    <col min="11014" max="11014" width="14.54296875" customWidth="1"/>
+    <col min="11015" max="11015" width="15.26953125" customWidth="1"/>
+    <col min="11016" max="11017" width="14.453125" customWidth="1"/>
+    <col min="11018" max="11018" width="13.1796875" customWidth="1"/>
+    <col min="11019" max="11021" width="14.453125" customWidth="1"/>
+    <col min="11022" max="11022" width="15.81640625" customWidth="1"/>
+    <col min="11023" max="11023" width="7.81640625" customWidth="1"/>
+    <col min="11024" max="11024" width="5.453125" customWidth="1"/>
+    <col min="11025" max="11025" width="6.453125" customWidth="1"/>
+    <col min="11026" max="11026" width="7.81640625" customWidth="1"/>
+    <col min="11027" max="11027" width="3" customWidth="1"/>
+    <col min="11028" max="11028" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11265" max="11268" width="14.453125" customWidth="1"/>
+    <col min="11269" max="11269" width="15.453125" customWidth="1"/>
+    <col min="11270" max="11270" width="14.54296875" customWidth="1"/>
+    <col min="11271" max="11271" width="15.26953125" customWidth="1"/>
+    <col min="11272" max="11273" width="14.453125" customWidth="1"/>
+    <col min="11274" max="11274" width="13.1796875" customWidth="1"/>
+    <col min="11275" max="11277" width="14.453125" customWidth="1"/>
+    <col min="11278" max="11278" width="15.81640625" customWidth="1"/>
+    <col min="11279" max="11279" width="7.81640625" customWidth="1"/>
+    <col min="11280" max="11280" width="5.453125" customWidth="1"/>
+    <col min="11281" max="11281" width="6.453125" customWidth="1"/>
+    <col min="11282" max="11282" width="7.81640625" customWidth="1"/>
+    <col min="11283" max="11283" width="3" customWidth="1"/>
+    <col min="11284" max="11284" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11521" max="11524" width="14.453125" customWidth="1"/>
+    <col min="11525" max="11525" width="15.453125" customWidth="1"/>
+    <col min="11526" max="11526" width="14.54296875" customWidth="1"/>
+    <col min="11527" max="11527" width="15.26953125" customWidth="1"/>
+    <col min="11528" max="11529" width="14.453125" customWidth="1"/>
+    <col min="11530" max="11530" width="13.1796875" customWidth="1"/>
+    <col min="11531" max="11533" width="14.453125" customWidth="1"/>
+    <col min="11534" max="11534" width="15.81640625" customWidth="1"/>
+    <col min="11535" max="11535" width="7.81640625" customWidth="1"/>
+    <col min="11536" max="11536" width="5.453125" customWidth="1"/>
+    <col min="11537" max="11537" width="6.453125" customWidth="1"/>
+    <col min="11538" max="11538" width="7.81640625" customWidth="1"/>
+    <col min="11539" max="11539" width="3" customWidth="1"/>
+    <col min="11540" max="11540" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11777" max="11780" width="14.453125" customWidth="1"/>
+    <col min="11781" max="11781" width="15.453125" customWidth="1"/>
+    <col min="11782" max="11782" width="14.54296875" customWidth="1"/>
+    <col min="11783" max="11783" width="15.26953125" customWidth="1"/>
+    <col min="11784" max="11785" width="14.453125" customWidth="1"/>
+    <col min="11786" max="11786" width="13.1796875" customWidth="1"/>
+    <col min="11787" max="11789" width="14.453125" customWidth="1"/>
+    <col min="11790" max="11790" width="15.81640625" customWidth="1"/>
+    <col min="11791" max="11791" width="7.81640625" customWidth="1"/>
+    <col min="11792" max="11792" width="5.453125" customWidth="1"/>
+    <col min="11793" max="11793" width="6.453125" customWidth="1"/>
+    <col min="11794" max="11794" width="7.81640625" customWidth="1"/>
+    <col min="11795" max="11795" width="3" customWidth="1"/>
+    <col min="11796" max="11796" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12033" max="12036" width="14.453125" customWidth="1"/>
+    <col min="12037" max="12037" width="15.453125" customWidth="1"/>
+    <col min="12038" max="12038" width="14.54296875" customWidth="1"/>
+    <col min="12039" max="12039" width="15.26953125" customWidth="1"/>
+    <col min="12040" max="12041" width="14.453125" customWidth="1"/>
+    <col min="12042" max="12042" width="13.1796875" customWidth="1"/>
+    <col min="12043" max="12045" width="14.453125" customWidth="1"/>
+    <col min="12046" max="12046" width="15.81640625" customWidth="1"/>
+    <col min="12047" max="12047" width="7.81640625" customWidth="1"/>
+    <col min="12048" max="12048" width="5.453125" customWidth="1"/>
+    <col min="12049" max="12049" width="6.453125" customWidth="1"/>
+    <col min="12050" max="12050" width="7.81640625" customWidth="1"/>
+    <col min="12051" max="12051" width="3" customWidth="1"/>
+    <col min="12052" max="12052" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12289" max="12292" width="14.453125" customWidth="1"/>
+    <col min="12293" max="12293" width="15.453125" customWidth="1"/>
+    <col min="12294" max="12294" width="14.54296875" customWidth="1"/>
+    <col min="12295" max="12295" width="15.26953125" customWidth="1"/>
+    <col min="12296" max="12297" width="14.453125" customWidth="1"/>
+    <col min="12298" max="12298" width="13.1796875" customWidth="1"/>
+    <col min="12299" max="12301" width="14.453125" customWidth="1"/>
+    <col min="12302" max="12302" width="15.81640625" customWidth="1"/>
+    <col min="12303" max="12303" width="7.81640625" customWidth="1"/>
+    <col min="12304" max="12304" width="5.453125" customWidth="1"/>
+    <col min="12305" max="12305" width="6.453125" customWidth="1"/>
+    <col min="12306" max="12306" width="7.81640625" customWidth="1"/>
+    <col min="12307" max="12307" width="3" customWidth="1"/>
+    <col min="12308" max="12308" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12545" max="12548" width="14.453125" customWidth="1"/>
+    <col min="12549" max="12549" width="15.453125" customWidth="1"/>
+    <col min="12550" max="12550" width="14.54296875" customWidth="1"/>
+    <col min="12551" max="12551" width="15.26953125" customWidth="1"/>
+    <col min="12552" max="12553" width="14.453125" customWidth="1"/>
+    <col min="12554" max="12554" width="13.1796875" customWidth="1"/>
+    <col min="12555" max="12557" width="14.453125" customWidth="1"/>
+    <col min="12558" max="12558" width="15.81640625" customWidth="1"/>
+    <col min="12559" max="12559" width="7.81640625" customWidth="1"/>
+    <col min="12560" max="12560" width="5.453125" customWidth="1"/>
+    <col min="12561" max="12561" width="6.453125" customWidth="1"/>
+    <col min="12562" max="12562" width="7.81640625" customWidth="1"/>
+    <col min="12563" max="12563" width="3" customWidth="1"/>
+    <col min="12564" max="12564" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12801" max="12804" width="14.453125" customWidth="1"/>
+    <col min="12805" max="12805" width="15.453125" customWidth="1"/>
+    <col min="12806" max="12806" width="14.54296875" customWidth="1"/>
+    <col min="12807" max="12807" width="15.26953125" customWidth="1"/>
+    <col min="12808" max="12809" width="14.453125" customWidth="1"/>
+    <col min="12810" max="12810" width="13.1796875" customWidth="1"/>
+    <col min="12811" max="12813" width="14.453125" customWidth="1"/>
+    <col min="12814" max="12814" width="15.81640625" customWidth="1"/>
+    <col min="12815" max="12815" width="7.81640625" customWidth="1"/>
+    <col min="12816" max="12816" width="5.453125" customWidth="1"/>
+    <col min="12817" max="12817" width="6.453125" customWidth="1"/>
+    <col min="12818" max="12818" width="7.81640625" customWidth="1"/>
+    <col min="12819" max="12819" width="3" customWidth="1"/>
+    <col min="12820" max="12820" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13057" max="13060" width="14.453125" customWidth="1"/>
+    <col min="13061" max="13061" width="15.453125" customWidth="1"/>
+    <col min="13062" max="13062" width="14.54296875" customWidth="1"/>
+    <col min="13063" max="13063" width="15.26953125" customWidth="1"/>
+    <col min="13064" max="13065" width="14.453125" customWidth="1"/>
+    <col min="13066" max="13066" width="13.1796875" customWidth="1"/>
+    <col min="13067" max="13069" width="14.453125" customWidth="1"/>
+    <col min="13070" max="13070" width="15.81640625" customWidth="1"/>
+    <col min="13071" max="13071" width="7.81640625" customWidth="1"/>
+    <col min="13072" max="13072" width="5.453125" customWidth="1"/>
+    <col min="13073" max="13073" width="6.453125" customWidth="1"/>
+    <col min="13074" max="13074" width="7.81640625" customWidth="1"/>
+    <col min="13075" max="13075" width="3" customWidth="1"/>
+    <col min="13076" max="13076" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13313" max="13316" width="14.453125" customWidth="1"/>
+    <col min="13317" max="13317" width="15.453125" customWidth="1"/>
+    <col min="13318" max="13318" width="14.54296875" customWidth="1"/>
+    <col min="13319" max="13319" width="15.26953125" customWidth="1"/>
+    <col min="13320" max="13321" width="14.453125" customWidth="1"/>
+    <col min="13322" max="13322" width="13.1796875" customWidth="1"/>
+    <col min="13323" max="13325" width="14.453125" customWidth="1"/>
+    <col min="13326" max="13326" width="15.81640625" customWidth="1"/>
+    <col min="13327" max="13327" width="7.81640625" customWidth="1"/>
+    <col min="13328" max="13328" width="5.453125" customWidth="1"/>
+    <col min="13329" max="13329" width="6.453125" customWidth="1"/>
+    <col min="13330" max="13330" width="7.81640625" customWidth="1"/>
+    <col min="13331" max="13331" width="3" customWidth="1"/>
+    <col min="13332" max="13332" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13569" max="13572" width="14.453125" customWidth="1"/>
+    <col min="13573" max="13573" width="15.453125" customWidth="1"/>
+    <col min="13574" max="13574" width="14.54296875" customWidth="1"/>
+    <col min="13575" max="13575" width="15.26953125" customWidth="1"/>
+    <col min="13576" max="13577" width="14.453125" customWidth="1"/>
+    <col min="13578" max="13578" width="13.1796875" customWidth="1"/>
+    <col min="13579" max="13581" width="14.453125" customWidth="1"/>
+    <col min="13582" max="13582" width="15.81640625" customWidth="1"/>
+    <col min="13583" max="13583" width="7.81640625" customWidth="1"/>
+    <col min="13584" max="13584" width="5.453125" customWidth="1"/>
+    <col min="13585" max="13585" width="6.453125" customWidth="1"/>
+    <col min="13586" max="13586" width="7.81640625" customWidth="1"/>
+    <col min="13587" max="13587" width="3" customWidth="1"/>
+    <col min="13588" max="13588" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13825" max="13828" width="14.453125" customWidth="1"/>
+    <col min="13829" max="13829" width="15.453125" customWidth="1"/>
+    <col min="13830" max="13830" width="14.54296875" customWidth="1"/>
+    <col min="13831" max="13831" width="15.26953125" customWidth="1"/>
+    <col min="13832" max="13833" width="14.453125" customWidth="1"/>
+    <col min="13834" max="13834" width="13.1796875" customWidth="1"/>
+    <col min="13835" max="13837" width="14.453125" customWidth="1"/>
+    <col min="13838" max="13838" width="15.81640625" customWidth="1"/>
+    <col min="13839" max="13839" width="7.81640625" customWidth="1"/>
+    <col min="13840" max="13840" width="5.453125" customWidth="1"/>
+    <col min="13841" max="13841" width="6.453125" customWidth="1"/>
+    <col min="13842" max="13842" width="7.81640625" customWidth="1"/>
+    <col min="13843" max="13843" width="3" customWidth="1"/>
+    <col min="13844" max="13844" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14081" max="14084" width="14.453125" customWidth="1"/>
+    <col min="14085" max="14085" width="15.453125" customWidth="1"/>
+    <col min="14086" max="14086" width="14.54296875" customWidth="1"/>
+    <col min="14087" max="14087" width="15.26953125" customWidth="1"/>
+    <col min="14088" max="14089" width="14.453125" customWidth="1"/>
+    <col min="14090" max="14090" width="13.1796875" customWidth="1"/>
+    <col min="14091" max="14093" width="14.453125" customWidth="1"/>
+    <col min="14094" max="14094" width="15.81640625" customWidth="1"/>
+    <col min="14095" max="14095" width="7.81640625" customWidth="1"/>
+    <col min="14096" max="14096" width="5.453125" customWidth="1"/>
+    <col min="14097" max="14097" width="6.453125" customWidth="1"/>
+    <col min="14098" max="14098" width="7.81640625" customWidth="1"/>
+    <col min="14099" max="14099" width="3" customWidth="1"/>
+    <col min="14100" max="14100" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14337" max="14340" width="14.453125" customWidth="1"/>
+    <col min="14341" max="14341" width="15.453125" customWidth="1"/>
+    <col min="14342" max="14342" width="14.54296875" customWidth="1"/>
+    <col min="14343" max="14343" width="15.26953125" customWidth="1"/>
+    <col min="14344" max="14345" width="14.453125" customWidth="1"/>
+    <col min="14346" max="14346" width="13.1796875" customWidth="1"/>
+    <col min="14347" max="14349" width="14.453125" customWidth="1"/>
+    <col min="14350" max="14350" width="15.81640625" customWidth="1"/>
+    <col min="14351" max="14351" width="7.81640625" customWidth="1"/>
+    <col min="14352" max="14352" width="5.453125" customWidth="1"/>
+    <col min="14353" max="14353" width="6.453125" customWidth="1"/>
+    <col min="14354" max="14354" width="7.81640625" customWidth="1"/>
+    <col min="14355" max="14355" width="3" customWidth="1"/>
+    <col min="14356" max="14356" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14593" max="14596" width="14.453125" customWidth="1"/>
+    <col min="14597" max="14597" width="15.453125" customWidth="1"/>
+    <col min="14598" max="14598" width="14.54296875" customWidth="1"/>
+    <col min="14599" max="14599" width="15.26953125" customWidth="1"/>
+    <col min="14600" max="14601" width="14.453125" customWidth="1"/>
+    <col min="14602" max="14602" width="13.1796875" customWidth="1"/>
+    <col min="14603" max="14605" width="14.453125" customWidth="1"/>
+    <col min="14606" max="14606" width="15.81640625" customWidth="1"/>
+    <col min="14607" max="14607" width="7.81640625" customWidth="1"/>
+    <col min="14608" max="14608" width="5.453125" customWidth="1"/>
+    <col min="14609" max="14609" width="6.453125" customWidth="1"/>
+    <col min="14610" max="14610" width="7.81640625" customWidth="1"/>
+    <col min="14611" max="14611" width="3" customWidth="1"/>
+    <col min="14612" max="14612" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14849" max="14852" width="14.453125" customWidth="1"/>
+    <col min="14853" max="14853" width="15.453125" customWidth="1"/>
+    <col min="14854" max="14854" width="14.54296875" customWidth="1"/>
+    <col min="14855" max="14855" width="15.26953125" customWidth="1"/>
+    <col min="14856" max="14857" width="14.453125" customWidth="1"/>
+    <col min="14858" max="14858" width="13.1796875" customWidth="1"/>
+    <col min="14859" max="14861" width="14.453125" customWidth="1"/>
+    <col min="14862" max="14862" width="15.81640625" customWidth="1"/>
+    <col min="14863" max="14863" width="7.81640625" customWidth="1"/>
+    <col min="14864" max="14864" width="5.453125" customWidth="1"/>
+    <col min="14865" max="14865" width="6.453125" customWidth="1"/>
+    <col min="14866" max="14866" width="7.81640625" customWidth="1"/>
+    <col min="14867" max="14867" width="3" customWidth="1"/>
+    <col min="14868" max="14868" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15105" max="15108" width="14.453125" customWidth="1"/>
+    <col min="15109" max="15109" width="15.453125" customWidth="1"/>
+    <col min="15110" max="15110" width="14.54296875" customWidth="1"/>
+    <col min="15111" max="15111" width="15.26953125" customWidth="1"/>
+    <col min="15112" max="15113" width="14.453125" customWidth="1"/>
+    <col min="15114" max="15114" width="13.1796875" customWidth="1"/>
+    <col min="15115" max="15117" width="14.453125" customWidth="1"/>
+    <col min="15118" max="15118" width="15.81640625" customWidth="1"/>
+    <col min="15119" max="15119" width="7.81640625" customWidth="1"/>
+    <col min="15120" max="15120" width="5.453125" customWidth="1"/>
+    <col min="15121" max="15121" width="6.453125" customWidth="1"/>
+    <col min="15122" max="15122" width="7.81640625" customWidth="1"/>
+    <col min="15123" max="15123" width="3" customWidth="1"/>
+    <col min="15124" max="15124" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15361" max="15364" width="14.453125" customWidth="1"/>
+    <col min="15365" max="15365" width="15.453125" customWidth="1"/>
+    <col min="15366" max="15366" width="14.54296875" customWidth="1"/>
+    <col min="15367" max="15367" width="15.26953125" customWidth="1"/>
+    <col min="15368" max="15369" width="14.453125" customWidth="1"/>
+    <col min="15370" max="15370" width="13.1796875" customWidth="1"/>
+    <col min="15371" max="15373" width="14.453125" customWidth="1"/>
+    <col min="15374" max="15374" width="15.81640625" customWidth="1"/>
+    <col min="15375" max="15375" width="7.81640625" customWidth="1"/>
+    <col min="15376" max="15376" width="5.453125" customWidth="1"/>
+    <col min="15377" max="15377" width="6.453125" customWidth="1"/>
+    <col min="15378" max="15378" width="7.81640625" customWidth="1"/>
+    <col min="15379" max="15379" width="3" customWidth="1"/>
+    <col min="15380" max="15380" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15617" max="15620" width="14.453125" customWidth="1"/>
+    <col min="15621" max="15621" width="15.453125" customWidth="1"/>
+    <col min="15622" max="15622" width="14.54296875" customWidth="1"/>
+    <col min="15623" max="15623" width="15.26953125" customWidth="1"/>
+    <col min="15624" max="15625" width="14.453125" customWidth="1"/>
+    <col min="15626" max="15626" width="13.1796875" customWidth="1"/>
+    <col min="15627" max="15629" width="14.453125" customWidth="1"/>
+    <col min="15630" max="15630" width="15.81640625" customWidth="1"/>
+    <col min="15631" max="15631" width="7.81640625" customWidth="1"/>
+    <col min="15632" max="15632" width="5.453125" customWidth="1"/>
+    <col min="15633" max="15633" width="6.453125" customWidth="1"/>
+    <col min="15634" max="15634" width="7.81640625" customWidth="1"/>
+    <col min="15635" max="15635" width="3" customWidth="1"/>
+    <col min="15636" max="15636" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15873" max="15876" width="14.453125" customWidth="1"/>
+    <col min="15877" max="15877" width="15.453125" customWidth="1"/>
+    <col min="15878" max="15878" width="14.54296875" customWidth="1"/>
+    <col min="15879" max="15879" width="15.26953125" customWidth="1"/>
+    <col min="15880" max="15881" width="14.453125" customWidth="1"/>
+    <col min="15882" max="15882" width="13.1796875" customWidth="1"/>
+    <col min="15883" max="15885" width="14.453125" customWidth="1"/>
+    <col min="15886" max="15886" width="15.81640625" customWidth="1"/>
+    <col min="15887" max="15887" width="7.81640625" customWidth="1"/>
+    <col min="15888" max="15888" width="5.453125" customWidth="1"/>
+    <col min="15889" max="15889" width="6.453125" customWidth="1"/>
+    <col min="15890" max="15890" width="7.81640625" customWidth="1"/>
+    <col min="15891" max="15891" width="3" customWidth="1"/>
+    <col min="15892" max="15892" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="16129" max="16132" width="14.453125" customWidth="1"/>
+    <col min="16133" max="16133" width="15.453125" customWidth="1"/>
+    <col min="16134" max="16134" width="14.54296875" customWidth="1"/>
+    <col min="16135" max="16135" width="15.26953125" customWidth="1"/>
+    <col min="16136" max="16137" width="14.453125" customWidth="1"/>
+    <col min="16138" max="16138" width="13.1796875" customWidth="1"/>
+    <col min="16139" max="16141" width="14.453125" customWidth="1"/>
+    <col min="16142" max="16142" width="15.81640625" customWidth="1"/>
+    <col min="16143" max="16143" width="7.81640625" customWidth="1"/>
+    <col min="16144" max="16144" width="5.453125" customWidth="1"/>
+    <col min="16145" max="16145" width="6.453125" customWidth="1"/>
+    <col min="16146" max="16146" width="7.81640625" customWidth="1"/>
+    <col min="16147" max="16147" width="3" customWidth="1"/>
+    <col min="16148" max="16148" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="265" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
+      <c r="S1"/>
+    </row>
+    <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2"/>
+    </row>
+    <row r="3" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" s="61"/>
+      <c r="E3" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F3" s="254" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="129" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="256" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="261" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="26"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="258" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" s="259"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="251" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="252"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="29"/>
+    </row>
+    <row r="4" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="61"/>
+      <c r="E4" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F4" s="254"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="256"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="261"/>
+      <c r="O4" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" s="249" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" s="250" t="s">
+        <v>71</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" s="245" t="s">
+        <v>70</v>
+      </c>
+      <c r="U4" s="246" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" s="37"/>
+      <c r="E5" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="F5" s="257" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="254" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="54"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="38"/>
+      <c r="O5" s="39">
+        <v>31</v>
+      </c>
+      <c r="P5" s="40">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="41">
+        <v>19</v>
+      </c>
+      <c r="R5" s="42">
+        <v>11</v>
+      </c>
+      <c r="S5" s="40">
+        <v>31</v>
+      </c>
+      <c r="T5" s="41">
+        <v>19</v>
+      </c>
+      <c r="U5" s="42">
+        <v>11</v>
+      </c>
+      <c r="V5" s="43">
+        <f t="shared" ref="V5:V17" si="0">-SUM(S5-P5)*-1</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="44"/>
+    </row>
+    <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="257"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="129" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="254"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="126" t="s">
+        <v>215</v>
+      </c>
+      <c r="N6" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" s="47">
+        <v>49</v>
+      </c>
+      <c r="P6" s="48">
+        <f t="shared" ref="P6:P17" si="1">SUM(Q6:R6)</f>
+        <v>12</v>
+      </c>
+      <c r="Q6" s="49">
+        <v>7</v>
+      </c>
+      <c r="R6" s="50">
+        <v>5</v>
+      </c>
+      <c r="S6" s="48">
+        <f t="shared" ref="S6:S17" si="2">SUM(T6:U6)</f>
+        <v>12</v>
+      </c>
+      <c r="T6" s="49">
+        <v>7</v>
+      </c>
+      <c r="U6" s="50">
+        <v>5</v>
+      </c>
+      <c r="V6" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="52"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="53"/>
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="257" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="64"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="47">
+        <v>22</v>
+      </c>
+      <c r="P7" s="48">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Q7" s="49">
+        <v>11</v>
+      </c>
+      <c r="R7" s="50">
+        <v>4</v>
+      </c>
+      <c r="S7" s="48">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="T7" s="49">
+        <v>11</v>
+      </c>
+      <c r="U7" s="50">
+        <v>4</v>
+      </c>
+      <c r="V7" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W7" s="52"/>
+    </row>
+    <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="45"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="257"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="56">
+        <v>46255</v>
+      </c>
+      <c r="O8" s="47">
+        <v>24</v>
+      </c>
+      <c r="P8" s="48">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Q8" s="49">
+        <v>3</v>
+      </c>
+      <c r="R8" s="50">
+        <v>3</v>
+      </c>
+      <c r="S8" s="48">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="T8" s="49">
+        <v>2</v>
+      </c>
+      <c r="U8" s="50">
+        <v>2</v>
+      </c>
+      <c r="V8" s="51">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="W8" s="52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="45"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="58"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="64"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9" s="47"/>
+      <c r="P9" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="49"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W9" s="52"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="45"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="129" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="61"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="64"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="49"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="52"/>
+    </row>
+    <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="64"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="244" t="s">
+        <v>149</v>
+      </c>
+      <c r="G11" s="64"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="66"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="68"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="70"/>
+    </row>
+    <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="71"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="244" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="64"/>
+      <c r="H12" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="L12" s="73" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" s="74"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="68"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W12" s="70"/>
+    </row>
+    <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="61"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="128" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="260" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" s="30"/>
+      <c r="J13" s="127" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="128"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="60"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="68"/>
+      <c r="U13" s="69"/>
+      <c r="V13" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="70"/>
+    </row>
+    <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="8"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="248" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="260"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="60"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="68"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="70"/>
+    </row>
+    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="129"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="248"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="260" t="s">
+        <v>84</v>
+      </c>
+      <c r="I15" s="30"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="107"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="68"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="70"/>
+    </row>
+    <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="8"/>
+      <c r="B16" s="260" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="260"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="107"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="68"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="68"/>
+      <c r="U16" s="69"/>
+      <c r="V16" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="70"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="8"/>
+      <c r="B17" s="260"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="261" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="30"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="80"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="82">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="83"/>
+    </row>
+    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="261"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="77"/>
+      <c r="M18" s="77"/>
+      <c r="R18" s="84"/>
+      <c r="S18"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="248"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="261" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" s="30"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="77"/>
+      <c r="R19" s="84"/>
+      <c r="S19"/>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="85" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="248"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="158"/>
+      <c r="H20" s="261"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="R20" s="84"/>
+      <c r="S20"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="D21" s="61"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="261" t="s">
+        <v>82</v>
+      </c>
+      <c r="I21" s="30"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="R21" s="84"/>
+      <c r="S21"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="6"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="248"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="261"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="R22" s="84"/>
+      <c r="S22"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="R23" s="84"/>
+      <c r="S23"/>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="R24" s="84"/>
+      <c r="S24"/>
+    </row>
+    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="30"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="R25" s="84"/>
+      <c r="S25"/>
+    </row>
+    <row r="26" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="248"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="R26" s="84"/>
+      <c r="S26"/>
+    </row>
+    <row r="27" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="R27" s="84"/>
+      <c r="S27"/>
+    </row>
+    <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="266" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="266"/>
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
+      <c r="E28" s="266"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="R28" s="84"/>
+      <c r="S28"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="30"/>
+      <c r="I29" s="248"/>
+      <c r="J29" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K29" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="92" t="s">
+        <v>25</v>
+      </c>
+      <c r="R29" s="84"/>
+      <c r="S29"/>
+    </row>
+    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="B30" s="94"/>
+      <c r="C30" s="93" t="s">
+        <v>231</v>
+      </c>
+      <c r="D30" s="93" t="s">
+        <v>234</v>
+      </c>
+      <c r="E30" s="255" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="8"/>
+      <c r="G30" s="247" t="s">
+        <v>240</v>
+      </c>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="159" t="s">
+        <v>141</v>
+      </c>
+      <c r="K30" s="124" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="224" t="s">
+        <v>242</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="R30" s="84"/>
+      <c r="S30"/>
+    </row>
+    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="93" t="s">
+        <v>232</v>
+      </c>
+      <c r="D31" s="93" t="s">
+        <v>233</v>
+      </c>
+      <c r="E31" s="255"/>
+      <c r="F31" s="8"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="159" t="s">
+        <v>205</v>
+      </c>
+      <c r="K31" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="L31" s="224" t="s">
+        <v>119</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" s="84"/>
+      <c r="S31"/>
+    </row>
+    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="94"/>
+      <c r="C32" s="93" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="93" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" s="255" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="143"/>
+      <c r="K32" s="110" t="s">
+        <v>150</v>
+      </c>
+      <c r="L32" s="224" t="s">
+        <v>122</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="R32" s="84"/>
+      <c r="S32"/>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="8"/>
+      <c r="C33" s="93" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="93" t="s">
+        <v>236</v>
+      </c>
+      <c r="E33" s="255"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="224" t="s">
+        <v>16</v>
+      </c>
+      <c r="L33" s="224" t="s">
+        <v>243</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="R33" s="84"/>
+      <c r="S33"/>
+    </row>
+    <row r="34" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="94"/>
+      <c r="B34" s="95"/>
+      <c r="D34" s="93" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" s="253" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="K34" s="224" t="s">
+        <v>81</v>
+      </c>
+      <c r="L34" s="224" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="8"/>
+      <c r="R34" s="84"/>
+      <c r="S34"/>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="94"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="93" t="s">
+        <v>238</v>
+      </c>
+      <c r="E35" s="253"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="224" t="s">
+        <v>244</v>
+      </c>
+      <c r="L35" s="218" t="s">
+        <v>38</v>
+      </c>
+      <c r="M35" s="13"/>
+      <c r="R35" s="84"/>
+      <c r="S35"/>
+    </row>
+    <row r="36" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="94"/>
+      <c r="B36" s="94"/>
+      <c r="D36" s="93" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="255" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="97"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="124" t="s">
+        <v>120</v>
+      </c>
+      <c r="L36" s="8"/>
+      <c r="M36" s="94"/>
+      <c r="R36" s="84"/>
+      <c r="S36"/>
+    </row>
+    <row r="37" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="E37" s="255"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="100"/>
+      <c r="K37" s="124" t="s">
+        <v>211</v>
+      </c>
+      <c r="L37" s="8"/>
+      <c r="M37" s="94"/>
+      <c r="R37" s="84"/>
+      <c r="S37"/>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="77"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="247" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" s="77"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="124" t="s">
+        <v>212</v>
+      </c>
+      <c r="L38" s="8"/>
+      <c r="M38" s="2"/>
+      <c r="R38" s="84"/>
+      <c r="S38"/>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="74"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="247" t="s">
+        <v>92</v>
+      </c>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="2"/>
+      <c r="S39"/>
+    </row>
+    <row r="40" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="105"/>
+      <c r="S40"/>
+    </row>
+    <row r="41" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="104"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="104"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="93" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="8"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="101"/>
+      <c r="M41" s="106"/>
+      <c r="S41"/>
+    </row>
+    <row r="42" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="104"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="104"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="247" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="106"/>
+      <c r="S42"/>
+    </row>
+    <row r="43" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="104"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="247" t="s">
+        <v>216</v>
+      </c>
+      <c r="F43" s="107"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="106"/>
+      <c r="S43"/>
+    </row>
+    <row r="44" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="104"/>
+      <c r="B44" s="104"/>
+      <c r="C44" s="104"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="109"/>
+      <c r="S44"/>
+    </row>
+    <row r="45" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="104"/>
+      <c r="B45" s="104"/>
+      <c r="C45" s="104"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="110"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="111"/>
+      <c r="S45"/>
+    </row>
+    <row r="46" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="104"/>
+      <c r="B46" s="104"/>
+      <c r="C46" s="104"/>
+      <c r="D46" s="104"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="104"/>
+      <c r="J46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="111"/>
+      <c r="S46"/>
+    </row>
+    <row r="47" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="104"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="104"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="104"/>
+      <c r="H47" s="104"/>
+      <c r="I47" s="248"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="112"/>
+      <c r="S47"/>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="84"/>
+      <c r="S48"/>
+    </row>
+    <row r="49" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="77"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="113"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="104"/>
+      <c r="I49" s="248"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="84"/>
+      <c r="S49"/>
+    </row>
+    <row r="50" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="77"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="84"/>
+      <c r="S50"/>
+    </row>
+    <row r="51" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="77"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="77"/>
+      <c r="D51" s="113"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="77"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="84"/>
+      <c r="S51"/>
+    </row>
+    <row r="52" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="77"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="113"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="77"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="77"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+    </row>
+    <row r="53" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="77"/>
+      <c r="B53" s="77"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="113"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="77"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="114"/>
+      <c r="M53" s="8"/>
+    </row>
+    <row r="54" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="77"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="113"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="77"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="77"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="114"/>
+      <c r="M54" s="8"/>
+    </row>
+    <row r="55" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="77"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="113"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="77"/>
+      <c r="G55" s="77"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="104"/>
+      <c r="J55" s="77"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="114"/>
+      <c r="M55" s="8"/>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="77"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="113"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="77"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="77"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="114"/>
+      <c r="M56" s="8"/>
+    </row>
+    <row r="57" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="77"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="77"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="114"/>
+      <c r="M57" s="8"/>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="77"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="113"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="77"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="115"/>
+      <c r="L58" s="114"/>
+      <c r="M58" s="8"/>
+    </row>
+    <row r="59" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="77"/>
+      <c r="B59" s="77"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="113"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="77"/>
+      <c r="G59" s="77"/>
+      <c r="H59" s="104"/>
+      <c r="I59" s="104"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="115"/>
+      <c r="L59" s="114"/>
+      <c r="M59" s="8"/>
+    </row>
+    <row r="60" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="77"/>
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="77"/>
+      <c r="G60" s="77"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="115"/>
+      <c r="L60" s="114"/>
+      <c r="M60" s="8"/>
+    </row>
+    <row r="61" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="77"/>
+      <c r="B61" s="77"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="113"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="114"/>
+      <c r="M61" s="8"/>
+    </row>
+    <row r="62" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="77"/>
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="77"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="114"/>
+      <c r="M62" s="8"/>
+    </row>
+    <row r="63" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="77"/>
+      <c r="B63" s="77"/>
+      <c r="C63" s="77"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="104"/>
+      <c r="I63" s="104"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="77"/>
+      <c r="M63" s="8"/>
+    </row>
+    <row r="64" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="77"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="77"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="77"/>
+      <c r="H64" s="104"/>
+      <c r="I64" s="104"/>
+      <c r="J64" s="77"/>
+      <c r="K64" s="116">
+        <v>22</v>
+      </c>
+      <c r="L64" s="117">
+        <v>6</v>
+      </c>
+      <c r="M64" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="61"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
+      <c r="S65"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L66" s="119" t="s">
+        <v>94</v>
+      </c>
+      <c r="M66" s="25">
+        <v>97</v>
+      </c>
+      <c r="S66"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L67" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="M67" s="25">
+        <f>SUM(M66-(M68+M69+M70))</f>
+        <v>69</v>
+      </c>
+      <c r="S67"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L68" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" s="25">
+        <v>15</v>
+      </c>
+      <c r="S68"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L69" s="121" t="s">
+        <v>24</v>
+      </c>
+      <c r="M69" s="25">
+        <v>9</v>
+      </c>
+      <c r="S69"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L70" s="122" t="s">
+        <v>25</v>
+      </c>
+      <c r="M70" s="25">
+        <v>4</v>
+      </c>
+      <c r="S70"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L71" t="s">
+        <v>96</v>
+      </c>
+      <c r="M71" s="25">
+        <v>13</v>
+      </c>
+      <c r="S71"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="M72" s="25"/>
+      <c r="S72"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H21:H22"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="T3:U3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -9607,21 +12290,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="246" t="s">
+      <c r="A1" s="265" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="246"/>
-      <c r="C1" s="246"/>
-      <c r="D1" s="246"/>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
-      <c r="G1" s="246"/>
-      <c r="H1" s="246"/>
-      <c r="I1" s="246"/>
-      <c r="J1" s="246"/>
-      <c r="K1" s="246"/>
-      <c r="L1" s="246"/>
-      <c r="M1" s="246"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -9676,13 +12359,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="247" t="s">
+      <c r="D3" s="254" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="247" t="s">
+      <c r="F3" s="254" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -9691,24 +12374,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="245" t="s">
+      <c r="J3" s="260" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="248" t="s">
+      <c r="M3" s="261" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="256" t="s">
+      <c r="Q3" s="258" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="257"/>
+      <c r="R3" s="259"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="250" t="s">
+      <c r="T3" s="251" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="251"/>
+      <c r="U3" s="252"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -9720,20 +12403,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="247"/>
+      <c r="D4" s="254"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="247"/>
+      <c r="F4" s="254"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="245"/>
+      <c r="J4" s="260"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="248"/>
+      <c r="M4" s="261"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -9772,7 +12455,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="255" t="s">
+      <c r="F5" s="257" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -9780,7 +12463,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="247" t="s">
+      <c r="J5" s="254" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -9825,13 +12508,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="255"/>
+      <c r="F6" s="257"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="247"/>
+      <c r="J6" s="254"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -9880,13 +12563,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="245" t="s">
+      <c r="F7" s="260" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="254" t="s">
+      <c r="J7" s="256" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -9934,11 +12617,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="245"/>
+      <c r="F8" s="260"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="254"/>
+      <c r="J8" s="256"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -9982,7 +12665,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="255" t="s">
+      <c r="F9" s="257" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -10022,7 +12705,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="255"/>
+      <c r="F10" s="257"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -10148,7 +12831,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="248" t="s">
+      <c r="I13" s="261" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -10189,7 +12872,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="248"/>
+      <c r="I14" s="261"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -10249,13 +12932,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="245" t="s">
+      <c r="A16" s="260" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="245" t="s">
+      <c r="B16" s="260" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="258" t="s">
+      <c r="C16" s="262" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -10290,9 +12973,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="245"/>
-      <c r="B17" s="245"/>
-      <c r="C17" s="259"/>
+      <c r="A17" s="260"/>
+      <c r="B17" s="260"/>
+      <c r="C17" s="263"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -10325,7 +13008,7 @@
     <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="248" t="s">
+      <c r="C18" s="261" t="s">
         <v>82</v>
       </c>
       <c r="D18" s="61"/>
@@ -10343,7 +13026,7 @@
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="147"/>
-      <c r="C19" s="248"/>
+      <c r="C19" s="261"/>
       <c r="D19" s="125"/>
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
@@ -10502,13 +13185,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="249" t="s">
+      <c r="A28" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="249"/>
-      <c r="C28" s="249"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
+      <c r="B28" s="266"/>
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
+      <c r="E28" s="266"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -10568,7 +13251,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="253" t="s">
+      <c r="E30" s="255" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -10602,7 +13285,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="253"/>
+      <c r="E31" s="255"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -10632,7 +13315,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="253" t="s">
+      <c r="E32" s="255" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -10662,7 +13345,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="253"/>
+      <c r="E33" s="255"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -10686,7 +13369,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="252" t="s">
+      <c r="E34" s="253" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -10711,7 +13394,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="252"/>
+      <c r="E35" s="253"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -10730,7 +13413,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="253" t="s">
+      <c r="E36" s="255" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -10750,7 +13433,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="253"/>
+      <c r="E37" s="255"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -11278,28 +13961,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="C18:C19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -12220,21 +14903,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="246" t="s">
+      <c r="A1" s="265" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="246"/>
-      <c r="C1" s="246"/>
-      <c r="D1" s="246"/>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
-      <c r="G1" s="246"/>
-      <c r="H1" s="246"/>
-      <c r="I1" s="246"/>
-      <c r="J1" s="246"/>
-      <c r="K1" s="246"/>
-      <c r="L1" s="246"/>
-      <c r="M1" s="246"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -12289,13 +14972,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="247" t="s">
+      <c r="D3" s="254" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="247" t="s">
+      <c r="F3" s="254" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -12304,24 +14987,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="245" t="s">
+      <c r="J3" s="260" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="248" t="s">
+      <c r="M3" s="261" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="256" t="s">
+      <c r="Q3" s="258" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="257"/>
+      <c r="R3" s="259"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="250" t="s">
+      <c r="T3" s="251" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="251"/>
+      <c r="U3" s="252"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -12333,20 +15016,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="247"/>
+      <c r="D4" s="254"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="247"/>
+      <c r="F4" s="254"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="245"/>
+      <c r="J4" s="260"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="248"/>
+      <c r="M4" s="261"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -12385,7 +15068,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="255" t="s">
+      <c r="F5" s="257" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -12393,7 +15076,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="247" t="s">
+      <c r="J5" s="254" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -12438,13 +15121,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="255"/>
+      <c r="F6" s="257"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="247"/>
+      <c r="J6" s="254"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -12488,13 +15171,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="245" t="s">
+      <c r="F7" s="260" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="254" t="s">
+      <c r="J7" s="256" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -12542,11 +15225,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="245"/>
+      <c r="F8" s="260"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="254"/>
+      <c r="J8" s="256"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -12590,7 +15273,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="255" t="s">
+      <c r="F9" s="257" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -12630,7 +15313,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="255"/>
+      <c r="F10" s="257"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -12756,7 +15439,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="248" t="s">
+      <c r="I13" s="261" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -12797,7 +15480,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="248"/>
+      <c r="I14" s="261"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -12832,7 +15515,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="248" t="s">
+      <c r="I15" s="261" t="s">
         <v>82</v>
       </c>
       <c r="J15" s="60"/>
@@ -12859,13 +15542,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="245" t="s">
+      <c r="A16" s="260" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="245" t="s">
+      <c r="B16" s="260" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="258" t="s">
+      <c r="C16" s="262" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -12875,7 +15558,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="248"/>
+      <c r="I16" s="261"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -12900,15 +15583,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="245"/>
-      <c r="B17" s="245"/>
-      <c r="C17" s="259"/>
+      <c r="A17" s="260"/>
+      <c r="B17" s="260"/>
+      <c r="C17" s="263"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="255" t="s">
+      <c r="I17" s="257" t="s">
         <v>139</v>
       </c>
       <c r="J17" s="71"/>
@@ -12943,7 +15626,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="255"/>
+      <c r="I18" s="257"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -13115,13 +15798,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="249" t="s">
+      <c r="A28" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="249"/>
-      <c r="C28" s="249"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
+      <c r="B28" s="266"/>
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
+      <c r="E28" s="266"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -13181,7 +15864,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="253" t="s">
+      <c r="E30" s="255" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -13215,7 +15898,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="253"/>
+      <c r="E31" s="255"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -13245,7 +15928,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="253" t="s">
+      <c r="E32" s="255" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -13275,7 +15958,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="253"/>
+      <c r="E33" s="255"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -13301,7 +15984,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="252" t="s">
+      <c r="E34" s="253" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -13324,7 +16007,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="252"/>
+      <c r="E35" s="253"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -13344,7 +16027,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="253" t="s">
+      <c r="E36" s="255" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -13361,7 +16044,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="253"/>
+      <c r="E37" s="255"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -13889,29 +16572,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="I17:I18"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="I13:I14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -14829,21 +17512,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="246" t="s">
+      <c r="A1" s="265" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="246"/>
-      <c r="C1" s="246"/>
-      <c r="D1" s="246"/>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
-      <c r="G1" s="246"/>
-      <c r="H1" s="246"/>
-      <c r="I1" s="246"/>
-      <c r="J1" s="246"/>
-      <c r="K1" s="246"/>
-      <c r="L1" s="246"/>
-      <c r="M1" s="246"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -14896,13 +17579,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="247" t="s">
+      <c r="D3" s="254" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="247" t="s">
+      <c r="F3" s="254" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -14911,24 +17594,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="245" t="s">
+      <c r="J3" s="260" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="248" t="s">
+      <c r="M3" s="261" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="256" t="s">
+      <c r="Q3" s="258" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="257"/>
+      <c r="R3" s="259"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="250" t="s">
+      <c r="T3" s="251" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="251"/>
+      <c r="U3" s="252"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -14940,20 +17623,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="247"/>
+      <c r="D4" s="254"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="247"/>
+      <c r="F4" s="254"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="245"/>
+      <c r="J4" s="260"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="248"/>
+      <c r="M4" s="261"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -14992,7 +17675,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="255" t="s">
+      <c r="F5" s="257" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -15000,7 +17683,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="247" t="s">
+      <c r="J5" s="254" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -15045,13 +17728,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="255"/>
+      <c r="F6" s="257"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="247"/>
+      <c r="J6" s="254"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -15095,13 +17778,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="245" t="s">
+      <c r="F7" s="260" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="254" t="s">
+      <c r="J7" s="256" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -15149,13 +17832,13 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="245"/>
+      <c r="F8" s="260"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="J8" s="254"/>
+      <c r="J8" s="256"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -15199,13 +17882,13 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="255" t="s">
+      <c r="F9" s="257" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
       <c r="H9" s="30"/>
       <c r="I9" s="134"/>
-      <c r="J9" s="248" t="s">
+      <c r="J9" s="261" t="s">
         <v>82</v>
       </c>
       <c r="K9" s="54"/>
@@ -15241,11 +17924,11 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="255"/>
+      <c r="F10" s="257"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
-      <c r="J10" s="248"/>
+      <c r="J10" s="261"/>
       <c r="K10" s="6"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
@@ -15368,7 +18051,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="248" t="s">
+      <c r="I13" s="261" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -15409,7 +18092,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="248"/>
+      <c r="I14" s="261"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -15444,7 +18127,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="260" t="s">
+      <c r="I15" s="267" t="s">
         <v>139</v>
       </c>
       <c r="J15" s="60"/>
@@ -15471,13 +18154,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="245" t="s">
+      <c r="A16" s="260" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="245" t="s">
+      <c r="B16" s="260" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="258" t="s">
+      <c r="C16" s="262" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -15487,7 +18170,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="260"/>
+      <c r="I16" s="267"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -15512,9 +18195,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="245"/>
-      <c r="B17" s="245"/>
-      <c r="C17" s="259"/>
+      <c r="A17" s="260"/>
+      <c r="B17" s="260"/>
+      <c r="C17" s="263"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -15725,13 +18408,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="249" t="s">
+      <c r="A28" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="249"/>
-      <c r="C28" s="249"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
+      <c r="B28" s="266"/>
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
+      <c r="E28" s="266"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -15791,7 +18474,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="253" t="s">
+      <c r="E30" s="255" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -15825,7 +18508,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="253"/>
+      <c r="E31" s="255"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -15855,7 +18538,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="253" t="s">
+      <c r="E32" s="255" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -15880,7 +18563,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="253"/>
+      <c r="E33" s="255"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -15901,7 +18584,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="252" t="s">
+      <c r="E34" s="253" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -15924,7 +18607,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="252"/>
+      <c r="E35" s="253"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -15944,7 +18627,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="253" t="s">
+      <c r="E36" s="255" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -15964,7 +18647,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="253"/>
+      <c r="E37" s="255"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -16492,11 +19175,17 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="A16:A17"/>
@@ -16504,17 +19193,11 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="F9:F10"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17431,21 +20114,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="246" t="s">
+      <c r="A1" s="265" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="246"/>
-      <c r="C1" s="246"/>
-      <c r="D1" s="246"/>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
-      <c r="G1" s="246"/>
-      <c r="H1" s="246"/>
-      <c r="I1" s="246"/>
-      <c r="J1" s="246"/>
-      <c r="K1" s="246"/>
-      <c r="L1" s="246"/>
-      <c r="M1" s="246"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -17500,13 +20183,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="247" t="s">
+      <c r="D3" s="254" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="247" t="s">
+      <c r="F3" s="254" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -17515,24 +20198,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="245" t="s">
+      <c r="J3" s="260" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="248" t="s">
+      <c r="M3" s="261" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="256" t="s">
+      <c r="Q3" s="258" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="257"/>
+      <c r="R3" s="259"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="250" t="s">
+      <c r="T3" s="251" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="251"/>
+      <c r="U3" s="252"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -17544,20 +20227,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="247"/>
+      <c r="D4" s="254"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="247"/>
+      <c r="F4" s="254"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="245"/>
+      <c r="J4" s="260"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="248"/>
+      <c r="M4" s="261"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -17596,7 +20279,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="255" t="s">
+      <c r="F5" s="257" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -17604,7 +20287,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="247" t="s">
+      <c r="J5" s="254" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -17649,13 +20332,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="255"/>
+      <c r="F6" s="257"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="247"/>
+      <c r="J6" s="254"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -17702,7 +20385,7 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="245" t="s">
+      <c r="F7" s="260" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
@@ -17710,7 +20393,7 @@
       <c r="I7" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="254" t="s">
+      <c r="J7" s="256" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -17758,10 +20441,10 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="245"/>
+      <c r="F8" s="260"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
-      <c r="J8" s="254"/>
+      <c r="J8" s="256"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -17805,7 +20488,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="255" t="s">
+      <c r="F9" s="257" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -17845,7 +20528,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="255"/>
+      <c r="F10" s="257"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -17972,7 +20655,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="248" t="s">
+      <c r="I13" s="261" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -18010,7 +20693,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="248"/>
+      <c r="I14" s="261"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -18045,7 +20728,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="248" t="s">
+      <c r="I15" s="261" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -18072,13 +20755,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="245" t="s">
+      <c r="A16" s="260" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="245" t="s">
+      <c r="B16" s="260" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="255" t="s">
+      <c r="C16" s="257" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -18088,7 +20771,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="248"/>
+      <c r="I16" s="261"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -18113,15 +20796,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="245"/>
-      <c r="B17" s="245"/>
-      <c r="C17" s="255"/>
+      <c r="A17" s="260"/>
+      <c r="B17" s="260"/>
+      <c r="C17" s="257"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="248" t="s">
+      <c r="I17" s="261" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -18156,7 +20839,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="248"/>
+      <c r="I18" s="261"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -18326,13 +21009,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="249" t="s">
+      <c r="A28" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="249"/>
-      <c r="C28" s="249"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
+      <c r="B28" s="266"/>
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
+      <c r="E28" s="266"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -18392,7 +21075,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="253" t="s">
+      <c r="E30" s="255" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -18426,7 +21109,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="253"/>
+      <c r="E31" s="255"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -18456,7 +21139,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="253" t="s">
+      <c r="E32" s="255" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -18482,7 +21165,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="253"/>
+      <c r="E33" s="255"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -18504,7 +21187,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="252" t="s">
+      <c r="E34" s="253" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -18527,7 +21210,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="252"/>
+      <c r="E35" s="253"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -18547,7 +21230,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="253" t="s">
+      <c r="E36" s="255" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -18564,7 +21247,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="253"/>
+      <c r="E37" s="255"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -19092,6 +21775,17 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="I17:I18"/>
     <mergeCell ref="A1:M1"/>
@@ -19104,17 +21798,6 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="I13:I14"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20034,21 +22717,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="246" t="s">
+      <c r="A1" s="265" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="246"/>
-      <c r="C1" s="246"/>
-      <c r="D1" s="246"/>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
-      <c r="G1" s="246"/>
-      <c r="H1" s="246"/>
-      <c r="I1" s="246"/>
-      <c r="J1" s="246"/>
-      <c r="K1" s="246"/>
-      <c r="L1" s="246"/>
-      <c r="M1" s="246"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -20103,13 +22786,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="247" t="s">
+      <c r="D3" s="254" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="247" t="s">
+      <c r="F3" s="254" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -20118,24 +22801,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="245" t="s">
+      <c r="J3" s="260" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="248" t="s">
+      <c r="M3" s="261" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="256" t="s">
+      <c r="Q3" s="258" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="257"/>
+      <c r="R3" s="259"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="250" t="s">
+      <c r="T3" s="251" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="251"/>
+      <c r="U3" s="252"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -20147,20 +22830,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="247"/>
+      <c r="D4" s="254"/>
       <c r="E4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="247"/>
+      <c r="F4" s="254"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="245"/>
+      <c r="J4" s="260"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="248"/>
+      <c r="M4" s="261"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -20199,7 +22882,7 @@
       <c r="E5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F5" s="255" t="s">
+      <c r="F5" s="257" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -20207,7 +22890,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="247" t="s">
+      <c r="J5" s="254" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -20252,13 +22935,13 @@
       <c r="E6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="255"/>
+      <c r="F6" s="257"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="247"/>
+      <c r="J6" s="254"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -20305,13 +22988,13 @@
       <c r="E7" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="245" t="s">
+      <c r="F7" s="260" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="254" t="s">
+      <c r="J7" s="256" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -20357,11 +23040,11 @@
         <v>17</v>
       </c>
       <c r="E8" s="30"/>
-      <c r="F8" s="245"/>
+      <c r="F8" s="260"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="254"/>
+      <c r="J8" s="256"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -20406,7 +23089,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="255" t="s">
+      <c r="F9" s="257" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -20446,7 +23129,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="255"/>
+      <c r="F10" s="257"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -20573,7 +23256,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="248" t="s">
+      <c r="I13" s="261" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -20614,7 +23297,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="248"/>
+      <c r="I14" s="261"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -20649,7 +23332,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="248" t="s">
+      <c r="I15" s="261" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -20676,13 +23359,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="245" t="s">
+      <c r="A16" s="260" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="245" t="s">
+      <c r="B16" s="260" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="255" t="s">
+      <c r="C16" s="257" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -20692,7 +23375,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="248"/>
+      <c r="I16" s="261"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -20717,15 +23400,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="245"/>
-      <c r="B17" s="245"/>
-      <c r="C17" s="255"/>
+      <c r="A17" s="260"/>
+      <c r="B17" s="260"/>
+      <c r="C17" s="257"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="248" t="s">
+      <c r="I17" s="261" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -20760,7 +23443,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="248"/>
+      <c r="I18" s="261"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -20931,13 +23614,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="249" t="s">
+      <c r="A28" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="249"/>
-      <c r="C28" s="249"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
+      <c r="B28" s="266"/>
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
+      <c r="E28" s="266"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -20997,7 +23680,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="253" t="s">
+      <c r="E30" s="255" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -21031,7 +23714,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="253"/>
+      <c r="E31" s="255"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -21059,7 +23742,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="253" t="s">
+      <c r="E32" s="255" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -21085,7 +23768,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="253"/>
+      <c r="E33" s="255"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -21107,7 +23790,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="252" t="s">
+      <c r="E34" s="253" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -21130,7 +23813,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="252"/>
+      <c r="E35" s="253"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -21150,7 +23833,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="253" t="s">
+      <c r="E36" s="255" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -21170,7 +23853,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="253"/>
+      <c r="E37" s="255"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -21700,29 +24383,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="I17:I18"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -21754,18 +24437,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="193" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="261" t="s">
+      <c r="A1" s="275" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="262"/>
-      <c r="C1" s="262"/>
-      <c r="D1" s="262"/>
-      <c r="E1" s="262"/>
-      <c r="F1" s="262"/>
-      <c r="G1" s="262"/>
-      <c r="H1" s="262"/>
-      <c r="I1" s="263"/>
-      <c r="J1" s="263"/>
+      <c r="B1" s="276"/>
+      <c r="C1" s="276"/>
+      <c r="D1" s="276"/>
+      <c r="E1" s="276"/>
+      <c r="F1" s="276"/>
+      <c r="G1" s="276"/>
+      <c r="H1" s="276"/>
+      <c r="I1" s="277"/>
+      <c r="J1" s="277"/>
       <c r="K1" s="190"/>
       <c r="L1" s="190"/>
       <c r="M1" s="191"/>
@@ -21871,22 +24554,22 @@
       <c r="C3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="247" t="s">
+      <c r="D3" s="254" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="201" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="264" t="s">
+      <c r="F3" s="268" t="s">
         <v>160</v>
       </c>
       <c r="H3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="254" t="s">
+      <c r="I3" s="256" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="265" t="s">
+      <c r="K3" s="269" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="2"/>
@@ -21902,16 +24585,16 @@
       <c r="C4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="247"/>
+      <c r="D4" s="254"/>
       <c r="E4" s="201" t="s">
         <v>162</v>
       </c>
-      <c r="F4" s="264"/>
+      <c r="F4" s="268"/>
       <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="254"/>
-      <c r="K4" s="266"/>
+      <c r="I4" s="256"/>
+      <c r="K4" s="270"/>
       <c r="L4" s="203" t="s">
         <v>163</v>
       </c>
@@ -21924,13 +24607,13 @@
       <c r="E5" s="129" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="264" t="s">
+      <c r="F5" s="268" t="s">
         <v>165</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="247" t="s">
+      <c r="I5" s="254" t="s">
         <v>166</v>
       </c>
       <c r="K5" s="2"/>
@@ -21944,11 +24627,11 @@
       <c r="E6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="264"/>
+      <c r="F6" s="268"/>
       <c r="H6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="247"/>
+      <c r="I6" s="254"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -21963,10 +24646,10 @@
       <c r="E7" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F7" s="247" t="s">
+      <c r="F7" s="254" t="s">
         <v>168</v>
       </c>
-      <c r="I7" s="247" t="s">
+      <c r="I7" s="254" t="s">
         <v>15</v>
       </c>
       <c r="K7" s="2"/>
@@ -21980,17 +24663,17 @@
       <c r="E8" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="247"/>
-      <c r="I8" s="247"/>
+      <c r="F8" s="254"/>
+      <c r="I8" s="254"/>
       <c r="K8" s="2"/>
       <c r="L8" s="206"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="258" t="s">
+      <c r="A9" s="262" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="247" t="s">
+      <c r="B9" s="254" t="s">
         <v>171</v>
       </c>
       <c r="C9" s="207" t="s">
@@ -21999,7 +24682,7 @@
       <c r="E9" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="264" t="s">
+      <c r="F9" s="268" t="s">
         <v>173</v>
       </c>
       <c r="K9" s="2"/>
@@ -22009,15 +24692,15 @@
       <c r="P9"/>
     </row>
     <row r="10" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="259"/>
-      <c r="B10" s="247"/>
+      <c r="A10" s="263"/>
+      <c r="B10" s="254"/>
       <c r="C10" s="208" t="s">
         <v>174</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>175</v>
       </c>
-      <c r="F10" s="264"/>
+      <c r="F10" s="268"/>
       <c r="K10" s="209"/>
       <c r="L10" s="2"/>
       <c r="M10" s="206"/>
@@ -22044,7 +24727,7 @@
       <c r="E11" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="F11" s="245" t="s">
+      <c r="F11" s="260" t="s">
         <v>177</v>
       </c>
       <c r="K11" s="209"/>
@@ -22073,7 +24756,7 @@
       <c r="E12" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="245"/>
+      <c r="F12" s="260"/>
       <c r="G12" s="212" t="s">
         <v>179</v>
       </c>
@@ -22112,10 +24795,10 @@
       <c r="E13" s="183" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="267" t="s">
+      <c r="F13" s="271" t="s">
         <v>184</v>
       </c>
-      <c r="H13" s="258" t="s">
+      <c r="H13" s="262" t="s">
         <v>185</v>
       </c>
       <c r="K13" s="2"/>
@@ -22145,8 +24828,8 @@
       <c r="E14" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="F14" s="268"/>
-      <c r="H14" s="259"/>
+      <c r="F14" s="272"/>
+      <c r="H14" s="263"/>
       <c r="K14" s="2"/>
       <c r="L14" s="6"/>
       <c r="M14" s="2"/>
@@ -22173,10 +24856,10 @@
       <c r="E15" s="183" t="s">
         <v>189</v>
       </c>
-      <c r="F15" s="247" t="s">
+      <c r="F15" s="254" t="s">
         <v>190</v>
       </c>
-      <c r="H15" s="265" t="s">
+      <c r="H15" s="269" t="s">
         <v>45</v>
       </c>
       <c r="K15" s="2"/>
@@ -22201,8 +24884,8 @@
       <c r="C16" s="183" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="247"/>
-      <c r="H16" s="266"/>
+      <c r="F16" s="254"/>
+      <c r="H16" s="270"/>
       <c r="K16" s="2"/>
       <c r="L16" s="209"/>
       <c r="M16" s="8"/>
@@ -22229,7 +24912,7 @@
       </c>
       <c r="D17" s="206"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="269" t="s">
+      <c r="F17" s="273" t="s">
         <v>193</v>
       </c>
       <c r="G17" s="2"/>
@@ -22246,7 +24929,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="270"/>
+      <c r="F18" s="274"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="209"/>
@@ -22297,7 +24980,7 @@
       <c r="B20" s="133" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="247" t="s">
+      <c r="C20" s="254" t="s">
         <v>197</v>
       </c>
       <c r="D20" s="2"/>
@@ -22329,7 +25012,7 @@
         <v>199</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="247"/>
+      <c r="C21" s="254"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="219" t="s">
@@ -22337,7 +25020,7 @@
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="265" t="s">
+      <c r="I21" s="269" t="s">
         <v>82</v>
       </c>
       <c r="J21" s="209"/>
@@ -22371,7 +25054,7 @@
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="266"/>
+      <c r="I22" s="270"/>
       <c r="J22" s="209"/>
       <c r="K22" s="101" t="s">
         <v>40</v>
@@ -23101,11 +25784,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="F9:F10"/>
@@ -23116,11 +25799,11 @@
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="F17:F18"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -24040,21 +26723,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="246" t="s">
+      <c r="A1" s="265" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="246"/>
-      <c r="C1" s="246"/>
-      <c r="D1" s="246"/>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
-      <c r="G1" s="246"/>
-      <c r="H1" s="246"/>
-      <c r="I1" s="246"/>
-      <c r="J1" s="246"/>
-      <c r="K1" s="246"/>
-      <c r="L1" s="246"/>
-      <c r="M1" s="246"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -24109,13 +26792,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="248" t="s">
+      <c r="D3" s="261" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="247" t="s">
+      <c r="F3" s="254" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -24124,24 +26807,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="248" t="s">
+      <c r="J3" s="261" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="271" t="s">
+      <c r="M3" s="278" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="256" t="s">
+      <c r="Q3" s="258" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="257"/>
+      <c r="R3" s="259"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="250" t="s">
+      <c r="T3" s="251" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="251"/>
+      <c r="U3" s="252"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -24155,20 +26838,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="248"/>
+      <c r="D4" s="261"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="247"/>
+      <c r="F4" s="254"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="248"/>
+      <c r="J4" s="261"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="271"/>
+      <c r="M4" s="278"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -24207,7 +26890,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="255" t="s">
+      <c r="F5" s="257" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -24215,7 +26898,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="247" t="s">
+      <c r="J5" s="254" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -24260,13 +26943,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="255"/>
+      <c r="F6" s="257"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="247"/>
+      <c r="J6" s="254"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -24310,13 +26993,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="245" t="s">
+      <c r="F7" s="260" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="254" t="s">
+      <c r="J7" s="256" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -24364,11 +27047,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="245"/>
+      <c r="F8" s="260"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="254"/>
+      <c r="J8" s="256"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -24413,7 +27096,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="255" t="s">
+      <c r="F9" s="257" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -24453,7 +27136,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="255"/>
+      <c r="F10" s="257"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -24675,13 +27358,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="245" t="s">
+      <c r="A16" s="260" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="245" t="s">
+      <c r="B16" s="260" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="248" t="s">
+      <c r="C16" s="261" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -24716,9 +27399,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="245"/>
-      <c r="B17" s="245"/>
-      <c r="C17" s="248"/>
+      <c r="A17" s="260"/>
+      <c r="B17" s="260"/>
+      <c r="C17" s="261"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -24928,13 +27611,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="249" t="s">
+      <c r="A28" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="249"/>
-      <c r="C28" s="249"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
+      <c r="B28" s="266"/>
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
+      <c r="E28" s="266"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -24994,7 +27677,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="253" t="s">
+      <c r="E30" s="255" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -25026,7 +27709,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="253"/>
+      <c r="E31" s="255"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -25054,7 +27737,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="253" t="s">
+      <c r="E32" s="255" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -25082,7 +27765,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="253"/>
+      <c r="E33" s="255"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -25106,7 +27789,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="252" t="s">
+      <c r="E34" s="253" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -25129,7 +27812,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="252"/>
+      <c r="E35" s="253"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -25149,7 +27832,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="253" t="s">
+      <c r="E36" s="255" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -25169,7 +27852,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="253"/>
+      <c r="E37" s="255"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -25697,26 +28380,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -26634,21 +29317,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="246" t="s">
+      <c r="A1" s="265" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="246"/>
-      <c r="C1" s="246"/>
-      <c r="D1" s="246"/>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
-      <c r="G1" s="246"/>
-      <c r="H1" s="246"/>
-      <c r="I1" s="246"/>
-      <c r="J1" s="246"/>
-      <c r="K1" s="246"/>
-      <c r="L1" s="246"/>
-      <c r="M1" s="246"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
+      <c r="K1" s="265"/>
+      <c r="L1" s="265"/>
+      <c r="M1" s="265"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -26703,13 +29386,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="248" t="s">
+      <c r="D3" s="261" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="247" t="s">
+      <c r="F3" s="254" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -26718,24 +29401,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="248" t="s">
+      <c r="J3" s="261" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="271" t="s">
+      <c r="M3" s="278" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="256" t="s">
+      <c r="Q3" s="258" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="257"/>
+      <c r="R3" s="259"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="250" t="s">
+      <c r="T3" s="251" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="251"/>
+      <c r="U3" s="252"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -26749,20 +29432,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="248"/>
+      <c r="D4" s="261"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="247"/>
+      <c r="F4" s="254"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="248"/>
+      <c r="J4" s="261"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="271"/>
+      <c r="M4" s="278"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -26801,7 +29484,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="255" t="s">
+      <c r="F5" s="257" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -26809,7 +29492,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="247" t="s">
+      <c r="J5" s="254" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -26854,13 +29537,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="255"/>
+      <c r="F6" s="257"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="247"/>
+      <c r="J6" s="254"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -26904,13 +29587,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="245" t="s">
+      <c r="F7" s="260" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="254" t="s">
+      <c r="J7" s="256" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -26958,11 +29641,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="245"/>
+      <c r="F8" s="260"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="254"/>
+      <c r="J8" s="256"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -27007,7 +29690,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="255" t="s">
+      <c r="F9" s="257" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -27047,7 +29730,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="255"/>
+      <c r="F10" s="257"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -27269,13 +29952,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="245" t="s">
+      <c r="A16" s="260" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="245" t="s">
+      <c r="B16" s="260" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="248" t="s">
+      <c r="C16" s="261" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -27310,9 +29993,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="245"/>
-      <c r="B17" s="245"/>
-      <c r="C17" s="248"/>
+      <c r="A17" s="260"/>
+      <c r="B17" s="260"/>
+      <c r="C17" s="261"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -27522,13 +30205,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="249" t="s">
+      <c r="A28" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="249"/>
-      <c r="C28" s="249"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
+      <c r="B28" s="266"/>
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
+      <c r="E28" s="266"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -27588,7 +30271,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="253" t="s">
+      <c r="E30" s="255" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -27622,7 +30305,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="253"/>
+      <c r="E31" s="255"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -27650,7 +30333,7 @@
       <c r="D32" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="253" t="s">
+      <c r="E32" s="255" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -27678,7 +30361,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="253"/>
+      <c r="E33" s="255"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -27702,7 +30385,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="252" t="s">
+      <c r="E34" s="253" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -27727,7 +30410,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="252"/>
+      <c r="E35" s="253"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -27749,7 +30432,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="253" t="s">
+      <c r="E36" s="255" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -27771,7 +30454,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="253"/>
+      <c r="E37" s="255"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -28299,18 +30982,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="A16:A17"/>
@@ -28319,6 +30990,18 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/raw/D3.xlsx
+++ b/raw/D3.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971B6A8C-AC8E-4944-AF4D-C9CB341F7F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6375DA3-D005-41F7-9DEA-069D9C58345D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30-2" sheetId="34" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="16" sheetId="42" r:id="rId9"/>
     <sheet name="17" sheetId="43" r:id="rId10"/>
     <sheet name="17-2" sheetId="44" r:id="rId11"/>
+    <sheet name="18" sheetId="45" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -218,6 +219,62 @@
           </rPr>
           <t>Алібек
 87012894507</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{E44DACBB-9641-4BEF-8811-86790F380B93}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Аслан
+87014988298</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{6E5BDA00-2299-473E-9E55-CA44B73E9FA4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Алібек
+87012894507</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{A7732882-F2F4-4DBE-A347-39AE42F4652A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Даулет
+87025167087</t>
         </r>
       </text>
     </comment>
@@ -921,7 +978,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="245">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -2476,7 +2533,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="279">
+  <cellXfs count="291">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3205,10 +3262,46 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3225,28 +3318,22 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3270,17 +3357,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4475,21 +4568,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="265" t="s">
+      <c r="A1" s="260" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
+      <c r="L1" s="260"/>
+      <c r="M1" s="260"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4544,13 +4637,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="254" t="s">
+      <c r="D3" s="261" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="254" t="s">
+      <c r="F3" s="261" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -4562,24 +4655,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="260" t="s">
+      <c r="J3" s="259" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="261" t="s">
+      <c r="M3" s="262" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="258" t="s">
+      <c r="Q3" s="270" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="259"/>
+      <c r="R3" s="271"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="251" t="s">
+      <c r="T3" s="264" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="252"/>
+      <c r="U3" s="265"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -4591,20 +4684,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="254"/>
+      <c r="D4" s="261"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="254"/>
+      <c r="F4" s="261"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="260"/>
+      <c r="J4" s="259"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="261"/>
+      <c r="M4" s="262"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -4643,7 +4736,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="257" t="s">
+      <c r="F5" s="269" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -4651,7 +4744,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="254" t="s">
+      <c r="J5" s="261" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -4696,13 +4789,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="257"/>
+      <c r="F6" s="269"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="254"/>
+      <c r="J6" s="261"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -4748,13 +4841,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="260" t="s">
+      <c r="F7" s="259" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="256" t="s">
+      <c r="J7" s="268" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -4802,11 +4895,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="260"/>
+      <c r="F8" s="259"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="256"/>
+      <c r="J8" s="268"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -4850,7 +4943,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="257" t="s">
+      <c r="F9" s="269" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -4890,7 +4983,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="257"/>
+      <c r="F10" s="269"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -5015,7 +5108,7 @@
         <v>115</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="261" t="s">
+      <c r="H13" s="262" t="s">
         <v>82</v>
       </c>
       <c r="I13" s="30"/>
@@ -5054,7 +5147,7 @@
       <c r="F14" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="261"/>
+      <c r="H14" s="262"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -5089,7 +5182,7 @@
         <v>83</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="261" t="s">
+      <c r="H15" s="262" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="30"/>
@@ -5126,7 +5219,7 @@
         <v>81</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="261"/>
+      <c r="H16" s="262"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -5158,7 +5251,7 @@
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="262" t="s">
+      <c r="H17" s="272" t="s">
         <v>45</v>
       </c>
       <c r="I17" s="30"/>
@@ -5193,7 +5286,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="263"/>
+      <c r="H18" s="273"/>
       <c r="I18" s="30"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
@@ -5210,7 +5303,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="260" t="s">
+      <c r="H19" s="259" t="s">
         <v>85</v>
       </c>
       <c r="I19" s="30"/>
@@ -5235,7 +5328,7 @@
       <c r="E20" s="137"/>
       <c r="F20" s="8"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="260"/>
+      <c r="H20" s="259"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -5254,7 +5347,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="260" t="s">
+      <c r="H21" s="259" t="s">
         <v>84</v>
       </c>
       <c r="I21" s="30"/>
@@ -5271,7 +5364,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="137"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="260"/>
+      <c r="H22" s="259"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -5368,13 +5461,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="266" t="s">
+      <c r="A28" s="263" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="266"/>
-      <c r="C28" s="266"/>
-      <c r="D28" s="266"/>
-      <c r="E28" s="266"/>
+      <c r="B28" s="263"/>
+      <c r="C28" s="263"/>
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -5434,7 +5527,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="255" t="s">
+      <c r="E30" s="267" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -5468,7 +5561,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="267"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -5498,7 +5591,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="255" t="s">
+      <c r="E32" s="267" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="8"/>
@@ -5524,7 +5617,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="255"/>
+      <c r="E33" s="267"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
       <c r="I33" s="30"/>
@@ -5547,7 +5640,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="253" t="s">
+      <c r="E34" s="266" t="s">
         <v>133</v>
       </c>
       <c r="G34" s="8"/>
@@ -5568,7 +5661,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="253"/>
+      <c r="E35" s="266"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
       <c r="I35" s="30"/>
@@ -5587,7 +5680,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="255" t="s">
+      <c r="E36" s="267" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -5607,7 +5700,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="255"/>
+      <c r="E37" s="267"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -6074,7 +6167,7 @@
       <c r="S65"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A66" s="264" t="s">
+      <c r="A66" s="258" t="s">
         <v>139</v>
       </c>
       <c r="L66" s="119" t="s">
@@ -6086,7 +6179,7 @@
       <c r="S66"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A67" s="264"/>
+      <c r="A67" s="258"/>
       <c r="L67" s="119" t="s">
         <v>95</v>
       </c>
@@ -6138,14 +6231,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A28:E28"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="J5:J6"/>
@@ -6161,6 +6246,14 @@
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="H17:H18"/>
     <mergeCell ref="H19:H20"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A28:E28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -7077,21 +7170,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="265" t="s">
+      <c r="A1" s="260" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
+      <c r="L1" s="260"/>
+      <c r="M1" s="260"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -7150,7 +7243,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="254" t="s">
+      <c r="F3" s="261" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -7159,24 +7252,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="256" t="s">
+      <c r="J3" s="268" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="278" t="s">
+      <c r="M3" s="285" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="258" t="s">
+      <c r="Q3" s="270" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="259"/>
+      <c r="R3" s="271"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="251" t="s">
+      <c r="T3" s="264" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="252"/>
+      <c r="U3" s="265"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -7194,16 +7287,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="254"/>
+      <c r="F4" s="261"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="256"/>
+      <c r="J4" s="268"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="278"/>
+      <c r="M4" s="285"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -7242,7 +7335,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="257" t="s">
+      <c r="F5" s="269" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -7250,7 +7343,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="254" t="s">
+      <c r="J5" s="261" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -7295,13 +7388,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="257"/>
+      <c r="F6" s="269"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="254"/>
+      <c r="J6" s="261"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -7348,7 +7441,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="257" t="s">
+      <c r="F7" s="269" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -7400,7 +7493,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="257"/>
+      <c r="F8" s="269"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -7616,7 +7709,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="260" t="s">
+      <c r="H13" s="259" t="s">
         <v>121</v>
       </c>
       <c r="I13" s="30"/>
@@ -7652,7 +7745,7 @@
       <c r="F14" s="240" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="260"/>
+      <c r="H14" s="259"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -7685,7 +7778,7 @@
       <c r="E15" s="240"/>
       <c r="F15" s="8"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="260" t="s">
+      <c r="H15" s="259" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="30"/>
@@ -7714,7 +7807,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="260" t="s">
+      <c r="B16" s="259" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="8"/>
@@ -7722,7 +7815,7 @@
       <c r="E16" s="59"/>
       <c r="F16" s="8"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="260"/>
+      <c r="H16" s="259"/>
       <c r="I16" s="30"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
@@ -7749,13 +7842,13 @@
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
-      <c r="B17" s="260"/>
+      <c r="B17" s="259"/>
       <c r="C17" s="8"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="261" t="s">
+      <c r="H17" s="262" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -7790,7 +7883,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="261"/>
+      <c r="H18" s="262"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -7807,7 +7900,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="261" t="s">
+      <c r="H19" s="262" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -7832,7 +7925,7 @@
       <c r="E20" s="240"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="261"/>
+      <c r="H20" s="262"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -7851,7 +7944,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="261" t="s">
+      <c r="H21" s="262" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -7869,7 +7962,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="240"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="261"/>
+      <c r="H22" s="262"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -7966,13 +8059,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="266" t="s">
+      <c r="A28" s="263" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="266"/>
-      <c r="C28" s="266"/>
-      <c r="D28" s="266"/>
-      <c r="E28" s="266"/>
+      <c r="B28" s="263"/>
+      <c r="C28" s="263"/>
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -8032,7 +8125,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="255" t="s">
+      <c r="E30" s="267" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -8066,7 +8159,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="267"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -8093,7 +8186,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="255" t="s">
+      <c r="E32" s="267" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -8121,7 +8214,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="255"/>
+      <c r="E33" s="267"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -8145,7 +8238,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="253" t="s">
+      <c r="E34" s="266" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -8170,7 +8263,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="253"/>
+      <c r="E35" s="266"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -8192,7 +8285,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="255" t="s">
+      <c r="E36" s="267" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -8214,7 +8307,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="255"/>
+      <c r="E37" s="267"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -8746,18 +8839,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="H15:H16"/>
@@ -8766,6 +8847,18 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -9682,21 +9775,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="265" t="s">
+      <c r="A1" s="260" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
+      <c r="L1" s="260"/>
+      <c r="M1" s="260"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -9755,7 +9848,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="254" t="s">
+      <c r="F3" s="261" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -9764,24 +9857,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="256" t="s">
+      <c r="J3" s="268" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="261" t="s">
+      <c r="M3" s="262" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="258" t="s">
+      <c r="Q3" s="270" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="259"/>
+      <c r="R3" s="271"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="251" t="s">
+      <c r="T3" s="264" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="252"/>
+      <c r="U3" s="265"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -9799,16 +9892,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="254"/>
+      <c r="F4" s="261"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="256"/>
+      <c r="J4" s="268"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="261"/>
+      <c r="M4" s="262"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -9847,7 +9940,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="257" t="s">
+      <c r="F5" s="269" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -9855,7 +9948,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="254" t="s">
+      <c r="J5" s="261" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -9900,13 +9993,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="257"/>
+      <c r="F6" s="269"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="254"/>
+      <c r="J6" s="261"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -9953,7 +10046,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="257" t="s">
+      <c r="F7" s="269" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -10005,7 +10098,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="257"/>
+      <c r="F8" s="269"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -10221,7 +10314,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="260" t="s">
+      <c r="H13" s="259" t="s">
         <v>121</v>
       </c>
       <c r="I13" s="30"/>
@@ -10257,7 +10350,7 @@
       <c r="F14" s="248" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="260"/>
+      <c r="H14" s="259"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -10290,7 +10383,7 @@
       <c r="E15" s="248"/>
       <c r="F15" s="8"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="260" t="s">
+      <c r="H15" s="259" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="30"/>
@@ -10319,7 +10412,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="260" t="s">
+      <c r="B16" s="259" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="8"/>
@@ -10327,7 +10420,7 @@
       <c r="E16" s="59"/>
       <c r="F16" s="8"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="260"/>
+      <c r="H16" s="259"/>
       <c r="I16" s="30"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
@@ -10354,13 +10447,13 @@
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
-      <c r="B17" s="260"/>
+      <c r="B17" s="259"/>
       <c r="C17" s="8"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="261" t="s">
+      <c r="H17" s="262" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -10395,7 +10488,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="261"/>
+      <c r="H18" s="262"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -10412,7 +10505,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="261" t="s">
+      <c r="H19" s="262" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -10437,7 +10530,7 @@
       <c r="E20" s="248"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="261"/>
+      <c r="H20" s="262"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -10456,7 +10549,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="261" t="s">
+      <c r="H21" s="262" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -10474,7 +10567,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="248"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="261"/>
+      <c r="H22" s="262"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -10571,13 +10664,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="266" t="s">
+      <c r="A28" s="263" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="266"/>
-      <c r="C28" s="266"/>
-      <c r="D28" s="266"/>
-      <c r="E28" s="266"/>
+      <c r="B28" s="263"/>
+      <c r="C28" s="263"/>
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -10637,7 +10730,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="255" t="s">
+      <c r="E30" s="267" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -10671,7 +10764,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="267"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -10701,7 +10794,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="255" t="s">
+      <c r="E32" s="267" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -10729,7 +10822,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="255"/>
+      <c r="E33" s="267"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -10753,7 +10846,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="253" t="s">
+      <c r="E34" s="266" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -10777,7 +10870,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="253"/>
+      <c r="E35" s="266"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -10799,7 +10892,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="255" t="s">
+      <c r="E36" s="267" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -10819,7 +10912,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="255"/>
+      <c r="E37" s="267"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -11351,6 +11444,19 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="H19:H20"/>
     <mergeCell ref="H21:H22"/>
@@ -11358,13 +11464,2603 @@
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="E34:E35"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B58EED56-DD65-43F7-989E-9E340DCA549D}">
+  <dimension ref="A1:W72"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" style="98" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" style="25" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" style="25" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" style="25" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" customWidth="1"/>
+    <col min="14" max="14" width="21.26953125" customWidth="1"/>
+    <col min="15" max="15" width="9.7265625" customWidth="1"/>
+    <col min="16" max="16" width="7.7265625" customWidth="1"/>
+    <col min="17" max="17" width="6.453125" customWidth="1"/>
+    <col min="18" max="18" width="7.81640625" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" style="84" customWidth="1"/>
+    <col min="20" max="20" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="257" max="260" width="14.453125" customWidth="1"/>
+    <col min="261" max="261" width="15.453125" customWidth="1"/>
+    <col min="262" max="262" width="14.54296875" customWidth="1"/>
+    <col min="263" max="263" width="15.26953125" customWidth="1"/>
+    <col min="264" max="265" width="14.453125" customWidth="1"/>
+    <col min="266" max="266" width="13.1796875" customWidth="1"/>
+    <col min="267" max="269" width="14.453125" customWidth="1"/>
+    <col min="270" max="270" width="15.81640625" customWidth="1"/>
+    <col min="271" max="271" width="7.81640625" customWidth="1"/>
+    <col min="272" max="272" width="5.453125" customWidth="1"/>
+    <col min="273" max="273" width="6.453125" customWidth="1"/>
+    <col min="274" max="274" width="7.81640625" customWidth="1"/>
+    <col min="275" max="275" width="3" customWidth="1"/>
+    <col min="276" max="276" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="513" max="516" width="14.453125" customWidth="1"/>
+    <col min="517" max="517" width="15.453125" customWidth="1"/>
+    <col min="518" max="518" width="14.54296875" customWidth="1"/>
+    <col min="519" max="519" width="15.26953125" customWidth="1"/>
+    <col min="520" max="521" width="14.453125" customWidth="1"/>
+    <col min="522" max="522" width="13.1796875" customWidth="1"/>
+    <col min="523" max="525" width="14.453125" customWidth="1"/>
+    <col min="526" max="526" width="15.81640625" customWidth="1"/>
+    <col min="527" max="527" width="7.81640625" customWidth="1"/>
+    <col min="528" max="528" width="5.453125" customWidth="1"/>
+    <col min="529" max="529" width="6.453125" customWidth="1"/>
+    <col min="530" max="530" width="7.81640625" customWidth="1"/>
+    <col min="531" max="531" width="3" customWidth="1"/>
+    <col min="532" max="532" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="769" max="772" width="14.453125" customWidth="1"/>
+    <col min="773" max="773" width="15.453125" customWidth="1"/>
+    <col min="774" max="774" width="14.54296875" customWidth="1"/>
+    <col min="775" max="775" width="15.26953125" customWidth="1"/>
+    <col min="776" max="777" width="14.453125" customWidth="1"/>
+    <col min="778" max="778" width="13.1796875" customWidth="1"/>
+    <col min="779" max="781" width="14.453125" customWidth="1"/>
+    <col min="782" max="782" width="15.81640625" customWidth="1"/>
+    <col min="783" max="783" width="7.81640625" customWidth="1"/>
+    <col min="784" max="784" width="5.453125" customWidth="1"/>
+    <col min="785" max="785" width="6.453125" customWidth="1"/>
+    <col min="786" max="786" width="7.81640625" customWidth="1"/>
+    <col min="787" max="787" width="3" customWidth="1"/>
+    <col min="788" max="788" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1025" max="1028" width="14.453125" customWidth="1"/>
+    <col min="1029" max="1029" width="15.453125" customWidth="1"/>
+    <col min="1030" max="1030" width="14.54296875" customWidth="1"/>
+    <col min="1031" max="1031" width="15.26953125" customWidth="1"/>
+    <col min="1032" max="1033" width="14.453125" customWidth="1"/>
+    <col min="1034" max="1034" width="13.1796875" customWidth="1"/>
+    <col min="1035" max="1037" width="14.453125" customWidth="1"/>
+    <col min="1038" max="1038" width="15.81640625" customWidth="1"/>
+    <col min="1039" max="1039" width="7.81640625" customWidth="1"/>
+    <col min="1040" max="1040" width="5.453125" customWidth="1"/>
+    <col min="1041" max="1041" width="6.453125" customWidth="1"/>
+    <col min="1042" max="1042" width="7.81640625" customWidth="1"/>
+    <col min="1043" max="1043" width="3" customWidth="1"/>
+    <col min="1044" max="1044" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1281" max="1284" width="14.453125" customWidth="1"/>
+    <col min="1285" max="1285" width="15.453125" customWidth="1"/>
+    <col min="1286" max="1286" width="14.54296875" customWidth="1"/>
+    <col min="1287" max="1287" width="15.26953125" customWidth="1"/>
+    <col min="1288" max="1289" width="14.453125" customWidth="1"/>
+    <col min="1290" max="1290" width="13.1796875" customWidth="1"/>
+    <col min="1291" max="1293" width="14.453125" customWidth="1"/>
+    <col min="1294" max="1294" width="15.81640625" customWidth="1"/>
+    <col min="1295" max="1295" width="7.81640625" customWidth="1"/>
+    <col min="1296" max="1296" width="5.453125" customWidth="1"/>
+    <col min="1297" max="1297" width="6.453125" customWidth="1"/>
+    <col min="1298" max="1298" width="7.81640625" customWidth="1"/>
+    <col min="1299" max="1299" width="3" customWidth="1"/>
+    <col min="1300" max="1300" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1537" max="1540" width="14.453125" customWidth="1"/>
+    <col min="1541" max="1541" width="15.453125" customWidth="1"/>
+    <col min="1542" max="1542" width="14.54296875" customWidth="1"/>
+    <col min="1543" max="1543" width="15.26953125" customWidth="1"/>
+    <col min="1544" max="1545" width="14.453125" customWidth="1"/>
+    <col min="1546" max="1546" width="13.1796875" customWidth="1"/>
+    <col min="1547" max="1549" width="14.453125" customWidth="1"/>
+    <col min="1550" max="1550" width="15.81640625" customWidth="1"/>
+    <col min="1551" max="1551" width="7.81640625" customWidth="1"/>
+    <col min="1552" max="1552" width="5.453125" customWidth="1"/>
+    <col min="1553" max="1553" width="6.453125" customWidth="1"/>
+    <col min="1554" max="1554" width="7.81640625" customWidth="1"/>
+    <col min="1555" max="1555" width="3" customWidth="1"/>
+    <col min="1556" max="1556" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1793" max="1796" width="14.453125" customWidth="1"/>
+    <col min="1797" max="1797" width="15.453125" customWidth="1"/>
+    <col min="1798" max="1798" width="14.54296875" customWidth="1"/>
+    <col min="1799" max="1799" width="15.26953125" customWidth="1"/>
+    <col min="1800" max="1801" width="14.453125" customWidth="1"/>
+    <col min="1802" max="1802" width="13.1796875" customWidth="1"/>
+    <col min="1803" max="1805" width="14.453125" customWidth="1"/>
+    <col min="1806" max="1806" width="15.81640625" customWidth="1"/>
+    <col min="1807" max="1807" width="7.81640625" customWidth="1"/>
+    <col min="1808" max="1808" width="5.453125" customWidth="1"/>
+    <col min="1809" max="1809" width="6.453125" customWidth="1"/>
+    <col min="1810" max="1810" width="7.81640625" customWidth="1"/>
+    <col min="1811" max="1811" width="3" customWidth="1"/>
+    <col min="1812" max="1812" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2049" max="2052" width="14.453125" customWidth="1"/>
+    <col min="2053" max="2053" width="15.453125" customWidth="1"/>
+    <col min="2054" max="2054" width="14.54296875" customWidth="1"/>
+    <col min="2055" max="2055" width="15.26953125" customWidth="1"/>
+    <col min="2056" max="2057" width="14.453125" customWidth="1"/>
+    <col min="2058" max="2058" width="13.1796875" customWidth="1"/>
+    <col min="2059" max="2061" width="14.453125" customWidth="1"/>
+    <col min="2062" max="2062" width="15.81640625" customWidth="1"/>
+    <col min="2063" max="2063" width="7.81640625" customWidth="1"/>
+    <col min="2064" max="2064" width="5.453125" customWidth="1"/>
+    <col min="2065" max="2065" width="6.453125" customWidth="1"/>
+    <col min="2066" max="2066" width="7.81640625" customWidth="1"/>
+    <col min="2067" max="2067" width="3" customWidth="1"/>
+    <col min="2068" max="2068" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2305" max="2308" width="14.453125" customWidth="1"/>
+    <col min="2309" max="2309" width="15.453125" customWidth="1"/>
+    <col min="2310" max="2310" width="14.54296875" customWidth="1"/>
+    <col min="2311" max="2311" width="15.26953125" customWidth="1"/>
+    <col min="2312" max="2313" width="14.453125" customWidth="1"/>
+    <col min="2314" max="2314" width="13.1796875" customWidth="1"/>
+    <col min="2315" max="2317" width="14.453125" customWidth="1"/>
+    <col min="2318" max="2318" width="15.81640625" customWidth="1"/>
+    <col min="2319" max="2319" width="7.81640625" customWidth="1"/>
+    <col min="2320" max="2320" width="5.453125" customWidth="1"/>
+    <col min="2321" max="2321" width="6.453125" customWidth="1"/>
+    <col min="2322" max="2322" width="7.81640625" customWidth="1"/>
+    <col min="2323" max="2323" width="3" customWidth="1"/>
+    <col min="2324" max="2324" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2561" max="2564" width="14.453125" customWidth="1"/>
+    <col min="2565" max="2565" width="15.453125" customWidth="1"/>
+    <col min="2566" max="2566" width="14.54296875" customWidth="1"/>
+    <col min="2567" max="2567" width="15.26953125" customWidth="1"/>
+    <col min="2568" max="2569" width="14.453125" customWidth="1"/>
+    <col min="2570" max="2570" width="13.1796875" customWidth="1"/>
+    <col min="2571" max="2573" width="14.453125" customWidth="1"/>
+    <col min="2574" max="2574" width="15.81640625" customWidth="1"/>
+    <col min="2575" max="2575" width="7.81640625" customWidth="1"/>
+    <col min="2576" max="2576" width="5.453125" customWidth="1"/>
+    <col min="2577" max="2577" width="6.453125" customWidth="1"/>
+    <col min="2578" max="2578" width="7.81640625" customWidth="1"/>
+    <col min="2579" max="2579" width="3" customWidth="1"/>
+    <col min="2580" max="2580" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2817" max="2820" width="14.453125" customWidth="1"/>
+    <col min="2821" max="2821" width="15.453125" customWidth="1"/>
+    <col min="2822" max="2822" width="14.54296875" customWidth="1"/>
+    <col min="2823" max="2823" width="15.26953125" customWidth="1"/>
+    <col min="2824" max="2825" width="14.453125" customWidth="1"/>
+    <col min="2826" max="2826" width="13.1796875" customWidth="1"/>
+    <col min="2827" max="2829" width="14.453125" customWidth="1"/>
+    <col min="2830" max="2830" width="15.81640625" customWidth="1"/>
+    <col min="2831" max="2831" width="7.81640625" customWidth="1"/>
+    <col min="2832" max="2832" width="5.453125" customWidth="1"/>
+    <col min="2833" max="2833" width="6.453125" customWidth="1"/>
+    <col min="2834" max="2834" width="7.81640625" customWidth="1"/>
+    <col min="2835" max="2835" width="3" customWidth="1"/>
+    <col min="2836" max="2836" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3073" max="3076" width="14.453125" customWidth="1"/>
+    <col min="3077" max="3077" width="15.453125" customWidth="1"/>
+    <col min="3078" max="3078" width="14.54296875" customWidth="1"/>
+    <col min="3079" max="3079" width="15.26953125" customWidth="1"/>
+    <col min="3080" max="3081" width="14.453125" customWidth="1"/>
+    <col min="3082" max="3082" width="13.1796875" customWidth="1"/>
+    <col min="3083" max="3085" width="14.453125" customWidth="1"/>
+    <col min="3086" max="3086" width="15.81640625" customWidth="1"/>
+    <col min="3087" max="3087" width="7.81640625" customWidth="1"/>
+    <col min="3088" max="3088" width="5.453125" customWidth="1"/>
+    <col min="3089" max="3089" width="6.453125" customWidth="1"/>
+    <col min="3090" max="3090" width="7.81640625" customWidth="1"/>
+    <col min="3091" max="3091" width="3" customWidth="1"/>
+    <col min="3092" max="3092" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3329" max="3332" width="14.453125" customWidth="1"/>
+    <col min="3333" max="3333" width="15.453125" customWidth="1"/>
+    <col min="3334" max="3334" width="14.54296875" customWidth="1"/>
+    <col min="3335" max="3335" width="15.26953125" customWidth="1"/>
+    <col min="3336" max="3337" width="14.453125" customWidth="1"/>
+    <col min="3338" max="3338" width="13.1796875" customWidth="1"/>
+    <col min="3339" max="3341" width="14.453125" customWidth="1"/>
+    <col min="3342" max="3342" width="15.81640625" customWidth="1"/>
+    <col min="3343" max="3343" width="7.81640625" customWidth="1"/>
+    <col min="3344" max="3344" width="5.453125" customWidth="1"/>
+    <col min="3345" max="3345" width="6.453125" customWidth="1"/>
+    <col min="3346" max="3346" width="7.81640625" customWidth="1"/>
+    <col min="3347" max="3347" width="3" customWidth="1"/>
+    <col min="3348" max="3348" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3585" max="3588" width="14.453125" customWidth="1"/>
+    <col min="3589" max="3589" width="15.453125" customWidth="1"/>
+    <col min="3590" max="3590" width="14.54296875" customWidth="1"/>
+    <col min="3591" max="3591" width="15.26953125" customWidth="1"/>
+    <col min="3592" max="3593" width="14.453125" customWidth="1"/>
+    <col min="3594" max="3594" width="13.1796875" customWidth="1"/>
+    <col min="3595" max="3597" width="14.453125" customWidth="1"/>
+    <col min="3598" max="3598" width="15.81640625" customWidth="1"/>
+    <col min="3599" max="3599" width="7.81640625" customWidth="1"/>
+    <col min="3600" max="3600" width="5.453125" customWidth="1"/>
+    <col min="3601" max="3601" width="6.453125" customWidth="1"/>
+    <col min="3602" max="3602" width="7.81640625" customWidth="1"/>
+    <col min="3603" max="3603" width="3" customWidth="1"/>
+    <col min="3604" max="3604" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3841" max="3844" width="14.453125" customWidth="1"/>
+    <col min="3845" max="3845" width="15.453125" customWidth="1"/>
+    <col min="3846" max="3846" width="14.54296875" customWidth="1"/>
+    <col min="3847" max="3847" width="15.26953125" customWidth="1"/>
+    <col min="3848" max="3849" width="14.453125" customWidth="1"/>
+    <col min="3850" max="3850" width="13.1796875" customWidth="1"/>
+    <col min="3851" max="3853" width="14.453125" customWidth="1"/>
+    <col min="3854" max="3854" width="15.81640625" customWidth="1"/>
+    <col min="3855" max="3855" width="7.81640625" customWidth="1"/>
+    <col min="3856" max="3856" width="5.453125" customWidth="1"/>
+    <col min="3857" max="3857" width="6.453125" customWidth="1"/>
+    <col min="3858" max="3858" width="7.81640625" customWidth="1"/>
+    <col min="3859" max="3859" width="3" customWidth="1"/>
+    <col min="3860" max="3860" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4097" max="4100" width="14.453125" customWidth="1"/>
+    <col min="4101" max="4101" width="15.453125" customWidth="1"/>
+    <col min="4102" max="4102" width="14.54296875" customWidth="1"/>
+    <col min="4103" max="4103" width="15.26953125" customWidth="1"/>
+    <col min="4104" max="4105" width="14.453125" customWidth="1"/>
+    <col min="4106" max="4106" width="13.1796875" customWidth="1"/>
+    <col min="4107" max="4109" width="14.453125" customWidth="1"/>
+    <col min="4110" max="4110" width="15.81640625" customWidth="1"/>
+    <col min="4111" max="4111" width="7.81640625" customWidth="1"/>
+    <col min="4112" max="4112" width="5.453125" customWidth="1"/>
+    <col min="4113" max="4113" width="6.453125" customWidth="1"/>
+    <col min="4114" max="4114" width="7.81640625" customWidth="1"/>
+    <col min="4115" max="4115" width="3" customWidth="1"/>
+    <col min="4116" max="4116" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4353" max="4356" width="14.453125" customWidth="1"/>
+    <col min="4357" max="4357" width="15.453125" customWidth="1"/>
+    <col min="4358" max="4358" width="14.54296875" customWidth="1"/>
+    <col min="4359" max="4359" width="15.26953125" customWidth="1"/>
+    <col min="4360" max="4361" width="14.453125" customWidth="1"/>
+    <col min="4362" max="4362" width="13.1796875" customWidth="1"/>
+    <col min="4363" max="4365" width="14.453125" customWidth="1"/>
+    <col min="4366" max="4366" width="15.81640625" customWidth="1"/>
+    <col min="4367" max="4367" width="7.81640625" customWidth="1"/>
+    <col min="4368" max="4368" width="5.453125" customWidth="1"/>
+    <col min="4369" max="4369" width="6.453125" customWidth="1"/>
+    <col min="4370" max="4370" width="7.81640625" customWidth="1"/>
+    <col min="4371" max="4371" width="3" customWidth="1"/>
+    <col min="4372" max="4372" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4609" max="4612" width="14.453125" customWidth="1"/>
+    <col min="4613" max="4613" width="15.453125" customWidth="1"/>
+    <col min="4614" max="4614" width="14.54296875" customWidth="1"/>
+    <col min="4615" max="4615" width="15.26953125" customWidth="1"/>
+    <col min="4616" max="4617" width="14.453125" customWidth="1"/>
+    <col min="4618" max="4618" width="13.1796875" customWidth="1"/>
+    <col min="4619" max="4621" width="14.453125" customWidth="1"/>
+    <col min="4622" max="4622" width="15.81640625" customWidth="1"/>
+    <col min="4623" max="4623" width="7.81640625" customWidth="1"/>
+    <col min="4624" max="4624" width="5.453125" customWidth="1"/>
+    <col min="4625" max="4625" width="6.453125" customWidth="1"/>
+    <col min="4626" max="4626" width="7.81640625" customWidth="1"/>
+    <col min="4627" max="4627" width="3" customWidth="1"/>
+    <col min="4628" max="4628" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4865" max="4868" width="14.453125" customWidth="1"/>
+    <col min="4869" max="4869" width="15.453125" customWidth="1"/>
+    <col min="4870" max="4870" width="14.54296875" customWidth="1"/>
+    <col min="4871" max="4871" width="15.26953125" customWidth="1"/>
+    <col min="4872" max="4873" width="14.453125" customWidth="1"/>
+    <col min="4874" max="4874" width="13.1796875" customWidth="1"/>
+    <col min="4875" max="4877" width="14.453125" customWidth="1"/>
+    <col min="4878" max="4878" width="15.81640625" customWidth="1"/>
+    <col min="4879" max="4879" width="7.81640625" customWidth="1"/>
+    <col min="4880" max="4880" width="5.453125" customWidth="1"/>
+    <col min="4881" max="4881" width="6.453125" customWidth="1"/>
+    <col min="4882" max="4882" width="7.81640625" customWidth="1"/>
+    <col min="4883" max="4883" width="3" customWidth="1"/>
+    <col min="4884" max="4884" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5121" max="5124" width="14.453125" customWidth="1"/>
+    <col min="5125" max="5125" width="15.453125" customWidth="1"/>
+    <col min="5126" max="5126" width="14.54296875" customWidth="1"/>
+    <col min="5127" max="5127" width="15.26953125" customWidth="1"/>
+    <col min="5128" max="5129" width="14.453125" customWidth="1"/>
+    <col min="5130" max="5130" width="13.1796875" customWidth="1"/>
+    <col min="5131" max="5133" width="14.453125" customWidth="1"/>
+    <col min="5134" max="5134" width="15.81640625" customWidth="1"/>
+    <col min="5135" max="5135" width="7.81640625" customWidth="1"/>
+    <col min="5136" max="5136" width="5.453125" customWidth="1"/>
+    <col min="5137" max="5137" width="6.453125" customWidth="1"/>
+    <col min="5138" max="5138" width="7.81640625" customWidth="1"/>
+    <col min="5139" max="5139" width="3" customWidth="1"/>
+    <col min="5140" max="5140" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5377" max="5380" width="14.453125" customWidth="1"/>
+    <col min="5381" max="5381" width="15.453125" customWidth="1"/>
+    <col min="5382" max="5382" width="14.54296875" customWidth="1"/>
+    <col min="5383" max="5383" width="15.26953125" customWidth="1"/>
+    <col min="5384" max="5385" width="14.453125" customWidth="1"/>
+    <col min="5386" max="5386" width="13.1796875" customWidth="1"/>
+    <col min="5387" max="5389" width="14.453125" customWidth="1"/>
+    <col min="5390" max="5390" width="15.81640625" customWidth="1"/>
+    <col min="5391" max="5391" width="7.81640625" customWidth="1"/>
+    <col min="5392" max="5392" width="5.453125" customWidth="1"/>
+    <col min="5393" max="5393" width="6.453125" customWidth="1"/>
+    <col min="5394" max="5394" width="7.81640625" customWidth="1"/>
+    <col min="5395" max="5395" width="3" customWidth="1"/>
+    <col min="5396" max="5396" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5633" max="5636" width="14.453125" customWidth="1"/>
+    <col min="5637" max="5637" width="15.453125" customWidth="1"/>
+    <col min="5638" max="5638" width="14.54296875" customWidth="1"/>
+    <col min="5639" max="5639" width="15.26953125" customWidth="1"/>
+    <col min="5640" max="5641" width="14.453125" customWidth="1"/>
+    <col min="5642" max="5642" width="13.1796875" customWidth="1"/>
+    <col min="5643" max="5645" width="14.453125" customWidth="1"/>
+    <col min="5646" max="5646" width="15.81640625" customWidth="1"/>
+    <col min="5647" max="5647" width="7.81640625" customWidth="1"/>
+    <col min="5648" max="5648" width="5.453125" customWidth="1"/>
+    <col min="5649" max="5649" width="6.453125" customWidth="1"/>
+    <col min="5650" max="5650" width="7.81640625" customWidth="1"/>
+    <col min="5651" max="5651" width="3" customWidth="1"/>
+    <col min="5652" max="5652" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5889" max="5892" width="14.453125" customWidth="1"/>
+    <col min="5893" max="5893" width="15.453125" customWidth="1"/>
+    <col min="5894" max="5894" width="14.54296875" customWidth="1"/>
+    <col min="5895" max="5895" width="15.26953125" customWidth="1"/>
+    <col min="5896" max="5897" width="14.453125" customWidth="1"/>
+    <col min="5898" max="5898" width="13.1796875" customWidth="1"/>
+    <col min="5899" max="5901" width="14.453125" customWidth="1"/>
+    <col min="5902" max="5902" width="15.81640625" customWidth="1"/>
+    <col min="5903" max="5903" width="7.81640625" customWidth="1"/>
+    <col min="5904" max="5904" width="5.453125" customWidth="1"/>
+    <col min="5905" max="5905" width="6.453125" customWidth="1"/>
+    <col min="5906" max="5906" width="7.81640625" customWidth="1"/>
+    <col min="5907" max="5907" width="3" customWidth="1"/>
+    <col min="5908" max="5908" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6145" max="6148" width="14.453125" customWidth="1"/>
+    <col min="6149" max="6149" width="15.453125" customWidth="1"/>
+    <col min="6150" max="6150" width="14.54296875" customWidth="1"/>
+    <col min="6151" max="6151" width="15.26953125" customWidth="1"/>
+    <col min="6152" max="6153" width="14.453125" customWidth="1"/>
+    <col min="6154" max="6154" width="13.1796875" customWidth="1"/>
+    <col min="6155" max="6157" width="14.453125" customWidth="1"/>
+    <col min="6158" max="6158" width="15.81640625" customWidth="1"/>
+    <col min="6159" max="6159" width="7.81640625" customWidth="1"/>
+    <col min="6160" max="6160" width="5.453125" customWidth="1"/>
+    <col min="6161" max="6161" width="6.453125" customWidth="1"/>
+    <col min="6162" max="6162" width="7.81640625" customWidth="1"/>
+    <col min="6163" max="6163" width="3" customWidth="1"/>
+    <col min="6164" max="6164" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6401" max="6404" width="14.453125" customWidth="1"/>
+    <col min="6405" max="6405" width="15.453125" customWidth="1"/>
+    <col min="6406" max="6406" width="14.54296875" customWidth="1"/>
+    <col min="6407" max="6407" width="15.26953125" customWidth="1"/>
+    <col min="6408" max="6409" width="14.453125" customWidth="1"/>
+    <col min="6410" max="6410" width="13.1796875" customWidth="1"/>
+    <col min="6411" max="6413" width="14.453125" customWidth="1"/>
+    <col min="6414" max="6414" width="15.81640625" customWidth="1"/>
+    <col min="6415" max="6415" width="7.81640625" customWidth="1"/>
+    <col min="6416" max="6416" width="5.453125" customWidth="1"/>
+    <col min="6417" max="6417" width="6.453125" customWidth="1"/>
+    <col min="6418" max="6418" width="7.81640625" customWidth="1"/>
+    <col min="6419" max="6419" width="3" customWidth="1"/>
+    <col min="6420" max="6420" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6657" max="6660" width="14.453125" customWidth="1"/>
+    <col min="6661" max="6661" width="15.453125" customWidth="1"/>
+    <col min="6662" max="6662" width="14.54296875" customWidth="1"/>
+    <col min="6663" max="6663" width="15.26953125" customWidth="1"/>
+    <col min="6664" max="6665" width="14.453125" customWidth="1"/>
+    <col min="6666" max="6666" width="13.1796875" customWidth="1"/>
+    <col min="6667" max="6669" width="14.453125" customWidth="1"/>
+    <col min="6670" max="6670" width="15.81640625" customWidth="1"/>
+    <col min="6671" max="6671" width="7.81640625" customWidth="1"/>
+    <col min="6672" max="6672" width="5.453125" customWidth="1"/>
+    <col min="6673" max="6673" width="6.453125" customWidth="1"/>
+    <col min="6674" max="6674" width="7.81640625" customWidth="1"/>
+    <col min="6675" max="6675" width="3" customWidth="1"/>
+    <col min="6676" max="6676" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6913" max="6916" width="14.453125" customWidth="1"/>
+    <col min="6917" max="6917" width="15.453125" customWidth="1"/>
+    <col min="6918" max="6918" width="14.54296875" customWidth="1"/>
+    <col min="6919" max="6919" width="15.26953125" customWidth="1"/>
+    <col min="6920" max="6921" width="14.453125" customWidth="1"/>
+    <col min="6922" max="6922" width="13.1796875" customWidth="1"/>
+    <col min="6923" max="6925" width="14.453125" customWidth="1"/>
+    <col min="6926" max="6926" width="15.81640625" customWidth="1"/>
+    <col min="6927" max="6927" width="7.81640625" customWidth="1"/>
+    <col min="6928" max="6928" width="5.453125" customWidth="1"/>
+    <col min="6929" max="6929" width="6.453125" customWidth="1"/>
+    <col min="6930" max="6930" width="7.81640625" customWidth="1"/>
+    <col min="6931" max="6931" width="3" customWidth="1"/>
+    <col min="6932" max="6932" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7169" max="7172" width="14.453125" customWidth="1"/>
+    <col min="7173" max="7173" width="15.453125" customWidth="1"/>
+    <col min="7174" max="7174" width="14.54296875" customWidth="1"/>
+    <col min="7175" max="7175" width="15.26953125" customWidth="1"/>
+    <col min="7176" max="7177" width="14.453125" customWidth="1"/>
+    <col min="7178" max="7178" width="13.1796875" customWidth="1"/>
+    <col min="7179" max="7181" width="14.453125" customWidth="1"/>
+    <col min="7182" max="7182" width="15.81640625" customWidth="1"/>
+    <col min="7183" max="7183" width="7.81640625" customWidth="1"/>
+    <col min="7184" max="7184" width="5.453125" customWidth="1"/>
+    <col min="7185" max="7185" width="6.453125" customWidth="1"/>
+    <col min="7186" max="7186" width="7.81640625" customWidth="1"/>
+    <col min="7187" max="7187" width="3" customWidth="1"/>
+    <col min="7188" max="7188" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7425" max="7428" width="14.453125" customWidth="1"/>
+    <col min="7429" max="7429" width="15.453125" customWidth="1"/>
+    <col min="7430" max="7430" width="14.54296875" customWidth="1"/>
+    <col min="7431" max="7431" width="15.26953125" customWidth="1"/>
+    <col min="7432" max="7433" width="14.453125" customWidth="1"/>
+    <col min="7434" max="7434" width="13.1796875" customWidth="1"/>
+    <col min="7435" max="7437" width="14.453125" customWidth="1"/>
+    <col min="7438" max="7438" width="15.81640625" customWidth="1"/>
+    <col min="7439" max="7439" width="7.81640625" customWidth="1"/>
+    <col min="7440" max="7440" width="5.453125" customWidth="1"/>
+    <col min="7441" max="7441" width="6.453125" customWidth="1"/>
+    <col min="7442" max="7442" width="7.81640625" customWidth="1"/>
+    <col min="7443" max="7443" width="3" customWidth="1"/>
+    <col min="7444" max="7444" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7681" max="7684" width="14.453125" customWidth="1"/>
+    <col min="7685" max="7685" width="15.453125" customWidth="1"/>
+    <col min="7686" max="7686" width="14.54296875" customWidth="1"/>
+    <col min="7687" max="7687" width="15.26953125" customWidth="1"/>
+    <col min="7688" max="7689" width="14.453125" customWidth="1"/>
+    <col min="7690" max="7690" width="13.1796875" customWidth="1"/>
+    <col min="7691" max="7693" width="14.453125" customWidth="1"/>
+    <col min="7694" max="7694" width="15.81640625" customWidth="1"/>
+    <col min="7695" max="7695" width="7.81640625" customWidth="1"/>
+    <col min="7696" max="7696" width="5.453125" customWidth="1"/>
+    <col min="7697" max="7697" width="6.453125" customWidth="1"/>
+    <col min="7698" max="7698" width="7.81640625" customWidth="1"/>
+    <col min="7699" max="7699" width="3" customWidth="1"/>
+    <col min="7700" max="7700" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7937" max="7940" width="14.453125" customWidth="1"/>
+    <col min="7941" max="7941" width="15.453125" customWidth="1"/>
+    <col min="7942" max="7942" width="14.54296875" customWidth="1"/>
+    <col min="7943" max="7943" width="15.26953125" customWidth="1"/>
+    <col min="7944" max="7945" width="14.453125" customWidth="1"/>
+    <col min="7946" max="7946" width="13.1796875" customWidth="1"/>
+    <col min="7947" max="7949" width="14.453125" customWidth="1"/>
+    <col min="7950" max="7950" width="15.81640625" customWidth="1"/>
+    <col min="7951" max="7951" width="7.81640625" customWidth="1"/>
+    <col min="7952" max="7952" width="5.453125" customWidth="1"/>
+    <col min="7953" max="7953" width="6.453125" customWidth="1"/>
+    <col min="7954" max="7954" width="7.81640625" customWidth="1"/>
+    <col min="7955" max="7955" width="3" customWidth="1"/>
+    <col min="7956" max="7956" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8193" max="8196" width="14.453125" customWidth="1"/>
+    <col min="8197" max="8197" width="15.453125" customWidth="1"/>
+    <col min="8198" max="8198" width="14.54296875" customWidth="1"/>
+    <col min="8199" max="8199" width="15.26953125" customWidth="1"/>
+    <col min="8200" max="8201" width="14.453125" customWidth="1"/>
+    <col min="8202" max="8202" width="13.1796875" customWidth="1"/>
+    <col min="8203" max="8205" width="14.453125" customWidth="1"/>
+    <col min="8206" max="8206" width="15.81640625" customWidth="1"/>
+    <col min="8207" max="8207" width="7.81640625" customWidth="1"/>
+    <col min="8208" max="8208" width="5.453125" customWidth="1"/>
+    <col min="8209" max="8209" width="6.453125" customWidth="1"/>
+    <col min="8210" max="8210" width="7.81640625" customWidth="1"/>
+    <col min="8211" max="8211" width="3" customWidth="1"/>
+    <col min="8212" max="8212" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8449" max="8452" width="14.453125" customWidth="1"/>
+    <col min="8453" max="8453" width="15.453125" customWidth="1"/>
+    <col min="8454" max="8454" width="14.54296875" customWidth="1"/>
+    <col min="8455" max="8455" width="15.26953125" customWidth="1"/>
+    <col min="8456" max="8457" width="14.453125" customWidth="1"/>
+    <col min="8458" max="8458" width="13.1796875" customWidth="1"/>
+    <col min="8459" max="8461" width="14.453125" customWidth="1"/>
+    <col min="8462" max="8462" width="15.81640625" customWidth="1"/>
+    <col min="8463" max="8463" width="7.81640625" customWidth="1"/>
+    <col min="8464" max="8464" width="5.453125" customWidth="1"/>
+    <col min="8465" max="8465" width="6.453125" customWidth="1"/>
+    <col min="8466" max="8466" width="7.81640625" customWidth="1"/>
+    <col min="8467" max="8467" width="3" customWidth="1"/>
+    <col min="8468" max="8468" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8705" max="8708" width="14.453125" customWidth="1"/>
+    <col min="8709" max="8709" width="15.453125" customWidth="1"/>
+    <col min="8710" max="8710" width="14.54296875" customWidth="1"/>
+    <col min="8711" max="8711" width="15.26953125" customWidth="1"/>
+    <col min="8712" max="8713" width="14.453125" customWidth="1"/>
+    <col min="8714" max="8714" width="13.1796875" customWidth="1"/>
+    <col min="8715" max="8717" width="14.453125" customWidth="1"/>
+    <col min="8718" max="8718" width="15.81640625" customWidth="1"/>
+    <col min="8719" max="8719" width="7.81640625" customWidth="1"/>
+    <col min="8720" max="8720" width="5.453125" customWidth="1"/>
+    <col min="8721" max="8721" width="6.453125" customWidth="1"/>
+    <col min="8722" max="8722" width="7.81640625" customWidth="1"/>
+    <col min="8723" max="8723" width="3" customWidth="1"/>
+    <col min="8724" max="8724" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8961" max="8964" width="14.453125" customWidth="1"/>
+    <col min="8965" max="8965" width="15.453125" customWidth="1"/>
+    <col min="8966" max="8966" width="14.54296875" customWidth="1"/>
+    <col min="8967" max="8967" width="15.26953125" customWidth="1"/>
+    <col min="8968" max="8969" width="14.453125" customWidth="1"/>
+    <col min="8970" max="8970" width="13.1796875" customWidth="1"/>
+    <col min="8971" max="8973" width="14.453125" customWidth="1"/>
+    <col min="8974" max="8974" width="15.81640625" customWidth="1"/>
+    <col min="8975" max="8975" width="7.81640625" customWidth="1"/>
+    <col min="8976" max="8976" width="5.453125" customWidth="1"/>
+    <col min="8977" max="8977" width="6.453125" customWidth="1"/>
+    <col min="8978" max="8978" width="7.81640625" customWidth="1"/>
+    <col min="8979" max="8979" width="3" customWidth="1"/>
+    <col min="8980" max="8980" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9217" max="9220" width="14.453125" customWidth="1"/>
+    <col min="9221" max="9221" width="15.453125" customWidth="1"/>
+    <col min="9222" max="9222" width="14.54296875" customWidth="1"/>
+    <col min="9223" max="9223" width="15.26953125" customWidth="1"/>
+    <col min="9224" max="9225" width="14.453125" customWidth="1"/>
+    <col min="9226" max="9226" width="13.1796875" customWidth="1"/>
+    <col min="9227" max="9229" width="14.453125" customWidth="1"/>
+    <col min="9230" max="9230" width="15.81640625" customWidth="1"/>
+    <col min="9231" max="9231" width="7.81640625" customWidth="1"/>
+    <col min="9232" max="9232" width="5.453125" customWidth="1"/>
+    <col min="9233" max="9233" width="6.453125" customWidth="1"/>
+    <col min="9234" max="9234" width="7.81640625" customWidth="1"/>
+    <col min="9235" max="9235" width="3" customWidth="1"/>
+    <col min="9236" max="9236" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9473" max="9476" width="14.453125" customWidth="1"/>
+    <col min="9477" max="9477" width="15.453125" customWidth="1"/>
+    <col min="9478" max="9478" width="14.54296875" customWidth="1"/>
+    <col min="9479" max="9479" width="15.26953125" customWidth="1"/>
+    <col min="9480" max="9481" width="14.453125" customWidth="1"/>
+    <col min="9482" max="9482" width="13.1796875" customWidth="1"/>
+    <col min="9483" max="9485" width="14.453125" customWidth="1"/>
+    <col min="9486" max="9486" width="15.81640625" customWidth="1"/>
+    <col min="9487" max="9487" width="7.81640625" customWidth="1"/>
+    <col min="9488" max="9488" width="5.453125" customWidth="1"/>
+    <col min="9489" max="9489" width="6.453125" customWidth="1"/>
+    <col min="9490" max="9490" width="7.81640625" customWidth="1"/>
+    <col min="9491" max="9491" width="3" customWidth="1"/>
+    <col min="9492" max="9492" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9729" max="9732" width="14.453125" customWidth="1"/>
+    <col min="9733" max="9733" width="15.453125" customWidth="1"/>
+    <col min="9734" max="9734" width="14.54296875" customWidth="1"/>
+    <col min="9735" max="9735" width="15.26953125" customWidth="1"/>
+    <col min="9736" max="9737" width="14.453125" customWidth="1"/>
+    <col min="9738" max="9738" width="13.1796875" customWidth="1"/>
+    <col min="9739" max="9741" width="14.453125" customWidth="1"/>
+    <col min="9742" max="9742" width="15.81640625" customWidth="1"/>
+    <col min="9743" max="9743" width="7.81640625" customWidth="1"/>
+    <col min="9744" max="9744" width="5.453125" customWidth="1"/>
+    <col min="9745" max="9745" width="6.453125" customWidth="1"/>
+    <col min="9746" max="9746" width="7.81640625" customWidth="1"/>
+    <col min="9747" max="9747" width="3" customWidth="1"/>
+    <col min="9748" max="9748" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9985" max="9988" width="14.453125" customWidth="1"/>
+    <col min="9989" max="9989" width="15.453125" customWidth="1"/>
+    <col min="9990" max="9990" width="14.54296875" customWidth="1"/>
+    <col min="9991" max="9991" width="15.26953125" customWidth="1"/>
+    <col min="9992" max="9993" width="14.453125" customWidth="1"/>
+    <col min="9994" max="9994" width="13.1796875" customWidth="1"/>
+    <col min="9995" max="9997" width="14.453125" customWidth="1"/>
+    <col min="9998" max="9998" width="15.81640625" customWidth="1"/>
+    <col min="9999" max="9999" width="7.81640625" customWidth="1"/>
+    <col min="10000" max="10000" width="5.453125" customWidth="1"/>
+    <col min="10001" max="10001" width="6.453125" customWidth="1"/>
+    <col min="10002" max="10002" width="7.81640625" customWidth="1"/>
+    <col min="10003" max="10003" width="3" customWidth="1"/>
+    <col min="10004" max="10004" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10241" max="10244" width="14.453125" customWidth="1"/>
+    <col min="10245" max="10245" width="15.453125" customWidth="1"/>
+    <col min="10246" max="10246" width="14.54296875" customWidth="1"/>
+    <col min="10247" max="10247" width="15.26953125" customWidth="1"/>
+    <col min="10248" max="10249" width="14.453125" customWidth="1"/>
+    <col min="10250" max="10250" width="13.1796875" customWidth="1"/>
+    <col min="10251" max="10253" width="14.453125" customWidth="1"/>
+    <col min="10254" max="10254" width="15.81640625" customWidth="1"/>
+    <col min="10255" max="10255" width="7.81640625" customWidth="1"/>
+    <col min="10256" max="10256" width="5.453125" customWidth="1"/>
+    <col min="10257" max="10257" width="6.453125" customWidth="1"/>
+    <col min="10258" max="10258" width="7.81640625" customWidth="1"/>
+    <col min="10259" max="10259" width="3" customWidth="1"/>
+    <col min="10260" max="10260" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10497" max="10500" width="14.453125" customWidth="1"/>
+    <col min="10501" max="10501" width="15.453125" customWidth="1"/>
+    <col min="10502" max="10502" width="14.54296875" customWidth="1"/>
+    <col min="10503" max="10503" width="15.26953125" customWidth="1"/>
+    <col min="10504" max="10505" width="14.453125" customWidth="1"/>
+    <col min="10506" max="10506" width="13.1796875" customWidth="1"/>
+    <col min="10507" max="10509" width="14.453125" customWidth="1"/>
+    <col min="10510" max="10510" width="15.81640625" customWidth="1"/>
+    <col min="10511" max="10511" width="7.81640625" customWidth="1"/>
+    <col min="10512" max="10512" width="5.453125" customWidth="1"/>
+    <col min="10513" max="10513" width="6.453125" customWidth="1"/>
+    <col min="10514" max="10514" width="7.81640625" customWidth="1"/>
+    <col min="10515" max="10515" width="3" customWidth="1"/>
+    <col min="10516" max="10516" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10753" max="10756" width="14.453125" customWidth="1"/>
+    <col min="10757" max="10757" width="15.453125" customWidth="1"/>
+    <col min="10758" max="10758" width="14.54296875" customWidth="1"/>
+    <col min="10759" max="10759" width="15.26953125" customWidth="1"/>
+    <col min="10760" max="10761" width="14.453125" customWidth="1"/>
+    <col min="10762" max="10762" width="13.1796875" customWidth="1"/>
+    <col min="10763" max="10765" width="14.453125" customWidth="1"/>
+    <col min="10766" max="10766" width="15.81640625" customWidth="1"/>
+    <col min="10767" max="10767" width="7.81640625" customWidth="1"/>
+    <col min="10768" max="10768" width="5.453125" customWidth="1"/>
+    <col min="10769" max="10769" width="6.453125" customWidth="1"/>
+    <col min="10770" max="10770" width="7.81640625" customWidth="1"/>
+    <col min="10771" max="10771" width="3" customWidth="1"/>
+    <col min="10772" max="10772" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11009" max="11012" width="14.453125" customWidth="1"/>
+    <col min="11013" max="11013" width="15.453125" customWidth="1"/>
+    <col min="11014" max="11014" width="14.54296875" customWidth="1"/>
+    <col min="11015" max="11015" width="15.26953125" customWidth="1"/>
+    <col min="11016" max="11017" width="14.453125" customWidth="1"/>
+    <col min="11018" max="11018" width="13.1796875" customWidth="1"/>
+    <col min="11019" max="11021" width="14.453125" customWidth="1"/>
+    <col min="11022" max="11022" width="15.81640625" customWidth="1"/>
+    <col min="11023" max="11023" width="7.81640625" customWidth="1"/>
+    <col min="11024" max="11024" width="5.453125" customWidth="1"/>
+    <col min="11025" max="11025" width="6.453125" customWidth="1"/>
+    <col min="11026" max="11026" width="7.81640625" customWidth="1"/>
+    <col min="11027" max="11027" width="3" customWidth="1"/>
+    <col min="11028" max="11028" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11265" max="11268" width="14.453125" customWidth="1"/>
+    <col min="11269" max="11269" width="15.453125" customWidth="1"/>
+    <col min="11270" max="11270" width="14.54296875" customWidth="1"/>
+    <col min="11271" max="11271" width="15.26953125" customWidth="1"/>
+    <col min="11272" max="11273" width="14.453125" customWidth="1"/>
+    <col min="11274" max="11274" width="13.1796875" customWidth="1"/>
+    <col min="11275" max="11277" width="14.453125" customWidth="1"/>
+    <col min="11278" max="11278" width="15.81640625" customWidth="1"/>
+    <col min="11279" max="11279" width="7.81640625" customWidth="1"/>
+    <col min="11280" max="11280" width="5.453125" customWidth="1"/>
+    <col min="11281" max="11281" width="6.453125" customWidth="1"/>
+    <col min="11282" max="11282" width="7.81640625" customWidth="1"/>
+    <col min="11283" max="11283" width="3" customWidth="1"/>
+    <col min="11284" max="11284" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11521" max="11524" width="14.453125" customWidth="1"/>
+    <col min="11525" max="11525" width="15.453125" customWidth="1"/>
+    <col min="11526" max="11526" width="14.54296875" customWidth="1"/>
+    <col min="11527" max="11527" width="15.26953125" customWidth="1"/>
+    <col min="11528" max="11529" width="14.453125" customWidth="1"/>
+    <col min="11530" max="11530" width="13.1796875" customWidth="1"/>
+    <col min="11531" max="11533" width="14.453125" customWidth="1"/>
+    <col min="11534" max="11534" width="15.81640625" customWidth="1"/>
+    <col min="11535" max="11535" width="7.81640625" customWidth="1"/>
+    <col min="11536" max="11536" width="5.453125" customWidth="1"/>
+    <col min="11537" max="11537" width="6.453125" customWidth="1"/>
+    <col min="11538" max="11538" width="7.81640625" customWidth="1"/>
+    <col min="11539" max="11539" width="3" customWidth="1"/>
+    <col min="11540" max="11540" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11777" max="11780" width="14.453125" customWidth="1"/>
+    <col min="11781" max="11781" width="15.453125" customWidth="1"/>
+    <col min="11782" max="11782" width="14.54296875" customWidth="1"/>
+    <col min="11783" max="11783" width="15.26953125" customWidth="1"/>
+    <col min="11784" max="11785" width="14.453125" customWidth="1"/>
+    <col min="11786" max="11786" width="13.1796875" customWidth="1"/>
+    <col min="11787" max="11789" width="14.453125" customWidth="1"/>
+    <col min="11790" max="11790" width="15.81640625" customWidth="1"/>
+    <col min="11791" max="11791" width="7.81640625" customWidth="1"/>
+    <col min="11792" max="11792" width="5.453125" customWidth="1"/>
+    <col min="11793" max="11793" width="6.453125" customWidth="1"/>
+    <col min="11794" max="11794" width="7.81640625" customWidth="1"/>
+    <col min="11795" max="11795" width="3" customWidth="1"/>
+    <col min="11796" max="11796" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12033" max="12036" width="14.453125" customWidth="1"/>
+    <col min="12037" max="12037" width="15.453125" customWidth="1"/>
+    <col min="12038" max="12038" width="14.54296875" customWidth="1"/>
+    <col min="12039" max="12039" width="15.26953125" customWidth="1"/>
+    <col min="12040" max="12041" width="14.453125" customWidth="1"/>
+    <col min="12042" max="12042" width="13.1796875" customWidth="1"/>
+    <col min="12043" max="12045" width="14.453125" customWidth="1"/>
+    <col min="12046" max="12046" width="15.81640625" customWidth="1"/>
+    <col min="12047" max="12047" width="7.81640625" customWidth="1"/>
+    <col min="12048" max="12048" width="5.453125" customWidth="1"/>
+    <col min="12049" max="12049" width="6.453125" customWidth="1"/>
+    <col min="12050" max="12050" width="7.81640625" customWidth="1"/>
+    <col min="12051" max="12051" width="3" customWidth="1"/>
+    <col min="12052" max="12052" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12289" max="12292" width="14.453125" customWidth="1"/>
+    <col min="12293" max="12293" width="15.453125" customWidth="1"/>
+    <col min="12294" max="12294" width="14.54296875" customWidth="1"/>
+    <col min="12295" max="12295" width="15.26953125" customWidth="1"/>
+    <col min="12296" max="12297" width="14.453125" customWidth="1"/>
+    <col min="12298" max="12298" width="13.1796875" customWidth="1"/>
+    <col min="12299" max="12301" width="14.453125" customWidth="1"/>
+    <col min="12302" max="12302" width="15.81640625" customWidth="1"/>
+    <col min="12303" max="12303" width="7.81640625" customWidth="1"/>
+    <col min="12304" max="12304" width="5.453125" customWidth="1"/>
+    <col min="12305" max="12305" width="6.453125" customWidth="1"/>
+    <col min="12306" max="12306" width="7.81640625" customWidth="1"/>
+    <col min="12307" max="12307" width="3" customWidth="1"/>
+    <col min="12308" max="12308" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12545" max="12548" width="14.453125" customWidth="1"/>
+    <col min="12549" max="12549" width="15.453125" customWidth="1"/>
+    <col min="12550" max="12550" width="14.54296875" customWidth="1"/>
+    <col min="12551" max="12551" width="15.26953125" customWidth="1"/>
+    <col min="12552" max="12553" width="14.453125" customWidth="1"/>
+    <col min="12554" max="12554" width="13.1796875" customWidth="1"/>
+    <col min="12555" max="12557" width="14.453125" customWidth="1"/>
+    <col min="12558" max="12558" width="15.81640625" customWidth="1"/>
+    <col min="12559" max="12559" width="7.81640625" customWidth="1"/>
+    <col min="12560" max="12560" width="5.453125" customWidth="1"/>
+    <col min="12561" max="12561" width="6.453125" customWidth="1"/>
+    <col min="12562" max="12562" width="7.81640625" customWidth="1"/>
+    <col min="12563" max="12563" width="3" customWidth="1"/>
+    <col min="12564" max="12564" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12801" max="12804" width="14.453125" customWidth="1"/>
+    <col min="12805" max="12805" width="15.453125" customWidth="1"/>
+    <col min="12806" max="12806" width="14.54296875" customWidth="1"/>
+    <col min="12807" max="12807" width="15.26953125" customWidth="1"/>
+    <col min="12808" max="12809" width="14.453125" customWidth="1"/>
+    <col min="12810" max="12810" width="13.1796875" customWidth="1"/>
+    <col min="12811" max="12813" width="14.453125" customWidth="1"/>
+    <col min="12814" max="12814" width="15.81640625" customWidth="1"/>
+    <col min="12815" max="12815" width="7.81640625" customWidth="1"/>
+    <col min="12816" max="12816" width="5.453125" customWidth="1"/>
+    <col min="12817" max="12817" width="6.453125" customWidth="1"/>
+    <col min="12818" max="12818" width="7.81640625" customWidth="1"/>
+    <col min="12819" max="12819" width="3" customWidth="1"/>
+    <col min="12820" max="12820" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13057" max="13060" width="14.453125" customWidth="1"/>
+    <col min="13061" max="13061" width="15.453125" customWidth="1"/>
+    <col min="13062" max="13062" width="14.54296875" customWidth="1"/>
+    <col min="13063" max="13063" width="15.26953125" customWidth="1"/>
+    <col min="13064" max="13065" width="14.453125" customWidth="1"/>
+    <col min="13066" max="13066" width="13.1796875" customWidth="1"/>
+    <col min="13067" max="13069" width="14.453125" customWidth="1"/>
+    <col min="13070" max="13070" width="15.81640625" customWidth="1"/>
+    <col min="13071" max="13071" width="7.81640625" customWidth="1"/>
+    <col min="13072" max="13072" width="5.453125" customWidth="1"/>
+    <col min="13073" max="13073" width="6.453125" customWidth="1"/>
+    <col min="13074" max="13074" width="7.81640625" customWidth="1"/>
+    <col min="13075" max="13075" width="3" customWidth="1"/>
+    <col min="13076" max="13076" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13313" max="13316" width="14.453125" customWidth="1"/>
+    <col min="13317" max="13317" width="15.453125" customWidth="1"/>
+    <col min="13318" max="13318" width="14.54296875" customWidth="1"/>
+    <col min="13319" max="13319" width="15.26953125" customWidth="1"/>
+    <col min="13320" max="13321" width="14.453125" customWidth="1"/>
+    <col min="13322" max="13322" width="13.1796875" customWidth="1"/>
+    <col min="13323" max="13325" width="14.453125" customWidth="1"/>
+    <col min="13326" max="13326" width="15.81640625" customWidth="1"/>
+    <col min="13327" max="13327" width="7.81640625" customWidth="1"/>
+    <col min="13328" max="13328" width="5.453125" customWidth="1"/>
+    <col min="13329" max="13329" width="6.453125" customWidth="1"/>
+    <col min="13330" max="13330" width="7.81640625" customWidth="1"/>
+    <col min="13331" max="13331" width="3" customWidth="1"/>
+    <col min="13332" max="13332" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13569" max="13572" width="14.453125" customWidth="1"/>
+    <col min="13573" max="13573" width="15.453125" customWidth="1"/>
+    <col min="13574" max="13574" width="14.54296875" customWidth="1"/>
+    <col min="13575" max="13575" width="15.26953125" customWidth="1"/>
+    <col min="13576" max="13577" width="14.453125" customWidth="1"/>
+    <col min="13578" max="13578" width="13.1796875" customWidth="1"/>
+    <col min="13579" max="13581" width="14.453125" customWidth="1"/>
+    <col min="13582" max="13582" width="15.81640625" customWidth="1"/>
+    <col min="13583" max="13583" width="7.81640625" customWidth="1"/>
+    <col min="13584" max="13584" width="5.453125" customWidth="1"/>
+    <col min="13585" max="13585" width="6.453125" customWidth="1"/>
+    <col min="13586" max="13586" width="7.81640625" customWidth="1"/>
+    <col min="13587" max="13587" width="3" customWidth="1"/>
+    <col min="13588" max="13588" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13825" max="13828" width="14.453125" customWidth="1"/>
+    <col min="13829" max="13829" width="15.453125" customWidth="1"/>
+    <col min="13830" max="13830" width="14.54296875" customWidth="1"/>
+    <col min="13831" max="13831" width="15.26953125" customWidth="1"/>
+    <col min="13832" max="13833" width="14.453125" customWidth="1"/>
+    <col min="13834" max="13834" width="13.1796875" customWidth="1"/>
+    <col min="13835" max="13837" width="14.453125" customWidth="1"/>
+    <col min="13838" max="13838" width="15.81640625" customWidth="1"/>
+    <col min="13839" max="13839" width="7.81640625" customWidth="1"/>
+    <col min="13840" max="13840" width="5.453125" customWidth="1"/>
+    <col min="13841" max="13841" width="6.453125" customWidth="1"/>
+    <col min="13842" max="13842" width="7.81640625" customWidth="1"/>
+    <col min="13843" max="13843" width="3" customWidth="1"/>
+    <col min="13844" max="13844" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14081" max="14084" width="14.453125" customWidth="1"/>
+    <col min="14085" max="14085" width="15.453125" customWidth="1"/>
+    <col min="14086" max="14086" width="14.54296875" customWidth="1"/>
+    <col min="14087" max="14087" width="15.26953125" customWidth="1"/>
+    <col min="14088" max="14089" width="14.453125" customWidth="1"/>
+    <col min="14090" max="14090" width="13.1796875" customWidth="1"/>
+    <col min="14091" max="14093" width="14.453125" customWidth="1"/>
+    <col min="14094" max="14094" width="15.81640625" customWidth="1"/>
+    <col min="14095" max="14095" width="7.81640625" customWidth="1"/>
+    <col min="14096" max="14096" width="5.453125" customWidth="1"/>
+    <col min="14097" max="14097" width="6.453125" customWidth="1"/>
+    <col min="14098" max="14098" width="7.81640625" customWidth="1"/>
+    <col min="14099" max="14099" width="3" customWidth="1"/>
+    <col min="14100" max="14100" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14337" max="14340" width="14.453125" customWidth="1"/>
+    <col min="14341" max="14341" width="15.453125" customWidth="1"/>
+    <col min="14342" max="14342" width="14.54296875" customWidth="1"/>
+    <col min="14343" max="14343" width="15.26953125" customWidth="1"/>
+    <col min="14344" max="14345" width="14.453125" customWidth="1"/>
+    <col min="14346" max="14346" width="13.1796875" customWidth="1"/>
+    <col min="14347" max="14349" width="14.453125" customWidth="1"/>
+    <col min="14350" max="14350" width="15.81640625" customWidth="1"/>
+    <col min="14351" max="14351" width="7.81640625" customWidth="1"/>
+    <col min="14352" max="14352" width="5.453125" customWidth="1"/>
+    <col min="14353" max="14353" width="6.453125" customWidth="1"/>
+    <col min="14354" max="14354" width="7.81640625" customWidth="1"/>
+    <col min="14355" max="14355" width="3" customWidth="1"/>
+    <col min="14356" max="14356" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14593" max="14596" width="14.453125" customWidth="1"/>
+    <col min="14597" max="14597" width="15.453125" customWidth="1"/>
+    <col min="14598" max="14598" width="14.54296875" customWidth="1"/>
+    <col min="14599" max="14599" width="15.26953125" customWidth="1"/>
+    <col min="14600" max="14601" width="14.453125" customWidth="1"/>
+    <col min="14602" max="14602" width="13.1796875" customWidth="1"/>
+    <col min="14603" max="14605" width="14.453125" customWidth="1"/>
+    <col min="14606" max="14606" width="15.81640625" customWidth="1"/>
+    <col min="14607" max="14607" width="7.81640625" customWidth="1"/>
+    <col min="14608" max="14608" width="5.453125" customWidth="1"/>
+    <col min="14609" max="14609" width="6.453125" customWidth="1"/>
+    <col min="14610" max="14610" width="7.81640625" customWidth="1"/>
+    <col min="14611" max="14611" width="3" customWidth="1"/>
+    <col min="14612" max="14612" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14849" max="14852" width="14.453125" customWidth="1"/>
+    <col min="14853" max="14853" width="15.453125" customWidth="1"/>
+    <col min="14854" max="14854" width="14.54296875" customWidth="1"/>
+    <col min="14855" max="14855" width="15.26953125" customWidth="1"/>
+    <col min="14856" max="14857" width="14.453125" customWidth="1"/>
+    <col min="14858" max="14858" width="13.1796875" customWidth="1"/>
+    <col min="14859" max="14861" width="14.453125" customWidth="1"/>
+    <col min="14862" max="14862" width="15.81640625" customWidth="1"/>
+    <col min="14863" max="14863" width="7.81640625" customWidth="1"/>
+    <col min="14864" max="14864" width="5.453125" customWidth="1"/>
+    <col min="14865" max="14865" width="6.453125" customWidth="1"/>
+    <col min="14866" max="14866" width="7.81640625" customWidth="1"/>
+    <col min="14867" max="14867" width="3" customWidth="1"/>
+    <col min="14868" max="14868" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15105" max="15108" width="14.453125" customWidth="1"/>
+    <col min="15109" max="15109" width="15.453125" customWidth="1"/>
+    <col min="15110" max="15110" width="14.54296875" customWidth="1"/>
+    <col min="15111" max="15111" width="15.26953125" customWidth="1"/>
+    <col min="15112" max="15113" width="14.453125" customWidth="1"/>
+    <col min="15114" max="15114" width="13.1796875" customWidth="1"/>
+    <col min="15115" max="15117" width="14.453125" customWidth="1"/>
+    <col min="15118" max="15118" width="15.81640625" customWidth="1"/>
+    <col min="15119" max="15119" width="7.81640625" customWidth="1"/>
+    <col min="15120" max="15120" width="5.453125" customWidth="1"/>
+    <col min="15121" max="15121" width="6.453125" customWidth="1"/>
+    <col min="15122" max="15122" width="7.81640625" customWidth="1"/>
+    <col min="15123" max="15123" width="3" customWidth="1"/>
+    <col min="15124" max="15124" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15361" max="15364" width="14.453125" customWidth="1"/>
+    <col min="15365" max="15365" width="15.453125" customWidth="1"/>
+    <col min="15366" max="15366" width="14.54296875" customWidth="1"/>
+    <col min="15367" max="15367" width="15.26953125" customWidth="1"/>
+    <col min="15368" max="15369" width="14.453125" customWidth="1"/>
+    <col min="15370" max="15370" width="13.1796875" customWidth="1"/>
+    <col min="15371" max="15373" width="14.453125" customWidth="1"/>
+    <col min="15374" max="15374" width="15.81640625" customWidth="1"/>
+    <col min="15375" max="15375" width="7.81640625" customWidth="1"/>
+    <col min="15376" max="15376" width="5.453125" customWidth="1"/>
+    <col min="15377" max="15377" width="6.453125" customWidth="1"/>
+    <col min="15378" max="15378" width="7.81640625" customWidth="1"/>
+    <col min="15379" max="15379" width="3" customWidth="1"/>
+    <col min="15380" max="15380" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15617" max="15620" width="14.453125" customWidth="1"/>
+    <col min="15621" max="15621" width="15.453125" customWidth="1"/>
+    <col min="15622" max="15622" width="14.54296875" customWidth="1"/>
+    <col min="15623" max="15623" width="15.26953125" customWidth="1"/>
+    <col min="15624" max="15625" width="14.453125" customWidth="1"/>
+    <col min="15626" max="15626" width="13.1796875" customWidth="1"/>
+    <col min="15627" max="15629" width="14.453125" customWidth="1"/>
+    <col min="15630" max="15630" width="15.81640625" customWidth="1"/>
+    <col min="15631" max="15631" width="7.81640625" customWidth="1"/>
+    <col min="15632" max="15632" width="5.453125" customWidth="1"/>
+    <col min="15633" max="15633" width="6.453125" customWidth="1"/>
+    <col min="15634" max="15634" width="7.81640625" customWidth="1"/>
+    <col min="15635" max="15635" width="3" customWidth="1"/>
+    <col min="15636" max="15636" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15873" max="15876" width="14.453125" customWidth="1"/>
+    <col min="15877" max="15877" width="15.453125" customWidth="1"/>
+    <col min="15878" max="15878" width="14.54296875" customWidth="1"/>
+    <col min="15879" max="15879" width="15.26953125" customWidth="1"/>
+    <col min="15880" max="15881" width="14.453125" customWidth="1"/>
+    <col min="15882" max="15882" width="13.1796875" customWidth="1"/>
+    <col min="15883" max="15885" width="14.453125" customWidth="1"/>
+    <col min="15886" max="15886" width="15.81640625" customWidth="1"/>
+    <col min="15887" max="15887" width="7.81640625" customWidth="1"/>
+    <col min="15888" max="15888" width="5.453125" customWidth="1"/>
+    <col min="15889" max="15889" width="6.453125" customWidth="1"/>
+    <col min="15890" max="15890" width="7.81640625" customWidth="1"/>
+    <col min="15891" max="15891" width="3" customWidth="1"/>
+    <col min="15892" max="15892" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="16129" max="16132" width="14.453125" customWidth="1"/>
+    <col min="16133" max="16133" width="15.453125" customWidth="1"/>
+    <col min="16134" max="16134" width="14.54296875" customWidth="1"/>
+    <col min="16135" max="16135" width="15.26953125" customWidth="1"/>
+    <col min="16136" max="16137" width="14.453125" customWidth="1"/>
+    <col min="16138" max="16138" width="13.1796875" customWidth="1"/>
+    <col min="16139" max="16141" width="14.453125" customWidth="1"/>
+    <col min="16142" max="16142" width="15.81640625" customWidth="1"/>
+    <col min="16143" max="16143" width="7.81640625" customWidth="1"/>
+    <col min="16144" max="16144" width="5.453125" customWidth="1"/>
+    <col min="16145" max="16145" width="6.453125" customWidth="1"/>
+    <col min="16146" max="16146" width="7.81640625" customWidth="1"/>
+    <col min="16147" max="16147" width="3" customWidth="1"/>
+    <col min="16148" max="16148" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="260" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
+      <c r="L1" s="260"/>
+      <c r="M1" s="260"/>
+      <c r="S1"/>
+    </row>
+    <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2"/>
+    </row>
+    <row r="3" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" s="262" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F3" s="261" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="129" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="268" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="262" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="26"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="270" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" s="271"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="264" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="265"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="29"/>
+    </row>
+    <row r="4" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="289" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="262"/>
+      <c r="E4" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F4" s="261"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="268"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="262"/>
+      <c r="O4" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" s="255" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" s="256" t="s">
+        <v>71</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" s="251" t="s">
+        <v>70</v>
+      </c>
+      <c r="U4" s="252" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" s="37"/>
+      <c r="E5" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="F5" s="269" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="261" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="54"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="38"/>
+      <c r="O5" s="39">
+        <v>31</v>
+      </c>
+      <c r="P5" s="40">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="41">
+        <v>19</v>
+      </c>
+      <c r="R5" s="42">
+        <v>11</v>
+      </c>
+      <c r="S5" s="40">
+        <v>31</v>
+      </c>
+      <c r="T5" s="41">
+        <v>19</v>
+      </c>
+      <c r="U5" s="42">
+        <v>11</v>
+      </c>
+      <c r="V5" s="43">
+        <f t="shared" ref="V5:V17" si="0">-SUM(S5-P5)*-1</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="44"/>
+    </row>
+    <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="289" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="269"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="129" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="261"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="126" t="s">
+        <v>215</v>
+      </c>
+      <c r="N6" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" s="47">
+        <v>49</v>
+      </c>
+      <c r="P6" s="48">
+        <f t="shared" ref="P6:P17" si="1">SUM(Q6:R6)</f>
+        <v>12</v>
+      </c>
+      <c r="Q6" s="49">
+        <v>7</v>
+      </c>
+      <c r="R6" s="50">
+        <v>5</v>
+      </c>
+      <c r="S6" s="48">
+        <f t="shared" ref="S6:S17" si="2">SUM(T6:U6)</f>
+        <v>12</v>
+      </c>
+      <c r="T6" s="49">
+        <v>7</v>
+      </c>
+      <c r="U6" s="50">
+        <v>5</v>
+      </c>
+      <c r="V6" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="52"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="53"/>
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="289" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="287" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="64"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="262" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" s="54"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="47">
+        <v>22</v>
+      </c>
+      <c r="P7" s="48">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Q7" s="49">
+        <v>11</v>
+      </c>
+      <c r="R7" s="50">
+        <v>4</v>
+      </c>
+      <c r="S7" s="48">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="T7" s="49">
+        <v>11</v>
+      </c>
+      <c r="U7" s="50">
+        <v>4</v>
+      </c>
+      <c r="V7" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W7" s="52"/>
+    </row>
+    <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="45"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="287"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="262"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="56">
+        <v>46313</v>
+      </c>
+      <c r="O8" s="47">
+        <v>24</v>
+      </c>
+      <c r="P8" s="48">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Q8" s="49">
+        <v>3</v>
+      </c>
+      <c r="R8" s="50">
+        <v>3</v>
+      </c>
+      <c r="S8" s="48">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="T8" s="49">
+        <v>2</v>
+      </c>
+      <c r="U8" s="50">
+        <v>2</v>
+      </c>
+      <c r="V8" s="51">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="W8" s="52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="45"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="58"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="259" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="64"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9" s="47"/>
+      <c r="P9" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="49"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W9" s="52"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="45"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="129" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="61"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="259"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="49"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="52"/>
+    </row>
+    <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="64"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="286" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="64"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="66"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="68"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="70"/>
+    </row>
+    <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="71"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="64"/>
+      <c r="H12" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="L12" s="73" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" s="74"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="68"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W12" s="70"/>
+    </row>
+    <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="61"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="257" t="s">
+        <v>149</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="127" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="128"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="60"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="68"/>
+      <c r="U13" s="69"/>
+      <c r="V13" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="70"/>
+    </row>
+    <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="8"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="290" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="60"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="68"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="70"/>
+    </row>
+    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="129"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="254"/>
+      <c r="F15" s="128" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="107"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="68"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="70"/>
+    </row>
+    <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="259" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="259" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="262" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="61"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="107"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="68"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="68"/>
+      <c r="U16" s="69"/>
+      <c r="V16" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="70"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="259"/>
+      <c r="B17" s="259"/>
+      <c r="C17" s="262"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="288" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="80"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="82">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="83"/>
+    </row>
+    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="59"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="77"/>
+      <c r="M18" s="77"/>
+      <c r="R18" s="84"/>
+      <c r="S18"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="254"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="77"/>
+      <c r="R19" s="84"/>
+      <c r="S19"/>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="85" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="254"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="158"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="R20" s="84"/>
+      <c r="S20"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="D21" s="61"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="R21" s="84"/>
+      <c r="S21"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="6"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="254"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="R22" s="84"/>
+      <c r="S22"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="R23" s="84"/>
+      <c r="S23"/>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="R24" s="84"/>
+      <c r="S24"/>
+    </row>
+    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="30"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="R25" s="84"/>
+      <c r="S25"/>
+    </row>
+    <row r="26" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="254"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="R26" s="84"/>
+      <c r="S26"/>
+    </row>
+    <row r="27" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="R27" s="84"/>
+      <c r="S27"/>
+    </row>
+    <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="263" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="263"/>
+      <c r="C28" s="263"/>
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="R28" s="84"/>
+      <c r="S28"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="30"/>
+      <c r="I29" s="254"/>
+      <c r="J29" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K29" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="92" t="s">
+        <v>25</v>
+      </c>
+      <c r="R29" s="84"/>
+      <c r="S29"/>
+    </row>
+    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="B30" s="94"/>
+      <c r="C30" s="93" t="s">
+        <v>231</v>
+      </c>
+      <c r="D30" s="93" t="s">
+        <v>234</v>
+      </c>
+      <c r="E30" s="267" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="8"/>
+      <c r="G30" s="253" t="s">
+        <v>240</v>
+      </c>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="159" t="s">
+        <v>81</v>
+      </c>
+      <c r="K30" s="124" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="218" t="s">
+        <v>242</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="R30" s="84"/>
+      <c r="S30"/>
+    </row>
+    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="93" t="s">
+        <v>232</v>
+      </c>
+      <c r="D31" s="93" t="s">
+        <v>233</v>
+      </c>
+      <c r="E31" s="267"/>
+      <c r="F31" s="8"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="159" t="s">
+        <v>244</v>
+      </c>
+      <c r="K31" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="L31" s="218" t="s">
+        <v>119</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" s="84"/>
+      <c r="S31"/>
+    </row>
+    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="94"/>
+      <c r="C32" s="93" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="93" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" s="267" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="159" t="s">
+        <v>205</v>
+      </c>
+      <c r="K32" s="224" t="s">
+        <v>50</v>
+      </c>
+      <c r="L32" s="218" t="s">
+        <v>122</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="R32" s="84"/>
+      <c r="S32"/>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="8"/>
+      <c r="C33" s="93" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="93" t="s">
+        <v>236</v>
+      </c>
+      <c r="E33" s="267"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="110" t="s">
+        <v>150</v>
+      </c>
+      <c r="L33" s="218" t="s">
+        <v>243</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="R33" s="84"/>
+      <c r="S33"/>
+    </row>
+    <row r="34" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="94"/>
+      <c r="B34" s="95"/>
+      <c r="D34" s="93" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" s="266" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="K34" s="224" t="s">
+        <v>16</v>
+      </c>
+      <c r="L34" s="218" t="s">
+        <v>38</v>
+      </c>
+      <c r="M34" s="8"/>
+      <c r="R34" s="84"/>
+      <c r="S34"/>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="94"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="93" t="s">
+        <v>238</v>
+      </c>
+      <c r="E35" s="266"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="124" t="s">
+        <v>120</v>
+      </c>
+      <c r="M35" s="13"/>
+      <c r="R35" s="84"/>
+      <c r="S35"/>
+    </row>
+    <row r="36" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="94"/>
+      <c r="B36" s="94"/>
+      <c r="D36" s="93" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="267" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="97"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="124" t="s">
+        <v>211</v>
+      </c>
+      <c r="L36" s="8"/>
+      <c r="M36" s="94"/>
+      <c r="R36" s="84"/>
+      <c r="S36"/>
+    </row>
+    <row r="37" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="E37" s="267"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="100"/>
+      <c r="K37" s="124" t="s">
+        <v>212</v>
+      </c>
+      <c r="L37" s="8"/>
+      <c r="M37" s="94"/>
+      <c r="R37" s="84"/>
+      <c r="S37"/>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="77"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="253" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" s="77"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="2"/>
+      <c r="R38" s="84"/>
+      <c r="S38"/>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="74"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="253" t="s">
+        <v>92</v>
+      </c>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="2"/>
+      <c r="S39"/>
+    </row>
+    <row r="40" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="105"/>
+      <c r="S40"/>
+    </row>
+    <row r="41" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="104"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="104"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="93" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="8"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="101"/>
+      <c r="M41" s="106"/>
+      <c r="S41"/>
+    </row>
+    <row r="42" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="104"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="104"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="253" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="106"/>
+      <c r="S42"/>
+    </row>
+    <row r="43" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="104"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="253" t="s">
+        <v>216</v>
+      </c>
+      <c r="F43" s="107"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="106"/>
+      <c r="S43"/>
+    </row>
+    <row r="44" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="104"/>
+      <c r="B44" s="104"/>
+      <c r="C44" s="104"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="109"/>
+      <c r="S44"/>
+    </row>
+    <row r="45" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="104"/>
+      <c r="B45" s="104"/>
+      <c r="C45" s="104"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="110"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="111"/>
+      <c r="S45"/>
+    </row>
+    <row r="46" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="104"/>
+      <c r="B46" s="104"/>
+      <c r="C46" s="104"/>
+      <c r="D46" s="104"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="104"/>
+      <c r="J46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="111"/>
+      <c r="S46"/>
+    </row>
+    <row r="47" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="104"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="104"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="104"/>
+      <c r="H47" s="104"/>
+      <c r="I47" s="254"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="112"/>
+      <c r="S47"/>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="84"/>
+      <c r="S48"/>
+    </row>
+    <row r="49" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="77"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="113"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="104"/>
+      <c r="I49" s="254"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="84"/>
+      <c r="S49"/>
+    </row>
+    <row r="50" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="77"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="84"/>
+      <c r="S50"/>
+    </row>
+    <row r="51" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="77"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="77"/>
+      <c r="D51" s="113"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="77"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="84"/>
+      <c r="S51"/>
+    </row>
+    <row r="52" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="77"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="113"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="77"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="77"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+    </row>
+    <row r="53" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="77"/>
+      <c r="B53" s="77"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="113"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="77"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="114"/>
+      <c r="M53" s="8"/>
+    </row>
+    <row r="54" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="77"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="113"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="77"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="77"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="114"/>
+      <c r="M54" s="8"/>
+    </row>
+    <row r="55" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="77"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="113"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="77"/>
+      <c r="G55" s="77"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="104"/>
+      <c r="J55" s="77"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="114"/>
+      <c r="M55" s="8"/>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="77"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="113"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="77"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="77"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="114"/>
+      <c r="M56" s="8"/>
+    </row>
+    <row r="57" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="77"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="77"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="114"/>
+      <c r="M57" s="8"/>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="77"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="113"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="77"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="115"/>
+      <c r="L58" s="114"/>
+      <c r="M58" s="8"/>
+    </row>
+    <row r="59" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="77"/>
+      <c r="B59" s="77"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="113"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="77"/>
+      <c r="G59" s="77"/>
+      <c r="H59" s="104"/>
+      <c r="I59" s="104"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="115"/>
+      <c r="L59" s="114"/>
+      <c r="M59" s="8"/>
+    </row>
+    <row r="60" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="77"/>
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="77"/>
+      <c r="G60" s="77"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="115"/>
+      <c r="L60" s="114"/>
+      <c r="M60" s="8"/>
+    </row>
+    <row r="61" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="77"/>
+      <c r="B61" s="77"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="113"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="114"/>
+      <c r="M61" s="8"/>
+    </row>
+    <row r="62" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="77"/>
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="77"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="114"/>
+      <c r="M62" s="8"/>
+    </row>
+    <row r="63" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="77"/>
+      <c r="B63" s="77"/>
+      <c r="C63" s="77"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="104"/>
+      <c r="I63" s="104"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="77"/>
+      <c r="M63" s="8"/>
+    </row>
+    <row r="64" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="77"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="77"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="77"/>
+      <c r="H64" s="104"/>
+      <c r="I64" s="104"/>
+      <c r="J64" s="77"/>
+      <c r="K64" s="116">
+        <v>22</v>
+      </c>
+      <c r="L64" s="117">
+        <v>6</v>
+      </c>
+      <c r="M64" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="61"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
+      <c r="S65"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L66" s="119" t="s">
+        <v>94</v>
+      </c>
+      <c r="M66" s="25">
+        <v>97</v>
+      </c>
+      <c r="S66"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L67" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="M67" s="25">
+        <f>SUM(M66-(M68+M69+M70))</f>
+        <v>69</v>
+      </c>
+      <c r="S67"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L68" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" s="25">
+        <v>15</v>
+      </c>
+      <c r="S68"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L69" s="121" t="s">
+        <v>24</v>
+      </c>
+      <c r="M69" s="25">
+        <v>9</v>
+      </c>
+      <c r="S69"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L70" s="122" t="s">
+        <v>25</v>
+      </c>
+      <c r="M70" s="25">
+        <v>4</v>
+      </c>
+      <c r="S70"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L71" t="s">
+        <v>96</v>
+      </c>
+      <c r="M71" s="25">
+        <v>13</v>
+      </c>
+      <c r="S71"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="M72" s="25"/>
+      <c r="S72"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
-    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="C16:C17"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="J3:J4"/>
@@ -12290,21 +14986,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="265" t="s">
+      <c r="A1" s="260" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
+      <c r="L1" s="260"/>
+      <c r="M1" s="260"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -12359,13 +15055,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="254" t="s">
+      <c r="D3" s="261" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="254" t="s">
+      <c r="F3" s="261" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -12374,24 +15070,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="260" t="s">
+      <c r="J3" s="259" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="261" t="s">
+      <c r="M3" s="262" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="258" t="s">
+      <c r="Q3" s="270" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="259"/>
+      <c r="R3" s="271"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="251" t="s">
+      <c r="T3" s="264" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="252"/>
+      <c r="U3" s="265"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -12403,20 +15099,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="254"/>
+      <c r="D4" s="261"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="254"/>
+      <c r="F4" s="261"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="260"/>
+      <c r="J4" s="259"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="261"/>
+      <c r="M4" s="262"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -12455,7 +15151,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="257" t="s">
+      <c r="F5" s="269" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -12463,7 +15159,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="254" t="s">
+      <c r="J5" s="261" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -12508,13 +15204,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="257"/>
+      <c r="F6" s="269"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="254"/>
+      <c r="J6" s="261"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -12563,13 +15259,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="260" t="s">
+      <c r="F7" s="259" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="256" t="s">
+      <c r="J7" s="268" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -12617,11 +15313,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="260"/>
+      <c r="F8" s="259"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="256"/>
+      <c r="J8" s="268"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -12665,7 +15361,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="257" t="s">
+      <c r="F9" s="269" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -12705,7 +15401,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="257"/>
+      <c r="F10" s="269"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -12831,7 +15527,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="261" t="s">
+      <c r="I13" s="262" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -12872,7 +15568,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="261"/>
+      <c r="I14" s="262"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -12932,13 +15628,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="260" t="s">
+      <c r="A16" s="259" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="260" t="s">
+      <c r="B16" s="259" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="262" t="s">
+      <c r="C16" s="272" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -12973,9 +15669,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="260"/>
-      <c r="B17" s="260"/>
-      <c r="C17" s="263"/>
+      <c r="A17" s="259"/>
+      <c r="B17" s="259"/>
+      <c r="C17" s="273"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -13008,7 +15704,7 @@
     <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="261" t="s">
+      <c r="C18" s="262" t="s">
         <v>82</v>
       </c>
       <c r="D18" s="61"/>
@@ -13026,7 +15722,7 @@
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="147"/>
-      <c r="C19" s="261"/>
+      <c r="C19" s="262"/>
       <c r="D19" s="125"/>
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
@@ -13185,13 +15881,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="266" t="s">
+      <c r="A28" s="263" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="266"/>
-      <c r="C28" s="266"/>
-      <c r="D28" s="266"/>
-      <c r="E28" s="266"/>
+      <c r="B28" s="263"/>
+      <c r="C28" s="263"/>
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -13251,7 +15947,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="255" t="s">
+      <c r="E30" s="267" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -13285,7 +15981,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="267"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -13315,7 +16011,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="255" t="s">
+      <c r="E32" s="267" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -13345,7 +16041,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="255"/>
+      <c r="E33" s="267"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -13369,7 +16065,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="253" t="s">
+      <c r="E34" s="266" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -13394,7 +16090,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="253"/>
+      <c r="E35" s="266"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -13413,7 +16109,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="255" t="s">
+      <c r="E36" s="267" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -13433,7 +16129,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="255"/>
+      <c r="E37" s="267"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -13961,28 +16657,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="C18:C19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -14903,21 +17599,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="265" t="s">
+      <c r="A1" s="260" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
+      <c r="L1" s="260"/>
+      <c r="M1" s="260"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -14972,13 +17668,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="254" t="s">
+      <c r="D3" s="261" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="254" t="s">
+      <c r="F3" s="261" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -14987,24 +17683,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="260" t="s">
+      <c r="J3" s="259" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="261" t="s">
+      <c r="M3" s="262" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="258" t="s">
+      <c r="Q3" s="270" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="259"/>
+      <c r="R3" s="271"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="251" t="s">
+      <c r="T3" s="264" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="252"/>
+      <c r="U3" s="265"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -15016,20 +17712,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="254"/>
+      <c r="D4" s="261"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="254"/>
+      <c r="F4" s="261"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="260"/>
+      <c r="J4" s="259"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="261"/>
+      <c r="M4" s="262"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -15068,7 +17764,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="257" t="s">
+      <c r="F5" s="269" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -15076,7 +17772,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="254" t="s">
+      <c r="J5" s="261" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -15121,13 +17817,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="257"/>
+      <c r="F6" s="269"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="254"/>
+      <c r="J6" s="261"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -15171,13 +17867,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="260" t="s">
+      <c r="F7" s="259" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="256" t="s">
+      <c r="J7" s="268" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -15225,11 +17921,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="260"/>
+      <c r="F8" s="259"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="256"/>
+      <c r="J8" s="268"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -15273,7 +17969,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="257" t="s">
+      <c r="F9" s="269" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -15313,7 +18009,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="257"/>
+      <c r="F10" s="269"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -15439,7 +18135,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="261" t="s">
+      <c r="I13" s="262" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -15480,7 +18176,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="261"/>
+      <c r="I14" s="262"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -15515,7 +18211,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="261" t="s">
+      <c r="I15" s="262" t="s">
         <v>82</v>
       </c>
       <c r="J15" s="60"/>
@@ -15542,13 +18238,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="260" t="s">
+      <c r="A16" s="259" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="260" t="s">
+      <c r="B16" s="259" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="262" t="s">
+      <c r="C16" s="272" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -15558,7 +18254,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="261"/>
+      <c r="I16" s="262"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -15583,15 +18279,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="260"/>
-      <c r="B17" s="260"/>
-      <c r="C17" s="263"/>
+      <c r="A17" s="259"/>
+      <c r="B17" s="259"/>
+      <c r="C17" s="273"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="257" t="s">
+      <c r="I17" s="269" t="s">
         <v>139</v>
       </c>
       <c r="J17" s="71"/>
@@ -15626,7 +18322,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="257"/>
+      <c r="I18" s="269"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -15798,13 +18494,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="266" t="s">
+      <c r="A28" s="263" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="266"/>
-      <c r="C28" s="266"/>
-      <c r="D28" s="266"/>
-      <c r="E28" s="266"/>
+      <c r="B28" s="263"/>
+      <c r="C28" s="263"/>
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -15864,7 +18560,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="255" t="s">
+      <c r="E30" s="267" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -15898,7 +18594,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="267"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -15928,7 +18624,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="255" t="s">
+      <c r="E32" s="267" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -15958,7 +18654,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="255"/>
+      <c r="E33" s="267"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -15984,7 +18680,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="253" t="s">
+      <c r="E34" s="266" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -16007,7 +18703,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="253"/>
+      <c r="E35" s="266"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -16027,7 +18723,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="255" t="s">
+      <c r="E36" s="267" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -16044,7 +18740,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="255"/>
+      <c r="E37" s="267"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -16572,29 +19268,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="I13:I14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -17512,21 +20208,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="265" t="s">
+      <c r="A1" s="260" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
+      <c r="L1" s="260"/>
+      <c r="M1" s="260"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -17579,13 +20275,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="254" t="s">
+      <c r="D3" s="261" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="254" t="s">
+      <c r="F3" s="261" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -17594,24 +20290,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="260" t="s">
+      <c r="J3" s="259" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="261" t="s">
+      <c r="M3" s="262" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="258" t="s">
+      <c r="Q3" s="270" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="259"/>
+      <c r="R3" s="271"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="251" t="s">
+      <c r="T3" s="264" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="252"/>
+      <c r="U3" s="265"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -17623,20 +20319,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="254"/>
+      <c r="D4" s="261"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="254"/>
+      <c r="F4" s="261"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="260"/>
+      <c r="J4" s="259"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="261"/>
+      <c r="M4" s="262"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -17675,7 +20371,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="257" t="s">
+      <c r="F5" s="269" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -17683,7 +20379,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="254" t="s">
+      <c r="J5" s="261" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -17728,13 +20424,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="257"/>
+      <c r="F6" s="269"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="254"/>
+      <c r="J6" s="261"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -17778,13 +20474,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="260" t="s">
+      <c r="F7" s="259" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="256" t="s">
+      <c r="J7" s="268" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -17832,13 +20528,13 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="260"/>
+      <c r="F8" s="259"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="J8" s="256"/>
+      <c r="J8" s="268"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -17882,13 +20578,13 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="257" t="s">
+      <c r="F9" s="269" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
       <c r="H9" s="30"/>
       <c r="I9" s="134"/>
-      <c r="J9" s="261" t="s">
+      <c r="J9" s="262" t="s">
         <v>82</v>
       </c>
       <c r="K9" s="54"/>
@@ -17924,11 +20620,11 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="257"/>
+      <c r="F10" s="269"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
-      <c r="J10" s="261"/>
+      <c r="J10" s="262"/>
       <c r="K10" s="6"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
@@ -18051,7 +20747,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="261" t="s">
+      <c r="I13" s="262" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -18092,7 +20788,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="261"/>
+      <c r="I14" s="262"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -18127,7 +20823,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="267" t="s">
+      <c r="I15" s="274" t="s">
         <v>139</v>
       </c>
       <c r="J15" s="60"/>
@@ -18154,13 +20850,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="260" t="s">
+      <c r="A16" s="259" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="260" t="s">
+      <c r="B16" s="259" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="262" t="s">
+      <c r="C16" s="272" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -18170,7 +20866,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="267"/>
+      <c r="I16" s="274"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -18195,9 +20891,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="260"/>
-      <c r="B17" s="260"/>
-      <c r="C17" s="263"/>
+      <c r="A17" s="259"/>
+      <c r="B17" s="259"/>
+      <c r="C17" s="273"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -18408,13 +21104,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="266" t="s">
+      <c r="A28" s="263" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="266"/>
-      <c r="C28" s="266"/>
-      <c r="D28" s="266"/>
-      <c r="E28" s="266"/>
+      <c r="B28" s="263"/>
+      <c r="C28" s="263"/>
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -18474,7 +21170,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="255" t="s">
+      <c r="E30" s="267" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -18508,7 +21204,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="267"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -18538,7 +21234,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="255" t="s">
+      <c r="E32" s="267" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -18563,7 +21259,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="255"/>
+      <c r="E33" s="267"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -18584,7 +21280,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="253" t="s">
+      <c r="E34" s="266" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -18607,7 +21303,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="253"/>
+      <c r="E35" s="266"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -18627,7 +21323,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="255" t="s">
+      <c r="E36" s="267" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -18647,7 +21343,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="255"/>
+      <c r="E37" s="267"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -19175,17 +21871,11 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="A16:A17"/>
@@ -19193,11 +21883,17 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20114,21 +22810,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="265" t="s">
+      <c r="A1" s="260" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
+      <c r="L1" s="260"/>
+      <c r="M1" s="260"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -20183,13 +22879,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="254" t="s">
+      <c r="D3" s="261" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="254" t="s">
+      <c r="F3" s="261" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -20198,24 +22894,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="260" t="s">
+      <c r="J3" s="259" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="261" t="s">
+      <c r="M3" s="262" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="258" t="s">
+      <c r="Q3" s="270" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="259"/>
+      <c r="R3" s="271"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="251" t="s">
+      <c r="T3" s="264" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="252"/>
+      <c r="U3" s="265"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -20227,20 +22923,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="254"/>
+      <c r="D4" s="261"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="254"/>
+      <c r="F4" s="261"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="260"/>
+      <c r="J4" s="259"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="261"/>
+      <c r="M4" s="262"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -20279,7 +22975,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="257" t="s">
+      <c r="F5" s="269" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -20287,7 +22983,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="254" t="s">
+      <c r="J5" s="261" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -20332,13 +23028,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="257"/>
+      <c r="F6" s="269"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="254"/>
+      <c r="J6" s="261"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -20385,7 +23081,7 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="260" t="s">
+      <c r="F7" s="259" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
@@ -20393,7 +23089,7 @@
       <c r="I7" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="256" t="s">
+      <c r="J7" s="268" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -20441,10 +23137,10 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="260"/>
+      <c r="F8" s="259"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
-      <c r="J8" s="256"/>
+      <c r="J8" s="268"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -20488,7 +23184,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="257" t="s">
+      <c r="F9" s="269" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -20528,7 +23224,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="257"/>
+      <c r="F10" s="269"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -20655,7 +23351,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="261" t="s">
+      <c r="I13" s="262" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -20693,7 +23389,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="261"/>
+      <c r="I14" s="262"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -20728,7 +23424,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="261" t="s">
+      <c r="I15" s="262" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -20755,13 +23451,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="260" t="s">
+      <c r="A16" s="259" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="260" t="s">
+      <c r="B16" s="259" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="257" t="s">
+      <c r="C16" s="269" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -20771,7 +23467,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="261"/>
+      <c r="I16" s="262"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -20796,15 +23492,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="260"/>
-      <c r="B17" s="260"/>
-      <c r="C17" s="257"/>
+      <c r="A17" s="259"/>
+      <c r="B17" s="259"/>
+      <c r="C17" s="269"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="261" t="s">
+      <c r="I17" s="262" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -20839,7 +23535,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="261"/>
+      <c r="I18" s="262"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -21009,13 +23705,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="266" t="s">
+      <c r="A28" s="263" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="266"/>
-      <c r="C28" s="266"/>
-      <c r="D28" s="266"/>
-      <c r="E28" s="266"/>
+      <c r="B28" s="263"/>
+      <c r="C28" s="263"/>
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -21075,7 +23771,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="255" t="s">
+      <c r="E30" s="267" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -21109,7 +23805,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="267"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -21139,7 +23835,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="255" t="s">
+      <c r="E32" s="267" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -21165,7 +23861,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="255"/>
+      <c r="E33" s="267"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -21187,7 +23883,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="253" t="s">
+      <c r="E34" s="266" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -21210,7 +23906,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="253"/>
+      <c r="E35" s="266"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -21230,7 +23926,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="255" t="s">
+      <c r="E36" s="267" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -21247,7 +23943,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="255"/>
+      <c r="E37" s="267"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -21775,17 +24471,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="I17:I18"/>
     <mergeCell ref="A1:M1"/>
@@ -21798,6 +24483,17 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="I13:I14"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -22717,21 +25413,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="265" t="s">
+      <c r="A1" s="260" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
+      <c r="L1" s="260"/>
+      <c r="M1" s="260"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -22786,13 +25482,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="254" t="s">
+      <c r="D3" s="261" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="254" t="s">
+      <c r="F3" s="261" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -22801,24 +25497,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="260" t="s">
+      <c r="J3" s="259" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="261" t="s">
+      <c r="M3" s="262" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="258" t="s">
+      <c r="Q3" s="270" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="259"/>
+      <c r="R3" s="271"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="251" t="s">
+      <c r="T3" s="264" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="252"/>
+      <c r="U3" s="265"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -22830,20 +25526,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="254"/>
+      <c r="D4" s="261"/>
       <c r="E4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="254"/>
+      <c r="F4" s="261"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="260"/>
+      <c r="J4" s="259"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="261"/>
+      <c r="M4" s="262"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -22882,7 +25578,7 @@
       <c r="E5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F5" s="257" t="s">
+      <c r="F5" s="269" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -22890,7 +25586,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="254" t="s">
+      <c r="J5" s="261" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -22935,13 +25631,13 @@
       <c r="E6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="257"/>
+      <c r="F6" s="269"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="254"/>
+      <c r="J6" s="261"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -22988,13 +25684,13 @@
       <c r="E7" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="260" t="s">
+      <c r="F7" s="259" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="256" t="s">
+      <c r="J7" s="268" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -23040,11 +25736,11 @@
         <v>17</v>
       </c>
       <c r="E8" s="30"/>
-      <c r="F8" s="260"/>
+      <c r="F8" s="259"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="256"/>
+      <c r="J8" s="268"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -23089,7 +25785,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="257" t="s">
+      <c r="F9" s="269" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -23129,7 +25825,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="257"/>
+      <c r="F10" s="269"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -23256,7 +25952,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="261" t="s">
+      <c r="I13" s="262" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -23297,7 +25993,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="261"/>
+      <c r="I14" s="262"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -23332,7 +26028,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="261" t="s">
+      <c r="I15" s="262" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -23359,13 +26055,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="260" t="s">
+      <c r="A16" s="259" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="260" t="s">
+      <c r="B16" s="259" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="257" t="s">
+      <c r="C16" s="269" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -23375,7 +26071,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="261"/>
+      <c r="I16" s="262"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -23400,15 +26096,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="260"/>
-      <c r="B17" s="260"/>
-      <c r="C17" s="257"/>
+      <c r="A17" s="259"/>
+      <c r="B17" s="259"/>
+      <c r="C17" s="269"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="261" t="s">
+      <c r="I17" s="262" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -23443,7 +26139,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="261"/>
+      <c r="I18" s="262"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -23614,13 +26310,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="266" t="s">
+      <c r="A28" s="263" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="266"/>
-      <c r="C28" s="266"/>
-      <c r="D28" s="266"/>
-      <c r="E28" s="266"/>
+      <c r="B28" s="263"/>
+      <c r="C28" s="263"/>
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -23680,7 +26376,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="255" t="s">
+      <c r="E30" s="267" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -23714,7 +26410,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="267"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -23742,7 +26438,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="255" t="s">
+      <c r="E32" s="267" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -23768,7 +26464,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="255"/>
+      <c r="E33" s="267"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -23790,7 +26486,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="253" t="s">
+      <c r="E34" s="266" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -23813,7 +26509,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="253"/>
+      <c r="E35" s="266"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -23833,7 +26529,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="255" t="s">
+      <c r="E36" s="267" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -23853,7 +26549,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="255"/>
+      <c r="E37" s="267"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -24383,29 +27079,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -24554,22 +27250,22 @@
       <c r="C3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="254" t="s">
+      <c r="D3" s="261" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="201" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="268" t="s">
+      <c r="F3" s="278" t="s">
         <v>160</v>
       </c>
       <c r="H3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="256" t="s">
+      <c r="I3" s="268" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="269" t="s">
+      <c r="K3" s="279" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="2"/>
@@ -24585,16 +27281,16 @@
       <c r="C4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="254"/>
+      <c r="D4" s="261"/>
       <c r="E4" s="201" t="s">
         <v>162</v>
       </c>
-      <c r="F4" s="268"/>
+      <c r="F4" s="278"/>
       <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="256"/>
-      <c r="K4" s="270"/>
+      <c r="I4" s="268"/>
+      <c r="K4" s="280"/>
       <c r="L4" s="203" t="s">
         <v>163</v>
       </c>
@@ -24607,13 +27303,13 @@
       <c r="E5" s="129" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="268" t="s">
+      <c r="F5" s="278" t="s">
         <v>165</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="254" t="s">
+      <c r="I5" s="261" t="s">
         <v>166</v>
       </c>
       <c r="K5" s="2"/>
@@ -24627,11 +27323,11 @@
       <c r="E6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="268"/>
+      <c r="F6" s="278"/>
       <c r="H6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="254"/>
+      <c r="I6" s="261"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -24646,10 +27342,10 @@
       <c r="E7" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F7" s="254" t="s">
+      <c r="F7" s="261" t="s">
         <v>168</v>
       </c>
-      <c r="I7" s="254" t="s">
+      <c r="I7" s="261" t="s">
         <v>15</v>
       </c>
       <c r="K7" s="2"/>
@@ -24663,17 +27359,17 @@
       <c r="E8" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="254"/>
-      <c r="I8" s="254"/>
+      <c r="F8" s="261"/>
+      <c r="I8" s="261"/>
       <c r="K8" s="2"/>
       <c r="L8" s="206"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="262" t="s">
+      <c r="A9" s="272" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="254" t="s">
+      <c r="B9" s="261" t="s">
         <v>171</v>
       </c>
       <c r="C9" s="207" t="s">
@@ -24682,7 +27378,7 @@
       <c r="E9" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="268" t="s">
+      <c r="F9" s="278" t="s">
         <v>173</v>
       </c>
       <c r="K9" s="2"/>
@@ -24692,15 +27388,15 @@
       <c r="P9"/>
     </row>
     <row r="10" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="263"/>
-      <c r="B10" s="254"/>
+      <c r="A10" s="273"/>
+      <c r="B10" s="261"/>
       <c r="C10" s="208" t="s">
         <v>174</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>175</v>
       </c>
-      <c r="F10" s="268"/>
+      <c r="F10" s="278"/>
       <c r="K10" s="209"/>
       <c r="L10" s="2"/>
       <c r="M10" s="206"/>
@@ -24727,7 +27423,7 @@
       <c r="E11" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="F11" s="260" t="s">
+      <c r="F11" s="259" t="s">
         <v>177</v>
       </c>
       <c r="K11" s="209"/>
@@ -24756,7 +27452,7 @@
       <c r="E12" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="260"/>
+      <c r="F12" s="259"/>
       <c r="G12" s="212" t="s">
         <v>179</v>
       </c>
@@ -24795,10 +27491,10 @@
       <c r="E13" s="183" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="271" t="s">
+      <c r="F13" s="281" t="s">
         <v>184</v>
       </c>
-      <c r="H13" s="262" t="s">
+      <c r="H13" s="272" t="s">
         <v>185</v>
       </c>
       <c r="K13" s="2"/>
@@ -24828,8 +27524,8 @@
       <c r="E14" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="F14" s="272"/>
-      <c r="H14" s="263"/>
+      <c r="F14" s="282"/>
+      <c r="H14" s="273"/>
       <c r="K14" s="2"/>
       <c r="L14" s="6"/>
       <c r="M14" s="2"/>
@@ -24856,10 +27552,10 @@
       <c r="E15" s="183" t="s">
         <v>189</v>
       </c>
-      <c r="F15" s="254" t="s">
+      <c r="F15" s="261" t="s">
         <v>190</v>
       </c>
-      <c r="H15" s="269" t="s">
+      <c r="H15" s="279" t="s">
         <v>45</v>
       </c>
       <c r="K15" s="2"/>
@@ -24884,8 +27580,8 @@
       <c r="C16" s="183" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="254"/>
-      <c r="H16" s="270"/>
+      <c r="F16" s="261"/>
+      <c r="H16" s="280"/>
       <c r="K16" s="2"/>
       <c r="L16" s="209"/>
       <c r="M16" s="8"/>
@@ -24912,7 +27608,7 @@
       </c>
       <c r="D17" s="206"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="273" t="s">
+      <c r="F17" s="283" t="s">
         <v>193</v>
       </c>
       <c r="G17" s="2"/>
@@ -24929,7 +27625,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="274"/>
+      <c r="F18" s="284"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="209"/>
@@ -24980,7 +27676,7 @@
       <c r="B20" s="133" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="254" t="s">
+      <c r="C20" s="261" t="s">
         <v>197</v>
       </c>
       <c r="D20" s="2"/>
@@ -25012,7 +27708,7 @@
         <v>199</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="254"/>
+      <c r="C21" s="261"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="219" t="s">
@@ -25020,7 +27716,7 @@
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="269" t="s">
+      <c r="I21" s="279" t="s">
         <v>82</v>
       </c>
       <c r="J21" s="209"/>
@@ -25054,7 +27750,7 @@
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="270"/>
+      <c r="I22" s="280"/>
       <c r="J22" s="209"/>
       <c r="K22" s="101" t="s">
         <v>40</v>
@@ -25784,11 +28480,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="F9:F10"/>
@@ -25799,11 +28495,11 @@
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="F17:F18"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -26723,21 +29419,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="265" t="s">
+      <c r="A1" s="260" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
+      <c r="L1" s="260"/>
+      <c r="M1" s="260"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -26792,13 +29488,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="261" t="s">
+      <c r="D3" s="262" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="254" t="s">
+      <c r="F3" s="261" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -26807,24 +29503,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="261" t="s">
+      <c r="J3" s="262" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="278" t="s">
+      <c r="M3" s="285" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="258" t="s">
+      <c r="Q3" s="270" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="259"/>
+      <c r="R3" s="271"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="251" t="s">
+      <c r="T3" s="264" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="252"/>
+      <c r="U3" s="265"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -26838,20 +29534,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="261"/>
+      <c r="D4" s="262"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="254"/>
+      <c r="F4" s="261"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="261"/>
+      <c r="J4" s="262"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="278"/>
+      <c r="M4" s="285"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -26890,7 +29586,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="257" t="s">
+      <c r="F5" s="269" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -26898,7 +29594,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="254" t="s">
+      <c r="J5" s="261" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -26943,13 +29639,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="257"/>
+      <c r="F6" s="269"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="254"/>
+      <c r="J6" s="261"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -26993,13 +29689,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="260" t="s">
+      <c r="F7" s="259" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="256" t="s">
+      <c r="J7" s="268" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -27047,11 +29743,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="260"/>
+      <c r="F8" s="259"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="256"/>
+      <c r="J8" s="268"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -27096,7 +29792,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="257" t="s">
+      <c r="F9" s="269" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -27136,7 +29832,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="257"/>
+      <c r="F10" s="269"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -27358,13 +30054,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="260" t="s">
+      <c r="A16" s="259" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="260" t="s">
+      <c r="B16" s="259" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="261" t="s">
+      <c r="C16" s="262" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -27399,9 +30095,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="260"/>
-      <c r="B17" s="260"/>
-      <c r="C17" s="261"/>
+      <c r="A17" s="259"/>
+      <c r="B17" s="259"/>
+      <c r="C17" s="262"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -27611,13 +30307,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="266" t="s">
+      <c r="A28" s="263" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="266"/>
-      <c r="C28" s="266"/>
-      <c r="D28" s="266"/>
-      <c r="E28" s="266"/>
+      <c r="B28" s="263"/>
+      <c r="C28" s="263"/>
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -27677,7 +30373,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="255" t="s">
+      <c r="E30" s="267" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -27709,7 +30405,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="267"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -27737,7 +30433,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="255" t="s">
+      <c r="E32" s="267" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -27765,7 +30461,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="255"/>
+      <c r="E33" s="267"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -27789,7 +30485,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="253" t="s">
+      <c r="E34" s="266" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -27812,7 +30508,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="253"/>
+      <c r="E35" s="266"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -27832,7 +30528,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="255" t="s">
+      <c r="E36" s="267" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -27852,7 +30548,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="255"/>
+      <c r="E37" s="267"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -28380,26 +31076,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -29317,21 +32013,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="265" t="s">
+      <c r="A1" s="260" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265"/>
-      <c r="M1" s="265"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
+      <c r="L1" s="260"/>
+      <c r="M1" s="260"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -29386,13 +32082,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="261" t="s">
+      <c r="D3" s="262" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="254" t="s">
+      <c r="F3" s="261" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -29401,24 +32097,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="261" t="s">
+      <c r="J3" s="262" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="278" t="s">
+      <c r="M3" s="285" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="258" t="s">
+      <c r="Q3" s="270" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="259"/>
+      <c r="R3" s="271"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="251" t="s">
+      <c r="T3" s="264" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="252"/>
+      <c r="U3" s="265"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -29432,20 +32128,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="261"/>
+      <c r="D4" s="262"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="254"/>
+      <c r="F4" s="261"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="261"/>
+      <c r="J4" s="262"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="278"/>
+      <c r="M4" s="285"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -29484,7 +32180,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="257" t="s">
+      <c r="F5" s="269" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -29492,7 +32188,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="254" t="s">
+      <c r="J5" s="261" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -29537,13 +32233,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="257"/>
+      <c r="F6" s="269"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="254"/>
+      <c r="J6" s="261"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -29587,13 +32283,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="260" t="s">
+      <c r="F7" s="259" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="256" t="s">
+      <c r="J7" s="268" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -29641,11 +32337,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="260"/>
+      <c r="F8" s="259"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="256"/>
+      <c r="J8" s="268"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -29690,7 +32386,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="257" t="s">
+      <c r="F9" s="269" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -29730,7 +32426,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="257"/>
+      <c r="F10" s="269"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -29952,13 +32648,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="260" t="s">
+      <c r="A16" s="259" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="260" t="s">
+      <c r="B16" s="259" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="261" t="s">
+      <c r="C16" s="262" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -29993,9 +32689,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="260"/>
-      <c r="B17" s="260"/>
-      <c r="C17" s="261"/>
+      <c r="A17" s="259"/>
+      <c r="B17" s="259"/>
+      <c r="C17" s="262"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -30205,13 +32901,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="266" t="s">
+      <c r="A28" s="263" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="266"/>
-      <c r="C28" s="266"/>
-      <c r="D28" s="266"/>
-      <c r="E28" s="266"/>
+      <c r="B28" s="263"/>
+      <c r="C28" s="263"/>
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -30271,7 +32967,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="255" t="s">
+      <c r="E30" s="267" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -30305,7 +33001,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="255"/>
+      <c r="E31" s="267"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -30333,7 +33029,7 @@
       <c r="D32" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="255" t="s">
+      <c r="E32" s="267" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -30361,7 +33057,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="255"/>
+      <c r="E33" s="267"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -30385,7 +33081,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="253" t="s">
+      <c r="E34" s="266" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -30410,7 +33106,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="253"/>
+      <c r="E35" s="266"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -30432,7 +33128,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="255" t="s">
+      <c r="E36" s="267" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -30454,7 +33150,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="255"/>
+      <c r="E37" s="267"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -30982,6 +33678,18 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="A16:A17"/>
@@ -30990,18 +33698,6 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/raw/D3.xlsx
+++ b/raw/D3.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6375DA3-D005-41F7-9DEA-069D9C58345D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="30-2" sheetId="34" r:id="rId1"/>
@@ -20,8 +19,9 @@
     <sheet name="17" sheetId="43" r:id="rId10"/>
     <sheet name="17-2" sheetId="44" r:id="rId11"/>
     <sheet name="18" sheetId="45" r:id="rId12"/>
+    <sheet name="19" sheetId="46" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029" calcMode="manual"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,12 +43,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{4CD500F1-224C-468B-BC75-45FF0F75C995}">
+    <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="0" shapeId="0" xr:uid="{A3499307-494A-42FE-9C37-C75FEFBA96AD}">
+    <comment ref="H13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0" xr:uid="{4E1207C1-4E6A-4CBC-9182-486DC93A48F8}">
+    <comment ref="H15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -94,7 +94,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H17" authorId="0" shapeId="0" xr:uid="{9852720D-93EF-4442-88FF-604CD1243A19}">
+    <comment ref="H17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -115,12 +115,12 @@
 </file>
 
 <file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="H17" authorId="0" shapeId="0" xr:uid="{DB11EAC8-E36B-467E-B5F7-A8976A1623C1}">
+    <comment ref="H17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -135,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H19" authorId="0" shapeId="0" xr:uid="{F786351A-3C6C-434C-B6B8-53861529347C}">
+    <comment ref="H19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -151,7 +151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{D7B936F9-5C1D-4D19-91FE-1CAA3AE7D317}">
+    <comment ref="H21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -171,12 +171,12 @@
 </file>
 
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="H17" authorId="0" shapeId="0" xr:uid="{9C7CAB6F-AF20-440C-9EBD-CA5B15DEAEAD}">
+    <comment ref="H17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -191,7 +191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H19" authorId="0" shapeId="0" xr:uid="{C8439274-2B6B-4780-92B1-6DA5EFDE26CC}">
+    <comment ref="H19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -207,7 +207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{4D05B01B-D97E-4028-B035-581F1C24A551}">
+    <comment ref="H21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -227,12 +227,12 @@
 </file>
 
 <file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{E44DACBB-9641-4BEF-8811-86790F380B93}">
+    <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -248,7 +248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{6E5BDA00-2299-473E-9E55-CA44B73E9FA4}">
+    <comment ref="J7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -263,7 +263,63 @@
         </r>
       </text>
     </comment>
-    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{A7732882-F2F4-4DBE-A347-39AE42F4652A}">
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Даулет
+87025167087</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments13.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="J7" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Алібек
+87012894507</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I13" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Аслан
+87014988298</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -283,12 +339,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="M6" authorId="0" shapeId="0" xr:uid="{32E01F06-9257-49C0-B74C-64626E3A2B39}">
+    <comment ref="M6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -304,7 +360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{6417B75C-6AEA-4910-A154-9B91CE0B1909}">
+    <comment ref="I13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -319,7 +375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{D6495D18-02B3-4057-AD68-D89C90A86526}">
+    <comment ref="C16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -335,7 +391,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{35AE1A52-2835-4D93-A47E-7D5480258FD3}">
+    <comment ref="C18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -355,12 +411,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{D1D25F21-8E88-4F96-ADB4-23D8019BDA35}">
+    <comment ref="I13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -375,7 +431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{A2D2B716-9063-436C-A536-6C3623EE6584}">
+    <comment ref="I15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -390,7 +446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{93C29B7D-AC36-41C1-94C6-FB5BC033147A}">
+    <comment ref="C16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -406,7 +462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{6EFD43E2-7695-4A42-A99C-CE3F26E5F55B}">
+    <comment ref="I19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -427,12 +483,12 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="J9" authorId="0" shapeId="0" xr:uid="{6F991953-F55D-473C-8A5E-EB7CEDD6EB49}">
+    <comment ref="J9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -447,7 +503,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{B3605F89-4C8A-4055-BC7E-AE3DE713264F}">
+    <comment ref="I13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -462,7 +518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{21BC0C24-2321-4BFF-AC27-FCB792175ACA}">
+    <comment ref="I15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -489,7 +545,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{69828691-FED1-4C3A-8F44-E314AAF681BC}">
+    <comment ref="C16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -505,7 +561,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{D92B9CBC-2663-477E-868A-906B79C9A8CC}">
+    <comment ref="I18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -526,12 +582,12 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="M6" authorId="0" shapeId="0" xr:uid="{DB7C653E-960A-4064-903E-FFE64AE5D9DA}">
+    <comment ref="M6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -547,7 +603,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{78BF3933-6E6C-4ABA-8BE7-669D2CE10ACD}">
+    <comment ref="I13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -562,7 +618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{68E32F67-4D82-46E6-929C-C5B69495A5CE}">
+    <comment ref="I15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -578,7 +634,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{B864C7EB-469B-4973-9A5F-992DF5AA5E5E}">
+    <comment ref="C16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -605,7 +661,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{84026822-AC18-4A89-94CD-E908D5A3A054}">
+    <comment ref="I17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -625,12 +681,12 @@
 </file>
 
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="M6" authorId="0" shapeId="0" xr:uid="{D0D8401A-DE17-4E74-87F5-EAEB3E6F7497}">
+    <comment ref="M6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -646,7 +702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{FBCBA0F6-B967-401A-B7EC-D65947FE8856}">
+    <comment ref="I13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -661,7 +717,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{D80D6F6E-7E74-4A96-886F-AB3D7E1B32CD}">
+    <comment ref="I15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -677,7 +733,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{DFE0C80A-E678-4351-893F-8B5BE2D1DB78}">
+    <comment ref="C16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -704,7 +760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{EA97C766-4AD3-40A9-A801-CBCAD5E63FF9}">
+    <comment ref="I17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -724,12 +780,12 @@
 </file>
 
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{9E8C9B03-AE28-48C7-AB85-E79316DB77E9}">
+    <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -755,7 +811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L4" authorId="0" shapeId="0" xr:uid="{DB61E8F3-2A5A-4EA4-ABF8-EE626CB66AD7}">
+    <comment ref="L4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -782,7 +838,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0" xr:uid="{F75EA2D0-9506-4F0B-B64C-DDD4ED5CB945}">
+    <comment ref="H15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -808,7 +864,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{F1D38241-4389-4D8C-B446-6117512ABF88}">
+    <comment ref="I21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -834,7 +890,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F28" authorId="0" shapeId="0" xr:uid="{F1BEFD49-6D93-49D0-A7A9-2637CE76584A}">
+    <comment ref="F28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -866,12 +922,12 @@
 </file>
 
 <file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{68874BE8-B12C-49AA-8C73-5B9481F88741}">
+    <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -887,7 +943,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{F6BB724B-3D0B-41E1-9292-97BB559A1669}">
+    <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -902,7 +958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{A0935094-829E-4AF9-97B8-4A79E2047966}">
+    <comment ref="C16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -922,12 +978,12 @@
 </file>
 
 <file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{AD3CE946-7399-40D7-8A4D-AE7319B10F28}">
+    <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -943,7 +999,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{C978F013-9913-43C6-A5D2-011F3DDF049E}">
+    <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -958,7 +1014,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{BF615D80-0B4B-4588-82D9-DD6EB2A8F023}">
+    <comment ref="C16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -978,7 +1034,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="246">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -1714,15 +1770,18 @@
   <si>
     <t>49-Н180112</t>
   </si>
+  <si>
+    <t>31-H3134/12</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="36" x14ac:knownFonts="1">
     <font>
@@ -2527,21 +2586,21 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="291">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2567,17 +2626,17 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2586,7 +2645,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2692,7 +2751,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2883,7 +2942,7 @@
     <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2898,7 +2957,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3105,7 +3164,7 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3117,7 +3176,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3156,10 +3215,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3276,23 +3335,41 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3302,6 +3379,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3318,22 +3398,28 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3357,29 +3443,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal 4" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Percent 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 4" xfId="4"/>
+    <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009 2 2" xfId="3"/>
+    <cellStyle name="Percent 2" xfId="5"/>
     <cellStyle name="Денежный" xfId="2" builtinId="4"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
@@ -3659,7 +3742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26164B13-15F5-4C82-BDB5-440BA0589D5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4568,21 +4651,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="284"/>
+      <c r="M1" s="284"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4637,13 +4720,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="261" t="s">
+      <c r="D3" s="273" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="261" t="s">
+      <c r="F3" s="273" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -4655,24 +4738,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="259" t="s">
+      <c r="J3" s="279" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="262" t="s">
+      <c r="M3" s="280" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="270" t="s">
+      <c r="Q3" s="277" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="271"/>
+      <c r="R3" s="278"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="270" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="265"/>
+      <c r="U3" s="271"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -4684,20 +4767,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="261"/>
+      <c r="D4" s="273"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="261"/>
+      <c r="F4" s="273"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="259"/>
+      <c r="J4" s="279"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="262"/>
+      <c r="M4" s="280"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -4736,7 +4819,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="269" t="s">
+      <c r="F5" s="276" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -4744,7 +4827,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="261" t="s">
+      <c r="J5" s="273" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -4789,13 +4872,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="269"/>
+      <c r="F6" s="276"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="261"/>
+      <c r="J6" s="273"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -4841,13 +4924,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="259" t="s">
+      <c r="F7" s="279" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="268" t="s">
+      <c r="J7" s="275" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -4895,11 +4978,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="259"/>
+      <c r="F8" s="279"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="268"/>
+      <c r="J8" s="275"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -4943,7 +5026,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="269" t="s">
+      <c r="F9" s="276" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -4983,7 +5066,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="269"/>
+      <c r="F10" s="276"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -5108,7 +5191,7 @@
         <v>115</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="262" t="s">
+      <c r="H13" s="280" t="s">
         <v>82</v>
       </c>
       <c r="I13" s="30"/>
@@ -5147,7 +5230,7 @@
       <c r="F14" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="262"/>
+      <c r="H14" s="280"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -5182,7 +5265,7 @@
         <v>83</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="262" t="s">
+      <c r="H15" s="280" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="30"/>
@@ -5219,7 +5302,7 @@
         <v>81</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="262"/>
+      <c r="H16" s="280"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -5251,7 +5334,7 @@
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="272" t="s">
+      <c r="H17" s="281" t="s">
         <v>45</v>
       </c>
       <c r="I17" s="30"/>
@@ -5286,7 +5369,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="273"/>
+      <c r="H18" s="282"/>
       <c r="I18" s="30"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
@@ -5303,7 +5386,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="259" t="s">
+      <c r="H19" s="279" t="s">
         <v>85</v>
       </c>
       <c r="I19" s="30"/>
@@ -5328,7 +5411,7 @@
       <c r="E20" s="137"/>
       <c r="F20" s="8"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="259"/>
+      <c r="H20" s="279"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -5347,7 +5430,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="259" t="s">
+      <c r="H21" s="279" t="s">
         <v>84</v>
       </c>
       <c r="I21" s="30"/>
@@ -5364,7 +5447,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="137"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="259"/>
+      <c r="H22" s="279"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -5461,13 +5544,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="263" t="s">
+      <c r="A28" s="285" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="263"/>
-      <c r="C28" s="263"/>
-      <c r="D28" s="263"/>
-      <c r="E28" s="263"/>
+      <c r="B28" s="285"/>
+      <c r="C28" s="285"/>
+      <c r="D28" s="285"/>
+      <c r="E28" s="285"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -5527,7 +5610,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="267" t="s">
+      <c r="E30" s="274" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -5561,7 +5644,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="267"/>
+      <c r="E31" s="274"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -5591,7 +5674,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="267" t="s">
+      <c r="E32" s="274" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="8"/>
@@ -5617,7 +5700,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="267"/>
+      <c r="E33" s="274"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
       <c r="I33" s="30"/>
@@ -5640,7 +5723,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="266" t="s">
+      <c r="E34" s="272" t="s">
         <v>133</v>
       </c>
       <c r="G34" s="8"/>
@@ -5661,7 +5744,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="266"/>
+      <c r="E35" s="272"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
       <c r="I35" s="30"/>
@@ -5680,7 +5763,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="267" t="s">
+      <c r="E36" s="274" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -5700,7 +5783,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="267"/>
+      <c r="E37" s="274"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -6167,7 +6250,7 @@
       <c r="S65"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A66" s="258" t="s">
+      <c r="A66" s="283" t="s">
         <v>139</v>
       </c>
       <c r="L66" s="119" t="s">
@@ -6179,7 +6262,7 @@
       <c r="S66"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A67" s="258"/>
+      <c r="A67" s="283"/>
       <c r="L67" s="119" t="s">
         <v>95</v>
       </c>
@@ -6231,6 +6314,14 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="J5:J6"/>
@@ -6246,14 +6337,6 @@
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="H17:H18"/>
     <mergeCell ref="H19:H20"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A28:E28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6261,7 +6344,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83BEC9BE-4127-4590-88B0-716BDF9EF620}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7170,21 +7253,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="284"/>
+      <c r="M1" s="284"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -7243,7 +7326,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="261" t="s">
+      <c r="F3" s="273" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -7252,24 +7335,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="268" t="s">
+      <c r="J3" s="275" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="285" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="270" t="s">
+      <c r="Q3" s="277" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="271"/>
+      <c r="R3" s="278"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="270" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="265"/>
+      <c r="U3" s="271"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -7287,16 +7370,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="261"/>
+      <c r="F4" s="273"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="268"/>
+      <c r="J4" s="275"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="285"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -7335,7 +7418,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="269" t="s">
+      <c r="F5" s="276" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -7343,7 +7426,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="261" t="s">
+      <c r="J5" s="273" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -7388,13 +7471,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="269"/>
+      <c r="F6" s="276"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="261"/>
+      <c r="J6" s="273"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -7441,7 +7524,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="269" t="s">
+      <c r="F7" s="276" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -7493,7 +7576,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="269"/>
+      <c r="F8" s="276"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -7709,7 +7792,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="259" t="s">
+      <c r="H13" s="279" t="s">
         <v>121</v>
       </c>
       <c r="I13" s="30"/>
@@ -7745,7 +7828,7 @@
       <c r="F14" s="240" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="259"/>
+      <c r="H14" s="279"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -7778,7 +7861,7 @@
       <c r="E15" s="240"/>
       <c r="F15" s="8"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="259" t="s">
+      <c r="H15" s="279" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="30"/>
@@ -7807,7 +7890,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="259" t="s">
+      <c r="B16" s="279" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="8"/>
@@ -7815,7 +7898,7 @@
       <c r="E16" s="59"/>
       <c r="F16" s="8"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="259"/>
+      <c r="H16" s="279"/>
       <c r="I16" s="30"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
@@ -7842,13 +7925,13 @@
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
-      <c r="B17" s="259"/>
+      <c r="B17" s="279"/>
       <c r="C17" s="8"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="262" t="s">
+      <c r="H17" s="280" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -7883,7 +7966,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="262"/>
+      <c r="H18" s="280"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -7900,7 +7983,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="262" t="s">
+      <c r="H19" s="280" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -7925,7 +8008,7 @@
       <c r="E20" s="240"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="262"/>
+      <c r="H20" s="280"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -7944,7 +8027,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="262" t="s">
+      <c r="H21" s="280" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -7962,7 +8045,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="240"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="262"/>
+      <c r="H22" s="280"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -8059,13 +8142,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="263" t="s">
+      <c r="A28" s="285" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="263"/>
-      <c r="C28" s="263"/>
-      <c r="D28" s="263"/>
-      <c r="E28" s="263"/>
+      <c r="B28" s="285"/>
+      <c r="C28" s="285"/>
+      <c r="D28" s="285"/>
+      <c r="E28" s="285"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -8125,7 +8208,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="267" t="s">
+      <c r="E30" s="274" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -8159,7 +8242,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="267"/>
+      <c r="E31" s="274"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -8186,7 +8269,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="267" t="s">
+      <c r="E32" s="274" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -8214,7 +8297,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="267"/>
+      <c r="E33" s="274"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -8238,7 +8321,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="266" t="s">
+      <c r="E34" s="272" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -8263,7 +8346,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="266"/>
+      <c r="E35" s="272"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -8285,7 +8368,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="267" t="s">
+      <c r="E36" s="274" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -8307,7 +8390,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="267"/>
+      <c r="E37" s="274"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -8839,6 +8922,18 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="H15:H16"/>
@@ -8847,18 +8942,6 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -8866,7 +8949,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7E415CA-04DB-4992-97B1-F5E37849C194}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -9775,21 +9858,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="284"/>
+      <c r="M1" s="284"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -9848,7 +9931,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="261" t="s">
+      <c r="F3" s="273" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -9857,24 +9940,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="268" t="s">
+      <c r="J3" s="275" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="262" t="s">
+      <c r="M3" s="280" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="270" t="s">
+      <c r="Q3" s="277" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="271"/>
+      <c r="R3" s="278"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="270" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="265"/>
+      <c r="U3" s="271"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -9892,16 +9975,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="261"/>
+      <c r="F4" s="273"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="268"/>
+      <c r="J4" s="275"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="262"/>
+      <c r="M4" s="280"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -9940,7 +10023,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="269" t="s">
+      <c r="F5" s="276" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -9948,7 +10031,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="261" t="s">
+      <c r="J5" s="273" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -9993,13 +10076,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="269"/>
+      <c r="F6" s="276"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="261"/>
+      <c r="J6" s="273"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -10046,7 +10129,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="269" t="s">
+      <c r="F7" s="276" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -10098,7 +10181,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="269"/>
+      <c r="F8" s="276"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -10314,7 +10397,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="259" t="s">
+      <c r="H13" s="279" t="s">
         <v>121</v>
       </c>
       <c r="I13" s="30"/>
@@ -10350,7 +10433,7 @@
       <c r="F14" s="248" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="259"/>
+      <c r="H14" s="279"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -10383,7 +10466,7 @@
       <c r="E15" s="248"/>
       <c r="F15" s="8"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="259" t="s">
+      <c r="H15" s="279" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="30"/>
@@ -10412,7 +10495,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="259" t="s">
+      <c r="B16" s="279" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="8"/>
@@ -10420,7 +10503,7 @@
       <c r="E16" s="59"/>
       <c r="F16" s="8"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="259"/>
+      <c r="H16" s="279"/>
       <c r="I16" s="30"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
@@ -10447,13 +10530,13 @@
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
-      <c r="B17" s="259"/>
+      <c r="B17" s="279"/>
       <c r="C17" s="8"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="262" t="s">
+      <c r="H17" s="280" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -10488,7 +10571,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="262"/>
+      <c r="H18" s="280"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -10505,7 +10588,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="262" t="s">
+      <c r="H19" s="280" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -10530,7 +10613,7 @@
       <c r="E20" s="248"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="262"/>
+      <c r="H20" s="280"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -10549,7 +10632,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="262" t="s">
+      <c r="H21" s="280" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -10567,7 +10650,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="248"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="262"/>
+      <c r="H22" s="280"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -10664,13 +10747,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="263" t="s">
+      <c r="A28" s="285" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="263"/>
-      <c r="C28" s="263"/>
-      <c r="D28" s="263"/>
-      <c r="E28" s="263"/>
+      <c r="B28" s="285"/>
+      <c r="C28" s="285"/>
+      <c r="D28" s="285"/>
+      <c r="E28" s="285"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -10730,7 +10813,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="267" t="s">
+      <c r="E30" s="274" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -10764,7 +10847,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="267"/>
+      <c r="E31" s="274"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -10794,7 +10877,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="267" t="s">
+      <c r="E32" s="274" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -10822,7 +10905,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="267"/>
+      <c r="E33" s="274"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -10846,7 +10929,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="266" t="s">
+      <c r="E34" s="272" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -10870,7 +10953,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="266"/>
+      <c r="E35" s="272"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -10892,7 +10975,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="267" t="s">
+      <c r="E36" s="274" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -10912,7 +10995,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="267"/>
+      <c r="E37" s="274"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -11444,6 +11527,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="B16:B17"/>
@@ -11457,13 +11547,6 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="H15:H16"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -11471,7 +11554,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B58EED56-DD65-43F7-989E-9E340DCA549D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -12380,21 +12463,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="284"/>
+      <c r="M1" s="284"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -12449,13 +12532,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="262" t="s">
+      <c r="D3" s="280" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="261" t="s">
+      <c r="F3" s="273" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -12464,29 +12547,29 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="268" t="s">
+      <c r="J3" s="275" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="262" t="s">
+      <c r="M3" s="280" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="270" t="s">
+      <c r="Q3" s="277" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="271"/>
+      <c r="R3" s="278"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="270" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="265"/>
+      <c r="U3" s="271"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
     <row r="4" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="289" t="s">
+      <c r="A4" s="260" t="s">
         <v>51</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -12495,20 +12578,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="262"/>
+      <c r="D4" s="280"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="261"/>
+      <c r="F4" s="273"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="268"/>
+      <c r="J4" s="275"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="262"/>
+      <c r="M4" s="280"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -12547,7 +12630,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="269" t="s">
+      <c r="F5" s="276" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -12555,7 +12638,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="261" t="s">
+      <c r="J5" s="273" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -12591,7 +12674,7 @@
     <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8"/>
       <c r="B6" s="45"/>
-      <c r="C6" s="289" t="s">
+      <c r="C6" s="260" t="s">
         <v>224</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -12600,13 +12683,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="269"/>
+      <c r="F6" s="276"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="261"/>
+      <c r="J6" s="273"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -12650,16 +12733,16 @@
         <v>12</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="289" t="s">
+      <c r="E7" s="260" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="287" t="s">
+      <c r="F7" s="298" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="262" t="s">
+      <c r="J7" s="280" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -12707,11 +12790,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="287"/>
+      <c r="F8" s="298"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="262"/>
+      <c r="J8" s="280"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -12756,7 +12839,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="259" t="s">
+      <c r="F9" s="279" t="s">
         <v>121</v>
       </c>
       <c r="G9" s="64"/>
@@ -12796,7 +12879,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="259"/>
+      <c r="F10" s="279"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -12833,7 +12916,7 @@
         <v>159</v>
       </c>
       <c r="E11" s="7"/>
-      <c r="F11" s="286" t="s">
+      <c r="F11" s="258" t="s">
         <v>48</v>
       </c>
       <c r="G11" s="64"/>
@@ -12952,7 +13035,7 @@
       <c r="B14" s="8"/>
       <c r="D14" s="61"/>
       <c r="E14" s="75"/>
-      <c r="F14" s="290" t="s">
+      <c r="F14" s="261" t="s">
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
@@ -13016,13 +13099,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="259" t="s">
+      <c r="A16" s="279" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="259" t="s">
+      <c r="B16" s="279" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="262" t="s">
+      <c r="C16" s="280" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -13057,12 +13140,12 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="259"/>
-      <c r="B17" s="259"/>
-      <c r="C17" s="262"/>
+      <c r="A17" s="279"/>
+      <c r="B17" s="279"/>
+      <c r="C17" s="280"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
-      <c r="F17" s="288" t="s">
+      <c r="F17" s="259" t="s">
         <v>83</v>
       </c>
       <c r="G17" s="6"/>
@@ -13270,13 +13353,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="263" t="s">
+      <c r="A28" s="285" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="263"/>
-      <c r="C28" s="263"/>
-      <c r="D28" s="263"/>
-      <c r="E28" s="263"/>
+      <c r="B28" s="285"/>
+      <c r="C28" s="285"/>
+      <c r="D28" s="285"/>
+      <c r="E28" s="285"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -13336,7 +13419,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="267" t="s">
+      <c r="E30" s="274" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -13370,7 +13453,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="267"/>
+      <c r="E31" s="274"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -13400,7 +13483,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="267" t="s">
+      <c r="E32" s="274" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -13430,7 +13513,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="267"/>
+      <c r="E33" s="274"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -13454,7 +13537,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="266" t="s">
+      <c r="E34" s="272" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -13478,7 +13561,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="266"/>
+      <c r="E35" s="272"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -13497,7 +13580,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="267" t="s">
+      <c r="E36" s="274" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -13517,7 +13600,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="267"/>
+      <c r="E37" s="274"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -14047,6 +14130,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="J7:J8"/>
@@ -14061,12 +14150,2612 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:W72"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" style="98" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" style="25" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" style="25" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" style="25" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" customWidth="1"/>
+    <col min="14" max="14" width="21.26953125" customWidth="1"/>
+    <col min="15" max="15" width="9.7265625" customWidth="1"/>
+    <col min="16" max="16" width="7.7265625" customWidth="1"/>
+    <col min="17" max="17" width="6.453125" customWidth="1"/>
+    <col min="18" max="18" width="7.81640625" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" style="84" customWidth="1"/>
+    <col min="20" max="20" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="257" max="260" width="14.453125" customWidth="1"/>
+    <col min="261" max="261" width="15.453125" customWidth="1"/>
+    <col min="262" max="262" width="14.54296875" customWidth="1"/>
+    <col min="263" max="263" width="15.26953125" customWidth="1"/>
+    <col min="264" max="265" width="14.453125" customWidth="1"/>
+    <col min="266" max="266" width="13.1796875" customWidth="1"/>
+    <col min="267" max="269" width="14.453125" customWidth="1"/>
+    <col min="270" max="270" width="15.81640625" customWidth="1"/>
+    <col min="271" max="271" width="7.81640625" customWidth="1"/>
+    <col min="272" max="272" width="5.453125" customWidth="1"/>
+    <col min="273" max="273" width="6.453125" customWidth="1"/>
+    <col min="274" max="274" width="7.81640625" customWidth="1"/>
+    <col min="275" max="275" width="3" customWidth="1"/>
+    <col min="276" max="276" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="513" max="516" width="14.453125" customWidth="1"/>
+    <col min="517" max="517" width="15.453125" customWidth="1"/>
+    <col min="518" max="518" width="14.54296875" customWidth="1"/>
+    <col min="519" max="519" width="15.26953125" customWidth="1"/>
+    <col min="520" max="521" width="14.453125" customWidth="1"/>
+    <col min="522" max="522" width="13.1796875" customWidth="1"/>
+    <col min="523" max="525" width="14.453125" customWidth="1"/>
+    <col min="526" max="526" width="15.81640625" customWidth="1"/>
+    <col min="527" max="527" width="7.81640625" customWidth="1"/>
+    <col min="528" max="528" width="5.453125" customWidth="1"/>
+    <col min="529" max="529" width="6.453125" customWidth="1"/>
+    <col min="530" max="530" width="7.81640625" customWidth="1"/>
+    <col min="531" max="531" width="3" customWidth="1"/>
+    <col min="532" max="532" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="769" max="772" width="14.453125" customWidth="1"/>
+    <col min="773" max="773" width="15.453125" customWidth="1"/>
+    <col min="774" max="774" width="14.54296875" customWidth="1"/>
+    <col min="775" max="775" width="15.26953125" customWidth="1"/>
+    <col min="776" max="777" width="14.453125" customWidth="1"/>
+    <col min="778" max="778" width="13.1796875" customWidth="1"/>
+    <col min="779" max="781" width="14.453125" customWidth="1"/>
+    <col min="782" max="782" width="15.81640625" customWidth="1"/>
+    <col min="783" max="783" width="7.81640625" customWidth="1"/>
+    <col min="784" max="784" width="5.453125" customWidth="1"/>
+    <col min="785" max="785" width="6.453125" customWidth="1"/>
+    <col min="786" max="786" width="7.81640625" customWidth="1"/>
+    <col min="787" max="787" width="3" customWidth="1"/>
+    <col min="788" max="788" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1025" max="1028" width="14.453125" customWidth="1"/>
+    <col min="1029" max="1029" width="15.453125" customWidth="1"/>
+    <col min="1030" max="1030" width="14.54296875" customWidth="1"/>
+    <col min="1031" max="1031" width="15.26953125" customWidth="1"/>
+    <col min="1032" max="1033" width="14.453125" customWidth="1"/>
+    <col min="1034" max="1034" width="13.1796875" customWidth="1"/>
+    <col min="1035" max="1037" width="14.453125" customWidth="1"/>
+    <col min="1038" max="1038" width="15.81640625" customWidth="1"/>
+    <col min="1039" max="1039" width="7.81640625" customWidth="1"/>
+    <col min="1040" max="1040" width="5.453125" customWidth="1"/>
+    <col min="1041" max="1041" width="6.453125" customWidth="1"/>
+    <col min="1042" max="1042" width="7.81640625" customWidth="1"/>
+    <col min="1043" max="1043" width="3" customWidth="1"/>
+    <col min="1044" max="1044" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1281" max="1284" width="14.453125" customWidth="1"/>
+    <col min="1285" max="1285" width="15.453125" customWidth="1"/>
+    <col min="1286" max="1286" width="14.54296875" customWidth="1"/>
+    <col min="1287" max="1287" width="15.26953125" customWidth="1"/>
+    <col min="1288" max="1289" width="14.453125" customWidth="1"/>
+    <col min="1290" max="1290" width="13.1796875" customWidth="1"/>
+    <col min="1291" max="1293" width="14.453125" customWidth="1"/>
+    <col min="1294" max="1294" width="15.81640625" customWidth="1"/>
+    <col min="1295" max="1295" width="7.81640625" customWidth="1"/>
+    <col min="1296" max="1296" width="5.453125" customWidth="1"/>
+    <col min="1297" max="1297" width="6.453125" customWidth="1"/>
+    <col min="1298" max="1298" width="7.81640625" customWidth="1"/>
+    <col min="1299" max="1299" width="3" customWidth="1"/>
+    <col min="1300" max="1300" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1537" max="1540" width="14.453125" customWidth="1"/>
+    <col min="1541" max="1541" width="15.453125" customWidth="1"/>
+    <col min="1542" max="1542" width="14.54296875" customWidth="1"/>
+    <col min="1543" max="1543" width="15.26953125" customWidth="1"/>
+    <col min="1544" max="1545" width="14.453125" customWidth="1"/>
+    <col min="1546" max="1546" width="13.1796875" customWidth="1"/>
+    <col min="1547" max="1549" width="14.453125" customWidth="1"/>
+    <col min="1550" max="1550" width="15.81640625" customWidth="1"/>
+    <col min="1551" max="1551" width="7.81640625" customWidth="1"/>
+    <col min="1552" max="1552" width="5.453125" customWidth="1"/>
+    <col min="1553" max="1553" width="6.453125" customWidth="1"/>
+    <col min="1554" max="1554" width="7.81640625" customWidth="1"/>
+    <col min="1555" max="1555" width="3" customWidth="1"/>
+    <col min="1556" max="1556" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1793" max="1796" width="14.453125" customWidth="1"/>
+    <col min="1797" max="1797" width="15.453125" customWidth="1"/>
+    <col min="1798" max="1798" width="14.54296875" customWidth="1"/>
+    <col min="1799" max="1799" width="15.26953125" customWidth="1"/>
+    <col min="1800" max="1801" width="14.453125" customWidth="1"/>
+    <col min="1802" max="1802" width="13.1796875" customWidth="1"/>
+    <col min="1803" max="1805" width="14.453125" customWidth="1"/>
+    <col min="1806" max="1806" width="15.81640625" customWidth="1"/>
+    <col min="1807" max="1807" width="7.81640625" customWidth="1"/>
+    <col min="1808" max="1808" width="5.453125" customWidth="1"/>
+    <col min="1809" max="1809" width="6.453125" customWidth="1"/>
+    <col min="1810" max="1810" width="7.81640625" customWidth="1"/>
+    <col min="1811" max="1811" width="3" customWidth="1"/>
+    <col min="1812" max="1812" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2049" max="2052" width="14.453125" customWidth="1"/>
+    <col min="2053" max="2053" width="15.453125" customWidth="1"/>
+    <col min="2054" max="2054" width="14.54296875" customWidth="1"/>
+    <col min="2055" max="2055" width="15.26953125" customWidth="1"/>
+    <col min="2056" max="2057" width="14.453125" customWidth="1"/>
+    <col min="2058" max="2058" width="13.1796875" customWidth="1"/>
+    <col min="2059" max="2061" width="14.453125" customWidth="1"/>
+    <col min="2062" max="2062" width="15.81640625" customWidth="1"/>
+    <col min="2063" max="2063" width="7.81640625" customWidth="1"/>
+    <col min="2064" max="2064" width="5.453125" customWidth="1"/>
+    <col min="2065" max="2065" width="6.453125" customWidth="1"/>
+    <col min="2066" max="2066" width="7.81640625" customWidth="1"/>
+    <col min="2067" max="2067" width="3" customWidth="1"/>
+    <col min="2068" max="2068" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2305" max="2308" width="14.453125" customWidth="1"/>
+    <col min="2309" max="2309" width="15.453125" customWidth="1"/>
+    <col min="2310" max="2310" width="14.54296875" customWidth="1"/>
+    <col min="2311" max="2311" width="15.26953125" customWidth="1"/>
+    <col min="2312" max="2313" width="14.453125" customWidth="1"/>
+    <col min="2314" max="2314" width="13.1796875" customWidth="1"/>
+    <col min="2315" max="2317" width="14.453125" customWidth="1"/>
+    <col min="2318" max="2318" width="15.81640625" customWidth="1"/>
+    <col min="2319" max="2319" width="7.81640625" customWidth="1"/>
+    <col min="2320" max="2320" width="5.453125" customWidth="1"/>
+    <col min="2321" max="2321" width="6.453125" customWidth="1"/>
+    <col min="2322" max="2322" width="7.81640625" customWidth="1"/>
+    <col min="2323" max="2323" width="3" customWidth="1"/>
+    <col min="2324" max="2324" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2561" max="2564" width="14.453125" customWidth="1"/>
+    <col min="2565" max="2565" width="15.453125" customWidth="1"/>
+    <col min="2566" max="2566" width="14.54296875" customWidth="1"/>
+    <col min="2567" max="2567" width="15.26953125" customWidth="1"/>
+    <col min="2568" max="2569" width="14.453125" customWidth="1"/>
+    <col min="2570" max="2570" width="13.1796875" customWidth="1"/>
+    <col min="2571" max="2573" width="14.453125" customWidth="1"/>
+    <col min="2574" max="2574" width="15.81640625" customWidth="1"/>
+    <col min="2575" max="2575" width="7.81640625" customWidth="1"/>
+    <col min="2576" max="2576" width="5.453125" customWidth="1"/>
+    <col min="2577" max="2577" width="6.453125" customWidth="1"/>
+    <col min="2578" max="2578" width="7.81640625" customWidth="1"/>
+    <col min="2579" max="2579" width="3" customWidth="1"/>
+    <col min="2580" max="2580" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2817" max="2820" width="14.453125" customWidth="1"/>
+    <col min="2821" max="2821" width="15.453125" customWidth="1"/>
+    <col min="2822" max="2822" width="14.54296875" customWidth="1"/>
+    <col min="2823" max="2823" width="15.26953125" customWidth="1"/>
+    <col min="2824" max="2825" width="14.453125" customWidth="1"/>
+    <col min="2826" max="2826" width="13.1796875" customWidth="1"/>
+    <col min="2827" max="2829" width="14.453125" customWidth="1"/>
+    <col min="2830" max="2830" width="15.81640625" customWidth="1"/>
+    <col min="2831" max="2831" width="7.81640625" customWidth="1"/>
+    <col min="2832" max="2832" width="5.453125" customWidth="1"/>
+    <col min="2833" max="2833" width="6.453125" customWidth="1"/>
+    <col min="2834" max="2834" width="7.81640625" customWidth="1"/>
+    <col min="2835" max="2835" width="3" customWidth="1"/>
+    <col min="2836" max="2836" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3073" max="3076" width="14.453125" customWidth="1"/>
+    <col min="3077" max="3077" width="15.453125" customWidth="1"/>
+    <col min="3078" max="3078" width="14.54296875" customWidth="1"/>
+    <col min="3079" max="3079" width="15.26953125" customWidth="1"/>
+    <col min="3080" max="3081" width="14.453125" customWidth="1"/>
+    <col min="3082" max="3082" width="13.1796875" customWidth="1"/>
+    <col min="3083" max="3085" width="14.453125" customWidth="1"/>
+    <col min="3086" max="3086" width="15.81640625" customWidth="1"/>
+    <col min="3087" max="3087" width="7.81640625" customWidth="1"/>
+    <col min="3088" max="3088" width="5.453125" customWidth="1"/>
+    <col min="3089" max="3089" width="6.453125" customWidth="1"/>
+    <col min="3090" max="3090" width="7.81640625" customWidth="1"/>
+    <col min="3091" max="3091" width="3" customWidth="1"/>
+    <col min="3092" max="3092" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3329" max="3332" width="14.453125" customWidth="1"/>
+    <col min="3333" max="3333" width="15.453125" customWidth="1"/>
+    <col min="3334" max="3334" width="14.54296875" customWidth="1"/>
+    <col min="3335" max="3335" width="15.26953125" customWidth="1"/>
+    <col min="3336" max="3337" width="14.453125" customWidth="1"/>
+    <col min="3338" max="3338" width="13.1796875" customWidth="1"/>
+    <col min="3339" max="3341" width="14.453125" customWidth="1"/>
+    <col min="3342" max="3342" width="15.81640625" customWidth="1"/>
+    <col min="3343" max="3343" width="7.81640625" customWidth="1"/>
+    <col min="3344" max="3344" width="5.453125" customWidth="1"/>
+    <col min="3345" max="3345" width="6.453125" customWidth="1"/>
+    <col min="3346" max="3346" width="7.81640625" customWidth="1"/>
+    <col min="3347" max="3347" width="3" customWidth="1"/>
+    <col min="3348" max="3348" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3585" max="3588" width="14.453125" customWidth="1"/>
+    <col min="3589" max="3589" width="15.453125" customWidth="1"/>
+    <col min="3590" max="3590" width="14.54296875" customWidth="1"/>
+    <col min="3591" max="3591" width="15.26953125" customWidth="1"/>
+    <col min="3592" max="3593" width="14.453125" customWidth="1"/>
+    <col min="3594" max="3594" width="13.1796875" customWidth="1"/>
+    <col min="3595" max="3597" width="14.453125" customWidth="1"/>
+    <col min="3598" max="3598" width="15.81640625" customWidth="1"/>
+    <col min="3599" max="3599" width="7.81640625" customWidth="1"/>
+    <col min="3600" max="3600" width="5.453125" customWidth="1"/>
+    <col min="3601" max="3601" width="6.453125" customWidth="1"/>
+    <col min="3602" max="3602" width="7.81640625" customWidth="1"/>
+    <col min="3603" max="3603" width="3" customWidth="1"/>
+    <col min="3604" max="3604" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3841" max="3844" width="14.453125" customWidth="1"/>
+    <col min="3845" max="3845" width="15.453125" customWidth="1"/>
+    <col min="3846" max="3846" width="14.54296875" customWidth="1"/>
+    <col min="3847" max="3847" width="15.26953125" customWidth="1"/>
+    <col min="3848" max="3849" width="14.453125" customWidth="1"/>
+    <col min="3850" max="3850" width="13.1796875" customWidth="1"/>
+    <col min="3851" max="3853" width="14.453125" customWidth="1"/>
+    <col min="3854" max="3854" width="15.81640625" customWidth="1"/>
+    <col min="3855" max="3855" width="7.81640625" customWidth="1"/>
+    <col min="3856" max="3856" width="5.453125" customWidth="1"/>
+    <col min="3857" max="3857" width="6.453125" customWidth="1"/>
+    <col min="3858" max="3858" width="7.81640625" customWidth="1"/>
+    <col min="3859" max="3859" width="3" customWidth="1"/>
+    <col min="3860" max="3860" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4097" max="4100" width="14.453125" customWidth="1"/>
+    <col min="4101" max="4101" width="15.453125" customWidth="1"/>
+    <col min="4102" max="4102" width="14.54296875" customWidth="1"/>
+    <col min="4103" max="4103" width="15.26953125" customWidth="1"/>
+    <col min="4104" max="4105" width="14.453125" customWidth="1"/>
+    <col min="4106" max="4106" width="13.1796875" customWidth="1"/>
+    <col min="4107" max="4109" width="14.453125" customWidth="1"/>
+    <col min="4110" max="4110" width="15.81640625" customWidth="1"/>
+    <col min="4111" max="4111" width="7.81640625" customWidth="1"/>
+    <col min="4112" max="4112" width="5.453125" customWidth="1"/>
+    <col min="4113" max="4113" width="6.453125" customWidth="1"/>
+    <col min="4114" max="4114" width="7.81640625" customWidth="1"/>
+    <col min="4115" max="4115" width="3" customWidth="1"/>
+    <col min="4116" max="4116" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4353" max="4356" width="14.453125" customWidth="1"/>
+    <col min="4357" max="4357" width="15.453125" customWidth="1"/>
+    <col min="4358" max="4358" width="14.54296875" customWidth="1"/>
+    <col min="4359" max="4359" width="15.26953125" customWidth="1"/>
+    <col min="4360" max="4361" width="14.453125" customWidth="1"/>
+    <col min="4362" max="4362" width="13.1796875" customWidth="1"/>
+    <col min="4363" max="4365" width="14.453125" customWidth="1"/>
+    <col min="4366" max="4366" width="15.81640625" customWidth="1"/>
+    <col min="4367" max="4367" width="7.81640625" customWidth="1"/>
+    <col min="4368" max="4368" width="5.453125" customWidth="1"/>
+    <col min="4369" max="4369" width="6.453125" customWidth="1"/>
+    <col min="4370" max="4370" width="7.81640625" customWidth="1"/>
+    <col min="4371" max="4371" width="3" customWidth="1"/>
+    <col min="4372" max="4372" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4609" max="4612" width="14.453125" customWidth="1"/>
+    <col min="4613" max="4613" width="15.453125" customWidth="1"/>
+    <col min="4614" max="4614" width="14.54296875" customWidth="1"/>
+    <col min="4615" max="4615" width="15.26953125" customWidth="1"/>
+    <col min="4616" max="4617" width="14.453125" customWidth="1"/>
+    <col min="4618" max="4618" width="13.1796875" customWidth="1"/>
+    <col min="4619" max="4621" width="14.453125" customWidth="1"/>
+    <col min="4622" max="4622" width="15.81640625" customWidth="1"/>
+    <col min="4623" max="4623" width="7.81640625" customWidth="1"/>
+    <col min="4624" max="4624" width="5.453125" customWidth="1"/>
+    <col min="4625" max="4625" width="6.453125" customWidth="1"/>
+    <col min="4626" max="4626" width="7.81640625" customWidth="1"/>
+    <col min="4627" max="4627" width="3" customWidth="1"/>
+    <col min="4628" max="4628" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4865" max="4868" width="14.453125" customWidth="1"/>
+    <col min="4869" max="4869" width="15.453125" customWidth="1"/>
+    <col min="4870" max="4870" width="14.54296875" customWidth="1"/>
+    <col min="4871" max="4871" width="15.26953125" customWidth="1"/>
+    <col min="4872" max="4873" width="14.453125" customWidth="1"/>
+    <col min="4874" max="4874" width="13.1796875" customWidth="1"/>
+    <col min="4875" max="4877" width="14.453125" customWidth="1"/>
+    <col min="4878" max="4878" width="15.81640625" customWidth="1"/>
+    <col min="4879" max="4879" width="7.81640625" customWidth="1"/>
+    <col min="4880" max="4880" width="5.453125" customWidth="1"/>
+    <col min="4881" max="4881" width="6.453125" customWidth="1"/>
+    <col min="4882" max="4882" width="7.81640625" customWidth="1"/>
+    <col min="4883" max="4883" width="3" customWidth="1"/>
+    <col min="4884" max="4884" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5121" max="5124" width="14.453125" customWidth="1"/>
+    <col min="5125" max="5125" width="15.453125" customWidth="1"/>
+    <col min="5126" max="5126" width="14.54296875" customWidth="1"/>
+    <col min="5127" max="5127" width="15.26953125" customWidth="1"/>
+    <col min="5128" max="5129" width="14.453125" customWidth="1"/>
+    <col min="5130" max="5130" width="13.1796875" customWidth="1"/>
+    <col min="5131" max="5133" width="14.453125" customWidth="1"/>
+    <col min="5134" max="5134" width="15.81640625" customWidth="1"/>
+    <col min="5135" max="5135" width="7.81640625" customWidth="1"/>
+    <col min="5136" max="5136" width="5.453125" customWidth="1"/>
+    <col min="5137" max="5137" width="6.453125" customWidth="1"/>
+    <col min="5138" max="5138" width="7.81640625" customWidth="1"/>
+    <col min="5139" max="5139" width="3" customWidth="1"/>
+    <col min="5140" max="5140" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5377" max="5380" width="14.453125" customWidth="1"/>
+    <col min="5381" max="5381" width="15.453125" customWidth="1"/>
+    <col min="5382" max="5382" width="14.54296875" customWidth="1"/>
+    <col min="5383" max="5383" width="15.26953125" customWidth="1"/>
+    <col min="5384" max="5385" width="14.453125" customWidth="1"/>
+    <col min="5386" max="5386" width="13.1796875" customWidth="1"/>
+    <col min="5387" max="5389" width="14.453125" customWidth="1"/>
+    <col min="5390" max="5390" width="15.81640625" customWidth="1"/>
+    <col min="5391" max="5391" width="7.81640625" customWidth="1"/>
+    <col min="5392" max="5392" width="5.453125" customWidth="1"/>
+    <col min="5393" max="5393" width="6.453125" customWidth="1"/>
+    <col min="5394" max="5394" width="7.81640625" customWidth="1"/>
+    <col min="5395" max="5395" width="3" customWidth="1"/>
+    <col min="5396" max="5396" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5633" max="5636" width="14.453125" customWidth="1"/>
+    <col min="5637" max="5637" width="15.453125" customWidth="1"/>
+    <col min="5638" max="5638" width="14.54296875" customWidth="1"/>
+    <col min="5639" max="5639" width="15.26953125" customWidth="1"/>
+    <col min="5640" max="5641" width="14.453125" customWidth="1"/>
+    <col min="5642" max="5642" width="13.1796875" customWidth="1"/>
+    <col min="5643" max="5645" width="14.453125" customWidth="1"/>
+    <col min="5646" max="5646" width="15.81640625" customWidth="1"/>
+    <col min="5647" max="5647" width="7.81640625" customWidth="1"/>
+    <col min="5648" max="5648" width="5.453125" customWidth="1"/>
+    <col min="5649" max="5649" width="6.453125" customWidth="1"/>
+    <col min="5650" max="5650" width="7.81640625" customWidth="1"/>
+    <col min="5651" max="5651" width="3" customWidth="1"/>
+    <col min="5652" max="5652" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5889" max="5892" width="14.453125" customWidth="1"/>
+    <col min="5893" max="5893" width="15.453125" customWidth="1"/>
+    <col min="5894" max="5894" width="14.54296875" customWidth="1"/>
+    <col min="5895" max="5895" width="15.26953125" customWidth="1"/>
+    <col min="5896" max="5897" width="14.453125" customWidth="1"/>
+    <col min="5898" max="5898" width="13.1796875" customWidth="1"/>
+    <col min="5899" max="5901" width="14.453125" customWidth="1"/>
+    <col min="5902" max="5902" width="15.81640625" customWidth="1"/>
+    <col min="5903" max="5903" width="7.81640625" customWidth="1"/>
+    <col min="5904" max="5904" width="5.453125" customWidth="1"/>
+    <col min="5905" max="5905" width="6.453125" customWidth="1"/>
+    <col min="5906" max="5906" width="7.81640625" customWidth="1"/>
+    <col min="5907" max="5907" width="3" customWidth="1"/>
+    <col min="5908" max="5908" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6145" max="6148" width="14.453125" customWidth="1"/>
+    <col min="6149" max="6149" width="15.453125" customWidth="1"/>
+    <col min="6150" max="6150" width="14.54296875" customWidth="1"/>
+    <col min="6151" max="6151" width="15.26953125" customWidth="1"/>
+    <col min="6152" max="6153" width="14.453125" customWidth="1"/>
+    <col min="6154" max="6154" width="13.1796875" customWidth="1"/>
+    <col min="6155" max="6157" width="14.453125" customWidth="1"/>
+    <col min="6158" max="6158" width="15.81640625" customWidth="1"/>
+    <col min="6159" max="6159" width="7.81640625" customWidth="1"/>
+    <col min="6160" max="6160" width="5.453125" customWidth="1"/>
+    <col min="6161" max="6161" width="6.453125" customWidth="1"/>
+    <col min="6162" max="6162" width="7.81640625" customWidth="1"/>
+    <col min="6163" max="6163" width="3" customWidth="1"/>
+    <col min="6164" max="6164" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6401" max="6404" width="14.453125" customWidth="1"/>
+    <col min="6405" max="6405" width="15.453125" customWidth="1"/>
+    <col min="6406" max="6406" width="14.54296875" customWidth="1"/>
+    <col min="6407" max="6407" width="15.26953125" customWidth="1"/>
+    <col min="6408" max="6409" width="14.453125" customWidth="1"/>
+    <col min="6410" max="6410" width="13.1796875" customWidth="1"/>
+    <col min="6411" max="6413" width="14.453125" customWidth="1"/>
+    <col min="6414" max="6414" width="15.81640625" customWidth="1"/>
+    <col min="6415" max="6415" width="7.81640625" customWidth="1"/>
+    <col min="6416" max="6416" width="5.453125" customWidth="1"/>
+    <col min="6417" max="6417" width="6.453125" customWidth="1"/>
+    <col min="6418" max="6418" width="7.81640625" customWidth="1"/>
+    <col min="6419" max="6419" width="3" customWidth="1"/>
+    <col min="6420" max="6420" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6657" max="6660" width="14.453125" customWidth="1"/>
+    <col min="6661" max="6661" width="15.453125" customWidth="1"/>
+    <col min="6662" max="6662" width="14.54296875" customWidth="1"/>
+    <col min="6663" max="6663" width="15.26953125" customWidth="1"/>
+    <col min="6664" max="6665" width="14.453125" customWidth="1"/>
+    <col min="6666" max="6666" width="13.1796875" customWidth="1"/>
+    <col min="6667" max="6669" width="14.453125" customWidth="1"/>
+    <col min="6670" max="6670" width="15.81640625" customWidth="1"/>
+    <col min="6671" max="6671" width="7.81640625" customWidth="1"/>
+    <col min="6672" max="6672" width="5.453125" customWidth="1"/>
+    <col min="6673" max="6673" width="6.453125" customWidth="1"/>
+    <col min="6674" max="6674" width="7.81640625" customWidth="1"/>
+    <col min="6675" max="6675" width="3" customWidth="1"/>
+    <col min="6676" max="6676" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6913" max="6916" width="14.453125" customWidth="1"/>
+    <col min="6917" max="6917" width="15.453125" customWidth="1"/>
+    <col min="6918" max="6918" width="14.54296875" customWidth="1"/>
+    <col min="6919" max="6919" width="15.26953125" customWidth="1"/>
+    <col min="6920" max="6921" width="14.453125" customWidth="1"/>
+    <col min="6922" max="6922" width="13.1796875" customWidth="1"/>
+    <col min="6923" max="6925" width="14.453125" customWidth="1"/>
+    <col min="6926" max="6926" width="15.81640625" customWidth="1"/>
+    <col min="6927" max="6927" width="7.81640625" customWidth="1"/>
+    <col min="6928" max="6928" width="5.453125" customWidth="1"/>
+    <col min="6929" max="6929" width="6.453125" customWidth="1"/>
+    <col min="6930" max="6930" width="7.81640625" customWidth="1"/>
+    <col min="6931" max="6931" width="3" customWidth="1"/>
+    <col min="6932" max="6932" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7169" max="7172" width="14.453125" customWidth="1"/>
+    <col min="7173" max="7173" width="15.453125" customWidth="1"/>
+    <col min="7174" max="7174" width="14.54296875" customWidth="1"/>
+    <col min="7175" max="7175" width="15.26953125" customWidth="1"/>
+    <col min="7176" max="7177" width="14.453125" customWidth="1"/>
+    <col min="7178" max="7178" width="13.1796875" customWidth="1"/>
+    <col min="7179" max="7181" width="14.453125" customWidth="1"/>
+    <col min="7182" max="7182" width="15.81640625" customWidth="1"/>
+    <col min="7183" max="7183" width="7.81640625" customWidth="1"/>
+    <col min="7184" max="7184" width="5.453125" customWidth="1"/>
+    <col min="7185" max="7185" width="6.453125" customWidth="1"/>
+    <col min="7186" max="7186" width="7.81640625" customWidth="1"/>
+    <col min="7187" max="7187" width="3" customWidth="1"/>
+    <col min="7188" max="7188" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7425" max="7428" width="14.453125" customWidth="1"/>
+    <col min="7429" max="7429" width="15.453125" customWidth="1"/>
+    <col min="7430" max="7430" width="14.54296875" customWidth="1"/>
+    <col min="7431" max="7431" width="15.26953125" customWidth="1"/>
+    <col min="7432" max="7433" width="14.453125" customWidth="1"/>
+    <col min="7434" max="7434" width="13.1796875" customWidth="1"/>
+    <col min="7435" max="7437" width="14.453125" customWidth="1"/>
+    <col min="7438" max="7438" width="15.81640625" customWidth="1"/>
+    <col min="7439" max="7439" width="7.81640625" customWidth="1"/>
+    <col min="7440" max="7440" width="5.453125" customWidth="1"/>
+    <col min="7441" max="7441" width="6.453125" customWidth="1"/>
+    <col min="7442" max="7442" width="7.81640625" customWidth="1"/>
+    <col min="7443" max="7443" width="3" customWidth="1"/>
+    <col min="7444" max="7444" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7681" max="7684" width="14.453125" customWidth="1"/>
+    <col min="7685" max="7685" width="15.453125" customWidth="1"/>
+    <col min="7686" max="7686" width="14.54296875" customWidth="1"/>
+    <col min="7687" max="7687" width="15.26953125" customWidth="1"/>
+    <col min="7688" max="7689" width="14.453125" customWidth="1"/>
+    <col min="7690" max="7690" width="13.1796875" customWidth="1"/>
+    <col min="7691" max="7693" width="14.453125" customWidth="1"/>
+    <col min="7694" max="7694" width="15.81640625" customWidth="1"/>
+    <col min="7695" max="7695" width="7.81640625" customWidth="1"/>
+    <col min="7696" max="7696" width="5.453125" customWidth="1"/>
+    <col min="7697" max="7697" width="6.453125" customWidth="1"/>
+    <col min="7698" max="7698" width="7.81640625" customWidth="1"/>
+    <col min="7699" max="7699" width="3" customWidth="1"/>
+    <col min="7700" max="7700" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7937" max="7940" width="14.453125" customWidth="1"/>
+    <col min="7941" max="7941" width="15.453125" customWidth="1"/>
+    <col min="7942" max="7942" width="14.54296875" customWidth="1"/>
+    <col min="7943" max="7943" width="15.26953125" customWidth="1"/>
+    <col min="7944" max="7945" width="14.453125" customWidth="1"/>
+    <col min="7946" max="7946" width="13.1796875" customWidth="1"/>
+    <col min="7947" max="7949" width="14.453125" customWidth="1"/>
+    <col min="7950" max="7950" width="15.81640625" customWidth="1"/>
+    <col min="7951" max="7951" width="7.81640625" customWidth="1"/>
+    <col min="7952" max="7952" width="5.453125" customWidth="1"/>
+    <col min="7953" max="7953" width="6.453125" customWidth="1"/>
+    <col min="7954" max="7954" width="7.81640625" customWidth="1"/>
+    <col min="7955" max="7955" width="3" customWidth="1"/>
+    <col min="7956" max="7956" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8193" max="8196" width="14.453125" customWidth="1"/>
+    <col min="8197" max="8197" width="15.453125" customWidth="1"/>
+    <col min="8198" max="8198" width="14.54296875" customWidth="1"/>
+    <col min="8199" max="8199" width="15.26953125" customWidth="1"/>
+    <col min="8200" max="8201" width="14.453125" customWidth="1"/>
+    <col min="8202" max="8202" width="13.1796875" customWidth="1"/>
+    <col min="8203" max="8205" width="14.453125" customWidth="1"/>
+    <col min="8206" max="8206" width="15.81640625" customWidth="1"/>
+    <col min="8207" max="8207" width="7.81640625" customWidth="1"/>
+    <col min="8208" max="8208" width="5.453125" customWidth="1"/>
+    <col min="8209" max="8209" width="6.453125" customWidth="1"/>
+    <col min="8210" max="8210" width="7.81640625" customWidth="1"/>
+    <col min="8211" max="8211" width="3" customWidth="1"/>
+    <col min="8212" max="8212" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8449" max="8452" width="14.453125" customWidth="1"/>
+    <col min="8453" max="8453" width="15.453125" customWidth="1"/>
+    <col min="8454" max="8454" width="14.54296875" customWidth="1"/>
+    <col min="8455" max="8455" width="15.26953125" customWidth="1"/>
+    <col min="8456" max="8457" width="14.453125" customWidth="1"/>
+    <col min="8458" max="8458" width="13.1796875" customWidth="1"/>
+    <col min="8459" max="8461" width="14.453125" customWidth="1"/>
+    <col min="8462" max="8462" width="15.81640625" customWidth="1"/>
+    <col min="8463" max="8463" width="7.81640625" customWidth="1"/>
+    <col min="8464" max="8464" width="5.453125" customWidth="1"/>
+    <col min="8465" max="8465" width="6.453125" customWidth="1"/>
+    <col min="8466" max="8466" width="7.81640625" customWidth="1"/>
+    <col min="8467" max="8467" width="3" customWidth="1"/>
+    <col min="8468" max="8468" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8705" max="8708" width="14.453125" customWidth="1"/>
+    <col min="8709" max="8709" width="15.453125" customWidth="1"/>
+    <col min="8710" max="8710" width="14.54296875" customWidth="1"/>
+    <col min="8711" max="8711" width="15.26953125" customWidth="1"/>
+    <col min="8712" max="8713" width="14.453125" customWidth="1"/>
+    <col min="8714" max="8714" width="13.1796875" customWidth="1"/>
+    <col min="8715" max="8717" width="14.453125" customWidth="1"/>
+    <col min="8718" max="8718" width="15.81640625" customWidth="1"/>
+    <col min="8719" max="8719" width="7.81640625" customWidth="1"/>
+    <col min="8720" max="8720" width="5.453125" customWidth="1"/>
+    <col min="8721" max="8721" width="6.453125" customWidth="1"/>
+    <col min="8722" max="8722" width="7.81640625" customWidth="1"/>
+    <col min="8723" max="8723" width="3" customWidth="1"/>
+    <col min="8724" max="8724" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8961" max="8964" width="14.453125" customWidth="1"/>
+    <col min="8965" max="8965" width="15.453125" customWidth="1"/>
+    <col min="8966" max="8966" width="14.54296875" customWidth="1"/>
+    <col min="8967" max="8967" width="15.26953125" customWidth="1"/>
+    <col min="8968" max="8969" width="14.453125" customWidth="1"/>
+    <col min="8970" max="8970" width="13.1796875" customWidth="1"/>
+    <col min="8971" max="8973" width="14.453125" customWidth="1"/>
+    <col min="8974" max="8974" width="15.81640625" customWidth="1"/>
+    <col min="8975" max="8975" width="7.81640625" customWidth="1"/>
+    <col min="8976" max="8976" width="5.453125" customWidth="1"/>
+    <col min="8977" max="8977" width="6.453125" customWidth="1"/>
+    <col min="8978" max="8978" width="7.81640625" customWidth="1"/>
+    <col min="8979" max="8979" width="3" customWidth="1"/>
+    <col min="8980" max="8980" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9217" max="9220" width="14.453125" customWidth="1"/>
+    <col min="9221" max="9221" width="15.453125" customWidth="1"/>
+    <col min="9222" max="9222" width="14.54296875" customWidth="1"/>
+    <col min="9223" max="9223" width="15.26953125" customWidth="1"/>
+    <col min="9224" max="9225" width="14.453125" customWidth="1"/>
+    <col min="9226" max="9226" width="13.1796875" customWidth="1"/>
+    <col min="9227" max="9229" width="14.453125" customWidth="1"/>
+    <col min="9230" max="9230" width="15.81640625" customWidth="1"/>
+    <col min="9231" max="9231" width="7.81640625" customWidth="1"/>
+    <col min="9232" max="9232" width="5.453125" customWidth="1"/>
+    <col min="9233" max="9233" width="6.453125" customWidth="1"/>
+    <col min="9234" max="9234" width="7.81640625" customWidth="1"/>
+    <col min="9235" max="9235" width="3" customWidth="1"/>
+    <col min="9236" max="9236" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9473" max="9476" width="14.453125" customWidth="1"/>
+    <col min="9477" max="9477" width="15.453125" customWidth="1"/>
+    <col min="9478" max="9478" width="14.54296875" customWidth="1"/>
+    <col min="9479" max="9479" width="15.26953125" customWidth="1"/>
+    <col min="9480" max="9481" width="14.453125" customWidth="1"/>
+    <col min="9482" max="9482" width="13.1796875" customWidth="1"/>
+    <col min="9483" max="9485" width="14.453125" customWidth="1"/>
+    <col min="9486" max="9486" width="15.81640625" customWidth="1"/>
+    <col min="9487" max="9487" width="7.81640625" customWidth="1"/>
+    <col min="9488" max="9488" width="5.453125" customWidth="1"/>
+    <col min="9489" max="9489" width="6.453125" customWidth="1"/>
+    <col min="9490" max="9490" width="7.81640625" customWidth="1"/>
+    <col min="9491" max="9491" width="3" customWidth="1"/>
+    <col min="9492" max="9492" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9729" max="9732" width="14.453125" customWidth="1"/>
+    <col min="9733" max="9733" width="15.453125" customWidth="1"/>
+    <col min="9734" max="9734" width="14.54296875" customWidth="1"/>
+    <col min="9735" max="9735" width="15.26953125" customWidth="1"/>
+    <col min="9736" max="9737" width="14.453125" customWidth="1"/>
+    <col min="9738" max="9738" width="13.1796875" customWidth="1"/>
+    <col min="9739" max="9741" width="14.453125" customWidth="1"/>
+    <col min="9742" max="9742" width="15.81640625" customWidth="1"/>
+    <col min="9743" max="9743" width="7.81640625" customWidth="1"/>
+    <col min="9744" max="9744" width="5.453125" customWidth="1"/>
+    <col min="9745" max="9745" width="6.453125" customWidth="1"/>
+    <col min="9746" max="9746" width="7.81640625" customWidth="1"/>
+    <col min="9747" max="9747" width="3" customWidth="1"/>
+    <col min="9748" max="9748" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9985" max="9988" width="14.453125" customWidth="1"/>
+    <col min="9989" max="9989" width="15.453125" customWidth="1"/>
+    <col min="9990" max="9990" width="14.54296875" customWidth="1"/>
+    <col min="9991" max="9991" width="15.26953125" customWidth="1"/>
+    <col min="9992" max="9993" width="14.453125" customWidth="1"/>
+    <col min="9994" max="9994" width="13.1796875" customWidth="1"/>
+    <col min="9995" max="9997" width="14.453125" customWidth="1"/>
+    <col min="9998" max="9998" width="15.81640625" customWidth="1"/>
+    <col min="9999" max="9999" width="7.81640625" customWidth="1"/>
+    <col min="10000" max="10000" width="5.453125" customWidth="1"/>
+    <col min="10001" max="10001" width="6.453125" customWidth="1"/>
+    <col min="10002" max="10002" width="7.81640625" customWidth="1"/>
+    <col min="10003" max="10003" width="3" customWidth="1"/>
+    <col min="10004" max="10004" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10241" max="10244" width="14.453125" customWidth="1"/>
+    <col min="10245" max="10245" width="15.453125" customWidth="1"/>
+    <col min="10246" max="10246" width="14.54296875" customWidth="1"/>
+    <col min="10247" max="10247" width="15.26953125" customWidth="1"/>
+    <col min="10248" max="10249" width="14.453125" customWidth="1"/>
+    <col min="10250" max="10250" width="13.1796875" customWidth="1"/>
+    <col min="10251" max="10253" width="14.453125" customWidth="1"/>
+    <col min="10254" max="10254" width="15.81640625" customWidth="1"/>
+    <col min="10255" max="10255" width="7.81640625" customWidth="1"/>
+    <col min="10256" max="10256" width="5.453125" customWidth="1"/>
+    <col min="10257" max="10257" width="6.453125" customWidth="1"/>
+    <col min="10258" max="10258" width="7.81640625" customWidth="1"/>
+    <col min="10259" max="10259" width="3" customWidth="1"/>
+    <col min="10260" max="10260" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10497" max="10500" width="14.453125" customWidth="1"/>
+    <col min="10501" max="10501" width="15.453125" customWidth="1"/>
+    <col min="10502" max="10502" width="14.54296875" customWidth="1"/>
+    <col min="10503" max="10503" width="15.26953125" customWidth="1"/>
+    <col min="10504" max="10505" width="14.453125" customWidth="1"/>
+    <col min="10506" max="10506" width="13.1796875" customWidth="1"/>
+    <col min="10507" max="10509" width="14.453125" customWidth="1"/>
+    <col min="10510" max="10510" width="15.81640625" customWidth="1"/>
+    <col min="10511" max="10511" width="7.81640625" customWidth="1"/>
+    <col min="10512" max="10512" width="5.453125" customWidth="1"/>
+    <col min="10513" max="10513" width="6.453125" customWidth="1"/>
+    <col min="10514" max="10514" width="7.81640625" customWidth="1"/>
+    <col min="10515" max="10515" width="3" customWidth="1"/>
+    <col min="10516" max="10516" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10753" max="10756" width="14.453125" customWidth="1"/>
+    <col min="10757" max="10757" width="15.453125" customWidth="1"/>
+    <col min="10758" max="10758" width="14.54296875" customWidth="1"/>
+    <col min="10759" max="10759" width="15.26953125" customWidth="1"/>
+    <col min="10760" max="10761" width="14.453125" customWidth="1"/>
+    <col min="10762" max="10762" width="13.1796875" customWidth="1"/>
+    <col min="10763" max="10765" width="14.453125" customWidth="1"/>
+    <col min="10766" max="10766" width="15.81640625" customWidth="1"/>
+    <col min="10767" max="10767" width="7.81640625" customWidth="1"/>
+    <col min="10768" max="10768" width="5.453125" customWidth="1"/>
+    <col min="10769" max="10769" width="6.453125" customWidth="1"/>
+    <col min="10770" max="10770" width="7.81640625" customWidth="1"/>
+    <col min="10771" max="10771" width="3" customWidth="1"/>
+    <col min="10772" max="10772" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11009" max="11012" width="14.453125" customWidth="1"/>
+    <col min="11013" max="11013" width="15.453125" customWidth="1"/>
+    <col min="11014" max="11014" width="14.54296875" customWidth="1"/>
+    <col min="11015" max="11015" width="15.26953125" customWidth="1"/>
+    <col min="11016" max="11017" width="14.453125" customWidth="1"/>
+    <col min="11018" max="11018" width="13.1796875" customWidth="1"/>
+    <col min="11019" max="11021" width="14.453125" customWidth="1"/>
+    <col min="11022" max="11022" width="15.81640625" customWidth="1"/>
+    <col min="11023" max="11023" width="7.81640625" customWidth="1"/>
+    <col min="11024" max="11024" width="5.453125" customWidth="1"/>
+    <col min="11025" max="11025" width="6.453125" customWidth="1"/>
+    <col min="11026" max="11026" width="7.81640625" customWidth="1"/>
+    <col min="11027" max="11027" width="3" customWidth="1"/>
+    <col min="11028" max="11028" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11265" max="11268" width="14.453125" customWidth="1"/>
+    <col min="11269" max="11269" width="15.453125" customWidth="1"/>
+    <col min="11270" max="11270" width="14.54296875" customWidth="1"/>
+    <col min="11271" max="11271" width="15.26953125" customWidth="1"/>
+    <col min="11272" max="11273" width="14.453125" customWidth="1"/>
+    <col min="11274" max="11274" width="13.1796875" customWidth="1"/>
+    <col min="11275" max="11277" width="14.453125" customWidth="1"/>
+    <col min="11278" max="11278" width="15.81640625" customWidth="1"/>
+    <col min="11279" max="11279" width="7.81640625" customWidth="1"/>
+    <col min="11280" max="11280" width="5.453125" customWidth="1"/>
+    <col min="11281" max="11281" width="6.453125" customWidth="1"/>
+    <col min="11282" max="11282" width="7.81640625" customWidth="1"/>
+    <col min="11283" max="11283" width="3" customWidth="1"/>
+    <col min="11284" max="11284" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11521" max="11524" width="14.453125" customWidth="1"/>
+    <col min="11525" max="11525" width="15.453125" customWidth="1"/>
+    <col min="11526" max="11526" width="14.54296875" customWidth="1"/>
+    <col min="11527" max="11527" width="15.26953125" customWidth="1"/>
+    <col min="11528" max="11529" width="14.453125" customWidth="1"/>
+    <col min="11530" max="11530" width="13.1796875" customWidth="1"/>
+    <col min="11531" max="11533" width="14.453125" customWidth="1"/>
+    <col min="11534" max="11534" width="15.81640625" customWidth="1"/>
+    <col min="11535" max="11535" width="7.81640625" customWidth="1"/>
+    <col min="11536" max="11536" width="5.453125" customWidth="1"/>
+    <col min="11537" max="11537" width="6.453125" customWidth="1"/>
+    <col min="11538" max="11538" width="7.81640625" customWidth="1"/>
+    <col min="11539" max="11539" width="3" customWidth="1"/>
+    <col min="11540" max="11540" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11777" max="11780" width="14.453125" customWidth="1"/>
+    <col min="11781" max="11781" width="15.453125" customWidth="1"/>
+    <col min="11782" max="11782" width="14.54296875" customWidth="1"/>
+    <col min="11783" max="11783" width="15.26953125" customWidth="1"/>
+    <col min="11784" max="11785" width="14.453125" customWidth="1"/>
+    <col min="11786" max="11786" width="13.1796875" customWidth="1"/>
+    <col min="11787" max="11789" width="14.453125" customWidth="1"/>
+    <col min="11790" max="11790" width="15.81640625" customWidth="1"/>
+    <col min="11791" max="11791" width="7.81640625" customWidth="1"/>
+    <col min="11792" max="11792" width="5.453125" customWidth="1"/>
+    <col min="11793" max="11793" width="6.453125" customWidth="1"/>
+    <col min="11794" max="11794" width="7.81640625" customWidth="1"/>
+    <col min="11795" max="11795" width="3" customWidth="1"/>
+    <col min="11796" max="11796" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12033" max="12036" width="14.453125" customWidth="1"/>
+    <col min="12037" max="12037" width="15.453125" customWidth="1"/>
+    <col min="12038" max="12038" width="14.54296875" customWidth="1"/>
+    <col min="12039" max="12039" width="15.26953125" customWidth="1"/>
+    <col min="12040" max="12041" width="14.453125" customWidth="1"/>
+    <col min="12042" max="12042" width="13.1796875" customWidth="1"/>
+    <col min="12043" max="12045" width="14.453125" customWidth="1"/>
+    <col min="12046" max="12046" width="15.81640625" customWidth="1"/>
+    <col min="12047" max="12047" width="7.81640625" customWidth="1"/>
+    <col min="12048" max="12048" width="5.453125" customWidth="1"/>
+    <col min="12049" max="12049" width="6.453125" customWidth="1"/>
+    <col min="12050" max="12050" width="7.81640625" customWidth="1"/>
+    <col min="12051" max="12051" width="3" customWidth="1"/>
+    <col min="12052" max="12052" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12289" max="12292" width="14.453125" customWidth="1"/>
+    <col min="12293" max="12293" width="15.453125" customWidth="1"/>
+    <col min="12294" max="12294" width="14.54296875" customWidth="1"/>
+    <col min="12295" max="12295" width="15.26953125" customWidth="1"/>
+    <col min="12296" max="12297" width="14.453125" customWidth="1"/>
+    <col min="12298" max="12298" width="13.1796875" customWidth="1"/>
+    <col min="12299" max="12301" width="14.453125" customWidth="1"/>
+    <col min="12302" max="12302" width="15.81640625" customWidth="1"/>
+    <col min="12303" max="12303" width="7.81640625" customWidth="1"/>
+    <col min="12304" max="12304" width="5.453125" customWidth="1"/>
+    <col min="12305" max="12305" width="6.453125" customWidth="1"/>
+    <col min="12306" max="12306" width="7.81640625" customWidth="1"/>
+    <col min="12307" max="12307" width="3" customWidth="1"/>
+    <col min="12308" max="12308" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12545" max="12548" width="14.453125" customWidth="1"/>
+    <col min="12549" max="12549" width="15.453125" customWidth="1"/>
+    <col min="12550" max="12550" width="14.54296875" customWidth="1"/>
+    <col min="12551" max="12551" width="15.26953125" customWidth="1"/>
+    <col min="12552" max="12553" width="14.453125" customWidth="1"/>
+    <col min="12554" max="12554" width="13.1796875" customWidth="1"/>
+    <col min="12555" max="12557" width="14.453125" customWidth="1"/>
+    <col min="12558" max="12558" width="15.81640625" customWidth="1"/>
+    <col min="12559" max="12559" width="7.81640625" customWidth="1"/>
+    <col min="12560" max="12560" width="5.453125" customWidth="1"/>
+    <col min="12561" max="12561" width="6.453125" customWidth="1"/>
+    <col min="12562" max="12562" width="7.81640625" customWidth="1"/>
+    <col min="12563" max="12563" width="3" customWidth="1"/>
+    <col min="12564" max="12564" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12801" max="12804" width="14.453125" customWidth="1"/>
+    <col min="12805" max="12805" width="15.453125" customWidth="1"/>
+    <col min="12806" max="12806" width="14.54296875" customWidth="1"/>
+    <col min="12807" max="12807" width="15.26953125" customWidth="1"/>
+    <col min="12808" max="12809" width="14.453125" customWidth="1"/>
+    <col min="12810" max="12810" width="13.1796875" customWidth="1"/>
+    <col min="12811" max="12813" width="14.453125" customWidth="1"/>
+    <col min="12814" max="12814" width="15.81640625" customWidth="1"/>
+    <col min="12815" max="12815" width="7.81640625" customWidth="1"/>
+    <col min="12816" max="12816" width="5.453125" customWidth="1"/>
+    <col min="12817" max="12817" width="6.453125" customWidth="1"/>
+    <col min="12818" max="12818" width="7.81640625" customWidth="1"/>
+    <col min="12819" max="12819" width="3" customWidth="1"/>
+    <col min="12820" max="12820" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13057" max="13060" width="14.453125" customWidth="1"/>
+    <col min="13061" max="13061" width="15.453125" customWidth="1"/>
+    <col min="13062" max="13062" width="14.54296875" customWidth="1"/>
+    <col min="13063" max="13063" width="15.26953125" customWidth="1"/>
+    <col min="13064" max="13065" width="14.453125" customWidth="1"/>
+    <col min="13066" max="13066" width="13.1796875" customWidth="1"/>
+    <col min="13067" max="13069" width="14.453125" customWidth="1"/>
+    <col min="13070" max="13070" width="15.81640625" customWidth="1"/>
+    <col min="13071" max="13071" width="7.81640625" customWidth="1"/>
+    <col min="13072" max="13072" width="5.453125" customWidth="1"/>
+    <col min="13073" max="13073" width="6.453125" customWidth="1"/>
+    <col min="13074" max="13074" width="7.81640625" customWidth="1"/>
+    <col min="13075" max="13075" width="3" customWidth="1"/>
+    <col min="13076" max="13076" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13313" max="13316" width="14.453125" customWidth="1"/>
+    <col min="13317" max="13317" width="15.453125" customWidth="1"/>
+    <col min="13318" max="13318" width="14.54296875" customWidth="1"/>
+    <col min="13319" max="13319" width="15.26953125" customWidth="1"/>
+    <col min="13320" max="13321" width="14.453125" customWidth="1"/>
+    <col min="13322" max="13322" width="13.1796875" customWidth="1"/>
+    <col min="13323" max="13325" width="14.453125" customWidth="1"/>
+    <col min="13326" max="13326" width="15.81640625" customWidth="1"/>
+    <col min="13327" max="13327" width="7.81640625" customWidth="1"/>
+    <col min="13328" max="13328" width="5.453125" customWidth="1"/>
+    <col min="13329" max="13329" width="6.453125" customWidth="1"/>
+    <col min="13330" max="13330" width="7.81640625" customWidth="1"/>
+    <col min="13331" max="13331" width="3" customWidth="1"/>
+    <col min="13332" max="13332" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13569" max="13572" width="14.453125" customWidth="1"/>
+    <col min="13573" max="13573" width="15.453125" customWidth="1"/>
+    <col min="13574" max="13574" width="14.54296875" customWidth="1"/>
+    <col min="13575" max="13575" width="15.26953125" customWidth="1"/>
+    <col min="13576" max="13577" width="14.453125" customWidth="1"/>
+    <col min="13578" max="13578" width="13.1796875" customWidth="1"/>
+    <col min="13579" max="13581" width="14.453125" customWidth="1"/>
+    <col min="13582" max="13582" width="15.81640625" customWidth="1"/>
+    <col min="13583" max="13583" width="7.81640625" customWidth="1"/>
+    <col min="13584" max="13584" width="5.453125" customWidth="1"/>
+    <col min="13585" max="13585" width="6.453125" customWidth="1"/>
+    <col min="13586" max="13586" width="7.81640625" customWidth="1"/>
+    <col min="13587" max="13587" width="3" customWidth="1"/>
+    <col min="13588" max="13588" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13825" max="13828" width="14.453125" customWidth="1"/>
+    <col min="13829" max="13829" width="15.453125" customWidth="1"/>
+    <col min="13830" max="13830" width="14.54296875" customWidth="1"/>
+    <col min="13831" max="13831" width="15.26953125" customWidth="1"/>
+    <col min="13832" max="13833" width="14.453125" customWidth="1"/>
+    <col min="13834" max="13834" width="13.1796875" customWidth="1"/>
+    <col min="13835" max="13837" width="14.453125" customWidth="1"/>
+    <col min="13838" max="13838" width="15.81640625" customWidth="1"/>
+    <col min="13839" max="13839" width="7.81640625" customWidth="1"/>
+    <col min="13840" max="13840" width="5.453125" customWidth="1"/>
+    <col min="13841" max="13841" width="6.453125" customWidth="1"/>
+    <col min="13842" max="13842" width="7.81640625" customWidth="1"/>
+    <col min="13843" max="13843" width="3" customWidth="1"/>
+    <col min="13844" max="13844" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14081" max="14084" width="14.453125" customWidth="1"/>
+    <col min="14085" max="14085" width="15.453125" customWidth="1"/>
+    <col min="14086" max="14086" width="14.54296875" customWidth="1"/>
+    <col min="14087" max="14087" width="15.26953125" customWidth="1"/>
+    <col min="14088" max="14089" width="14.453125" customWidth="1"/>
+    <col min="14090" max="14090" width="13.1796875" customWidth="1"/>
+    <col min="14091" max="14093" width="14.453125" customWidth="1"/>
+    <col min="14094" max="14094" width="15.81640625" customWidth="1"/>
+    <col min="14095" max="14095" width="7.81640625" customWidth="1"/>
+    <col min="14096" max="14096" width="5.453125" customWidth="1"/>
+    <col min="14097" max="14097" width="6.453125" customWidth="1"/>
+    <col min="14098" max="14098" width="7.81640625" customWidth="1"/>
+    <col min="14099" max="14099" width="3" customWidth="1"/>
+    <col min="14100" max="14100" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14337" max="14340" width="14.453125" customWidth="1"/>
+    <col min="14341" max="14341" width="15.453125" customWidth="1"/>
+    <col min="14342" max="14342" width="14.54296875" customWidth="1"/>
+    <col min="14343" max="14343" width="15.26953125" customWidth="1"/>
+    <col min="14344" max="14345" width="14.453125" customWidth="1"/>
+    <col min="14346" max="14346" width="13.1796875" customWidth="1"/>
+    <col min="14347" max="14349" width="14.453125" customWidth="1"/>
+    <col min="14350" max="14350" width="15.81640625" customWidth="1"/>
+    <col min="14351" max="14351" width="7.81640625" customWidth="1"/>
+    <col min="14352" max="14352" width="5.453125" customWidth="1"/>
+    <col min="14353" max="14353" width="6.453125" customWidth="1"/>
+    <col min="14354" max="14354" width="7.81640625" customWidth="1"/>
+    <col min="14355" max="14355" width="3" customWidth="1"/>
+    <col min="14356" max="14356" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14593" max="14596" width="14.453125" customWidth="1"/>
+    <col min="14597" max="14597" width="15.453125" customWidth="1"/>
+    <col min="14598" max="14598" width="14.54296875" customWidth="1"/>
+    <col min="14599" max="14599" width="15.26953125" customWidth="1"/>
+    <col min="14600" max="14601" width="14.453125" customWidth="1"/>
+    <col min="14602" max="14602" width="13.1796875" customWidth="1"/>
+    <col min="14603" max="14605" width="14.453125" customWidth="1"/>
+    <col min="14606" max="14606" width="15.81640625" customWidth="1"/>
+    <col min="14607" max="14607" width="7.81640625" customWidth="1"/>
+    <col min="14608" max="14608" width="5.453125" customWidth="1"/>
+    <col min="14609" max="14609" width="6.453125" customWidth="1"/>
+    <col min="14610" max="14610" width="7.81640625" customWidth="1"/>
+    <col min="14611" max="14611" width="3" customWidth="1"/>
+    <col min="14612" max="14612" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14849" max="14852" width="14.453125" customWidth="1"/>
+    <col min="14853" max="14853" width="15.453125" customWidth="1"/>
+    <col min="14854" max="14854" width="14.54296875" customWidth="1"/>
+    <col min="14855" max="14855" width="15.26953125" customWidth="1"/>
+    <col min="14856" max="14857" width="14.453125" customWidth="1"/>
+    <col min="14858" max="14858" width="13.1796875" customWidth="1"/>
+    <col min="14859" max="14861" width="14.453125" customWidth="1"/>
+    <col min="14862" max="14862" width="15.81640625" customWidth="1"/>
+    <col min="14863" max="14863" width="7.81640625" customWidth="1"/>
+    <col min="14864" max="14864" width="5.453125" customWidth="1"/>
+    <col min="14865" max="14865" width="6.453125" customWidth="1"/>
+    <col min="14866" max="14866" width="7.81640625" customWidth="1"/>
+    <col min="14867" max="14867" width="3" customWidth="1"/>
+    <col min="14868" max="14868" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15105" max="15108" width="14.453125" customWidth="1"/>
+    <col min="15109" max="15109" width="15.453125" customWidth="1"/>
+    <col min="15110" max="15110" width="14.54296875" customWidth="1"/>
+    <col min="15111" max="15111" width="15.26953125" customWidth="1"/>
+    <col min="15112" max="15113" width="14.453125" customWidth="1"/>
+    <col min="15114" max="15114" width="13.1796875" customWidth="1"/>
+    <col min="15115" max="15117" width="14.453125" customWidth="1"/>
+    <col min="15118" max="15118" width="15.81640625" customWidth="1"/>
+    <col min="15119" max="15119" width="7.81640625" customWidth="1"/>
+    <col min="15120" max="15120" width="5.453125" customWidth="1"/>
+    <col min="15121" max="15121" width="6.453125" customWidth="1"/>
+    <col min="15122" max="15122" width="7.81640625" customWidth="1"/>
+    <col min="15123" max="15123" width="3" customWidth="1"/>
+    <col min="15124" max="15124" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15361" max="15364" width="14.453125" customWidth="1"/>
+    <col min="15365" max="15365" width="15.453125" customWidth="1"/>
+    <col min="15366" max="15366" width="14.54296875" customWidth="1"/>
+    <col min="15367" max="15367" width="15.26953125" customWidth="1"/>
+    <col min="15368" max="15369" width="14.453125" customWidth="1"/>
+    <col min="15370" max="15370" width="13.1796875" customWidth="1"/>
+    <col min="15371" max="15373" width="14.453125" customWidth="1"/>
+    <col min="15374" max="15374" width="15.81640625" customWidth="1"/>
+    <col min="15375" max="15375" width="7.81640625" customWidth="1"/>
+    <col min="15376" max="15376" width="5.453125" customWidth="1"/>
+    <col min="15377" max="15377" width="6.453125" customWidth="1"/>
+    <col min="15378" max="15378" width="7.81640625" customWidth="1"/>
+    <col min="15379" max="15379" width="3" customWidth="1"/>
+    <col min="15380" max="15380" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15617" max="15620" width="14.453125" customWidth="1"/>
+    <col min="15621" max="15621" width="15.453125" customWidth="1"/>
+    <col min="15622" max="15622" width="14.54296875" customWidth="1"/>
+    <col min="15623" max="15623" width="15.26953125" customWidth="1"/>
+    <col min="15624" max="15625" width="14.453125" customWidth="1"/>
+    <col min="15626" max="15626" width="13.1796875" customWidth="1"/>
+    <col min="15627" max="15629" width="14.453125" customWidth="1"/>
+    <col min="15630" max="15630" width="15.81640625" customWidth="1"/>
+    <col min="15631" max="15631" width="7.81640625" customWidth="1"/>
+    <col min="15632" max="15632" width="5.453125" customWidth="1"/>
+    <col min="15633" max="15633" width="6.453125" customWidth="1"/>
+    <col min="15634" max="15634" width="7.81640625" customWidth="1"/>
+    <col min="15635" max="15635" width="3" customWidth="1"/>
+    <col min="15636" max="15636" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15873" max="15876" width="14.453125" customWidth="1"/>
+    <col min="15877" max="15877" width="15.453125" customWidth="1"/>
+    <col min="15878" max="15878" width="14.54296875" customWidth="1"/>
+    <col min="15879" max="15879" width="15.26953125" customWidth="1"/>
+    <col min="15880" max="15881" width="14.453125" customWidth="1"/>
+    <col min="15882" max="15882" width="13.1796875" customWidth="1"/>
+    <col min="15883" max="15885" width="14.453125" customWidth="1"/>
+    <col min="15886" max="15886" width="15.81640625" customWidth="1"/>
+    <col min="15887" max="15887" width="7.81640625" customWidth="1"/>
+    <col min="15888" max="15888" width="5.453125" customWidth="1"/>
+    <col min="15889" max="15889" width="6.453125" customWidth="1"/>
+    <col min="15890" max="15890" width="7.81640625" customWidth="1"/>
+    <col min="15891" max="15891" width="3" customWidth="1"/>
+    <col min="15892" max="15892" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="16129" max="16132" width="14.453125" customWidth="1"/>
+    <col min="16133" max="16133" width="15.453125" customWidth="1"/>
+    <col min="16134" max="16134" width="14.54296875" customWidth="1"/>
+    <col min="16135" max="16135" width="15.26953125" customWidth="1"/>
+    <col min="16136" max="16137" width="14.453125" customWidth="1"/>
+    <col min="16138" max="16138" width="13.1796875" customWidth="1"/>
+    <col min="16139" max="16141" width="14.453125" customWidth="1"/>
+    <col min="16142" max="16142" width="15.81640625" customWidth="1"/>
+    <col min="16143" max="16143" width="7.81640625" customWidth="1"/>
+    <col min="16144" max="16144" width="5.453125" customWidth="1"/>
+    <col min="16145" max="16145" width="6.453125" customWidth="1"/>
+    <col min="16146" max="16146" width="7.81640625" customWidth="1"/>
+    <col min="16147" max="16147" width="3" customWidth="1"/>
+    <col min="16148" max="16148" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="284" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="284"/>
+      <c r="M1" s="284"/>
+      <c r="S1"/>
+    </row>
+    <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2"/>
+    </row>
+    <row r="3" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" s="273" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F3" s="273" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="129" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="275" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="280" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="26"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="277" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" s="278"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="270" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="271"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="29"/>
+    </row>
+    <row r="4" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="260" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="273"/>
+      <c r="E4" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F4" s="273"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="275"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="280"/>
+      <c r="O4" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" s="266" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" s="267" t="s">
+        <v>71</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" s="262" t="s">
+        <v>70</v>
+      </c>
+      <c r="U4" s="263" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" s="37"/>
+      <c r="E5" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F5" s="276" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="273" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="54"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="38"/>
+      <c r="O5" s="39">
+        <v>31</v>
+      </c>
+      <c r="P5" s="40">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="41">
+        <v>19</v>
+      </c>
+      <c r="R5" s="42">
+        <v>11</v>
+      </c>
+      <c r="S5" s="40">
+        <v>31</v>
+      </c>
+      <c r="T5" s="41">
+        <v>19</v>
+      </c>
+      <c r="U5" s="42">
+        <v>11</v>
+      </c>
+      <c r="V5" s="43">
+        <f t="shared" ref="V5:V17" si="0">-SUM(S5-P5)*-1</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="44"/>
+    </row>
+    <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="260" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="276"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="129" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="273"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="126" t="s">
+        <v>215</v>
+      </c>
+      <c r="N6" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" s="47">
+        <v>49</v>
+      </c>
+      <c r="P6" s="48">
+        <f t="shared" ref="P6:P17" si="1">SUM(Q6:R6)</f>
+        <v>12</v>
+      </c>
+      <c r="Q6" s="49">
+        <v>7</v>
+      </c>
+      <c r="R6" s="50">
+        <v>5</v>
+      </c>
+      <c r="S6" s="48">
+        <f t="shared" ref="S6:S17" si="2">SUM(T6:U6)</f>
+        <v>12</v>
+      </c>
+      <c r="T6" s="49">
+        <v>7</v>
+      </c>
+      <c r="U6" s="50">
+        <v>5</v>
+      </c>
+      <c r="V6" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="52"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="53"/>
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="260" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="298" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="64"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="280" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" s="54"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="47">
+        <v>22</v>
+      </c>
+      <c r="P7" s="48">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Q7" s="49">
+        <v>11</v>
+      </c>
+      <c r="R7" s="50">
+        <v>4</v>
+      </c>
+      <c r="S7" s="48">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="T7" s="49">
+        <v>11</v>
+      </c>
+      <c r="U7" s="50">
+        <v>4</v>
+      </c>
+      <c r="V7" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W7" s="52"/>
+    </row>
+    <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="45"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="298"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="280"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="56">
+        <v>46314</v>
+      </c>
+      <c r="O8" s="47">
+        <v>24</v>
+      </c>
+      <c r="P8" s="48">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Q8" s="49">
+        <v>3</v>
+      </c>
+      <c r="R8" s="50">
+        <v>3</v>
+      </c>
+      <c r="S8" s="48">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="T8" s="49">
+        <v>2</v>
+      </c>
+      <c r="U8" s="50">
+        <v>2</v>
+      </c>
+      <c r="V8" s="51">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="W8" s="52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="45"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="58"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="279" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="64"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9" s="47"/>
+      <c r="P9" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="49"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W9" s="52"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="45"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="129" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="61"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="279"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="49"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="52"/>
+    </row>
+    <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="64"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="61"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="258" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="64"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="66"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="68"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="70"/>
+    </row>
+    <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="71"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="64"/>
+      <c r="H12" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="L12" s="73" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" s="74"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="68"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W12" s="70"/>
+    </row>
+    <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="61"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="268" t="s">
+        <v>149</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="280" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="127" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="128"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="60"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="68"/>
+      <c r="U13" s="69"/>
+      <c r="V13" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="70"/>
+    </row>
+    <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="8"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="261" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="30"/>
+      <c r="I14" s="280"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="60"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="68"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="70"/>
+    </row>
+    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="129"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="265"/>
+      <c r="F15" s="128" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="107"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="68"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="70"/>
+    </row>
+    <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="279" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="279" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="280" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="61"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="107"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="68"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="68"/>
+      <c r="U16" s="69"/>
+      <c r="V16" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="70"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="279"/>
+      <c r="B17" s="279"/>
+      <c r="C17" s="280"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="269" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="80"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="82">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="83"/>
+    </row>
+    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="59"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="77"/>
+      <c r="M18" s="77"/>
+      <c r="R18" s="84"/>
+      <c r="S18"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="265"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="77"/>
+      <c r="R19" s="84"/>
+      <c r="S19"/>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="85" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="265"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="158"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="R20" s="84"/>
+      <c r="S20"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="D21" s="61"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="R21" s="84"/>
+      <c r="S21"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="6"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="265"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="R22" s="84"/>
+      <c r="S22"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="R23" s="84"/>
+      <c r="S23"/>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="R24" s="84"/>
+      <c r="S24"/>
+    </row>
+    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="30"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="R25" s="84"/>
+      <c r="S25"/>
+    </row>
+    <row r="26" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="265"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="R26" s="84"/>
+      <c r="S26"/>
+    </row>
+    <row r="27" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="R27" s="84"/>
+      <c r="S27"/>
+    </row>
+    <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="285" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="285"/>
+      <c r="C28" s="285"/>
+      <c r="D28" s="285"/>
+      <c r="E28" s="285"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="R28" s="84"/>
+      <c r="S28"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="30"/>
+      <c r="I29" s="265"/>
+      <c r="J29" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K29" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="92" t="s">
+        <v>25</v>
+      </c>
+      <c r="R29" s="84"/>
+      <c r="S29"/>
+    </row>
+    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="B30" s="94"/>
+      <c r="C30" s="93" t="s">
+        <v>231</v>
+      </c>
+      <c r="D30" s="93" t="s">
+        <v>234</v>
+      </c>
+      <c r="E30" s="274" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="8"/>
+      <c r="G30" s="264" t="s">
+        <v>240</v>
+      </c>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="K30" s="124" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="218" t="s">
+        <v>119</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="R30" s="84"/>
+      <c r="S30"/>
+    </row>
+    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="93" t="s">
+        <v>232</v>
+      </c>
+      <c r="D31" s="93" t="s">
+        <v>233</v>
+      </c>
+      <c r="E31" s="274"/>
+      <c r="F31" s="8"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="159"/>
+      <c r="K31" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="L31" s="218" t="s">
+        <v>122</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" s="84"/>
+      <c r="S31"/>
+    </row>
+    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="94"/>
+      <c r="C32" s="93" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="93" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" s="274" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="159"/>
+      <c r="K32" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="L32" s="218" t="s">
+        <v>243</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="R32" s="84"/>
+      <c r="S32"/>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="8"/>
+      <c r="C33" s="93" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="93" t="s">
+        <v>236</v>
+      </c>
+      <c r="E33" s="274"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="224" t="s">
+        <v>42</v>
+      </c>
+      <c r="L33" s="218" t="s">
+        <v>38</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="R33" s="84"/>
+      <c r="S33"/>
+    </row>
+    <row r="34" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="94"/>
+      <c r="B34" s="95"/>
+      <c r="D34" s="93" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" s="272" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="K34" s="110" t="s">
+        <v>150</v>
+      </c>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="R34" s="84"/>
+      <c r="S34"/>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="94"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="93" t="s">
+        <v>238</v>
+      </c>
+      <c r="E35" s="272"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="110" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="8"/>
+      <c r="M35" s="13"/>
+      <c r="R35" s="84"/>
+      <c r="S35"/>
+    </row>
+    <row r="36" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="94"/>
+      <c r="B36" s="94"/>
+      <c r="D36" s="93" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="274" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="97"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="124" t="s">
+        <v>120</v>
+      </c>
+      <c r="L36" s="8"/>
+      <c r="M36" s="94"/>
+      <c r="R36" s="84"/>
+      <c r="S36"/>
+    </row>
+    <row r="37" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="100"/>
+      <c r="K37" s="224" t="s">
+        <v>203</v>
+      </c>
+      <c r="L37" s="8"/>
+      <c r="M37" s="94"/>
+      <c r="R37" s="84"/>
+      <c r="S37"/>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="77"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="264" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" s="77"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="124" t="s">
+        <v>211</v>
+      </c>
+      <c r="L38" s="8"/>
+      <c r="M38" s="2"/>
+      <c r="R38" s="84"/>
+      <c r="S38"/>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="74"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="264" t="s">
+        <v>92</v>
+      </c>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="124" t="s">
+        <v>212</v>
+      </c>
+      <c r="L39" s="16"/>
+      <c r="M39" s="2"/>
+      <c r="S39"/>
+    </row>
+    <row r="40" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="105"/>
+      <c r="S40"/>
+    </row>
+    <row r="41" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="104"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="104"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="93" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="8"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="101"/>
+      <c r="M41" s="106"/>
+      <c r="S41"/>
+    </row>
+    <row r="42" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="104"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="104"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="264" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="106"/>
+      <c r="S42"/>
+    </row>
+    <row r="43" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="104"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="264" t="s">
+        <v>216</v>
+      </c>
+      <c r="F43" s="107"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="106"/>
+      <c r="S43"/>
+    </row>
+    <row r="44" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="104"/>
+      <c r="B44" s="104"/>
+      <c r="C44" s="104"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="109"/>
+      <c r="S44"/>
+    </row>
+    <row r="45" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="104"/>
+      <c r="B45" s="104"/>
+      <c r="C45" s="104"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="110"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="111"/>
+      <c r="S45"/>
+    </row>
+    <row r="46" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="104"/>
+      <c r="B46" s="104"/>
+      <c r="C46" s="104"/>
+      <c r="D46" s="104"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="104"/>
+      <c r="J46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="111"/>
+      <c r="S46"/>
+    </row>
+    <row r="47" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="104"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="104"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="104"/>
+      <c r="H47" s="104"/>
+      <c r="I47" s="265"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="112"/>
+      <c r="S47"/>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="84"/>
+      <c r="S48"/>
+    </row>
+    <row r="49" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="77"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="113"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="104"/>
+      <c r="I49" s="265"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="84"/>
+      <c r="S49"/>
+    </row>
+    <row r="50" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="77"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="84"/>
+      <c r="S50"/>
+    </row>
+    <row r="51" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="77"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="77"/>
+      <c r="D51" s="113"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="77"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="84"/>
+      <c r="S51"/>
+    </row>
+    <row r="52" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="77"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="113"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="77"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="77"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+    </row>
+    <row r="53" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="77"/>
+      <c r="B53" s="77"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="113"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="77"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="114"/>
+      <c r="M53" s="8"/>
+    </row>
+    <row r="54" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="77"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="113"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="77"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="77"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="114"/>
+      <c r="M54" s="8"/>
+    </row>
+    <row r="55" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="77"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="113"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="77"/>
+      <c r="G55" s="77"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="104"/>
+      <c r="J55" s="77"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="114"/>
+      <c r="M55" s="8"/>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="77"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="113"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="77"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="77"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="114"/>
+      <c r="M56" s="8"/>
+    </row>
+    <row r="57" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="77"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="77"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="114"/>
+      <c r="M57" s="8"/>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="77"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="113"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="77"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="115"/>
+      <c r="L58" s="114"/>
+      <c r="M58" s="8"/>
+    </row>
+    <row r="59" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="77"/>
+      <c r="B59" s="77"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="113"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="77"/>
+      <c r="G59" s="77"/>
+      <c r="H59" s="104"/>
+      <c r="I59" s="104"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="115"/>
+      <c r="L59" s="114"/>
+      <c r="M59" s="8"/>
+    </row>
+    <row r="60" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="77"/>
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="77"/>
+      <c r="G60" s="77"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="115"/>
+      <c r="L60" s="114"/>
+      <c r="M60" s="8"/>
+    </row>
+    <row r="61" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="77"/>
+      <c r="B61" s="77"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="113"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="114"/>
+      <c r="M61" s="8"/>
+    </row>
+    <row r="62" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="77"/>
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="77"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="114"/>
+      <c r="M62" s="8"/>
+    </row>
+    <row r="63" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="77"/>
+      <c r="B63" s="77"/>
+      <c r="C63" s="77"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="104"/>
+      <c r="I63" s="104"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="77"/>
+      <c r="M63" s="8"/>
+    </row>
+    <row r="64" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="77"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="77"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="77"/>
+      <c r="H64" s="104"/>
+      <c r="I64" s="104"/>
+      <c r="J64" s="77"/>
+      <c r="K64" s="116">
+        <v>22</v>
+      </c>
+      <c r="L64" s="117">
+        <v>6</v>
+      </c>
+      <c r="M64" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="61"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
+      <c r="S65"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L66" s="119" t="s">
+        <v>94</v>
+      </c>
+      <c r="M66" s="25">
+        <v>97</v>
+      </c>
+      <c r="S66"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L67" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="M67" s="25">
+        <f>SUM(M66-(M68+M69+M70))</f>
+        <v>69</v>
+      </c>
+      <c r="S67"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L68" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" s="25">
+        <v>15</v>
+      </c>
+      <c r="S68"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L69" s="121" t="s">
+        <v>24</v>
+      </c>
+      <c r="M69" s="25">
+        <v>9</v>
+      </c>
+      <c r="S69"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L70" s="122" t="s">
+        <v>25</v>
+      </c>
+      <c r="M70" s="25">
+        <v>4</v>
+      </c>
+      <c r="S70"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L71" t="s">
+        <v>96</v>
+      </c>
+      <c r="M71" s="25">
+        <v>13</v>
+      </c>
+      <c r="S71"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="M72" s="25"/>
+      <c r="S72"/>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
     <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -14074,7 +16763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAEFA27C-E172-4F4A-AB91-EB8B6E2464E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -14986,21 +17675,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="284"/>
+      <c r="M1" s="284"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -15055,13 +17744,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="261" t="s">
+      <c r="D3" s="273" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="261" t="s">
+      <c r="F3" s="273" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -15070,24 +17759,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="259" t="s">
+      <c r="J3" s="279" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="262" t="s">
+      <c r="M3" s="280" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="270" t="s">
+      <c r="Q3" s="277" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="271"/>
+      <c r="R3" s="278"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="270" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="265"/>
+      <c r="U3" s="271"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -15099,20 +17788,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="261"/>
+      <c r="D4" s="273"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="261"/>
+      <c r="F4" s="273"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="259"/>
+      <c r="J4" s="279"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="262"/>
+      <c r="M4" s="280"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -15151,7 +17840,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="269" t="s">
+      <c r="F5" s="276" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -15159,7 +17848,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="261" t="s">
+      <c r="J5" s="273" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -15204,13 +17893,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="269"/>
+      <c r="F6" s="276"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="261"/>
+      <c r="J6" s="273"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -15259,13 +17948,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="259" t="s">
+      <c r="F7" s="279" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="268" t="s">
+      <c r="J7" s="275" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -15313,11 +18002,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="259"/>
+      <c r="F8" s="279"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="268"/>
+      <c r="J8" s="275"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -15361,7 +18050,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="269" t="s">
+      <c r="F9" s="276" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -15401,7 +18090,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="269"/>
+      <c r="F10" s="276"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -15527,7 +18216,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="262" t="s">
+      <c r="I13" s="280" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -15568,7 +18257,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="262"/>
+      <c r="I14" s="280"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -15628,13 +18317,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="259" t="s">
+      <c r="A16" s="279" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="259" t="s">
+      <c r="B16" s="279" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="272" t="s">
+      <c r="C16" s="281" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -15669,9 +18358,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="259"/>
-      <c r="B17" s="259"/>
-      <c r="C17" s="273"/>
+      <c r="A17" s="279"/>
+      <c r="B17" s="279"/>
+      <c r="C17" s="282"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -15704,7 +18393,7 @@
     <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="262" t="s">
+      <c r="C18" s="280" t="s">
         <v>82</v>
       </c>
       <c r="D18" s="61"/>
@@ -15722,7 +18411,7 @@
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="147"/>
-      <c r="C19" s="262"/>
+      <c r="C19" s="280"/>
       <c r="D19" s="125"/>
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
@@ -15881,13 +18570,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="263" t="s">
+      <c r="A28" s="285" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="263"/>
-      <c r="C28" s="263"/>
-      <c r="D28" s="263"/>
-      <c r="E28" s="263"/>
+      <c r="B28" s="285"/>
+      <c r="C28" s="285"/>
+      <c r="D28" s="285"/>
+      <c r="E28" s="285"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -15947,7 +18636,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="267" t="s">
+      <c r="E30" s="274" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -15981,7 +18670,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="267"/>
+      <c r="E31" s="274"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -16011,7 +18700,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="267" t="s">
+      <c r="E32" s="274" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -16041,7 +18730,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="267"/>
+      <c r="E33" s="274"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -16065,7 +18754,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="266" t="s">
+      <c r="E34" s="272" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -16090,7 +18779,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="266"/>
+      <c r="E35" s="272"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -16109,7 +18798,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="267" t="s">
+      <c r="E36" s="274" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -16129,7 +18818,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="267"/>
+      <c r="E37" s="274"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -16657,28 +19346,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="C18:C19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -16687,7 +19376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86284CDF-7A93-420E-9CD6-2839FAEB19D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -17599,21 +20288,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="284"/>
+      <c r="M1" s="284"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -17668,13 +20357,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="261" t="s">
+      <c r="D3" s="273" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="261" t="s">
+      <c r="F3" s="273" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -17683,24 +20372,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="259" t="s">
+      <c r="J3" s="279" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="262" t="s">
+      <c r="M3" s="280" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="270" t="s">
+      <c r="Q3" s="277" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="271"/>
+      <c r="R3" s="278"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="270" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="265"/>
+      <c r="U3" s="271"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -17712,20 +20401,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="261"/>
+      <c r="D4" s="273"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="261"/>
+      <c r="F4" s="273"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="259"/>
+      <c r="J4" s="279"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="262"/>
+      <c r="M4" s="280"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -17764,7 +20453,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="269" t="s">
+      <c r="F5" s="276" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -17772,7 +20461,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="261" t="s">
+      <c r="J5" s="273" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -17817,13 +20506,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="269"/>
+      <c r="F6" s="276"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="261"/>
+      <c r="J6" s="273"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -17867,13 +20556,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="259" t="s">
+      <c r="F7" s="279" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="268" t="s">
+      <c r="J7" s="275" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -17921,11 +20610,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="259"/>
+      <c r="F8" s="279"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="268"/>
+      <c r="J8" s="275"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -17969,7 +20658,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="269" t="s">
+      <c r="F9" s="276" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -18009,7 +20698,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="269"/>
+      <c r="F10" s="276"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -18135,7 +20824,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="262" t="s">
+      <c r="I13" s="280" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -18176,7 +20865,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="262"/>
+      <c r="I14" s="280"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -18211,7 +20900,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="262" t="s">
+      <c r="I15" s="280" t="s">
         <v>82</v>
       </c>
       <c r="J15" s="60"/>
@@ -18238,13 +20927,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="259" t="s">
+      <c r="A16" s="279" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="259" t="s">
+      <c r="B16" s="279" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="272" t="s">
+      <c r="C16" s="281" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -18254,7 +20943,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="262"/>
+      <c r="I16" s="280"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -18279,15 +20968,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="259"/>
-      <c r="B17" s="259"/>
-      <c r="C17" s="273"/>
+      <c r="A17" s="279"/>
+      <c r="B17" s="279"/>
+      <c r="C17" s="282"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="269" t="s">
+      <c r="I17" s="276" t="s">
         <v>139</v>
       </c>
       <c r="J17" s="71"/>
@@ -18322,7 +21011,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="269"/>
+      <c r="I18" s="276"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -18494,13 +21183,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="263" t="s">
+      <c r="A28" s="285" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="263"/>
-      <c r="C28" s="263"/>
-      <c r="D28" s="263"/>
-      <c r="E28" s="263"/>
+      <c r="B28" s="285"/>
+      <c r="C28" s="285"/>
+      <c r="D28" s="285"/>
+      <c r="E28" s="285"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -18560,7 +21249,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="267" t="s">
+      <c r="E30" s="274" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -18594,7 +21283,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="267"/>
+      <c r="E31" s="274"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -18624,7 +21313,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="267" t="s">
+      <c r="E32" s="274" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -18654,7 +21343,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="267"/>
+      <c r="E33" s="274"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -18680,7 +21369,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="266" t="s">
+      <c r="E34" s="272" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -18703,7 +21392,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="266"/>
+      <c r="E35" s="272"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -18723,7 +21412,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="267" t="s">
+      <c r="E36" s="274" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -18740,7 +21429,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="267"/>
+      <c r="E37" s="274"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -19268,29 +21957,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="I17:I18"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="I13:I14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -19299,7 +21988,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8F7372-7841-4B0C-B11B-EBC4ACF4AD77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -20208,21 +22897,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="284"/>
+      <c r="M1" s="284"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -20275,13 +22964,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="261" t="s">
+      <c r="D3" s="273" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="261" t="s">
+      <c r="F3" s="273" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -20290,24 +22979,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="259" t="s">
+      <c r="J3" s="279" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="262" t="s">
+      <c r="M3" s="280" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="270" t="s">
+      <c r="Q3" s="277" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="271"/>
+      <c r="R3" s="278"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="270" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="265"/>
+      <c r="U3" s="271"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -20319,20 +23008,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="261"/>
+      <c r="D4" s="273"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="261"/>
+      <c r="F4" s="273"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="259"/>
+      <c r="J4" s="279"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="262"/>
+      <c r="M4" s="280"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -20371,7 +23060,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="269" t="s">
+      <c r="F5" s="276" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -20379,7 +23068,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="261" t="s">
+      <c r="J5" s="273" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -20424,13 +23113,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="269"/>
+      <c r="F6" s="276"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="261"/>
+      <c r="J6" s="273"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -20474,13 +23163,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="259" t="s">
+      <c r="F7" s="279" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="268" t="s">
+      <c r="J7" s="275" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -20528,13 +23217,13 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="259"/>
+      <c r="F8" s="279"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="J8" s="268"/>
+      <c r="J8" s="275"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -20578,13 +23267,13 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="269" t="s">
+      <c r="F9" s="276" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
       <c r="H9" s="30"/>
       <c r="I9" s="134"/>
-      <c r="J9" s="262" t="s">
+      <c r="J9" s="280" t="s">
         <v>82</v>
       </c>
       <c r="K9" s="54"/>
@@ -20620,11 +23309,11 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="269"/>
+      <c r="F10" s="276"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
-      <c r="J10" s="262"/>
+      <c r="J10" s="280"/>
       <c r="K10" s="6"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
@@ -20747,7 +23436,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="262" t="s">
+      <c r="I13" s="280" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -20788,7 +23477,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="262"/>
+      <c r="I14" s="280"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -20823,7 +23512,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="274" t="s">
+      <c r="I15" s="286" t="s">
         <v>139</v>
       </c>
       <c r="J15" s="60"/>
@@ -20850,13 +23539,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="259" t="s">
+      <c r="A16" s="279" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="259" t="s">
+      <c r="B16" s="279" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="272" t="s">
+      <c r="C16" s="281" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -20866,7 +23555,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="274"/>
+      <c r="I16" s="286"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -20891,9 +23580,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="259"/>
-      <c r="B17" s="259"/>
-      <c r="C17" s="273"/>
+      <c r="A17" s="279"/>
+      <c r="B17" s="279"/>
+      <c r="C17" s="282"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -21104,13 +23793,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="263" t="s">
+      <c r="A28" s="285" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="263"/>
-      <c r="C28" s="263"/>
-      <c r="D28" s="263"/>
-      <c r="E28" s="263"/>
+      <c r="B28" s="285"/>
+      <c r="C28" s="285"/>
+      <c r="D28" s="285"/>
+      <c r="E28" s="285"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -21170,7 +23859,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="267" t="s">
+      <c r="E30" s="274" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -21204,7 +23893,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="267"/>
+      <c r="E31" s="274"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -21234,7 +23923,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="267" t="s">
+      <c r="E32" s="274" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -21259,7 +23948,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="267"/>
+      <c r="E33" s="274"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -21280,7 +23969,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="266" t="s">
+      <c r="E34" s="272" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -21303,7 +23992,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="266"/>
+      <c r="E35" s="272"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -21323,7 +24012,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="267" t="s">
+      <c r="E36" s="274" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -21343,7 +24032,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="267"/>
+      <c r="E37" s="274"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -21871,11 +24560,17 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="A16:A17"/>
@@ -21883,17 +24578,11 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="F9:F10"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21901,7 +24590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B92903-E178-43FB-9A39-93C7F9630DFD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -22810,21 +25499,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="284"/>
+      <c r="M1" s="284"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -22879,13 +25568,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="261" t="s">
+      <c r="D3" s="273" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="261" t="s">
+      <c r="F3" s="273" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -22894,24 +25583,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="259" t="s">
+      <c r="J3" s="279" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="262" t="s">
+      <c r="M3" s="280" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="270" t="s">
+      <c r="Q3" s="277" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="271"/>
+      <c r="R3" s="278"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="270" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="265"/>
+      <c r="U3" s="271"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -22923,20 +25612,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="261"/>
+      <c r="D4" s="273"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="261"/>
+      <c r="F4" s="273"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="259"/>
+      <c r="J4" s="279"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="262"/>
+      <c r="M4" s="280"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -22975,7 +25664,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="269" t="s">
+      <c r="F5" s="276" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -22983,7 +25672,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="261" t="s">
+      <c r="J5" s="273" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -23028,13 +25717,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="269"/>
+      <c r="F6" s="276"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="261"/>
+      <c r="J6" s="273"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -23081,7 +25770,7 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="259" t="s">
+      <c r="F7" s="279" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
@@ -23089,7 +25778,7 @@
       <c r="I7" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="268" t="s">
+      <c r="J7" s="275" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -23137,10 +25826,10 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="259"/>
+      <c r="F8" s="279"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
-      <c r="J8" s="268"/>
+      <c r="J8" s="275"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -23184,7 +25873,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="269" t="s">
+      <c r="F9" s="276" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -23224,7 +25913,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="269"/>
+      <c r="F10" s="276"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -23351,7 +26040,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="262" t="s">
+      <c r="I13" s="280" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -23389,7 +26078,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="262"/>
+      <c r="I14" s="280"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -23424,7 +26113,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="262" t="s">
+      <c r="I15" s="280" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -23451,13 +26140,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="259" t="s">
+      <c r="A16" s="279" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="259" t="s">
+      <c r="B16" s="279" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="269" t="s">
+      <c r="C16" s="276" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -23467,7 +26156,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="262"/>
+      <c r="I16" s="280"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -23492,15 +26181,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="259"/>
-      <c r="B17" s="259"/>
-      <c r="C17" s="269"/>
+      <c r="A17" s="279"/>
+      <c r="B17" s="279"/>
+      <c r="C17" s="276"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="262" t="s">
+      <c r="I17" s="280" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -23535,7 +26224,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="262"/>
+      <c r="I18" s="280"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -23705,13 +26394,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="263" t="s">
+      <c r="A28" s="285" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="263"/>
-      <c r="C28" s="263"/>
-      <c r="D28" s="263"/>
-      <c r="E28" s="263"/>
+      <c r="B28" s="285"/>
+      <c r="C28" s="285"/>
+      <c r="D28" s="285"/>
+      <c r="E28" s="285"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -23771,7 +26460,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="267" t="s">
+      <c r="E30" s="274" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -23805,7 +26494,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="267"/>
+      <c r="E31" s="274"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -23835,7 +26524,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="267" t="s">
+      <c r="E32" s="274" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -23861,7 +26550,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="267"/>
+      <c r="E33" s="274"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -23883,7 +26572,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="266" t="s">
+      <c r="E34" s="272" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -23906,7 +26595,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="266"/>
+      <c r="E35" s="272"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -23926,7 +26615,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="267" t="s">
+      <c r="E36" s="274" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -23943,7 +26632,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="267"/>
+      <c r="E37" s="274"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -24471,6 +27160,17 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="I17:I18"/>
     <mergeCell ref="A1:M1"/>
@@ -24483,17 +27183,6 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="I13:I14"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -24501,7 +27190,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1EFD9FB-FFE6-40E3-B089-6D8E41EDC80B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -25413,21 +28102,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="284"/>
+      <c r="M1" s="284"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -25482,13 +28171,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="261" t="s">
+      <c r="D3" s="273" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="261" t="s">
+      <c r="F3" s="273" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -25497,24 +28186,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="259" t="s">
+      <c r="J3" s="279" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="262" t="s">
+      <c r="M3" s="280" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="270" t="s">
+      <c r="Q3" s="277" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="271"/>
+      <c r="R3" s="278"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="270" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="265"/>
+      <c r="U3" s="271"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -25526,20 +28215,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="261"/>
+      <c r="D4" s="273"/>
       <c r="E4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="261"/>
+      <c r="F4" s="273"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="259"/>
+      <c r="J4" s="279"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="262"/>
+      <c r="M4" s="280"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -25578,7 +28267,7 @@
       <c r="E5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F5" s="269" t="s">
+      <c r="F5" s="276" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -25586,7 +28275,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="261" t="s">
+      <c r="J5" s="273" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -25631,13 +28320,13 @@
       <c r="E6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="269"/>
+      <c r="F6" s="276"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="261"/>
+      <c r="J6" s="273"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -25684,13 +28373,13 @@
       <c r="E7" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="259" t="s">
+      <c r="F7" s="279" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="268" t="s">
+      <c r="J7" s="275" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -25736,11 +28425,11 @@
         <v>17</v>
       </c>
       <c r="E8" s="30"/>
-      <c r="F8" s="259"/>
+      <c r="F8" s="279"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="268"/>
+      <c r="J8" s="275"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -25785,7 +28474,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="269" t="s">
+      <c r="F9" s="276" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -25825,7 +28514,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="269"/>
+      <c r="F10" s="276"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -25952,7 +28641,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="262" t="s">
+      <c r="I13" s="280" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -25993,7 +28682,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="262"/>
+      <c r="I14" s="280"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -26028,7 +28717,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="262" t="s">
+      <c r="I15" s="280" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -26055,13 +28744,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="259" t="s">
+      <c r="A16" s="279" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="259" t="s">
+      <c r="B16" s="279" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="269" t="s">
+      <c r="C16" s="276" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -26071,7 +28760,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="262"/>
+      <c r="I16" s="280"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -26096,15 +28785,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="259"/>
-      <c r="B17" s="259"/>
-      <c r="C17" s="269"/>
+      <c r="A17" s="279"/>
+      <c r="B17" s="279"/>
+      <c r="C17" s="276"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="262" t="s">
+      <c r="I17" s="280" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -26139,7 +28828,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="262"/>
+      <c r="I18" s="280"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -26310,13 +28999,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="263" t="s">
+      <c r="A28" s="285" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="263"/>
-      <c r="C28" s="263"/>
-      <c r="D28" s="263"/>
-      <c r="E28" s="263"/>
+      <c r="B28" s="285"/>
+      <c r="C28" s="285"/>
+      <c r="D28" s="285"/>
+      <c r="E28" s="285"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -26376,7 +29065,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="267" t="s">
+      <c r="E30" s="274" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -26410,7 +29099,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="267"/>
+      <c r="E31" s="274"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -26438,7 +29127,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="267" t="s">
+      <c r="E32" s="274" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -26464,7 +29153,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="267"/>
+      <c r="E33" s="274"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -26486,7 +29175,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="266" t="s">
+      <c r="E34" s="272" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -26509,7 +29198,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="266"/>
+      <c r="E35" s="272"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -26529,7 +29218,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="267" t="s">
+      <c r="E36" s="274" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -26549,7 +29238,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="267"/>
+      <c r="E37" s="274"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -27079,29 +29768,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="I17:I18"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -27110,7 +29799,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABA1F0C-88EE-4709-944B-FB9B848CEC03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AP57"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -27133,18 +29822,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="193" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="275" t="s">
+      <c r="A1" s="294" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="276"/>
-      <c r="C1" s="276"/>
-      <c r="D1" s="276"/>
-      <c r="E1" s="276"/>
-      <c r="F1" s="276"/>
-      <c r="G1" s="276"/>
-      <c r="H1" s="276"/>
-      <c r="I1" s="277"/>
-      <c r="J1" s="277"/>
+      <c r="B1" s="295"/>
+      <c r="C1" s="295"/>
+      <c r="D1" s="295"/>
+      <c r="E1" s="295"/>
+      <c r="F1" s="295"/>
+      <c r="G1" s="295"/>
+      <c r="H1" s="295"/>
+      <c r="I1" s="296"/>
+      <c r="J1" s="296"/>
       <c r="K1" s="190"/>
       <c r="L1" s="190"/>
       <c r="M1" s="191"/>
@@ -27250,22 +29939,22 @@
       <c r="C3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="261" t="s">
+      <c r="D3" s="273" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="201" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="278" t="s">
+      <c r="F3" s="287" t="s">
         <v>160</v>
       </c>
       <c r="H3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="268" t="s">
+      <c r="I3" s="275" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="279" t="s">
+      <c r="K3" s="288" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="2"/>
@@ -27281,16 +29970,16 @@
       <c r="C4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="261"/>
+      <c r="D4" s="273"/>
       <c r="E4" s="201" t="s">
         <v>162</v>
       </c>
-      <c r="F4" s="278"/>
+      <c r="F4" s="287"/>
       <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="268"/>
-      <c r="K4" s="280"/>
+      <c r="I4" s="275"/>
+      <c r="K4" s="289"/>
       <c r="L4" s="203" t="s">
         <v>163</v>
       </c>
@@ -27303,13 +29992,13 @@
       <c r="E5" s="129" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="278" t="s">
+      <c r="F5" s="287" t="s">
         <v>165</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="261" t="s">
+      <c r="I5" s="273" t="s">
         <v>166</v>
       </c>
       <c r="K5" s="2"/>
@@ -27323,11 +30012,11 @@
       <c r="E6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="278"/>
+      <c r="F6" s="287"/>
       <c r="H6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="261"/>
+      <c r="I6" s="273"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -27342,10 +30031,10 @@
       <c r="E7" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F7" s="261" t="s">
+      <c r="F7" s="273" t="s">
         <v>168</v>
       </c>
-      <c r="I7" s="261" t="s">
+      <c r="I7" s="273" t="s">
         <v>15</v>
       </c>
       <c r="K7" s="2"/>
@@ -27359,17 +30048,17 @@
       <c r="E8" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="261"/>
-      <c r="I8" s="261"/>
+      <c r="F8" s="273"/>
+      <c r="I8" s="273"/>
       <c r="K8" s="2"/>
       <c r="L8" s="206"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="272" t="s">
+      <c r="A9" s="281" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="261" t="s">
+      <c r="B9" s="273" t="s">
         <v>171</v>
       </c>
       <c r="C9" s="207" t="s">
@@ -27378,7 +30067,7 @@
       <c r="E9" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="278" t="s">
+      <c r="F9" s="287" t="s">
         <v>173</v>
       </c>
       <c r="K9" s="2"/>
@@ -27388,15 +30077,15 @@
       <c r="P9"/>
     </row>
     <row r="10" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="273"/>
-      <c r="B10" s="261"/>
+      <c r="A10" s="282"/>
+      <c r="B10" s="273"/>
       <c r="C10" s="208" t="s">
         <v>174</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>175</v>
       </c>
-      <c r="F10" s="278"/>
+      <c r="F10" s="287"/>
       <c r="K10" s="209"/>
       <c r="L10" s="2"/>
       <c r="M10" s="206"/>
@@ -27423,7 +30112,7 @@
       <c r="E11" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="F11" s="259" t="s">
+      <c r="F11" s="279" t="s">
         <v>177</v>
       </c>
       <c r="K11" s="209"/>
@@ -27452,7 +30141,7 @@
       <c r="E12" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="259"/>
+      <c r="F12" s="279"/>
       <c r="G12" s="212" t="s">
         <v>179</v>
       </c>
@@ -27491,10 +30180,10 @@
       <c r="E13" s="183" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="281" t="s">
+      <c r="F13" s="290" t="s">
         <v>184</v>
       </c>
-      <c r="H13" s="272" t="s">
+      <c r="H13" s="281" t="s">
         <v>185</v>
       </c>
       <c r="K13" s="2"/>
@@ -27524,8 +30213,8 @@
       <c r="E14" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="F14" s="282"/>
-      <c r="H14" s="273"/>
+      <c r="F14" s="291"/>
+      <c r="H14" s="282"/>
       <c r="K14" s="2"/>
       <c r="L14" s="6"/>
       <c r="M14" s="2"/>
@@ -27552,10 +30241,10 @@
       <c r="E15" s="183" t="s">
         <v>189</v>
       </c>
-      <c r="F15" s="261" t="s">
+      <c r="F15" s="273" t="s">
         <v>190</v>
       </c>
-      <c r="H15" s="279" t="s">
+      <c r="H15" s="288" t="s">
         <v>45</v>
       </c>
       <c r="K15" s="2"/>
@@ -27580,8 +30269,8 @@
       <c r="C16" s="183" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="261"/>
-      <c r="H16" s="280"/>
+      <c r="F16" s="273"/>
+      <c r="H16" s="289"/>
       <c r="K16" s="2"/>
       <c r="L16" s="209"/>
       <c r="M16" s="8"/>
@@ -27608,7 +30297,7 @@
       </c>
       <c r="D17" s="206"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="283" t="s">
+      <c r="F17" s="292" t="s">
         <v>193</v>
       </c>
       <c r="G17" s="2"/>
@@ -27625,7 +30314,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="284"/>
+      <c r="F18" s="293"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="209"/>
@@ -27676,7 +30365,7 @@
       <c r="B20" s="133" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="261" t="s">
+      <c r="C20" s="273" t="s">
         <v>197</v>
       </c>
       <c r="D20" s="2"/>
@@ -27708,7 +30397,7 @@
         <v>199</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="261"/>
+      <c r="C21" s="273"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="219" t="s">
@@ -27716,7 +30405,7 @@
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="279" t="s">
+      <c r="I21" s="288" t="s">
         <v>82</v>
       </c>
       <c r="J21" s="209"/>
@@ -27750,7 +30439,7 @@
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="280"/>
+      <c r="I22" s="289"/>
       <c r="J22" s="209"/>
       <c r="K22" s="101" t="s">
         <v>40</v>
@@ -28480,11 +31169,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="F9:F10"/>
@@ -28495,11 +31184,11 @@
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="F17:F18"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -28507,7 +31196,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CC5DA19-72BD-43FC-9AE9-FEE55A4EC0CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -29419,21 +32108,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="284"/>
+      <c r="M1" s="284"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -29488,13 +32177,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="262" t="s">
+      <c r="D3" s="280" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="261" t="s">
+      <c r="F3" s="273" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -29503,24 +32192,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="262" t="s">
+      <c r="J3" s="280" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="285" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="270" t="s">
+      <c r="Q3" s="277" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="271"/>
+      <c r="R3" s="278"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="270" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="265"/>
+      <c r="U3" s="271"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -29534,20 +32223,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="262"/>
+      <c r="D4" s="280"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="261"/>
+      <c r="F4" s="273"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="262"/>
+      <c r="J4" s="280"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="285"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -29586,7 +32275,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="269" t="s">
+      <c r="F5" s="276" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -29594,7 +32283,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="261" t="s">
+      <c r="J5" s="273" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -29639,13 +32328,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="269"/>
+      <c r="F6" s="276"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="261"/>
+      <c r="J6" s="273"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -29689,13 +32378,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="259" t="s">
+      <c r="F7" s="279" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="268" t="s">
+      <c r="J7" s="275" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -29743,11 +32432,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="259"/>
+      <c r="F8" s="279"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="268"/>
+      <c r="J8" s="275"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -29792,7 +32481,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="269" t="s">
+      <c r="F9" s="276" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -29832,7 +32521,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="269"/>
+      <c r="F10" s="276"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -30054,13 +32743,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="259" t="s">
+      <c r="A16" s="279" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="259" t="s">
+      <c r="B16" s="279" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="262" t="s">
+      <c r="C16" s="280" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -30095,9 +32784,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="259"/>
-      <c r="B17" s="259"/>
-      <c r="C17" s="262"/>
+      <c r="A17" s="279"/>
+      <c r="B17" s="279"/>
+      <c r="C17" s="280"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -30307,13 +32996,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="263" t="s">
+      <c r="A28" s="285" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="263"/>
-      <c r="C28" s="263"/>
-      <c r="D28" s="263"/>
-      <c r="E28" s="263"/>
+      <c r="B28" s="285"/>
+      <c r="C28" s="285"/>
+      <c r="D28" s="285"/>
+      <c r="E28" s="285"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -30373,7 +33062,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="267" t="s">
+      <c r="E30" s="274" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -30405,7 +33094,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="267"/>
+      <c r="E31" s="274"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -30433,7 +33122,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="267" t="s">
+      <c r="E32" s="274" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -30461,7 +33150,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="267"/>
+      <c r="E33" s="274"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -30485,7 +33174,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="266" t="s">
+      <c r="E34" s="272" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -30508,7 +33197,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="266"/>
+      <c r="E35" s="272"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -30528,7 +33217,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="267" t="s">
+      <c r="E36" s="274" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -30548,7 +33237,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="267"/>
+      <c r="E37" s="274"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -31076,26 +33765,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="F9:F10"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -31104,7 +33793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C36E9801-E4AE-4274-9B6A-11A36D735737}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -32013,21 +34702,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="284" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="260"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="284"/>
+      <c r="M1" s="284"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -32082,13 +34771,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="262" t="s">
+      <c r="D3" s="280" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="261" t="s">
+      <c r="F3" s="273" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -32097,24 +34786,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="262" t="s">
+      <c r="J3" s="280" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="285" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="270" t="s">
+      <c r="Q3" s="277" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="271"/>
+      <c r="R3" s="278"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="264" t="s">
+      <c r="T3" s="270" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="265"/>
+      <c r="U3" s="271"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -32128,20 +34817,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="262"/>
+      <c r="D4" s="280"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="261"/>
+      <c r="F4" s="273"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="262"/>
+      <c r="J4" s="280"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="285"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -32180,7 +34869,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="269" t="s">
+      <c r="F5" s="276" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -32188,7 +34877,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="261" t="s">
+      <c r="J5" s="273" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -32233,13 +34922,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="269"/>
+      <c r="F6" s="276"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="261"/>
+      <c r="J6" s="273"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -32283,13 +34972,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="259" t="s">
+      <c r="F7" s="279" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="268" t="s">
+      <c r="J7" s="275" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -32337,11 +35026,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="259"/>
+      <c r="F8" s="279"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="268"/>
+      <c r="J8" s="275"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -32386,7 +35075,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="269" t="s">
+      <c r="F9" s="276" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -32426,7 +35115,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="269"/>
+      <c r="F10" s="276"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -32648,13 +35337,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="259" t="s">
+      <c r="A16" s="279" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="259" t="s">
+      <c r="B16" s="279" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="262" t="s">
+      <c r="C16" s="280" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -32689,9 +35378,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="259"/>
-      <c r="B17" s="259"/>
-      <c r="C17" s="262"/>
+      <c r="A17" s="279"/>
+      <c r="B17" s="279"/>
+      <c r="C17" s="280"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -32901,13 +35590,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="263" t="s">
+      <c r="A28" s="285" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="263"/>
-      <c r="C28" s="263"/>
-      <c r="D28" s="263"/>
-      <c r="E28" s="263"/>
+      <c r="B28" s="285"/>
+      <c r="C28" s="285"/>
+      <c r="D28" s="285"/>
+      <c r="E28" s="285"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -32967,7 +35656,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="267" t="s">
+      <c r="E30" s="274" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -33001,7 +35690,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="267"/>
+      <c r="E31" s="274"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -33029,7 +35718,7 @@
       <c r="D32" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="267" t="s">
+      <c r="E32" s="274" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -33057,7 +35746,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="267"/>
+      <c r="E33" s="274"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -33081,7 +35770,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="266" t="s">
+      <c r="E34" s="272" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -33106,7 +35795,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="266"/>
+      <c r="E35" s="272"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -33128,7 +35817,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="267" t="s">
+      <c r="E36" s="274" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -33150,7 +35839,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="267"/>
+      <c r="E37" s="274"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -33678,18 +36367,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="A16:A17"/>
@@ -33698,6 +36375,18 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/raw/D3.xlsx
+++ b/raw/D3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="12"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="4" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="30-2" sheetId="34" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="17-2" sheetId="44" r:id="rId11"/>
     <sheet name="18" sheetId="45" r:id="rId12"/>
     <sheet name="19" sheetId="46" r:id="rId13"/>
+    <sheet name="20" sheetId="47" r:id="rId14"/>
+    <sheet name="20-2" sheetId="48" r:id="rId15"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -283,6 +285,118 @@
 </file>
 
 <file path=xl/comments13.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="J7" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Алібек
+87012894507</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I13" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Аслан
+87014988298</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Даулет
+87025167087</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="J7" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Алібек
+87012894507</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Даулет
+87025167087</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Аслан
+87014988298</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments15.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Автор</author>
@@ -1034,7 +1148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="272">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -1772,6 +1886,84 @@
   </si>
   <si>
     <t>31-H3134/12</t>
+  </si>
+  <si>
+    <t>31-H3205/12</t>
+  </si>
+  <si>
+    <t>31-Н3013/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31-863AI/12  </t>
+  </si>
+  <si>
+    <t>31-Н3445/12 н</t>
+  </si>
+  <si>
+    <t>31-Н3015/12 н</t>
+  </si>
+  <si>
+    <t>31-Н2978/12н</t>
+  </si>
+  <si>
+    <t>31-Н3152/12н</t>
+  </si>
+  <si>
+    <t>31-Н3162/12 н</t>
+  </si>
+  <si>
+    <t>31-Н3205/12 н</t>
+  </si>
+  <si>
+    <t>31-Н3474/12н</t>
+  </si>
+  <si>
+    <t>31-Н1559/12н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22-H194212      25-ВАА13/12   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22-H3051/12     25-44AZA12 </t>
+  </si>
+  <si>
+    <t>22-H265112      25-Н012/12 н</t>
+  </si>
+  <si>
+    <t>22-H3036/12     26-Н013/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22-H2862/12     25-Н017/12 н </t>
+  </si>
+  <si>
+    <t>24-Н3634/12</t>
+  </si>
+  <si>
+    <t>24-Н3649/12</t>
+  </si>
+  <si>
+    <t>24-Н3625/12</t>
+  </si>
+  <si>
+    <t>49-Н1507/12 н</t>
+  </si>
+  <si>
+    <t>49-Н1801/12 н</t>
+  </si>
+  <si>
+    <t>49-Н3390/12н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49-166AG/12 н  </t>
+  </si>
+  <si>
+    <t>24-Н3603/12 н</t>
+  </si>
+  <si>
+    <t>24-Н3575/12н</t>
+  </si>
+  <si>
+    <t>24-Н3598/12 н</t>
   </si>
 </sst>
 </file>
@@ -2592,7 +2784,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="299">
+  <cellXfs count="307">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3370,6 +3562,30 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4651,21 +4867,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="292" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
-      <c r="M1" s="284"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4720,13 +4936,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="273" t="s">
+      <c r="D3" s="281" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="273" t="s">
+      <c r="F3" s="281" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -4738,24 +4954,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="279" t="s">
+      <c r="J3" s="287" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="280" t="s">
+      <c r="M3" s="288" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="277" t="s">
+      <c r="Q3" s="285" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="278"/>
+      <c r="R3" s="286"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="270" t="s">
+      <c r="T3" s="278" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="271"/>
+      <c r="U3" s="279"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -4767,20 +4983,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="273"/>
+      <c r="D4" s="281"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="273"/>
+      <c r="F4" s="281"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="279"/>
+      <c r="J4" s="287"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="280"/>
+      <c r="M4" s="288"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -4819,7 +5035,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="276" t="s">
+      <c r="F5" s="284" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -4827,7 +5043,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="273" t="s">
+      <c r="J5" s="281" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -4872,13 +5088,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="276"/>
+      <c r="F6" s="284"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="273"/>
+      <c r="J6" s="281"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -4924,13 +5140,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="279" t="s">
+      <c r="F7" s="287" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="275" t="s">
+      <c r="J7" s="283" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -4978,11 +5194,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="279"/>
+      <c r="F8" s="287"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="275"/>
+      <c r="J8" s="283"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -5026,7 +5242,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="276" t="s">
+      <c r="F9" s="284" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -5066,7 +5282,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="276"/>
+      <c r="F10" s="284"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -5191,7 +5407,7 @@
         <v>115</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="280" t="s">
+      <c r="H13" s="288" t="s">
         <v>82</v>
       </c>
       <c r="I13" s="30"/>
@@ -5230,7 +5446,7 @@
       <c r="F14" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="280"/>
+      <c r="H14" s="288"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -5265,7 +5481,7 @@
         <v>83</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="280" t="s">
+      <c r="H15" s="288" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="30"/>
@@ -5302,7 +5518,7 @@
         <v>81</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="280"/>
+      <c r="H16" s="288"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -5334,7 +5550,7 @@
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="281" t="s">
+      <c r="H17" s="289" t="s">
         <v>45</v>
       </c>
       <c r="I17" s="30"/>
@@ -5369,7 +5585,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="282"/>
+      <c r="H18" s="290"/>
       <c r="I18" s="30"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
@@ -5386,7 +5602,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="279" t="s">
+      <c r="H19" s="287" t="s">
         <v>85</v>
       </c>
       <c r="I19" s="30"/>
@@ -5411,7 +5627,7 @@
       <c r="E20" s="137"/>
       <c r="F20" s="8"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="279"/>
+      <c r="H20" s="287"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -5430,7 +5646,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="279" t="s">
+      <c r="H21" s="287" t="s">
         <v>84</v>
       </c>
       <c r="I21" s="30"/>
@@ -5447,7 +5663,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="137"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="279"/>
+      <c r="H22" s="287"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -5544,13 +5760,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="285" t="s">
+      <c r="A28" s="293" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="285"/>
-      <c r="C28" s="285"/>
-      <c r="D28" s="285"/>
-      <c r="E28" s="285"/>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -5610,7 +5826,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="274" t="s">
+      <c r="E30" s="282" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -5644,7 +5860,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="274"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -5674,7 +5890,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="274" t="s">
+      <c r="E32" s="282" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="8"/>
@@ -5700,7 +5916,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="274"/>
+      <c r="E33" s="282"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
       <c r="I33" s="30"/>
@@ -5723,7 +5939,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="272" t="s">
+      <c r="E34" s="280" t="s">
         <v>133</v>
       </c>
       <c r="G34" s="8"/>
@@ -5744,7 +5960,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="272"/>
+      <c r="E35" s="280"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
       <c r="I35" s="30"/>
@@ -5763,7 +5979,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="274" t="s">
+      <c r="E36" s="282" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -5783,7 +5999,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="274"/>
+      <c r="E37" s="282"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -6250,7 +6466,7 @@
       <c r="S65"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A66" s="283" t="s">
+      <c r="A66" s="291" t="s">
         <v>139</v>
       </c>
       <c r="L66" s="119" t="s">
@@ -6262,7 +6478,7 @@
       <c r="S66"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A67" s="283"/>
+      <c r="A67" s="291"/>
       <c r="L67" s="119" t="s">
         <v>95</v>
       </c>
@@ -7253,21 +7469,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="292" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
-      <c r="M1" s="284"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -7326,7 +7542,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="273" t="s">
+      <c r="F3" s="281" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -7335,24 +7551,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="275" t="s">
+      <c r="J3" s="283" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="305" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="277" t="s">
+      <c r="Q3" s="285" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="278"/>
+      <c r="R3" s="286"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="270" t="s">
+      <c r="T3" s="278" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="271"/>
+      <c r="U3" s="279"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -7370,16 +7586,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="273"/>
+      <c r="F4" s="281"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="275"/>
+      <c r="J4" s="283"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="305"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -7418,7 +7634,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="276" t="s">
+      <c r="F5" s="284" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -7426,7 +7642,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="273" t="s">
+      <c r="J5" s="281" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -7471,13 +7687,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="276"/>
+      <c r="F6" s="284"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="273"/>
+      <c r="J6" s="281"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -7524,7 +7740,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="276" t="s">
+      <c r="F7" s="284" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -7576,7 +7792,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="276"/>
+      <c r="F8" s="284"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -7792,7 +8008,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="279" t="s">
+      <c r="H13" s="287" t="s">
         <v>121</v>
       </c>
       <c r="I13" s="30"/>
@@ -7828,7 +8044,7 @@
       <c r="F14" s="240" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="279"/>
+      <c r="H14" s="287"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -7861,7 +8077,7 @@
       <c r="E15" s="240"/>
       <c r="F15" s="8"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="279" t="s">
+      <c r="H15" s="287" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="30"/>
@@ -7890,7 +8106,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="279" t="s">
+      <c r="B16" s="287" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="8"/>
@@ -7898,7 +8114,7 @@
       <c r="E16" s="59"/>
       <c r="F16" s="8"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="279"/>
+      <c r="H16" s="287"/>
       <c r="I16" s="30"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
@@ -7925,13 +8141,13 @@
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
-      <c r="B17" s="279"/>
+      <c r="B17" s="287"/>
       <c r="C17" s="8"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="280" t="s">
+      <c r="H17" s="288" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -7966,7 +8182,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="280"/>
+      <c r="H18" s="288"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -7983,7 +8199,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="280" t="s">
+      <c r="H19" s="288" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -8008,7 +8224,7 @@
       <c r="E20" s="240"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="280"/>
+      <c r="H20" s="288"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -8027,7 +8243,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="280" t="s">
+      <c r="H21" s="288" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -8045,7 +8261,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="240"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="280"/>
+      <c r="H22" s="288"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -8142,13 +8358,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="285" t="s">
+      <c r="A28" s="293" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="285"/>
-      <c r="C28" s="285"/>
-      <c r="D28" s="285"/>
-      <c r="E28" s="285"/>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -8208,7 +8424,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="274" t="s">
+      <c r="E30" s="282" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -8242,7 +8458,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="274"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -8269,7 +8485,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="274" t="s">
+      <c r="E32" s="282" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -8297,7 +8513,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="274"/>
+      <c r="E33" s="282"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -8321,7 +8537,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="272" t="s">
+      <c r="E34" s="280" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -8346,7 +8562,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="272"/>
+      <c r="E35" s="280"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -8368,7 +8584,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="274" t="s">
+      <c r="E36" s="282" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -8390,7 +8606,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="274"/>
+      <c r="E37" s="282"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -9858,21 +10074,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="292" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
-      <c r="M1" s="284"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -9931,7 +10147,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="273" t="s">
+      <c r="F3" s="281" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -9940,24 +10156,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="275" t="s">
+      <c r="J3" s="283" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="280" t="s">
+      <c r="M3" s="288" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="277" t="s">
+      <c r="Q3" s="285" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="278"/>
+      <c r="R3" s="286"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="270" t="s">
+      <c r="T3" s="278" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="271"/>
+      <c r="U3" s="279"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -9975,16 +10191,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="273"/>
+      <c r="F4" s="281"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="275"/>
+      <c r="J4" s="283"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="280"/>
+      <c r="M4" s="288"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -10023,7 +10239,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="276" t="s">
+      <c r="F5" s="284" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -10031,7 +10247,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="273" t="s">
+      <c r="J5" s="281" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -10076,13 +10292,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="276"/>
+      <c r="F6" s="284"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="273"/>
+      <c r="J6" s="281"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -10129,7 +10345,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="276" t="s">
+      <c r="F7" s="284" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -10181,7 +10397,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="276"/>
+      <c r="F8" s="284"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -10397,7 +10613,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="279" t="s">
+      <c r="H13" s="287" t="s">
         <v>121</v>
       </c>
       <c r="I13" s="30"/>
@@ -10433,7 +10649,7 @@
       <c r="F14" s="248" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="279"/>
+      <c r="H14" s="287"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -10466,7 +10682,7 @@
       <c r="E15" s="248"/>
       <c r="F15" s="8"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="279" t="s">
+      <c r="H15" s="287" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="30"/>
@@ -10495,7 +10711,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="279" t="s">
+      <c r="B16" s="287" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="8"/>
@@ -10503,7 +10719,7 @@
       <c r="E16" s="59"/>
       <c r="F16" s="8"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="279"/>
+      <c r="H16" s="287"/>
       <c r="I16" s="30"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
@@ -10530,13 +10746,13 @@
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
-      <c r="B17" s="279"/>
+      <c r="B17" s="287"/>
       <c r="C17" s="8"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="280" t="s">
+      <c r="H17" s="288" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -10571,7 +10787,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="280"/>
+      <c r="H18" s="288"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -10588,7 +10804,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="280" t="s">
+      <c r="H19" s="288" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -10613,7 +10829,7 @@
       <c r="E20" s="248"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="280"/>
+      <c r="H20" s="288"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -10632,7 +10848,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="280" t="s">
+      <c r="H21" s="288" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -10650,7 +10866,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="248"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="280"/>
+      <c r="H22" s="288"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -10747,13 +10963,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="285" t="s">
+      <c r="A28" s="293" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="285"/>
-      <c r="C28" s="285"/>
-      <c r="D28" s="285"/>
-      <c r="E28" s="285"/>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -10813,7 +11029,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="274" t="s">
+      <c r="E30" s="282" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -10847,7 +11063,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="274"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -10877,7 +11093,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="274" t="s">
+      <c r="E32" s="282" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -10905,7 +11121,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="274"/>
+      <c r="E33" s="282"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -10929,7 +11145,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="272" t="s">
+      <c r="E34" s="280" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -10953,7 +11169,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="272"/>
+      <c r="E35" s="280"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -10975,7 +11191,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="274" t="s">
+      <c r="E36" s="282" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -10995,7 +11211,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="274"/>
+      <c r="E37" s="282"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -12463,21 +12679,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="292" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
-      <c r="M1" s="284"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -12532,13 +12748,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="280" t="s">
+      <c r="D3" s="288" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="273" t="s">
+      <c r="F3" s="281" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -12547,24 +12763,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="275" t="s">
+      <c r="J3" s="283" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="280" t="s">
+      <c r="M3" s="288" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="277" t="s">
+      <c r="Q3" s="285" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="278"/>
+      <c r="R3" s="286"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="270" t="s">
+      <c r="T3" s="278" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="271"/>
+      <c r="U3" s="279"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -12578,20 +12794,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="280"/>
+      <c r="D4" s="288"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="273"/>
+      <c r="F4" s="281"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="275"/>
+      <c r="J4" s="283"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="280"/>
+      <c r="M4" s="288"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -12630,7 +12846,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="276" t="s">
+      <c r="F5" s="284" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -12638,7 +12854,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="273" t="s">
+      <c r="J5" s="281" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -12683,13 +12899,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="276"/>
+      <c r="F6" s="284"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="273"/>
+      <c r="J6" s="281"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -12736,13 +12952,13 @@
       <c r="E7" s="260" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="298" t="s">
+      <c r="F7" s="306" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="280" t="s">
+      <c r="J7" s="288" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -12790,11 +13006,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="298"/>
+      <c r="F8" s="306"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="280"/>
+      <c r="J8" s="288"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -12839,7 +13055,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="279" t="s">
+      <c r="F9" s="287" t="s">
         <v>121</v>
       </c>
       <c r="G9" s="64"/>
@@ -12879,7 +13095,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="279"/>
+      <c r="F10" s="287"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -13099,13 +13315,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="279" t="s">
+      <c r="A16" s="287" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="279" t="s">
+      <c r="B16" s="287" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="280" t="s">
+      <c r="C16" s="288" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -13140,9 +13356,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="279"/>
-      <c r="B17" s="279"/>
-      <c r="C17" s="280"/>
+      <c r="A17" s="287"/>
+      <c r="B17" s="287"/>
+      <c r="C17" s="288"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="259" t="s">
@@ -13353,13 +13569,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="285" t="s">
+      <c r="A28" s="293" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="285"/>
-      <c r="C28" s="285"/>
-      <c r="D28" s="285"/>
-      <c r="E28" s="285"/>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -13419,7 +13635,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="274" t="s">
+      <c r="E30" s="282" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -13453,7 +13669,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="274"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -13483,7 +13699,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="274" t="s">
+      <c r="E32" s="282" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -13513,7 +13729,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="274"/>
+      <c r="E33" s="282"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -13537,7 +13753,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="272" t="s">
+      <c r="E34" s="280" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -13561,7 +13777,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="272"/>
+      <c r="E35" s="280"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -13580,7 +13796,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="274" t="s">
+      <c r="E36" s="282" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -13600,7 +13816,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="274"/>
+      <c r="E37" s="282"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -15066,21 +15282,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="292" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
-      <c r="M1" s="284"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -15135,13 +15351,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="273" t="s">
+      <c r="D3" s="281" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="273" t="s">
+      <c r="F3" s="281" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -15150,24 +15366,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="275" t="s">
+      <c r="J3" s="283" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="280" t="s">
+      <c r="M3" s="288" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="277" t="s">
+      <c r="Q3" s="285" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="278"/>
+      <c r="R3" s="286"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="270" t="s">
+      <c r="T3" s="278" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="271"/>
+      <c r="U3" s="279"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -15181,20 +15397,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="273"/>
+      <c r="D4" s="281"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="273"/>
+      <c r="F4" s="281"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="275"/>
+      <c r="J4" s="283"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="280"/>
+      <c r="M4" s="288"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -15233,7 +15449,7 @@
       <c r="E5" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="F5" s="276" t="s">
+      <c r="F5" s="284" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -15241,7 +15457,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="273" t="s">
+      <c r="J5" s="281" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -15286,13 +15502,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="276"/>
+      <c r="F6" s="284"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="273"/>
+      <c r="J6" s="281"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -15339,13 +15555,13 @@
       <c r="E7" s="260" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="298" t="s">
+      <c r="F7" s="306" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="280" t="s">
+      <c r="J7" s="288" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -15393,11 +15609,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="298"/>
+      <c r="F8" s="306"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="280"/>
+      <c r="J8" s="288"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -15442,7 +15658,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="279" t="s">
+      <c r="F9" s="287" t="s">
         <v>121</v>
       </c>
       <c r="G9" s="64"/>
@@ -15482,7 +15698,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="279"/>
+      <c r="F10" s="287"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -15609,7 +15825,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="280" t="s">
+      <c r="I13" s="288" t="s">
         <v>45</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -15645,7 +15861,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="280"/>
+      <c r="I14" s="288"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -15705,13 +15921,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="279" t="s">
+      <c r="A16" s="287" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="279" t="s">
+      <c r="B16" s="287" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="280" t="s">
+      <c r="C16" s="288" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -15746,9 +15962,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="279"/>
-      <c r="B17" s="279"/>
-      <c r="C17" s="280"/>
+      <c r="A17" s="287"/>
+      <c r="B17" s="287"/>
+      <c r="C17" s="288"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="269" t="s">
@@ -15959,13 +16175,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="285" t="s">
+      <c r="A28" s="293" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="285"/>
-      <c r="C28" s="285"/>
-      <c r="D28" s="285"/>
-      <c r="E28" s="285"/>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -16025,7 +16241,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="274" t="s">
+      <c r="E30" s="282" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -16059,7 +16275,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="274"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -16087,7 +16303,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="274" t="s">
+      <c r="E32" s="282" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -16115,7 +16331,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="274"/>
+      <c r="E33" s="282"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -16139,7 +16355,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="272" t="s">
+      <c r="E34" s="280" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -16161,7 +16377,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="272"/>
+      <c r="E35" s="280"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -16181,7 +16397,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="274" t="s">
+      <c r="E36" s="282" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -16201,7 +16417,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="274"/>
+      <c r="E37" s="282"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -16756,6 +16972,5214 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:W72"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" style="98" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" style="25" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" style="25" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" style="25" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" customWidth="1"/>
+    <col min="14" max="14" width="21.26953125" customWidth="1"/>
+    <col min="15" max="15" width="9.7265625" customWidth="1"/>
+    <col min="16" max="16" width="7.7265625" customWidth="1"/>
+    <col min="17" max="17" width="6.453125" customWidth="1"/>
+    <col min="18" max="18" width="7.81640625" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" style="84" customWidth="1"/>
+    <col min="20" max="20" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="257" max="260" width="14.453125" customWidth="1"/>
+    <col min="261" max="261" width="15.453125" customWidth="1"/>
+    <col min="262" max="262" width="14.54296875" customWidth="1"/>
+    <col min="263" max="263" width="15.26953125" customWidth="1"/>
+    <col min="264" max="265" width="14.453125" customWidth="1"/>
+    <col min="266" max="266" width="13.1796875" customWidth="1"/>
+    <col min="267" max="269" width="14.453125" customWidth="1"/>
+    <col min="270" max="270" width="15.81640625" customWidth="1"/>
+    <col min="271" max="271" width="7.81640625" customWidth="1"/>
+    <col min="272" max="272" width="5.453125" customWidth="1"/>
+    <col min="273" max="273" width="6.453125" customWidth="1"/>
+    <col min="274" max="274" width="7.81640625" customWidth="1"/>
+    <col min="275" max="275" width="3" customWidth="1"/>
+    <col min="276" max="276" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="513" max="516" width="14.453125" customWidth="1"/>
+    <col min="517" max="517" width="15.453125" customWidth="1"/>
+    <col min="518" max="518" width="14.54296875" customWidth="1"/>
+    <col min="519" max="519" width="15.26953125" customWidth="1"/>
+    <col min="520" max="521" width="14.453125" customWidth="1"/>
+    <col min="522" max="522" width="13.1796875" customWidth="1"/>
+    <col min="523" max="525" width="14.453125" customWidth="1"/>
+    <col min="526" max="526" width="15.81640625" customWidth="1"/>
+    <col min="527" max="527" width="7.81640625" customWidth="1"/>
+    <col min="528" max="528" width="5.453125" customWidth="1"/>
+    <col min="529" max="529" width="6.453125" customWidth="1"/>
+    <col min="530" max="530" width="7.81640625" customWidth="1"/>
+    <col min="531" max="531" width="3" customWidth="1"/>
+    <col min="532" max="532" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="769" max="772" width="14.453125" customWidth="1"/>
+    <col min="773" max="773" width="15.453125" customWidth="1"/>
+    <col min="774" max="774" width="14.54296875" customWidth="1"/>
+    <col min="775" max="775" width="15.26953125" customWidth="1"/>
+    <col min="776" max="777" width="14.453125" customWidth="1"/>
+    <col min="778" max="778" width="13.1796875" customWidth="1"/>
+    <col min="779" max="781" width="14.453125" customWidth="1"/>
+    <col min="782" max="782" width="15.81640625" customWidth="1"/>
+    <col min="783" max="783" width="7.81640625" customWidth="1"/>
+    <col min="784" max="784" width="5.453125" customWidth="1"/>
+    <col min="785" max="785" width="6.453125" customWidth="1"/>
+    <col min="786" max="786" width="7.81640625" customWidth="1"/>
+    <col min="787" max="787" width="3" customWidth="1"/>
+    <col min="788" max="788" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1025" max="1028" width="14.453125" customWidth="1"/>
+    <col min="1029" max="1029" width="15.453125" customWidth="1"/>
+    <col min="1030" max="1030" width="14.54296875" customWidth="1"/>
+    <col min="1031" max="1031" width="15.26953125" customWidth="1"/>
+    <col min="1032" max="1033" width="14.453125" customWidth="1"/>
+    <col min="1034" max="1034" width="13.1796875" customWidth="1"/>
+    <col min="1035" max="1037" width="14.453125" customWidth="1"/>
+    <col min="1038" max="1038" width="15.81640625" customWidth="1"/>
+    <col min="1039" max="1039" width="7.81640625" customWidth="1"/>
+    <col min="1040" max="1040" width="5.453125" customWidth="1"/>
+    <col min="1041" max="1041" width="6.453125" customWidth="1"/>
+    <col min="1042" max="1042" width="7.81640625" customWidth="1"/>
+    <col min="1043" max="1043" width="3" customWidth="1"/>
+    <col min="1044" max="1044" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1281" max="1284" width="14.453125" customWidth="1"/>
+    <col min="1285" max="1285" width="15.453125" customWidth="1"/>
+    <col min="1286" max="1286" width="14.54296875" customWidth="1"/>
+    <col min="1287" max="1287" width="15.26953125" customWidth="1"/>
+    <col min="1288" max="1289" width="14.453125" customWidth="1"/>
+    <col min="1290" max="1290" width="13.1796875" customWidth="1"/>
+    <col min="1291" max="1293" width="14.453125" customWidth="1"/>
+    <col min="1294" max="1294" width="15.81640625" customWidth="1"/>
+    <col min="1295" max="1295" width="7.81640625" customWidth="1"/>
+    <col min="1296" max="1296" width="5.453125" customWidth="1"/>
+    <col min="1297" max="1297" width="6.453125" customWidth="1"/>
+    <col min="1298" max="1298" width="7.81640625" customWidth="1"/>
+    <col min="1299" max="1299" width="3" customWidth="1"/>
+    <col min="1300" max="1300" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1537" max="1540" width="14.453125" customWidth="1"/>
+    <col min="1541" max="1541" width="15.453125" customWidth="1"/>
+    <col min="1542" max="1542" width="14.54296875" customWidth="1"/>
+    <col min="1543" max="1543" width="15.26953125" customWidth="1"/>
+    <col min="1544" max="1545" width="14.453125" customWidth="1"/>
+    <col min="1546" max="1546" width="13.1796875" customWidth="1"/>
+    <col min="1547" max="1549" width="14.453125" customWidth="1"/>
+    <col min="1550" max="1550" width="15.81640625" customWidth="1"/>
+    <col min="1551" max="1551" width="7.81640625" customWidth="1"/>
+    <col min="1552" max="1552" width="5.453125" customWidth="1"/>
+    <col min="1553" max="1553" width="6.453125" customWidth="1"/>
+    <col min="1554" max="1554" width="7.81640625" customWidth="1"/>
+    <col min="1555" max="1555" width="3" customWidth="1"/>
+    <col min="1556" max="1556" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1793" max="1796" width="14.453125" customWidth="1"/>
+    <col min="1797" max="1797" width="15.453125" customWidth="1"/>
+    <col min="1798" max="1798" width="14.54296875" customWidth="1"/>
+    <col min="1799" max="1799" width="15.26953125" customWidth="1"/>
+    <col min="1800" max="1801" width="14.453125" customWidth="1"/>
+    <col min="1802" max="1802" width="13.1796875" customWidth="1"/>
+    <col min="1803" max="1805" width="14.453125" customWidth="1"/>
+    <col min="1806" max="1806" width="15.81640625" customWidth="1"/>
+    <col min="1807" max="1807" width="7.81640625" customWidth="1"/>
+    <col min="1808" max="1808" width="5.453125" customWidth="1"/>
+    <col min="1809" max="1809" width="6.453125" customWidth="1"/>
+    <col min="1810" max="1810" width="7.81640625" customWidth="1"/>
+    <col min="1811" max="1811" width="3" customWidth="1"/>
+    <col min="1812" max="1812" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2049" max="2052" width="14.453125" customWidth="1"/>
+    <col min="2053" max="2053" width="15.453125" customWidth="1"/>
+    <col min="2054" max="2054" width="14.54296875" customWidth="1"/>
+    <col min="2055" max="2055" width="15.26953125" customWidth="1"/>
+    <col min="2056" max="2057" width="14.453125" customWidth="1"/>
+    <col min="2058" max="2058" width="13.1796875" customWidth="1"/>
+    <col min="2059" max="2061" width="14.453125" customWidth="1"/>
+    <col min="2062" max="2062" width="15.81640625" customWidth="1"/>
+    <col min="2063" max="2063" width="7.81640625" customWidth="1"/>
+    <col min="2064" max="2064" width="5.453125" customWidth="1"/>
+    <col min="2065" max="2065" width="6.453125" customWidth="1"/>
+    <col min="2066" max="2066" width="7.81640625" customWidth="1"/>
+    <col min="2067" max="2067" width="3" customWidth="1"/>
+    <col min="2068" max="2068" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2305" max="2308" width="14.453125" customWidth="1"/>
+    <col min="2309" max="2309" width="15.453125" customWidth="1"/>
+    <col min="2310" max="2310" width="14.54296875" customWidth="1"/>
+    <col min="2311" max="2311" width="15.26953125" customWidth="1"/>
+    <col min="2312" max="2313" width="14.453125" customWidth="1"/>
+    <col min="2314" max="2314" width="13.1796875" customWidth="1"/>
+    <col min="2315" max="2317" width="14.453125" customWidth="1"/>
+    <col min="2318" max="2318" width="15.81640625" customWidth="1"/>
+    <col min="2319" max="2319" width="7.81640625" customWidth="1"/>
+    <col min="2320" max="2320" width="5.453125" customWidth="1"/>
+    <col min="2321" max="2321" width="6.453125" customWidth="1"/>
+    <col min="2322" max="2322" width="7.81640625" customWidth="1"/>
+    <col min="2323" max="2323" width="3" customWidth="1"/>
+    <col min="2324" max="2324" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2561" max="2564" width="14.453125" customWidth="1"/>
+    <col min="2565" max="2565" width="15.453125" customWidth="1"/>
+    <col min="2566" max="2566" width="14.54296875" customWidth="1"/>
+    <col min="2567" max="2567" width="15.26953125" customWidth="1"/>
+    <col min="2568" max="2569" width="14.453125" customWidth="1"/>
+    <col min="2570" max="2570" width="13.1796875" customWidth="1"/>
+    <col min="2571" max="2573" width="14.453125" customWidth="1"/>
+    <col min="2574" max="2574" width="15.81640625" customWidth="1"/>
+    <col min="2575" max="2575" width="7.81640625" customWidth="1"/>
+    <col min="2576" max="2576" width="5.453125" customWidth="1"/>
+    <col min="2577" max="2577" width="6.453125" customWidth="1"/>
+    <col min="2578" max="2578" width="7.81640625" customWidth="1"/>
+    <col min="2579" max="2579" width="3" customWidth="1"/>
+    <col min="2580" max="2580" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2817" max="2820" width="14.453125" customWidth="1"/>
+    <col min="2821" max="2821" width="15.453125" customWidth="1"/>
+    <col min="2822" max="2822" width="14.54296875" customWidth="1"/>
+    <col min="2823" max="2823" width="15.26953125" customWidth="1"/>
+    <col min="2824" max="2825" width="14.453125" customWidth="1"/>
+    <col min="2826" max="2826" width="13.1796875" customWidth="1"/>
+    <col min="2827" max="2829" width="14.453125" customWidth="1"/>
+    <col min="2830" max="2830" width="15.81640625" customWidth="1"/>
+    <col min="2831" max="2831" width="7.81640625" customWidth="1"/>
+    <col min="2832" max="2832" width="5.453125" customWidth="1"/>
+    <col min="2833" max="2833" width="6.453125" customWidth="1"/>
+    <col min="2834" max="2834" width="7.81640625" customWidth="1"/>
+    <col min="2835" max="2835" width="3" customWidth="1"/>
+    <col min="2836" max="2836" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3073" max="3076" width="14.453125" customWidth="1"/>
+    <col min="3077" max="3077" width="15.453125" customWidth="1"/>
+    <col min="3078" max="3078" width="14.54296875" customWidth="1"/>
+    <col min="3079" max="3079" width="15.26953125" customWidth="1"/>
+    <col min="3080" max="3081" width="14.453125" customWidth="1"/>
+    <col min="3082" max="3082" width="13.1796875" customWidth="1"/>
+    <col min="3083" max="3085" width="14.453125" customWidth="1"/>
+    <col min="3086" max="3086" width="15.81640625" customWidth="1"/>
+    <col min="3087" max="3087" width="7.81640625" customWidth="1"/>
+    <col min="3088" max="3088" width="5.453125" customWidth="1"/>
+    <col min="3089" max="3089" width="6.453125" customWidth="1"/>
+    <col min="3090" max="3090" width="7.81640625" customWidth="1"/>
+    <col min="3091" max="3091" width="3" customWidth="1"/>
+    <col min="3092" max="3092" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3329" max="3332" width="14.453125" customWidth="1"/>
+    <col min="3333" max="3333" width="15.453125" customWidth="1"/>
+    <col min="3334" max="3334" width="14.54296875" customWidth="1"/>
+    <col min="3335" max="3335" width="15.26953125" customWidth="1"/>
+    <col min="3336" max="3337" width="14.453125" customWidth="1"/>
+    <col min="3338" max="3338" width="13.1796875" customWidth="1"/>
+    <col min="3339" max="3341" width="14.453125" customWidth="1"/>
+    <col min="3342" max="3342" width="15.81640625" customWidth="1"/>
+    <col min="3343" max="3343" width="7.81640625" customWidth="1"/>
+    <col min="3344" max="3344" width="5.453125" customWidth="1"/>
+    <col min="3345" max="3345" width="6.453125" customWidth="1"/>
+    <col min="3346" max="3346" width="7.81640625" customWidth="1"/>
+    <col min="3347" max="3347" width="3" customWidth="1"/>
+    <col min="3348" max="3348" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3585" max="3588" width="14.453125" customWidth="1"/>
+    <col min="3589" max="3589" width="15.453125" customWidth="1"/>
+    <col min="3590" max="3590" width="14.54296875" customWidth="1"/>
+    <col min="3591" max="3591" width="15.26953125" customWidth="1"/>
+    <col min="3592" max="3593" width="14.453125" customWidth="1"/>
+    <col min="3594" max="3594" width="13.1796875" customWidth="1"/>
+    <col min="3595" max="3597" width="14.453125" customWidth="1"/>
+    <col min="3598" max="3598" width="15.81640625" customWidth="1"/>
+    <col min="3599" max="3599" width="7.81640625" customWidth="1"/>
+    <col min="3600" max="3600" width="5.453125" customWidth="1"/>
+    <col min="3601" max="3601" width="6.453125" customWidth="1"/>
+    <col min="3602" max="3602" width="7.81640625" customWidth="1"/>
+    <col min="3603" max="3603" width="3" customWidth="1"/>
+    <col min="3604" max="3604" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3841" max="3844" width="14.453125" customWidth="1"/>
+    <col min="3845" max="3845" width="15.453125" customWidth="1"/>
+    <col min="3846" max="3846" width="14.54296875" customWidth="1"/>
+    <col min="3847" max="3847" width="15.26953125" customWidth="1"/>
+    <col min="3848" max="3849" width="14.453125" customWidth="1"/>
+    <col min="3850" max="3850" width="13.1796875" customWidth="1"/>
+    <col min="3851" max="3853" width="14.453125" customWidth="1"/>
+    <col min="3854" max="3854" width="15.81640625" customWidth="1"/>
+    <col min="3855" max="3855" width="7.81640625" customWidth="1"/>
+    <col min="3856" max="3856" width="5.453125" customWidth="1"/>
+    <col min="3857" max="3857" width="6.453125" customWidth="1"/>
+    <col min="3858" max="3858" width="7.81640625" customWidth="1"/>
+    <col min="3859" max="3859" width="3" customWidth="1"/>
+    <col min="3860" max="3860" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4097" max="4100" width="14.453125" customWidth="1"/>
+    <col min="4101" max="4101" width="15.453125" customWidth="1"/>
+    <col min="4102" max="4102" width="14.54296875" customWidth="1"/>
+    <col min="4103" max="4103" width="15.26953125" customWidth="1"/>
+    <col min="4104" max="4105" width="14.453125" customWidth="1"/>
+    <col min="4106" max="4106" width="13.1796875" customWidth="1"/>
+    <col min="4107" max="4109" width="14.453125" customWidth="1"/>
+    <col min="4110" max="4110" width="15.81640625" customWidth="1"/>
+    <col min="4111" max="4111" width="7.81640625" customWidth="1"/>
+    <col min="4112" max="4112" width="5.453125" customWidth="1"/>
+    <col min="4113" max="4113" width="6.453125" customWidth="1"/>
+    <col min="4114" max="4114" width="7.81640625" customWidth="1"/>
+    <col min="4115" max="4115" width="3" customWidth="1"/>
+    <col min="4116" max="4116" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4353" max="4356" width="14.453125" customWidth="1"/>
+    <col min="4357" max="4357" width="15.453125" customWidth="1"/>
+    <col min="4358" max="4358" width="14.54296875" customWidth="1"/>
+    <col min="4359" max="4359" width="15.26953125" customWidth="1"/>
+    <col min="4360" max="4361" width="14.453125" customWidth="1"/>
+    <col min="4362" max="4362" width="13.1796875" customWidth="1"/>
+    <col min="4363" max="4365" width="14.453125" customWidth="1"/>
+    <col min="4366" max="4366" width="15.81640625" customWidth="1"/>
+    <col min="4367" max="4367" width="7.81640625" customWidth="1"/>
+    <col min="4368" max="4368" width="5.453125" customWidth="1"/>
+    <col min="4369" max="4369" width="6.453125" customWidth="1"/>
+    <col min="4370" max="4370" width="7.81640625" customWidth="1"/>
+    <col min="4371" max="4371" width="3" customWidth="1"/>
+    <col min="4372" max="4372" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4609" max="4612" width="14.453125" customWidth="1"/>
+    <col min="4613" max="4613" width="15.453125" customWidth="1"/>
+    <col min="4614" max="4614" width="14.54296875" customWidth="1"/>
+    <col min="4615" max="4615" width="15.26953125" customWidth="1"/>
+    <col min="4616" max="4617" width="14.453125" customWidth="1"/>
+    <col min="4618" max="4618" width="13.1796875" customWidth="1"/>
+    <col min="4619" max="4621" width="14.453125" customWidth="1"/>
+    <col min="4622" max="4622" width="15.81640625" customWidth="1"/>
+    <col min="4623" max="4623" width="7.81640625" customWidth="1"/>
+    <col min="4624" max="4624" width="5.453125" customWidth="1"/>
+    <col min="4625" max="4625" width="6.453125" customWidth="1"/>
+    <col min="4626" max="4626" width="7.81640625" customWidth="1"/>
+    <col min="4627" max="4627" width="3" customWidth="1"/>
+    <col min="4628" max="4628" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4865" max="4868" width="14.453125" customWidth="1"/>
+    <col min="4869" max="4869" width="15.453125" customWidth="1"/>
+    <col min="4870" max="4870" width="14.54296875" customWidth="1"/>
+    <col min="4871" max="4871" width="15.26953125" customWidth="1"/>
+    <col min="4872" max="4873" width="14.453125" customWidth="1"/>
+    <col min="4874" max="4874" width="13.1796875" customWidth="1"/>
+    <col min="4875" max="4877" width="14.453125" customWidth="1"/>
+    <col min="4878" max="4878" width="15.81640625" customWidth="1"/>
+    <col min="4879" max="4879" width="7.81640625" customWidth="1"/>
+    <col min="4880" max="4880" width="5.453125" customWidth="1"/>
+    <col min="4881" max="4881" width="6.453125" customWidth="1"/>
+    <col min="4882" max="4882" width="7.81640625" customWidth="1"/>
+    <col min="4883" max="4883" width="3" customWidth="1"/>
+    <col min="4884" max="4884" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5121" max="5124" width="14.453125" customWidth="1"/>
+    <col min="5125" max="5125" width="15.453125" customWidth="1"/>
+    <col min="5126" max="5126" width="14.54296875" customWidth="1"/>
+    <col min="5127" max="5127" width="15.26953125" customWidth="1"/>
+    <col min="5128" max="5129" width="14.453125" customWidth="1"/>
+    <col min="5130" max="5130" width="13.1796875" customWidth="1"/>
+    <col min="5131" max="5133" width="14.453125" customWidth="1"/>
+    <col min="5134" max="5134" width="15.81640625" customWidth="1"/>
+    <col min="5135" max="5135" width="7.81640625" customWidth="1"/>
+    <col min="5136" max="5136" width="5.453125" customWidth="1"/>
+    <col min="5137" max="5137" width="6.453125" customWidth="1"/>
+    <col min="5138" max="5138" width="7.81640625" customWidth="1"/>
+    <col min="5139" max="5139" width="3" customWidth="1"/>
+    <col min="5140" max="5140" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5377" max="5380" width="14.453125" customWidth="1"/>
+    <col min="5381" max="5381" width="15.453125" customWidth="1"/>
+    <col min="5382" max="5382" width="14.54296875" customWidth="1"/>
+    <col min="5383" max="5383" width="15.26953125" customWidth="1"/>
+    <col min="5384" max="5385" width="14.453125" customWidth="1"/>
+    <col min="5386" max="5386" width="13.1796875" customWidth="1"/>
+    <col min="5387" max="5389" width="14.453125" customWidth="1"/>
+    <col min="5390" max="5390" width="15.81640625" customWidth="1"/>
+    <col min="5391" max="5391" width="7.81640625" customWidth="1"/>
+    <col min="5392" max="5392" width="5.453125" customWidth="1"/>
+    <col min="5393" max="5393" width="6.453125" customWidth="1"/>
+    <col min="5394" max="5394" width="7.81640625" customWidth="1"/>
+    <col min="5395" max="5395" width="3" customWidth="1"/>
+    <col min="5396" max="5396" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5633" max="5636" width="14.453125" customWidth="1"/>
+    <col min="5637" max="5637" width="15.453125" customWidth="1"/>
+    <col min="5638" max="5638" width="14.54296875" customWidth="1"/>
+    <col min="5639" max="5639" width="15.26953125" customWidth="1"/>
+    <col min="5640" max="5641" width="14.453125" customWidth="1"/>
+    <col min="5642" max="5642" width="13.1796875" customWidth="1"/>
+    <col min="5643" max="5645" width="14.453125" customWidth="1"/>
+    <col min="5646" max="5646" width="15.81640625" customWidth="1"/>
+    <col min="5647" max="5647" width="7.81640625" customWidth="1"/>
+    <col min="5648" max="5648" width="5.453125" customWidth="1"/>
+    <col min="5649" max="5649" width="6.453125" customWidth="1"/>
+    <col min="5650" max="5650" width="7.81640625" customWidth="1"/>
+    <col min="5651" max="5651" width="3" customWidth="1"/>
+    <col min="5652" max="5652" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5889" max="5892" width="14.453125" customWidth="1"/>
+    <col min="5893" max="5893" width="15.453125" customWidth="1"/>
+    <col min="5894" max="5894" width="14.54296875" customWidth="1"/>
+    <col min="5895" max="5895" width="15.26953125" customWidth="1"/>
+    <col min="5896" max="5897" width="14.453125" customWidth="1"/>
+    <col min="5898" max="5898" width="13.1796875" customWidth="1"/>
+    <col min="5899" max="5901" width="14.453125" customWidth="1"/>
+    <col min="5902" max="5902" width="15.81640625" customWidth="1"/>
+    <col min="5903" max="5903" width="7.81640625" customWidth="1"/>
+    <col min="5904" max="5904" width="5.453125" customWidth="1"/>
+    <col min="5905" max="5905" width="6.453125" customWidth="1"/>
+    <col min="5906" max="5906" width="7.81640625" customWidth="1"/>
+    <col min="5907" max="5907" width="3" customWidth="1"/>
+    <col min="5908" max="5908" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6145" max="6148" width="14.453125" customWidth="1"/>
+    <col min="6149" max="6149" width="15.453125" customWidth="1"/>
+    <col min="6150" max="6150" width="14.54296875" customWidth="1"/>
+    <col min="6151" max="6151" width="15.26953125" customWidth="1"/>
+    <col min="6152" max="6153" width="14.453125" customWidth="1"/>
+    <col min="6154" max="6154" width="13.1796875" customWidth="1"/>
+    <col min="6155" max="6157" width="14.453125" customWidth="1"/>
+    <col min="6158" max="6158" width="15.81640625" customWidth="1"/>
+    <col min="6159" max="6159" width="7.81640625" customWidth="1"/>
+    <col min="6160" max="6160" width="5.453125" customWidth="1"/>
+    <col min="6161" max="6161" width="6.453125" customWidth="1"/>
+    <col min="6162" max="6162" width="7.81640625" customWidth="1"/>
+    <col min="6163" max="6163" width="3" customWidth="1"/>
+    <col min="6164" max="6164" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6401" max="6404" width="14.453125" customWidth="1"/>
+    <col min="6405" max="6405" width="15.453125" customWidth="1"/>
+    <col min="6406" max="6406" width="14.54296875" customWidth="1"/>
+    <col min="6407" max="6407" width="15.26953125" customWidth="1"/>
+    <col min="6408" max="6409" width="14.453125" customWidth="1"/>
+    <col min="6410" max="6410" width="13.1796875" customWidth="1"/>
+    <col min="6411" max="6413" width="14.453125" customWidth="1"/>
+    <col min="6414" max="6414" width="15.81640625" customWidth="1"/>
+    <col min="6415" max="6415" width="7.81640625" customWidth="1"/>
+    <col min="6416" max="6416" width="5.453125" customWidth="1"/>
+    <col min="6417" max="6417" width="6.453125" customWidth="1"/>
+    <col min="6418" max="6418" width="7.81640625" customWidth="1"/>
+    <col min="6419" max="6419" width="3" customWidth="1"/>
+    <col min="6420" max="6420" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6657" max="6660" width="14.453125" customWidth="1"/>
+    <col min="6661" max="6661" width="15.453125" customWidth="1"/>
+    <col min="6662" max="6662" width="14.54296875" customWidth="1"/>
+    <col min="6663" max="6663" width="15.26953125" customWidth="1"/>
+    <col min="6664" max="6665" width="14.453125" customWidth="1"/>
+    <col min="6666" max="6666" width="13.1796875" customWidth="1"/>
+    <col min="6667" max="6669" width="14.453125" customWidth="1"/>
+    <col min="6670" max="6670" width="15.81640625" customWidth="1"/>
+    <col min="6671" max="6671" width="7.81640625" customWidth="1"/>
+    <col min="6672" max="6672" width="5.453125" customWidth="1"/>
+    <col min="6673" max="6673" width="6.453125" customWidth="1"/>
+    <col min="6674" max="6674" width="7.81640625" customWidth="1"/>
+    <col min="6675" max="6675" width="3" customWidth="1"/>
+    <col min="6676" max="6676" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6913" max="6916" width="14.453125" customWidth="1"/>
+    <col min="6917" max="6917" width="15.453125" customWidth="1"/>
+    <col min="6918" max="6918" width="14.54296875" customWidth="1"/>
+    <col min="6919" max="6919" width="15.26953125" customWidth="1"/>
+    <col min="6920" max="6921" width="14.453125" customWidth="1"/>
+    <col min="6922" max="6922" width="13.1796875" customWidth="1"/>
+    <col min="6923" max="6925" width="14.453125" customWidth="1"/>
+    <col min="6926" max="6926" width="15.81640625" customWidth="1"/>
+    <col min="6927" max="6927" width="7.81640625" customWidth="1"/>
+    <col min="6928" max="6928" width="5.453125" customWidth="1"/>
+    <col min="6929" max="6929" width="6.453125" customWidth="1"/>
+    <col min="6930" max="6930" width="7.81640625" customWidth="1"/>
+    <col min="6931" max="6931" width="3" customWidth="1"/>
+    <col min="6932" max="6932" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7169" max="7172" width="14.453125" customWidth="1"/>
+    <col min="7173" max="7173" width="15.453125" customWidth="1"/>
+    <col min="7174" max="7174" width="14.54296875" customWidth="1"/>
+    <col min="7175" max="7175" width="15.26953125" customWidth="1"/>
+    <col min="7176" max="7177" width="14.453125" customWidth="1"/>
+    <col min="7178" max="7178" width="13.1796875" customWidth="1"/>
+    <col min="7179" max="7181" width="14.453125" customWidth="1"/>
+    <col min="7182" max="7182" width="15.81640625" customWidth="1"/>
+    <col min="7183" max="7183" width="7.81640625" customWidth="1"/>
+    <col min="7184" max="7184" width="5.453125" customWidth="1"/>
+    <col min="7185" max="7185" width="6.453125" customWidth="1"/>
+    <col min="7186" max="7186" width="7.81640625" customWidth="1"/>
+    <col min="7187" max="7187" width="3" customWidth="1"/>
+    <col min="7188" max="7188" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7425" max="7428" width="14.453125" customWidth="1"/>
+    <col min="7429" max="7429" width="15.453125" customWidth="1"/>
+    <col min="7430" max="7430" width="14.54296875" customWidth="1"/>
+    <col min="7431" max="7431" width="15.26953125" customWidth="1"/>
+    <col min="7432" max="7433" width="14.453125" customWidth="1"/>
+    <col min="7434" max="7434" width="13.1796875" customWidth="1"/>
+    <col min="7435" max="7437" width="14.453125" customWidth="1"/>
+    <col min="7438" max="7438" width="15.81640625" customWidth="1"/>
+    <col min="7439" max="7439" width="7.81640625" customWidth="1"/>
+    <col min="7440" max="7440" width="5.453125" customWidth="1"/>
+    <col min="7441" max="7441" width="6.453125" customWidth="1"/>
+    <col min="7442" max="7442" width="7.81640625" customWidth="1"/>
+    <col min="7443" max="7443" width="3" customWidth="1"/>
+    <col min="7444" max="7444" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7681" max="7684" width="14.453125" customWidth="1"/>
+    <col min="7685" max="7685" width="15.453125" customWidth="1"/>
+    <col min="7686" max="7686" width="14.54296875" customWidth="1"/>
+    <col min="7687" max="7687" width="15.26953125" customWidth="1"/>
+    <col min="7688" max="7689" width="14.453125" customWidth="1"/>
+    <col min="7690" max="7690" width="13.1796875" customWidth="1"/>
+    <col min="7691" max="7693" width="14.453125" customWidth="1"/>
+    <col min="7694" max="7694" width="15.81640625" customWidth="1"/>
+    <col min="7695" max="7695" width="7.81640625" customWidth="1"/>
+    <col min="7696" max="7696" width="5.453125" customWidth="1"/>
+    <col min="7697" max="7697" width="6.453125" customWidth="1"/>
+    <col min="7698" max="7698" width="7.81640625" customWidth="1"/>
+    <col min="7699" max="7699" width="3" customWidth="1"/>
+    <col min="7700" max="7700" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7937" max="7940" width="14.453125" customWidth="1"/>
+    <col min="7941" max="7941" width="15.453125" customWidth="1"/>
+    <col min="7942" max="7942" width="14.54296875" customWidth="1"/>
+    <col min="7943" max="7943" width="15.26953125" customWidth="1"/>
+    <col min="7944" max="7945" width="14.453125" customWidth="1"/>
+    <col min="7946" max="7946" width="13.1796875" customWidth="1"/>
+    <col min="7947" max="7949" width="14.453125" customWidth="1"/>
+    <col min="7950" max="7950" width="15.81640625" customWidth="1"/>
+    <col min="7951" max="7951" width="7.81640625" customWidth="1"/>
+    <col min="7952" max="7952" width="5.453125" customWidth="1"/>
+    <col min="7953" max="7953" width="6.453125" customWidth="1"/>
+    <col min="7954" max="7954" width="7.81640625" customWidth="1"/>
+    <col min="7955" max="7955" width="3" customWidth="1"/>
+    <col min="7956" max="7956" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8193" max="8196" width="14.453125" customWidth="1"/>
+    <col min="8197" max="8197" width="15.453125" customWidth="1"/>
+    <col min="8198" max="8198" width="14.54296875" customWidth="1"/>
+    <col min="8199" max="8199" width="15.26953125" customWidth="1"/>
+    <col min="8200" max="8201" width="14.453125" customWidth="1"/>
+    <col min="8202" max="8202" width="13.1796875" customWidth="1"/>
+    <col min="8203" max="8205" width="14.453125" customWidth="1"/>
+    <col min="8206" max="8206" width="15.81640625" customWidth="1"/>
+    <col min="8207" max="8207" width="7.81640625" customWidth="1"/>
+    <col min="8208" max="8208" width="5.453125" customWidth="1"/>
+    <col min="8209" max="8209" width="6.453125" customWidth="1"/>
+    <col min="8210" max="8210" width="7.81640625" customWidth="1"/>
+    <col min="8211" max="8211" width="3" customWidth="1"/>
+    <col min="8212" max="8212" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8449" max="8452" width="14.453125" customWidth="1"/>
+    <col min="8453" max="8453" width="15.453125" customWidth="1"/>
+    <col min="8454" max="8454" width="14.54296875" customWidth="1"/>
+    <col min="8455" max="8455" width="15.26953125" customWidth="1"/>
+    <col min="8456" max="8457" width="14.453125" customWidth="1"/>
+    <col min="8458" max="8458" width="13.1796875" customWidth="1"/>
+    <col min="8459" max="8461" width="14.453125" customWidth="1"/>
+    <col min="8462" max="8462" width="15.81640625" customWidth="1"/>
+    <col min="8463" max="8463" width="7.81640625" customWidth="1"/>
+    <col min="8464" max="8464" width="5.453125" customWidth="1"/>
+    <col min="8465" max="8465" width="6.453125" customWidth="1"/>
+    <col min="8466" max="8466" width="7.81640625" customWidth="1"/>
+    <col min="8467" max="8467" width="3" customWidth="1"/>
+    <col min="8468" max="8468" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8705" max="8708" width="14.453125" customWidth="1"/>
+    <col min="8709" max="8709" width="15.453125" customWidth="1"/>
+    <col min="8710" max="8710" width="14.54296875" customWidth="1"/>
+    <col min="8711" max="8711" width="15.26953125" customWidth="1"/>
+    <col min="8712" max="8713" width="14.453125" customWidth="1"/>
+    <col min="8714" max="8714" width="13.1796875" customWidth="1"/>
+    <col min="8715" max="8717" width="14.453125" customWidth="1"/>
+    <col min="8718" max="8718" width="15.81640625" customWidth="1"/>
+    <col min="8719" max="8719" width="7.81640625" customWidth="1"/>
+    <col min="8720" max="8720" width="5.453125" customWidth="1"/>
+    <col min="8721" max="8721" width="6.453125" customWidth="1"/>
+    <col min="8722" max="8722" width="7.81640625" customWidth="1"/>
+    <col min="8723" max="8723" width="3" customWidth="1"/>
+    <col min="8724" max="8724" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8961" max="8964" width="14.453125" customWidth="1"/>
+    <col min="8965" max="8965" width="15.453125" customWidth="1"/>
+    <col min="8966" max="8966" width="14.54296875" customWidth="1"/>
+    <col min="8967" max="8967" width="15.26953125" customWidth="1"/>
+    <col min="8968" max="8969" width="14.453125" customWidth="1"/>
+    <col min="8970" max="8970" width="13.1796875" customWidth="1"/>
+    <col min="8971" max="8973" width="14.453125" customWidth="1"/>
+    <col min="8974" max="8974" width="15.81640625" customWidth="1"/>
+    <col min="8975" max="8975" width="7.81640625" customWidth="1"/>
+    <col min="8976" max="8976" width="5.453125" customWidth="1"/>
+    <col min="8977" max="8977" width="6.453125" customWidth="1"/>
+    <col min="8978" max="8978" width="7.81640625" customWidth="1"/>
+    <col min="8979" max="8979" width="3" customWidth="1"/>
+    <col min="8980" max="8980" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9217" max="9220" width="14.453125" customWidth="1"/>
+    <col min="9221" max="9221" width="15.453125" customWidth="1"/>
+    <col min="9222" max="9222" width="14.54296875" customWidth="1"/>
+    <col min="9223" max="9223" width="15.26953125" customWidth="1"/>
+    <col min="9224" max="9225" width="14.453125" customWidth="1"/>
+    <col min="9226" max="9226" width="13.1796875" customWidth="1"/>
+    <col min="9227" max="9229" width="14.453125" customWidth="1"/>
+    <col min="9230" max="9230" width="15.81640625" customWidth="1"/>
+    <col min="9231" max="9231" width="7.81640625" customWidth="1"/>
+    <col min="9232" max="9232" width="5.453125" customWidth="1"/>
+    <col min="9233" max="9233" width="6.453125" customWidth="1"/>
+    <col min="9234" max="9234" width="7.81640625" customWidth="1"/>
+    <col min="9235" max="9235" width="3" customWidth="1"/>
+    <col min="9236" max="9236" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9473" max="9476" width="14.453125" customWidth="1"/>
+    <col min="9477" max="9477" width="15.453125" customWidth="1"/>
+    <col min="9478" max="9478" width="14.54296875" customWidth="1"/>
+    <col min="9479" max="9479" width="15.26953125" customWidth="1"/>
+    <col min="9480" max="9481" width="14.453125" customWidth="1"/>
+    <col min="9482" max="9482" width="13.1796875" customWidth="1"/>
+    <col min="9483" max="9485" width="14.453125" customWidth="1"/>
+    <col min="9486" max="9486" width="15.81640625" customWidth="1"/>
+    <col min="9487" max="9487" width="7.81640625" customWidth="1"/>
+    <col min="9488" max="9488" width="5.453125" customWidth="1"/>
+    <col min="9489" max="9489" width="6.453125" customWidth="1"/>
+    <col min="9490" max="9490" width="7.81640625" customWidth="1"/>
+    <col min="9491" max="9491" width="3" customWidth="1"/>
+    <col min="9492" max="9492" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9729" max="9732" width="14.453125" customWidth="1"/>
+    <col min="9733" max="9733" width="15.453125" customWidth="1"/>
+    <col min="9734" max="9734" width="14.54296875" customWidth="1"/>
+    <col min="9735" max="9735" width="15.26953125" customWidth="1"/>
+    <col min="9736" max="9737" width="14.453125" customWidth="1"/>
+    <col min="9738" max="9738" width="13.1796875" customWidth="1"/>
+    <col min="9739" max="9741" width="14.453125" customWidth="1"/>
+    <col min="9742" max="9742" width="15.81640625" customWidth="1"/>
+    <col min="9743" max="9743" width="7.81640625" customWidth="1"/>
+    <col min="9744" max="9744" width="5.453125" customWidth="1"/>
+    <col min="9745" max="9745" width="6.453125" customWidth="1"/>
+    <col min="9746" max="9746" width="7.81640625" customWidth="1"/>
+    <col min="9747" max="9747" width="3" customWidth="1"/>
+    <col min="9748" max="9748" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9985" max="9988" width="14.453125" customWidth="1"/>
+    <col min="9989" max="9989" width="15.453125" customWidth="1"/>
+    <col min="9990" max="9990" width="14.54296875" customWidth="1"/>
+    <col min="9991" max="9991" width="15.26953125" customWidth="1"/>
+    <col min="9992" max="9993" width="14.453125" customWidth="1"/>
+    <col min="9994" max="9994" width="13.1796875" customWidth="1"/>
+    <col min="9995" max="9997" width="14.453125" customWidth="1"/>
+    <col min="9998" max="9998" width="15.81640625" customWidth="1"/>
+    <col min="9999" max="9999" width="7.81640625" customWidth="1"/>
+    <col min="10000" max="10000" width="5.453125" customWidth="1"/>
+    <col min="10001" max="10001" width="6.453125" customWidth="1"/>
+    <col min="10002" max="10002" width="7.81640625" customWidth="1"/>
+    <col min="10003" max="10003" width="3" customWidth="1"/>
+    <col min="10004" max="10004" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10241" max="10244" width="14.453125" customWidth="1"/>
+    <col min="10245" max="10245" width="15.453125" customWidth="1"/>
+    <col min="10246" max="10246" width="14.54296875" customWidth="1"/>
+    <col min="10247" max="10247" width="15.26953125" customWidth="1"/>
+    <col min="10248" max="10249" width="14.453125" customWidth="1"/>
+    <col min="10250" max="10250" width="13.1796875" customWidth="1"/>
+    <col min="10251" max="10253" width="14.453125" customWidth="1"/>
+    <col min="10254" max="10254" width="15.81640625" customWidth="1"/>
+    <col min="10255" max="10255" width="7.81640625" customWidth="1"/>
+    <col min="10256" max="10256" width="5.453125" customWidth="1"/>
+    <col min="10257" max="10257" width="6.453125" customWidth="1"/>
+    <col min="10258" max="10258" width="7.81640625" customWidth="1"/>
+    <col min="10259" max="10259" width="3" customWidth="1"/>
+    <col min="10260" max="10260" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10497" max="10500" width="14.453125" customWidth="1"/>
+    <col min="10501" max="10501" width="15.453125" customWidth="1"/>
+    <col min="10502" max="10502" width="14.54296875" customWidth="1"/>
+    <col min="10503" max="10503" width="15.26953125" customWidth="1"/>
+    <col min="10504" max="10505" width="14.453125" customWidth="1"/>
+    <col min="10506" max="10506" width="13.1796875" customWidth="1"/>
+    <col min="10507" max="10509" width="14.453125" customWidth="1"/>
+    <col min="10510" max="10510" width="15.81640625" customWidth="1"/>
+    <col min="10511" max="10511" width="7.81640625" customWidth="1"/>
+    <col min="10512" max="10512" width="5.453125" customWidth="1"/>
+    <col min="10513" max="10513" width="6.453125" customWidth="1"/>
+    <col min="10514" max="10514" width="7.81640625" customWidth="1"/>
+    <col min="10515" max="10515" width="3" customWidth="1"/>
+    <col min="10516" max="10516" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10753" max="10756" width="14.453125" customWidth="1"/>
+    <col min="10757" max="10757" width="15.453125" customWidth="1"/>
+    <col min="10758" max="10758" width="14.54296875" customWidth="1"/>
+    <col min="10759" max="10759" width="15.26953125" customWidth="1"/>
+    <col min="10760" max="10761" width="14.453125" customWidth="1"/>
+    <col min="10762" max="10762" width="13.1796875" customWidth="1"/>
+    <col min="10763" max="10765" width="14.453125" customWidth="1"/>
+    <col min="10766" max="10766" width="15.81640625" customWidth="1"/>
+    <col min="10767" max="10767" width="7.81640625" customWidth="1"/>
+    <col min="10768" max="10768" width="5.453125" customWidth="1"/>
+    <col min="10769" max="10769" width="6.453125" customWidth="1"/>
+    <col min="10770" max="10770" width="7.81640625" customWidth="1"/>
+    <col min="10771" max="10771" width="3" customWidth="1"/>
+    <col min="10772" max="10772" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11009" max="11012" width="14.453125" customWidth="1"/>
+    <col min="11013" max="11013" width="15.453125" customWidth="1"/>
+    <col min="11014" max="11014" width="14.54296875" customWidth="1"/>
+    <col min="11015" max="11015" width="15.26953125" customWidth="1"/>
+    <col min="11016" max="11017" width="14.453125" customWidth="1"/>
+    <col min="11018" max="11018" width="13.1796875" customWidth="1"/>
+    <col min="11019" max="11021" width="14.453125" customWidth="1"/>
+    <col min="11022" max="11022" width="15.81640625" customWidth="1"/>
+    <col min="11023" max="11023" width="7.81640625" customWidth="1"/>
+    <col min="11024" max="11024" width="5.453125" customWidth="1"/>
+    <col min="11025" max="11025" width="6.453125" customWidth="1"/>
+    <col min="11026" max="11026" width="7.81640625" customWidth="1"/>
+    <col min="11027" max="11027" width="3" customWidth="1"/>
+    <col min="11028" max="11028" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11265" max="11268" width="14.453125" customWidth="1"/>
+    <col min="11269" max="11269" width="15.453125" customWidth="1"/>
+    <col min="11270" max="11270" width="14.54296875" customWidth="1"/>
+    <col min="11271" max="11271" width="15.26953125" customWidth="1"/>
+    <col min="11272" max="11273" width="14.453125" customWidth="1"/>
+    <col min="11274" max="11274" width="13.1796875" customWidth="1"/>
+    <col min="11275" max="11277" width="14.453125" customWidth="1"/>
+    <col min="11278" max="11278" width="15.81640625" customWidth="1"/>
+    <col min="11279" max="11279" width="7.81640625" customWidth="1"/>
+    <col min="11280" max="11280" width="5.453125" customWidth="1"/>
+    <col min="11281" max="11281" width="6.453125" customWidth="1"/>
+    <col min="11282" max="11282" width="7.81640625" customWidth="1"/>
+    <col min="11283" max="11283" width="3" customWidth="1"/>
+    <col min="11284" max="11284" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11521" max="11524" width="14.453125" customWidth="1"/>
+    <col min="11525" max="11525" width="15.453125" customWidth="1"/>
+    <col min="11526" max="11526" width="14.54296875" customWidth="1"/>
+    <col min="11527" max="11527" width="15.26953125" customWidth="1"/>
+    <col min="11528" max="11529" width="14.453125" customWidth="1"/>
+    <col min="11530" max="11530" width="13.1796875" customWidth="1"/>
+    <col min="11531" max="11533" width="14.453125" customWidth="1"/>
+    <col min="11534" max="11534" width="15.81640625" customWidth="1"/>
+    <col min="11535" max="11535" width="7.81640625" customWidth="1"/>
+    <col min="11536" max="11536" width="5.453125" customWidth="1"/>
+    <col min="11537" max="11537" width="6.453125" customWidth="1"/>
+    <col min="11538" max="11538" width="7.81640625" customWidth="1"/>
+    <col min="11539" max="11539" width="3" customWidth="1"/>
+    <col min="11540" max="11540" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11777" max="11780" width="14.453125" customWidth="1"/>
+    <col min="11781" max="11781" width="15.453125" customWidth="1"/>
+    <col min="11782" max="11782" width="14.54296875" customWidth="1"/>
+    <col min="11783" max="11783" width="15.26953125" customWidth="1"/>
+    <col min="11784" max="11785" width="14.453125" customWidth="1"/>
+    <col min="11786" max="11786" width="13.1796875" customWidth="1"/>
+    <col min="11787" max="11789" width="14.453125" customWidth="1"/>
+    <col min="11790" max="11790" width="15.81640625" customWidth="1"/>
+    <col min="11791" max="11791" width="7.81640625" customWidth="1"/>
+    <col min="11792" max="11792" width="5.453125" customWidth="1"/>
+    <col min="11793" max="11793" width="6.453125" customWidth="1"/>
+    <col min="11794" max="11794" width="7.81640625" customWidth="1"/>
+    <col min="11795" max="11795" width="3" customWidth="1"/>
+    <col min="11796" max="11796" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12033" max="12036" width="14.453125" customWidth="1"/>
+    <col min="12037" max="12037" width="15.453125" customWidth="1"/>
+    <col min="12038" max="12038" width="14.54296875" customWidth="1"/>
+    <col min="12039" max="12039" width="15.26953125" customWidth="1"/>
+    <col min="12040" max="12041" width="14.453125" customWidth="1"/>
+    <col min="12042" max="12042" width="13.1796875" customWidth="1"/>
+    <col min="12043" max="12045" width="14.453125" customWidth="1"/>
+    <col min="12046" max="12046" width="15.81640625" customWidth="1"/>
+    <col min="12047" max="12047" width="7.81640625" customWidth="1"/>
+    <col min="12048" max="12048" width="5.453125" customWidth="1"/>
+    <col min="12049" max="12049" width="6.453125" customWidth="1"/>
+    <col min="12050" max="12050" width="7.81640625" customWidth="1"/>
+    <col min="12051" max="12051" width="3" customWidth="1"/>
+    <col min="12052" max="12052" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12289" max="12292" width="14.453125" customWidth="1"/>
+    <col min="12293" max="12293" width="15.453125" customWidth="1"/>
+    <col min="12294" max="12294" width="14.54296875" customWidth="1"/>
+    <col min="12295" max="12295" width="15.26953125" customWidth="1"/>
+    <col min="12296" max="12297" width="14.453125" customWidth="1"/>
+    <col min="12298" max="12298" width="13.1796875" customWidth="1"/>
+    <col min="12299" max="12301" width="14.453125" customWidth="1"/>
+    <col min="12302" max="12302" width="15.81640625" customWidth="1"/>
+    <col min="12303" max="12303" width="7.81640625" customWidth="1"/>
+    <col min="12304" max="12304" width="5.453125" customWidth="1"/>
+    <col min="12305" max="12305" width="6.453125" customWidth="1"/>
+    <col min="12306" max="12306" width="7.81640625" customWidth="1"/>
+    <col min="12307" max="12307" width="3" customWidth="1"/>
+    <col min="12308" max="12308" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12545" max="12548" width="14.453125" customWidth="1"/>
+    <col min="12549" max="12549" width="15.453125" customWidth="1"/>
+    <col min="12550" max="12550" width="14.54296875" customWidth="1"/>
+    <col min="12551" max="12551" width="15.26953125" customWidth="1"/>
+    <col min="12552" max="12553" width="14.453125" customWidth="1"/>
+    <col min="12554" max="12554" width="13.1796875" customWidth="1"/>
+    <col min="12555" max="12557" width="14.453125" customWidth="1"/>
+    <col min="12558" max="12558" width="15.81640625" customWidth="1"/>
+    <col min="12559" max="12559" width="7.81640625" customWidth="1"/>
+    <col min="12560" max="12560" width="5.453125" customWidth="1"/>
+    <col min="12561" max="12561" width="6.453125" customWidth="1"/>
+    <col min="12562" max="12562" width="7.81640625" customWidth="1"/>
+    <col min="12563" max="12563" width="3" customWidth="1"/>
+    <col min="12564" max="12564" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12801" max="12804" width="14.453125" customWidth="1"/>
+    <col min="12805" max="12805" width="15.453125" customWidth="1"/>
+    <col min="12806" max="12806" width="14.54296875" customWidth="1"/>
+    <col min="12807" max="12807" width="15.26953125" customWidth="1"/>
+    <col min="12808" max="12809" width="14.453125" customWidth="1"/>
+    <col min="12810" max="12810" width="13.1796875" customWidth="1"/>
+    <col min="12811" max="12813" width="14.453125" customWidth="1"/>
+    <col min="12814" max="12814" width="15.81640625" customWidth="1"/>
+    <col min="12815" max="12815" width="7.81640625" customWidth="1"/>
+    <col min="12816" max="12816" width="5.453125" customWidth="1"/>
+    <col min="12817" max="12817" width="6.453125" customWidth="1"/>
+    <col min="12818" max="12818" width="7.81640625" customWidth="1"/>
+    <col min="12819" max="12819" width="3" customWidth="1"/>
+    <col min="12820" max="12820" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13057" max="13060" width="14.453125" customWidth="1"/>
+    <col min="13061" max="13061" width="15.453125" customWidth="1"/>
+    <col min="13062" max="13062" width="14.54296875" customWidth="1"/>
+    <col min="13063" max="13063" width="15.26953125" customWidth="1"/>
+    <col min="13064" max="13065" width="14.453125" customWidth="1"/>
+    <col min="13066" max="13066" width="13.1796875" customWidth="1"/>
+    <col min="13067" max="13069" width="14.453125" customWidth="1"/>
+    <col min="13070" max="13070" width="15.81640625" customWidth="1"/>
+    <col min="13071" max="13071" width="7.81640625" customWidth="1"/>
+    <col min="13072" max="13072" width="5.453125" customWidth="1"/>
+    <col min="13073" max="13073" width="6.453125" customWidth="1"/>
+    <col min="13074" max="13074" width="7.81640625" customWidth="1"/>
+    <col min="13075" max="13075" width="3" customWidth="1"/>
+    <col min="13076" max="13076" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13313" max="13316" width="14.453125" customWidth="1"/>
+    <col min="13317" max="13317" width="15.453125" customWidth="1"/>
+    <col min="13318" max="13318" width="14.54296875" customWidth="1"/>
+    <col min="13319" max="13319" width="15.26953125" customWidth="1"/>
+    <col min="13320" max="13321" width="14.453125" customWidth="1"/>
+    <col min="13322" max="13322" width="13.1796875" customWidth="1"/>
+    <col min="13323" max="13325" width="14.453125" customWidth="1"/>
+    <col min="13326" max="13326" width="15.81640625" customWidth="1"/>
+    <col min="13327" max="13327" width="7.81640625" customWidth="1"/>
+    <col min="13328" max="13328" width="5.453125" customWidth="1"/>
+    <col min="13329" max="13329" width="6.453125" customWidth="1"/>
+    <col min="13330" max="13330" width="7.81640625" customWidth="1"/>
+    <col min="13331" max="13331" width="3" customWidth="1"/>
+    <col min="13332" max="13332" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13569" max="13572" width="14.453125" customWidth="1"/>
+    <col min="13573" max="13573" width="15.453125" customWidth="1"/>
+    <col min="13574" max="13574" width="14.54296875" customWidth="1"/>
+    <col min="13575" max="13575" width="15.26953125" customWidth="1"/>
+    <col min="13576" max="13577" width="14.453125" customWidth="1"/>
+    <col min="13578" max="13578" width="13.1796875" customWidth="1"/>
+    <col min="13579" max="13581" width="14.453125" customWidth="1"/>
+    <col min="13582" max="13582" width="15.81640625" customWidth="1"/>
+    <col min="13583" max="13583" width="7.81640625" customWidth="1"/>
+    <col min="13584" max="13584" width="5.453125" customWidth="1"/>
+    <col min="13585" max="13585" width="6.453125" customWidth="1"/>
+    <col min="13586" max="13586" width="7.81640625" customWidth="1"/>
+    <col min="13587" max="13587" width="3" customWidth="1"/>
+    <col min="13588" max="13588" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13825" max="13828" width="14.453125" customWidth="1"/>
+    <col min="13829" max="13829" width="15.453125" customWidth="1"/>
+    <col min="13830" max="13830" width="14.54296875" customWidth="1"/>
+    <col min="13831" max="13831" width="15.26953125" customWidth="1"/>
+    <col min="13832" max="13833" width="14.453125" customWidth="1"/>
+    <col min="13834" max="13834" width="13.1796875" customWidth="1"/>
+    <col min="13835" max="13837" width="14.453125" customWidth="1"/>
+    <col min="13838" max="13838" width="15.81640625" customWidth="1"/>
+    <col min="13839" max="13839" width="7.81640625" customWidth="1"/>
+    <col min="13840" max="13840" width="5.453125" customWidth="1"/>
+    <col min="13841" max="13841" width="6.453125" customWidth="1"/>
+    <col min="13842" max="13842" width="7.81640625" customWidth="1"/>
+    <col min="13843" max="13843" width="3" customWidth="1"/>
+    <col min="13844" max="13844" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14081" max="14084" width="14.453125" customWidth="1"/>
+    <col min="14085" max="14085" width="15.453125" customWidth="1"/>
+    <col min="14086" max="14086" width="14.54296875" customWidth="1"/>
+    <col min="14087" max="14087" width="15.26953125" customWidth="1"/>
+    <col min="14088" max="14089" width="14.453125" customWidth="1"/>
+    <col min="14090" max="14090" width="13.1796875" customWidth="1"/>
+    <col min="14091" max="14093" width="14.453125" customWidth="1"/>
+    <col min="14094" max="14094" width="15.81640625" customWidth="1"/>
+    <col min="14095" max="14095" width="7.81640625" customWidth="1"/>
+    <col min="14096" max="14096" width="5.453125" customWidth="1"/>
+    <col min="14097" max="14097" width="6.453125" customWidth="1"/>
+    <col min="14098" max="14098" width="7.81640625" customWidth="1"/>
+    <col min="14099" max="14099" width="3" customWidth="1"/>
+    <col min="14100" max="14100" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14337" max="14340" width="14.453125" customWidth="1"/>
+    <col min="14341" max="14341" width="15.453125" customWidth="1"/>
+    <col min="14342" max="14342" width="14.54296875" customWidth="1"/>
+    <col min="14343" max="14343" width="15.26953125" customWidth="1"/>
+    <col min="14344" max="14345" width="14.453125" customWidth="1"/>
+    <col min="14346" max="14346" width="13.1796875" customWidth="1"/>
+    <col min="14347" max="14349" width="14.453125" customWidth="1"/>
+    <col min="14350" max="14350" width="15.81640625" customWidth="1"/>
+    <col min="14351" max="14351" width="7.81640625" customWidth="1"/>
+    <col min="14352" max="14352" width="5.453125" customWidth="1"/>
+    <col min="14353" max="14353" width="6.453125" customWidth="1"/>
+    <col min="14354" max="14354" width="7.81640625" customWidth="1"/>
+    <col min="14355" max="14355" width="3" customWidth="1"/>
+    <col min="14356" max="14356" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14593" max="14596" width="14.453125" customWidth="1"/>
+    <col min="14597" max="14597" width="15.453125" customWidth="1"/>
+    <col min="14598" max="14598" width="14.54296875" customWidth="1"/>
+    <col min="14599" max="14599" width="15.26953125" customWidth="1"/>
+    <col min="14600" max="14601" width="14.453125" customWidth="1"/>
+    <col min="14602" max="14602" width="13.1796875" customWidth="1"/>
+    <col min="14603" max="14605" width="14.453125" customWidth="1"/>
+    <col min="14606" max="14606" width="15.81640625" customWidth="1"/>
+    <col min="14607" max="14607" width="7.81640625" customWidth="1"/>
+    <col min="14608" max="14608" width="5.453125" customWidth="1"/>
+    <col min="14609" max="14609" width="6.453125" customWidth="1"/>
+    <col min="14610" max="14610" width="7.81640625" customWidth="1"/>
+    <col min="14611" max="14611" width="3" customWidth="1"/>
+    <col min="14612" max="14612" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14849" max="14852" width="14.453125" customWidth="1"/>
+    <col min="14853" max="14853" width="15.453125" customWidth="1"/>
+    <col min="14854" max="14854" width="14.54296875" customWidth="1"/>
+    <col min="14855" max="14855" width="15.26953125" customWidth="1"/>
+    <col min="14856" max="14857" width="14.453125" customWidth="1"/>
+    <col min="14858" max="14858" width="13.1796875" customWidth="1"/>
+    <col min="14859" max="14861" width="14.453125" customWidth="1"/>
+    <col min="14862" max="14862" width="15.81640625" customWidth="1"/>
+    <col min="14863" max="14863" width="7.81640625" customWidth="1"/>
+    <col min="14864" max="14864" width="5.453125" customWidth="1"/>
+    <col min="14865" max="14865" width="6.453125" customWidth="1"/>
+    <col min="14866" max="14866" width="7.81640625" customWidth="1"/>
+    <col min="14867" max="14867" width="3" customWidth="1"/>
+    <col min="14868" max="14868" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15105" max="15108" width="14.453125" customWidth="1"/>
+    <col min="15109" max="15109" width="15.453125" customWidth="1"/>
+    <col min="15110" max="15110" width="14.54296875" customWidth="1"/>
+    <col min="15111" max="15111" width="15.26953125" customWidth="1"/>
+    <col min="15112" max="15113" width="14.453125" customWidth="1"/>
+    <col min="15114" max="15114" width="13.1796875" customWidth="1"/>
+    <col min="15115" max="15117" width="14.453125" customWidth="1"/>
+    <col min="15118" max="15118" width="15.81640625" customWidth="1"/>
+    <col min="15119" max="15119" width="7.81640625" customWidth="1"/>
+    <col min="15120" max="15120" width="5.453125" customWidth="1"/>
+    <col min="15121" max="15121" width="6.453125" customWidth="1"/>
+    <col min="15122" max="15122" width="7.81640625" customWidth="1"/>
+    <col min="15123" max="15123" width="3" customWidth="1"/>
+    <col min="15124" max="15124" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15361" max="15364" width="14.453125" customWidth="1"/>
+    <col min="15365" max="15365" width="15.453125" customWidth="1"/>
+    <col min="15366" max="15366" width="14.54296875" customWidth="1"/>
+    <col min="15367" max="15367" width="15.26953125" customWidth="1"/>
+    <col min="15368" max="15369" width="14.453125" customWidth="1"/>
+    <col min="15370" max="15370" width="13.1796875" customWidth="1"/>
+    <col min="15371" max="15373" width="14.453125" customWidth="1"/>
+    <col min="15374" max="15374" width="15.81640625" customWidth="1"/>
+    <col min="15375" max="15375" width="7.81640625" customWidth="1"/>
+    <col min="15376" max="15376" width="5.453125" customWidth="1"/>
+    <col min="15377" max="15377" width="6.453125" customWidth="1"/>
+    <col min="15378" max="15378" width="7.81640625" customWidth="1"/>
+    <col min="15379" max="15379" width="3" customWidth="1"/>
+    <col min="15380" max="15380" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15617" max="15620" width="14.453125" customWidth="1"/>
+    <col min="15621" max="15621" width="15.453125" customWidth="1"/>
+    <col min="15622" max="15622" width="14.54296875" customWidth="1"/>
+    <col min="15623" max="15623" width="15.26953125" customWidth="1"/>
+    <col min="15624" max="15625" width="14.453125" customWidth="1"/>
+    <col min="15626" max="15626" width="13.1796875" customWidth="1"/>
+    <col min="15627" max="15629" width="14.453125" customWidth="1"/>
+    <col min="15630" max="15630" width="15.81640625" customWidth="1"/>
+    <col min="15631" max="15631" width="7.81640625" customWidth="1"/>
+    <col min="15632" max="15632" width="5.453125" customWidth="1"/>
+    <col min="15633" max="15633" width="6.453125" customWidth="1"/>
+    <col min="15634" max="15634" width="7.81640625" customWidth="1"/>
+    <col min="15635" max="15635" width="3" customWidth="1"/>
+    <col min="15636" max="15636" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15873" max="15876" width="14.453125" customWidth="1"/>
+    <col min="15877" max="15877" width="15.453125" customWidth="1"/>
+    <col min="15878" max="15878" width="14.54296875" customWidth="1"/>
+    <col min="15879" max="15879" width="15.26953125" customWidth="1"/>
+    <col min="15880" max="15881" width="14.453125" customWidth="1"/>
+    <col min="15882" max="15882" width="13.1796875" customWidth="1"/>
+    <col min="15883" max="15885" width="14.453125" customWidth="1"/>
+    <col min="15886" max="15886" width="15.81640625" customWidth="1"/>
+    <col min="15887" max="15887" width="7.81640625" customWidth="1"/>
+    <col min="15888" max="15888" width="5.453125" customWidth="1"/>
+    <col min="15889" max="15889" width="6.453125" customWidth="1"/>
+    <col min="15890" max="15890" width="7.81640625" customWidth="1"/>
+    <col min="15891" max="15891" width="3" customWidth="1"/>
+    <col min="15892" max="15892" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="16129" max="16132" width="14.453125" customWidth="1"/>
+    <col min="16133" max="16133" width="15.453125" customWidth="1"/>
+    <col min="16134" max="16134" width="14.54296875" customWidth="1"/>
+    <col min="16135" max="16135" width="15.26953125" customWidth="1"/>
+    <col min="16136" max="16137" width="14.453125" customWidth="1"/>
+    <col min="16138" max="16138" width="13.1796875" customWidth="1"/>
+    <col min="16139" max="16141" width="14.453125" customWidth="1"/>
+    <col min="16142" max="16142" width="15.81640625" customWidth="1"/>
+    <col min="16143" max="16143" width="7.81640625" customWidth="1"/>
+    <col min="16144" max="16144" width="5.453125" customWidth="1"/>
+    <col min="16145" max="16145" width="6.453125" customWidth="1"/>
+    <col min="16146" max="16146" width="7.81640625" customWidth="1"/>
+    <col min="16147" max="16147" width="3" customWidth="1"/>
+    <col min="16148" max="16148" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="292" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
+      <c r="S1"/>
+    </row>
+    <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2"/>
+    </row>
+    <row r="3" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" s="281" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F3" s="281" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="129" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="283" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="288" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="26"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="285" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" s="286"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="278" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="279"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="29"/>
+    </row>
+    <row r="4" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="281"/>
+      <c r="E4" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F4" s="281"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="283"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="288"/>
+      <c r="O4" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" s="274" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" s="275" t="s">
+        <v>71</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" s="270" t="s">
+        <v>70</v>
+      </c>
+      <c r="U4" s="271" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" s="37"/>
+      <c r="E5" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F5" s="284" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="281" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="54"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="38"/>
+      <c r="O5" s="39">
+        <v>31</v>
+      </c>
+      <c r="P5" s="40">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="41">
+        <v>19</v>
+      </c>
+      <c r="R5" s="42">
+        <v>11</v>
+      </c>
+      <c r="S5" s="40">
+        <v>31</v>
+      </c>
+      <c r="T5" s="41">
+        <v>19</v>
+      </c>
+      <c r="U5" s="42">
+        <v>11</v>
+      </c>
+      <c r="V5" s="43">
+        <f t="shared" ref="V5:V17" si="0">-SUM(S5-P5)*-1</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="44"/>
+    </row>
+    <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="284"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="129" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="281"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="126" t="s">
+        <v>215</v>
+      </c>
+      <c r="N6" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" s="47">
+        <v>49</v>
+      </c>
+      <c r="P6" s="48">
+        <f t="shared" ref="P6:P17" si="1">SUM(Q6:R6)</f>
+        <v>12</v>
+      </c>
+      <c r="Q6" s="49">
+        <v>7</v>
+      </c>
+      <c r="R6" s="50">
+        <v>5</v>
+      </c>
+      <c r="S6" s="48">
+        <f t="shared" ref="S6:S17" si="2">SUM(T6:U6)</f>
+        <v>12</v>
+      </c>
+      <c r="T6" s="49">
+        <v>7</v>
+      </c>
+      <c r="U6" s="50">
+        <v>5</v>
+      </c>
+      <c r="V6" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="52"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="53"/>
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="284" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="64"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="288" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" s="54"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="47">
+        <v>22</v>
+      </c>
+      <c r="P7" s="48">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Q7" s="49">
+        <v>11</v>
+      </c>
+      <c r="R7" s="50">
+        <v>4</v>
+      </c>
+      <c r="S7" s="48">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="T7" s="49">
+        <v>11</v>
+      </c>
+      <c r="U7" s="50">
+        <v>4</v>
+      </c>
+      <c r="V7" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W7" s="52"/>
+    </row>
+    <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="45"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="284"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="288"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="56">
+        <v>46314</v>
+      </c>
+      <c r="O8" s="47">
+        <v>24</v>
+      </c>
+      <c r="P8" s="48">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Q8" s="49">
+        <v>3</v>
+      </c>
+      <c r="R8" s="50">
+        <v>3</v>
+      </c>
+      <c r="S8" s="48">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="T8" s="49">
+        <v>2</v>
+      </c>
+      <c r="U8" s="50">
+        <v>2</v>
+      </c>
+      <c r="V8" s="51">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="W8" s="52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="45"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="58"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="287" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="64"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9" s="47"/>
+      <c r="P9" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="49"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W9" s="52"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="45"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="129" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="61"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="287"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="49"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="52"/>
+    </row>
+    <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="64"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="61"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="64"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="66"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="68"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="70"/>
+    </row>
+    <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="71"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="64"/>
+      <c r="H12" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="L12" s="73" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" s="74"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="68"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W12" s="70"/>
+    </row>
+    <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="61"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="276" t="s">
+        <v>149</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="127" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="128"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="60"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="68"/>
+      <c r="U13" s="69"/>
+      <c r="V13" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="70"/>
+    </row>
+    <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="8"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="276" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="60"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="68"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="70"/>
+    </row>
+    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="129"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="273"/>
+      <c r="F15" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="107"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="68"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="70"/>
+    </row>
+    <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="287" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="287" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="288" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="61"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="273" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="107"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="68"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="68"/>
+      <c r="U16" s="69"/>
+      <c r="V16" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="70"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="287"/>
+      <c r="B17" s="287"/>
+      <c r="C17" s="288"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="80"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="82">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="83"/>
+    </row>
+    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="288" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="61"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="77"/>
+      <c r="M18" s="77"/>
+      <c r="R18" s="84"/>
+      <c r="S18"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="273"/>
+      <c r="C19" s="288"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="77"/>
+      <c r="R19" s="84"/>
+      <c r="S19"/>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="85" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="273"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="158"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="R20" s="84"/>
+      <c r="S20"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="128" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="D21" s="61"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="R21" s="84"/>
+      <c r="S21"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="6"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="273"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="R22" s="84"/>
+      <c r="S22"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="R23" s="84"/>
+      <c r="S23"/>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="R24" s="84"/>
+      <c r="S24"/>
+    </row>
+    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="30"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="R25" s="84"/>
+      <c r="S25"/>
+    </row>
+    <row r="26" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="273"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="R26" s="84"/>
+      <c r="S26"/>
+    </row>
+    <row r="27" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="R27" s="84"/>
+      <c r="S27"/>
+    </row>
+    <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="293" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="R28" s="84"/>
+      <c r="S28"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="30"/>
+      <c r="I29" s="273"/>
+      <c r="J29" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K29" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="92" t="s">
+        <v>25</v>
+      </c>
+      <c r="R29" s="84"/>
+      <c r="S29"/>
+    </row>
+    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="B30" s="94"/>
+      <c r="C30" s="93" t="s">
+        <v>231</v>
+      </c>
+      <c r="D30" s="93" t="s">
+        <v>234</v>
+      </c>
+      <c r="E30" s="282" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="8"/>
+      <c r="G30" s="272" t="s">
+        <v>240</v>
+      </c>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="K30" s="124" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="218" t="s">
+        <v>119</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="R30" s="84"/>
+      <c r="S30"/>
+    </row>
+    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="93" t="s">
+        <v>232</v>
+      </c>
+      <c r="D31" s="93" t="s">
+        <v>233</v>
+      </c>
+      <c r="E31" s="282"/>
+      <c r="F31" s="8"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="159"/>
+      <c r="K31" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="L31" s="218" t="s">
+        <v>122</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" s="84"/>
+      <c r="S31"/>
+    </row>
+    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="94"/>
+      <c r="C32" s="93" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="93" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" s="282" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="159"/>
+      <c r="K32" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="L32" s="218" t="s">
+        <v>243</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="R32" s="84"/>
+      <c r="S32"/>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="8"/>
+      <c r="C33" s="93" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="93" t="s">
+        <v>236</v>
+      </c>
+      <c r="E33" s="282"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="224" t="s">
+        <v>42</v>
+      </c>
+      <c r="L33" s="218" t="s">
+        <v>38</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="R33" s="84"/>
+      <c r="S33"/>
+    </row>
+    <row r="34" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="94"/>
+      <c r="B34" s="95"/>
+      <c r="D34" s="93" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" s="280" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="K34" s="110" t="s">
+        <v>150</v>
+      </c>
+      <c r="L34" s="224" t="s">
+        <v>100</v>
+      </c>
+      <c r="M34" s="8"/>
+      <c r="R34" s="84"/>
+      <c r="S34"/>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="94"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="93" t="s">
+        <v>238</v>
+      </c>
+      <c r="E35" s="280"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="110" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="8"/>
+      <c r="M35" s="13"/>
+      <c r="R35" s="84"/>
+      <c r="S35"/>
+    </row>
+    <row r="36" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="94"/>
+      <c r="B36" s="94"/>
+      <c r="D36" s="93" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="282" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="97"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="224" t="s">
+        <v>203</v>
+      </c>
+      <c r="L36" s="8"/>
+      <c r="M36" s="94"/>
+      <c r="R36" s="84"/>
+      <c r="S36"/>
+    </row>
+    <row r="37" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="E37" s="282"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="100"/>
+      <c r="K37" s="124" t="s">
+        <v>211</v>
+      </c>
+      <c r="L37" s="8"/>
+      <c r="M37" s="94"/>
+      <c r="R37" s="84"/>
+      <c r="S37"/>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="77"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="272" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" s="77"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="124" t="s">
+        <v>212</v>
+      </c>
+      <c r="L38" s="8"/>
+      <c r="M38" s="2"/>
+      <c r="R38" s="84"/>
+      <c r="S38"/>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="74"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="272" t="s">
+        <v>92</v>
+      </c>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="2"/>
+      <c r="S39"/>
+    </row>
+    <row r="40" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="105"/>
+      <c r="S40"/>
+    </row>
+    <row r="41" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="104"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="104"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="93" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="8"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="101"/>
+      <c r="M41" s="106"/>
+      <c r="S41"/>
+    </row>
+    <row r="42" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="104"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="104"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="272" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="106"/>
+      <c r="S42"/>
+    </row>
+    <row r="43" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="104"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="272" t="s">
+        <v>216</v>
+      </c>
+      <c r="F43" s="107"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="106"/>
+      <c r="S43"/>
+    </row>
+    <row r="44" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="104"/>
+      <c r="B44" s="104"/>
+      <c r="C44" s="104"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="109"/>
+      <c r="S44"/>
+    </row>
+    <row r="45" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="104"/>
+      <c r="B45" s="104"/>
+      <c r="C45" s="104"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="110"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="111"/>
+      <c r="S45"/>
+    </row>
+    <row r="46" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="104"/>
+      <c r="B46" s="104"/>
+      <c r="C46" s="104"/>
+      <c r="D46" s="104"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="104"/>
+      <c r="J46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="111"/>
+      <c r="S46"/>
+    </row>
+    <row r="47" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="104"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="104"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="104"/>
+      <c r="H47" s="104"/>
+      <c r="I47" s="273"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="112"/>
+      <c r="S47"/>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="84"/>
+      <c r="S48"/>
+    </row>
+    <row r="49" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="77"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="113"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="104"/>
+      <c r="I49" s="273"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="84"/>
+      <c r="S49"/>
+    </row>
+    <row r="50" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="77"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="84"/>
+      <c r="S50"/>
+    </row>
+    <row r="51" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="77"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="77"/>
+      <c r="D51" s="113"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="77"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="84"/>
+      <c r="S51"/>
+    </row>
+    <row r="52" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="77"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="113"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="77"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="77"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+    </row>
+    <row r="53" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="77"/>
+      <c r="B53" s="77"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="113"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="77"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="114"/>
+      <c r="M53" s="8"/>
+    </row>
+    <row r="54" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="77"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="113"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="77"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="77"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="114"/>
+      <c r="M54" s="8"/>
+    </row>
+    <row r="55" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="77"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="113"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="77"/>
+      <c r="G55" s="77"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="104"/>
+      <c r="J55" s="77"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="114"/>
+      <c r="M55" s="8"/>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="77"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="113"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="77"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="77"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="114"/>
+      <c r="M56" s="8"/>
+    </row>
+    <row r="57" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="77"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="77"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="114"/>
+      <c r="M57" s="8"/>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="77"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="113"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="77"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="115"/>
+      <c r="L58" s="114"/>
+      <c r="M58" s="8"/>
+    </row>
+    <row r="59" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="77"/>
+      <c r="B59" s="77"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="113"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="77"/>
+      <c r="G59" s="77"/>
+      <c r="H59" s="104"/>
+      <c r="I59" s="104"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="115"/>
+      <c r="L59" s="114"/>
+      <c r="M59" s="8"/>
+    </row>
+    <row r="60" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="77"/>
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="77"/>
+      <c r="G60" s="77"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="115"/>
+      <c r="L60" s="114"/>
+      <c r="M60" s="8"/>
+    </row>
+    <row r="61" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="77"/>
+      <c r="B61" s="77"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="113"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="114"/>
+      <c r="M61" s="8"/>
+    </row>
+    <row r="62" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="77"/>
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="77"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="114"/>
+      <c r="M62" s="8"/>
+    </row>
+    <row r="63" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="77"/>
+      <c r="B63" s="77"/>
+      <c r="C63" s="77"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="104"/>
+      <c r="I63" s="104"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="77"/>
+      <c r="M63" s="8"/>
+    </row>
+    <row r="64" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="77"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="77"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="77"/>
+      <c r="H64" s="104"/>
+      <c r="I64" s="104"/>
+      <c r="J64" s="77"/>
+      <c r="K64" s="116">
+        <v>22</v>
+      </c>
+      <c r="L64" s="117">
+        <v>6</v>
+      </c>
+      <c r="M64" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="61"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
+      <c r="S65"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L66" s="119" t="s">
+        <v>94</v>
+      </c>
+      <c r="M66" s="25">
+        <v>97</v>
+      </c>
+      <c r="S66"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L67" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="M67" s="25">
+        <f>SUM(M66-(M68+M69+M70))</f>
+        <v>69</v>
+      </c>
+      <c r="S67"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L68" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" s="25">
+        <v>15</v>
+      </c>
+      <c r="S68"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L69" s="121" t="s">
+        <v>24</v>
+      </c>
+      <c r="M69" s="25">
+        <v>9</v>
+      </c>
+      <c r="S69"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L70" s="122" t="s">
+        <v>25</v>
+      </c>
+      <c r="M70" s="25">
+        <v>4</v>
+      </c>
+      <c r="S70"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L71" t="s">
+        <v>96</v>
+      </c>
+      <c r="M71" s="25">
+        <v>13</v>
+      </c>
+      <c r="S71"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="M72" s="25"/>
+      <c r="S72"/>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:W72"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" style="98" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" style="25" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" style="25" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" style="25" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" customWidth="1"/>
+    <col min="14" max="14" width="21.26953125" customWidth="1"/>
+    <col min="15" max="15" width="9.7265625" customWidth="1"/>
+    <col min="16" max="16" width="7.7265625" customWidth="1"/>
+    <col min="17" max="17" width="6.453125" customWidth="1"/>
+    <col min="18" max="18" width="7.81640625" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" style="84" customWidth="1"/>
+    <col min="20" max="20" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="257" max="260" width="14.453125" customWidth="1"/>
+    <col min="261" max="261" width="15.453125" customWidth="1"/>
+    <col min="262" max="262" width="14.54296875" customWidth="1"/>
+    <col min="263" max="263" width="15.26953125" customWidth="1"/>
+    <col min="264" max="265" width="14.453125" customWidth="1"/>
+    <col min="266" max="266" width="13.1796875" customWidth="1"/>
+    <col min="267" max="269" width="14.453125" customWidth="1"/>
+    <col min="270" max="270" width="15.81640625" customWidth="1"/>
+    <col min="271" max="271" width="7.81640625" customWidth="1"/>
+    <col min="272" max="272" width="5.453125" customWidth="1"/>
+    <col min="273" max="273" width="6.453125" customWidth="1"/>
+    <col min="274" max="274" width="7.81640625" customWidth="1"/>
+    <col min="275" max="275" width="3" customWidth="1"/>
+    <col min="276" max="276" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="513" max="516" width="14.453125" customWidth="1"/>
+    <col min="517" max="517" width="15.453125" customWidth="1"/>
+    <col min="518" max="518" width="14.54296875" customWidth="1"/>
+    <col min="519" max="519" width="15.26953125" customWidth="1"/>
+    <col min="520" max="521" width="14.453125" customWidth="1"/>
+    <col min="522" max="522" width="13.1796875" customWidth="1"/>
+    <col min="523" max="525" width="14.453125" customWidth="1"/>
+    <col min="526" max="526" width="15.81640625" customWidth="1"/>
+    <col min="527" max="527" width="7.81640625" customWidth="1"/>
+    <col min="528" max="528" width="5.453125" customWidth="1"/>
+    <col min="529" max="529" width="6.453125" customWidth="1"/>
+    <col min="530" max="530" width="7.81640625" customWidth="1"/>
+    <col min="531" max="531" width="3" customWidth="1"/>
+    <col min="532" max="532" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="769" max="772" width="14.453125" customWidth="1"/>
+    <col min="773" max="773" width="15.453125" customWidth="1"/>
+    <col min="774" max="774" width="14.54296875" customWidth="1"/>
+    <col min="775" max="775" width="15.26953125" customWidth="1"/>
+    <col min="776" max="777" width="14.453125" customWidth="1"/>
+    <col min="778" max="778" width="13.1796875" customWidth="1"/>
+    <col min="779" max="781" width="14.453125" customWidth="1"/>
+    <col min="782" max="782" width="15.81640625" customWidth="1"/>
+    <col min="783" max="783" width="7.81640625" customWidth="1"/>
+    <col min="784" max="784" width="5.453125" customWidth="1"/>
+    <col min="785" max="785" width="6.453125" customWidth="1"/>
+    <col min="786" max="786" width="7.81640625" customWidth="1"/>
+    <col min="787" max="787" width="3" customWidth="1"/>
+    <col min="788" max="788" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1025" max="1028" width="14.453125" customWidth="1"/>
+    <col min="1029" max="1029" width="15.453125" customWidth="1"/>
+    <col min="1030" max="1030" width="14.54296875" customWidth="1"/>
+    <col min="1031" max="1031" width="15.26953125" customWidth="1"/>
+    <col min="1032" max="1033" width="14.453125" customWidth="1"/>
+    <col min="1034" max="1034" width="13.1796875" customWidth="1"/>
+    <col min="1035" max="1037" width="14.453125" customWidth="1"/>
+    <col min="1038" max="1038" width="15.81640625" customWidth="1"/>
+    <col min="1039" max="1039" width="7.81640625" customWidth="1"/>
+    <col min="1040" max="1040" width="5.453125" customWidth="1"/>
+    <col min="1041" max="1041" width="6.453125" customWidth="1"/>
+    <col min="1042" max="1042" width="7.81640625" customWidth="1"/>
+    <col min="1043" max="1043" width="3" customWidth="1"/>
+    <col min="1044" max="1044" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1281" max="1284" width="14.453125" customWidth="1"/>
+    <col min="1285" max="1285" width="15.453125" customWidth="1"/>
+    <col min="1286" max="1286" width="14.54296875" customWidth="1"/>
+    <col min="1287" max="1287" width="15.26953125" customWidth="1"/>
+    <col min="1288" max="1289" width="14.453125" customWidth="1"/>
+    <col min="1290" max="1290" width="13.1796875" customWidth="1"/>
+    <col min="1291" max="1293" width="14.453125" customWidth="1"/>
+    <col min="1294" max="1294" width="15.81640625" customWidth="1"/>
+    <col min="1295" max="1295" width="7.81640625" customWidth="1"/>
+    <col min="1296" max="1296" width="5.453125" customWidth="1"/>
+    <col min="1297" max="1297" width="6.453125" customWidth="1"/>
+    <col min="1298" max="1298" width="7.81640625" customWidth="1"/>
+    <col min="1299" max="1299" width="3" customWidth="1"/>
+    <col min="1300" max="1300" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1537" max="1540" width="14.453125" customWidth="1"/>
+    <col min="1541" max="1541" width="15.453125" customWidth="1"/>
+    <col min="1542" max="1542" width="14.54296875" customWidth="1"/>
+    <col min="1543" max="1543" width="15.26953125" customWidth="1"/>
+    <col min="1544" max="1545" width="14.453125" customWidth="1"/>
+    <col min="1546" max="1546" width="13.1796875" customWidth="1"/>
+    <col min="1547" max="1549" width="14.453125" customWidth="1"/>
+    <col min="1550" max="1550" width="15.81640625" customWidth="1"/>
+    <col min="1551" max="1551" width="7.81640625" customWidth="1"/>
+    <col min="1552" max="1552" width="5.453125" customWidth="1"/>
+    <col min="1553" max="1553" width="6.453125" customWidth="1"/>
+    <col min="1554" max="1554" width="7.81640625" customWidth="1"/>
+    <col min="1555" max="1555" width="3" customWidth="1"/>
+    <col min="1556" max="1556" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1793" max="1796" width="14.453125" customWidth="1"/>
+    <col min="1797" max="1797" width="15.453125" customWidth="1"/>
+    <col min="1798" max="1798" width="14.54296875" customWidth="1"/>
+    <col min="1799" max="1799" width="15.26953125" customWidth="1"/>
+    <col min="1800" max="1801" width="14.453125" customWidth="1"/>
+    <col min="1802" max="1802" width="13.1796875" customWidth="1"/>
+    <col min="1803" max="1805" width="14.453125" customWidth="1"/>
+    <col min="1806" max="1806" width="15.81640625" customWidth="1"/>
+    <col min="1807" max="1807" width="7.81640625" customWidth="1"/>
+    <col min="1808" max="1808" width="5.453125" customWidth="1"/>
+    <col min="1809" max="1809" width="6.453125" customWidth="1"/>
+    <col min="1810" max="1810" width="7.81640625" customWidth="1"/>
+    <col min="1811" max="1811" width="3" customWidth="1"/>
+    <col min="1812" max="1812" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2049" max="2052" width="14.453125" customWidth="1"/>
+    <col min="2053" max="2053" width="15.453125" customWidth="1"/>
+    <col min="2054" max="2054" width="14.54296875" customWidth="1"/>
+    <col min="2055" max="2055" width="15.26953125" customWidth="1"/>
+    <col min="2056" max="2057" width="14.453125" customWidth="1"/>
+    <col min="2058" max="2058" width="13.1796875" customWidth="1"/>
+    <col min="2059" max="2061" width="14.453125" customWidth="1"/>
+    <col min="2062" max="2062" width="15.81640625" customWidth="1"/>
+    <col min="2063" max="2063" width="7.81640625" customWidth="1"/>
+    <col min="2064" max="2064" width="5.453125" customWidth="1"/>
+    <col min="2065" max="2065" width="6.453125" customWidth="1"/>
+    <col min="2066" max="2066" width="7.81640625" customWidth="1"/>
+    <col min="2067" max="2067" width="3" customWidth="1"/>
+    <col min="2068" max="2068" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2305" max="2308" width="14.453125" customWidth="1"/>
+    <col min="2309" max="2309" width="15.453125" customWidth="1"/>
+    <col min="2310" max="2310" width="14.54296875" customWidth="1"/>
+    <col min="2311" max="2311" width="15.26953125" customWidth="1"/>
+    <col min="2312" max="2313" width="14.453125" customWidth="1"/>
+    <col min="2314" max="2314" width="13.1796875" customWidth="1"/>
+    <col min="2315" max="2317" width="14.453125" customWidth="1"/>
+    <col min="2318" max="2318" width="15.81640625" customWidth="1"/>
+    <col min="2319" max="2319" width="7.81640625" customWidth="1"/>
+    <col min="2320" max="2320" width="5.453125" customWidth="1"/>
+    <col min="2321" max="2321" width="6.453125" customWidth="1"/>
+    <col min="2322" max="2322" width="7.81640625" customWidth="1"/>
+    <col min="2323" max="2323" width="3" customWidth="1"/>
+    <col min="2324" max="2324" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2561" max="2564" width="14.453125" customWidth="1"/>
+    <col min="2565" max="2565" width="15.453125" customWidth="1"/>
+    <col min="2566" max="2566" width="14.54296875" customWidth="1"/>
+    <col min="2567" max="2567" width="15.26953125" customWidth="1"/>
+    <col min="2568" max="2569" width="14.453125" customWidth="1"/>
+    <col min="2570" max="2570" width="13.1796875" customWidth="1"/>
+    <col min="2571" max="2573" width="14.453125" customWidth="1"/>
+    <col min="2574" max="2574" width="15.81640625" customWidth="1"/>
+    <col min="2575" max="2575" width="7.81640625" customWidth="1"/>
+    <col min="2576" max="2576" width="5.453125" customWidth="1"/>
+    <col min="2577" max="2577" width="6.453125" customWidth="1"/>
+    <col min="2578" max="2578" width="7.81640625" customWidth="1"/>
+    <col min="2579" max="2579" width="3" customWidth="1"/>
+    <col min="2580" max="2580" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2817" max="2820" width="14.453125" customWidth="1"/>
+    <col min="2821" max="2821" width="15.453125" customWidth="1"/>
+    <col min="2822" max="2822" width="14.54296875" customWidth="1"/>
+    <col min="2823" max="2823" width="15.26953125" customWidth="1"/>
+    <col min="2824" max="2825" width="14.453125" customWidth="1"/>
+    <col min="2826" max="2826" width="13.1796875" customWidth="1"/>
+    <col min="2827" max="2829" width="14.453125" customWidth="1"/>
+    <col min="2830" max="2830" width="15.81640625" customWidth="1"/>
+    <col min="2831" max="2831" width="7.81640625" customWidth="1"/>
+    <col min="2832" max="2832" width="5.453125" customWidth="1"/>
+    <col min="2833" max="2833" width="6.453125" customWidth="1"/>
+    <col min="2834" max="2834" width="7.81640625" customWidth="1"/>
+    <col min="2835" max="2835" width="3" customWidth="1"/>
+    <col min="2836" max="2836" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3073" max="3076" width="14.453125" customWidth="1"/>
+    <col min="3077" max="3077" width="15.453125" customWidth="1"/>
+    <col min="3078" max="3078" width="14.54296875" customWidth="1"/>
+    <col min="3079" max="3079" width="15.26953125" customWidth="1"/>
+    <col min="3080" max="3081" width="14.453125" customWidth="1"/>
+    <col min="3082" max="3082" width="13.1796875" customWidth="1"/>
+    <col min="3083" max="3085" width="14.453125" customWidth="1"/>
+    <col min="3086" max="3086" width="15.81640625" customWidth="1"/>
+    <col min="3087" max="3087" width="7.81640625" customWidth="1"/>
+    <col min="3088" max="3088" width="5.453125" customWidth="1"/>
+    <col min="3089" max="3089" width="6.453125" customWidth="1"/>
+    <col min="3090" max="3090" width="7.81640625" customWidth="1"/>
+    <col min="3091" max="3091" width="3" customWidth="1"/>
+    <col min="3092" max="3092" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3329" max="3332" width="14.453125" customWidth="1"/>
+    <col min="3333" max="3333" width="15.453125" customWidth="1"/>
+    <col min="3334" max="3334" width="14.54296875" customWidth="1"/>
+    <col min="3335" max="3335" width="15.26953125" customWidth="1"/>
+    <col min="3336" max="3337" width="14.453125" customWidth="1"/>
+    <col min="3338" max="3338" width="13.1796875" customWidth="1"/>
+    <col min="3339" max="3341" width="14.453125" customWidth="1"/>
+    <col min="3342" max="3342" width="15.81640625" customWidth="1"/>
+    <col min="3343" max="3343" width="7.81640625" customWidth="1"/>
+    <col min="3344" max="3344" width="5.453125" customWidth="1"/>
+    <col min="3345" max="3345" width="6.453125" customWidth="1"/>
+    <col min="3346" max="3346" width="7.81640625" customWidth="1"/>
+    <col min="3347" max="3347" width="3" customWidth="1"/>
+    <col min="3348" max="3348" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3585" max="3588" width="14.453125" customWidth="1"/>
+    <col min="3589" max="3589" width="15.453125" customWidth="1"/>
+    <col min="3590" max="3590" width="14.54296875" customWidth="1"/>
+    <col min="3591" max="3591" width="15.26953125" customWidth="1"/>
+    <col min="3592" max="3593" width="14.453125" customWidth="1"/>
+    <col min="3594" max="3594" width="13.1796875" customWidth="1"/>
+    <col min="3595" max="3597" width="14.453125" customWidth="1"/>
+    <col min="3598" max="3598" width="15.81640625" customWidth="1"/>
+    <col min="3599" max="3599" width="7.81640625" customWidth="1"/>
+    <col min="3600" max="3600" width="5.453125" customWidth="1"/>
+    <col min="3601" max="3601" width="6.453125" customWidth="1"/>
+    <col min="3602" max="3602" width="7.81640625" customWidth="1"/>
+    <col min="3603" max="3603" width="3" customWidth="1"/>
+    <col min="3604" max="3604" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3841" max="3844" width="14.453125" customWidth="1"/>
+    <col min="3845" max="3845" width="15.453125" customWidth="1"/>
+    <col min="3846" max="3846" width="14.54296875" customWidth="1"/>
+    <col min="3847" max="3847" width="15.26953125" customWidth="1"/>
+    <col min="3848" max="3849" width="14.453125" customWidth="1"/>
+    <col min="3850" max="3850" width="13.1796875" customWidth="1"/>
+    <col min="3851" max="3853" width="14.453125" customWidth="1"/>
+    <col min="3854" max="3854" width="15.81640625" customWidth="1"/>
+    <col min="3855" max="3855" width="7.81640625" customWidth="1"/>
+    <col min="3856" max="3856" width="5.453125" customWidth="1"/>
+    <col min="3857" max="3857" width="6.453125" customWidth="1"/>
+    <col min="3858" max="3858" width="7.81640625" customWidth="1"/>
+    <col min="3859" max="3859" width="3" customWidth="1"/>
+    <col min="3860" max="3860" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4097" max="4100" width="14.453125" customWidth="1"/>
+    <col min="4101" max="4101" width="15.453125" customWidth="1"/>
+    <col min="4102" max="4102" width="14.54296875" customWidth="1"/>
+    <col min="4103" max="4103" width="15.26953125" customWidth="1"/>
+    <col min="4104" max="4105" width="14.453125" customWidth="1"/>
+    <col min="4106" max="4106" width="13.1796875" customWidth="1"/>
+    <col min="4107" max="4109" width="14.453125" customWidth="1"/>
+    <col min="4110" max="4110" width="15.81640625" customWidth="1"/>
+    <col min="4111" max="4111" width="7.81640625" customWidth="1"/>
+    <col min="4112" max="4112" width="5.453125" customWidth="1"/>
+    <col min="4113" max="4113" width="6.453125" customWidth="1"/>
+    <col min="4114" max="4114" width="7.81640625" customWidth="1"/>
+    <col min="4115" max="4115" width="3" customWidth="1"/>
+    <col min="4116" max="4116" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4353" max="4356" width="14.453125" customWidth="1"/>
+    <col min="4357" max="4357" width="15.453125" customWidth="1"/>
+    <col min="4358" max="4358" width="14.54296875" customWidth="1"/>
+    <col min="4359" max="4359" width="15.26953125" customWidth="1"/>
+    <col min="4360" max="4361" width="14.453125" customWidth="1"/>
+    <col min="4362" max="4362" width="13.1796875" customWidth="1"/>
+    <col min="4363" max="4365" width="14.453125" customWidth="1"/>
+    <col min="4366" max="4366" width="15.81640625" customWidth="1"/>
+    <col min="4367" max="4367" width="7.81640625" customWidth="1"/>
+    <col min="4368" max="4368" width="5.453125" customWidth="1"/>
+    <col min="4369" max="4369" width="6.453125" customWidth="1"/>
+    <col min="4370" max="4370" width="7.81640625" customWidth="1"/>
+    <col min="4371" max="4371" width="3" customWidth="1"/>
+    <col min="4372" max="4372" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4609" max="4612" width="14.453125" customWidth="1"/>
+    <col min="4613" max="4613" width="15.453125" customWidth="1"/>
+    <col min="4614" max="4614" width="14.54296875" customWidth="1"/>
+    <col min="4615" max="4615" width="15.26953125" customWidth="1"/>
+    <col min="4616" max="4617" width="14.453125" customWidth="1"/>
+    <col min="4618" max="4618" width="13.1796875" customWidth="1"/>
+    <col min="4619" max="4621" width="14.453125" customWidth="1"/>
+    <col min="4622" max="4622" width="15.81640625" customWidth="1"/>
+    <col min="4623" max="4623" width="7.81640625" customWidth="1"/>
+    <col min="4624" max="4624" width="5.453125" customWidth="1"/>
+    <col min="4625" max="4625" width="6.453125" customWidth="1"/>
+    <col min="4626" max="4626" width="7.81640625" customWidth="1"/>
+    <col min="4627" max="4627" width="3" customWidth="1"/>
+    <col min="4628" max="4628" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4865" max="4868" width="14.453125" customWidth="1"/>
+    <col min="4869" max="4869" width="15.453125" customWidth="1"/>
+    <col min="4870" max="4870" width="14.54296875" customWidth="1"/>
+    <col min="4871" max="4871" width="15.26953125" customWidth="1"/>
+    <col min="4872" max="4873" width="14.453125" customWidth="1"/>
+    <col min="4874" max="4874" width="13.1796875" customWidth="1"/>
+    <col min="4875" max="4877" width="14.453125" customWidth="1"/>
+    <col min="4878" max="4878" width="15.81640625" customWidth="1"/>
+    <col min="4879" max="4879" width="7.81640625" customWidth="1"/>
+    <col min="4880" max="4880" width="5.453125" customWidth="1"/>
+    <col min="4881" max="4881" width="6.453125" customWidth="1"/>
+    <col min="4882" max="4882" width="7.81640625" customWidth="1"/>
+    <col min="4883" max="4883" width="3" customWidth="1"/>
+    <col min="4884" max="4884" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5121" max="5124" width="14.453125" customWidth="1"/>
+    <col min="5125" max="5125" width="15.453125" customWidth="1"/>
+    <col min="5126" max="5126" width="14.54296875" customWidth="1"/>
+    <col min="5127" max="5127" width="15.26953125" customWidth="1"/>
+    <col min="5128" max="5129" width="14.453125" customWidth="1"/>
+    <col min="5130" max="5130" width="13.1796875" customWidth="1"/>
+    <col min="5131" max="5133" width="14.453125" customWidth="1"/>
+    <col min="5134" max="5134" width="15.81640625" customWidth="1"/>
+    <col min="5135" max="5135" width="7.81640625" customWidth="1"/>
+    <col min="5136" max="5136" width="5.453125" customWidth="1"/>
+    <col min="5137" max="5137" width="6.453125" customWidth="1"/>
+    <col min="5138" max="5138" width="7.81640625" customWidth="1"/>
+    <col min="5139" max="5139" width="3" customWidth="1"/>
+    <col min="5140" max="5140" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5377" max="5380" width="14.453125" customWidth="1"/>
+    <col min="5381" max="5381" width="15.453125" customWidth="1"/>
+    <col min="5382" max="5382" width="14.54296875" customWidth="1"/>
+    <col min="5383" max="5383" width="15.26953125" customWidth="1"/>
+    <col min="5384" max="5385" width="14.453125" customWidth="1"/>
+    <col min="5386" max="5386" width="13.1796875" customWidth="1"/>
+    <col min="5387" max="5389" width="14.453125" customWidth="1"/>
+    <col min="5390" max="5390" width="15.81640625" customWidth="1"/>
+    <col min="5391" max="5391" width="7.81640625" customWidth="1"/>
+    <col min="5392" max="5392" width="5.453125" customWidth="1"/>
+    <col min="5393" max="5393" width="6.453125" customWidth="1"/>
+    <col min="5394" max="5394" width="7.81640625" customWidth="1"/>
+    <col min="5395" max="5395" width="3" customWidth="1"/>
+    <col min="5396" max="5396" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5633" max="5636" width="14.453125" customWidth="1"/>
+    <col min="5637" max="5637" width="15.453125" customWidth="1"/>
+    <col min="5638" max="5638" width="14.54296875" customWidth="1"/>
+    <col min="5639" max="5639" width="15.26953125" customWidth="1"/>
+    <col min="5640" max="5641" width="14.453125" customWidth="1"/>
+    <col min="5642" max="5642" width="13.1796875" customWidth="1"/>
+    <col min="5643" max="5645" width="14.453125" customWidth="1"/>
+    <col min="5646" max="5646" width="15.81640625" customWidth="1"/>
+    <col min="5647" max="5647" width="7.81640625" customWidth="1"/>
+    <col min="5648" max="5648" width="5.453125" customWidth="1"/>
+    <col min="5649" max="5649" width="6.453125" customWidth="1"/>
+    <col min="5650" max="5650" width="7.81640625" customWidth="1"/>
+    <col min="5651" max="5651" width="3" customWidth="1"/>
+    <col min="5652" max="5652" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5889" max="5892" width="14.453125" customWidth="1"/>
+    <col min="5893" max="5893" width="15.453125" customWidth="1"/>
+    <col min="5894" max="5894" width="14.54296875" customWidth="1"/>
+    <col min="5895" max="5895" width="15.26953125" customWidth="1"/>
+    <col min="5896" max="5897" width="14.453125" customWidth="1"/>
+    <col min="5898" max="5898" width="13.1796875" customWidth="1"/>
+    <col min="5899" max="5901" width="14.453125" customWidth="1"/>
+    <col min="5902" max="5902" width="15.81640625" customWidth="1"/>
+    <col min="5903" max="5903" width="7.81640625" customWidth="1"/>
+    <col min="5904" max="5904" width="5.453125" customWidth="1"/>
+    <col min="5905" max="5905" width="6.453125" customWidth="1"/>
+    <col min="5906" max="5906" width="7.81640625" customWidth="1"/>
+    <col min="5907" max="5907" width="3" customWidth="1"/>
+    <col min="5908" max="5908" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6145" max="6148" width="14.453125" customWidth="1"/>
+    <col min="6149" max="6149" width="15.453125" customWidth="1"/>
+    <col min="6150" max="6150" width="14.54296875" customWidth="1"/>
+    <col min="6151" max="6151" width="15.26953125" customWidth="1"/>
+    <col min="6152" max="6153" width="14.453125" customWidth="1"/>
+    <col min="6154" max="6154" width="13.1796875" customWidth="1"/>
+    <col min="6155" max="6157" width="14.453125" customWidth="1"/>
+    <col min="6158" max="6158" width="15.81640625" customWidth="1"/>
+    <col min="6159" max="6159" width="7.81640625" customWidth="1"/>
+    <col min="6160" max="6160" width="5.453125" customWidth="1"/>
+    <col min="6161" max="6161" width="6.453125" customWidth="1"/>
+    <col min="6162" max="6162" width="7.81640625" customWidth="1"/>
+    <col min="6163" max="6163" width="3" customWidth="1"/>
+    <col min="6164" max="6164" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6401" max="6404" width="14.453125" customWidth="1"/>
+    <col min="6405" max="6405" width="15.453125" customWidth="1"/>
+    <col min="6406" max="6406" width="14.54296875" customWidth="1"/>
+    <col min="6407" max="6407" width="15.26953125" customWidth="1"/>
+    <col min="6408" max="6409" width="14.453125" customWidth="1"/>
+    <col min="6410" max="6410" width="13.1796875" customWidth="1"/>
+    <col min="6411" max="6413" width="14.453125" customWidth="1"/>
+    <col min="6414" max="6414" width="15.81640625" customWidth="1"/>
+    <col min="6415" max="6415" width="7.81640625" customWidth="1"/>
+    <col min="6416" max="6416" width="5.453125" customWidth="1"/>
+    <col min="6417" max="6417" width="6.453125" customWidth="1"/>
+    <col min="6418" max="6418" width="7.81640625" customWidth="1"/>
+    <col min="6419" max="6419" width="3" customWidth="1"/>
+    <col min="6420" max="6420" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6657" max="6660" width="14.453125" customWidth="1"/>
+    <col min="6661" max="6661" width="15.453125" customWidth="1"/>
+    <col min="6662" max="6662" width="14.54296875" customWidth="1"/>
+    <col min="6663" max="6663" width="15.26953125" customWidth="1"/>
+    <col min="6664" max="6665" width="14.453125" customWidth="1"/>
+    <col min="6666" max="6666" width="13.1796875" customWidth="1"/>
+    <col min="6667" max="6669" width="14.453125" customWidth="1"/>
+    <col min="6670" max="6670" width="15.81640625" customWidth="1"/>
+    <col min="6671" max="6671" width="7.81640625" customWidth="1"/>
+    <col min="6672" max="6672" width="5.453125" customWidth="1"/>
+    <col min="6673" max="6673" width="6.453125" customWidth="1"/>
+    <col min="6674" max="6674" width="7.81640625" customWidth="1"/>
+    <col min="6675" max="6675" width="3" customWidth="1"/>
+    <col min="6676" max="6676" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6913" max="6916" width="14.453125" customWidth="1"/>
+    <col min="6917" max="6917" width="15.453125" customWidth="1"/>
+    <col min="6918" max="6918" width="14.54296875" customWidth="1"/>
+    <col min="6919" max="6919" width="15.26953125" customWidth="1"/>
+    <col min="6920" max="6921" width="14.453125" customWidth="1"/>
+    <col min="6922" max="6922" width="13.1796875" customWidth="1"/>
+    <col min="6923" max="6925" width="14.453125" customWidth="1"/>
+    <col min="6926" max="6926" width="15.81640625" customWidth="1"/>
+    <col min="6927" max="6927" width="7.81640625" customWidth="1"/>
+    <col min="6928" max="6928" width="5.453125" customWidth="1"/>
+    <col min="6929" max="6929" width="6.453125" customWidth="1"/>
+    <col min="6930" max="6930" width="7.81640625" customWidth="1"/>
+    <col min="6931" max="6931" width="3" customWidth="1"/>
+    <col min="6932" max="6932" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7169" max="7172" width="14.453125" customWidth="1"/>
+    <col min="7173" max="7173" width="15.453125" customWidth="1"/>
+    <col min="7174" max="7174" width="14.54296875" customWidth="1"/>
+    <col min="7175" max="7175" width="15.26953125" customWidth="1"/>
+    <col min="7176" max="7177" width="14.453125" customWidth="1"/>
+    <col min="7178" max="7178" width="13.1796875" customWidth="1"/>
+    <col min="7179" max="7181" width="14.453125" customWidth="1"/>
+    <col min="7182" max="7182" width="15.81640625" customWidth="1"/>
+    <col min="7183" max="7183" width="7.81640625" customWidth="1"/>
+    <col min="7184" max="7184" width="5.453125" customWidth="1"/>
+    <col min="7185" max="7185" width="6.453125" customWidth="1"/>
+    <col min="7186" max="7186" width="7.81640625" customWidth="1"/>
+    <col min="7187" max="7187" width="3" customWidth="1"/>
+    <col min="7188" max="7188" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7425" max="7428" width="14.453125" customWidth="1"/>
+    <col min="7429" max="7429" width="15.453125" customWidth="1"/>
+    <col min="7430" max="7430" width="14.54296875" customWidth="1"/>
+    <col min="7431" max="7431" width="15.26953125" customWidth="1"/>
+    <col min="7432" max="7433" width="14.453125" customWidth="1"/>
+    <col min="7434" max="7434" width="13.1796875" customWidth="1"/>
+    <col min="7435" max="7437" width="14.453125" customWidth="1"/>
+    <col min="7438" max="7438" width="15.81640625" customWidth="1"/>
+    <col min="7439" max="7439" width="7.81640625" customWidth="1"/>
+    <col min="7440" max="7440" width="5.453125" customWidth="1"/>
+    <col min="7441" max="7441" width="6.453125" customWidth="1"/>
+    <col min="7442" max="7442" width="7.81640625" customWidth="1"/>
+    <col min="7443" max="7443" width="3" customWidth="1"/>
+    <col min="7444" max="7444" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7681" max="7684" width="14.453125" customWidth="1"/>
+    <col min="7685" max="7685" width="15.453125" customWidth="1"/>
+    <col min="7686" max="7686" width="14.54296875" customWidth="1"/>
+    <col min="7687" max="7687" width="15.26953125" customWidth="1"/>
+    <col min="7688" max="7689" width="14.453125" customWidth="1"/>
+    <col min="7690" max="7690" width="13.1796875" customWidth="1"/>
+    <col min="7691" max="7693" width="14.453125" customWidth="1"/>
+    <col min="7694" max="7694" width="15.81640625" customWidth="1"/>
+    <col min="7695" max="7695" width="7.81640625" customWidth="1"/>
+    <col min="7696" max="7696" width="5.453125" customWidth="1"/>
+    <col min="7697" max="7697" width="6.453125" customWidth="1"/>
+    <col min="7698" max="7698" width="7.81640625" customWidth="1"/>
+    <col min="7699" max="7699" width="3" customWidth="1"/>
+    <col min="7700" max="7700" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7937" max="7940" width="14.453125" customWidth="1"/>
+    <col min="7941" max="7941" width="15.453125" customWidth="1"/>
+    <col min="7942" max="7942" width="14.54296875" customWidth="1"/>
+    <col min="7943" max="7943" width="15.26953125" customWidth="1"/>
+    <col min="7944" max="7945" width="14.453125" customWidth="1"/>
+    <col min="7946" max="7946" width="13.1796875" customWidth="1"/>
+    <col min="7947" max="7949" width="14.453125" customWidth="1"/>
+    <col min="7950" max="7950" width="15.81640625" customWidth="1"/>
+    <col min="7951" max="7951" width="7.81640625" customWidth="1"/>
+    <col min="7952" max="7952" width="5.453125" customWidth="1"/>
+    <col min="7953" max="7953" width="6.453125" customWidth="1"/>
+    <col min="7954" max="7954" width="7.81640625" customWidth="1"/>
+    <col min="7955" max="7955" width="3" customWidth="1"/>
+    <col min="7956" max="7956" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8193" max="8196" width="14.453125" customWidth="1"/>
+    <col min="8197" max="8197" width="15.453125" customWidth="1"/>
+    <col min="8198" max="8198" width="14.54296875" customWidth="1"/>
+    <col min="8199" max="8199" width="15.26953125" customWidth="1"/>
+    <col min="8200" max="8201" width="14.453125" customWidth="1"/>
+    <col min="8202" max="8202" width="13.1796875" customWidth="1"/>
+    <col min="8203" max="8205" width="14.453125" customWidth="1"/>
+    <col min="8206" max="8206" width="15.81640625" customWidth="1"/>
+    <col min="8207" max="8207" width="7.81640625" customWidth="1"/>
+    <col min="8208" max="8208" width="5.453125" customWidth="1"/>
+    <col min="8209" max="8209" width="6.453125" customWidth="1"/>
+    <col min="8210" max="8210" width="7.81640625" customWidth="1"/>
+    <col min="8211" max="8211" width="3" customWidth="1"/>
+    <col min="8212" max="8212" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8449" max="8452" width="14.453125" customWidth="1"/>
+    <col min="8453" max="8453" width="15.453125" customWidth="1"/>
+    <col min="8454" max="8454" width="14.54296875" customWidth="1"/>
+    <col min="8455" max="8455" width="15.26953125" customWidth="1"/>
+    <col min="8456" max="8457" width="14.453125" customWidth="1"/>
+    <col min="8458" max="8458" width="13.1796875" customWidth="1"/>
+    <col min="8459" max="8461" width="14.453125" customWidth="1"/>
+    <col min="8462" max="8462" width="15.81640625" customWidth="1"/>
+    <col min="8463" max="8463" width="7.81640625" customWidth="1"/>
+    <col min="8464" max="8464" width="5.453125" customWidth="1"/>
+    <col min="8465" max="8465" width="6.453125" customWidth="1"/>
+    <col min="8466" max="8466" width="7.81640625" customWidth="1"/>
+    <col min="8467" max="8467" width="3" customWidth="1"/>
+    <col min="8468" max="8468" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8705" max="8708" width="14.453125" customWidth="1"/>
+    <col min="8709" max="8709" width="15.453125" customWidth="1"/>
+    <col min="8710" max="8710" width="14.54296875" customWidth="1"/>
+    <col min="8711" max="8711" width="15.26953125" customWidth="1"/>
+    <col min="8712" max="8713" width="14.453125" customWidth="1"/>
+    <col min="8714" max="8714" width="13.1796875" customWidth="1"/>
+    <col min="8715" max="8717" width="14.453125" customWidth="1"/>
+    <col min="8718" max="8718" width="15.81640625" customWidth="1"/>
+    <col min="8719" max="8719" width="7.81640625" customWidth="1"/>
+    <col min="8720" max="8720" width="5.453125" customWidth="1"/>
+    <col min="8721" max="8721" width="6.453125" customWidth="1"/>
+    <col min="8722" max="8722" width="7.81640625" customWidth="1"/>
+    <col min="8723" max="8723" width="3" customWidth="1"/>
+    <col min="8724" max="8724" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8961" max="8964" width="14.453125" customWidth="1"/>
+    <col min="8965" max="8965" width="15.453125" customWidth="1"/>
+    <col min="8966" max="8966" width="14.54296875" customWidth="1"/>
+    <col min="8967" max="8967" width="15.26953125" customWidth="1"/>
+    <col min="8968" max="8969" width="14.453125" customWidth="1"/>
+    <col min="8970" max="8970" width="13.1796875" customWidth="1"/>
+    <col min="8971" max="8973" width="14.453125" customWidth="1"/>
+    <col min="8974" max="8974" width="15.81640625" customWidth="1"/>
+    <col min="8975" max="8975" width="7.81640625" customWidth="1"/>
+    <col min="8976" max="8976" width="5.453125" customWidth="1"/>
+    <col min="8977" max="8977" width="6.453125" customWidth="1"/>
+    <col min="8978" max="8978" width="7.81640625" customWidth="1"/>
+    <col min="8979" max="8979" width="3" customWidth="1"/>
+    <col min="8980" max="8980" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9217" max="9220" width="14.453125" customWidth="1"/>
+    <col min="9221" max="9221" width="15.453125" customWidth="1"/>
+    <col min="9222" max="9222" width="14.54296875" customWidth="1"/>
+    <col min="9223" max="9223" width="15.26953125" customWidth="1"/>
+    <col min="9224" max="9225" width="14.453125" customWidth="1"/>
+    <col min="9226" max="9226" width="13.1796875" customWidth="1"/>
+    <col min="9227" max="9229" width="14.453125" customWidth="1"/>
+    <col min="9230" max="9230" width="15.81640625" customWidth="1"/>
+    <col min="9231" max="9231" width="7.81640625" customWidth="1"/>
+    <col min="9232" max="9232" width="5.453125" customWidth="1"/>
+    <col min="9233" max="9233" width="6.453125" customWidth="1"/>
+    <col min="9234" max="9234" width="7.81640625" customWidth="1"/>
+    <col min="9235" max="9235" width="3" customWidth="1"/>
+    <col min="9236" max="9236" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9473" max="9476" width="14.453125" customWidth="1"/>
+    <col min="9477" max="9477" width="15.453125" customWidth="1"/>
+    <col min="9478" max="9478" width="14.54296875" customWidth="1"/>
+    <col min="9479" max="9479" width="15.26953125" customWidth="1"/>
+    <col min="9480" max="9481" width="14.453125" customWidth="1"/>
+    <col min="9482" max="9482" width="13.1796875" customWidth="1"/>
+    <col min="9483" max="9485" width="14.453125" customWidth="1"/>
+    <col min="9486" max="9486" width="15.81640625" customWidth="1"/>
+    <col min="9487" max="9487" width="7.81640625" customWidth="1"/>
+    <col min="9488" max="9488" width="5.453125" customWidth="1"/>
+    <col min="9489" max="9489" width="6.453125" customWidth="1"/>
+    <col min="9490" max="9490" width="7.81640625" customWidth="1"/>
+    <col min="9491" max="9491" width="3" customWidth="1"/>
+    <col min="9492" max="9492" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9729" max="9732" width="14.453125" customWidth="1"/>
+    <col min="9733" max="9733" width="15.453125" customWidth="1"/>
+    <col min="9734" max="9734" width="14.54296875" customWidth="1"/>
+    <col min="9735" max="9735" width="15.26953125" customWidth="1"/>
+    <col min="9736" max="9737" width="14.453125" customWidth="1"/>
+    <col min="9738" max="9738" width="13.1796875" customWidth="1"/>
+    <col min="9739" max="9741" width="14.453125" customWidth="1"/>
+    <col min="9742" max="9742" width="15.81640625" customWidth="1"/>
+    <col min="9743" max="9743" width="7.81640625" customWidth="1"/>
+    <col min="9744" max="9744" width="5.453125" customWidth="1"/>
+    <col min="9745" max="9745" width="6.453125" customWidth="1"/>
+    <col min="9746" max="9746" width="7.81640625" customWidth="1"/>
+    <col min="9747" max="9747" width="3" customWidth="1"/>
+    <col min="9748" max="9748" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9985" max="9988" width="14.453125" customWidth="1"/>
+    <col min="9989" max="9989" width="15.453125" customWidth="1"/>
+    <col min="9990" max="9990" width="14.54296875" customWidth="1"/>
+    <col min="9991" max="9991" width="15.26953125" customWidth="1"/>
+    <col min="9992" max="9993" width="14.453125" customWidth="1"/>
+    <col min="9994" max="9994" width="13.1796875" customWidth="1"/>
+    <col min="9995" max="9997" width="14.453125" customWidth="1"/>
+    <col min="9998" max="9998" width="15.81640625" customWidth="1"/>
+    <col min="9999" max="9999" width="7.81640625" customWidth="1"/>
+    <col min="10000" max="10000" width="5.453125" customWidth="1"/>
+    <col min="10001" max="10001" width="6.453125" customWidth="1"/>
+    <col min="10002" max="10002" width="7.81640625" customWidth="1"/>
+    <col min="10003" max="10003" width="3" customWidth="1"/>
+    <col min="10004" max="10004" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10241" max="10244" width="14.453125" customWidth="1"/>
+    <col min="10245" max="10245" width="15.453125" customWidth="1"/>
+    <col min="10246" max="10246" width="14.54296875" customWidth="1"/>
+    <col min="10247" max="10247" width="15.26953125" customWidth="1"/>
+    <col min="10248" max="10249" width="14.453125" customWidth="1"/>
+    <col min="10250" max="10250" width="13.1796875" customWidth="1"/>
+    <col min="10251" max="10253" width="14.453125" customWidth="1"/>
+    <col min="10254" max="10254" width="15.81640625" customWidth="1"/>
+    <col min="10255" max="10255" width="7.81640625" customWidth="1"/>
+    <col min="10256" max="10256" width="5.453125" customWidth="1"/>
+    <col min="10257" max="10257" width="6.453125" customWidth="1"/>
+    <col min="10258" max="10258" width="7.81640625" customWidth="1"/>
+    <col min="10259" max="10259" width="3" customWidth="1"/>
+    <col min="10260" max="10260" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10497" max="10500" width="14.453125" customWidth="1"/>
+    <col min="10501" max="10501" width="15.453125" customWidth="1"/>
+    <col min="10502" max="10502" width="14.54296875" customWidth="1"/>
+    <col min="10503" max="10503" width="15.26953125" customWidth="1"/>
+    <col min="10504" max="10505" width="14.453125" customWidth="1"/>
+    <col min="10506" max="10506" width="13.1796875" customWidth="1"/>
+    <col min="10507" max="10509" width="14.453125" customWidth="1"/>
+    <col min="10510" max="10510" width="15.81640625" customWidth="1"/>
+    <col min="10511" max="10511" width="7.81640625" customWidth="1"/>
+    <col min="10512" max="10512" width="5.453125" customWidth="1"/>
+    <col min="10513" max="10513" width="6.453125" customWidth="1"/>
+    <col min="10514" max="10514" width="7.81640625" customWidth="1"/>
+    <col min="10515" max="10515" width="3" customWidth="1"/>
+    <col min="10516" max="10516" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10753" max="10756" width="14.453125" customWidth="1"/>
+    <col min="10757" max="10757" width="15.453125" customWidth="1"/>
+    <col min="10758" max="10758" width="14.54296875" customWidth="1"/>
+    <col min="10759" max="10759" width="15.26953125" customWidth="1"/>
+    <col min="10760" max="10761" width="14.453125" customWidth="1"/>
+    <col min="10762" max="10762" width="13.1796875" customWidth="1"/>
+    <col min="10763" max="10765" width="14.453125" customWidth="1"/>
+    <col min="10766" max="10766" width="15.81640625" customWidth="1"/>
+    <col min="10767" max="10767" width="7.81640625" customWidth="1"/>
+    <col min="10768" max="10768" width="5.453125" customWidth="1"/>
+    <col min="10769" max="10769" width="6.453125" customWidth="1"/>
+    <col min="10770" max="10770" width="7.81640625" customWidth="1"/>
+    <col min="10771" max="10771" width="3" customWidth="1"/>
+    <col min="10772" max="10772" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11009" max="11012" width="14.453125" customWidth="1"/>
+    <col min="11013" max="11013" width="15.453125" customWidth="1"/>
+    <col min="11014" max="11014" width="14.54296875" customWidth="1"/>
+    <col min="11015" max="11015" width="15.26953125" customWidth="1"/>
+    <col min="11016" max="11017" width="14.453125" customWidth="1"/>
+    <col min="11018" max="11018" width="13.1796875" customWidth="1"/>
+    <col min="11019" max="11021" width="14.453125" customWidth="1"/>
+    <col min="11022" max="11022" width="15.81640625" customWidth="1"/>
+    <col min="11023" max="11023" width="7.81640625" customWidth="1"/>
+    <col min="11024" max="11024" width="5.453125" customWidth="1"/>
+    <col min="11025" max="11025" width="6.453125" customWidth="1"/>
+    <col min="11026" max="11026" width="7.81640625" customWidth="1"/>
+    <col min="11027" max="11027" width="3" customWidth="1"/>
+    <col min="11028" max="11028" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11265" max="11268" width="14.453125" customWidth="1"/>
+    <col min="11269" max="11269" width="15.453125" customWidth="1"/>
+    <col min="11270" max="11270" width="14.54296875" customWidth="1"/>
+    <col min="11271" max="11271" width="15.26953125" customWidth="1"/>
+    <col min="11272" max="11273" width="14.453125" customWidth="1"/>
+    <col min="11274" max="11274" width="13.1796875" customWidth="1"/>
+    <col min="11275" max="11277" width="14.453125" customWidth="1"/>
+    <col min="11278" max="11278" width="15.81640625" customWidth="1"/>
+    <col min="11279" max="11279" width="7.81640625" customWidth="1"/>
+    <col min="11280" max="11280" width="5.453125" customWidth="1"/>
+    <col min="11281" max="11281" width="6.453125" customWidth="1"/>
+    <col min="11282" max="11282" width="7.81640625" customWidth="1"/>
+    <col min="11283" max="11283" width="3" customWidth="1"/>
+    <col min="11284" max="11284" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11521" max="11524" width="14.453125" customWidth="1"/>
+    <col min="11525" max="11525" width="15.453125" customWidth="1"/>
+    <col min="11526" max="11526" width="14.54296875" customWidth="1"/>
+    <col min="11527" max="11527" width="15.26953125" customWidth="1"/>
+    <col min="11528" max="11529" width="14.453125" customWidth="1"/>
+    <col min="11530" max="11530" width="13.1796875" customWidth="1"/>
+    <col min="11531" max="11533" width="14.453125" customWidth="1"/>
+    <col min="11534" max="11534" width="15.81640625" customWidth="1"/>
+    <col min="11535" max="11535" width="7.81640625" customWidth="1"/>
+    <col min="11536" max="11536" width="5.453125" customWidth="1"/>
+    <col min="11537" max="11537" width="6.453125" customWidth="1"/>
+    <col min="11538" max="11538" width="7.81640625" customWidth="1"/>
+    <col min="11539" max="11539" width="3" customWidth="1"/>
+    <col min="11540" max="11540" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11777" max="11780" width="14.453125" customWidth="1"/>
+    <col min="11781" max="11781" width="15.453125" customWidth="1"/>
+    <col min="11782" max="11782" width="14.54296875" customWidth="1"/>
+    <col min="11783" max="11783" width="15.26953125" customWidth="1"/>
+    <col min="11784" max="11785" width="14.453125" customWidth="1"/>
+    <col min="11786" max="11786" width="13.1796875" customWidth="1"/>
+    <col min="11787" max="11789" width="14.453125" customWidth="1"/>
+    <col min="11790" max="11790" width="15.81640625" customWidth="1"/>
+    <col min="11791" max="11791" width="7.81640625" customWidth="1"/>
+    <col min="11792" max="11792" width="5.453125" customWidth="1"/>
+    <col min="11793" max="11793" width="6.453125" customWidth="1"/>
+    <col min="11794" max="11794" width="7.81640625" customWidth="1"/>
+    <col min="11795" max="11795" width="3" customWidth="1"/>
+    <col min="11796" max="11796" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12033" max="12036" width="14.453125" customWidth="1"/>
+    <col min="12037" max="12037" width="15.453125" customWidth="1"/>
+    <col min="12038" max="12038" width="14.54296875" customWidth="1"/>
+    <col min="12039" max="12039" width="15.26953125" customWidth="1"/>
+    <col min="12040" max="12041" width="14.453125" customWidth="1"/>
+    <col min="12042" max="12042" width="13.1796875" customWidth="1"/>
+    <col min="12043" max="12045" width="14.453125" customWidth="1"/>
+    <col min="12046" max="12046" width="15.81640625" customWidth="1"/>
+    <col min="12047" max="12047" width="7.81640625" customWidth="1"/>
+    <col min="12048" max="12048" width="5.453125" customWidth="1"/>
+    <col min="12049" max="12049" width="6.453125" customWidth="1"/>
+    <col min="12050" max="12050" width="7.81640625" customWidth="1"/>
+    <col min="12051" max="12051" width="3" customWidth="1"/>
+    <col min="12052" max="12052" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12289" max="12292" width="14.453125" customWidth="1"/>
+    <col min="12293" max="12293" width="15.453125" customWidth="1"/>
+    <col min="12294" max="12294" width="14.54296875" customWidth="1"/>
+    <col min="12295" max="12295" width="15.26953125" customWidth="1"/>
+    <col min="12296" max="12297" width="14.453125" customWidth="1"/>
+    <col min="12298" max="12298" width="13.1796875" customWidth="1"/>
+    <col min="12299" max="12301" width="14.453125" customWidth="1"/>
+    <col min="12302" max="12302" width="15.81640625" customWidth="1"/>
+    <col min="12303" max="12303" width="7.81640625" customWidth="1"/>
+    <col min="12304" max="12304" width="5.453125" customWidth="1"/>
+    <col min="12305" max="12305" width="6.453125" customWidth="1"/>
+    <col min="12306" max="12306" width="7.81640625" customWidth="1"/>
+    <col min="12307" max="12307" width="3" customWidth="1"/>
+    <col min="12308" max="12308" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12545" max="12548" width="14.453125" customWidth="1"/>
+    <col min="12549" max="12549" width="15.453125" customWidth="1"/>
+    <col min="12550" max="12550" width="14.54296875" customWidth="1"/>
+    <col min="12551" max="12551" width="15.26953125" customWidth="1"/>
+    <col min="12552" max="12553" width="14.453125" customWidth="1"/>
+    <col min="12554" max="12554" width="13.1796875" customWidth="1"/>
+    <col min="12555" max="12557" width="14.453125" customWidth="1"/>
+    <col min="12558" max="12558" width="15.81640625" customWidth="1"/>
+    <col min="12559" max="12559" width="7.81640625" customWidth="1"/>
+    <col min="12560" max="12560" width="5.453125" customWidth="1"/>
+    <col min="12561" max="12561" width="6.453125" customWidth="1"/>
+    <col min="12562" max="12562" width="7.81640625" customWidth="1"/>
+    <col min="12563" max="12563" width="3" customWidth="1"/>
+    <col min="12564" max="12564" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12801" max="12804" width="14.453125" customWidth="1"/>
+    <col min="12805" max="12805" width="15.453125" customWidth="1"/>
+    <col min="12806" max="12806" width="14.54296875" customWidth="1"/>
+    <col min="12807" max="12807" width="15.26953125" customWidth="1"/>
+    <col min="12808" max="12809" width="14.453125" customWidth="1"/>
+    <col min="12810" max="12810" width="13.1796875" customWidth="1"/>
+    <col min="12811" max="12813" width="14.453125" customWidth="1"/>
+    <col min="12814" max="12814" width="15.81640625" customWidth="1"/>
+    <col min="12815" max="12815" width="7.81640625" customWidth="1"/>
+    <col min="12816" max="12816" width="5.453125" customWidth="1"/>
+    <col min="12817" max="12817" width="6.453125" customWidth="1"/>
+    <col min="12818" max="12818" width="7.81640625" customWidth="1"/>
+    <col min="12819" max="12819" width="3" customWidth="1"/>
+    <col min="12820" max="12820" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13057" max="13060" width="14.453125" customWidth="1"/>
+    <col min="13061" max="13061" width="15.453125" customWidth="1"/>
+    <col min="13062" max="13062" width="14.54296875" customWidth="1"/>
+    <col min="13063" max="13063" width="15.26953125" customWidth="1"/>
+    <col min="13064" max="13065" width="14.453125" customWidth="1"/>
+    <col min="13066" max="13066" width="13.1796875" customWidth="1"/>
+    <col min="13067" max="13069" width="14.453125" customWidth="1"/>
+    <col min="13070" max="13070" width="15.81640625" customWidth="1"/>
+    <col min="13071" max="13071" width="7.81640625" customWidth="1"/>
+    <col min="13072" max="13072" width="5.453125" customWidth="1"/>
+    <col min="13073" max="13073" width="6.453125" customWidth="1"/>
+    <col min="13074" max="13074" width="7.81640625" customWidth="1"/>
+    <col min="13075" max="13075" width="3" customWidth="1"/>
+    <col min="13076" max="13076" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13313" max="13316" width="14.453125" customWidth="1"/>
+    <col min="13317" max="13317" width="15.453125" customWidth="1"/>
+    <col min="13318" max="13318" width="14.54296875" customWidth="1"/>
+    <col min="13319" max="13319" width="15.26953125" customWidth="1"/>
+    <col min="13320" max="13321" width="14.453125" customWidth="1"/>
+    <col min="13322" max="13322" width="13.1796875" customWidth="1"/>
+    <col min="13323" max="13325" width="14.453125" customWidth="1"/>
+    <col min="13326" max="13326" width="15.81640625" customWidth="1"/>
+    <col min="13327" max="13327" width="7.81640625" customWidth="1"/>
+    <col min="13328" max="13328" width="5.453125" customWidth="1"/>
+    <col min="13329" max="13329" width="6.453125" customWidth="1"/>
+    <col min="13330" max="13330" width="7.81640625" customWidth="1"/>
+    <col min="13331" max="13331" width="3" customWidth="1"/>
+    <col min="13332" max="13332" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13569" max="13572" width="14.453125" customWidth="1"/>
+    <col min="13573" max="13573" width="15.453125" customWidth="1"/>
+    <col min="13574" max="13574" width="14.54296875" customWidth="1"/>
+    <col min="13575" max="13575" width="15.26953125" customWidth="1"/>
+    <col min="13576" max="13577" width="14.453125" customWidth="1"/>
+    <col min="13578" max="13578" width="13.1796875" customWidth="1"/>
+    <col min="13579" max="13581" width="14.453125" customWidth="1"/>
+    <col min="13582" max="13582" width="15.81640625" customWidth="1"/>
+    <col min="13583" max="13583" width="7.81640625" customWidth="1"/>
+    <col min="13584" max="13584" width="5.453125" customWidth="1"/>
+    <col min="13585" max="13585" width="6.453125" customWidth="1"/>
+    <col min="13586" max="13586" width="7.81640625" customWidth="1"/>
+    <col min="13587" max="13587" width="3" customWidth="1"/>
+    <col min="13588" max="13588" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13825" max="13828" width="14.453125" customWidth="1"/>
+    <col min="13829" max="13829" width="15.453125" customWidth="1"/>
+    <col min="13830" max="13830" width="14.54296875" customWidth="1"/>
+    <col min="13831" max="13831" width="15.26953125" customWidth="1"/>
+    <col min="13832" max="13833" width="14.453125" customWidth="1"/>
+    <col min="13834" max="13834" width="13.1796875" customWidth="1"/>
+    <col min="13835" max="13837" width="14.453125" customWidth="1"/>
+    <col min="13838" max="13838" width="15.81640625" customWidth="1"/>
+    <col min="13839" max="13839" width="7.81640625" customWidth="1"/>
+    <col min="13840" max="13840" width="5.453125" customWidth="1"/>
+    <col min="13841" max="13841" width="6.453125" customWidth="1"/>
+    <col min="13842" max="13842" width="7.81640625" customWidth="1"/>
+    <col min="13843" max="13843" width="3" customWidth="1"/>
+    <col min="13844" max="13844" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14081" max="14084" width="14.453125" customWidth="1"/>
+    <col min="14085" max="14085" width="15.453125" customWidth="1"/>
+    <col min="14086" max="14086" width="14.54296875" customWidth="1"/>
+    <col min="14087" max="14087" width="15.26953125" customWidth="1"/>
+    <col min="14088" max="14089" width="14.453125" customWidth="1"/>
+    <col min="14090" max="14090" width="13.1796875" customWidth="1"/>
+    <col min="14091" max="14093" width="14.453125" customWidth="1"/>
+    <col min="14094" max="14094" width="15.81640625" customWidth="1"/>
+    <col min="14095" max="14095" width="7.81640625" customWidth="1"/>
+    <col min="14096" max="14096" width="5.453125" customWidth="1"/>
+    <col min="14097" max="14097" width="6.453125" customWidth="1"/>
+    <col min="14098" max="14098" width="7.81640625" customWidth="1"/>
+    <col min="14099" max="14099" width="3" customWidth="1"/>
+    <col min="14100" max="14100" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14337" max="14340" width="14.453125" customWidth="1"/>
+    <col min="14341" max="14341" width="15.453125" customWidth="1"/>
+    <col min="14342" max="14342" width="14.54296875" customWidth="1"/>
+    <col min="14343" max="14343" width="15.26953125" customWidth="1"/>
+    <col min="14344" max="14345" width="14.453125" customWidth="1"/>
+    <col min="14346" max="14346" width="13.1796875" customWidth="1"/>
+    <col min="14347" max="14349" width="14.453125" customWidth="1"/>
+    <col min="14350" max="14350" width="15.81640625" customWidth="1"/>
+    <col min="14351" max="14351" width="7.81640625" customWidth="1"/>
+    <col min="14352" max="14352" width="5.453125" customWidth="1"/>
+    <col min="14353" max="14353" width="6.453125" customWidth="1"/>
+    <col min="14354" max="14354" width="7.81640625" customWidth="1"/>
+    <col min="14355" max="14355" width="3" customWidth="1"/>
+    <col min="14356" max="14356" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14593" max="14596" width="14.453125" customWidth="1"/>
+    <col min="14597" max="14597" width="15.453125" customWidth="1"/>
+    <col min="14598" max="14598" width="14.54296875" customWidth="1"/>
+    <col min="14599" max="14599" width="15.26953125" customWidth="1"/>
+    <col min="14600" max="14601" width="14.453125" customWidth="1"/>
+    <col min="14602" max="14602" width="13.1796875" customWidth="1"/>
+    <col min="14603" max="14605" width="14.453125" customWidth="1"/>
+    <col min="14606" max="14606" width="15.81640625" customWidth="1"/>
+    <col min="14607" max="14607" width="7.81640625" customWidth="1"/>
+    <col min="14608" max="14608" width="5.453125" customWidth="1"/>
+    <col min="14609" max="14609" width="6.453125" customWidth="1"/>
+    <col min="14610" max="14610" width="7.81640625" customWidth="1"/>
+    <col min="14611" max="14611" width="3" customWidth="1"/>
+    <col min="14612" max="14612" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14849" max="14852" width="14.453125" customWidth="1"/>
+    <col min="14853" max="14853" width="15.453125" customWidth="1"/>
+    <col min="14854" max="14854" width="14.54296875" customWidth="1"/>
+    <col min="14855" max="14855" width="15.26953125" customWidth="1"/>
+    <col min="14856" max="14857" width="14.453125" customWidth="1"/>
+    <col min="14858" max="14858" width="13.1796875" customWidth="1"/>
+    <col min="14859" max="14861" width="14.453125" customWidth="1"/>
+    <col min="14862" max="14862" width="15.81640625" customWidth="1"/>
+    <col min="14863" max="14863" width="7.81640625" customWidth="1"/>
+    <col min="14864" max="14864" width="5.453125" customWidth="1"/>
+    <col min="14865" max="14865" width="6.453125" customWidth="1"/>
+    <col min="14866" max="14866" width="7.81640625" customWidth="1"/>
+    <col min="14867" max="14867" width="3" customWidth="1"/>
+    <col min="14868" max="14868" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15105" max="15108" width="14.453125" customWidth="1"/>
+    <col min="15109" max="15109" width="15.453125" customWidth="1"/>
+    <col min="15110" max="15110" width="14.54296875" customWidth="1"/>
+    <col min="15111" max="15111" width="15.26953125" customWidth="1"/>
+    <col min="15112" max="15113" width="14.453125" customWidth="1"/>
+    <col min="15114" max="15114" width="13.1796875" customWidth="1"/>
+    <col min="15115" max="15117" width="14.453125" customWidth="1"/>
+    <col min="15118" max="15118" width="15.81640625" customWidth="1"/>
+    <col min="15119" max="15119" width="7.81640625" customWidth="1"/>
+    <col min="15120" max="15120" width="5.453125" customWidth="1"/>
+    <col min="15121" max="15121" width="6.453125" customWidth="1"/>
+    <col min="15122" max="15122" width="7.81640625" customWidth="1"/>
+    <col min="15123" max="15123" width="3" customWidth="1"/>
+    <col min="15124" max="15124" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15361" max="15364" width="14.453125" customWidth="1"/>
+    <col min="15365" max="15365" width="15.453125" customWidth="1"/>
+    <col min="15366" max="15366" width="14.54296875" customWidth="1"/>
+    <col min="15367" max="15367" width="15.26953125" customWidth="1"/>
+    <col min="15368" max="15369" width="14.453125" customWidth="1"/>
+    <col min="15370" max="15370" width="13.1796875" customWidth="1"/>
+    <col min="15371" max="15373" width="14.453125" customWidth="1"/>
+    <col min="15374" max="15374" width="15.81640625" customWidth="1"/>
+    <col min="15375" max="15375" width="7.81640625" customWidth="1"/>
+    <col min="15376" max="15376" width="5.453125" customWidth="1"/>
+    <col min="15377" max="15377" width="6.453125" customWidth="1"/>
+    <col min="15378" max="15378" width="7.81640625" customWidth="1"/>
+    <col min="15379" max="15379" width="3" customWidth="1"/>
+    <col min="15380" max="15380" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15617" max="15620" width="14.453125" customWidth="1"/>
+    <col min="15621" max="15621" width="15.453125" customWidth="1"/>
+    <col min="15622" max="15622" width="14.54296875" customWidth="1"/>
+    <col min="15623" max="15623" width="15.26953125" customWidth="1"/>
+    <col min="15624" max="15625" width="14.453125" customWidth="1"/>
+    <col min="15626" max="15626" width="13.1796875" customWidth="1"/>
+    <col min="15627" max="15629" width="14.453125" customWidth="1"/>
+    <col min="15630" max="15630" width="15.81640625" customWidth="1"/>
+    <col min="15631" max="15631" width="7.81640625" customWidth="1"/>
+    <col min="15632" max="15632" width="5.453125" customWidth="1"/>
+    <col min="15633" max="15633" width="6.453125" customWidth="1"/>
+    <col min="15634" max="15634" width="7.81640625" customWidth="1"/>
+    <col min="15635" max="15635" width="3" customWidth="1"/>
+    <col min="15636" max="15636" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15873" max="15876" width="14.453125" customWidth="1"/>
+    <col min="15877" max="15877" width="15.453125" customWidth="1"/>
+    <col min="15878" max="15878" width="14.54296875" customWidth="1"/>
+    <col min="15879" max="15879" width="15.26953125" customWidth="1"/>
+    <col min="15880" max="15881" width="14.453125" customWidth="1"/>
+    <col min="15882" max="15882" width="13.1796875" customWidth="1"/>
+    <col min="15883" max="15885" width="14.453125" customWidth="1"/>
+    <col min="15886" max="15886" width="15.81640625" customWidth="1"/>
+    <col min="15887" max="15887" width="7.81640625" customWidth="1"/>
+    <col min="15888" max="15888" width="5.453125" customWidth="1"/>
+    <col min="15889" max="15889" width="6.453125" customWidth="1"/>
+    <col min="15890" max="15890" width="7.81640625" customWidth="1"/>
+    <col min="15891" max="15891" width="3" customWidth="1"/>
+    <col min="15892" max="15892" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="16129" max="16132" width="14.453125" customWidth="1"/>
+    <col min="16133" max="16133" width="15.453125" customWidth="1"/>
+    <col min="16134" max="16134" width="14.54296875" customWidth="1"/>
+    <col min="16135" max="16135" width="15.26953125" customWidth="1"/>
+    <col min="16136" max="16137" width="14.453125" customWidth="1"/>
+    <col min="16138" max="16138" width="13.1796875" customWidth="1"/>
+    <col min="16139" max="16141" width="14.453125" customWidth="1"/>
+    <col min="16142" max="16142" width="15.81640625" customWidth="1"/>
+    <col min="16143" max="16143" width="7.81640625" customWidth="1"/>
+    <col min="16144" max="16144" width="5.453125" customWidth="1"/>
+    <col min="16145" max="16145" width="6.453125" customWidth="1"/>
+    <col min="16146" max="16146" width="7.81640625" customWidth="1"/>
+    <col min="16147" max="16147" width="3" customWidth="1"/>
+    <col min="16148" max="16148" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="292" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
+      <c r="S1"/>
+    </row>
+    <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2"/>
+    </row>
+    <row r="3" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="281" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="284" t="s">
+        <v>99</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="I3" s="129" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="283" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="288" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="26"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="285" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" s="286"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="278" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="279"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="29"/>
+    </row>
+    <row r="4" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="281"/>
+      <c r="E4" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" s="284"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="283"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="288"/>
+      <c r="O4" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" s="274" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" s="275" t="s">
+        <v>71</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" s="270" t="s">
+        <v>70</v>
+      </c>
+      <c r="U4" s="271" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="37"/>
+      <c r="E5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="284" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="281" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="54"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="38"/>
+      <c r="O5" s="39">
+        <v>31</v>
+      </c>
+      <c r="P5" s="40">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="41">
+        <v>19</v>
+      </c>
+      <c r="R5" s="42">
+        <v>11</v>
+      </c>
+      <c r="S5" s="40">
+        <v>31</v>
+      </c>
+      <c r="T5" s="41">
+        <v>19</v>
+      </c>
+      <c r="U5" s="42">
+        <v>11</v>
+      </c>
+      <c r="V5" s="43">
+        <f t="shared" ref="V5:V17" si="0">-SUM(S5-P5)*-1</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="44"/>
+    </row>
+    <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F6" s="284"/>
+      <c r="G6" s="277"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="129" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="281"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="8"/>
+      <c r="N6" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" s="47">
+        <v>49</v>
+      </c>
+      <c r="P6" s="48">
+        <f t="shared" ref="P6:P17" si="1">SUM(Q6:R6)</f>
+        <v>12</v>
+      </c>
+      <c r="Q6" s="49">
+        <v>7</v>
+      </c>
+      <c r="R6" s="50">
+        <v>5</v>
+      </c>
+      <c r="S6" s="48">
+        <f t="shared" ref="S6:S17" si="2">SUM(T6:U6)</f>
+        <v>12</v>
+      </c>
+      <c r="T6" s="49">
+        <v>7</v>
+      </c>
+      <c r="U6" s="50">
+        <v>5</v>
+      </c>
+      <c r="V6" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="52"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="53"/>
+      <c r="C7" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="284" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" s="277"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="288" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" s="54"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="47">
+        <v>22</v>
+      </c>
+      <c r="P7" s="48">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Q7" s="49">
+        <v>11</v>
+      </c>
+      <c r="R7" s="50">
+        <v>4</v>
+      </c>
+      <c r="S7" s="48">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="T7" s="49">
+        <v>11</v>
+      </c>
+      <c r="U7" s="50">
+        <v>4</v>
+      </c>
+      <c r="V7" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W7" s="52"/>
+    </row>
+    <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="45"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F8" s="284"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="288"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="56">
+        <v>46314</v>
+      </c>
+      <c r="O8" s="47">
+        <v>24</v>
+      </c>
+      <c r="P8" s="48">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Q8" s="49">
+        <v>3</v>
+      </c>
+      <c r="R8" s="50">
+        <v>3</v>
+      </c>
+      <c r="S8" s="48">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="T8" s="49">
+        <v>2</v>
+      </c>
+      <c r="U8" s="50">
+        <v>2</v>
+      </c>
+      <c r="V8" s="51">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="W8" s="52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="45"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="58"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="287" t="s">
+        <v>258</v>
+      </c>
+      <c r="G9" s="62"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9" s="47"/>
+      <c r="P9" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="49"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W9" s="52"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="45"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="129" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="61"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="287"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="49"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="52"/>
+    </row>
+    <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="64"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="D11" s="61"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="G11" s="64"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="66"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="68"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="70"/>
+    </row>
+    <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="71"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="G12" s="64"/>
+      <c r="H12" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="L12" s="73" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" s="74"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="68"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W12" s="70"/>
+    </row>
+    <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="61"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="276" t="s">
+        <v>149</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="288" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="127" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="128"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="60"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="68"/>
+      <c r="U13" s="69"/>
+      <c r="V13" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="70"/>
+    </row>
+    <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="8"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="276" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="30"/>
+      <c r="I14" s="288"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="60"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="68"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="70"/>
+    </row>
+    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="129"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="273"/>
+      <c r="F15" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="126" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="60"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="107"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="68"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="70"/>
+    </row>
+    <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="287" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="287" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="288" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="61"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="273" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="107"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="68"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="68"/>
+      <c r="U16" s="69"/>
+      <c r="V16" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="70"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="287"/>
+      <c r="B17" s="287"/>
+      <c r="C17" s="288"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="80"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="82">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="83"/>
+    </row>
+    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="77"/>
+      <c r="M18" s="77"/>
+      <c r="R18" s="84"/>
+      <c r="S18"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="273"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="77"/>
+      <c r="R19" s="84"/>
+      <c r="S19"/>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="85" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="273"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="158"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="R20" s="84"/>
+      <c r="S20"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="128" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="D21" s="61"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="R21" s="84"/>
+      <c r="S21"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="6"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="273"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="R22" s="84"/>
+      <c r="S22"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="R23" s="84"/>
+      <c r="S23"/>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="R24" s="84"/>
+      <c r="S24"/>
+    </row>
+    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="30"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="R25" s="84"/>
+      <c r="S25"/>
+    </row>
+    <row r="26" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="273"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="R26" s="84"/>
+      <c r="S26"/>
+    </row>
+    <row r="27" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="R27" s="84"/>
+      <c r="S27"/>
+    </row>
+    <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="293" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="R28" s="84"/>
+      <c r="S28"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="30"/>
+      <c r="I29" s="273"/>
+      <c r="J29" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K29" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="92" t="s">
+        <v>25</v>
+      </c>
+      <c r="R29" s="84"/>
+      <c r="S29"/>
+    </row>
+    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="93" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="94"/>
+      <c r="C30" s="93" t="s">
+        <v>249</v>
+      </c>
+      <c r="D30" s="93" t="s">
+        <v>251</v>
+      </c>
+      <c r="E30" s="282" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="8"/>
+      <c r="G30" s="272" t="s">
+        <v>269</v>
+      </c>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="224" t="s">
+        <v>42</v>
+      </c>
+      <c r="K30" s="124" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="218" t="s">
+        <v>119</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="R30" s="84"/>
+      <c r="S30"/>
+    </row>
+    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C31" s="93" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" s="93" t="s">
+        <v>252</v>
+      </c>
+      <c r="E31" s="282"/>
+      <c r="F31" s="8"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="159"/>
+      <c r="K31" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="L31" s="218" t="s">
+        <v>122</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" s="84"/>
+      <c r="S31"/>
+    </row>
+    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="B32" s="94"/>
+      <c r="C32" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="93" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="282" t="s">
+        <v>259</v>
+      </c>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="159"/>
+      <c r="K32" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="L32" s="218" t="s">
+        <v>243</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="R32" s="84"/>
+      <c r="S32"/>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="8"/>
+      <c r="C33" s="93" t="s">
+        <v>267</v>
+      </c>
+      <c r="D33" s="93" t="s">
+        <v>253</v>
+      </c>
+      <c r="E33" s="282"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="110" t="s">
+        <v>150</v>
+      </c>
+      <c r="L33" s="218" t="s">
+        <v>38</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="R33" s="84"/>
+      <c r="S33"/>
+    </row>
+    <row r="34" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="94"/>
+      <c r="B34" s="95"/>
+      <c r="D34" s="93" t="s">
+        <v>254</v>
+      </c>
+      <c r="E34" s="282" t="s">
+        <v>260</v>
+      </c>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="K34" s="110" t="s">
+        <v>16</v>
+      </c>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="R34" s="84"/>
+      <c r="S34"/>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="94"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="93" t="s">
+        <v>255</v>
+      </c>
+      <c r="E35" s="282"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="124" t="s">
+        <v>120</v>
+      </c>
+      <c r="L35" s="8"/>
+      <c r="M35" s="13"/>
+      <c r="R35" s="84"/>
+      <c r="S35"/>
+    </row>
+    <row r="36" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="94"/>
+      <c r="B36" s="94"/>
+      <c r="D36" s="93" t="s">
+        <v>256</v>
+      </c>
+      <c r="E36" s="282" t="s">
+        <v>261</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="97"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="224" t="s">
+        <v>203</v>
+      </c>
+      <c r="L36" s="8"/>
+      <c r="M36" s="94"/>
+      <c r="R36" s="84"/>
+      <c r="S36"/>
+    </row>
+    <row r="37" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="E37" s="282"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="100"/>
+      <c r="K37" s="124" t="s">
+        <v>211</v>
+      </c>
+      <c r="L37" s="8"/>
+      <c r="M37" s="94"/>
+      <c r="R37" s="84"/>
+      <c r="S37"/>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="77"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="272" t="s">
+        <v>270</v>
+      </c>
+      <c r="F38" s="77"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="124" t="s">
+        <v>212</v>
+      </c>
+      <c r="L38" s="8"/>
+      <c r="M38" s="2"/>
+      <c r="R38" s="84"/>
+      <c r="S38"/>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="74"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="272" t="s">
+        <v>271</v>
+      </c>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="2"/>
+      <c r="S39"/>
+    </row>
+    <row r="40" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="105"/>
+      <c r="S40"/>
+    </row>
+    <row r="41" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="104"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="104"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="93" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="8"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="101"/>
+      <c r="M41" s="106"/>
+      <c r="S41"/>
+    </row>
+    <row r="42" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="104"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="104"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="272" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="106"/>
+      <c r="S42"/>
+    </row>
+    <row r="43" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="104"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="272" t="s">
+        <v>268</v>
+      </c>
+      <c r="F43" s="107"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="106"/>
+      <c r="S43"/>
+    </row>
+    <row r="44" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="104"/>
+      <c r="B44" s="104"/>
+      <c r="C44" s="104"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="109"/>
+      <c r="S44"/>
+    </row>
+    <row r="45" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="104"/>
+      <c r="B45" s="104"/>
+      <c r="C45" s="104"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="110"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="111"/>
+      <c r="S45"/>
+    </row>
+    <row r="46" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="104"/>
+      <c r="B46" s="104"/>
+      <c r="C46" s="104"/>
+      <c r="D46" s="104"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="104"/>
+      <c r="J46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="111"/>
+      <c r="S46"/>
+    </row>
+    <row r="47" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="104"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="104"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="104"/>
+      <c r="H47" s="104"/>
+      <c r="I47" s="273"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="112"/>
+      <c r="S47"/>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="84"/>
+      <c r="S48"/>
+    </row>
+    <row r="49" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="77"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="113"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="104"/>
+      <c r="I49" s="273"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="84"/>
+      <c r="S49"/>
+    </row>
+    <row r="50" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="77"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="84"/>
+      <c r="S50"/>
+    </row>
+    <row r="51" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="77"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="77"/>
+      <c r="D51" s="113"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="77"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="84"/>
+      <c r="S51"/>
+    </row>
+    <row r="52" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="77"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="113"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="77"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="77"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+    </row>
+    <row r="53" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="77"/>
+      <c r="B53" s="77"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="113"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="77"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="114"/>
+      <c r="M53" s="8"/>
+    </row>
+    <row r="54" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="77"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="113"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="77"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="77"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="114"/>
+      <c r="M54" s="8"/>
+    </row>
+    <row r="55" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="77"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="113"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="77"/>
+      <c r="G55" s="77"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="104"/>
+      <c r="J55" s="77"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="114"/>
+      <c r="M55" s="8"/>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="77"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="113"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="77"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="77"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="114"/>
+      <c r="M56" s="8"/>
+    </row>
+    <row r="57" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="77"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="77"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="114"/>
+      <c r="M57" s="8"/>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="77"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="113"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="77"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="115"/>
+      <c r="L58" s="114"/>
+      <c r="M58" s="8"/>
+    </row>
+    <row r="59" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="77"/>
+      <c r="B59" s="77"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="113"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="77"/>
+      <c r="G59" s="77"/>
+      <c r="H59" s="104"/>
+      <c r="I59" s="104"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="115"/>
+      <c r="L59" s="114"/>
+      <c r="M59" s="8"/>
+    </row>
+    <row r="60" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="77"/>
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="77"/>
+      <c r="G60" s="77"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="115"/>
+      <c r="L60" s="114"/>
+      <c r="M60" s="8"/>
+    </row>
+    <row r="61" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="77"/>
+      <c r="B61" s="77"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="113"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="114"/>
+      <c r="M61" s="8"/>
+    </row>
+    <row r="62" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="77"/>
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="77"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="114"/>
+      <c r="M62" s="8"/>
+    </row>
+    <row r="63" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="77"/>
+      <c r="B63" s="77"/>
+      <c r="C63" s="77"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="104"/>
+      <c r="I63" s="104"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="77"/>
+      <c r="M63" s="8"/>
+    </row>
+    <row r="64" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="77"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="77"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="77"/>
+      <c r="H64" s="104"/>
+      <c r="I64" s="104"/>
+      <c r="J64" s="77"/>
+      <c r="K64" s="116">
+        <v>22</v>
+      </c>
+      <c r="L64" s="117">
+        <v>6</v>
+      </c>
+      <c r="M64" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="61"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
+      <c r="S65"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L66" s="119" t="s">
+        <v>94</v>
+      </c>
+      <c r="M66" s="25">
+        <v>97</v>
+      </c>
+      <c r="S66"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L67" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="M67" s="25">
+        <f>SUM(M66-(M68+M69+M70))</f>
+        <v>69</v>
+      </c>
+      <c r="S67"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L68" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" s="25">
+        <v>15</v>
+      </c>
+      <c r="S68"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L69" s="121" t="s">
+        <v>24</v>
+      </c>
+      <c r="M69" s="25">
+        <v>9</v>
+      </c>
+      <c r="S69"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L70" s="122" t="s">
+        <v>25</v>
+      </c>
+      <c r="M70" s="25">
+        <v>4</v>
+      </c>
+      <c r="S70"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L71" t="s">
+        <v>96</v>
+      </c>
+      <c r="M71" s="25">
+        <v>13</v>
+      </c>
+      <c r="S71"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="M72" s="25"/>
+      <c r="S72"/>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="E30:E31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17675,21 +23099,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="292" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
-      <c r="M1" s="284"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -17744,13 +23168,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="273" t="s">
+      <c r="D3" s="281" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="273" t="s">
+      <c r="F3" s="281" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -17759,24 +23183,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="279" t="s">
+      <c r="J3" s="287" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="280" t="s">
+      <c r="M3" s="288" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="277" t="s">
+      <c r="Q3" s="285" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="278"/>
+      <c r="R3" s="286"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="270" t="s">
+      <c r="T3" s="278" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="271"/>
+      <c r="U3" s="279"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -17788,20 +23212,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="273"/>
+      <c r="D4" s="281"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="273"/>
+      <c r="F4" s="281"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="279"/>
+      <c r="J4" s="287"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="280"/>
+      <c r="M4" s="288"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -17840,7 +23264,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="276" t="s">
+      <c r="F5" s="284" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -17848,7 +23272,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="273" t="s">
+      <c r="J5" s="281" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -17893,13 +23317,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="276"/>
+      <c r="F6" s="284"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="273"/>
+      <c r="J6" s="281"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -17948,13 +23372,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="279" t="s">
+      <c r="F7" s="287" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="275" t="s">
+      <c r="J7" s="283" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -18002,11 +23426,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="279"/>
+      <c r="F8" s="287"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="275"/>
+      <c r="J8" s="283"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -18050,7 +23474,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="276" t="s">
+      <c r="F9" s="284" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -18090,7 +23514,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="276"/>
+      <c r="F10" s="284"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -18216,7 +23640,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="280" t="s">
+      <c r="I13" s="288" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -18257,7 +23681,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="280"/>
+      <c r="I14" s="288"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -18317,13 +23741,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="279" t="s">
+      <c r="A16" s="287" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="279" t="s">
+      <c r="B16" s="287" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="281" t="s">
+      <c r="C16" s="289" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -18358,9 +23782,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="279"/>
-      <c r="B17" s="279"/>
-      <c r="C17" s="282"/>
+      <c r="A17" s="287"/>
+      <c r="B17" s="287"/>
+      <c r="C17" s="290"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -18393,7 +23817,7 @@
     <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="280" t="s">
+      <c r="C18" s="288" t="s">
         <v>82</v>
       </c>
       <c r="D18" s="61"/>
@@ -18411,7 +23835,7 @@
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="147"/>
-      <c r="C19" s="280"/>
+      <c r="C19" s="288"/>
       <c r="D19" s="125"/>
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
@@ -18570,13 +23994,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="285" t="s">
+      <c r="A28" s="293" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="285"/>
-      <c r="C28" s="285"/>
-      <c r="D28" s="285"/>
-      <c r="E28" s="285"/>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -18636,7 +24060,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="274" t="s">
+      <c r="E30" s="282" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -18670,7 +24094,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="274"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -18700,7 +24124,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="274" t="s">
+      <c r="E32" s="282" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -18730,7 +24154,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="274"/>
+      <c r="E33" s="282"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -18754,7 +24178,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="272" t="s">
+      <c r="E34" s="280" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -18779,7 +24203,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="272"/>
+      <c r="E35" s="280"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -18798,7 +24222,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="274" t="s">
+      <c r="E36" s="282" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -18818,7 +24242,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="274"/>
+      <c r="E37" s="282"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -20288,21 +25712,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="292" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
-      <c r="M1" s="284"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -20357,13 +25781,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="273" t="s">
+      <c r="D3" s="281" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="273" t="s">
+      <c r="F3" s="281" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -20372,24 +25796,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="279" t="s">
+      <c r="J3" s="287" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="280" t="s">
+      <c r="M3" s="288" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="277" t="s">
+      <c r="Q3" s="285" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="278"/>
+      <c r="R3" s="286"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="270" t="s">
+      <c r="T3" s="278" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="271"/>
+      <c r="U3" s="279"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -20401,20 +25825,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="273"/>
+      <c r="D4" s="281"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="273"/>
+      <c r="F4" s="281"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="279"/>
+      <c r="J4" s="287"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="280"/>
+      <c r="M4" s="288"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -20453,7 +25877,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="276" t="s">
+      <c r="F5" s="284" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -20461,7 +25885,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="273" t="s">
+      <c r="J5" s="281" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -20506,13 +25930,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="276"/>
+      <c r="F6" s="284"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="273"/>
+      <c r="J6" s="281"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -20556,13 +25980,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="279" t="s">
+      <c r="F7" s="287" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="275" t="s">
+      <c r="J7" s="283" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -20610,11 +26034,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="279"/>
+      <c r="F8" s="287"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="275"/>
+      <c r="J8" s="283"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -20658,7 +26082,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="276" t="s">
+      <c r="F9" s="284" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -20698,7 +26122,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="276"/>
+      <c r="F10" s="284"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -20824,7 +26248,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="280" t="s">
+      <c r="I13" s="288" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -20865,7 +26289,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="280"/>
+      <c r="I14" s="288"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -20900,7 +26324,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="280" t="s">
+      <c r="I15" s="288" t="s">
         <v>82</v>
       </c>
       <c r="J15" s="60"/>
@@ -20927,13 +26351,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="279" t="s">
+      <c r="A16" s="287" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="279" t="s">
+      <c r="B16" s="287" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="281" t="s">
+      <c r="C16" s="289" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -20943,7 +26367,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="280"/>
+      <c r="I16" s="288"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -20968,15 +26392,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="279"/>
-      <c r="B17" s="279"/>
-      <c r="C17" s="282"/>
+      <c r="A17" s="287"/>
+      <c r="B17" s="287"/>
+      <c r="C17" s="290"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="276" t="s">
+      <c r="I17" s="284" t="s">
         <v>139</v>
       </c>
       <c r="J17" s="71"/>
@@ -21011,7 +26435,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="276"/>
+      <c r="I18" s="284"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -21183,13 +26607,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="285" t="s">
+      <c r="A28" s="293" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="285"/>
-      <c r="C28" s="285"/>
-      <c r="D28" s="285"/>
-      <c r="E28" s="285"/>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -21249,7 +26673,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="274" t="s">
+      <c r="E30" s="282" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -21283,7 +26707,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="274"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -21313,7 +26737,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="274" t="s">
+      <c r="E32" s="282" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -21343,7 +26767,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="274"/>
+      <c r="E33" s="282"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -21369,7 +26793,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="272" t="s">
+      <c r="E34" s="280" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -21392,7 +26816,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="272"/>
+      <c r="E35" s="280"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -21412,7 +26836,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="274" t="s">
+      <c r="E36" s="282" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -21429,7 +26853,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="274"/>
+      <c r="E37" s="282"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -22897,21 +28321,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="292" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
-      <c r="M1" s="284"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -22964,13 +28388,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="273" t="s">
+      <c r="D3" s="281" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="273" t="s">
+      <c r="F3" s="281" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -22979,24 +28403,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="279" t="s">
+      <c r="J3" s="287" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="280" t="s">
+      <c r="M3" s="288" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="277" t="s">
+      <c r="Q3" s="285" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="278"/>
+      <c r="R3" s="286"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="270" t="s">
+      <c r="T3" s="278" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="271"/>
+      <c r="U3" s="279"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -23008,20 +28432,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="273"/>
+      <c r="D4" s="281"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="273"/>
+      <c r="F4" s="281"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="279"/>
+      <c r="J4" s="287"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="280"/>
+      <c r="M4" s="288"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -23060,7 +28484,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="276" t="s">
+      <c r="F5" s="284" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -23068,7 +28492,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="273" t="s">
+      <c r="J5" s="281" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -23113,13 +28537,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="276"/>
+      <c r="F6" s="284"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="273"/>
+      <c r="J6" s="281"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -23163,13 +28587,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="279" t="s">
+      <c r="F7" s="287" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="275" t="s">
+      <c r="J7" s="283" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -23217,13 +28641,13 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="279"/>
+      <c r="F8" s="287"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="J8" s="275"/>
+      <c r="J8" s="283"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -23267,13 +28691,13 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="276" t="s">
+      <c r="F9" s="284" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
       <c r="H9" s="30"/>
       <c r="I9" s="134"/>
-      <c r="J9" s="280" t="s">
+      <c r="J9" s="288" t="s">
         <v>82</v>
       </c>
       <c r="K9" s="54"/>
@@ -23309,11 +28733,11 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="276"/>
+      <c r="F10" s="284"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
-      <c r="J10" s="280"/>
+      <c r="J10" s="288"/>
       <c r="K10" s="6"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
@@ -23436,7 +28860,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="280" t="s">
+      <c r="I13" s="288" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -23477,7 +28901,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="280"/>
+      <c r="I14" s="288"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -23512,7 +28936,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="286" t="s">
+      <c r="I15" s="294" t="s">
         <v>139</v>
       </c>
       <c r="J15" s="60"/>
@@ -23539,13 +28963,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="279" t="s">
+      <c r="A16" s="287" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="279" t="s">
+      <c r="B16" s="287" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="281" t="s">
+      <c r="C16" s="289" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -23555,7 +28979,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="286"/>
+      <c r="I16" s="294"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -23580,9 +29004,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="279"/>
-      <c r="B17" s="279"/>
-      <c r="C17" s="282"/>
+      <c r="A17" s="287"/>
+      <c r="B17" s="287"/>
+      <c r="C17" s="290"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -23793,13 +29217,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="285" t="s">
+      <c r="A28" s="293" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="285"/>
-      <c r="C28" s="285"/>
-      <c r="D28" s="285"/>
-      <c r="E28" s="285"/>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -23859,7 +29283,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="274" t="s">
+      <c r="E30" s="282" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -23893,7 +29317,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="274"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -23923,7 +29347,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="274" t="s">
+      <c r="E32" s="282" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -23948,7 +29372,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="274"/>
+      <c r="E33" s="282"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -23969,7 +29393,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="272" t="s">
+      <c r="E34" s="280" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -23992,7 +29416,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="272"/>
+      <c r="E35" s="280"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -24012,7 +29436,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="274" t="s">
+      <c r="E36" s="282" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -24032,7 +29456,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="274"/>
+      <c r="E37" s="282"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -25499,21 +30923,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="292" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
-      <c r="M1" s="284"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -25568,13 +30992,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="273" t="s">
+      <c r="D3" s="281" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="273" t="s">
+      <c r="F3" s="281" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -25583,24 +31007,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="279" t="s">
+      <c r="J3" s="287" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="280" t="s">
+      <c r="M3" s="288" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="277" t="s">
+      <c r="Q3" s="285" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="278"/>
+      <c r="R3" s="286"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="270" t="s">
+      <c r="T3" s="278" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="271"/>
+      <c r="U3" s="279"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -25612,20 +31036,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="273"/>
+      <c r="D4" s="281"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="273"/>
+      <c r="F4" s="281"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="279"/>
+      <c r="J4" s="287"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="280"/>
+      <c r="M4" s="288"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -25664,7 +31088,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="276" t="s">
+      <c r="F5" s="284" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -25672,7 +31096,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="273" t="s">
+      <c r="J5" s="281" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -25717,13 +31141,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="276"/>
+      <c r="F6" s="284"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="273"/>
+      <c r="J6" s="281"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -25770,7 +31194,7 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="279" t="s">
+      <c r="F7" s="287" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
@@ -25778,7 +31202,7 @@
       <c r="I7" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="275" t="s">
+      <c r="J7" s="283" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -25826,10 +31250,10 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="279"/>
+      <c r="F8" s="287"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
-      <c r="J8" s="275"/>
+      <c r="J8" s="283"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -25873,7 +31297,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="276" t="s">
+      <c r="F9" s="284" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -25913,7 +31337,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="276"/>
+      <c r="F10" s="284"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -26040,7 +31464,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="280" t="s">
+      <c r="I13" s="288" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -26078,7 +31502,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="280"/>
+      <c r="I14" s="288"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -26113,7 +31537,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="280" t="s">
+      <c r="I15" s="288" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -26140,13 +31564,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="279" t="s">
+      <c r="A16" s="287" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="279" t="s">
+      <c r="B16" s="287" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="276" t="s">
+      <c r="C16" s="284" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -26156,7 +31580,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="280"/>
+      <c r="I16" s="288"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -26181,15 +31605,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="279"/>
-      <c r="B17" s="279"/>
-      <c r="C17" s="276"/>
+      <c r="A17" s="287"/>
+      <c r="B17" s="287"/>
+      <c r="C17" s="284"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="280" t="s">
+      <c r="I17" s="288" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -26224,7 +31648,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="280"/>
+      <c r="I18" s="288"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -26394,13 +31818,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="285" t="s">
+      <c r="A28" s="293" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="285"/>
-      <c r="C28" s="285"/>
-      <c r="D28" s="285"/>
-      <c r="E28" s="285"/>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -26460,7 +31884,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="274" t="s">
+      <c r="E30" s="282" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -26494,7 +31918,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="274"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -26524,7 +31948,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="274" t="s">
+      <c r="E32" s="282" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -26550,7 +31974,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="274"/>
+      <c r="E33" s="282"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -26572,7 +31996,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="272" t="s">
+      <c r="E34" s="280" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -26595,7 +32019,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="272"/>
+      <c r="E35" s="280"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -26615,7 +32039,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="274" t="s">
+      <c r="E36" s="282" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -26632,7 +32056,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="274"/>
+      <c r="E37" s="282"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -28102,21 +33526,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="292" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
-      <c r="M1" s="284"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -28171,13 +33595,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="273" t="s">
+      <c r="D3" s="281" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="273" t="s">
+      <c r="F3" s="281" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -28186,24 +33610,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="279" t="s">
+      <c r="J3" s="287" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="280" t="s">
+      <c r="M3" s="288" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="277" t="s">
+      <c r="Q3" s="285" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="278"/>
+      <c r="R3" s="286"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="270" t="s">
+      <c r="T3" s="278" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="271"/>
+      <c r="U3" s="279"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -28215,20 +33639,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="273"/>
+      <c r="D4" s="281"/>
       <c r="E4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="273"/>
+      <c r="F4" s="281"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="279"/>
+      <c r="J4" s="287"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="280"/>
+      <c r="M4" s="288"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -28267,7 +33691,7 @@
       <c r="E5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F5" s="276" t="s">
+      <c r="F5" s="284" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -28275,7 +33699,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="273" t="s">
+      <c r="J5" s="281" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -28320,13 +33744,13 @@
       <c r="E6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="276"/>
+      <c r="F6" s="284"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="273"/>
+      <c r="J6" s="281"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -28373,13 +33797,13 @@
       <c r="E7" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="279" t="s">
+      <c r="F7" s="287" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="275" t="s">
+      <c r="J7" s="283" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -28425,11 +33849,11 @@
         <v>17</v>
       </c>
       <c r="E8" s="30"/>
-      <c r="F8" s="279"/>
+      <c r="F8" s="287"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="275"/>
+      <c r="J8" s="283"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -28474,7 +33898,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="276" t="s">
+      <c r="F9" s="284" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -28514,7 +33938,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="276"/>
+      <c r="F10" s="284"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -28641,7 +34065,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="280" t="s">
+      <c r="I13" s="288" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -28682,7 +34106,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="280"/>
+      <c r="I14" s="288"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -28717,7 +34141,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="280" t="s">
+      <c r="I15" s="288" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -28744,13 +34168,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="279" t="s">
+      <c r="A16" s="287" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="279" t="s">
+      <c r="B16" s="287" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="276" t="s">
+      <c r="C16" s="284" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -28760,7 +34184,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="280"/>
+      <c r="I16" s="288"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -28785,15 +34209,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="279"/>
-      <c r="B17" s="279"/>
-      <c r="C17" s="276"/>
+      <c r="A17" s="287"/>
+      <c r="B17" s="287"/>
+      <c r="C17" s="284"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="280" t="s">
+      <c r="I17" s="288" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -28828,7 +34252,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="280"/>
+      <c r="I18" s="288"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -28999,13 +34423,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="285" t="s">
+      <c r="A28" s="293" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="285"/>
-      <c r="C28" s="285"/>
-      <c r="D28" s="285"/>
-      <c r="E28" s="285"/>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -29065,7 +34489,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="274" t="s">
+      <c r="E30" s="282" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -29099,7 +34523,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="274"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -29127,7 +34551,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="274" t="s">
+      <c r="E32" s="282" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -29153,7 +34577,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="274"/>
+      <c r="E33" s="282"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -29175,7 +34599,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="272" t="s">
+      <c r="E34" s="280" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -29198,7 +34622,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="272"/>
+      <c r="E35" s="280"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -29218,7 +34642,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="274" t="s">
+      <c r="E36" s="282" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -29238,7 +34662,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="274"/>
+      <c r="E37" s="282"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -29822,18 +35246,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="193" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="294" t="s">
+      <c r="A1" s="302" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="295"/>
-      <c r="C1" s="295"/>
-      <c r="D1" s="295"/>
-      <c r="E1" s="295"/>
-      <c r="F1" s="295"/>
-      <c r="G1" s="295"/>
-      <c r="H1" s="295"/>
-      <c r="I1" s="296"/>
-      <c r="J1" s="296"/>
+      <c r="B1" s="303"/>
+      <c r="C1" s="303"/>
+      <c r="D1" s="303"/>
+      <c r="E1" s="303"/>
+      <c r="F1" s="303"/>
+      <c r="G1" s="303"/>
+      <c r="H1" s="303"/>
+      <c r="I1" s="304"/>
+      <c r="J1" s="304"/>
       <c r="K1" s="190"/>
       <c r="L1" s="190"/>
       <c r="M1" s="191"/>
@@ -29939,22 +35363,22 @@
       <c r="C3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="273" t="s">
+      <c r="D3" s="281" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="201" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="287" t="s">
+      <c r="F3" s="295" t="s">
         <v>160</v>
       </c>
       <c r="H3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="275" t="s">
+      <c r="I3" s="283" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="288" t="s">
+      <c r="K3" s="296" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="2"/>
@@ -29970,16 +35394,16 @@
       <c r="C4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="273"/>
+      <c r="D4" s="281"/>
       <c r="E4" s="201" t="s">
         <v>162</v>
       </c>
-      <c r="F4" s="287"/>
+      <c r="F4" s="295"/>
       <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="275"/>
-      <c r="K4" s="289"/>
+      <c r="I4" s="283"/>
+      <c r="K4" s="297"/>
       <c r="L4" s="203" t="s">
         <v>163</v>
       </c>
@@ -29992,13 +35416,13 @@
       <c r="E5" s="129" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="287" t="s">
+      <c r="F5" s="295" t="s">
         <v>165</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="273" t="s">
+      <c r="I5" s="281" t="s">
         <v>166</v>
       </c>
       <c r="K5" s="2"/>
@@ -30012,11 +35436,11 @@
       <c r="E6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="287"/>
+      <c r="F6" s="295"/>
       <c r="H6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="273"/>
+      <c r="I6" s="281"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -30031,10 +35455,10 @@
       <c r="E7" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F7" s="273" t="s">
+      <c r="F7" s="281" t="s">
         <v>168</v>
       </c>
-      <c r="I7" s="273" t="s">
+      <c r="I7" s="281" t="s">
         <v>15</v>
       </c>
       <c r="K7" s="2"/>
@@ -30048,17 +35472,17 @@
       <c r="E8" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="273"/>
-      <c r="I8" s="273"/>
+      <c r="F8" s="281"/>
+      <c r="I8" s="281"/>
       <c r="K8" s="2"/>
       <c r="L8" s="206"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="281" t="s">
+      <c r="A9" s="289" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="273" t="s">
+      <c r="B9" s="281" t="s">
         <v>171</v>
       </c>
       <c r="C9" s="207" t="s">
@@ -30067,7 +35491,7 @@
       <c r="E9" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="287" t="s">
+      <c r="F9" s="295" t="s">
         <v>173</v>
       </c>
       <c r="K9" s="2"/>
@@ -30077,15 +35501,15 @@
       <c r="P9"/>
     </row>
     <row r="10" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="282"/>
-      <c r="B10" s="273"/>
+      <c r="A10" s="290"/>
+      <c r="B10" s="281"/>
       <c r="C10" s="208" t="s">
         <v>174</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>175</v>
       </c>
-      <c r="F10" s="287"/>
+      <c r="F10" s="295"/>
       <c r="K10" s="209"/>
       <c r="L10" s="2"/>
       <c r="M10" s="206"/>
@@ -30112,7 +35536,7 @@
       <c r="E11" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="F11" s="279" t="s">
+      <c r="F11" s="287" t="s">
         <v>177</v>
       </c>
       <c r="K11" s="209"/>
@@ -30141,7 +35565,7 @@
       <c r="E12" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="279"/>
+      <c r="F12" s="287"/>
       <c r="G12" s="212" t="s">
         <v>179</v>
       </c>
@@ -30180,10 +35604,10 @@
       <c r="E13" s="183" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="290" t="s">
+      <c r="F13" s="298" t="s">
         <v>184</v>
       </c>
-      <c r="H13" s="281" t="s">
+      <c r="H13" s="289" t="s">
         <v>185</v>
       </c>
       <c r="K13" s="2"/>
@@ -30213,8 +35637,8 @@
       <c r="E14" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="F14" s="291"/>
-      <c r="H14" s="282"/>
+      <c r="F14" s="299"/>
+      <c r="H14" s="290"/>
       <c r="K14" s="2"/>
       <c r="L14" s="6"/>
       <c r="M14" s="2"/>
@@ -30241,10 +35665,10 @@
       <c r="E15" s="183" t="s">
         <v>189</v>
       </c>
-      <c r="F15" s="273" t="s">
+      <c r="F15" s="281" t="s">
         <v>190</v>
       </c>
-      <c r="H15" s="288" t="s">
+      <c r="H15" s="296" t="s">
         <v>45</v>
       </c>
       <c r="K15" s="2"/>
@@ -30269,8 +35693,8 @@
       <c r="C16" s="183" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="273"/>
-      <c r="H16" s="289"/>
+      <c r="F16" s="281"/>
+      <c r="H16" s="297"/>
       <c r="K16" s="2"/>
       <c r="L16" s="209"/>
       <c r="M16" s="8"/>
@@ -30297,7 +35721,7 @@
       </c>
       <c r="D17" s="206"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="292" t="s">
+      <c r="F17" s="300" t="s">
         <v>193</v>
       </c>
       <c r="G17" s="2"/>
@@ -30314,7 +35738,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="293"/>
+      <c r="F18" s="301"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="209"/>
@@ -30365,7 +35789,7 @@
       <c r="B20" s="133" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="273" t="s">
+      <c r="C20" s="281" t="s">
         <v>197</v>
       </c>
       <c r="D20" s="2"/>
@@ -30397,7 +35821,7 @@
         <v>199</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="273"/>
+      <c r="C21" s="281"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="219" t="s">
@@ -30405,7 +35829,7 @@
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="288" t="s">
+      <c r="I21" s="296" t="s">
         <v>82</v>
       </c>
       <c r="J21" s="209"/>
@@ -30439,7 +35863,7 @@
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="289"/>
+      <c r="I22" s="297"/>
       <c r="J22" s="209"/>
       <c r="K22" s="101" t="s">
         <v>40</v>
@@ -32108,21 +37532,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="292" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
-      <c r="M1" s="284"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -32177,13 +37601,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="280" t="s">
+      <c r="D3" s="288" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="273" t="s">
+      <c r="F3" s="281" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -32192,24 +37616,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="280" t="s">
+      <c r="J3" s="288" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="305" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="277" t="s">
+      <c r="Q3" s="285" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="278"/>
+      <c r="R3" s="286"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="270" t="s">
+      <c r="T3" s="278" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="271"/>
+      <c r="U3" s="279"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -32223,20 +37647,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="280"/>
+      <c r="D4" s="288"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="273"/>
+      <c r="F4" s="281"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="280"/>
+      <c r="J4" s="288"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="305"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -32275,7 +37699,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="276" t="s">
+      <c r="F5" s="284" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -32283,7 +37707,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="273" t="s">
+      <c r="J5" s="281" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -32328,13 +37752,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="276"/>
+      <c r="F6" s="284"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="273"/>
+      <c r="J6" s="281"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -32378,13 +37802,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="279" t="s">
+      <c r="F7" s="287" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="275" t="s">
+      <c r="J7" s="283" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -32432,11 +37856,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="279"/>
+      <c r="F8" s="287"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="275"/>
+      <c r="J8" s="283"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -32481,7 +37905,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="276" t="s">
+      <c r="F9" s="284" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -32521,7 +37945,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="276"/>
+      <c r="F10" s="284"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -32743,13 +38167,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="279" t="s">
+      <c r="A16" s="287" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="279" t="s">
+      <c r="B16" s="287" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="280" t="s">
+      <c r="C16" s="288" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -32784,9 +38208,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="279"/>
-      <c r="B17" s="279"/>
-      <c r="C17" s="280"/>
+      <c r="A17" s="287"/>
+      <c r="B17" s="287"/>
+      <c r="C17" s="288"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -32996,13 +38420,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="285" t="s">
+      <c r="A28" s="293" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="285"/>
-      <c r="C28" s="285"/>
-      <c r="D28" s="285"/>
-      <c r="E28" s="285"/>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -33062,7 +38486,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="274" t="s">
+      <c r="E30" s="282" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -33094,7 +38518,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="274"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -33122,7 +38546,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="274" t="s">
+      <c r="E32" s="282" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -33150,7 +38574,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="274"/>
+      <c r="E33" s="282"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -33174,7 +38598,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="272" t="s">
+      <c r="E34" s="280" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -33197,7 +38621,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="272"/>
+      <c r="E35" s="280"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -33217,7 +38641,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="274" t="s">
+      <c r="E36" s="282" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -33237,7 +38661,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="274"/>
+      <c r="E37" s="282"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -34702,21 +40126,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="292" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
-      <c r="L1" s="284"/>
-      <c r="M1" s="284"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="292"/>
+      <c r="H1" s="292"/>
+      <c r="I1" s="292"/>
+      <c r="J1" s="292"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
+      <c r="M1" s="292"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -34771,13 +40195,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="280" t="s">
+      <c r="D3" s="288" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="273" t="s">
+      <c r="F3" s="281" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -34786,24 +40210,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="280" t="s">
+      <c r="J3" s="288" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="305" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="277" t="s">
+      <c r="Q3" s="285" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="278"/>
+      <c r="R3" s="286"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="270" t="s">
+      <c r="T3" s="278" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="271"/>
+      <c r="U3" s="279"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -34817,20 +40241,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="280"/>
+      <c r="D4" s="288"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="273"/>
+      <c r="F4" s="281"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="280"/>
+      <c r="J4" s="288"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="305"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -34869,7 +40293,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="276" t="s">
+      <c r="F5" s="284" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -34877,7 +40301,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="273" t="s">
+      <c r="J5" s="281" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -34922,13 +40346,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="276"/>
+      <c r="F6" s="284"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="273"/>
+      <c r="J6" s="281"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -34972,13 +40396,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="279" t="s">
+      <c r="F7" s="287" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="275" t="s">
+      <c r="J7" s="283" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -35026,11 +40450,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="279"/>
+      <c r="F8" s="287"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="275"/>
+      <c r="J8" s="283"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -35075,7 +40499,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="276" t="s">
+      <c r="F9" s="284" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -35115,7 +40539,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="276"/>
+      <c r="F10" s="284"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -35337,13 +40761,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="279" t="s">
+      <c r="A16" s="287" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="279" t="s">
+      <c r="B16" s="287" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="280" t="s">
+      <c r="C16" s="288" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -35378,9 +40802,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="279"/>
-      <c r="B17" s="279"/>
-      <c r="C17" s="280"/>
+      <c r="A17" s="287"/>
+      <c r="B17" s="287"/>
+      <c r="C17" s="288"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -35590,13 +41014,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="285" t="s">
+      <c r="A28" s="293" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="285"/>
-      <c r="C28" s="285"/>
-      <c r="D28" s="285"/>
-      <c r="E28" s="285"/>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="293"/>
+      <c r="E28" s="293"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -35656,7 +41080,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="274" t="s">
+      <c r="E30" s="282" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -35690,7 +41114,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="274"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -35718,7 +41142,7 @@
       <c r="D32" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="274" t="s">
+      <c r="E32" s="282" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -35746,7 +41170,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="274"/>
+      <c r="E33" s="282"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -35770,7 +41194,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="272" t="s">
+      <c r="E34" s="280" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -35795,7 +41219,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="272"/>
+      <c r="E35" s="280"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -35817,7 +41241,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="274" t="s">
+      <c r="E36" s="282" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -35839,7 +41263,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="274"/>
+      <c r="E37" s="282"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>

--- a/raw/D3.xlsx
+++ b/raw/D3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="4" activeTab="13"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="4" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="30-2" sheetId="34" r:id="rId1"/>
@@ -1148,7 +1148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="272">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -2784,7 +2784,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="307">
+  <cellXfs count="308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3583,6 +3583,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -4867,21 +4870,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4936,13 +4939,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="281" t="s">
+      <c r="D3" s="282" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="281" t="s">
+      <c r="F3" s="282" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -4954,24 +4957,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="287" t="s">
+      <c r="J3" s="288" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="288" t="s">
+      <c r="M3" s="289" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -4983,20 +4986,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="281"/>
+      <c r="D4" s="282"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="281"/>
+      <c r="F4" s="282"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="287"/>
+      <c r="J4" s="288"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="288"/>
+      <c r="M4" s="289"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -5035,7 +5038,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -5043,7 +5046,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -5088,13 +5091,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="284"/>
+      <c r="F6" s="285"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -5140,13 +5143,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="287" t="s">
+      <c r="F7" s="288" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="283" t="s">
+      <c r="J7" s="284" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -5194,11 +5197,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="287"/>
+      <c r="F8" s="288"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="283"/>
+      <c r="J8" s="284"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -5242,7 +5245,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="284" t="s">
+      <c r="F9" s="285" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -5282,7 +5285,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="284"/>
+      <c r="F10" s="285"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -5407,7 +5410,7 @@
         <v>115</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="288" t="s">
+      <c r="H13" s="289" t="s">
         <v>82</v>
       </c>
       <c r="I13" s="30"/>
@@ -5446,7 +5449,7 @@
       <c r="F14" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="288"/>
+      <c r="H14" s="289"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -5481,7 +5484,7 @@
         <v>83</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="288" t="s">
+      <c r="H15" s="289" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="30"/>
@@ -5518,7 +5521,7 @@
         <v>81</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="288"/>
+      <c r="H16" s="289"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -5550,7 +5553,7 @@
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="289" t="s">
+      <c r="H17" s="290" t="s">
         <v>45</v>
       </c>
       <c r="I17" s="30"/>
@@ -5585,7 +5588,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="290"/>
+      <c r="H18" s="291"/>
       <c r="I18" s="30"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
@@ -5602,7 +5605,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="287" t="s">
+      <c r="H19" s="288" t="s">
         <v>85</v>
       </c>
       <c r="I19" s="30"/>
@@ -5627,7 +5630,7 @@
       <c r="E20" s="137"/>
       <c r="F20" s="8"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="287"/>
+      <c r="H20" s="288"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -5646,7 +5649,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="287" t="s">
+      <c r="H21" s="288" t="s">
         <v>84</v>
       </c>
       <c r="I21" s="30"/>
@@ -5663,7 +5666,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="137"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="287"/>
+      <c r="H22" s="288"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -5760,13 +5763,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -5826,7 +5829,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -5860,7 +5863,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -5890,7 +5893,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="8"/>
@@ -5916,7 +5919,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
       <c r="I33" s="30"/>
@@ -5939,7 +5942,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="280" t="s">
+      <c r="E34" s="281" t="s">
         <v>133</v>
       </c>
       <c r="G34" s="8"/>
@@ -5960,7 +5963,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="280"/>
+      <c r="E35" s="281"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
       <c r="I35" s="30"/>
@@ -5979,7 +5982,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -5999,7 +6002,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -6466,7 +6469,7 @@
       <c r="S65"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A66" s="291" t="s">
+      <c r="A66" s="292" t="s">
         <v>139</v>
       </c>
       <c r="L66" s="119" t="s">
@@ -6478,7 +6481,7 @@
       <c r="S66"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A67" s="291"/>
+      <c r="A67" s="292"/>
       <c r="L67" s="119" t="s">
         <v>95</v>
       </c>
@@ -7469,21 +7472,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -7542,7 +7545,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="281" t="s">
+      <c r="F3" s="282" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -7551,24 +7554,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="283" t="s">
+      <c r="J3" s="284" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="305" t="s">
+      <c r="M3" s="306" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -7586,16 +7589,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="281"/>
+      <c r="F4" s="282"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="283"/>
+      <c r="J4" s="284"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="305"/>
+      <c r="M4" s="306"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -7634,7 +7637,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -7642,7 +7645,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -7687,13 +7690,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="284"/>
+      <c r="F6" s="285"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -7740,7 +7743,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="284" t="s">
+      <c r="F7" s="285" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -7792,7 +7795,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="284"/>
+      <c r="F8" s="285"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -8008,7 +8011,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="287" t="s">
+      <c r="H13" s="288" t="s">
         <v>121</v>
       </c>
       <c r="I13" s="30"/>
@@ -8044,7 +8047,7 @@
       <c r="F14" s="240" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="287"/>
+      <c r="H14" s="288"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -8077,7 +8080,7 @@
       <c r="E15" s="240"/>
       <c r="F15" s="8"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="287" t="s">
+      <c r="H15" s="288" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="30"/>
@@ -8106,7 +8109,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="288" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="8"/>
@@ -8114,7 +8117,7 @@
       <c r="E16" s="59"/>
       <c r="F16" s="8"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="287"/>
+      <c r="H16" s="288"/>
       <c r="I16" s="30"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
@@ -8141,13 +8144,13 @@
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
-      <c r="B17" s="287"/>
+      <c r="B17" s="288"/>
       <c r="C17" s="8"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="288" t="s">
+      <c r="H17" s="289" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -8182,7 +8185,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="288"/>
+      <c r="H18" s="289"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -8199,7 +8202,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="288" t="s">
+      <c r="H19" s="289" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -8224,7 +8227,7 @@
       <c r="E20" s="240"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="288"/>
+      <c r="H20" s="289"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -8243,7 +8246,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="288" t="s">
+      <c r="H21" s="289" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -8261,7 +8264,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="240"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="288"/>
+      <c r="H22" s="289"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -8358,13 +8361,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -8424,7 +8427,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -8458,7 +8461,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -8485,7 +8488,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -8513,7 +8516,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -8537,7 +8540,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="280" t="s">
+      <c r="E34" s="281" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -8562,7 +8565,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="280"/>
+      <c r="E35" s="281"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -8584,7 +8587,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -8606,7 +8609,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -10074,21 +10077,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -10147,7 +10150,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="281" t="s">
+      <c r="F3" s="282" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -10156,24 +10159,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="283" t="s">
+      <c r="J3" s="284" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="288" t="s">
+      <c r="M3" s="289" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -10191,16 +10194,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="281"/>
+      <c r="F4" s="282"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="283"/>
+      <c r="J4" s="284"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="288"/>
+      <c r="M4" s="289"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -10239,7 +10242,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -10247,7 +10250,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -10292,13 +10295,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="284"/>
+      <c r="F6" s="285"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -10345,7 +10348,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="284" t="s">
+      <c r="F7" s="285" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -10397,7 +10400,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="284"/>
+      <c r="F8" s="285"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -10613,7 +10616,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="287" t="s">
+      <c r="H13" s="288" t="s">
         <v>121</v>
       </c>
       <c r="I13" s="30"/>
@@ -10649,7 +10652,7 @@
       <c r="F14" s="248" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="287"/>
+      <c r="H14" s="288"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -10682,7 +10685,7 @@
       <c r="E15" s="248"/>
       <c r="F15" s="8"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="287" t="s">
+      <c r="H15" s="288" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="30"/>
@@ -10711,7 +10714,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="288" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="8"/>
@@ -10719,7 +10722,7 @@
       <c r="E16" s="59"/>
       <c r="F16" s="8"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="287"/>
+      <c r="H16" s="288"/>
       <c r="I16" s="30"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
@@ -10746,13 +10749,13 @@
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
-      <c r="B17" s="287"/>
+      <c r="B17" s="288"/>
       <c r="C17" s="8"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="288" t="s">
+      <c r="H17" s="289" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -10787,7 +10790,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="288"/>
+      <c r="H18" s="289"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -10804,7 +10807,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="288" t="s">
+      <c r="H19" s="289" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -10829,7 +10832,7 @@
       <c r="E20" s="248"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="288"/>
+      <c r="H20" s="289"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -10848,7 +10851,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="288" t="s">
+      <c r="H21" s="289" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -10866,7 +10869,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="248"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="288"/>
+      <c r="H22" s="289"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -10963,13 +10966,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -11029,7 +11032,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -11063,7 +11066,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -11093,7 +11096,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -11121,7 +11124,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -11145,7 +11148,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="280" t="s">
+      <c r="E34" s="281" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -11169,7 +11172,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="280"/>
+      <c r="E35" s="281"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -11191,7 +11194,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -11211,7 +11214,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -12679,21 +12682,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -12748,13 +12751,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="288" t="s">
+      <c r="D3" s="289" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="281" t="s">
+      <c r="F3" s="282" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -12763,24 +12766,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="283" t="s">
+      <c r="J3" s="284" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="288" t="s">
+      <c r="M3" s="289" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -12794,20 +12797,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="288"/>
+      <c r="D4" s="289"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="281"/>
+      <c r="F4" s="282"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="283"/>
+      <c r="J4" s="284"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="288"/>
+      <c r="M4" s="289"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -12846,7 +12849,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -12854,7 +12857,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -12899,13 +12902,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="284"/>
+      <c r="F6" s="285"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -12952,13 +12955,13 @@
       <c r="E7" s="260" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="306" t="s">
+      <c r="F7" s="307" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="288" t="s">
+      <c r="J7" s="289" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -13006,11 +13009,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="306"/>
+      <c r="F8" s="307"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="288"/>
+      <c r="J8" s="289"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -13055,7 +13058,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="287" t="s">
+      <c r="F9" s="288" t="s">
         <v>121</v>
       </c>
       <c r="G9" s="64"/>
@@ -13095,7 +13098,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="287"/>
+      <c r="F10" s="288"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -13315,13 +13318,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="288" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="288" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="288" t="s">
+      <c r="C16" s="289" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -13356,9 +13359,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="287"/>
-      <c r="B17" s="287"/>
-      <c r="C17" s="288"/>
+      <c r="A17" s="288"/>
+      <c r="B17" s="288"/>
+      <c r="C17" s="289"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="259" t="s">
@@ -13569,13 +13572,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -13635,7 +13638,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -13669,7 +13672,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -13699,7 +13702,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -13729,7 +13732,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -13753,7 +13756,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="280" t="s">
+      <c r="E34" s="281" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -13777,7 +13780,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="280"/>
+      <c r="E35" s="281"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -13796,7 +13799,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -13816,7 +13819,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -15282,21 +15285,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -15351,13 +15354,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="281" t="s">
+      <c r="D3" s="282" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="281" t="s">
+      <c r="F3" s="282" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -15366,24 +15369,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="283" t="s">
+      <c r="J3" s="284" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="288" t="s">
+      <c r="M3" s="289" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -15397,20 +15400,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="281"/>
+      <c r="D4" s="282"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="281"/>
+      <c r="F4" s="282"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="283"/>
+      <c r="J4" s="284"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="288"/>
+      <c r="M4" s="289"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -15449,7 +15452,7 @@
       <c r="E5" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -15457,7 +15460,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -15502,13 +15505,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="284"/>
+      <c r="F6" s="285"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -15555,13 +15558,13 @@
       <c r="E7" s="260" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="306" t="s">
+      <c r="F7" s="307" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="288" t="s">
+      <c r="J7" s="289" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -15609,11 +15612,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="306"/>
+      <c r="F8" s="307"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="288"/>
+      <c r="J8" s="289"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -15658,7 +15661,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="287" t="s">
+      <c r="F9" s="288" t="s">
         <v>121</v>
       </c>
       <c r="G9" s="64"/>
@@ -15698,7 +15701,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="287"/>
+      <c r="F10" s="288"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -15825,7 +15828,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="288" t="s">
+      <c r="I13" s="289" t="s">
         <v>45</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -15861,7 +15864,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="288"/>
+      <c r="I14" s="289"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -15921,13 +15924,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="288" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="288" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="288" t="s">
+      <c r="C16" s="289" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -15962,9 +15965,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="287"/>
-      <c r="B17" s="287"/>
-      <c r="C17" s="288"/>
+      <c r="A17" s="288"/>
+      <c r="B17" s="288"/>
+      <c r="C17" s="289"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="269" t="s">
@@ -16175,13 +16178,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -16241,7 +16244,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -16275,7 +16278,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -16303,7 +16306,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -16331,7 +16334,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -16355,7 +16358,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="280" t="s">
+      <c r="E34" s="281" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -16377,7 +16380,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="280"/>
+      <c r="E35" s="281"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -16397,7 +16400,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -16417,7 +16420,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -17888,21 +17891,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -17957,13 +17960,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="281" t="s">
+      <c r="D3" s="282" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="281" t="s">
+      <c r="F3" s="282" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -17972,24 +17975,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="283" t="s">
+      <c r="J3" s="284" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="288" t="s">
+      <c r="M3" s="289" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -18003,20 +18006,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="281"/>
+      <c r="D4" s="282"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="281"/>
+      <c r="F4" s="282"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="283"/>
+      <c r="J4" s="284"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="288"/>
+      <c r="M4" s="289"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -18055,7 +18058,7 @@
       <c r="E5" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -18063,7 +18066,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -18108,13 +18111,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="284"/>
+      <c r="F6" s="285"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -18161,13 +18164,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="284" t="s">
+      <c r="F7" s="285" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="288" t="s">
+      <c r="J7" s="289" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -18215,11 +18218,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="284"/>
+      <c r="F8" s="285"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="288"/>
+      <c r="J8" s="289"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -18264,7 +18267,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="287" t="s">
+      <c r="F9" s="288" t="s">
         <v>121</v>
       </c>
       <c r="G9" s="64"/>
@@ -18304,7 +18307,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="287"/>
+      <c r="F10" s="288"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -18525,13 +18528,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="288" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="288" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="288" t="s">
+      <c r="C16" s="289" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -18566,9 +18569,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="287"/>
-      <c r="B17" s="287"/>
-      <c r="C17" s="288"/>
+      <c r="A17" s="288"/>
+      <c r="B17" s="288"/>
+      <c r="C17" s="289"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -18601,7 +18604,7 @@
     <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="288" t="s">
+      <c r="C18" s="289" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="61"/>
@@ -18620,7 +18623,7 @@
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="273"/>
-      <c r="C19" s="288"/>
+      <c r="C19" s="289"/>
       <c r="D19" s="125"/>
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
@@ -18780,13 +18783,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -18846,7 +18849,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -18880,7 +18883,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -18908,7 +18911,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -18936,7 +18939,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -18960,7 +18963,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="280" t="s">
+      <c r="E34" s="281" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -18984,7 +18987,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="280"/>
+      <c r="E35" s="281"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -19004,7 +19007,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -19024,7 +19027,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -20494,21 +20497,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -20563,13 +20566,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="281" t="s">
+      <c r="D3" s="282" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="284" t="s">
+      <c r="F3" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -20578,24 +20581,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="283" t="s">
+      <c r="J3" s="284" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="288" t="s">
+      <c r="M3" s="289" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -20603,26 +20606,23 @@
       <c r="A4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="C4" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="281"/>
+      <c r="D4" s="282"/>
       <c r="E4" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="F4" s="284"/>
+      <c r="F4" s="285"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="283"/>
+      <c r="J4" s="284"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="288"/>
+      <c r="M4" s="289"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -20652,7 +20652,9 @@
       </c>
     </row>
     <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7"/>
+      <c r="A5" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="B5" s="7"/>
       <c r="C5" s="11" t="s">
         <v>245</v>
@@ -20661,7 +20663,7 @@
       <c r="E5" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>257</v>
       </c>
       <c r="G5" s="8"/>
@@ -20669,7 +20671,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -20714,13 +20716,13 @@
       <c r="E6" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F6" s="284"/>
-      <c r="G6" s="277"/>
+      <c r="F6" s="285"/>
+      <c r="G6" s="278"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -20764,13 +20766,13 @@
       <c r="E7" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="284" t="s">
+      <c r="F7" s="285" t="s">
         <v>110</v>
       </c>
-      <c r="G7" s="277"/>
+      <c r="G7" s="278"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="288" t="s">
+      <c r="J7" s="289" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -20818,11 +20820,11 @@
       <c r="E8" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F8" s="284"/>
+      <c r="F8" s="285"/>
       <c r="G8" s="62"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="288"/>
+      <c r="J8" s="289"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -20867,7 +20869,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="287" t="s">
+      <c r="F9" s="288" t="s">
         <v>258</v>
       </c>
       <c r="G9" s="62"/>
@@ -20907,7 +20909,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="287"/>
+      <c r="F10" s="288"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -21034,7 +21036,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="288" t="s">
+      <c r="I13" s="289" t="s">
         <v>45</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -21070,7 +21072,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="288"/>
+      <c r="I14" s="289"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -21132,18 +21134,18 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="288" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="288" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="288" t="s">
+      <c r="C16" s="289" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="59"/>
-      <c r="F16" s="273" t="s">
+      <c r="F16" s="277" t="s">
         <v>83</v>
       </c>
       <c r="G16" s="6"/>
@@ -21173,12 +21175,14 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="287"/>
-      <c r="B17" s="287"/>
-      <c r="C17" s="288"/>
+      <c r="A17" s="288"/>
+      <c r="B17" s="288"/>
+      <c r="C17" s="289"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
-      <c r="F17" s="8"/>
+      <c r="F17" s="128" t="s">
+        <v>120</v>
+      </c>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
       <c r="I17" s="30"/>
@@ -21385,13 +21389,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -21451,7 +21455,7 @@
       <c r="D30" s="93" t="s">
         <v>251</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -21485,7 +21489,7 @@
       <c r="D31" s="93" t="s">
         <v>252</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -21513,7 +21517,7 @@
       <c r="D32" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>259</v>
       </c>
       <c r="F32" s="8"/>
@@ -21541,7 +21545,7 @@
       <c r="D33" s="93" t="s">
         <v>253</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -21565,7 +21569,7 @@
       <c r="D34" s="93" t="s">
         <v>254</v>
       </c>
-      <c r="E34" s="282" t="s">
+      <c r="E34" s="283" t="s">
         <v>260</v>
       </c>
       <c r="F34" s="8"/>
@@ -21587,7 +21591,7 @@
       <c r="D35" s="93" t="s">
         <v>255</v>
       </c>
-      <c r="E35" s="282"/>
+      <c r="E35" s="283"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -21607,7 +21611,7 @@
       <c r="D36" s="93" t="s">
         <v>256</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>261</v>
       </c>
       <c r="F36" s="53"/>
@@ -21627,7 +21631,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -22182,7 +22186,8 @@
     <mergeCell ref="E30:E31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -23099,21 +23104,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -23168,13 +23173,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="281" t="s">
+      <c r="D3" s="282" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="281" t="s">
+      <c r="F3" s="282" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -23183,24 +23188,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="287" t="s">
+      <c r="J3" s="288" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="288" t="s">
+      <c r="M3" s="289" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -23212,20 +23217,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="281"/>
+      <c r="D4" s="282"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="281"/>
+      <c r="F4" s="282"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="287"/>
+      <c r="J4" s="288"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="288"/>
+      <c r="M4" s="289"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -23264,7 +23269,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -23272,7 +23277,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -23317,13 +23322,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="284"/>
+      <c r="F6" s="285"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -23372,13 +23377,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="287" t="s">
+      <c r="F7" s="288" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="283" t="s">
+      <c r="J7" s="284" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -23426,11 +23431,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="287"/>
+      <c r="F8" s="288"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="283"/>
+      <c r="J8" s="284"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -23474,7 +23479,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="284" t="s">
+      <c r="F9" s="285" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -23514,7 +23519,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="284"/>
+      <c r="F10" s="285"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -23640,7 +23645,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="288" t="s">
+      <c r="I13" s="289" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -23681,7 +23686,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="288"/>
+      <c r="I14" s="289"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -23741,13 +23746,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="288" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="288" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="289" t="s">
+      <c r="C16" s="290" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -23782,9 +23787,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="287"/>
-      <c r="B17" s="287"/>
-      <c r="C17" s="290"/>
+      <c r="A17" s="288"/>
+      <c r="B17" s="288"/>
+      <c r="C17" s="291"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -23817,7 +23822,7 @@
     <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="288" t="s">
+      <c r="C18" s="289" t="s">
         <v>82</v>
       </c>
       <c r="D18" s="61"/>
@@ -23835,7 +23840,7 @@
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="147"/>
-      <c r="C19" s="288"/>
+      <c r="C19" s="289"/>
       <c r="D19" s="125"/>
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
@@ -23994,13 +23999,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -24060,7 +24065,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -24094,7 +24099,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -24124,7 +24129,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -24154,7 +24159,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -24178,7 +24183,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="280" t="s">
+      <c r="E34" s="281" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -24203,7 +24208,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="280"/>
+      <c r="E35" s="281"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -24222,7 +24227,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -24242,7 +24247,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -25712,21 +25717,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -25781,13 +25786,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="281" t="s">
+      <c r="D3" s="282" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="281" t="s">
+      <c r="F3" s="282" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -25796,24 +25801,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="287" t="s">
+      <c r="J3" s="288" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="288" t="s">
+      <c r="M3" s="289" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -25825,20 +25830,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="281"/>
+      <c r="D4" s="282"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="281"/>
+      <c r="F4" s="282"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="287"/>
+      <c r="J4" s="288"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="288"/>
+      <c r="M4" s="289"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -25877,7 +25882,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -25885,7 +25890,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -25930,13 +25935,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="284"/>
+      <c r="F6" s="285"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -25980,13 +25985,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="287" t="s">
+      <c r="F7" s="288" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="283" t="s">
+      <c r="J7" s="284" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -26034,11 +26039,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="287"/>
+      <c r="F8" s="288"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="283"/>
+      <c r="J8" s="284"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -26082,7 +26087,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="284" t="s">
+      <c r="F9" s="285" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -26122,7 +26127,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="284"/>
+      <c r="F10" s="285"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -26248,7 +26253,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="288" t="s">
+      <c r="I13" s="289" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -26289,7 +26294,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="288"/>
+      <c r="I14" s="289"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -26324,7 +26329,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="288" t="s">
+      <c r="I15" s="289" t="s">
         <v>82</v>
       </c>
       <c r="J15" s="60"/>
@@ -26351,13 +26356,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="288" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="288" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="289" t="s">
+      <c r="C16" s="290" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -26367,7 +26372,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="288"/>
+      <c r="I16" s="289"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -26392,15 +26397,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="287"/>
-      <c r="B17" s="287"/>
-      <c r="C17" s="290"/>
+      <c r="A17" s="288"/>
+      <c r="B17" s="288"/>
+      <c r="C17" s="291"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="284" t="s">
+      <c r="I17" s="285" t="s">
         <v>139</v>
       </c>
       <c r="J17" s="71"/>
@@ -26435,7 +26440,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="284"/>
+      <c r="I18" s="285"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -26607,13 +26612,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -26673,7 +26678,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -26707,7 +26712,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -26737,7 +26742,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -26767,7 +26772,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -26793,7 +26798,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="280" t="s">
+      <c r="E34" s="281" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -26816,7 +26821,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="280"/>
+      <c r="E35" s="281"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -26836,7 +26841,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -26853,7 +26858,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -28321,21 +28326,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -28388,13 +28393,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="281" t="s">
+      <c r="D3" s="282" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="281" t="s">
+      <c r="F3" s="282" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -28403,24 +28408,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="287" t="s">
+      <c r="J3" s="288" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="288" t="s">
+      <c r="M3" s="289" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -28432,20 +28437,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="281"/>
+      <c r="D4" s="282"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="281"/>
+      <c r="F4" s="282"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="287"/>
+      <c r="J4" s="288"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="288"/>
+      <c r="M4" s="289"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -28484,7 +28489,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -28492,7 +28497,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -28537,13 +28542,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="284"/>
+      <c r="F6" s="285"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -28587,13 +28592,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="287" t="s">
+      <c r="F7" s="288" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="283" t="s">
+      <c r="J7" s="284" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -28641,13 +28646,13 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="287"/>
+      <c r="F8" s="288"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="J8" s="283"/>
+      <c r="J8" s="284"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -28691,13 +28696,13 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="284" t="s">
+      <c r="F9" s="285" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
       <c r="H9" s="30"/>
       <c r="I9" s="134"/>
-      <c r="J9" s="288" t="s">
+      <c r="J9" s="289" t="s">
         <v>82</v>
       </c>
       <c r="K9" s="54"/>
@@ -28733,11 +28738,11 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="284"/>
+      <c r="F10" s="285"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
-      <c r="J10" s="288"/>
+      <c r="J10" s="289"/>
       <c r="K10" s="6"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
@@ -28860,7 +28865,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="288" t="s">
+      <c r="I13" s="289" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -28901,7 +28906,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="288"/>
+      <c r="I14" s="289"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -28936,7 +28941,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="294" t="s">
+      <c r="I15" s="295" t="s">
         <v>139</v>
       </c>
       <c r="J15" s="60"/>
@@ -28963,13 +28968,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="288" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="288" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="289" t="s">
+      <c r="C16" s="290" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -28979,7 +28984,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="294"/>
+      <c r="I16" s="295"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -29004,9 +29009,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="287"/>
-      <c r="B17" s="287"/>
-      <c r="C17" s="290"/>
+      <c r="A17" s="288"/>
+      <c r="B17" s="288"/>
+      <c r="C17" s="291"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -29217,13 +29222,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -29283,7 +29288,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -29317,7 +29322,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -29347,7 +29352,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -29372,7 +29377,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -29393,7 +29398,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="280" t="s">
+      <c r="E34" s="281" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -29416,7 +29421,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="280"/>
+      <c r="E35" s="281"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -29436,7 +29441,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -29456,7 +29461,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -30923,21 +30928,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -30992,13 +30997,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="281" t="s">
+      <c r="D3" s="282" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="281" t="s">
+      <c r="F3" s="282" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -31007,24 +31012,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="287" t="s">
+      <c r="J3" s="288" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="288" t="s">
+      <c r="M3" s="289" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -31036,20 +31041,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="281"/>
+      <c r="D4" s="282"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="281"/>
+      <c r="F4" s="282"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="287"/>
+      <c r="J4" s="288"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="288"/>
+      <c r="M4" s="289"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -31088,7 +31093,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -31096,7 +31101,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -31141,13 +31146,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="284"/>
+      <c r="F6" s="285"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -31194,7 +31199,7 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="287" t="s">
+      <c r="F7" s="288" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
@@ -31202,7 +31207,7 @@
       <c r="I7" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="283" t="s">
+      <c r="J7" s="284" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -31250,10 +31255,10 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="287"/>
+      <c r="F8" s="288"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
-      <c r="J8" s="283"/>
+      <c r="J8" s="284"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -31297,7 +31302,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="284" t="s">
+      <c r="F9" s="285" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -31337,7 +31342,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="284"/>
+      <c r="F10" s="285"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -31464,7 +31469,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="288" t="s">
+      <c r="I13" s="289" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -31502,7 +31507,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="288"/>
+      <c r="I14" s="289"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -31537,7 +31542,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="288" t="s">
+      <c r="I15" s="289" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -31564,13 +31569,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="288" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="288" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="284" t="s">
+      <c r="C16" s="285" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -31580,7 +31585,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="288"/>
+      <c r="I16" s="289"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -31605,15 +31610,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="287"/>
-      <c r="B17" s="287"/>
-      <c r="C17" s="284"/>
+      <c r="A17" s="288"/>
+      <c r="B17" s="288"/>
+      <c r="C17" s="285"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="288" t="s">
+      <c r="I17" s="289" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -31648,7 +31653,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="288"/>
+      <c r="I18" s="289"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -31818,13 +31823,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -31884,7 +31889,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -31918,7 +31923,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -31948,7 +31953,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -31974,7 +31979,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -31996,7 +32001,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="280" t="s">
+      <c r="E34" s="281" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -32019,7 +32024,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="280"/>
+      <c r="E35" s="281"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -32039,7 +32044,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -32056,7 +32061,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -33526,21 +33531,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -33595,13 +33600,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="281" t="s">
+      <c r="D3" s="282" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="281" t="s">
+      <c r="F3" s="282" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -33610,24 +33615,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="287" t="s">
+      <c r="J3" s="288" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="288" t="s">
+      <c r="M3" s="289" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -33639,20 +33644,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="281"/>
+      <c r="D4" s="282"/>
       <c r="E4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="281"/>
+      <c r="F4" s="282"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="287"/>
+      <c r="J4" s="288"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="288"/>
+      <c r="M4" s="289"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -33691,7 +33696,7 @@
       <c r="E5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -33699,7 +33704,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -33744,13 +33749,13 @@
       <c r="E6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="284"/>
+      <c r="F6" s="285"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -33797,13 +33802,13 @@
       <c r="E7" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="287" t="s">
+      <c r="F7" s="288" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="283" t="s">
+      <c r="J7" s="284" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -33849,11 +33854,11 @@
         <v>17</v>
       </c>
       <c r="E8" s="30"/>
-      <c r="F8" s="287"/>
+      <c r="F8" s="288"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="283"/>
+      <c r="J8" s="284"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -33898,7 +33903,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="284" t="s">
+      <c r="F9" s="285" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -33938,7 +33943,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="284"/>
+      <c r="F10" s="285"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -34065,7 +34070,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="288" t="s">
+      <c r="I13" s="289" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -34106,7 +34111,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="288"/>
+      <c r="I14" s="289"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -34141,7 +34146,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="288" t="s">
+      <c r="I15" s="289" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -34168,13 +34173,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="288" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="288" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="284" t="s">
+      <c r="C16" s="285" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -34184,7 +34189,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="288"/>
+      <c r="I16" s="289"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -34209,15 +34214,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="287"/>
-      <c r="B17" s="287"/>
-      <c r="C17" s="284"/>
+      <c r="A17" s="288"/>
+      <c r="B17" s="288"/>
+      <c r="C17" s="285"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="288" t="s">
+      <c r="I17" s="289" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -34252,7 +34257,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="288"/>
+      <c r="I18" s="289"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -34423,13 +34428,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -34489,7 +34494,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -34523,7 +34528,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -34551,7 +34556,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -34577,7 +34582,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -34599,7 +34604,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="280" t="s">
+      <c r="E34" s="281" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -34622,7 +34627,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="280"/>
+      <c r="E35" s="281"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -34642,7 +34647,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -34662,7 +34667,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -35246,18 +35251,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="193" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="302" t="s">
+      <c r="A1" s="303" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="303"/>
-      <c r="C1" s="303"/>
-      <c r="D1" s="303"/>
-      <c r="E1" s="303"/>
-      <c r="F1" s="303"/>
-      <c r="G1" s="303"/>
-      <c r="H1" s="303"/>
-      <c r="I1" s="304"/>
-      <c r="J1" s="304"/>
+      <c r="B1" s="304"/>
+      <c r="C1" s="304"/>
+      <c r="D1" s="304"/>
+      <c r="E1" s="304"/>
+      <c r="F1" s="304"/>
+      <c r="G1" s="304"/>
+      <c r="H1" s="304"/>
+      <c r="I1" s="305"/>
+      <c r="J1" s="305"/>
       <c r="K1" s="190"/>
       <c r="L1" s="190"/>
       <c r="M1" s="191"/>
@@ -35363,22 +35368,22 @@
       <c r="C3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="281" t="s">
+      <c r="D3" s="282" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="201" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="295" t="s">
+      <c r="F3" s="296" t="s">
         <v>160</v>
       </c>
       <c r="H3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="283" t="s">
+      <c r="I3" s="284" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="296" t="s">
+      <c r="K3" s="297" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="2"/>
@@ -35394,16 +35399,16 @@
       <c r="C4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="281"/>
+      <c r="D4" s="282"/>
       <c r="E4" s="201" t="s">
         <v>162</v>
       </c>
-      <c r="F4" s="295"/>
+      <c r="F4" s="296"/>
       <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="283"/>
-      <c r="K4" s="297"/>
+      <c r="I4" s="284"/>
+      <c r="K4" s="298"/>
       <c r="L4" s="203" t="s">
         <v>163</v>
       </c>
@@ -35416,13 +35421,13 @@
       <c r="E5" s="129" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="295" t="s">
+      <c r="F5" s="296" t="s">
         <v>165</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="281" t="s">
+      <c r="I5" s="282" t="s">
         <v>166</v>
       </c>
       <c r="K5" s="2"/>
@@ -35436,11 +35441,11 @@
       <c r="E6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="295"/>
+      <c r="F6" s="296"/>
       <c r="H6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="281"/>
+      <c r="I6" s="282"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -35455,10 +35460,10 @@
       <c r="E7" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F7" s="281" t="s">
+      <c r="F7" s="282" t="s">
         <v>168</v>
       </c>
-      <c r="I7" s="281" t="s">
+      <c r="I7" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K7" s="2"/>
@@ -35472,17 +35477,17 @@
       <c r="E8" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="281"/>
-      <c r="I8" s="281"/>
+      <c r="F8" s="282"/>
+      <c r="I8" s="282"/>
       <c r="K8" s="2"/>
       <c r="L8" s="206"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="289" t="s">
+      <c r="A9" s="290" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="281" t="s">
+      <c r="B9" s="282" t="s">
         <v>171</v>
       </c>
       <c r="C9" s="207" t="s">
@@ -35491,7 +35496,7 @@
       <c r="E9" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="295" t="s">
+      <c r="F9" s="296" t="s">
         <v>173</v>
       </c>
       <c r="K9" s="2"/>
@@ -35501,15 +35506,15 @@
       <c r="P9"/>
     </row>
     <row r="10" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="290"/>
-      <c r="B10" s="281"/>
+      <c r="A10" s="291"/>
+      <c r="B10" s="282"/>
       <c r="C10" s="208" t="s">
         <v>174</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>175</v>
       </c>
-      <c r="F10" s="295"/>
+      <c r="F10" s="296"/>
       <c r="K10" s="209"/>
       <c r="L10" s="2"/>
       <c r="M10" s="206"/>
@@ -35536,7 +35541,7 @@
       <c r="E11" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="F11" s="287" t="s">
+      <c r="F11" s="288" t="s">
         <v>177</v>
       </c>
       <c r="K11" s="209"/>
@@ -35565,7 +35570,7 @@
       <c r="E12" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="287"/>
+      <c r="F12" s="288"/>
       <c r="G12" s="212" t="s">
         <v>179</v>
       </c>
@@ -35604,10 +35609,10 @@
       <c r="E13" s="183" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="298" t="s">
+      <c r="F13" s="299" t="s">
         <v>184</v>
       </c>
-      <c r="H13" s="289" t="s">
+      <c r="H13" s="290" t="s">
         <v>185</v>
       </c>
       <c r="K13" s="2"/>
@@ -35637,8 +35642,8 @@
       <c r="E14" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="F14" s="299"/>
-      <c r="H14" s="290"/>
+      <c r="F14" s="300"/>
+      <c r="H14" s="291"/>
       <c r="K14" s="2"/>
       <c r="L14" s="6"/>
       <c r="M14" s="2"/>
@@ -35665,10 +35670,10 @@
       <c r="E15" s="183" t="s">
         <v>189</v>
       </c>
-      <c r="F15" s="281" t="s">
+      <c r="F15" s="282" t="s">
         <v>190</v>
       </c>
-      <c r="H15" s="296" t="s">
+      <c r="H15" s="297" t="s">
         <v>45</v>
       </c>
       <c r="K15" s="2"/>
@@ -35693,8 +35698,8 @@
       <c r="C16" s="183" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="281"/>
-      <c r="H16" s="297"/>
+      <c r="F16" s="282"/>
+      <c r="H16" s="298"/>
       <c r="K16" s="2"/>
       <c r="L16" s="209"/>
       <c r="M16" s="8"/>
@@ -35721,7 +35726,7 @@
       </c>
       <c r="D17" s="206"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="300" t="s">
+      <c r="F17" s="301" t="s">
         <v>193</v>
       </c>
       <c r="G17" s="2"/>
@@ -35738,7 +35743,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="301"/>
+      <c r="F18" s="302"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="209"/>
@@ -35789,7 +35794,7 @@
       <c r="B20" s="133" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="281" t="s">
+      <c r="C20" s="282" t="s">
         <v>197</v>
       </c>
       <c r="D20" s="2"/>
@@ -35821,7 +35826,7 @@
         <v>199</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="281"/>
+      <c r="C21" s="282"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="219" t="s">
@@ -35829,7 +35834,7 @@
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="296" t="s">
+      <c r="I21" s="297" t="s">
         <v>82</v>
       </c>
       <c r="J21" s="209"/>
@@ -35863,7 +35868,7 @@
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="297"/>
+      <c r="I22" s="298"/>
       <c r="J22" s="209"/>
       <c r="K22" s="101" t="s">
         <v>40</v>
@@ -37532,21 +37537,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -37601,13 +37606,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="288" t="s">
+      <c r="D3" s="289" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="281" t="s">
+      <c r="F3" s="282" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -37616,24 +37621,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="288" t="s">
+      <c r="J3" s="289" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="305" t="s">
+      <c r="M3" s="306" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -37647,20 +37652,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="288"/>
+      <c r="D4" s="289"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="281"/>
+      <c r="F4" s="282"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="288"/>
+      <c r="J4" s="289"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="305"/>
+      <c r="M4" s="306"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -37699,7 +37704,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -37707,7 +37712,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -37752,13 +37757,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="284"/>
+      <c r="F6" s="285"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -37802,13 +37807,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="287" t="s">
+      <c r="F7" s="288" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="283" t="s">
+      <c r="J7" s="284" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -37856,11 +37861,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="287"/>
+      <c r="F8" s="288"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="283"/>
+      <c r="J8" s="284"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -37905,7 +37910,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="284" t="s">
+      <c r="F9" s="285" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -37945,7 +37950,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="284"/>
+      <c r="F10" s="285"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -38167,13 +38172,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="288" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="288" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="288" t="s">
+      <c r="C16" s="289" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -38208,9 +38213,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="287"/>
-      <c r="B17" s="287"/>
-      <c r="C17" s="288"/>
+      <c r="A17" s="288"/>
+      <c r="B17" s="288"/>
+      <c r="C17" s="289"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -38420,13 +38425,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -38486,7 +38491,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -38518,7 +38523,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -38546,7 +38551,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -38574,7 +38579,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -38598,7 +38603,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="280" t="s">
+      <c r="E34" s="281" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -38621,7 +38626,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="280"/>
+      <c r="E35" s="281"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -38641,7 +38646,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -38661,7 +38666,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -40126,21 +40131,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="292" t="s">
+      <c r="A1" s="293" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="292"/>
-      <c r="H1" s="292"/>
-      <c r="I1" s="292"/>
-      <c r="J1" s="292"/>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
-      <c r="M1" s="292"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="293"/>
+      <c r="G1" s="293"/>
+      <c r="H1" s="293"/>
+      <c r="I1" s="293"/>
+      <c r="J1" s="293"/>
+      <c r="K1" s="293"/>
+      <c r="L1" s="293"/>
+      <c r="M1" s="293"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -40195,13 +40200,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="288" t="s">
+      <c r="D3" s="289" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="281" t="s">
+      <c r="F3" s="282" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -40210,24 +40215,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="288" t="s">
+      <c r="J3" s="289" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="305" t="s">
+      <c r="M3" s="306" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="285" t="s">
+      <c r="Q3" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="286"/>
+      <c r="R3" s="287"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="278" t="s">
+      <c r="T3" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="279"/>
+      <c r="U3" s="280"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -40241,20 +40246,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="288"/>
+      <c r="D4" s="289"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="281"/>
+      <c r="F4" s="282"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="288"/>
+      <c r="J4" s="289"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="305"/>
+      <c r="M4" s="306"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -40293,7 +40298,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="284" t="s">
+      <c r="F5" s="285" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -40301,7 +40306,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="281" t="s">
+      <c r="J5" s="282" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -40346,13 +40351,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="284"/>
+      <c r="F6" s="285"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="281"/>
+      <c r="J6" s="282"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -40396,13 +40401,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="287" t="s">
+      <c r="F7" s="288" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="283" t="s">
+      <c r="J7" s="284" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -40450,11 +40455,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="287"/>
+      <c r="F8" s="288"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="283"/>
+      <c r="J8" s="284"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -40499,7 +40504,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="284" t="s">
+      <c r="F9" s="285" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -40539,7 +40544,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="284"/>
+      <c r="F10" s="285"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -40761,13 +40766,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="288" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="288" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="288" t="s">
+      <c r="C16" s="289" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -40802,9 +40807,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="287"/>
-      <c r="B17" s="287"/>
-      <c r="C17" s="288"/>
+      <c r="A17" s="288"/>
+      <c r="B17" s="288"/>
+      <c r="C17" s="289"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -41014,13 +41019,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="293" t="s">
+      <c r="A28" s="294" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -41080,7 +41085,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="282" t="s">
+      <c r="E30" s="283" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -41114,7 +41119,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="282"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -41142,7 +41147,7 @@
       <c r="D32" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="282" t="s">
+      <c r="E32" s="283" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -41170,7 +41175,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="282"/>
+      <c r="E33" s="283"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -41194,7 +41199,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="280" t="s">
+      <c r="E34" s="281" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -41219,7 +41224,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="280"/>
+      <c r="E35" s="281"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -41241,7 +41246,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="282" t="s">
+      <c r="E36" s="283" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -41263,7 +41268,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="282"/>
+      <c r="E37" s="283"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>

--- a/raw/D3.xlsx
+++ b/raw/D3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="4" activeTab="14"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="4" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="30-2" sheetId="34" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="19" sheetId="46" r:id="rId13"/>
     <sheet name="20" sheetId="47" r:id="rId14"/>
     <sheet name="20-2" sheetId="48" r:id="rId15"/>
+    <sheet name="21" sheetId="49" r:id="rId16"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -402,6 +403,78 @@
     <author>Автор</author>
   </authors>
   <commentList>
+    <comment ref="J7" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Алібек
+87012894507</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I13" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Аслан
+87014988298</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Даулет
+87025167087</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments16.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="M6" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Сандыбай Берды
+87759316709</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="J7" authorId="0" shapeId="0">
       <text>
         <r>
@@ -1148,7 +1221,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2383" uniqueCount="273">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -1964,6 +2037,9 @@
   </si>
   <si>
     <t>24-Н3598/12 н</t>
+  </si>
+  <si>
+    <t>31-H2994/12</t>
   </si>
 </sst>
 </file>
@@ -2784,7 +2860,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="308">
+  <cellXfs count="316">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3589,6 +3665,30 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4870,21 +4970,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4939,13 +5039,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="282" t="s">
+      <c r="D3" s="290" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="282" t="s">
+      <c r="F3" s="290" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -4957,24 +5057,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="288" t="s">
+      <c r="J3" s="296" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="289" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -4986,20 +5086,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="282"/>
+      <c r="D4" s="290"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="282"/>
+      <c r="F4" s="290"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="288"/>
+      <c r="J4" s="296"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="289"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -5038,7 +5138,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -5046,7 +5146,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -5091,13 +5191,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -5143,13 +5243,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="288" t="s">
+      <c r="F7" s="296" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="284" t="s">
+      <c r="J7" s="292" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -5197,11 +5297,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="288"/>
+      <c r="F8" s="296"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="284"/>
+      <c r="J8" s="292"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -5245,7 +5345,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="285" t="s">
+      <c r="F9" s="293" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -5285,7 +5385,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="285"/>
+      <c r="F10" s="293"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -5410,7 +5510,7 @@
         <v>115</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="289" t="s">
+      <c r="H13" s="297" t="s">
         <v>82</v>
       </c>
       <c r="I13" s="30"/>
@@ -5449,7 +5549,7 @@
       <c r="F14" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="289"/>
+      <c r="H14" s="297"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -5484,7 +5584,7 @@
         <v>83</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="289" t="s">
+      <c r="H15" s="297" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="30"/>
@@ -5521,7 +5621,7 @@
         <v>81</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="289"/>
+      <c r="H16" s="297"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -5553,7 +5653,7 @@
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="290" t="s">
+      <c r="H17" s="298" t="s">
         <v>45</v>
       </c>
       <c r="I17" s="30"/>
@@ -5588,7 +5688,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="291"/>
+      <c r="H18" s="299"/>
       <c r="I18" s="30"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
@@ -5605,7 +5705,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="288" t="s">
+      <c r="H19" s="296" t="s">
         <v>85</v>
       </c>
       <c r="I19" s="30"/>
@@ -5630,7 +5730,7 @@
       <c r="E20" s="137"/>
       <c r="F20" s="8"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="288"/>
+      <c r="H20" s="296"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -5649,7 +5749,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="288" t="s">
+      <c r="H21" s="296" t="s">
         <v>84</v>
       </c>
       <c r="I21" s="30"/>
@@ -5666,7 +5766,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="137"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="288"/>
+      <c r="H22" s="296"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -5763,13 +5863,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -5829,7 +5929,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -5863,7 +5963,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -5893,7 +5993,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="8"/>
@@ -5919,7 +6019,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
       <c r="I33" s="30"/>
@@ -5942,7 +6042,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="281" t="s">
+      <c r="E34" s="289" t="s">
         <v>133</v>
       </c>
       <c r="G34" s="8"/>
@@ -5963,7 +6063,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="281"/>
+      <c r="E35" s="289"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
       <c r="I35" s="30"/>
@@ -5982,7 +6082,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -6002,7 +6102,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -6469,7 +6569,7 @@
       <c r="S65"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A66" s="292" t="s">
+      <c r="A66" s="300" t="s">
         <v>139</v>
       </c>
       <c r="L66" s="119" t="s">
@@ -6481,7 +6581,7 @@
       <c r="S66"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A67" s="292"/>
+      <c r="A67" s="300"/>
       <c r="L67" s="119" t="s">
         <v>95</v>
       </c>
@@ -7472,21 +7572,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -7545,7 +7645,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="282" t="s">
+      <c r="F3" s="290" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -7554,24 +7654,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="284" t="s">
+      <c r="J3" s="292" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="306" t="s">
+      <c r="M3" s="314" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -7589,16 +7689,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="282"/>
+      <c r="F4" s="290"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="284"/>
+      <c r="J4" s="292"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="306"/>
+      <c r="M4" s="314"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -7637,7 +7737,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -7645,7 +7745,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -7690,13 +7790,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -7743,7 +7843,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="285" t="s">
+      <c r="F7" s="293" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -7795,7 +7895,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="285"/>
+      <c r="F8" s="293"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -8011,7 +8111,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="288" t="s">
+      <c r="H13" s="296" t="s">
         <v>121</v>
       </c>
       <c r="I13" s="30"/>
@@ -8047,7 +8147,7 @@
       <c r="F14" s="240" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="288"/>
+      <c r="H14" s="296"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -8080,7 +8180,7 @@
       <c r="E15" s="240"/>
       <c r="F15" s="8"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="288" t="s">
+      <c r="H15" s="296" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="30"/>
@@ -8109,7 +8209,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="8"/>
@@ -8117,7 +8217,7 @@
       <c r="E16" s="59"/>
       <c r="F16" s="8"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="288"/>
+      <c r="H16" s="296"/>
       <c r="I16" s="30"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
@@ -8144,13 +8244,13 @@
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
-      <c r="B17" s="288"/>
+      <c r="B17" s="296"/>
       <c r="C17" s="8"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="289" t="s">
+      <c r="H17" s="297" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -8185,7 +8285,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="289"/>
+      <c r="H18" s="297"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -8202,7 +8302,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="289" t="s">
+      <c r="H19" s="297" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -8227,7 +8327,7 @@
       <c r="E20" s="240"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="289"/>
+      <c r="H20" s="297"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -8246,7 +8346,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="289" t="s">
+      <c r="H21" s="297" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -8264,7 +8364,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="240"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="289"/>
+      <c r="H22" s="297"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -8361,13 +8461,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -8427,7 +8527,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -8461,7 +8561,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -8488,7 +8588,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -8516,7 +8616,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -8540,7 +8640,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="281" t="s">
+      <c r="E34" s="289" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -8565,7 +8665,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="281"/>
+      <c r="E35" s="289"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -8587,7 +8687,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -8609,7 +8709,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -10077,21 +10177,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -10150,7 +10250,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="282" t="s">
+      <c r="F3" s="290" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -10159,24 +10259,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="284" t="s">
+      <c r="J3" s="292" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="289" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -10194,16 +10294,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="282"/>
+      <c r="F4" s="290"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="284"/>
+      <c r="J4" s="292"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="289"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -10242,7 +10342,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -10250,7 +10350,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -10295,13 +10395,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -10348,7 +10448,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="285" t="s">
+      <c r="F7" s="293" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -10400,7 +10500,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="285"/>
+      <c r="F8" s="293"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -10616,7 +10716,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="288" t="s">
+      <c r="H13" s="296" t="s">
         <v>121</v>
       </c>
       <c r="I13" s="30"/>
@@ -10652,7 +10752,7 @@
       <c r="F14" s="248" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="288"/>
+      <c r="H14" s="296"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -10685,7 +10785,7 @@
       <c r="E15" s="248"/>
       <c r="F15" s="8"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="288" t="s">
+      <c r="H15" s="296" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="30"/>
@@ -10714,7 +10814,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="8"/>
@@ -10722,7 +10822,7 @@
       <c r="E16" s="59"/>
       <c r="F16" s="8"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="288"/>
+      <c r="H16" s="296"/>
       <c r="I16" s="30"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
@@ -10749,13 +10849,13 @@
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
-      <c r="B17" s="288"/>
+      <c r="B17" s="296"/>
       <c r="C17" s="8"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="289" t="s">
+      <c r="H17" s="297" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -10790,7 +10890,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="289"/>
+      <c r="H18" s="297"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -10807,7 +10907,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="289" t="s">
+      <c r="H19" s="297" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -10832,7 +10932,7 @@
       <c r="E20" s="248"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="289"/>
+      <c r="H20" s="297"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -10851,7 +10951,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="289" t="s">
+      <c r="H21" s="297" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -10869,7 +10969,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="248"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="289"/>
+      <c r="H22" s="297"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -10966,13 +11066,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -11032,7 +11132,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -11066,7 +11166,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -11096,7 +11196,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -11124,7 +11224,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -11148,7 +11248,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="281" t="s">
+      <c r="E34" s="289" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -11172,7 +11272,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="281"/>
+      <c r="E35" s="289"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -11194,7 +11294,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -11214,7 +11314,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -12682,21 +12782,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -12751,13 +12851,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="289" t="s">
+      <c r="D3" s="297" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="282" t="s">
+      <c r="F3" s="290" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -12766,24 +12866,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="284" t="s">
+      <c r="J3" s="292" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="289" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -12797,20 +12897,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="289"/>
+      <c r="D4" s="297"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="282"/>
+      <c r="F4" s="290"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="284"/>
+      <c r="J4" s="292"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="289"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -12849,7 +12949,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -12857,7 +12957,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -12902,13 +13002,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -12955,13 +13055,13 @@
       <c r="E7" s="260" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="307" t="s">
+      <c r="F7" s="315" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="289" t="s">
+      <c r="J7" s="297" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -13009,11 +13109,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="307"/>
+      <c r="F8" s="315"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="289"/>
+      <c r="J8" s="297"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -13058,7 +13158,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="288" t="s">
+      <c r="F9" s="296" t="s">
         <v>121</v>
       </c>
       <c r="G9" s="64"/>
@@ -13098,7 +13198,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="288"/>
+      <c r="F10" s="296"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -13318,13 +13418,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="296" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="289" t="s">
+      <c r="C16" s="297" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -13359,9 +13459,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="288"/>
-      <c r="B17" s="288"/>
-      <c r="C17" s="289"/>
+      <c r="A17" s="296"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="297"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="259" t="s">
@@ -13572,13 +13672,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -13638,7 +13738,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -13672,7 +13772,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -13702,7 +13802,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -13732,7 +13832,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -13756,7 +13856,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="281" t="s">
+      <c r="E34" s="289" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -13780,7 +13880,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="281"/>
+      <c r="E35" s="289"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -13799,7 +13899,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -13819,7 +13919,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -15285,21 +15385,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -15354,13 +15454,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="282" t="s">
+      <c r="D3" s="290" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="282" t="s">
+      <c r="F3" s="290" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -15369,24 +15469,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="284" t="s">
+      <c r="J3" s="292" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="289" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -15400,20 +15500,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="282"/>
+      <c r="D4" s="290"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="282"/>
+      <c r="F4" s="290"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="284"/>
+      <c r="J4" s="292"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="289"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -15452,7 +15552,7 @@
       <c r="E5" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -15460,7 +15560,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -15505,13 +15605,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -15558,13 +15658,13 @@
       <c r="E7" s="260" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="307" t="s">
+      <c r="F7" s="315" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="289" t="s">
+      <c r="J7" s="297" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -15612,11 +15712,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="307"/>
+      <c r="F8" s="315"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="289"/>
+      <c r="J8" s="297"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -15661,7 +15761,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="288" t="s">
+      <c r="F9" s="296" t="s">
         <v>121</v>
       </c>
       <c r="G9" s="64"/>
@@ -15701,7 +15801,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="288"/>
+      <c r="F10" s="296"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -15828,7 +15928,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="289" t="s">
+      <c r="I13" s="297" t="s">
         <v>45</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -15864,7 +15964,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="289"/>
+      <c r="I14" s="297"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -15924,13 +16024,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="296" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="289" t="s">
+      <c r="C16" s="297" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -15965,9 +16065,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="288"/>
-      <c r="B17" s="288"/>
-      <c r="C17" s="289"/>
+      <c r="A17" s="296"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="297"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="269" t="s">
@@ -16178,13 +16278,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -16244,7 +16344,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -16278,7 +16378,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -16306,7 +16406,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -16334,7 +16434,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -16358,7 +16458,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="281" t="s">
+      <c r="E34" s="289" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -16380,7 +16480,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="281"/>
+      <c r="E35" s="289"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -16400,7 +16500,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -16420,7 +16520,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -17891,21 +17991,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -17960,13 +18060,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="282" t="s">
+      <c r="D3" s="290" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="282" t="s">
+      <c r="F3" s="290" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -17975,24 +18075,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="284" t="s">
+      <c r="J3" s="292" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="289" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -18006,20 +18106,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="282"/>
+      <c r="D4" s="290"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="282"/>
+      <c r="F4" s="290"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="284"/>
+      <c r="J4" s="292"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="289"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -18058,7 +18158,7 @@
       <c r="E5" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -18066,7 +18166,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -18111,13 +18211,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -18164,13 +18264,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="285" t="s">
+      <c r="F7" s="293" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="289" t="s">
+      <c r="J7" s="297" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -18218,11 +18318,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="285"/>
+      <c r="F8" s="293"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="289"/>
+      <c r="J8" s="297"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -18267,7 +18367,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="288" t="s">
+      <c r="F9" s="296" t="s">
         <v>121</v>
       </c>
       <c r="G9" s="64"/>
@@ -18307,7 +18407,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="288"/>
+      <c r="F10" s="296"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -18528,13 +18628,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="296" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="289" t="s">
+      <c r="C16" s="297" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -18569,9 +18669,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="288"/>
-      <c r="B17" s="288"/>
-      <c r="C17" s="289"/>
+      <c r="A17" s="296"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="297"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -18604,7 +18704,7 @@
     <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="289" t="s">
+      <c r="C18" s="297" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="61"/>
@@ -18623,7 +18723,7 @@
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="273"/>
-      <c r="C19" s="289"/>
+      <c r="C19" s="297"/>
       <c r="D19" s="125"/>
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
@@ -18783,13 +18883,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -18849,7 +18949,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -18883,7 +18983,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -18911,7 +19011,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -18939,7 +19039,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -18963,7 +19063,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="281" t="s">
+      <c r="E34" s="289" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -18987,7 +19087,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="281"/>
+      <c r="E35" s="289"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -19007,7 +19107,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -19027,7 +19127,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -19588,6 +19688,2613 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:W72"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" style="98" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" style="25" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" style="25" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" style="25" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" customWidth="1"/>
+    <col min="14" max="14" width="21.26953125" customWidth="1"/>
+    <col min="15" max="15" width="9.7265625" customWidth="1"/>
+    <col min="16" max="16" width="7.7265625" customWidth="1"/>
+    <col min="17" max="17" width="6.453125" customWidth="1"/>
+    <col min="18" max="18" width="7.81640625" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" style="84" customWidth="1"/>
+    <col min="20" max="20" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="257" max="260" width="14.453125" customWidth="1"/>
+    <col min="261" max="261" width="15.453125" customWidth="1"/>
+    <col min="262" max="262" width="14.54296875" customWidth="1"/>
+    <col min="263" max="263" width="15.26953125" customWidth="1"/>
+    <col min="264" max="265" width="14.453125" customWidth="1"/>
+    <col min="266" max="266" width="13.1796875" customWidth="1"/>
+    <col min="267" max="269" width="14.453125" customWidth="1"/>
+    <col min="270" max="270" width="15.81640625" customWidth="1"/>
+    <col min="271" max="271" width="7.81640625" customWidth="1"/>
+    <col min="272" max="272" width="5.453125" customWidth="1"/>
+    <col min="273" max="273" width="6.453125" customWidth="1"/>
+    <col min="274" max="274" width="7.81640625" customWidth="1"/>
+    <col min="275" max="275" width="3" customWidth="1"/>
+    <col min="276" max="276" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="513" max="516" width="14.453125" customWidth="1"/>
+    <col min="517" max="517" width="15.453125" customWidth="1"/>
+    <col min="518" max="518" width="14.54296875" customWidth="1"/>
+    <col min="519" max="519" width="15.26953125" customWidth="1"/>
+    <col min="520" max="521" width="14.453125" customWidth="1"/>
+    <col min="522" max="522" width="13.1796875" customWidth="1"/>
+    <col min="523" max="525" width="14.453125" customWidth="1"/>
+    <col min="526" max="526" width="15.81640625" customWidth="1"/>
+    <col min="527" max="527" width="7.81640625" customWidth="1"/>
+    <col min="528" max="528" width="5.453125" customWidth="1"/>
+    <col min="529" max="529" width="6.453125" customWidth="1"/>
+    <col min="530" max="530" width="7.81640625" customWidth="1"/>
+    <col min="531" max="531" width="3" customWidth="1"/>
+    <col min="532" max="532" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="769" max="772" width="14.453125" customWidth="1"/>
+    <col min="773" max="773" width="15.453125" customWidth="1"/>
+    <col min="774" max="774" width="14.54296875" customWidth="1"/>
+    <col min="775" max="775" width="15.26953125" customWidth="1"/>
+    <col min="776" max="777" width="14.453125" customWidth="1"/>
+    <col min="778" max="778" width="13.1796875" customWidth="1"/>
+    <col min="779" max="781" width="14.453125" customWidth="1"/>
+    <col min="782" max="782" width="15.81640625" customWidth="1"/>
+    <col min="783" max="783" width="7.81640625" customWidth="1"/>
+    <col min="784" max="784" width="5.453125" customWidth="1"/>
+    <col min="785" max="785" width="6.453125" customWidth="1"/>
+    <col min="786" max="786" width="7.81640625" customWidth="1"/>
+    <col min="787" max="787" width="3" customWidth="1"/>
+    <col min="788" max="788" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1025" max="1028" width="14.453125" customWidth="1"/>
+    <col min="1029" max="1029" width="15.453125" customWidth="1"/>
+    <col min="1030" max="1030" width="14.54296875" customWidth="1"/>
+    <col min="1031" max="1031" width="15.26953125" customWidth="1"/>
+    <col min="1032" max="1033" width="14.453125" customWidth="1"/>
+    <col min="1034" max="1034" width="13.1796875" customWidth="1"/>
+    <col min="1035" max="1037" width="14.453125" customWidth="1"/>
+    <col min="1038" max="1038" width="15.81640625" customWidth="1"/>
+    <col min="1039" max="1039" width="7.81640625" customWidth="1"/>
+    <col min="1040" max="1040" width="5.453125" customWidth="1"/>
+    <col min="1041" max="1041" width="6.453125" customWidth="1"/>
+    <col min="1042" max="1042" width="7.81640625" customWidth="1"/>
+    <col min="1043" max="1043" width="3" customWidth="1"/>
+    <col min="1044" max="1044" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1281" max="1284" width="14.453125" customWidth="1"/>
+    <col min="1285" max="1285" width="15.453125" customWidth="1"/>
+    <col min="1286" max="1286" width="14.54296875" customWidth="1"/>
+    <col min="1287" max="1287" width="15.26953125" customWidth="1"/>
+    <col min="1288" max="1289" width="14.453125" customWidth="1"/>
+    <col min="1290" max="1290" width="13.1796875" customWidth="1"/>
+    <col min="1291" max="1293" width="14.453125" customWidth="1"/>
+    <col min="1294" max="1294" width="15.81640625" customWidth="1"/>
+    <col min="1295" max="1295" width="7.81640625" customWidth="1"/>
+    <col min="1296" max="1296" width="5.453125" customWidth="1"/>
+    <col min="1297" max="1297" width="6.453125" customWidth="1"/>
+    <col min="1298" max="1298" width="7.81640625" customWidth="1"/>
+    <col min="1299" max="1299" width="3" customWidth="1"/>
+    <col min="1300" max="1300" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1537" max="1540" width="14.453125" customWidth="1"/>
+    <col min="1541" max="1541" width="15.453125" customWidth="1"/>
+    <col min="1542" max="1542" width="14.54296875" customWidth="1"/>
+    <col min="1543" max="1543" width="15.26953125" customWidth="1"/>
+    <col min="1544" max="1545" width="14.453125" customWidth="1"/>
+    <col min="1546" max="1546" width="13.1796875" customWidth="1"/>
+    <col min="1547" max="1549" width="14.453125" customWidth="1"/>
+    <col min="1550" max="1550" width="15.81640625" customWidth="1"/>
+    <col min="1551" max="1551" width="7.81640625" customWidth="1"/>
+    <col min="1552" max="1552" width="5.453125" customWidth="1"/>
+    <col min="1553" max="1553" width="6.453125" customWidth="1"/>
+    <col min="1554" max="1554" width="7.81640625" customWidth="1"/>
+    <col min="1555" max="1555" width="3" customWidth="1"/>
+    <col min="1556" max="1556" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1793" max="1796" width="14.453125" customWidth="1"/>
+    <col min="1797" max="1797" width="15.453125" customWidth="1"/>
+    <col min="1798" max="1798" width="14.54296875" customWidth="1"/>
+    <col min="1799" max="1799" width="15.26953125" customWidth="1"/>
+    <col min="1800" max="1801" width="14.453125" customWidth="1"/>
+    <col min="1802" max="1802" width="13.1796875" customWidth="1"/>
+    <col min="1803" max="1805" width="14.453125" customWidth="1"/>
+    <col min="1806" max="1806" width="15.81640625" customWidth="1"/>
+    <col min="1807" max="1807" width="7.81640625" customWidth="1"/>
+    <col min="1808" max="1808" width="5.453125" customWidth="1"/>
+    <col min="1809" max="1809" width="6.453125" customWidth="1"/>
+    <col min="1810" max="1810" width="7.81640625" customWidth="1"/>
+    <col min="1811" max="1811" width="3" customWidth="1"/>
+    <col min="1812" max="1812" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2049" max="2052" width="14.453125" customWidth="1"/>
+    <col min="2053" max="2053" width="15.453125" customWidth="1"/>
+    <col min="2054" max="2054" width="14.54296875" customWidth="1"/>
+    <col min="2055" max="2055" width="15.26953125" customWidth="1"/>
+    <col min="2056" max="2057" width="14.453125" customWidth="1"/>
+    <col min="2058" max="2058" width="13.1796875" customWidth="1"/>
+    <col min="2059" max="2061" width="14.453125" customWidth="1"/>
+    <col min="2062" max="2062" width="15.81640625" customWidth="1"/>
+    <col min="2063" max="2063" width="7.81640625" customWidth="1"/>
+    <col min="2064" max="2064" width="5.453125" customWidth="1"/>
+    <col min="2065" max="2065" width="6.453125" customWidth="1"/>
+    <col min="2066" max="2066" width="7.81640625" customWidth="1"/>
+    <col min="2067" max="2067" width="3" customWidth="1"/>
+    <col min="2068" max="2068" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2305" max="2308" width="14.453125" customWidth="1"/>
+    <col min="2309" max="2309" width="15.453125" customWidth="1"/>
+    <col min="2310" max="2310" width="14.54296875" customWidth="1"/>
+    <col min="2311" max="2311" width="15.26953125" customWidth="1"/>
+    <col min="2312" max="2313" width="14.453125" customWidth="1"/>
+    <col min="2314" max="2314" width="13.1796875" customWidth="1"/>
+    <col min="2315" max="2317" width="14.453125" customWidth="1"/>
+    <col min="2318" max="2318" width="15.81640625" customWidth="1"/>
+    <col min="2319" max="2319" width="7.81640625" customWidth="1"/>
+    <col min="2320" max="2320" width="5.453125" customWidth="1"/>
+    <col min="2321" max="2321" width="6.453125" customWidth="1"/>
+    <col min="2322" max="2322" width="7.81640625" customWidth="1"/>
+    <col min="2323" max="2323" width="3" customWidth="1"/>
+    <col min="2324" max="2324" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2561" max="2564" width="14.453125" customWidth="1"/>
+    <col min="2565" max="2565" width="15.453125" customWidth="1"/>
+    <col min="2566" max="2566" width="14.54296875" customWidth="1"/>
+    <col min="2567" max="2567" width="15.26953125" customWidth="1"/>
+    <col min="2568" max="2569" width="14.453125" customWidth="1"/>
+    <col min="2570" max="2570" width="13.1796875" customWidth="1"/>
+    <col min="2571" max="2573" width="14.453125" customWidth="1"/>
+    <col min="2574" max="2574" width="15.81640625" customWidth="1"/>
+    <col min="2575" max="2575" width="7.81640625" customWidth="1"/>
+    <col min="2576" max="2576" width="5.453125" customWidth="1"/>
+    <col min="2577" max="2577" width="6.453125" customWidth="1"/>
+    <col min="2578" max="2578" width="7.81640625" customWidth="1"/>
+    <col min="2579" max="2579" width="3" customWidth="1"/>
+    <col min="2580" max="2580" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2817" max="2820" width="14.453125" customWidth="1"/>
+    <col min="2821" max="2821" width="15.453125" customWidth="1"/>
+    <col min="2822" max="2822" width="14.54296875" customWidth="1"/>
+    <col min="2823" max="2823" width="15.26953125" customWidth="1"/>
+    <col min="2824" max="2825" width="14.453125" customWidth="1"/>
+    <col min="2826" max="2826" width="13.1796875" customWidth="1"/>
+    <col min="2827" max="2829" width="14.453125" customWidth="1"/>
+    <col min="2830" max="2830" width="15.81640625" customWidth="1"/>
+    <col min="2831" max="2831" width="7.81640625" customWidth="1"/>
+    <col min="2832" max="2832" width="5.453125" customWidth="1"/>
+    <col min="2833" max="2833" width="6.453125" customWidth="1"/>
+    <col min="2834" max="2834" width="7.81640625" customWidth="1"/>
+    <col min="2835" max="2835" width="3" customWidth="1"/>
+    <col min="2836" max="2836" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3073" max="3076" width="14.453125" customWidth="1"/>
+    <col min="3077" max="3077" width="15.453125" customWidth="1"/>
+    <col min="3078" max="3078" width="14.54296875" customWidth="1"/>
+    <col min="3079" max="3079" width="15.26953125" customWidth="1"/>
+    <col min="3080" max="3081" width="14.453125" customWidth="1"/>
+    <col min="3082" max="3082" width="13.1796875" customWidth="1"/>
+    <col min="3083" max="3085" width="14.453125" customWidth="1"/>
+    <col min="3086" max="3086" width="15.81640625" customWidth="1"/>
+    <col min="3087" max="3087" width="7.81640625" customWidth="1"/>
+    <col min="3088" max="3088" width="5.453125" customWidth="1"/>
+    <col min="3089" max="3089" width="6.453125" customWidth="1"/>
+    <col min="3090" max="3090" width="7.81640625" customWidth="1"/>
+    <col min="3091" max="3091" width="3" customWidth="1"/>
+    <col min="3092" max="3092" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3329" max="3332" width="14.453125" customWidth="1"/>
+    <col min="3333" max="3333" width="15.453125" customWidth="1"/>
+    <col min="3334" max="3334" width="14.54296875" customWidth="1"/>
+    <col min="3335" max="3335" width="15.26953125" customWidth="1"/>
+    <col min="3336" max="3337" width="14.453125" customWidth="1"/>
+    <col min="3338" max="3338" width="13.1796875" customWidth="1"/>
+    <col min="3339" max="3341" width="14.453125" customWidth="1"/>
+    <col min="3342" max="3342" width="15.81640625" customWidth="1"/>
+    <col min="3343" max="3343" width="7.81640625" customWidth="1"/>
+    <col min="3344" max="3344" width="5.453125" customWidth="1"/>
+    <col min="3345" max="3345" width="6.453125" customWidth="1"/>
+    <col min="3346" max="3346" width="7.81640625" customWidth="1"/>
+    <col min="3347" max="3347" width="3" customWidth="1"/>
+    <col min="3348" max="3348" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3585" max="3588" width="14.453125" customWidth="1"/>
+    <col min="3589" max="3589" width="15.453125" customWidth="1"/>
+    <col min="3590" max="3590" width="14.54296875" customWidth="1"/>
+    <col min="3591" max="3591" width="15.26953125" customWidth="1"/>
+    <col min="3592" max="3593" width="14.453125" customWidth="1"/>
+    <col min="3594" max="3594" width="13.1796875" customWidth="1"/>
+    <col min="3595" max="3597" width="14.453125" customWidth="1"/>
+    <col min="3598" max="3598" width="15.81640625" customWidth="1"/>
+    <col min="3599" max="3599" width="7.81640625" customWidth="1"/>
+    <col min="3600" max="3600" width="5.453125" customWidth="1"/>
+    <col min="3601" max="3601" width="6.453125" customWidth="1"/>
+    <col min="3602" max="3602" width="7.81640625" customWidth="1"/>
+    <col min="3603" max="3603" width="3" customWidth="1"/>
+    <col min="3604" max="3604" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3841" max="3844" width="14.453125" customWidth="1"/>
+    <col min="3845" max="3845" width="15.453125" customWidth="1"/>
+    <col min="3846" max="3846" width="14.54296875" customWidth="1"/>
+    <col min="3847" max="3847" width="15.26953125" customWidth="1"/>
+    <col min="3848" max="3849" width="14.453125" customWidth="1"/>
+    <col min="3850" max="3850" width="13.1796875" customWidth="1"/>
+    <col min="3851" max="3853" width="14.453125" customWidth="1"/>
+    <col min="3854" max="3854" width="15.81640625" customWidth="1"/>
+    <col min="3855" max="3855" width="7.81640625" customWidth="1"/>
+    <col min="3856" max="3856" width="5.453125" customWidth="1"/>
+    <col min="3857" max="3857" width="6.453125" customWidth="1"/>
+    <col min="3858" max="3858" width="7.81640625" customWidth="1"/>
+    <col min="3859" max="3859" width="3" customWidth="1"/>
+    <col min="3860" max="3860" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4097" max="4100" width="14.453125" customWidth="1"/>
+    <col min="4101" max="4101" width="15.453125" customWidth="1"/>
+    <col min="4102" max="4102" width="14.54296875" customWidth="1"/>
+    <col min="4103" max="4103" width="15.26953125" customWidth="1"/>
+    <col min="4104" max="4105" width="14.453125" customWidth="1"/>
+    <col min="4106" max="4106" width="13.1796875" customWidth="1"/>
+    <col min="4107" max="4109" width="14.453125" customWidth="1"/>
+    <col min="4110" max="4110" width="15.81640625" customWidth="1"/>
+    <col min="4111" max="4111" width="7.81640625" customWidth="1"/>
+    <col min="4112" max="4112" width="5.453125" customWidth="1"/>
+    <col min="4113" max="4113" width="6.453125" customWidth="1"/>
+    <col min="4114" max="4114" width="7.81640625" customWidth="1"/>
+    <col min="4115" max="4115" width="3" customWidth="1"/>
+    <col min="4116" max="4116" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4353" max="4356" width="14.453125" customWidth="1"/>
+    <col min="4357" max="4357" width="15.453125" customWidth="1"/>
+    <col min="4358" max="4358" width="14.54296875" customWidth="1"/>
+    <col min="4359" max="4359" width="15.26953125" customWidth="1"/>
+    <col min="4360" max="4361" width="14.453125" customWidth="1"/>
+    <col min="4362" max="4362" width="13.1796875" customWidth="1"/>
+    <col min="4363" max="4365" width="14.453125" customWidth="1"/>
+    <col min="4366" max="4366" width="15.81640625" customWidth="1"/>
+    <col min="4367" max="4367" width="7.81640625" customWidth="1"/>
+    <col min="4368" max="4368" width="5.453125" customWidth="1"/>
+    <col min="4369" max="4369" width="6.453125" customWidth="1"/>
+    <col min="4370" max="4370" width="7.81640625" customWidth="1"/>
+    <col min="4371" max="4371" width="3" customWidth="1"/>
+    <col min="4372" max="4372" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4609" max="4612" width="14.453125" customWidth="1"/>
+    <col min="4613" max="4613" width="15.453125" customWidth="1"/>
+    <col min="4614" max="4614" width="14.54296875" customWidth="1"/>
+    <col min="4615" max="4615" width="15.26953125" customWidth="1"/>
+    <col min="4616" max="4617" width="14.453125" customWidth="1"/>
+    <col min="4618" max="4618" width="13.1796875" customWidth="1"/>
+    <col min="4619" max="4621" width="14.453125" customWidth="1"/>
+    <col min="4622" max="4622" width="15.81640625" customWidth="1"/>
+    <col min="4623" max="4623" width="7.81640625" customWidth="1"/>
+    <col min="4624" max="4624" width="5.453125" customWidth="1"/>
+    <col min="4625" max="4625" width="6.453125" customWidth="1"/>
+    <col min="4626" max="4626" width="7.81640625" customWidth="1"/>
+    <col min="4627" max="4627" width="3" customWidth="1"/>
+    <col min="4628" max="4628" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4865" max="4868" width="14.453125" customWidth="1"/>
+    <col min="4869" max="4869" width="15.453125" customWidth="1"/>
+    <col min="4870" max="4870" width="14.54296875" customWidth="1"/>
+    <col min="4871" max="4871" width="15.26953125" customWidth="1"/>
+    <col min="4872" max="4873" width="14.453125" customWidth="1"/>
+    <col min="4874" max="4874" width="13.1796875" customWidth="1"/>
+    <col min="4875" max="4877" width="14.453125" customWidth="1"/>
+    <col min="4878" max="4878" width="15.81640625" customWidth="1"/>
+    <col min="4879" max="4879" width="7.81640625" customWidth="1"/>
+    <col min="4880" max="4880" width="5.453125" customWidth="1"/>
+    <col min="4881" max="4881" width="6.453125" customWidth="1"/>
+    <col min="4882" max="4882" width="7.81640625" customWidth="1"/>
+    <col min="4883" max="4883" width="3" customWidth="1"/>
+    <col min="4884" max="4884" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5121" max="5124" width="14.453125" customWidth="1"/>
+    <col min="5125" max="5125" width="15.453125" customWidth="1"/>
+    <col min="5126" max="5126" width="14.54296875" customWidth="1"/>
+    <col min="5127" max="5127" width="15.26953125" customWidth="1"/>
+    <col min="5128" max="5129" width="14.453125" customWidth="1"/>
+    <col min="5130" max="5130" width="13.1796875" customWidth="1"/>
+    <col min="5131" max="5133" width="14.453125" customWidth="1"/>
+    <col min="5134" max="5134" width="15.81640625" customWidth="1"/>
+    <col min="5135" max="5135" width="7.81640625" customWidth="1"/>
+    <col min="5136" max="5136" width="5.453125" customWidth="1"/>
+    <col min="5137" max="5137" width="6.453125" customWidth="1"/>
+    <col min="5138" max="5138" width="7.81640625" customWidth="1"/>
+    <col min="5139" max="5139" width="3" customWidth="1"/>
+    <col min="5140" max="5140" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5377" max="5380" width="14.453125" customWidth="1"/>
+    <col min="5381" max="5381" width="15.453125" customWidth="1"/>
+    <col min="5382" max="5382" width="14.54296875" customWidth="1"/>
+    <col min="5383" max="5383" width="15.26953125" customWidth="1"/>
+    <col min="5384" max="5385" width="14.453125" customWidth="1"/>
+    <col min="5386" max="5386" width="13.1796875" customWidth="1"/>
+    <col min="5387" max="5389" width="14.453125" customWidth="1"/>
+    <col min="5390" max="5390" width="15.81640625" customWidth="1"/>
+    <col min="5391" max="5391" width="7.81640625" customWidth="1"/>
+    <col min="5392" max="5392" width="5.453125" customWidth="1"/>
+    <col min="5393" max="5393" width="6.453125" customWidth="1"/>
+    <col min="5394" max="5394" width="7.81640625" customWidth="1"/>
+    <col min="5395" max="5395" width="3" customWidth="1"/>
+    <col min="5396" max="5396" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5633" max="5636" width="14.453125" customWidth="1"/>
+    <col min="5637" max="5637" width="15.453125" customWidth="1"/>
+    <col min="5638" max="5638" width="14.54296875" customWidth="1"/>
+    <col min="5639" max="5639" width="15.26953125" customWidth="1"/>
+    <col min="5640" max="5641" width="14.453125" customWidth="1"/>
+    <col min="5642" max="5642" width="13.1796875" customWidth="1"/>
+    <col min="5643" max="5645" width="14.453125" customWidth="1"/>
+    <col min="5646" max="5646" width="15.81640625" customWidth="1"/>
+    <col min="5647" max="5647" width="7.81640625" customWidth="1"/>
+    <col min="5648" max="5648" width="5.453125" customWidth="1"/>
+    <col min="5649" max="5649" width="6.453125" customWidth="1"/>
+    <col min="5650" max="5650" width="7.81640625" customWidth="1"/>
+    <col min="5651" max="5651" width="3" customWidth="1"/>
+    <col min="5652" max="5652" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5889" max="5892" width="14.453125" customWidth="1"/>
+    <col min="5893" max="5893" width="15.453125" customWidth="1"/>
+    <col min="5894" max="5894" width="14.54296875" customWidth="1"/>
+    <col min="5895" max="5895" width="15.26953125" customWidth="1"/>
+    <col min="5896" max="5897" width="14.453125" customWidth="1"/>
+    <col min="5898" max="5898" width="13.1796875" customWidth="1"/>
+    <col min="5899" max="5901" width="14.453125" customWidth="1"/>
+    <col min="5902" max="5902" width="15.81640625" customWidth="1"/>
+    <col min="5903" max="5903" width="7.81640625" customWidth="1"/>
+    <col min="5904" max="5904" width="5.453125" customWidth="1"/>
+    <col min="5905" max="5905" width="6.453125" customWidth="1"/>
+    <col min="5906" max="5906" width="7.81640625" customWidth="1"/>
+    <col min="5907" max="5907" width="3" customWidth="1"/>
+    <col min="5908" max="5908" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6145" max="6148" width="14.453125" customWidth="1"/>
+    <col min="6149" max="6149" width="15.453125" customWidth="1"/>
+    <col min="6150" max="6150" width="14.54296875" customWidth="1"/>
+    <col min="6151" max="6151" width="15.26953125" customWidth="1"/>
+    <col min="6152" max="6153" width="14.453125" customWidth="1"/>
+    <col min="6154" max="6154" width="13.1796875" customWidth="1"/>
+    <col min="6155" max="6157" width="14.453125" customWidth="1"/>
+    <col min="6158" max="6158" width="15.81640625" customWidth="1"/>
+    <col min="6159" max="6159" width="7.81640625" customWidth="1"/>
+    <col min="6160" max="6160" width="5.453125" customWidth="1"/>
+    <col min="6161" max="6161" width="6.453125" customWidth="1"/>
+    <col min="6162" max="6162" width="7.81640625" customWidth="1"/>
+    <col min="6163" max="6163" width="3" customWidth="1"/>
+    <col min="6164" max="6164" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6401" max="6404" width="14.453125" customWidth="1"/>
+    <col min="6405" max="6405" width="15.453125" customWidth="1"/>
+    <col min="6406" max="6406" width="14.54296875" customWidth="1"/>
+    <col min="6407" max="6407" width="15.26953125" customWidth="1"/>
+    <col min="6408" max="6409" width="14.453125" customWidth="1"/>
+    <col min="6410" max="6410" width="13.1796875" customWidth="1"/>
+    <col min="6411" max="6413" width="14.453125" customWidth="1"/>
+    <col min="6414" max="6414" width="15.81640625" customWidth="1"/>
+    <col min="6415" max="6415" width="7.81640625" customWidth="1"/>
+    <col min="6416" max="6416" width="5.453125" customWidth="1"/>
+    <col min="6417" max="6417" width="6.453125" customWidth="1"/>
+    <col min="6418" max="6418" width="7.81640625" customWidth="1"/>
+    <col min="6419" max="6419" width="3" customWidth="1"/>
+    <col min="6420" max="6420" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6657" max="6660" width="14.453125" customWidth="1"/>
+    <col min="6661" max="6661" width="15.453125" customWidth="1"/>
+    <col min="6662" max="6662" width="14.54296875" customWidth="1"/>
+    <col min="6663" max="6663" width="15.26953125" customWidth="1"/>
+    <col min="6664" max="6665" width="14.453125" customWidth="1"/>
+    <col min="6666" max="6666" width="13.1796875" customWidth="1"/>
+    <col min="6667" max="6669" width="14.453125" customWidth="1"/>
+    <col min="6670" max="6670" width="15.81640625" customWidth="1"/>
+    <col min="6671" max="6671" width="7.81640625" customWidth="1"/>
+    <col min="6672" max="6672" width="5.453125" customWidth="1"/>
+    <col min="6673" max="6673" width="6.453125" customWidth="1"/>
+    <col min="6674" max="6674" width="7.81640625" customWidth="1"/>
+    <col min="6675" max="6675" width="3" customWidth="1"/>
+    <col min="6676" max="6676" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6913" max="6916" width="14.453125" customWidth="1"/>
+    <col min="6917" max="6917" width="15.453125" customWidth="1"/>
+    <col min="6918" max="6918" width="14.54296875" customWidth="1"/>
+    <col min="6919" max="6919" width="15.26953125" customWidth="1"/>
+    <col min="6920" max="6921" width="14.453125" customWidth="1"/>
+    <col min="6922" max="6922" width="13.1796875" customWidth="1"/>
+    <col min="6923" max="6925" width="14.453125" customWidth="1"/>
+    <col min="6926" max="6926" width="15.81640625" customWidth="1"/>
+    <col min="6927" max="6927" width="7.81640625" customWidth="1"/>
+    <col min="6928" max="6928" width="5.453125" customWidth="1"/>
+    <col min="6929" max="6929" width="6.453125" customWidth="1"/>
+    <col min="6930" max="6930" width="7.81640625" customWidth="1"/>
+    <col min="6931" max="6931" width="3" customWidth="1"/>
+    <col min="6932" max="6932" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7169" max="7172" width="14.453125" customWidth="1"/>
+    <col min="7173" max="7173" width="15.453125" customWidth="1"/>
+    <col min="7174" max="7174" width="14.54296875" customWidth="1"/>
+    <col min="7175" max="7175" width="15.26953125" customWidth="1"/>
+    <col min="7176" max="7177" width="14.453125" customWidth="1"/>
+    <col min="7178" max="7178" width="13.1796875" customWidth="1"/>
+    <col min="7179" max="7181" width="14.453125" customWidth="1"/>
+    <col min="7182" max="7182" width="15.81640625" customWidth="1"/>
+    <col min="7183" max="7183" width="7.81640625" customWidth="1"/>
+    <col min="7184" max="7184" width="5.453125" customWidth="1"/>
+    <col min="7185" max="7185" width="6.453125" customWidth="1"/>
+    <col min="7186" max="7186" width="7.81640625" customWidth="1"/>
+    <col min="7187" max="7187" width="3" customWidth="1"/>
+    <col min="7188" max="7188" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7425" max="7428" width="14.453125" customWidth="1"/>
+    <col min="7429" max="7429" width="15.453125" customWidth="1"/>
+    <col min="7430" max="7430" width="14.54296875" customWidth="1"/>
+    <col min="7431" max="7431" width="15.26953125" customWidth="1"/>
+    <col min="7432" max="7433" width="14.453125" customWidth="1"/>
+    <col min="7434" max="7434" width="13.1796875" customWidth="1"/>
+    <col min="7435" max="7437" width="14.453125" customWidth="1"/>
+    <col min="7438" max="7438" width="15.81640625" customWidth="1"/>
+    <col min="7439" max="7439" width="7.81640625" customWidth="1"/>
+    <col min="7440" max="7440" width="5.453125" customWidth="1"/>
+    <col min="7441" max="7441" width="6.453125" customWidth="1"/>
+    <col min="7442" max="7442" width="7.81640625" customWidth="1"/>
+    <col min="7443" max="7443" width="3" customWidth="1"/>
+    <col min="7444" max="7444" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7681" max="7684" width="14.453125" customWidth="1"/>
+    <col min="7685" max="7685" width="15.453125" customWidth="1"/>
+    <col min="7686" max="7686" width="14.54296875" customWidth="1"/>
+    <col min="7687" max="7687" width="15.26953125" customWidth="1"/>
+    <col min="7688" max="7689" width="14.453125" customWidth="1"/>
+    <col min="7690" max="7690" width="13.1796875" customWidth="1"/>
+    <col min="7691" max="7693" width="14.453125" customWidth="1"/>
+    <col min="7694" max="7694" width="15.81640625" customWidth="1"/>
+    <col min="7695" max="7695" width="7.81640625" customWidth="1"/>
+    <col min="7696" max="7696" width="5.453125" customWidth="1"/>
+    <col min="7697" max="7697" width="6.453125" customWidth="1"/>
+    <col min="7698" max="7698" width="7.81640625" customWidth="1"/>
+    <col min="7699" max="7699" width="3" customWidth="1"/>
+    <col min="7700" max="7700" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7937" max="7940" width="14.453125" customWidth="1"/>
+    <col min="7941" max="7941" width="15.453125" customWidth="1"/>
+    <col min="7942" max="7942" width="14.54296875" customWidth="1"/>
+    <col min="7943" max="7943" width="15.26953125" customWidth="1"/>
+    <col min="7944" max="7945" width="14.453125" customWidth="1"/>
+    <col min="7946" max="7946" width="13.1796875" customWidth="1"/>
+    <col min="7947" max="7949" width="14.453125" customWidth="1"/>
+    <col min="7950" max="7950" width="15.81640625" customWidth="1"/>
+    <col min="7951" max="7951" width="7.81640625" customWidth="1"/>
+    <col min="7952" max="7952" width="5.453125" customWidth="1"/>
+    <col min="7953" max="7953" width="6.453125" customWidth="1"/>
+    <col min="7954" max="7954" width="7.81640625" customWidth="1"/>
+    <col min="7955" max="7955" width="3" customWidth="1"/>
+    <col min="7956" max="7956" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8193" max="8196" width="14.453125" customWidth="1"/>
+    <col min="8197" max="8197" width="15.453125" customWidth="1"/>
+    <col min="8198" max="8198" width="14.54296875" customWidth="1"/>
+    <col min="8199" max="8199" width="15.26953125" customWidth="1"/>
+    <col min="8200" max="8201" width="14.453125" customWidth="1"/>
+    <col min="8202" max="8202" width="13.1796875" customWidth="1"/>
+    <col min="8203" max="8205" width="14.453125" customWidth="1"/>
+    <col min="8206" max="8206" width="15.81640625" customWidth="1"/>
+    <col min="8207" max="8207" width="7.81640625" customWidth="1"/>
+    <col min="8208" max="8208" width="5.453125" customWidth="1"/>
+    <col min="8209" max="8209" width="6.453125" customWidth="1"/>
+    <col min="8210" max="8210" width="7.81640625" customWidth="1"/>
+    <col min="8211" max="8211" width="3" customWidth="1"/>
+    <col min="8212" max="8212" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8449" max="8452" width="14.453125" customWidth="1"/>
+    <col min="8453" max="8453" width="15.453125" customWidth="1"/>
+    <col min="8454" max="8454" width="14.54296875" customWidth="1"/>
+    <col min="8455" max="8455" width="15.26953125" customWidth="1"/>
+    <col min="8456" max="8457" width="14.453125" customWidth="1"/>
+    <col min="8458" max="8458" width="13.1796875" customWidth="1"/>
+    <col min="8459" max="8461" width="14.453125" customWidth="1"/>
+    <col min="8462" max="8462" width="15.81640625" customWidth="1"/>
+    <col min="8463" max="8463" width="7.81640625" customWidth="1"/>
+    <col min="8464" max="8464" width="5.453125" customWidth="1"/>
+    <col min="8465" max="8465" width="6.453125" customWidth="1"/>
+    <col min="8466" max="8466" width="7.81640625" customWidth="1"/>
+    <col min="8467" max="8467" width="3" customWidth="1"/>
+    <col min="8468" max="8468" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8705" max="8708" width="14.453125" customWidth="1"/>
+    <col min="8709" max="8709" width="15.453125" customWidth="1"/>
+    <col min="8710" max="8710" width="14.54296875" customWidth="1"/>
+    <col min="8711" max="8711" width="15.26953125" customWidth="1"/>
+    <col min="8712" max="8713" width="14.453125" customWidth="1"/>
+    <col min="8714" max="8714" width="13.1796875" customWidth="1"/>
+    <col min="8715" max="8717" width="14.453125" customWidth="1"/>
+    <col min="8718" max="8718" width="15.81640625" customWidth="1"/>
+    <col min="8719" max="8719" width="7.81640625" customWidth="1"/>
+    <col min="8720" max="8720" width="5.453125" customWidth="1"/>
+    <col min="8721" max="8721" width="6.453125" customWidth="1"/>
+    <col min="8722" max="8722" width="7.81640625" customWidth="1"/>
+    <col min="8723" max="8723" width="3" customWidth="1"/>
+    <col min="8724" max="8724" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8961" max="8964" width="14.453125" customWidth="1"/>
+    <col min="8965" max="8965" width="15.453125" customWidth="1"/>
+    <col min="8966" max="8966" width="14.54296875" customWidth="1"/>
+    <col min="8967" max="8967" width="15.26953125" customWidth="1"/>
+    <col min="8968" max="8969" width="14.453125" customWidth="1"/>
+    <col min="8970" max="8970" width="13.1796875" customWidth="1"/>
+    <col min="8971" max="8973" width="14.453125" customWidth="1"/>
+    <col min="8974" max="8974" width="15.81640625" customWidth="1"/>
+    <col min="8975" max="8975" width="7.81640625" customWidth="1"/>
+    <col min="8976" max="8976" width="5.453125" customWidth="1"/>
+    <col min="8977" max="8977" width="6.453125" customWidth="1"/>
+    <col min="8978" max="8978" width="7.81640625" customWidth="1"/>
+    <col min="8979" max="8979" width="3" customWidth="1"/>
+    <col min="8980" max="8980" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9217" max="9220" width="14.453125" customWidth="1"/>
+    <col min="9221" max="9221" width="15.453125" customWidth="1"/>
+    <col min="9222" max="9222" width="14.54296875" customWidth="1"/>
+    <col min="9223" max="9223" width="15.26953125" customWidth="1"/>
+    <col min="9224" max="9225" width="14.453125" customWidth="1"/>
+    <col min="9226" max="9226" width="13.1796875" customWidth="1"/>
+    <col min="9227" max="9229" width="14.453125" customWidth="1"/>
+    <col min="9230" max="9230" width="15.81640625" customWidth="1"/>
+    <col min="9231" max="9231" width="7.81640625" customWidth="1"/>
+    <col min="9232" max="9232" width="5.453125" customWidth="1"/>
+    <col min="9233" max="9233" width="6.453125" customWidth="1"/>
+    <col min="9234" max="9234" width="7.81640625" customWidth="1"/>
+    <col min="9235" max="9235" width="3" customWidth="1"/>
+    <col min="9236" max="9236" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9473" max="9476" width="14.453125" customWidth="1"/>
+    <col min="9477" max="9477" width="15.453125" customWidth="1"/>
+    <col min="9478" max="9478" width="14.54296875" customWidth="1"/>
+    <col min="9479" max="9479" width="15.26953125" customWidth="1"/>
+    <col min="9480" max="9481" width="14.453125" customWidth="1"/>
+    <col min="9482" max="9482" width="13.1796875" customWidth="1"/>
+    <col min="9483" max="9485" width="14.453125" customWidth="1"/>
+    <col min="9486" max="9486" width="15.81640625" customWidth="1"/>
+    <col min="9487" max="9487" width="7.81640625" customWidth="1"/>
+    <col min="9488" max="9488" width="5.453125" customWidth="1"/>
+    <col min="9489" max="9489" width="6.453125" customWidth="1"/>
+    <col min="9490" max="9490" width="7.81640625" customWidth="1"/>
+    <col min="9491" max="9491" width="3" customWidth="1"/>
+    <col min="9492" max="9492" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9729" max="9732" width="14.453125" customWidth="1"/>
+    <col min="9733" max="9733" width="15.453125" customWidth="1"/>
+    <col min="9734" max="9734" width="14.54296875" customWidth="1"/>
+    <col min="9735" max="9735" width="15.26953125" customWidth="1"/>
+    <col min="9736" max="9737" width="14.453125" customWidth="1"/>
+    <col min="9738" max="9738" width="13.1796875" customWidth="1"/>
+    <col min="9739" max="9741" width="14.453125" customWidth="1"/>
+    <col min="9742" max="9742" width="15.81640625" customWidth="1"/>
+    <col min="9743" max="9743" width="7.81640625" customWidth="1"/>
+    <col min="9744" max="9744" width="5.453125" customWidth="1"/>
+    <col min="9745" max="9745" width="6.453125" customWidth="1"/>
+    <col min="9746" max="9746" width="7.81640625" customWidth="1"/>
+    <col min="9747" max="9747" width="3" customWidth="1"/>
+    <col min="9748" max="9748" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9985" max="9988" width="14.453125" customWidth="1"/>
+    <col min="9989" max="9989" width="15.453125" customWidth="1"/>
+    <col min="9990" max="9990" width="14.54296875" customWidth="1"/>
+    <col min="9991" max="9991" width="15.26953125" customWidth="1"/>
+    <col min="9992" max="9993" width="14.453125" customWidth="1"/>
+    <col min="9994" max="9994" width="13.1796875" customWidth="1"/>
+    <col min="9995" max="9997" width="14.453125" customWidth="1"/>
+    <col min="9998" max="9998" width="15.81640625" customWidth="1"/>
+    <col min="9999" max="9999" width="7.81640625" customWidth="1"/>
+    <col min="10000" max="10000" width="5.453125" customWidth="1"/>
+    <col min="10001" max="10001" width="6.453125" customWidth="1"/>
+    <col min="10002" max="10002" width="7.81640625" customWidth="1"/>
+    <col min="10003" max="10003" width="3" customWidth="1"/>
+    <col min="10004" max="10004" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10241" max="10244" width="14.453125" customWidth="1"/>
+    <col min="10245" max="10245" width="15.453125" customWidth="1"/>
+    <col min="10246" max="10246" width="14.54296875" customWidth="1"/>
+    <col min="10247" max="10247" width="15.26953125" customWidth="1"/>
+    <col min="10248" max="10249" width="14.453125" customWidth="1"/>
+    <col min="10250" max="10250" width="13.1796875" customWidth="1"/>
+    <col min="10251" max="10253" width="14.453125" customWidth="1"/>
+    <col min="10254" max="10254" width="15.81640625" customWidth="1"/>
+    <col min="10255" max="10255" width="7.81640625" customWidth="1"/>
+    <col min="10256" max="10256" width="5.453125" customWidth="1"/>
+    <col min="10257" max="10257" width="6.453125" customWidth="1"/>
+    <col min="10258" max="10258" width="7.81640625" customWidth="1"/>
+    <col min="10259" max="10259" width="3" customWidth="1"/>
+    <col min="10260" max="10260" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10497" max="10500" width="14.453125" customWidth="1"/>
+    <col min="10501" max="10501" width="15.453125" customWidth="1"/>
+    <col min="10502" max="10502" width="14.54296875" customWidth="1"/>
+    <col min="10503" max="10503" width="15.26953125" customWidth="1"/>
+    <col min="10504" max="10505" width="14.453125" customWidth="1"/>
+    <col min="10506" max="10506" width="13.1796875" customWidth="1"/>
+    <col min="10507" max="10509" width="14.453125" customWidth="1"/>
+    <col min="10510" max="10510" width="15.81640625" customWidth="1"/>
+    <col min="10511" max="10511" width="7.81640625" customWidth="1"/>
+    <col min="10512" max="10512" width="5.453125" customWidth="1"/>
+    <col min="10513" max="10513" width="6.453125" customWidth="1"/>
+    <col min="10514" max="10514" width="7.81640625" customWidth="1"/>
+    <col min="10515" max="10515" width="3" customWidth="1"/>
+    <col min="10516" max="10516" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10753" max="10756" width="14.453125" customWidth="1"/>
+    <col min="10757" max="10757" width="15.453125" customWidth="1"/>
+    <col min="10758" max="10758" width="14.54296875" customWidth="1"/>
+    <col min="10759" max="10759" width="15.26953125" customWidth="1"/>
+    <col min="10760" max="10761" width="14.453125" customWidth="1"/>
+    <col min="10762" max="10762" width="13.1796875" customWidth="1"/>
+    <col min="10763" max="10765" width="14.453125" customWidth="1"/>
+    <col min="10766" max="10766" width="15.81640625" customWidth="1"/>
+    <col min="10767" max="10767" width="7.81640625" customWidth="1"/>
+    <col min="10768" max="10768" width="5.453125" customWidth="1"/>
+    <col min="10769" max="10769" width="6.453125" customWidth="1"/>
+    <col min="10770" max="10770" width="7.81640625" customWidth="1"/>
+    <col min="10771" max="10771" width="3" customWidth="1"/>
+    <col min="10772" max="10772" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11009" max="11012" width="14.453125" customWidth="1"/>
+    <col min="11013" max="11013" width="15.453125" customWidth="1"/>
+    <col min="11014" max="11014" width="14.54296875" customWidth="1"/>
+    <col min="11015" max="11015" width="15.26953125" customWidth="1"/>
+    <col min="11016" max="11017" width="14.453125" customWidth="1"/>
+    <col min="11018" max="11018" width="13.1796875" customWidth="1"/>
+    <col min="11019" max="11021" width="14.453125" customWidth="1"/>
+    <col min="11022" max="11022" width="15.81640625" customWidth="1"/>
+    <col min="11023" max="11023" width="7.81640625" customWidth="1"/>
+    <col min="11024" max="11024" width="5.453125" customWidth="1"/>
+    <col min="11025" max="11025" width="6.453125" customWidth="1"/>
+    <col min="11026" max="11026" width="7.81640625" customWidth="1"/>
+    <col min="11027" max="11027" width="3" customWidth="1"/>
+    <col min="11028" max="11028" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11265" max="11268" width="14.453125" customWidth="1"/>
+    <col min="11269" max="11269" width="15.453125" customWidth="1"/>
+    <col min="11270" max="11270" width="14.54296875" customWidth="1"/>
+    <col min="11271" max="11271" width="15.26953125" customWidth="1"/>
+    <col min="11272" max="11273" width="14.453125" customWidth="1"/>
+    <col min="11274" max="11274" width="13.1796875" customWidth="1"/>
+    <col min="11275" max="11277" width="14.453125" customWidth="1"/>
+    <col min="11278" max="11278" width="15.81640625" customWidth="1"/>
+    <col min="11279" max="11279" width="7.81640625" customWidth="1"/>
+    <col min="11280" max="11280" width="5.453125" customWidth="1"/>
+    <col min="11281" max="11281" width="6.453125" customWidth="1"/>
+    <col min="11282" max="11282" width="7.81640625" customWidth="1"/>
+    <col min="11283" max="11283" width="3" customWidth="1"/>
+    <col min="11284" max="11284" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11521" max="11524" width="14.453125" customWidth="1"/>
+    <col min="11525" max="11525" width="15.453125" customWidth="1"/>
+    <col min="11526" max="11526" width="14.54296875" customWidth="1"/>
+    <col min="11527" max="11527" width="15.26953125" customWidth="1"/>
+    <col min="11528" max="11529" width="14.453125" customWidth="1"/>
+    <col min="11530" max="11530" width="13.1796875" customWidth="1"/>
+    <col min="11531" max="11533" width="14.453125" customWidth="1"/>
+    <col min="11534" max="11534" width="15.81640625" customWidth="1"/>
+    <col min="11535" max="11535" width="7.81640625" customWidth="1"/>
+    <col min="11536" max="11536" width="5.453125" customWidth="1"/>
+    <col min="11537" max="11537" width="6.453125" customWidth="1"/>
+    <col min="11538" max="11538" width="7.81640625" customWidth="1"/>
+    <col min="11539" max="11539" width="3" customWidth="1"/>
+    <col min="11540" max="11540" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11777" max="11780" width="14.453125" customWidth="1"/>
+    <col min="11781" max="11781" width="15.453125" customWidth="1"/>
+    <col min="11782" max="11782" width="14.54296875" customWidth="1"/>
+    <col min="11783" max="11783" width="15.26953125" customWidth="1"/>
+    <col min="11784" max="11785" width="14.453125" customWidth="1"/>
+    <col min="11786" max="11786" width="13.1796875" customWidth="1"/>
+    <col min="11787" max="11789" width="14.453125" customWidth="1"/>
+    <col min="11790" max="11790" width="15.81640625" customWidth="1"/>
+    <col min="11791" max="11791" width="7.81640625" customWidth="1"/>
+    <col min="11792" max="11792" width="5.453125" customWidth="1"/>
+    <col min="11793" max="11793" width="6.453125" customWidth="1"/>
+    <col min="11794" max="11794" width="7.81640625" customWidth="1"/>
+    <col min="11795" max="11795" width="3" customWidth="1"/>
+    <col min="11796" max="11796" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12033" max="12036" width="14.453125" customWidth="1"/>
+    <col min="12037" max="12037" width="15.453125" customWidth="1"/>
+    <col min="12038" max="12038" width="14.54296875" customWidth="1"/>
+    <col min="12039" max="12039" width="15.26953125" customWidth="1"/>
+    <col min="12040" max="12041" width="14.453125" customWidth="1"/>
+    <col min="12042" max="12042" width="13.1796875" customWidth="1"/>
+    <col min="12043" max="12045" width="14.453125" customWidth="1"/>
+    <col min="12046" max="12046" width="15.81640625" customWidth="1"/>
+    <col min="12047" max="12047" width="7.81640625" customWidth="1"/>
+    <col min="12048" max="12048" width="5.453125" customWidth="1"/>
+    <col min="12049" max="12049" width="6.453125" customWidth="1"/>
+    <col min="12050" max="12050" width="7.81640625" customWidth="1"/>
+    <col min="12051" max="12051" width="3" customWidth="1"/>
+    <col min="12052" max="12052" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12289" max="12292" width="14.453125" customWidth="1"/>
+    <col min="12293" max="12293" width="15.453125" customWidth="1"/>
+    <col min="12294" max="12294" width="14.54296875" customWidth="1"/>
+    <col min="12295" max="12295" width="15.26953125" customWidth="1"/>
+    <col min="12296" max="12297" width="14.453125" customWidth="1"/>
+    <col min="12298" max="12298" width="13.1796875" customWidth="1"/>
+    <col min="12299" max="12301" width="14.453125" customWidth="1"/>
+    <col min="12302" max="12302" width="15.81640625" customWidth="1"/>
+    <col min="12303" max="12303" width="7.81640625" customWidth="1"/>
+    <col min="12304" max="12304" width="5.453125" customWidth="1"/>
+    <col min="12305" max="12305" width="6.453125" customWidth="1"/>
+    <col min="12306" max="12306" width="7.81640625" customWidth="1"/>
+    <col min="12307" max="12307" width="3" customWidth="1"/>
+    <col min="12308" max="12308" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12545" max="12548" width="14.453125" customWidth="1"/>
+    <col min="12549" max="12549" width="15.453125" customWidth="1"/>
+    <col min="12550" max="12550" width="14.54296875" customWidth="1"/>
+    <col min="12551" max="12551" width="15.26953125" customWidth="1"/>
+    <col min="12552" max="12553" width="14.453125" customWidth="1"/>
+    <col min="12554" max="12554" width="13.1796875" customWidth="1"/>
+    <col min="12555" max="12557" width="14.453125" customWidth="1"/>
+    <col min="12558" max="12558" width="15.81640625" customWidth="1"/>
+    <col min="12559" max="12559" width="7.81640625" customWidth="1"/>
+    <col min="12560" max="12560" width="5.453125" customWidth="1"/>
+    <col min="12561" max="12561" width="6.453125" customWidth="1"/>
+    <col min="12562" max="12562" width="7.81640625" customWidth="1"/>
+    <col min="12563" max="12563" width="3" customWidth="1"/>
+    <col min="12564" max="12564" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12801" max="12804" width="14.453125" customWidth="1"/>
+    <col min="12805" max="12805" width="15.453125" customWidth="1"/>
+    <col min="12806" max="12806" width="14.54296875" customWidth="1"/>
+    <col min="12807" max="12807" width="15.26953125" customWidth="1"/>
+    <col min="12808" max="12809" width="14.453125" customWidth="1"/>
+    <col min="12810" max="12810" width="13.1796875" customWidth="1"/>
+    <col min="12811" max="12813" width="14.453125" customWidth="1"/>
+    <col min="12814" max="12814" width="15.81640625" customWidth="1"/>
+    <col min="12815" max="12815" width="7.81640625" customWidth="1"/>
+    <col min="12816" max="12816" width="5.453125" customWidth="1"/>
+    <col min="12817" max="12817" width="6.453125" customWidth="1"/>
+    <col min="12818" max="12818" width="7.81640625" customWidth="1"/>
+    <col min="12819" max="12819" width="3" customWidth="1"/>
+    <col min="12820" max="12820" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13057" max="13060" width="14.453125" customWidth="1"/>
+    <col min="13061" max="13061" width="15.453125" customWidth="1"/>
+    <col min="13062" max="13062" width="14.54296875" customWidth="1"/>
+    <col min="13063" max="13063" width="15.26953125" customWidth="1"/>
+    <col min="13064" max="13065" width="14.453125" customWidth="1"/>
+    <col min="13066" max="13066" width="13.1796875" customWidth="1"/>
+    <col min="13067" max="13069" width="14.453125" customWidth="1"/>
+    <col min="13070" max="13070" width="15.81640625" customWidth="1"/>
+    <col min="13071" max="13071" width="7.81640625" customWidth="1"/>
+    <col min="13072" max="13072" width="5.453125" customWidth="1"/>
+    <col min="13073" max="13073" width="6.453125" customWidth="1"/>
+    <col min="13074" max="13074" width="7.81640625" customWidth="1"/>
+    <col min="13075" max="13075" width="3" customWidth="1"/>
+    <col min="13076" max="13076" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13313" max="13316" width="14.453125" customWidth="1"/>
+    <col min="13317" max="13317" width="15.453125" customWidth="1"/>
+    <col min="13318" max="13318" width="14.54296875" customWidth="1"/>
+    <col min="13319" max="13319" width="15.26953125" customWidth="1"/>
+    <col min="13320" max="13321" width="14.453125" customWidth="1"/>
+    <col min="13322" max="13322" width="13.1796875" customWidth="1"/>
+    <col min="13323" max="13325" width="14.453125" customWidth="1"/>
+    <col min="13326" max="13326" width="15.81640625" customWidth="1"/>
+    <col min="13327" max="13327" width="7.81640625" customWidth="1"/>
+    <col min="13328" max="13328" width="5.453125" customWidth="1"/>
+    <col min="13329" max="13329" width="6.453125" customWidth="1"/>
+    <col min="13330" max="13330" width="7.81640625" customWidth="1"/>
+    <col min="13331" max="13331" width="3" customWidth="1"/>
+    <col min="13332" max="13332" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13569" max="13572" width="14.453125" customWidth="1"/>
+    <col min="13573" max="13573" width="15.453125" customWidth="1"/>
+    <col min="13574" max="13574" width="14.54296875" customWidth="1"/>
+    <col min="13575" max="13575" width="15.26953125" customWidth="1"/>
+    <col min="13576" max="13577" width="14.453125" customWidth="1"/>
+    <col min="13578" max="13578" width="13.1796875" customWidth="1"/>
+    <col min="13579" max="13581" width="14.453125" customWidth="1"/>
+    <col min="13582" max="13582" width="15.81640625" customWidth="1"/>
+    <col min="13583" max="13583" width="7.81640625" customWidth="1"/>
+    <col min="13584" max="13584" width="5.453125" customWidth="1"/>
+    <col min="13585" max="13585" width="6.453125" customWidth="1"/>
+    <col min="13586" max="13586" width="7.81640625" customWidth="1"/>
+    <col min="13587" max="13587" width="3" customWidth="1"/>
+    <col min="13588" max="13588" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13825" max="13828" width="14.453125" customWidth="1"/>
+    <col min="13829" max="13829" width="15.453125" customWidth="1"/>
+    <col min="13830" max="13830" width="14.54296875" customWidth="1"/>
+    <col min="13831" max="13831" width="15.26953125" customWidth="1"/>
+    <col min="13832" max="13833" width="14.453125" customWidth="1"/>
+    <col min="13834" max="13834" width="13.1796875" customWidth="1"/>
+    <col min="13835" max="13837" width="14.453125" customWidth="1"/>
+    <col min="13838" max="13838" width="15.81640625" customWidth="1"/>
+    <col min="13839" max="13839" width="7.81640625" customWidth="1"/>
+    <col min="13840" max="13840" width="5.453125" customWidth="1"/>
+    <col min="13841" max="13841" width="6.453125" customWidth="1"/>
+    <col min="13842" max="13842" width="7.81640625" customWidth="1"/>
+    <col min="13843" max="13843" width="3" customWidth="1"/>
+    <col min="13844" max="13844" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14081" max="14084" width="14.453125" customWidth="1"/>
+    <col min="14085" max="14085" width="15.453125" customWidth="1"/>
+    <col min="14086" max="14086" width="14.54296875" customWidth="1"/>
+    <col min="14087" max="14087" width="15.26953125" customWidth="1"/>
+    <col min="14088" max="14089" width="14.453125" customWidth="1"/>
+    <col min="14090" max="14090" width="13.1796875" customWidth="1"/>
+    <col min="14091" max="14093" width="14.453125" customWidth="1"/>
+    <col min="14094" max="14094" width="15.81640625" customWidth="1"/>
+    <col min="14095" max="14095" width="7.81640625" customWidth="1"/>
+    <col min="14096" max="14096" width="5.453125" customWidth="1"/>
+    <col min="14097" max="14097" width="6.453125" customWidth="1"/>
+    <col min="14098" max="14098" width="7.81640625" customWidth="1"/>
+    <col min="14099" max="14099" width="3" customWidth="1"/>
+    <col min="14100" max="14100" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14337" max="14340" width="14.453125" customWidth="1"/>
+    <col min="14341" max="14341" width="15.453125" customWidth="1"/>
+    <col min="14342" max="14342" width="14.54296875" customWidth="1"/>
+    <col min="14343" max="14343" width="15.26953125" customWidth="1"/>
+    <col min="14344" max="14345" width="14.453125" customWidth="1"/>
+    <col min="14346" max="14346" width="13.1796875" customWidth="1"/>
+    <col min="14347" max="14349" width="14.453125" customWidth="1"/>
+    <col min="14350" max="14350" width="15.81640625" customWidth="1"/>
+    <col min="14351" max="14351" width="7.81640625" customWidth="1"/>
+    <col min="14352" max="14352" width="5.453125" customWidth="1"/>
+    <col min="14353" max="14353" width="6.453125" customWidth="1"/>
+    <col min="14354" max="14354" width="7.81640625" customWidth="1"/>
+    <col min="14355" max="14355" width="3" customWidth="1"/>
+    <col min="14356" max="14356" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14593" max="14596" width="14.453125" customWidth="1"/>
+    <col min="14597" max="14597" width="15.453125" customWidth="1"/>
+    <col min="14598" max="14598" width="14.54296875" customWidth="1"/>
+    <col min="14599" max="14599" width="15.26953125" customWidth="1"/>
+    <col min="14600" max="14601" width="14.453125" customWidth="1"/>
+    <col min="14602" max="14602" width="13.1796875" customWidth="1"/>
+    <col min="14603" max="14605" width="14.453125" customWidth="1"/>
+    <col min="14606" max="14606" width="15.81640625" customWidth="1"/>
+    <col min="14607" max="14607" width="7.81640625" customWidth="1"/>
+    <col min="14608" max="14608" width="5.453125" customWidth="1"/>
+    <col min="14609" max="14609" width="6.453125" customWidth="1"/>
+    <col min="14610" max="14610" width="7.81640625" customWidth="1"/>
+    <col min="14611" max="14611" width="3" customWidth="1"/>
+    <col min="14612" max="14612" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14849" max="14852" width="14.453125" customWidth="1"/>
+    <col min="14853" max="14853" width="15.453125" customWidth="1"/>
+    <col min="14854" max="14854" width="14.54296875" customWidth="1"/>
+    <col min="14855" max="14855" width="15.26953125" customWidth="1"/>
+    <col min="14856" max="14857" width="14.453125" customWidth="1"/>
+    <col min="14858" max="14858" width="13.1796875" customWidth="1"/>
+    <col min="14859" max="14861" width="14.453125" customWidth="1"/>
+    <col min="14862" max="14862" width="15.81640625" customWidth="1"/>
+    <col min="14863" max="14863" width="7.81640625" customWidth="1"/>
+    <col min="14864" max="14864" width="5.453125" customWidth="1"/>
+    <col min="14865" max="14865" width="6.453125" customWidth="1"/>
+    <col min="14866" max="14866" width="7.81640625" customWidth="1"/>
+    <col min="14867" max="14867" width="3" customWidth="1"/>
+    <col min="14868" max="14868" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15105" max="15108" width="14.453125" customWidth="1"/>
+    <col min="15109" max="15109" width="15.453125" customWidth="1"/>
+    <col min="15110" max="15110" width="14.54296875" customWidth="1"/>
+    <col min="15111" max="15111" width="15.26953125" customWidth="1"/>
+    <col min="15112" max="15113" width="14.453125" customWidth="1"/>
+    <col min="15114" max="15114" width="13.1796875" customWidth="1"/>
+    <col min="15115" max="15117" width="14.453125" customWidth="1"/>
+    <col min="15118" max="15118" width="15.81640625" customWidth="1"/>
+    <col min="15119" max="15119" width="7.81640625" customWidth="1"/>
+    <col min="15120" max="15120" width="5.453125" customWidth="1"/>
+    <col min="15121" max="15121" width="6.453125" customWidth="1"/>
+    <col min="15122" max="15122" width="7.81640625" customWidth="1"/>
+    <col min="15123" max="15123" width="3" customWidth="1"/>
+    <col min="15124" max="15124" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15361" max="15364" width="14.453125" customWidth="1"/>
+    <col min="15365" max="15365" width="15.453125" customWidth="1"/>
+    <col min="15366" max="15366" width="14.54296875" customWidth="1"/>
+    <col min="15367" max="15367" width="15.26953125" customWidth="1"/>
+    <col min="15368" max="15369" width="14.453125" customWidth="1"/>
+    <col min="15370" max="15370" width="13.1796875" customWidth="1"/>
+    <col min="15371" max="15373" width="14.453125" customWidth="1"/>
+    <col min="15374" max="15374" width="15.81640625" customWidth="1"/>
+    <col min="15375" max="15375" width="7.81640625" customWidth="1"/>
+    <col min="15376" max="15376" width="5.453125" customWidth="1"/>
+    <col min="15377" max="15377" width="6.453125" customWidth="1"/>
+    <col min="15378" max="15378" width="7.81640625" customWidth="1"/>
+    <col min="15379" max="15379" width="3" customWidth="1"/>
+    <col min="15380" max="15380" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15617" max="15620" width="14.453125" customWidth="1"/>
+    <col min="15621" max="15621" width="15.453125" customWidth="1"/>
+    <col min="15622" max="15622" width="14.54296875" customWidth="1"/>
+    <col min="15623" max="15623" width="15.26953125" customWidth="1"/>
+    <col min="15624" max="15625" width="14.453125" customWidth="1"/>
+    <col min="15626" max="15626" width="13.1796875" customWidth="1"/>
+    <col min="15627" max="15629" width="14.453125" customWidth="1"/>
+    <col min="15630" max="15630" width="15.81640625" customWidth="1"/>
+    <col min="15631" max="15631" width="7.81640625" customWidth="1"/>
+    <col min="15632" max="15632" width="5.453125" customWidth="1"/>
+    <col min="15633" max="15633" width="6.453125" customWidth="1"/>
+    <col min="15634" max="15634" width="7.81640625" customWidth="1"/>
+    <col min="15635" max="15635" width="3" customWidth="1"/>
+    <col min="15636" max="15636" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15873" max="15876" width="14.453125" customWidth="1"/>
+    <col min="15877" max="15877" width="15.453125" customWidth="1"/>
+    <col min="15878" max="15878" width="14.54296875" customWidth="1"/>
+    <col min="15879" max="15879" width="15.26953125" customWidth="1"/>
+    <col min="15880" max="15881" width="14.453125" customWidth="1"/>
+    <col min="15882" max="15882" width="13.1796875" customWidth="1"/>
+    <col min="15883" max="15885" width="14.453125" customWidth="1"/>
+    <col min="15886" max="15886" width="15.81640625" customWidth="1"/>
+    <col min="15887" max="15887" width="7.81640625" customWidth="1"/>
+    <col min="15888" max="15888" width="5.453125" customWidth="1"/>
+    <col min="15889" max="15889" width="6.453125" customWidth="1"/>
+    <col min="15890" max="15890" width="7.81640625" customWidth="1"/>
+    <col min="15891" max="15891" width="3" customWidth="1"/>
+    <col min="15892" max="15892" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="16129" max="16132" width="14.453125" customWidth="1"/>
+    <col min="16133" max="16133" width="15.453125" customWidth="1"/>
+    <col min="16134" max="16134" width="14.54296875" customWidth="1"/>
+    <col min="16135" max="16135" width="15.26953125" customWidth="1"/>
+    <col min="16136" max="16137" width="14.453125" customWidth="1"/>
+    <col min="16138" max="16138" width="13.1796875" customWidth="1"/>
+    <col min="16139" max="16141" width="14.453125" customWidth="1"/>
+    <col min="16142" max="16142" width="15.81640625" customWidth="1"/>
+    <col min="16143" max="16143" width="7.81640625" customWidth="1"/>
+    <col min="16144" max="16144" width="5.453125" customWidth="1"/>
+    <col min="16145" max="16145" width="6.453125" customWidth="1"/>
+    <col min="16146" max="16146" width="7.81640625" customWidth="1"/>
+    <col min="16147" max="16147" width="3" customWidth="1"/>
+    <col min="16148" max="16148" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="301" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
+      <c r="S1"/>
+    </row>
+    <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2"/>
+    </row>
+    <row r="3" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="290" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="293" t="s">
+        <v>99</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="I3" s="129" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="292" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="297" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="26"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="294" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" s="295"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="287" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="288"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="29"/>
+    </row>
+    <row r="4" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="290"/>
+      <c r="E4" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" s="293"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="292"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="297"/>
+      <c r="O4" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" s="274" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" s="275" t="s">
+        <v>71</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" s="270" t="s">
+        <v>70</v>
+      </c>
+      <c r="U4" s="271" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="37"/>
+      <c r="E5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="293" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="290" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="54"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="38"/>
+      <c r="O5" s="39">
+        <v>31</v>
+      </c>
+      <c r="P5" s="40">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="41">
+        <v>19</v>
+      </c>
+      <c r="R5" s="42">
+        <v>11</v>
+      </c>
+      <c r="S5" s="40">
+        <v>31</v>
+      </c>
+      <c r="T5" s="41">
+        <v>19</v>
+      </c>
+      <c r="U5" s="42">
+        <v>11</v>
+      </c>
+      <c r="V5" s="43">
+        <f t="shared" ref="V5:V17" si="0">-SUM(S5-P5)*-1</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="44"/>
+    </row>
+    <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F6" s="293"/>
+      <c r="G6" s="278"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="129" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="290"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="8"/>
+      <c r="N6" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" s="47">
+        <v>49</v>
+      </c>
+      <c r="P6" s="48">
+        <f t="shared" ref="P6:P17" si="1">SUM(Q6:R6)</f>
+        <v>12</v>
+      </c>
+      <c r="Q6" s="49">
+        <v>7</v>
+      </c>
+      <c r="R6" s="50">
+        <v>5</v>
+      </c>
+      <c r="S6" s="48">
+        <f t="shared" ref="S6:S17" si="2">SUM(T6:U6)</f>
+        <v>12</v>
+      </c>
+      <c r="T6" s="49">
+        <v>7</v>
+      </c>
+      <c r="U6" s="50">
+        <v>5</v>
+      </c>
+      <c r="V6" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="52"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="53"/>
+      <c r="C7" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="293" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" s="278"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="297" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" s="54"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="47">
+        <v>22</v>
+      </c>
+      <c r="P7" s="48">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Q7" s="49">
+        <v>11</v>
+      </c>
+      <c r="R7" s="50">
+        <v>4</v>
+      </c>
+      <c r="S7" s="48">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="T7" s="49">
+        <v>11</v>
+      </c>
+      <c r="U7" s="50">
+        <v>4</v>
+      </c>
+      <c r="V7" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W7" s="52"/>
+    </row>
+    <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="45"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F8" s="293"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="297"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="56">
+        <v>46314</v>
+      </c>
+      <c r="O8" s="47">
+        <v>24</v>
+      </c>
+      <c r="P8" s="48">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Q8" s="49">
+        <v>3</v>
+      </c>
+      <c r="R8" s="50">
+        <v>3</v>
+      </c>
+      <c r="S8" s="48">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="T8" s="49">
+        <v>2</v>
+      </c>
+      <c r="U8" s="50">
+        <v>2</v>
+      </c>
+      <c r="V8" s="51">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="W8" s="52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="45"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="58"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="296" t="s">
+        <v>258</v>
+      </c>
+      <c r="G9" s="62"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9" s="47"/>
+      <c r="P9" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="49"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W9" s="52"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="45"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="129" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="61"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="296"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="49"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="52"/>
+    </row>
+    <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="64"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="D11" s="61"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="G11" s="64"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="66"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="68"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="70"/>
+    </row>
+    <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="71"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="G12" s="64"/>
+      <c r="H12" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="L12" s="73" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" s="74"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="68"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W12" s="70"/>
+    </row>
+    <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="61"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="276" t="s">
+        <v>149</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="297" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="127" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="128"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="60"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="68"/>
+      <c r="U13" s="69"/>
+      <c r="V13" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="70"/>
+    </row>
+    <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="8"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="276" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="30"/>
+      <c r="I14" s="297"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="60"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="68"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="70"/>
+    </row>
+    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="129"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="273"/>
+      <c r="F15" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="126" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="60"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="107"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="68"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="70"/>
+    </row>
+    <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="296" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="296" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="297" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="61"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="277" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="107"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="68"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="68"/>
+      <c r="U16" s="69"/>
+      <c r="V16" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="70"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="296"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="297"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="128" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="80"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="82">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="83"/>
+    </row>
+    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="77"/>
+      <c r="M18" s="77"/>
+      <c r="R18" s="84"/>
+      <c r="S18"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="273"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="77"/>
+      <c r="R19" s="84"/>
+      <c r="S19"/>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="85" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="273"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="158"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="R20" s="84"/>
+      <c r="S20"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="128" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="D21" s="61"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="R21" s="84"/>
+      <c r="S21"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="6"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="273"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="R22" s="84"/>
+      <c r="S22"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="R23" s="84"/>
+      <c r="S23"/>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="R24" s="84"/>
+      <c r="S24"/>
+    </row>
+    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="30"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="R25" s="84"/>
+      <c r="S25"/>
+    </row>
+    <row r="26" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="273"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="R26" s="84"/>
+      <c r="S26"/>
+    </row>
+    <row r="27" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="R27" s="84"/>
+      <c r="S27"/>
+    </row>
+    <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="302" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="R28" s="84"/>
+      <c r="S28"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="30"/>
+      <c r="I29" s="273"/>
+      <c r="J29" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K29" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="92" t="s">
+        <v>25</v>
+      </c>
+      <c r="R29" s="84"/>
+      <c r="S29"/>
+    </row>
+    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="93" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="94"/>
+      <c r="C30" s="93" t="s">
+        <v>249</v>
+      </c>
+      <c r="D30" s="93" t="s">
+        <v>251</v>
+      </c>
+      <c r="E30" s="291" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="8"/>
+      <c r="G30" s="272" t="s">
+        <v>269</v>
+      </c>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="224" t="s">
+        <v>42</v>
+      </c>
+      <c r="K30" s="124" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="218" t="s">
+        <v>119</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="R30" s="84"/>
+      <c r="S30"/>
+    </row>
+    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C31" s="93" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" s="93" t="s">
+        <v>252</v>
+      </c>
+      <c r="E31" s="291"/>
+      <c r="F31" s="8"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="159"/>
+      <c r="K31" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="L31" s="218" t="s">
+        <v>122</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" s="84"/>
+      <c r="S31"/>
+    </row>
+    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="B32" s="94"/>
+      <c r="C32" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="93" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="291" t="s">
+        <v>259</v>
+      </c>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="159"/>
+      <c r="K32" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="L32" s="218" t="s">
+        <v>243</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="R32" s="84"/>
+      <c r="S32"/>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="8"/>
+      <c r="C33" s="93" t="s">
+        <v>267</v>
+      </c>
+      <c r="D33" s="93" t="s">
+        <v>253</v>
+      </c>
+      <c r="E33" s="291"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="110" t="s">
+        <v>150</v>
+      </c>
+      <c r="L33" s="218" t="s">
+        <v>38</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="R33" s="84"/>
+      <c r="S33"/>
+    </row>
+    <row r="34" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="94"/>
+      <c r="B34" s="95"/>
+      <c r="D34" s="93" t="s">
+        <v>254</v>
+      </c>
+      <c r="E34" s="291" t="s">
+        <v>260</v>
+      </c>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="K34" s="110" t="s">
+        <v>16</v>
+      </c>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="R34" s="84"/>
+      <c r="S34"/>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="94"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="93" t="s">
+        <v>255</v>
+      </c>
+      <c r="E35" s="291"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="124" t="s">
+        <v>120</v>
+      </c>
+      <c r="L35" s="8"/>
+      <c r="M35" s="13"/>
+      <c r="R35" s="84"/>
+      <c r="S35"/>
+    </row>
+    <row r="36" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="94"/>
+      <c r="B36" s="94"/>
+      <c r="D36" s="93" t="s">
+        <v>256</v>
+      </c>
+      <c r="E36" s="291" t="s">
+        <v>261</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="97"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="224" t="s">
+        <v>203</v>
+      </c>
+      <c r="L36" s="8"/>
+      <c r="M36" s="94"/>
+      <c r="R36" s="84"/>
+      <c r="S36"/>
+    </row>
+    <row r="37" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="E37" s="291"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="100"/>
+      <c r="K37" s="124" t="s">
+        <v>211</v>
+      </c>
+      <c r="L37" s="8"/>
+      <c r="M37" s="94"/>
+      <c r="R37" s="84"/>
+      <c r="S37"/>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="77"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="272" t="s">
+        <v>270</v>
+      </c>
+      <c r="F38" s="77"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="124" t="s">
+        <v>212</v>
+      </c>
+      <c r="L38" s="8"/>
+      <c r="M38" s="2"/>
+      <c r="R38" s="84"/>
+      <c r="S38"/>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="74"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="272" t="s">
+        <v>271</v>
+      </c>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="2"/>
+      <c r="S39"/>
+    </row>
+    <row r="40" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="105"/>
+      <c r="S40"/>
+    </row>
+    <row r="41" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="104"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="104"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="93" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="8"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="101"/>
+      <c r="M41" s="106"/>
+      <c r="S41"/>
+    </row>
+    <row r="42" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="104"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="104"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="272" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="106"/>
+      <c r="S42"/>
+    </row>
+    <row r="43" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="104"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="272" t="s">
+        <v>268</v>
+      </c>
+      <c r="F43" s="107"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="106"/>
+      <c r="S43"/>
+    </row>
+    <row r="44" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="104"/>
+      <c r="B44" s="104"/>
+      <c r="C44" s="104"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="109"/>
+      <c r="S44"/>
+    </row>
+    <row r="45" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="104"/>
+      <c r="B45" s="104"/>
+      <c r="C45" s="104"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="110"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="111"/>
+      <c r="S45"/>
+    </row>
+    <row r="46" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="104"/>
+      <c r="B46" s="104"/>
+      <c r="C46" s="104"/>
+      <c r="D46" s="104"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="104"/>
+      <c r="J46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="111"/>
+      <c r="S46"/>
+    </row>
+    <row r="47" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="104"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="104"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="104"/>
+      <c r="H47" s="104"/>
+      <c r="I47" s="273"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="112"/>
+      <c r="S47"/>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="84"/>
+      <c r="S48"/>
+    </row>
+    <row r="49" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="77"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="113"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="104"/>
+      <c r="I49" s="273"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="84"/>
+      <c r="S49"/>
+    </row>
+    <row r="50" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="77"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="84"/>
+      <c r="S50"/>
+    </row>
+    <row r="51" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="77"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="77"/>
+      <c r="D51" s="113"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="77"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="84"/>
+      <c r="S51"/>
+    </row>
+    <row r="52" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="77"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="113"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="77"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="77"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+    </row>
+    <row r="53" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="77"/>
+      <c r="B53" s="77"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="113"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="77"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="114"/>
+      <c r="M53" s="8"/>
+    </row>
+    <row r="54" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="77"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="113"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="77"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="77"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="114"/>
+      <c r="M54" s="8"/>
+    </row>
+    <row r="55" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="77"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="113"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="77"/>
+      <c r="G55" s="77"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="104"/>
+      <c r="J55" s="77"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="114"/>
+      <c r="M55" s="8"/>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="77"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="113"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="77"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="77"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="114"/>
+      <c r="M56" s="8"/>
+    </row>
+    <row r="57" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="77"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="77"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="114"/>
+      <c r="M57" s="8"/>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="77"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="113"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="77"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="115"/>
+      <c r="L58" s="114"/>
+      <c r="M58" s="8"/>
+    </row>
+    <row r="59" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="77"/>
+      <c r="B59" s="77"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="113"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="77"/>
+      <c r="G59" s="77"/>
+      <c r="H59" s="104"/>
+      <c r="I59" s="104"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="115"/>
+      <c r="L59" s="114"/>
+      <c r="M59" s="8"/>
+    </row>
+    <row r="60" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="77"/>
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="77"/>
+      <c r="G60" s="77"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="115"/>
+      <c r="L60" s="114"/>
+      <c r="M60" s="8"/>
+    </row>
+    <row r="61" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="77"/>
+      <c r="B61" s="77"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="113"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="114"/>
+      <c r="M61" s="8"/>
+    </row>
+    <row r="62" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="77"/>
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="77"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="114"/>
+      <c r="M62" s="8"/>
+    </row>
+    <row r="63" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="77"/>
+      <c r="B63" s="77"/>
+      <c r="C63" s="77"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="104"/>
+      <c r="I63" s="104"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="77"/>
+      <c r="M63" s="8"/>
+    </row>
+    <row r="64" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="77"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="77"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="77"/>
+      <c r="H64" s="104"/>
+      <c r="I64" s="104"/>
+      <c r="J64" s="77"/>
+      <c r="K64" s="116">
+        <v>22</v>
+      </c>
+      <c r="L64" s="117">
+        <v>6</v>
+      </c>
+      <c r="M64" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="61"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
+      <c r="S65"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L66" s="119" t="s">
+        <v>94</v>
+      </c>
+      <c r="M66" s="25">
+        <v>97</v>
+      </c>
+      <c r="S66"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L67" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="M67" s="25">
+        <f>SUM(M66-(M68+M69+M70))</f>
+        <v>69</v>
+      </c>
+      <c r="S67"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L68" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" s="25">
+        <v>15</v>
+      </c>
+      <c r="S68"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L69" s="121" t="s">
+        <v>24</v>
+      </c>
+      <c r="M69" s="25">
+        <v>9</v>
+      </c>
+      <c r="S69"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L70" s="122" t="s">
+        <v>25</v>
+      </c>
+      <c r="M70" s="25">
+        <v>4</v>
+      </c>
+      <c r="S70"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L71" t="s">
+        <v>96</v>
+      </c>
+      <c r="M71" s="25">
+        <v>13</v>
+      </c>
+      <c r="S71"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="M72" s="25"/>
+      <c r="S72"/>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="E30:E31"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -20497,21 +23204,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -20558,7 +23265,7 @@
     </row>
     <row r="3" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>107</v>
@@ -20566,39 +23273,40 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="282" t="s">
+      <c r="D3" s="290" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="285" t="s">
+      <c r="F3" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="284" t="s">
+      <c r="J3" s="292" t="s">
         <v>10</v>
       </c>
+      <c r="K3" s="8"/>
       <c r="L3" s="8"/>
-      <c r="M3" s="289" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -20609,39 +23317,39 @@
       <c r="C4" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="282"/>
-      <c r="E4" s="11" t="s">
+      <c r="D4" s="290"/>
+      <c r="E4" s="258" t="s">
         <v>182</v>
       </c>
-      <c r="F4" s="285"/>
+      <c r="F4" s="293"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="284"/>
-      <c r="K4" s="54"/>
+      <c r="J4" s="292"/>
+      <c r="K4" s="8"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="289"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
       <c r="P4" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="Q4" s="274" t="s">
+      <c r="Q4" s="283" t="s">
         <v>70</v>
       </c>
-      <c r="R4" s="275" t="s">
+      <c r="R4" s="284" t="s">
         <v>71</v>
       </c>
       <c r="S4" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="T4" s="270" t="s">
+      <c r="T4" s="279" t="s">
         <v>70</v>
       </c>
-      <c r="U4" s="271" t="s">
+      <c r="U4" s="280" t="s">
         <v>71</v>
       </c>
       <c r="V4" s="34" t="s">
@@ -20652,8 +23360,8 @@
       </c>
     </row>
     <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
-        <v>41</v>
+      <c r="A5" s="260" t="s">
+        <v>247</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="11" t="s">
@@ -20663,7 +23371,7 @@
       <c r="E5" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>257</v>
       </c>
       <c r="G5" s="8"/>
@@ -20671,10 +23379,10 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="54"/>
+      <c r="K5" s="8"/>
       <c r="L5" s="8"/>
       <c r="M5" s="38"/>
       <c r="O5" s="39">
@@ -20705,10 +23413,9 @@
       <c r="W5" s="44"/>
     </row>
     <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="8"/>
       <c r="B6" s="45"/>
       <c r="C6" s="7" t="s">
-        <v>247</v>
+        <v>41</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>14</v>
@@ -20716,15 +23423,18 @@
       <c r="E6" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="278"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
+      <c r="M6" s="126" t="s">
+        <v>58</v>
+      </c>
       <c r="N6" s="46" t="s">
         <v>74</v>
       </c>
@@ -20766,13 +23476,13 @@
       <c r="E7" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="285" t="s">
+      <c r="F7" s="293" t="s">
         <v>110</v>
       </c>
       <c r="G7" s="278"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="289" t="s">
+      <c r="J7" s="297" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -20811,7 +23521,7 @@
     <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="45"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="260" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="21" t="s">
@@ -20820,15 +23530,15 @@
       <c r="E8" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F8" s="285"/>
+      <c r="F8" s="293"/>
       <c r="G8" s="62"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="289"/>
+      <c r="J8" s="297"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="O8" s="47">
         <v>24</v>
@@ -20869,7 +23579,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="288" t="s">
+      <c r="F9" s="296" t="s">
         <v>258</v>
       </c>
       <c r="G9" s="62"/>
@@ -20909,7 +23619,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="288"/>
+      <c r="F10" s="296"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -20984,10 +23694,9 @@
       </c>
       <c r="D12" s="71"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="G12" s="64"/>
+      <c r="F12" s="258" t="s">
+        <v>262</v>
+      </c>
       <c r="H12" s="24" t="s">
         <v>80</v>
       </c>
@@ -21031,12 +23740,12 @@
       </c>
       <c r="D13" s="61"/>
       <c r="E13" s="75"/>
-      <c r="F13" s="276" t="s">
+      <c r="F13" s="285" t="s">
         <v>149</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="289" t="s">
+      <c r="I13" s="297" t="s">
         <v>45</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -21068,11 +23777,11 @@
       <c r="B14" s="8"/>
       <c r="D14" s="61"/>
       <c r="E14" s="75"/>
-      <c r="F14" s="276" t="s">
+      <c r="F14" s="285" t="s">
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="289"/>
+      <c r="I14" s="297"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -21101,15 +23810,13 @@
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="61"/>
-      <c r="E15" s="273"/>
+      <c r="E15" s="282"/>
       <c r="F15" s="129" t="s">
         <v>81</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="126" t="s">
-        <v>58</v>
-      </c>
+      <c r="I15" s="30"/>
       <c r="J15" s="60"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
@@ -21134,18 +23841,18 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="296" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="289" t="s">
+      <c r="C16" s="297" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="59"/>
-      <c r="F16" s="277" t="s">
+      <c r="F16" s="286" t="s">
         <v>83</v>
       </c>
       <c r="G16" s="6"/>
@@ -21175,14 +23882,11 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="288"/>
-      <c r="B17" s="288"/>
-      <c r="C17" s="289"/>
+      <c r="A17" s="296"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="297"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
-      <c r="F17" s="128" t="s">
-        <v>120</v>
-      </c>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
       <c r="I17" s="30"/>
@@ -21228,7 +23932,7 @@
     </row>
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
-      <c r="B19" s="273"/>
+      <c r="B19" s="282"/>
       <c r="C19" s="8"/>
       <c r="D19" s="125"/>
       <c r="E19" s="59"/>
@@ -21244,8 +23948,8 @@
       <c r="S19"/>
     </row>
     <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="17" t="s">
-        <v>20</v>
+      <c r="A20" s="128" t="s">
+        <v>120</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>46</v>
@@ -21254,7 +23958,7 @@
         <v>146</v>
       </c>
       <c r="D20" s="12"/>
-      <c r="E20" s="273"/>
+      <c r="E20" s="282"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
       <c r="H20" s="30"/>
@@ -21290,7 +23994,7 @@
       <c r="C22" s="8"/>
       <c r="D22" s="61"/>
       <c r="E22" s="30"/>
-      <c r="F22" s="273"/>
+      <c r="F22" s="282"/>
       <c r="G22" s="6"/>
       <c r="H22" s="30"/>
       <c r="I22" s="30"/>
@@ -21361,7 +24065,7 @@
       <c r="D26" s="61"/>
       <c r="E26" s="30"/>
       <c r="F26" s="8"/>
-      <c r="G26" s="273"/>
+      <c r="G26" s="282"/>
       <c r="H26" s="89"/>
       <c r="I26" s="59"/>
       <c r="J26" s="8"/>
@@ -21389,13 +24093,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -21428,7 +24132,7 @@
         <v>62</v>
       </c>
       <c r="H29" s="30"/>
-      <c r="I29" s="273"/>
+      <c r="I29" s="282"/>
       <c r="J29" s="9" t="s">
         <v>88</v>
       </c>
@@ -21455,16 +24159,16 @@
       <c r="D30" s="93" t="s">
         <v>251</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
-      <c r="G30" s="272" t="s">
+      <c r="G30" s="281" t="s">
         <v>269</v>
       </c>
       <c r="H30" s="30"/>
       <c r="I30" s="30"/>
-      <c r="J30" s="224" t="s">
+      <c r="J30" s="159" t="s">
         <v>42</v>
       </c>
       <c r="K30" s="124" t="s">
@@ -21489,11 +24193,13 @@
       <c r="D31" s="93" t="s">
         <v>252</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
-      <c r="J31" s="159"/>
+      <c r="J31" s="10" t="s">
+        <v>120</v>
+      </c>
       <c r="K31" s="110" t="s">
         <v>201</v>
       </c>
@@ -21517,7 +24223,7 @@
       <c r="D32" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>259</v>
       </c>
       <c r="F32" s="8"/>
@@ -21545,14 +24251,14 @@
       <c r="D33" s="93" t="s">
         <v>253</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
       <c r="I33" s="30"/>
       <c r="J33" s="143"/>
       <c r="K33" s="110" t="s">
-        <v>150</v>
+        <v>16</v>
       </c>
       <c r="L33" s="218" t="s">
         <v>38</v>
@@ -21569,7 +24275,7 @@
       <c r="D34" s="93" t="s">
         <v>254</v>
       </c>
-      <c r="E34" s="283" t="s">
+      <c r="E34" s="291" t="s">
         <v>260</v>
       </c>
       <c r="F34" s="8"/>
@@ -21577,9 +24283,11 @@
       <c r="H34" s="30"/>
       <c r="I34" s="30"/>
       <c r="K34" s="110" t="s">
-        <v>16</v>
-      </c>
-      <c r="L34" s="8"/>
+        <v>203</v>
+      </c>
+      <c r="L34" s="224" t="s">
+        <v>150</v>
+      </c>
       <c r="M34" s="8"/>
       <c r="R34" s="84"/>
       <c r="S34"/>
@@ -21591,14 +24299,14 @@
       <c r="D35" s="93" t="s">
         <v>255</v>
       </c>
-      <c r="E35" s="283"/>
+      <c r="E35" s="291"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
       <c r="I35" s="30"/>
       <c r="J35" s="4"/>
-      <c r="K35" s="124" t="s">
-        <v>120</v>
+      <c r="K35" s="224" t="s">
+        <v>20</v>
       </c>
       <c r="L35" s="8"/>
       <c r="M35" s="13"/>
@@ -21611,7 +24319,7 @@
       <c r="D36" s="93" t="s">
         <v>256</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>261</v>
       </c>
       <c r="F36" s="53"/>
@@ -21619,8 +24327,8 @@
       <c r="H36" s="97"/>
       <c r="I36" s="30"/>
       <c r="J36" s="4"/>
-      <c r="K36" s="224" t="s">
-        <v>203</v>
+      <c r="K36" s="124" t="s">
+        <v>211</v>
       </c>
       <c r="L36" s="8"/>
       <c r="M36" s="94"/>
@@ -21631,14 +24339,14 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
       <c r="I37" s="30"/>
       <c r="J37" s="100"/>
       <c r="K37" s="124" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L37" s="8"/>
       <c r="M37" s="94"/>
@@ -21650,7 +24358,7 @@
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="D38" s="76"/>
-      <c r="E38" s="272" t="s">
+      <c r="E38" s="281" t="s">
         <v>270</v>
       </c>
       <c r="F38" s="77"/>
@@ -21658,9 +24366,6 @@
       <c r="H38" s="30"/>
       <c r="I38" s="30"/>
       <c r="J38" s="6"/>
-      <c r="K38" s="124" t="s">
-        <v>212</v>
-      </c>
       <c r="L38" s="8"/>
       <c r="M38" s="2"/>
       <c r="R38" s="84"/>
@@ -21671,7 +24376,7 @@
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
       <c r="D39" s="102"/>
-      <c r="E39" s="272" t="s">
+      <c r="E39" s="281" t="s">
         <v>271</v>
       </c>
       <c r="F39" s="77"/>
@@ -21725,7 +24430,7 @@
       <c r="B42" s="8"/>
       <c r="C42" s="104"/>
       <c r="D42" s="76"/>
-      <c r="E42" s="272" t="s">
+      <c r="E42" s="281" t="s">
         <v>47</v>
       </c>
       <c r="G42" s="104"/>
@@ -21742,7 +24447,7 @@
       <c r="B43" s="8"/>
       <c r="C43" s="104"/>
       <c r="D43" s="76"/>
-      <c r="E43" s="272" t="s">
+      <c r="E43" s="281" t="s">
         <v>268</v>
       </c>
       <c r="F43" s="107"/>
@@ -21810,7 +24515,7 @@
       <c r="F47" s="104"/>
       <c r="G47" s="104"/>
       <c r="H47" s="104"/>
-      <c r="I47" s="273"/>
+      <c r="I47" s="282"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
@@ -21843,7 +24548,7 @@
       <c r="F49" s="77"/>
       <c r="G49" s="77"/>
       <c r="H49" s="104"/>
-      <c r="I49" s="273"/>
+      <c r="I49" s="282"/>
       <c r="J49" s="8"/>
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
@@ -22163,26 +24868,26 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
     <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="F7:F8"/>
     <mergeCell ref="E30:E31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23104,21 +25809,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -23173,13 +25878,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="282" t="s">
+      <c r="D3" s="290" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="282" t="s">
+      <c r="F3" s="290" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -23188,24 +25893,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="288" t="s">
+      <c r="J3" s="296" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="289" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -23217,20 +25922,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="282"/>
+      <c r="D4" s="290"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="282"/>
+      <c r="F4" s="290"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="288"/>
+      <c r="J4" s="296"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="289"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -23269,7 +25974,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -23277,7 +25982,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -23322,13 +26027,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -23377,13 +26082,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="288" t="s">
+      <c r="F7" s="296" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="284" t="s">
+      <c r="J7" s="292" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -23431,11 +26136,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="288"/>
+      <c r="F8" s="296"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="284"/>
+      <c r="J8" s="292"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -23479,7 +26184,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="285" t="s">
+      <c r="F9" s="293" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -23519,7 +26224,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="285"/>
+      <c r="F10" s="293"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -23645,7 +26350,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="289" t="s">
+      <c r="I13" s="297" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -23686,7 +26391,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="289"/>
+      <c r="I14" s="297"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -23746,13 +26451,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="296" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="290" t="s">
+      <c r="C16" s="298" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -23787,9 +26492,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="288"/>
-      <c r="B17" s="288"/>
-      <c r="C17" s="291"/>
+      <c r="A17" s="296"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="299"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -23822,7 +26527,7 @@
     <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="289" t="s">
+      <c r="C18" s="297" t="s">
         <v>82</v>
       </c>
       <c r="D18" s="61"/>
@@ -23840,7 +26545,7 @@
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="147"/>
-      <c r="C19" s="289"/>
+      <c r="C19" s="297"/>
       <c r="D19" s="125"/>
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
@@ -23999,13 +26704,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -24065,7 +26770,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -24099,7 +26804,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -24129,7 +26834,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -24159,7 +26864,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -24183,7 +26888,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="281" t="s">
+      <c r="E34" s="289" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -24208,7 +26913,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="281"/>
+      <c r="E35" s="289"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -24227,7 +26932,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -24247,7 +26952,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -25717,21 +28422,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -25786,13 +28491,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="282" t="s">
+      <c r="D3" s="290" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="282" t="s">
+      <c r="F3" s="290" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -25801,24 +28506,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="288" t="s">
+      <c r="J3" s="296" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="289" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -25830,20 +28535,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="282"/>
+      <c r="D4" s="290"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="282"/>
+      <c r="F4" s="290"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="288"/>
+      <c r="J4" s="296"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="289"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -25882,7 +28587,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -25890,7 +28595,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -25935,13 +28640,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -25985,13 +28690,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="288" t="s">
+      <c r="F7" s="296" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="284" t="s">
+      <c r="J7" s="292" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -26039,11 +28744,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="288"/>
+      <c r="F8" s="296"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="284"/>
+      <c r="J8" s="292"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -26087,7 +28792,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="285" t="s">
+      <c r="F9" s="293" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -26127,7 +28832,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="285"/>
+      <c r="F10" s="293"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -26253,7 +28958,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="289" t="s">
+      <c r="I13" s="297" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -26294,7 +28999,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="289"/>
+      <c r="I14" s="297"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -26329,7 +29034,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="289" t="s">
+      <c r="I15" s="297" t="s">
         <v>82</v>
       </c>
       <c r="J15" s="60"/>
@@ -26356,13 +29061,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="296" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="290" t="s">
+      <c r="C16" s="298" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -26372,7 +29077,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="289"/>
+      <c r="I16" s="297"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -26397,15 +29102,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="288"/>
-      <c r="B17" s="288"/>
-      <c r="C17" s="291"/>
+      <c r="A17" s="296"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="299"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="285" t="s">
+      <c r="I17" s="293" t="s">
         <v>139</v>
       </c>
       <c r="J17" s="71"/>
@@ -26440,7 +29145,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="285"/>
+      <c r="I18" s="293"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -26612,13 +29317,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -26678,7 +29383,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -26712,7 +29417,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -26742,7 +29447,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -26772,7 +29477,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -26798,7 +29503,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="281" t="s">
+      <c r="E34" s="289" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -26821,7 +29526,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="281"/>
+      <c r="E35" s="289"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -26841,7 +29546,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -26858,7 +29563,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -28326,21 +31031,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -28393,13 +31098,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="282" t="s">
+      <c r="D3" s="290" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="282" t="s">
+      <c r="F3" s="290" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -28408,24 +31113,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="288" t="s">
+      <c r="J3" s="296" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="289" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -28437,20 +31142,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="282"/>
+      <c r="D4" s="290"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="282"/>
+      <c r="F4" s="290"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="288"/>
+      <c r="J4" s="296"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="289"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -28489,7 +31194,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -28497,7 +31202,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -28542,13 +31247,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -28592,13 +31297,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="288" t="s">
+      <c r="F7" s="296" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="284" t="s">
+      <c r="J7" s="292" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -28646,13 +31351,13 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="288"/>
+      <c r="F8" s="296"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="J8" s="284"/>
+      <c r="J8" s="292"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -28696,13 +31401,13 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="285" t="s">
+      <c r="F9" s="293" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
       <c r="H9" s="30"/>
       <c r="I9" s="134"/>
-      <c r="J9" s="289" t="s">
+      <c r="J9" s="297" t="s">
         <v>82</v>
       </c>
       <c r="K9" s="54"/>
@@ -28738,11 +31443,11 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="285"/>
+      <c r="F10" s="293"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
-      <c r="J10" s="289"/>
+      <c r="J10" s="297"/>
       <c r="K10" s="6"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
@@ -28865,7 +31570,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="289" t="s">
+      <c r="I13" s="297" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -28906,7 +31611,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="289"/>
+      <c r="I14" s="297"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -28941,7 +31646,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="295" t="s">
+      <c r="I15" s="303" t="s">
         <v>139</v>
       </c>
       <c r="J15" s="60"/>
@@ -28968,13 +31673,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="296" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="290" t="s">
+      <c r="C16" s="298" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -28984,7 +31689,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="295"/>
+      <c r="I16" s="303"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -29009,9 +31714,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="288"/>
-      <c r="B17" s="288"/>
-      <c r="C17" s="291"/>
+      <c r="A17" s="296"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="299"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -29222,13 +31927,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -29288,7 +31993,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -29322,7 +32027,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -29352,7 +32057,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -29377,7 +32082,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -29398,7 +32103,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="281" t="s">
+      <c r="E34" s="289" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -29421,7 +32126,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="281"/>
+      <c r="E35" s="289"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -29441,7 +32146,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -29461,7 +32166,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -30928,21 +33633,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -30997,13 +33702,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="282" t="s">
+      <c r="D3" s="290" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="282" t="s">
+      <c r="F3" s="290" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -31012,24 +33717,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="288" t="s">
+      <c r="J3" s="296" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="289" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -31041,20 +33746,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="282"/>
+      <c r="D4" s="290"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="282"/>
+      <c r="F4" s="290"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="288"/>
+      <c r="J4" s="296"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="289"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -31093,7 +33798,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -31101,7 +33806,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -31146,13 +33851,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -31199,7 +33904,7 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="288" t="s">
+      <c r="F7" s="296" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
@@ -31207,7 +33912,7 @@
       <c r="I7" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="284" t="s">
+      <c r="J7" s="292" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -31255,10 +33960,10 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="288"/>
+      <c r="F8" s="296"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
-      <c r="J8" s="284"/>
+      <c r="J8" s="292"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -31302,7 +34007,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="285" t="s">
+      <c r="F9" s="293" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -31342,7 +34047,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="285"/>
+      <c r="F10" s="293"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -31469,7 +34174,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="289" t="s">
+      <c r="I13" s="297" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -31507,7 +34212,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="289"/>
+      <c r="I14" s="297"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -31542,7 +34247,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="289" t="s">
+      <c r="I15" s="297" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -31569,13 +34274,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="296" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="285" t="s">
+      <c r="C16" s="293" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -31585,7 +34290,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="289"/>
+      <c r="I16" s="297"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -31610,15 +34315,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="288"/>
-      <c r="B17" s="288"/>
-      <c r="C17" s="285"/>
+      <c r="A17" s="296"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="293"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="289" t="s">
+      <c r="I17" s="297" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -31653,7 +34358,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="289"/>
+      <c r="I18" s="297"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -31823,13 +34528,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -31889,7 +34594,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -31923,7 +34628,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -31953,7 +34658,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -31979,7 +34684,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -32001,7 +34706,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="281" t="s">
+      <c r="E34" s="289" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -32024,7 +34729,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="281"/>
+      <c r="E35" s="289"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -32044,7 +34749,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -32061,7 +34766,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -33531,21 +36236,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -33600,13 +36305,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="282" t="s">
+      <c r="D3" s="290" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="282" t="s">
+      <c r="F3" s="290" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -33615,24 +36320,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="288" t="s">
+      <c r="J3" s="296" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="289" t="s">
+      <c r="M3" s="297" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -33644,20 +36349,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="282"/>
+      <c r="D4" s="290"/>
       <c r="E4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="282"/>
+      <c r="F4" s="290"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="288"/>
+      <c r="J4" s="296"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="289"/>
+      <c r="M4" s="297"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -33696,7 +36401,7 @@
       <c r="E5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -33704,7 +36409,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -33749,13 +36454,13 @@
       <c r="E6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -33802,13 +36507,13 @@
       <c r="E7" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="288" t="s">
+      <c r="F7" s="296" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="284" t="s">
+      <c r="J7" s="292" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -33854,11 +36559,11 @@
         <v>17</v>
       </c>
       <c r="E8" s="30"/>
-      <c r="F8" s="288"/>
+      <c r="F8" s="296"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="284"/>
+      <c r="J8" s="292"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -33903,7 +36608,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="285" t="s">
+      <c r="F9" s="293" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -33943,7 +36648,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="285"/>
+      <c r="F10" s="293"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -34070,7 +36775,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="289" t="s">
+      <c r="I13" s="297" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -34111,7 +36816,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="289"/>
+      <c r="I14" s="297"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -34146,7 +36851,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="289" t="s">
+      <c r="I15" s="297" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -34173,13 +36878,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="296" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="285" t="s">
+      <c r="C16" s="293" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -34189,7 +36894,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="289"/>
+      <c r="I16" s="297"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -34214,15 +36919,15 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="288"/>
-      <c r="B17" s="288"/>
-      <c r="C17" s="285"/>
+      <c r="A17" s="296"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="293"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="289" t="s">
+      <c r="I17" s="297" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -34257,7 +36962,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="289"/>
+      <c r="I18" s="297"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -34428,13 +37133,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -34494,7 +37199,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -34528,7 +37233,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -34556,7 +37261,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -34582,7 +37287,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -34604,7 +37309,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="281" t="s">
+      <c r="E34" s="289" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -34627,7 +37332,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="281"/>
+      <c r="E35" s="289"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -34647,7 +37352,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -34667,7 +37372,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -35251,18 +37956,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="193" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="303" t="s">
+      <c r="A1" s="311" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
-      <c r="F1" s="304"/>
-      <c r="G1" s="304"/>
-      <c r="H1" s="304"/>
-      <c r="I1" s="305"/>
-      <c r="J1" s="305"/>
+      <c r="B1" s="312"/>
+      <c r="C1" s="312"/>
+      <c r="D1" s="312"/>
+      <c r="E1" s="312"/>
+      <c r="F1" s="312"/>
+      <c r="G1" s="312"/>
+      <c r="H1" s="312"/>
+      <c r="I1" s="313"/>
+      <c r="J1" s="313"/>
       <c r="K1" s="190"/>
       <c r="L1" s="190"/>
       <c r="M1" s="191"/>
@@ -35368,22 +38073,22 @@
       <c r="C3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="282" t="s">
+      <c r="D3" s="290" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="201" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="296" t="s">
+      <c r="F3" s="304" t="s">
         <v>160</v>
       </c>
       <c r="H3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="284" t="s">
+      <c r="I3" s="292" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="297" t="s">
+      <c r="K3" s="305" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="2"/>
@@ -35399,16 +38104,16 @@
       <c r="C4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="282"/>
+      <c r="D4" s="290"/>
       <c r="E4" s="201" t="s">
         <v>162</v>
       </c>
-      <c r="F4" s="296"/>
+      <c r="F4" s="304"/>
       <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="284"/>
-      <c r="K4" s="298"/>
+      <c r="I4" s="292"/>
+      <c r="K4" s="306"/>
       <c r="L4" s="203" t="s">
         <v>163</v>
       </c>
@@ -35421,13 +38126,13 @@
       <c r="E5" s="129" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="296" t="s">
+      <c r="F5" s="304" t="s">
         <v>165</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="282" t="s">
+      <c r="I5" s="290" t="s">
         <v>166</v>
       </c>
       <c r="K5" s="2"/>
@@ -35441,11 +38146,11 @@
       <c r="E6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="296"/>
+      <c r="F6" s="304"/>
       <c r="H6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="282"/>
+      <c r="I6" s="290"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -35460,10 +38165,10 @@
       <c r="E7" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F7" s="282" t="s">
+      <c r="F7" s="290" t="s">
         <v>168</v>
       </c>
-      <c r="I7" s="282" t="s">
+      <c r="I7" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K7" s="2"/>
@@ -35477,17 +38182,17 @@
       <c r="E8" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="282"/>
-      <c r="I8" s="282"/>
+      <c r="F8" s="290"/>
+      <c r="I8" s="290"/>
       <c r="K8" s="2"/>
       <c r="L8" s="206"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="290" t="s">
+      <c r="A9" s="298" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="282" t="s">
+      <c r="B9" s="290" t="s">
         <v>171</v>
       </c>
       <c r="C9" s="207" t="s">
@@ -35496,7 +38201,7 @@
       <c r="E9" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="296" t="s">
+      <c r="F9" s="304" t="s">
         <v>173</v>
       </c>
       <c r="K9" s="2"/>
@@ -35506,15 +38211,15 @@
       <c r="P9"/>
     </row>
     <row r="10" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="291"/>
-      <c r="B10" s="282"/>
+      <c r="A10" s="299"/>
+      <c r="B10" s="290"/>
       <c r="C10" s="208" t="s">
         <v>174</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>175</v>
       </c>
-      <c r="F10" s="296"/>
+      <c r="F10" s="304"/>
       <c r="K10" s="209"/>
       <c r="L10" s="2"/>
       <c r="M10" s="206"/>
@@ -35541,7 +38246,7 @@
       <c r="E11" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="F11" s="288" t="s">
+      <c r="F11" s="296" t="s">
         <v>177</v>
       </c>
       <c r="K11" s="209"/>
@@ -35570,7 +38275,7 @@
       <c r="E12" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="288"/>
+      <c r="F12" s="296"/>
       <c r="G12" s="212" t="s">
         <v>179</v>
       </c>
@@ -35609,10 +38314,10 @@
       <c r="E13" s="183" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="299" t="s">
+      <c r="F13" s="307" t="s">
         <v>184</v>
       </c>
-      <c r="H13" s="290" t="s">
+      <c r="H13" s="298" t="s">
         <v>185</v>
       </c>
       <c r="K13" s="2"/>
@@ -35642,8 +38347,8 @@
       <c r="E14" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="F14" s="300"/>
-      <c r="H14" s="291"/>
+      <c r="F14" s="308"/>
+      <c r="H14" s="299"/>
       <c r="K14" s="2"/>
       <c r="L14" s="6"/>
       <c r="M14" s="2"/>
@@ -35670,10 +38375,10 @@
       <c r="E15" s="183" t="s">
         <v>189</v>
       </c>
-      <c r="F15" s="282" t="s">
+      <c r="F15" s="290" t="s">
         <v>190</v>
       </c>
-      <c r="H15" s="297" t="s">
+      <c r="H15" s="305" t="s">
         <v>45</v>
       </c>
       <c r="K15" s="2"/>
@@ -35698,8 +38403,8 @@
       <c r="C16" s="183" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="282"/>
-      <c r="H16" s="298"/>
+      <c r="F16" s="290"/>
+      <c r="H16" s="306"/>
       <c r="K16" s="2"/>
       <c r="L16" s="209"/>
       <c r="M16" s="8"/>
@@ -35726,7 +38431,7 @@
       </c>
       <c r="D17" s="206"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="301" t="s">
+      <c r="F17" s="309" t="s">
         <v>193</v>
       </c>
       <c r="G17" s="2"/>
@@ -35743,7 +38448,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="302"/>
+      <c r="F18" s="310"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="209"/>
@@ -35794,7 +38499,7 @@
       <c r="B20" s="133" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="282" t="s">
+      <c r="C20" s="290" t="s">
         <v>197</v>
       </c>
       <c r="D20" s="2"/>
@@ -35826,7 +38531,7 @@
         <v>199</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="282"/>
+      <c r="C21" s="290"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="219" t="s">
@@ -35834,7 +38539,7 @@
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="297" t="s">
+      <c r="I21" s="305" t="s">
         <v>82</v>
       </c>
       <c r="J21" s="209"/>
@@ -35868,7 +38573,7 @@
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="298"/>
+      <c r="I22" s="306"/>
       <c r="J22" s="209"/>
       <c r="K22" s="101" t="s">
         <v>40</v>
@@ -37537,21 +40242,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -37606,13 +40311,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="289" t="s">
+      <c r="D3" s="297" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="282" t="s">
+      <c r="F3" s="290" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -37621,24 +40326,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="289" t="s">
+      <c r="J3" s="297" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="306" t="s">
+      <c r="M3" s="314" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -37652,20 +40357,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="289"/>
+      <c r="D4" s="297"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="282"/>
+      <c r="F4" s="290"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="289"/>
+      <c r="J4" s="297"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="306"/>
+      <c r="M4" s="314"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -37704,7 +40409,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -37712,7 +40417,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -37757,13 +40462,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -37807,13 +40512,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="288" t="s">
+      <c r="F7" s="296" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="284" t="s">
+      <c r="J7" s="292" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -37861,11 +40566,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="288"/>
+      <c r="F8" s="296"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="284"/>
+      <c r="J8" s="292"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -37910,7 +40615,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="285" t="s">
+      <c r="F9" s="293" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -37950,7 +40655,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="285"/>
+      <c r="F10" s="293"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -38172,13 +40877,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="296" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="289" t="s">
+      <c r="C16" s="297" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -38213,9 +40918,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="288"/>
-      <c r="B17" s="288"/>
-      <c r="C17" s="289"/>
+      <c r="A17" s="296"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="297"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -38425,13 +41130,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -38491,7 +41196,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -38523,7 +41228,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -38551,7 +41256,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -38579,7 +41284,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -38603,7 +41308,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="281" t="s">
+      <c r="E34" s="289" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -38626,7 +41331,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="281"/>
+      <c r="E35" s="289"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -38646,7 +41351,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -38666,7 +41371,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -40131,21 +42836,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="301" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
-      <c r="M1" s="293"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -40200,13 +42905,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="289" t="s">
+      <c r="D3" s="297" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="282" t="s">
+      <c r="F3" s="290" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -40215,24 +42920,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="289" t="s">
+      <c r="J3" s="297" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="306" t="s">
+      <c r="M3" s="314" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="286" t="s">
+      <c r="Q3" s="294" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="287"/>
+      <c r="R3" s="295"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="279" t="s">
+      <c r="T3" s="287" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="280"/>
+      <c r="U3" s="288"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -40246,20 +42951,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="289"/>
+      <c r="D4" s="297"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="282"/>
+      <c r="F4" s="290"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="289"/>
+      <c r="J4" s="297"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="306"/>
+      <c r="M4" s="314"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -40298,7 +43003,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="285" t="s">
+      <c r="F5" s="293" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -40306,7 +43011,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="282" t="s">
+      <c r="J5" s="290" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -40351,13 +43056,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="293"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="282"/>
+      <c r="J6" s="290"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -40401,13 +43106,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="288" t="s">
+      <c r="F7" s="296" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="284" t="s">
+      <c r="J7" s="292" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -40455,11 +43160,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="288"/>
+      <c r="F8" s="296"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="284"/>
+      <c r="J8" s="292"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -40504,7 +43209,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="285" t="s">
+      <c r="F9" s="293" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -40544,7 +43249,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="285"/>
+      <c r="F10" s="293"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -40766,13 +43471,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="296" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="288" t="s">
+      <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="289" t="s">
+      <c r="C16" s="297" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -40807,9 +43512,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="288"/>
-      <c r="B17" s="288"/>
-      <c r="C17" s="289"/>
+      <c r="A17" s="296"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="297"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -41019,13 +43724,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
+      <c r="B28" s="302"/>
+      <c r="C28" s="302"/>
+      <c r="D28" s="302"/>
+      <c r="E28" s="302"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -41085,7 +43790,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="283" t="s">
+      <c r="E30" s="291" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -41119,7 +43824,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="283"/>
+      <c r="E31" s="291"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -41147,7 +43852,7 @@
       <c r="D32" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="283" t="s">
+      <c r="E32" s="291" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -41175,7 +43880,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="283"/>
+      <c r="E33" s="291"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -41199,7 +43904,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="281" t="s">
+      <c r="E34" s="289" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -41224,7 +43929,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="281"/>
+      <c r="E35" s="289"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -41246,7 +43951,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="283" t="s">
+      <c r="E36" s="291" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -41268,7 +43973,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="283"/>
+      <c r="E37" s="291"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>

--- a/raw/D3.xlsx
+++ b/raw/D3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="4" activeTab="15"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="4" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="30-2" sheetId="34" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="20" sheetId="47" r:id="rId14"/>
     <sheet name="20-2" sheetId="48" r:id="rId15"/>
     <sheet name="21" sheetId="49" r:id="rId16"/>
+    <sheet name="22" sheetId="50" r:id="rId17"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -518,6 +519,78 @@
           </rPr>
           <t>Даулет
 87025167087</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments17.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="J7" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Алібек
+87012894507</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H13" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Аслан
+87014988298</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Даулет
+87025167087</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K35" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Сандыбай Берды
+87759316709</t>
         </r>
       </text>
     </comment>
@@ -1221,7 +1294,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2383" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="273">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -2860,7 +2933,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="316">
+  <cellXfs count="324">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3697,10 +3770,49 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3717,28 +3829,22 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3761,15 +3867,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -4970,21 +5067,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -5039,13 +5136,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="290" t="s">
+      <c r="D3" s="298" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="298" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -5061,20 +5158,20 @@
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="299" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -5086,11 +5183,11 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="290"/>
+      <c r="D4" s="298"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="290"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
@@ -5099,7 +5196,7 @@
       <c r="J4" s="296"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="299"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -5138,7 +5235,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -5146,7 +5243,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -5191,13 +5288,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -5249,7 +5346,7 @@
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="292" t="s">
+      <c r="J7" s="305" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -5301,7 +5398,7 @@
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="292"/>
+      <c r="J8" s="305"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -5345,7 +5442,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="293" t="s">
+      <c r="F9" s="306" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -5385,7 +5482,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="293"/>
+      <c r="F10" s="306"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -5510,7 +5607,7 @@
         <v>115</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="297" t="s">
+      <c r="H13" s="299" t="s">
         <v>82</v>
       </c>
       <c r="I13" s="30"/>
@@ -5549,7 +5646,7 @@
       <c r="F14" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="297"/>
+      <c r="H14" s="299"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -5584,7 +5681,7 @@
         <v>83</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="297" t="s">
+      <c r="H15" s="299" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="30"/>
@@ -5621,7 +5718,7 @@
         <v>81</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="297"/>
+      <c r="H16" s="299"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -5653,7 +5750,7 @@
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="298" t="s">
+      <c r="H17" s="309" t="s">
         <v>45</v>
       </c>
       <c r="I17" s="30"/>
@@ -5688,7 +5785,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="299"/>
+      <c r="H18" s="310"/>
       <c r="I18" s="30"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
@@ -5863,13 +5960,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -5929,7 +6026,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -5963,7 +6060,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -5993,7 +6090,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="8"/>
@@ -6019,7 +6116,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
       <c r="I33" s="30"/>
@@ -6042,7 +6139,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="289" t="s">
+      <c r="E34" s="303" t="s">
         <v>133</v>
       </c>
       <c r="G34" s="8"/>
@@ -6063,7 +6160,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="289"/>
+      <c r="E35" s="303"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
       <c r="I35" s="30"/>
@@ -6082,7 +6179,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -6102,7 +6199,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -6569,7 +6666,7 @@
       <c r="S65"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A66" s="300" t="s">
+      <c r="A66" s="295" t="s">
         <v>139</v>
       </c>
       <c r="L66" s="119" t="s">
@@ -6581,7 +6678,7 @@
       <c r="S66"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A67" s="300"/>
+      <c r="A67" s="295"/>
       <c r="L67" s="119" t="s">
         <v>95</v>
       </c>
@@ -6633,14 +6730,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A28:E28"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="J5:J6"/>
@@ -6656,6 +6745,14 @@
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="H17:H18"/>
     <mergeCell ref="H19:H20"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A28:E28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -7572,21 +7669,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -7645,7 +7742,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="298" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -7654,24 +7751,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="292" t="s">
+      <c r="J3" s="305" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="314" t="s">
+      <c r="M3" s="322" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -7689,16 +7786,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="290"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="292"/>
+      <c r="J4" s="305"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="314"/>
+      <c r="M4" s="322"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -7737,7 +7834,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -7745,7 +7842,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -7790,13 +7887,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -7843,7 +7940,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="293" t="s">
+      <c r="F7" s="306" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -7895,7 +7992,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="293"/>
+      <c r="F8" s="306"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -8250,7 +8347,7 @@
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="297" t="s">
+      <c r="H17" s="299" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -8285,7 +8382,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="297"/>
+      <c r="H18" s="299"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -8302,7 +8399,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="297" t="s">
+      <c r="H19" s="299" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -8327,7 +8424,7 @@
       <c r="E20" s="240"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="297"/>
+      <c r="H20" s="299"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -8346,7 +8443,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="297" t="s">
+      <c r="H21" s="299" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -8364,7 +8461,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="240"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="297"/>
+      <c r="H22" s="299"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -8461,13 +8558,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -8527,7 +8624,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -8561,7 +8658,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -8588,7 +8685,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -8616,7 +8713,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -8640,7 +8737,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="289" t="s">
+      <c r="E34" s="303" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -8665,7 +8762,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="289"/>
+      <c r="E35" s="303"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -8687,7 +8784,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -8709,7 +8806,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -9241,18 +9338,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="H15:H16"/>
@@ -9261,6 +9346,18 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -10177,21 +10274,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -10250,7 +10347,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="298" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -10259,24 +10356,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="292" t="s">
+      <c r="J3" s="305" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="299" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -10294,16 +10391,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="290"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="292"/>
+      <c r="J4" s="305"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="299"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -10342,7 +10439,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -10350,7 +10447,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -10395,13 +10492,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -10448,7 +10545,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="293" t="s">
+      <c r="F7" s="306" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -10500,7 +10597,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="293"/>
+      <c r="F8" s="306"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -10855,7 +10952,7 @@
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="297" t="s">
+      <c r="H17" s="299" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -10890,7 +10987,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="297"/>
+      <c r="H18" s="299"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -10907,7 +11004,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="297" t="s">
+      <c r="H19" s="299" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -10932,7 +11029,7 @@
       <c r="E20" s="248"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="297"/>
+      <c r="H20" s="299"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -10951,7 +11048,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="297" t="s">
+      <c r="H21" s="299" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -10969,7 +11066,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="248"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="297"/>
+      <c r="H22" s="299"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -11066,13 +11163,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -11132,7 +11229,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -11166,7 +11263,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -11196,7 +11293,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -11224,7 +11321,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -11248,7 +11345,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="289" t="s">
+      <c r="E34" s="303" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -11272,7 +11369,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="289"/>
+      <c r="E35" s="303"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -11294,7 +11391,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -11314,7 +11411,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -11846,13 +11943,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="B16:B17"/>
@@ -11866,6 +11956,13 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="H15:H16"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -12782,21 +12879,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -12851,13 +12948,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="297" t="s">
+      <c r="D3" s="299" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="298" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -12866,24 +12963,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="292" t="s">
+      <c r="J3" s="305" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="299" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -12897,20 +12994,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="297"/>
+      <c r="D4" s="299"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="290"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="292"/>
+      <c r="J4" s="305"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="299"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -12949,7 +13046,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -12957,7 +13054,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -13002,13 +13099,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -13055,13 +13152,13 @@
       <c r="E7" s="260" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="315" t="s">
+      <c r="F7" s="323" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="297" t="s">
+      <c r="J7" s="299" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -13109,11 +13206,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="315"/>
+      <c r="F8" s="323"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="297"/>
+      <c r="J8" s="299"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -13424,7 +13521,7 @@
       <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="297" t="s">
+      <c r="C16" s="299" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -13461,7 +13558,7 @@
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="296"/>
       <c r="B17" s="296"/>
-      <c r="C17" s="297"/>
+      <c r="C17" s="299"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="259" t="s">
@@ -13672,13 +13769,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -13738,7 +13835,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -13772,7 +13869,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -13802,7 +13899,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -13832,7 +13929,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -13856,7 +13953,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="289" t="s">
+      <c r="E34" s="303" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -13880,7 +13977,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="289"/>
+      <c r="E35" s="303"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -13899,7 +13996,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -13919,7 +14016,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -14449,12 +14546,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="J7:J8"/>
@@ -14469,6 +14560,12 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="Q3:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -15385,21 +15482,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -15454,13 +15551,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="290" t="s">
+      <c r="D3" s="298" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="298" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -15469,24 +15566,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="292" t="s">
+      <c r="J3" s="305" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="299" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -15500,20 +15597,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="290"/>
+      <c r="D4" s="298"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="290"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="292"/>
+      <c r="J4" s="305"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="299"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -15552,7 +15649,7 @@
       <c r="E5" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -15560,7 +15657,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -15605,13 +15702,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -15658,13 +15755,13 @@
       <c r="E7" s="260" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="315" t="s">
+      <c r="F7" s="323" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="297" t="s">
+      <c r="J7" s="299" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -15712,11 +15809,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="315"/>
+      <c r="F8" s="323"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="297"/>
+      <c r="J8" s="299"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -15928,7 +16025,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="297" t="s">
+      <c r="I13" s="299" t="s">
         <v>45</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -15964,7 +16061,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="297"/>
+      <c r="I14" s="299"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -16030,7 +16127,7 @@
       <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="297" t="s">
+      <c r="C16" s="299" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -16067,7 +16164,7 @@
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="296"/>
       <c r="B17" s="296"/>
-      <c r="C17" s="297"/>
+      <c r="C17" s="299"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="269" t="s">
@@ -16278,13 +16375,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -16344,7 +16441,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -16378,7 +16475,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -16406,7 +16503,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -16434,7 +16531,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -16458,7 +16555,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="289" t="s">
+      <c r="E34" s="303" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -16480,7 +16577,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="289"/>
+      <c r="E35" s="303"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -16500,7 +16597,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -16520,7 +16617,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -17054,18 +17151,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="D3:D4"/>
@@ -17075,6 +17160,18 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17991,21 +18088,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -18060,13 +18157,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="290" t="s">
+      <c r="D3" s="298" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="298" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -18075,24 +18172,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="292" t="s">
+      <c r="J3" s="305" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="299" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -18106,20 +18203,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="290"/>
+      <c r="D4" s="298"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="290"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="292"/>
+      <c r="J4" s="305"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="299"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -18158,7 +18255,7 @@
       <c r="E5" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -18166,7 +18263,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -18211,13 +18308,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -18264,13 +18361,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="293" t="s">
+      <c r="F7" s="306" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="297" t="s">
+      <c r="J7" s="299" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -18318,11 +18415,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="293"/>
+      <c r="F8" s="306"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="297"/>
+      <c r="J8" s="299"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -18634,7 +18731,7 @@
       <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="297" t="s">
+      <c r="C16" s="299" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -18671,7 +18768,7 @@
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="296"/>
       <c r="B17" s="296"/>
-      <c r="C17" s="297"/>
+      <c r="C17" s="299"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -18704,7 +18801,7 @@
     <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="297" t="s">
+      <c r="C18" s="299" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="61"/>
@@ -18723,7 +18820,7 @@
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="273"/>
-      <c r="C19" s="297"/>
+      <c r="C19" s="299"/>
       <c r="D19" s="125"/>
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
@@ -18883,13 +18980,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -18949,7 +19046,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -18983,7 +19080,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -19011,7 +19108,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -19039,7 +19136,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -19063,7 +19160,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="289" t="s">
+      <c r="E34" s="303" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -19087,7 +19184,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="289"/>
+      <c r="E35" s="303"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -19107,7 +19204,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -19127,7 +19224,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -19659,18 +19756,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
@@ -19680,6 +19765,18 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20600,21 +20697,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -20669,13 +20766,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="290" t="s">
+      <c r="D3" s="298" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="293" t="s">
+      <c r="F3" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -20684,24 +20781,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="292" t="s">
+      <c r="J3" s="305" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="299" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -20712,20 +20809,20 @@
       <c r="C4" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="290"/>
+      <c r="D4" s="298"/>
       <c r="E4" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="F4" s="293"/>
+      <c r="F4" s="306"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="292"/>
+      <c r="J4" s="305"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="299"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -20766,7 +20863,7 @@
       <c r="E5" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>257</v>
       </c>
       <c r="G5" s="8"/>
@@ -20774,7 +20871,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -20819,13 +20916,13 @@
       <c r="E6" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="278"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -20869,13 +20966,13 @@
       <c r="E7" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="293" t="s">
+      <c r="F7" s="306" t="s">
         <v>110</v>
       </c>
       <c r="G7" s="278"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="297" t="s">
+      <c r="J7" s="299" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -20923,11 +21020,11 @@
       <c r="E8" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F8" s="293"/>
+      <c r="F8" s="306"/>
       <c r="G8" s="62"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="297"/>
+      <c r="J8" s="299"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -21139,7 +21236,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="297" t="s">
+      <c r="I13" s="299" t="s">
         <v>45</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -21175,7 +21272,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="297"/>
+      <c r="I14" s="299"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -21243,7 +21340,7 @@
       <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="297" t="s">
+      <c r="C16" s="299" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -21280,7 +21377,7 @@
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="296"/>
       <c r="B17" s="296"/>
-      <c r="C17" s="297"/>
+      <c r="C17" s="299"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="128" t="s">
@@ -21492,13 +21589,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -21558,7 +21655,7 @@
       <c r="D30" s="93" t="s">
         <v>251</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -21592,7 +21689,7 @@
       <c r="D31" s="93" t="s">
         <v>252</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -21620,7 +21717,7 @@
       <c r="D32" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>259</v>
       </c>
       <c r="F32" s="8"/>
@@ -21648,7 +21745,7 @@
       <c r="D33" s="93" t="s">
         <v>253</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -21672,7 +21769,7 @@
       <c r="D34" s="93" t="s">
         <v>254</v>
       </c>
-      <c r="E34" s="291" t="s">
+      <c r="E34" s="304" t="s">
         <v>260</v>
       </c>
       <c r="F34" s="8"/>
@@ -21694,7 +21791,7 @@
       <c r="D35" s="93" t="s">
         <v>255</v>
       </c>
-      <c r="E35" s="291"/>
+      <c r="E35" s="304"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -21714,7 +21811,7 @@
       <c r="D36" s="93" t="s">
         <v>256</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>261</v>
       </c>
       <c r="F36" s="53"/>
@@ -21734,7 +21831,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -22266,27 +22363,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="A28:E28"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="E30:E31"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="Q3:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -23204,21 +23301,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -23273,13 +23370,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="290" t="s">
+      <c r="D3" s="298" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="293" t="s">
+      <c r="F3" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -23288,25 +23385,25 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="292" t="s">
+      <c r="J3" s="305" t="s">
         <v>10</v>
       </c>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="299" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -23317,20 +23414,20 @@
       <c r="C4" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="290"/>
+      <c r="D4" s="298"/>
       <c r="E4" s="258" t="s">
         <v>182</v>
       </c>
-      <c r="F4" s="293"/>
+      <c r="F4" s="306"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="292"/>
+      <c r="J4" s="305"/>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="299"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -23371,7 +23468,7 @@
       <c r="E5" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>257</v>
       </c>
       <c r="G5" s="8"/>
@@ -23379,7 +23476,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="8"/>
@@ -23423,13 +23520,13 @@
       <c r="E6" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="278"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -23476,13 +23573,13 @@
       <c r="E7" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="293" t="s">
+      <c r="F7" s="306" t="s">
         <v>110</v>
       </c>
       <c r="G7" s="278"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="297" t="s">
+      <c r="J7" s="299" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -23530,11 +23627,11 @@
       <c r="E8" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F8" s="293"/>
+      <c r="F8" s="306"/>
       <c r="G8" s="62"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="297"/>
+      <c r="J8" s="299"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -23745,7 +23842,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="297" t="s">
+      <c r="I13" s="299" t="s">
         <v>45</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -23781,7 +23878,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="297"/>
+      <c r="I14" s="299"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -23847,7 +23944,7 @@
       <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="297" t="s">
+      <c r="C16" s="299" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -23884,7 +23981,7 @@
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="296"/>
       <c r="B17" s="296"/>
-      <c r="C17" s="297"/>
+      <c r="C17" s="299"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="G17" s="6"/>
@@ -24093,13 +24190,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -24159,7 +24256,7 @@
       <c r="D30" s="93" t="s">
         <v>251</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -24193,7 +24290,7 @@
       <c r="D31" s="93" t="s">
         <v>252</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -24223,7 +24320,7 @@
       <c r="D32" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>259</v>
       </c>
       <c r="F32" s="8"/>
@@ -24251,7 +24348,7 @@
       <c r="D33" s="93" t="s">
         <v>253</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -24275,7 +24372,7 @@
       <c r="D34" s="93" t="s">
         <v>254</v>
       </c>
-      <c r="E34" s="291" t="s">
+      <c r="E34" s="304" t="s">
         <v>260</v>
       </c>
       <c r="F34" s="8"/>
@@ -24299,7 +24396,7 @@
       <c r="D35" s="93" t="s">
         <v>255</v>
       </c>
-      <c r="E35" s="291"/>
+      <c r="E35" s="304"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -24319,7 +24416,7 @@
       <c r="D36" s="93" t="s">
         <v>256</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>261</v>
       </c>
       <c r="F36" s="53"/>
@@ -24339,7 +24436,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -24868,18 +24965,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
@@ -24889,6 +24974,2618 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:W72"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" style="98" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" style="25" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" style="25" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" style="25" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" customWidth="1"/>
+    <col min="14" max="14" width="21.26953125" customWidth="1"/>
+    <col min="15" max="15" width="9.7265625" customWidth="1"/>
+    <col min="16" max="16" width="7.7265625" customWidth="1"/>
+    <col min="17" max="17" width="6.453125" customWidth="1"/>
+    <col min="18" max="18" width="7.81640625" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" style="84" customWidth="1"/>
+    <col min="20" max="20" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="257" max="260" width="14.453125" customWidth="1"/>
+    <col min="261" max="261" width="15.453125" customWidth="1"/>
+    <col min="262" max="262" width="14.54296875" customWidth="1"/>
+    <col min="263" max="263" width="15.26953125" customWidth="1"/>
+    <col min="264" max="265" width="14.453125" customWidth="1"/>
+    <col min="266" max="266" width="13.1796875" customWidth="1"/>
+    <col min="267" max="269" width="14.453125" customWidth="1"/>
+    <col min="270" max="270" width="15.81640625" customWidth="1"/>
+    <col min="271" max="271" width="7.81640625" customWidth="1"/>
+    <col min="272" max="272" width="5.453125" customWidth="1"/>
+    <col min="273" max="273" width="6.453125" customWidth="1"/>
+    <col min="274" max="274" width="7.81640625" customWidth="1"/>
+    <col min="275" max="275" width="3" customWidth="1"/>
+    <col min="276" max="276" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="513" max="516" width="14.453125" customWidth="1"/>
+    <col min="517" max="517" width="15.453125" customWidth="1"/>
+    <col min="518" max="518" width="14.54296875" customWidth="1"/>
+    <col min="519" max="519" width="15.26953125" customWidth="1"/>
+    <col min="520" max="521" width="14.453125" customWidth="1"/>
+    <col min="522" max="522" width="13.1796875" customWidth="1"/>
+    <col min="523" max="525" width="14.453125" customWidth="1"/>
+    <col min="526" max="526" width="15.81640625" customWidth="1"/>
+    <col min="527" max="527" width="7.81640625" customWidth="1"/>
+    <col min="528" max="528" width="5.453125" customWidth="1"/>
+    <col min="529" max="529" width="6.453125" customWidth="1"/>
+    <col min="530" max="530" width="7.81640625" customWidth="1"/>
+    <col min="531" max="531" width="3" customWidth="1"/>
+    <col min="532" max="532" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="769" max="772" width="14.453125" customWidth="1"/>
+    <col min="773" max="773" width="15.453125" customWidth="1"/>
+    <col min="774" max="774" width="14.54296875" customWidth="1"/>
+    <col min="775" max="775" width="15.26953125" customWidth="1"/>
+    <col min="776" max="777" width="14.453125" customWidth="1"/>
+    <col min="778" max="778" width="13.1796875" customWidth="1"/>
+    <col min="779" max="781" width="14.453125" customWidth="1"/>
+    <col min="782" max="782" width="15.81640625" customWidth="1"/>
+    <col min="783" max="783" width="7.81640625" customWidth="1"/>
+    <col min="784" max="784" width="5.453125" customWidth="1"/>
+    <col min="785" max="785" width="6.453125" customWidth="1"/>
+    <col min="786" max="786" width="7.81640625" customWidth="1"/>
+    <col min="787" max="787" width="3" customWidth="1"/>
+    <col min="788" max="788" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1025" max="1028" width="14.453125" customWidth="1"/>
+    <col min="1029" max="1029" width="15.453125" customWidth="1"/>
+    <col min="1030" max="1030" width="14.54296875" customWidth="1"/>
+    <col min="1031" max="1031" width="15.26953125" customWidth="1"/>
+    <col min="1032" max="1033" width="14.453125" customWidth="1"/>
+    <col min="1034" max="1034" width="13.1796875" customWidth="1"/>
+    <col min="1035" max="1037" width="14.453125" customWidth="1"/>
+    <col min="1038" max="1038" width="15.81640625" customWidth="1"/>
+    <col min="1039" max="1039" width="7.81640625" customWidth="1"/>
+    <col min="1040" max="1040" width="5.453125" customWidth="1"/>
+    <col min="1041" max="1041" width="6.453125" customWidth="1"/>
+    <col min="1042" max="1042" width="7.81640625" customWidth="1"/>
+    <col min="1043" max="1043" width="3" customWidth="1"/>
+    <col min="1044" max="1044" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1281" max="1284" width="14.453125" customWidth="1"/>
+    <col min="1285" max="1285" width="15.453125" customWidth="1"/>
+    <col min="1286" max="1286" width="14.54296875" customWidth="1"/>
+    <col min="1287" max="1287" width="15.26953125" customWidth="1"/>
+    <col min="1288" max="1289" width="14.453125" customWidth="1"/>
+    <col min="1290" max="1290" width="13.1796875" customWidth="1"/>
+    <col min="1291" max="1293" width="14.453125" customWidth="1"/>
+    <col min="1294" max="1294" width="15.81640625" customWidth="1"/>
+    <col min="1295" max="1295" width="7.81640625" customWidth="1"/>
+    <col min="1296" max="1296" width="5.453125" customWidth="1"/>
+    <col min="1297" max="1297" width="6.453125" customWidth="1"/>
+    <col min="1298" max="1298" width="7.81640625" customWidth="1"/>
+    <col min="1299" max="1299" width="3" customWidth="1"/>
+    <col min="1300" max="1300" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1537" max="1540" width="14.453125" customWidth="1"/>
+    <col min="1541" max="1541" width="15.453125" customWidth="1"/>
+    <col min="1542" max="1542" width="14.54296875" customWidth="1"/>
+    <col min="1543" max="1543" width="15.26953125" customWidth="1"/>
+    <col min="1544" max="1545" width="14.453125" customWidth="1"/>
+    <col min="1546" max="1546" width="13.1796875" customWidth="1"/>
+    <col min="1547" max="1549" width="14.453125" customWidth="1"/>
+    <col min="1550" max="1550" width="15.81640625" customWidth="1"/>
+    <col min="1551" max="1551" width="7.81640625" customWidth="1"/>
+    <col min="1552" max="1552" width="5.453125" customWidth="1"/>
+    <col min="1553" max="1553" width="6.453125" customWidth="1"/>
+    <col min="1554" max="1554" width="7.81640625" customWidth="1"/>
+    <col min="1555" max="1555" width="3" customWidth="1"/>
+    <col min="1556" max="1556" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1793" max="1796" width="14.453125" customWidth="1"/>
+    <col min="1797" max="1797" width="15.453125" customWidth="1"/>
+    <col min="1798" max="1798" width="14.54296875" customWidth="1"/>
+    <col min="1799" max="1799" width="15.26953125" customWidth="1"/>
+    <col min="1800" max="1801" width="14.453125" customWidth="1"/>
+    <col min="1802" max="1802" width="13.1796875" customWidth="1"/>
+    <col min="1803" max="1805" width="14.453125" customWidth="1"/>
+    <col min="1806" max="1806" width="15.81640625" customWidth="1"/>
+    <col min="1807" max="1807" width="7.81640625" customWidth="1"/>
+    <col min="1808" max="1808" width="5.453125" customWidth="1"/>
+    <col min="1809" max="1809" width="6.453125" customWidth="1"/>
+    <col min="1810" max="1810" width="7.81640625" customWidth="1"/>
+    <col min="1811" max="1811" width="3" customWidth="1"/>
+    <col min="1812" max="1812" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2049" max="2052" width="14.453125" customWidth="1"/>
+    <col min="2053" max="2053" width="15.453125" customWidth="1"/>
+    <col min="2054" max="2054" width="14.54296875" customWidth="1"/>
+    <col min="2055" max="2055" width="15.26953125" customWidth="1"/>
+    <col min="2056" max="2057" width="14.453125" customWidth="1"/>
+    <col min="2058" max="2058" width="13.1796875" customWidth="1"/>
+    <col min="2059" max="2061" width="14.453125" customWidth="1"/>
+    <col min="2062" max="2062" width="15.81640625" customWidth="1"/>
+    <col min="2063" max="2063" width="7.81640625" customWidth="1"/>
+    <col min="2064" max="2064" width="5.453125" customWidth="1"/>
+    <col min="2065" max="2065" width="6.453125" customWidth="1"/>
+    <col min="2066" max="2066" width="7.81640625" customWidth="1"/>
+    <col min="2067" max="2067" width="3" customWidth="1"/>
+    <col min="2068" max="2068" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2305" max="2308" width="14.453125" customWidth="1"/>
+    <col min="2309" max="2309" width="15.453125" customWidth="1"/>
+    <col min="2310" max="2310" width="14.54296875" customWidth="1"/>
+    <col min="2311" max="2311" width="15.26953125" customWidth="1"/>
+    <col min="2312" max="2313" width="14.453125" customWidth="1"/>
+    <col min="2314" max="2314" width="13.1796875" customWidth="1"/>
+    <col min="2315" max="2317" width="14.453125" customWidth="1"/>
+    <col min="2318" max="2318" width="15.81640625" customWidth="1"/>
+    <col min="2319" max="2319" width="7.81640625" customWidth="1"/>
+    <col min="2320" max="2320" width="5.453125" customWidth="1"/>
+    <col min="2321" max="2321" width="6.453125" customWidth="1"/>
+    <col min="2322" max="2322" width="7.81640625" customWidth="1"/>
+    <col min="2323" max="2323" width="3" customWidth="1"/>
+    <col min="2324" max="2324" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2561" max="2564" width="14.453125" customWidth="1"/>
+    <col min="2565" max="2565" width="15.453125" customWidth="1"/>
+    <col min="2566" max="2566" width="14.54296875" customWidth="1"/>
+    <col min="2567" max="2567" width="15.26953125" customWidth="1"/>
+    <col min="2568" max="2569" width="14.453125" customWidth="1"/>
+    <col min="2570" max="2570" width="13.1796875" customWidth="1"/>
+    <col min="2571" max="2573" width="14.453125" customWidth="1"/>
+    <col min="2574" max="2574" width="15.81640625" customWidth="1"/>
+    <col min="2575" max="2575" width="7.81640625" customWidth="1"/>
+    <col min="2576" max="2576" width="5.453125" customWidth="1"/>
+    <col min="2577" max="2577" width="6.453125" customWidth="1"/>
+    <col min="2578" max="2578" width="7.81640625" customWidth="1"/>
+    <col min="2579" max="2579" width="3" customWidth="1"/>
+    <col min="2580" max="2580" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2817" max="2820" width="14.453125" customWidth="1"/>
+    <col min="2821" max="2821" width="15.453125" customWidth="1"/>
+    <col min="2822" max="2822" width="14.54296875" customWidth="1"/>
+    <col min="2823" max="2823" width="15.26953125" customWidth="1"/>
+    <col min="2824" max="2825" width="14.453125" customWidth="1"/>
+    <col min="2826" max="2826" width="13.1796875" customWidth="1"/>
+    <col min="2827" max="2829" width="14.453125" customWidth="1"/>
+    <col min="2830" max="2830" width="15.81640625" customWidth="1"/>
+    <col min="2831" max="2831" width="7.81640625" customWidth="1"/>
+    <col min="2832" max="2832" width="5.453125" customWidth="1"/>
+    <col min="2833" max="2833" width="6.453125" customWidth="1"/>
+    <col min="2834" max="2834" width="7.81640625" customWidth="1"/>
+    <col min="2835" max="2835" width="3" customWidth="1"/>
+    <col min="2836" max="2836" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3073" max="3076" width="14.453125" customWidth="1"/>
+    <col min="3077" max="3077" width="15.453125" customWidth="1"/>
+    <col min="3078" max="3078" width="14.54296875" customWidth="1"/>
+    <col min="3079" max="3079" width="15.26953125" customWidth="1"/>
+    <col min="3080" max="3081" width="14.453125" customWidth="1"/>
+    <col min="3082" max="3082" width="13.1796875" customWidth="1"/>
+    <col min="3083" max="3085" width="14.453125" customWidth="1"/>
+    <col min="3086" max="3086" width="15.81640625" customWidth="1"/>
+    <col min="3087" max="3087" width="7.81640625" customWidth="1"/>
+    <col min="3088" max="3088" width="5.453125" customWidth="1"/>
+    <col min="3089" max="3089" width="6.453125" customWidth="1"/>
+    <col min="3090" max="3090" width="7.81640625" customWidth="1"/>
+    <col min="3091" max="3091" width="3" customWidth="1"/>
+    <col min="3092" max="3092" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3329" max="3332" width="14.453125" customWidth="1"/>
+    <col min="3333" max="3333" width="15.453125" customWidth="1"/>
+    <col min="3334" max="3334" width="14.54296875" customWidth="1"/>
+    <col min="3335" max="3335" width="15.26953125" customWidth="1"/>
+    <col min="3336" max="3337" width="14.453125" customWidth="1"/>
+    <col min="3338" max="3338" width="13.1796875" customWidth="1"/>
+    <col min="3339" max="3341" width="14.453125" customWidth="1"/>
+    <col min="3342" max="3342" width="15.81640625" customWidth="1"/>
+    <col min="3343" max="3343" width="7.81640625" customWidth="1"/>
+    <col min="3344" max="3344" width="5.453125" customWidth="1"/>
+    <col min="3345" max="3345" width="6.453125" customWidth="1"/>
+    <col min="3346" max="3346" width="7.81640625" customWidth="1"/>
+    <col min="3347" max="3347" width="3" customWidth="1"/>
+    <col min="3348" max="3348" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3585" max="3588" width="14.453125" customWidth="1"/>
+    <col min="3589" max="3589" width="15.453125" customWidth="1"/>
+    <col min="3590" max="3590" width="14.54296875" customWidth="1"/>
+    <col min="3591" max="3591" width="15.26953125" customWidth="1"/>
+    <col min="3592" max="3593" width="14.453125" customWidth="1"/>
+    <col min="3594" max="3594" width="13.1796875" customWidth="1"/>
+    <col min="3595" max="3597" width="14.453125" customWidth="1"/>
+    <col min="3598" max="3598" width="15.81640625" customWidth="1"/>
+    <col min="3599" max="3599" width="7.81640625" customWidth="1"/>
+    <col min="3600" max="3600" width="5.453125" customWidth="1"/>
+    <col min="3601" max="3601" width="6.453125" customWidth="1"/>
+    <col min="3602" max="3602" width="7.81640625" customWidth="1"/>
+    <col min="3603" max="3603" width="3" customWidth="1"/>
+    <col min="3604" max="3604" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3841" max="3844" width="14.453125" customWidth="1"/>
+    <col min="3845" max="3845" width="15.453125" customWidth="1"/>
+    <col min="3846" max="3846" width="14.54296875" customWidth="1"/>
+    <col min="3847" max="3847" width="15.26953125" customWidth="1"/>
+    <col min="3848" max="3849" width="14.453125" customWidth="1"/>
+    <col min="3850" max="3850" width="13.1796875" customWidth="1"/>
+    <col min="3851" max="3853" width="14.453125" customWidth="1"/>
+    <col min="3854" max="3854" width="15.81640625" customWidth="1"/>
+    <col min="3855" max="3855" width="7.81640625" customWidth="1"/>
+    <col min="3856" max="3856" width="5.453125" customWidth="1"/>
+    <col min="3857" max="3857" width="6.453125" customWidth="1"/>
+    <col min="3858" max="3858" width="7.81640625" customWidth="1"/>
+    <col min="3859" max="3859" width="3" customWidth="1"/>
+    <col min="3860" max="3860" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4097" max="4100" width="14.453125" customWidth="1"/>
+    <col min="4101" max="4101" width="15.453125" customWidth="1"/>
+    <col min="4102" max="4102" width="14.54296875" customWidth="1"/>
+    <col min="4103" max="4103" width="15.26953125" customWidth="1"/>
+    <col min="4104" max="4105" width="14.453125" customWidth="1"/>
+    <col min="4106" max="4106" width="13.1796875" customWidth="1"/>
+    <col min="4107" max="4109" width="14.453125" customWidth="1"/>
+    <col min="4110" max="4110" width="15.81640625" customWidth="1"/>
+    <col min="4111" max="4111" width="7.81640625" customWidth="1"/>
+    <col min="4112" max="4112" width="5.453125" customWidth="1"/>
+    <col min="4113" max="4113" width="6.453125" customWidth="1"/>
+    <col min="4114" max="4114" width="7.81640625" customWidth="1"/>
+    <col min="4115" max="4115" width="3" customWidth="1"/>
+    <col min="4116" max="4116" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4353" max="4356" width="14.453125" customWidth="1"/>
+    <col min="4357" max="4357" width="15.453125" customWidth="1"/>
+    <col min="4358" max="4358" width="14.54296875" customWidth="1"/>
+    <col min="4359" max="4359" width="15.26953125" customWidth="1"/>
+    <col min="4360" max="4361" width="14.453125" customWidth="1"/>
+    <col min="4362" max="4362" width="13.1796875" customWidth="1"/>
+    <col min="4363" max="4365" width="14.453125" customWidth="1"/>
+    <col min="4366" max="4366" width="15.81640625" customWidth="1"/>
+    <col min="4367" max="4367" width="7.81640625" customWidth="1"/>
+    <col min="4368" max="4368" width="5.453125" customWidth="1"/>
+    <col min="4369" max="4369" width="6.453125" customWidth="1"/>
+    <col min="4370" max="4370" width="7.81640625" customWidth="1"/>
+    <col min="4371" max="4371" width="3" customWidth="1"/>
+    <col min="4372" max="4372" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4609" max="4612" width="14.453125" customWidth="1"/>
+    <col min="4613" max="4613" width="15.453125" customWidth="1"/>
+    <col min="4614" max="4614" width="14.54296875" customWidth="1"/>
+    <col min="4615" max="4615" width="15.26953125" customWidth="1"/>
+    <col min="4616" max="4617" width="14.453125" customWidth="1"/>
+    <col min="4618" max="4618" width="13.1796875" customWidth="1"/>
+    <col min="4619" max="4621" width="14.453125" customWidth="1"/>
+    <col min="4622" max="4622" width="15.81640625" customWidth="1"/>
+    <col min="4623" max="4623" width="7.81640625" customWidth="1"/>
+    <col min="4624" max="4624" width="5.453125" customWidth="1"/>
+    <col min="4625" max="4625" width="6.453125" customWidth="1"/>
+    <col min="4626" max="4626" width="7.81640625" customWidth="1"/>
+    <col min="4627" max="4627" width="3" customWidth="1"/>
+    <col min="4628" max="4628" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4865" max="4868" width="14.453125" customWidth="1"/>
+    <col min="4869" max="4869" width="15.453125" customWidth="1"/>
+    <col min="4870" max="4870" width="14.54296875" customWidth="1"/>
+    <col min="4871" max="4871" width="15.26953125" customWidth="1"/>
+    <col min="4872" max="4873" width="14.453125" customWidth="1"/>
+    <col min="4874" max="4874" width="13.1796875" customWidth="1"/>
+    <col min="4875" max="4877" width="14.453125" customWidth="1"/>
+    <col min="4878" max="4878" width="15.81640625" customWidth="1"/>
+    <col min="4879" max="4879" width="7.81640625" customWidth="1"/>
+    <col min="4880" max="4880" width="5.453125" customWidth="1"/>
+    <col min="4881" max="4881" width="6.453125" customWidth="1"/>
+    <col min="4882" max="4882" width="7.81640625" customWidth="1"/>
+    <col min="4883" max="4883" width="3" customWidth="1"/>
+    <col min="4884" max="4884" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5121" max="5124" width="14.453125" customWidth="1"/>
+    <col min="5125" max="5125" width="15.453125" customWidth="1"/>
+    <col min="5126" max="5126" width="14.54296875" customWidth="1"/>
+    <col min="5127" max="5127" width="15.26953125" customWidth="1"/>
+    <col min="5128" max="5129" width="14.453125" customWidth="1"/>
+    <col min="5130" max="5130" width="13.1796875" customWidth="1"/>
+    <col min="5131" max="5133" width="14.453125" customWidth="1"/>
+    <col min="5134" max="5134" width="15.81640625" customWidth="1"/>
+    <col min="5135" max="5135" width="7.81640625" customWidth="1"/>
+    <col min="5136" max="5136" width="5.453125" customWidth="1"/>
+    <col min="5137" max="5137" width="6.453125" customWidth="1"/>
+    <col min="5138" max="5138" width="7.81640625" customWidth="1"/>
+    <col min="5139" max="5139" width="3" customWidth="1"/>
+    <col min="5140" max="5140" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5377" max="5380" width="14.453125" customWidth="1"/>
+    <col min="5381" max="5381" width="15.453125" customWidth="1"/>
+    <col min="5382" max="5382" width="14.54296875" customWidth="1"/>
+    <col min="5383" max="5383" width="15.26953125" customWidth="1"/>
+    <col min="5384" max="5385" width="14.453125" customWidth="1"/>
+    <col min="5386" max="5386" width="13.1796875" customWidth="1"/>
+    <col min="5387" max="5389" width="14.453125" customWidth="1"/>
+    <col min="5390" max="5390" width="15.81640625" customWidth="1"/>
+    <col min="5391" max="5391" width="7.81640625" customWidth="1"/>
+    <col min="5392" max="5392" width="5.453125" customWidth="1"/>
+    <col min="5393" max="5393" width="6.453125" customWidth="1"/>
+    <col min="5394" max="5394" width="7.81640625" customWidth="1"/>
+    <col min="5395" max="5395" width="3" customWidth="1"/>
+    <col min="5396" max="5396" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5633" max="5636" width="14.453125" customWidth="1"/>
+    <col min="5637" max="5637" width="15.453125" customWidth="1"/>
+    <col min="5638" max="5638" width="14.54296875" customWidth="1"/>
+    <col min="5639" max="5639" width="15.26953125" customWidth="1"/>
+    <col min="5640" max="5641" width="14.453125" customWidth="1"/>
+    <col min="5642" max="5642" width="13.1796875" customWidth="1"/>
+    <col min="5643" max="5645" width="14.453125" customWidth="1"/>
+    <col min="5646" max="5646" width="15.81640625" customWidth="1"/>
+    <col min="5647" max="5647" width="7.81640625" customWidth="1"/>
+    <col min="5648" max="5648" width="5.453125" customWidth="1"/>
+    <col min="5649" max="5649" width="6.453125" customWidth="1"/>
+    <col min="5650" max="5650" width="7.81640625" customWidth="1"/>
+    <col min="5651" max="5651" width="3" customWidth="1"/>
+    <col min="5652" max="5652" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5889" max="5892" width="14.453125" customWidth="1"/>
+    <col min="5893" max="5893" width="15.453125" customWidth="1"/>
+    <col min="5894" max="5894" width="14.54296875" customWidth="1"/>
+    <col min="5895" max="5895" width="15.26953125" customWidth="1"/>
+    <col min="5896" max="5897" width="14.453125" customWidth="1"/>
+    <col min="5898" max="5898" width="13.1796875" customWidth="1"/>
+    <col min="5899" max="5901" width="14.453125" customWidth="1"/>
+    <col min="5902" max="5902" width="15.81640625" customWidth="1"/>
+    <col min="5903" max="5903" width="7.81640625" customWidth="1"/>
+    <col min="5904" max="5904" width="5.453125" customWidth="1"/>
+    <col min="5905" max="5905" width="6.453125" customWidth="1"/>
+    <col min="5906" max="5906" width="7.81640625" customWidth="1"/>
+    <col min="5907" max="5907" width="3" customWidth="1"/>
+    <col min="5908" max="5908" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6145" max="6148" width="14.453125" customWidth="1"/>
+    <col min="6149" max="6149" width="15.453125" customWidth="1"/>
+    <col min="6150" max="6150" width="14.54296875" customWidth="1"/>
+    <col min="6151" max="6151" width="15.26953125" customWidth="1"/>
+    <col min="6152" max="6153" width="14.453125" customWidth="1"/>
+    <col min="6154" max="6154" width="13.1796875" customWidth="1"/>
+    <col min="6155" max="6157" width="14.453125" customWidth="1"/>
+    <col min="6158" max="6158" width="15.81640625" customWidth="1"/>
+    <col min="6159" max="6159" width="7.81640625" customWidth="1"/>
+    <col min="6160" max="6160" width="5.453125" customWidth="1"/>
+    <col min="6161" max="6161" width="6.453125" customWidth="1"/>
+    <col min="6162" max="6162" width="7.81640625" customWidth="1"/>
+    <col min="6163" max="6163" width="3" customWidth="1"/>
+    <col min="6164" max="6164" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6401" max="6404" width="14.453125" customWidth="1"/>
+    <col min="6405" max="6405" width="15.453125" customWidth="1"/>
+    <col min="6406" max="6406" width="14.54296875" customWidth="1"/>
+    <col min="6407" max="6407" width="15.26953125" customWidth="1"/>
+    <col min="6408" max="6409" width="14.453125" customWidth="1"/>
+    <col min="6410" max="6410" width="13.1796875" customWidth="1"/>
+    <col min="6411" max="6413" width="14.453125" customWidth="1"/>
+    <col min="6414" max="6414" width="15.81640625" customWidth="1"/>
+    <col min="6415" max="6415" width="7.81640625" customWidth="1"/>
+    <col min="6416" max="6416" width="5.453125" customWidth="1"/>
+    <col min="6417" max="6417" width="6.453125" customWidth="1"/>
+    <col min="6418" max="6418" width="7.81640625" customWidth="1"/>
+    <col min="6419" max="6419" width="3" customWidth="1"/>
+    <col min="6420" max="6420" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6657" max="6660" width="14.453125" customWidth="1"/>
+    <col min="6661" max="6661" width="15.453125" customWidth="1"/>
+    <col min="6662" max="6662" width="14.54296875" customWidth="1"/>
+    <col min="6663" max="6663" width="15.26953125" customWidth="1"/>
+    <col min="6664" max="6665" width="14.453125" customWidth="1"/>
+    <col min="6666" max="6666" width="13.1796875" customWidth="1"/>
+    <col min="6667" max="6669" width="14.453125" customWidth="1"/>
+    <col min="6670" max="6670" width="15.81640625" customWidth="1"/>
+    <col min="6671" max="6671" width="7.81640625" customWidth="1"/>
+    <col min="6672" max="6672" width="5.453125" customWidth="1"/>
+    <col min="6673" max="6673" width="6.453125" customWidth="1"/>
+    <col min="6674" max="6674" width="7.81640625" customWidth="1"/>
+    <col min="6675" max="6675" width="3" customWidth="1"/>
+    <col min="6676" max="6676" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6913" max="6916" width="14.453125" customWidth="1"/>
+    <col min="6917" max="6917" width="15.453125" customWidth="1"/>
+    <col min="6918" max="6918" width="14.54296875" customWidth="1"/>
+    <col min="6919" max="6919" width="15.26953125" customWidth="1"/>
+    <col min="6920" max="6921" width="14.453125" customWidth="1"/>
+    <col min="6922" max="6922" width="13.1796875" customWidth="1"/>
+    <col min="6923" max="6925" width="14.453125" customWidth="1"/>
+    <col min="6926" max="6926" width="15.81640625" customWidth="1"/>
+    <col min="6927" max="6927" width="7.81640625" customWidth="1"/>
+    <col min="6928" max="6928" width="5.453125" customWidth="1"/>
+    <col min="6929" max="6929" width="6.453125" customWidth="1"/>
+    <col min="6930" max="6930" width="7.81640625" customWidth="1"/>
+    <col min="6931" max="6931" width="3" customWidth="1"/>
+    <col min="6932" max="6932" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7169" max="7172" width="14.453125" customWidth="1"/>
+    <col min="7173" max="7173" width="15.453125" customWidth="1"/>
+    <col min="7174" max="7174" width="14.54296875" customWidth="1"/>
+    <col min="7175" max="7175" width="15.26953125" customWidth="1"/>
+    <col min="7176" max="7177" width="14.453125" customWidth="1"/>
+    <col min="7178" max="7178" width="13.1796875" customWidth="1"/>
+    <col min="7179" max="7181" width="14.453125" customWidth="1"/>
+    <col min="7182" max="7182" width="15.81640625" customWidth="1"/>
+    <col min="7183" max="7183" width="7.81640625" customWidth="1"/>
+    <col min="7184" max="7184" width="5.453125" customWidth="1"/>
+    <col min="7185" max="7185" width="6.453125" customWidth="1"/>
+    <col min="7186" max="7186" width="7.81640625" customWidth="1"/>
+    <col min="7187" max="7187" width="3" customWidth="1"/>
+    <col min="7188" max="7188" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7425" max="7428" width="14.453125" customWidth="1"/>
+    <col min="7429" max="7429" width="15.453125" customWidth="1"/>
+    <col min="7430" max="7430" width="14.54296875" customWidth="1"/>
+    <col min="7431" max="7431" width="15.26953125" customWidth="1"/>
+    <col min="7432" max="7433" width="14.453125" customWidth="1"/>
+    <col min="7434" max="7434" width="13.1796875" customWidth="1"/>
+    <col min="7435" max="7437" width="14.453125" customWidth="1"/>
+    <col min="7438" max="7438" width="15.81640625" customWidth="1"/>
+    <col min="7439" max="7439" width="7.81640625" customWidth="1"/>
+    <col min="7440" max="7440" width="5.453125" customWidth="1"/>
+    <col min="7441" max="7441" width="6.453125" customWidth="1"/>
+    <col min="7442" max="7442" width="7.81640625" customWidth="1"/>
+    <col min="7443" max="7443" width="3" customWidth="1"/>
+    <col min="7444" max="7444" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7681" max="7684" width="14.453125" customWidth="1"/>
+    <col min="7685" max="7685" width="15.453125" customWidth="1"/>
+    <col min="7686" max="7686" width="14.54296875" customWidth="1"/>
+    <col min="7687" max="7687" width="15.26953125" customWidth="1"/>
+    <col min="7688" max="7689" width="14.453125" customWidth="1"/>
+    <col min="7690" max="7690" width="13.1796875" customWidth="1"/>
+    <col min="7691" max="7693" width="14.453125" customWidth="1"/>
+    <col min="7694" max="7694" width="15.81640625" customWidth="1"/>
+    <col min="7695" max="7695" width="7.81640625" customWidth="1"/>
+    <col min="7696" max="7696" width="5.453125" customWidth="1"/>
+    <col min="7697" max="7697" width="6.453125" customWidth="1"/>
+    <col min="7698" max="7698" width="7.81640625" customWidth="1"/>
+    <col min="7699" max="7699" width="3" customWidth="1"/>
+    <col min="7700" max="7700" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7937" max="7940" width="14.453125" customWidth="1"/>
+    <col min="7941" max="7941" width="15.453125" customWidth="1"/>
+    <col min="7942" max="7942" width="14.54296875" customWidth="1"/>
+    <col min="7943" max="7943" width="15.26953125" customWidth="1"/>
+    <col min="7944" max="7945" width="14.453125" customWidth="1"/>
+    <col min="7946" max="7946" width="13.1796875" customWidth="1"/>
+    <col min="7947" max="7949" width="14.453125" customWidth="1"/>
+    <col min="7950" max="7950" width="15.81640625" customWidth="1"/>
+    <col min="7951" max="7951" width="7.81640625" customWidth="1"/>
+    <col min="7952" max="7952" width="5.453125" customWidth="1"/>
+    <col min="7953" max="7953" width="6.453125" customWidth="1"/>
+    <col min="7954" max="7954" width="7.81640625" customWidth="1"/>
+    <col min="7955" max="7955" width="3" customWidth="1"/>
+    <col min="7956" max="7956" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8193" max="8196" width="14.453125" customWidth="1"/>
+    <col min="8197" max="8197" width="15.453125" customWidth="1"/>
+    <col min="8198" max="8198" width="14.54296875" customWidth="1"/>
+    <col min="8199" max="8199" width="15.26953125" customWidth="1"/>
+    <col min="8200" max="8201" width="14.453125" customWidth="1"/>
+    <col min="8202" max="8202" width="13.1796875" customWidth="1"/>
+    <col min="8203" max="8205" width="14.453125" customWidth="1"/>
+    <col min="8206" max="8206" width="15.81640625" customWidth="1"/>
+    <col min="8207" max="8207" width="7.81640625" customWidth="1"/>
+    <col min="8208" max="8208" width="5.453125" customWidth="1"/>
+    <col min="8209" max="8209" width="6.453125" customWidth="1"/>
+    <col min="8210" max="8210" width="7.81640625" customWidth="1"/>
+    <col min="8211" max="8211" width="3" customWidth="1"/>
+    <col min="8212" max="8212" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8449" max="8452" width="14.453125" customWidth="1"/>
+    <col min="8453" max="8453" width="15.453125" customWidth="1"/>
+    <col min="8454" max="8454" width="14.54296875" customWidth="1"/>
+    <col min="8455" max="8455" width="15.26953125" customWidth="1"/>
+    <col min="8456" max="8457" width="14.453125" customWidth="1"/>
+    <col min="8458" max="8458" width="13.1796875" customWidth="1"/>
+    <col min="8459" max="8461" width="14.453125" customWidth="1"/>
+    <col min="8462" max="8462" width="15.81640625" customWidth="1"/>
+    <col min="8463" max="8463" width="7.81640625" customWidth="1"/>
+    <col min="8464" max="8464" width="5.453125" customWidth="1"/>
+    <col min="8465" max="8465" width="6.453125" customWidth="1"/>
+    <col min="8466" max="8466" width="7.81640625" customWidth="1"/>
+    <col min="8467" max="8467" width="3" customWidth="1"/>
+    <col min="8468" max="8468" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8705" max="8708" width="14.453125" customWidth="1"/>
+    <col min="8709" max="8709" width="15.453125" customWidth="1"/>
+    <col min="8710" max="8710" width="14.54296875" customWidth="1"/>
+    <col min="8711" max="8711" width="15.26953125" customWidth="1"/>
+    <col min="8712" max="8713" width="14.453125" customWidth="1"/>
+    <col min="8714" max="8714" width="13.1796875" customWidth="1"/>
+    <col min="8715" max="8717" width="14.453125" customWidth="1"/>
+    <col min="8718" max="8718" width="15.81640625" customWidth="1"/>
+    <col min="8719" max="8719" width="7.81640625" customWidth="1"/>
+    <col min="8720" max="8720" width="5.453125" customWidth="1"/>
+    <col min="8721" max="8721" width="6.453125" customWidth="1"/>
+    <col min="8722" max="8722" width="7.81640625" customWidth="1"/>
+    <col min="8723" max="8723" width="3" customWidth="1"/>
+    <col min="8724" max="8724" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="8961" max="8964" width="14.453125" customWidth="1"/>
+    <col min="8965" max="8965" width="15.453125" customWidth="1"/>
+    <col min="8966" max="8966" width="14.54296875" customWidth="1"/>
+    <col min="8967" max="8967" width="15.26953125" customWidth="1"/>
+    <col min="8968" max="8969" width="14.453125" customWidth="1"/>
+    <col min="8970" max="8970" width="13.1796875" customWidth="1"/>
+    <col min="8971" max="8973" width="14.453125" customWidth="1"/>
+    <col min="8974" max="8974" width="15.81640625" customWidth="1"/>
+    <col min="8975" max="8975" width="7.81640625" customWidth="1"/>
+    <col min="8976" max="8976" width="5.453125" customWidth="1"/>
+    <col min="8977" max="8977" width="6.453125" customWidth="1"/>
+    <col min="8978" max="8978" width="7.81640625" customWidth="1"/>
+    <col min="8979" max="8979" width="3" customWidth="1"/>
+    <col min="8980" max="8980" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9217" max="9220" width="14.453125" customWidth="1"/>
+    <col min="9221" max="9221" width="15.453125" customWidth="1"/>
+    <col min="9222" max="9222" width="14.54296875" customWidth="1"/>
+    <col min="9223" max="9223" width="15.26953125" customWidth="1"/>
+    <col min="9224" max="9225" width="14.453125" customWidth="1"/>
+    <col min="9226" max="9226" width="13.1796875" customWidth="1"/>
+    <col min="9227" max="9229" width="14.453125" customWidth="1"/>
+    <col min="9230" max="9230" width="15.81640625" customWidth="1"/>
+    <col min="9231" max="9231" width="7.81640625" customWidth="1"/>
+    <col min="9232" max="9232" width="5.453125" customWidth="1"/>
+    <col min="9233" max="9233" width="6.453125" customWidth="1"/>
+    <col min="9234" max="9234" width="7.81640625" customWidth="1"/>
+    <col min="9235" max="9235" width="3" customWidth="1"/>
+    <col min="9236" max="9236" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9473" max="9476" width="14.453125" customWidth="1"/>
+    <col min="9477" max="9477" width="15.453125" customWidth="1"/>
+    <col min="9478" max="9478" width="14.54296875" customWidth="1"/>
+    <col min="9479" max="9479" width="15.26953125" customWidth="1"/>
+    <col min="9480" max="9481" width="14.453125" customWidth="1"/>
+    <col min="9482" max="9482" width="13.1796875" customWidth="1"/>
+    <col min="9483" max="9485" width="14.453125" customWidth="1"/>
+    <col min="9486" max="9486" width="15.81640625" customWidth="1"/>
+    <col min="9487" max="9487" width="7.81640625" customWidth="1"/>
+    <col min="9488" max="9488" width="5.453125" customWidth="1"/>
+    <col min="9489" max="9489" width="6.453125" customWidth="1"/>
+    <col min="9490" max="9490" width="7.81640625" customWidth="1"/>
+    <col min="9491" max="9491" width="3" customWidth="1"/>
+    <col min="9492" max="9492" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9729" max="9732" width="14.453125" customWidth="1"/>
+    <col min="9733" max="9733" width="15.453125" customWidth="1"/>
+    <col min="9734" max="9734" width="14.54296875" customWidth="1"/>
+    <col min="9735" max="9735" width="15.26953125" customWidth="1"/>
+    <col min="9736" max="9737" width="14.453125" customWidth="1"/>
+    <col min="9738" max="9738" width="13.1796875" customWidth="1"/>
+    <col min="9739" max="9741" width="14.453125" customWidth="1"/>
+    <col min="9742" max="9742" width="15.81640625" customWidth="1"/>
+    <col min="9743" max="9743" width="7.81640625" customWidth="1"/>
+    <col min="9744" max="9744" width="5.453125" customWidth="1"/>
+    <col min="9745" max="9745" width="6.453125" customWidth="1"/>
+    <col min="9746" max="9746" width="7.81640625" customWidth="1"/>
+    <col min="9747" max="9747" width="3" customWidth="1"/>
+    <col min="9748" max="9748" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9985" max="9988" width="14.453125" customWidth="1"/>
+    <col min="9989" max="9989" width="15.453125" customWidth="1"/>
+    <col min="9990" max="9990" width="14.54296875" customWidth="1"/>
+    <col min="9991" max="9991" width="15.26953125" customWidth="1"/>
+    <col min="9992" max="9993" width="14.453125" customWidth="1"/>
+    <col min="9994" max="9994" width="13.1796875" customWidth="1"/>
+    <col min="9995" max="9997" width="14.453125" customWidth="1"/>
+    <col min="9998" max="9998" width="15.81640625" customWidth="1"/>
+    <col min="9999" max="9999" width="7.81640625" customWidth="1"/>
+    <col min="10000" max="10000" width="5.453125" customWidth="1"/>
+    <col min="10001" max="10001" width="6.453125" customWidth="1"/>
+    <col min="10002" max="10002" width="7.81640625" customWidth="1"/>
+    <col min="10003" max="10003" width="3" customWidth="1"/>
+    <col min="10004" max="10004" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10241" max="10244" width="14.453125" customWidth="1"/>
+    <col min="10245" max="10245" width="15.453125" customWidth="1"/>
+    <col min="10246" max="10246" width="14.54296875" customWidth="1"/>
+    <col min="10247" max="10247" width="15.26953125" customWidth="1"/>
+    <col min="10248" max="10249" width="14.453125" customWidth="1"/>
+    <col min="10250" max="10250" width="13.1796875" customWidth="1"/>
+    <col min="10251" max="10253" width="14.453125" customWidth="1"/>
+    <col min="10254" max="10254" width="15.81640625" customWidth="1"/>
+    <col min="10255" max="10255" width="7.81640625" customWidth="1"/>
+    <col min="10256" max="10256" width="5.453125" customWidth="1"/>
+    <col min="10257" max="10257" width="6.453125" customWidth="1"/>
+    <col min="10258" max="10258" width="7.81640625" customWidth="1"/>
+    <col min="10259" max="10259" width="3" customWidth="1"/>
+    <col min="10260" max="10260" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10497" max="10500" width="14.453125" customWidth="1"/>
+    <col min="10501" max="10501" width="15.453125" customWidth="1"/>
+    <col min="10502" max="10502" width="14.54296875" customWidth="1"/>
+    <col min="10503" max="10503" width="15.26953125" customWidth="1"/>
+    <col min="10504" max="10505" width="14.453125" customWidth="1"/>
+    <col min="10506" max="10506" width="13.1796875" customWidth="1"/>
+    <col min="10507" max="10509" width="14.453125" customWidth="1"/>
+    <col min="10510" max="10510" width="15.81640625" customWidth="1"/>
+    <col min="10511" max="10511" width="7.81640625" customWidth="1"/>
+    <col min="10512" max="10512" width="5.453125" customWidth="1"/>
+    <col min="10513" max="10513" width="6.453125" customWidth="1"/>
+    <col min="10514" max="10514" width="7.81640625" customWidth="1"/>
+    <col min="10515" max="10515" width="3" customWidth="1"/>
+    <col min="10516" max="10516" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10753" max="10756" width="14.453125" customWidth="1"/>
+    <col min="10757" max="10757" width="15.453125" customWidth="1"/>
+    <col min="10758" max="10758" width="14.54296875" customWidth="1"/>
+    <col min="10759" max="10759" width="15.26953125" customWidth="1"/>
+    <col min="10760" max="10761" width="14.453125" customWidth="1"/>
+    <col min="10762" max="10762" width="13.1796875" customWidth="1"/>
+    <col min="10763" max="10765" width="14.453125" customWidth="1"/>
+    <col min="10766" max="10766" width="15.81640625" customWidth="1"/>
+    <col min="10767" max="10767" width="7.81640625" customWidth="1"/>
+    <col min="10768" max="10768" width="5.453125" customWidth="1"/>
+    <col min="10769" max="10769" width="6.453125" customWidth="1"/>
+    <col min="10770" max="10770" width="7.81640625" customWidth="1"/>
+    <col min="10771" max="10771" width="3" customWidth="1"/>
+    <col min="10772" max="10772" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11009" max="11012" width="14.453125" customWidth="1"/>
+    <col min="11013" max="11013" width="15.453125" customWidth="1"/>
+    <col min="11014" max="11014" width="14.54296875" customWidth="1"/>
+    <col min="11015" max="11015" width="15.26953125" customWidth="1"/>
+    <col min="11016" max="11017" width="14.453125" customWidth="1"/>
+    <col min="11018" max="11018" width="13.1796875" customWidth="1"/>
+    <col min="11019" max="11021" width="14.453125" customWidth="1"/>
+    <col min="11022" max="11022" width="15.81640625" customWidth="1"/>
+    <col min="11023" max="11023" width="7.81640625" customWidth="1"/>
+    <col min="11024" max="11024" width="5.453125" customWidth="1"/>
+    <col min="11025" max="11025" width="6.453125" customWidth="1"/>
+    <col min="11026" max="11026" width="7.81640625" customWidth="1"/>
+    <col min="11027" max="11027" width="3" customWidth="1"/>
+    <col min="11028" max="11028" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11265" max="11268" width="14.453125" customWidth="1"/>
+    <col min="11269" max="11269" width="15.453125" customWidth="1"/>
+    <col min="11270" max="11270" width="14.54296875" customWidth="1"/>
+    <col min="11271" max="11271" width="15.26953125" customWidth="1"/>
+    <col min="11272" max="11273" width="14.453125" customWidth="1"/>
+    <col min="11274" max="11274" width="13.1796875" customWidth="1"/>
+    <col min="11275" max="11277" width="14.453125" customWidth="1"/>
+    <col min="11278" max="11278" width="15.81640625" customWidth="1"/>
+    <col min="11279" max="11279" width="7.81640625" customWidth="1"/>
+    <col min="11280" max="11280" width="5.453125" customWidth="1"/>
+    <col min="11281" max="11281" width="6.453125" customWidth="1"/>
+    <col min="11282" max="11282" width="7.81640625" customWidth="1"/>
+    <col min="11283" max="11283" width="3" customWidth="1"/>
+    <col min="11284" max="11284" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11521" max="11524" width="14.453125" customWidth="1"/>
+    <col min="11525" max="11525" width="15.453125" customWidth="1"/>
+    <col min="11526" max="11526" width="14.54296875" customWidth="1"/>
+    <col min="11527" max="11527" width="15.26953125" customWidth="1"/>
+    <col min="11528" max="11529" width="14.453125" customWidth="1"/>
+    <col min="11530" max="11530" width="13.1796875" customWidth="1"/>
+    <col min="11531" max="11533" width="14.453125" customWidth="1"/>
+    <col min="11534" max="11534" width="15.81640625" customWidth="1"/>
+    <col min="11535" max="11535" width="7.81640625" customWidth="1"/>
+    <col min="11536" max="11536" width="5.453125" customWidth="1"/>
+    <col min="11537" max="11537" width="6.453125" customWidth="1"/>
+    <col min="11538" max="11538" width="7.81640625" customWidth="1"/>
+    <col min="11539" max="11539" width="3" customWidth="1"/>
+    <col min="11540" max="11540" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="11777" max="11780" width="14.453125" customWidth="1"/>
+    <col min="11781" max="11781" width="15.453125" customWidth="1"/>
+    <col min="11782" max="11782" width="14.54296875" customWidth="1"/>
+    <col min="11783" max="11783" width="15.26953125" customWidth="1"/>
+    <col min="11784" max="11785" width="14.453125" customWidth="1"/>
+    <col min="11786" max="11786" width="13.1796875" customWidth="1"/>
+    <col min="11787" max="11789" width="14.453125" customWidth="1"/>
+    <col min="11790" max="11790" width="15.81640625" customWidth="1"/>
+    <col min="11791" max="11791" width="7.81640625" customWidth="1"/>
+    <col min="11792" max="11792" width="5.453125" customWidth="1"/>
+    <col min="11793" max="11793" width="6.453125" customWidth="1"/>
+    <col min="11794" max="11794" width="7.81640625" customWidth="1"/>
+    <col min="11795" max="11795" width="3" customWidth="1"/>
+    <col min="11796" max="11796" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12033" max="12036" width="14.453125" customWidth="1"/>
+    <col min="12037" max="12037" width="15.453125" customWidth="1"/>
+    <col min="12038" max="12038" width="14.54296875" customWidth="1"/>
+    <col min="12039" max="12039" width="15.26953125" customWidth="1"/>
+    <col min="12040" max="12041" width="14.453125" customWidth="1"/>
+    <col min="12042" max="12042" width="13.1796875" customWidth="1"/>
+    <col min="12043" max="12045" width="14.453125" customWidth="1"/>
+    <col min="12046" max="12046" width="15.81640625" customWidth="1"/>
+    <col min="12047" max="12047" width="7.81640625" customWidth="1"/>
+    <col min="12048" max="12048" width="5.453125" customWidth="1"/>
+    <col min="12049" max="12049" width="6.453125" customWidth="1"/>
+    <col min="12050" max="12050" width="7.81640625" customWidth="1"/>
+    <col min="12051" max="12051" width="3" customWidth="1"/>
+    <col min="12052" max="12052" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12289" max="12292" width="14.453125" customWidth="1"/>
+    <col min="12293" max="12293" width="15.453125" customWidth="1"/>
+    <col min="12294" max="12294" width="14.54296875" customWidth="1"/>
+    <col min="12295" max="12295" width="15.26953125" customWidth="1"/>
+    <col min="12296" max="12297" width="14.453125" customWidth="1"/>
+    <col min="12298" max="12298" width="13.1796875" customWidth="1"/>
+    <col min="12299" max="12301" width="14.453125" customWidth="1"/>
+    <col min="12302" max="12302" width="15.81640625" customWidth="1"/>
+    <col min="12303" max="12303" width="7.81640625" customWidth="1"/>
+    <col min="12304" max="12304" width="5.453125" customWidth="1"/>
+    <col min="12305" max="12305" width="6.453125" customWidth="1"/>
+    <col min="12306" max="12306" width="7.81640625" customWidth="1"/>
+    <col min="12307" max="12307" width="3" customWidth="1"/>
+    <col min="12308" max="12308" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12545" max="12548" width="14.453125" customWidth="1"/>
+    <col min="12549" max="12549" width="15.453125" customWidth="1"/>
+    <col min="12550" max="12550" width="14.54296875" customWidth="1"/>
+    <col min="12551" max="12551" width="15.26953125" customWidth="1"/>
+    <col min="12552" max="12553" width="14.453125" customWidth="1"/>
+    <col min="12554" max="12554" width="13.1796875" customWidth="1"/>
+    <col min="12555" max="12557" width="14.453125" customWidth="1"/>
+    <col min="12558" max="12558" width="15.81640625" customWidth="1"/>
+    <col min="12559" max="12559" width="7.81640625" customWidth="1"/>
+    <col min="12560" max="12560" width="5.453125" customWidth="1"/>
+    <col min="12561" max="12561" width="6.453125" customWidth="1"/>
+    <col min="12562" max="12562" width="7.81640625" customWidth="1"/>
+    <col min="12563" max="12563" width="3" customWidth="1"/>
+    <col min="12564" max="12564" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12801" max="12804" width="14.453125" customWidth="1"/>
+    <col min="12805" max="12805" width="15.453125" customWidth="1"/>
+    <col min="12806" max="12806" width="14.54296875" customWidth="1"/>
+    <col min="12807" max="12807" width="15.26953125" customWidth="1"/>
+    <col min="12808" max="12809" width="14.453125" customWidth="1"/>
+    <col min="12810" max="12810" width="13.1796875" customWidth="1"/>
+    <col min="12811" max="12813" width="14.453125" customWidth="1"/>
+    <col min="12814" max="12814" width="15.81640625" customWidth="1"/>
+    <col min="12815" max="12815" width="7.81640625" customWidth="1"/>
+    <col min="12816" max="12816" width="5.453125" customWidth="1"/>
+    <col min="12817" max="12817" width="6.453125" customWidth="1"/>
+    <col min="12818" max="12818" width="7.81640625" customWidth="1"/>
+    <col min="12819" max="12819" width="3" customWidth="1"/>
+    <col min="12820" max="12820" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13057" max="13060" width="14.453125" customWidth="1"/>
+    <col min="13061" max="13061" width="15.453125" customWidth="1"/>
+    <col min="13062" max="13062" width="14.54296875" customWidth="1"/>
+    <col min="13063" max="13063" width="15.26953125" customWidth="1"/>
+    <col min="13064" max="13065" width="14.453125" customWidth="1"/>
+    <col min="13066" max="13066" width="13.1796875" customWidth="1"/>
+    <col min="13067" max="13069" width="14.453125" customWidth="1"/>
+    <col min="13070" max="13070" width="15.81640625" customWidth="1"/>
+    <col min="13071" max="13071" width="7.81640625" customWidth="1"/>
+    <col min="13072" max="13072" width="5.453125" customWidth="1"/>
+    <col min="13073" max="13073" width="6.453125" customWidth="1"/>
+    <col min="13074" max="13074" width="7.81640625" customWidth="1"/>
+    <col min="13075" max="13075" width="3" customWidth="1"/>
+    <col min="13076" max="13076" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13313" max="13316" width="14.453125" customWidth="1"/>
+    <col min="13317" max="13317" width="15.453125" customWidth="1"/>
+    <col min="13318" max="13318" width="14.54296875" customWidth="1"/>
+    <col min="13319" max="13319" width="15.26953125" customWidth="1"/>
+    <col min="13320" max="13321" width="14.453125" customWidth="1"/>
+    <col min="13322" max="13322" width="13.1796875" customWidth="1"/>
+    <col min="13323" max="13325" width="14.453125" customWidth="1"/>
+    <col min="13326" max="13326" width="15.81640625" customWidth="1"/>
+    <col min="13327" max="13327" width="7.81640625" customWidth="1"/>
+    <col min="13328" max="13328" width="5.453125" customWidth="1"/>
+    <col min="13329" max="13329" width="6.453125" customWidth="1"/>
+    <col min="13330" max="13330" width="7.81640625" customWidth="1"/>
+    <col min="13331" max="13331" width="3" customWidth="1"/>
+    <col min="13332" max="13332" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13569" max="13572" width="14.453125" customWidth="1"/>
+    <col min="13573" max="13573" width="15.453125" customWidth="1"/>
+    <col min="13574" max="13574" width="14.54296875" customWidth="1"/>
+    <col min="13575" max="13575" width="15.26953125" customWidth="1"/>
+    <col min="13576" max="13577" width="14.453125" customWidth="1"/>
+    <col min="13578" max="13578" width="13.1796875" customWidth="1"/>
+    <col min="13579" max="13581" width="14.453125" customWidth="1"/>
+    <col min="13582" max="13582" width="15.81640625" customWidth="1"/>
+    <col min="13583" max="13583" width="7.81640625" customWidth="1"/>
+    <col min="13584" max="13584" width="5.453125" customWidth="1"/>
+    <col min="13585" max="13585" width="6.453125" customWidth="1"/>
+    <col min="13586" max="13586" width="7.81640625" customWidth="1"/>
+    <col min="13587" max="13587" width="3" customWidth="1"/>
+    <col min="13588" max="13588" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13825" max="13828" width="14.453125" customWidth="1"/>
+    <col min="13829" max="13829" width="15.453125" customWidth="1"/>
+    <col min="13830" max="13830" width="14.54296875" customWidth="1"/>
+    <col min="13831" max="13831" width="15.26953125" customWidth="1"/>
+    <col min="13832" max="13833" width="14.453125" customWidth="1"/>
+    <col min="13834" max="13834" width="13.1796875" customWidth="1"/>
+    <col min="13835" max="13837" width="14.453125" customWidth="1"/>
+    <col min="13838" max="13838" width="15.81640625" customWidth="1"/>
+    <col min="13839" max="13839" width="7.81640625" customWidth="1"/>
+    <col min="13840" max="13840" width="5.453125" customWidth="1"/>
+    <col min="13841" max="13841" width="6.453125" customWidth="1"/>
+    <col min="13842" max="13842" width="7.81640625" customWidth="1"/>
+    <col min="13843" max="13843" width="3" customWidth="1"/>
+    <col min="13844" max="13844" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14081" max="14084" width="14.453125" customWidth="1"/>
+    <col min="14085" max="14085" width="15.453125" customWidth="1"/>
+    <col min="14086" max="14086" width="14.54296875" customWidth="1"/>
+    <col min="14087" max="14087" width="15.26953125" customWidth="1"/>
+    <col min="14088" max="14089" width="14.453125" customWidth="1"/>
+    <col min="14090" max="14090" width="13.1796875" customWidth="1"/>
+    <col min="14091" max="14093" width="14.453125" customWidth="1"/>
+    <col min="14094" max="14094" width="15.81640625" customWidth="1"/>
+    <col min="14095" max="14095" width="7.81640625" customWidth="1"/>
+    <col min="14096" max="14096" width="5.453125" customWidth="1"/>
+    <col min="14097" max="14097" width="6.453125" customWidth="1"/>
+    <col min="14098" max="14098" width="7.81640625" customWidth="1"/>
+    <col min="14099" max="14099" width="3" customWidth="1"/>
+    <col min="14100" max="14100" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14337" max="14340" width="14.453125" customWidth="1"/>
+    <col min="14341" max="14341" width="15.453125" customWidth="1"/>
+    <col min="14342" max="14342" width="14.54296875" customWidth="1"/>
+    <col min="14343" max="14343" width="15.26953125" customWidth="1"/>
+    <col min="14344" max="14345" width="14.453125" customWidth="1"/>
+    <col min="14346" max="14346" width="13.1796875" customWidth="1"/>
+    <col min="14347" max="14349" width="14.453125" customWidth="1"/>
+    <col min="14350" max="14350" width="15.81640625" customWidth="1"/>
+    <col min="14351" max="14351" width="7.81640625" customWidth="1"/>
+    <col min="14352" max="14352" width="5.453125" customWidth="1"/>
+    <col min="14353" max="14353" width="6.453125" customWidth="1"/>
+    <col min="14354" max="14354" width="7.81640625" customWidth="1"/>
+    <col min="14355" max="14355" width="3" customWidth="1"/>
+    <col min="14356" max="14356" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14593" max="14596" width="14.453125" customWidth="1"/>
+    <col min="14597" max="14597" width="15.453125" customWidth="1"/>
+    <col min="14598" max="14598" width="14.54296875" customWidth="1"/>
+    <col min="14599" max="14599" width="15.26953125" customWidth="1"/>
+    <col min="14600" max="14601" width="14.453125" customWidth="1"/>
+    <col min="14602" max="14602" width="13.1796875" customWidth="1"/>
+    <col min="14603" max="14605" width="14.453125" customWidth="1"/>
+    <col min="14606" max="14606" width="15.81640625" customWidth="1"/>
+    <col min="14607" max="14607" width="7.81640625" customWidth="1"/>
+    <col min="14608" max="14608" width="5.453125" customWidth="1"/>
+    <col min="14609" max="14609" width="6.453125" customWidth="1"/>
+    <col min="14610" max="14610" width="7.81640625" customWidth="1"/>
+    <col min="14611" max="14611" width="3" customWidth="1"/>
+    <col min="14612" max="14612" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="14849" max="14852" width="14.453125" customWidth="1"/>
+    <col min="14853" max="14853" width="15.453125" customWidth="1"/>
+    <col min="14854" max="14854" width="14.54296875" customWidth="1"/>
+    <col min="14855" max="14855" width="15.26953125" customWidth="1"/>
+    <col min="14856" max="14857" width="14.453125" customWidth="1"/>
+    <col min="14858" max="14858" width="13.1796875" customWidth="1"/>
+    <col min="14859" max="14861" width="14.453125" customWidth="1"/>
+    <col min="14862" max="14862" width="15.81640625" customWidth="1"/>
+    <col min="14863" max="14863" width="7.81640625" customWidth="1"/>
+    <col min="14864" max="14864" width="5.453125" customWidth="1"/>
+    <col min="14865" max="14865" width="6.453125" customWidth="1"/>
+    <col min="14866" max="14866" width="7.81640625" customWidth="1"/>
+    <col min="14867" max="14867" width="3" customWidth="1"/>
+    <col min="14868" max="14868" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15105" max="15108" width="14.453125" customWidth="1"/>
+    <col min="15109" max="15109" width="15.453125" customWidth="1"/>
+    <col min="15110" max="15110" width="14.54296875" customWidth="1"/>
+    <col min="15111" max="15111" width="15.26953125" customWidth="1"/>
+    <col min="15112" max="15113" width="14.453125" customWidth="1"/>
+    <col min="15114" max="15114" width="13.1796875" customWidth="1"/>
+    <col min="15115" max="15117" width="14.453125" customWidth="1"/>
+    <col min="15118" max="15118" width="15.81640625" customWidth="1"/>
+    <col min="15119" max="15119" width="7.81640625" customWidth="1"/>
+    <col min="15120" max="15120" width="5.453125" customWidth="1"/>
+    <col min="15121" max="15121" width="6.453125" customWidth="1"/>
+    <col min="15122" max="15122" width="7.81640625" customWidth="1"/>
+    <col min="15123" max="15123" width="3" customWidth="1"/>
+    <col min="15124" max="15124" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15361" max="15364" width="14.453125" customWidth="1"/>
+    <col min="15365" max="15365" width="15.453125" customWidth="1"/>
+    <col min="15366" max="15366" width="14.54296875" customWidth="1"/>
+    <col min="15367" max="15367" width="15.26953125" customWidth="1"/>
+    <col min="15368" max="15369" width="14.453125" customWidth="1"/>
+    <col min="15370" max="15370" width="13.1796875" customWidth="1"/>
+    <col min="15371" max="15373" width="14.453125" customWidth="1"/>
+    <col min="15374" max="15374" width="15.81640625" customWidth="1"/>
+    <col min="15375" max="15375" width="7.81640625" customWidth="1"/>
+    <col min="15376" max="15376" width="5.453125" customWidth="1"/>
+    <col min="15377" max="15377" width="6.453125" customWidth="1"/>
+    <col min="15378" max="15378" width="7.81640625" customWidth="1"/>
+    <col min="15379" max="15379" width="3" customWidth="1"/>
+    <col min="15380" max="15380" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15617" max="15620" width="14.453125" customWidth="1"/>
+    <col min="15621" max="15621" width="15.453125" customWidth="1"/>
+    <col min="15622" max="15622" width="14.54296875" customWidth="1"/>
+    <col min="15623" max="15623" width="15.26953125" customWidth="1"/>
+    <col min="15624" max="15625" width="14.453125" customWidth="1"/>
+    <col min="15626" max="15626" width="13.1796875" customWidth="1"/>
+    <col min="15627" max="15629" width="14.453125" customWidth="1"/>
+    <col min="15630" max="15630" width="15.81640625" customWidth="1"/>
+    <col min="15631" max="15631" width="7.81640625" customWidth="1"/>
+    <col min="15632" max="15632" width="5.453125" customWidth="1"/>
+    <col min="15633" max="15633" width="6.453125" customWidth="1"/>
+    <col min="15634" max="15634" width="7.81640625" customWidth="1"/>
+    <col min="15635" max="15635" width="3" customWidth="1"/>
+    <col min="15636" max="15636" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15873" max="15876" width="14.453125" customWidth="1"/>
+    <col min="15877" max="15877" width="15.453125" customWidth="1"/>
+    <col min="15878" max="15878" width="14.54296875" customWidth="1"/>
+    <col min="15879" max="15879" width="15.26953125" customWidth="1"/>
+    <col min="15880" max="15881" width="14.453125" customWidth="1"/>
+    <col min="15882" max="15882" width="13.1796875" customWidth="1"/>
+    <col min="15883" max="15885" width="14.453125" customWidth="1"/>
+    <col min="15886" max="15886" width="15.81640625" customWidth="1"/>
+    <col min="15887" max="15887" width="7.81640625" customWidth="1"/>
+    <col min="15888" max="15888" width="5.453125" customWidth="1"/>
+    <col min="15889" max="15889" width="6.453125" customWidth="1"/>
+    <col min="15890" max="15890" width="7.81640625" customWidth="1"/>
+    <col min="15891" max="15891" width="3" customWidth="1"/>
+    <col min="15892" max="15892" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="16129" max="16132" width="14.453125" customWidth="1"/>
+    <col min="16133" max="16133" width="15.453125" customWidth="1"/>
+    <col min="16134" max="16134" width="14.54296875" customWidth="1"/>
+    <col min="16135" max="16135" width="15.26953125" customWidth="1"/>
+    <col min="16136" max="16137" width="14.453125" customWidth="1"/>
+    <col min="16138" max="16138" width="13.1796875" customWidth="1"/>
+    <col min="16139" max="16141" width="14.453125" customWidth="1"/>
+    <col min="16142" max="16142" width="15.81640625" customWidth="1"/>
+    <col min="16143" max="16143" width="7.81640625" customWidth="1"/>
+    <col min="16144" max="16144" width="5.453125" customWidth="1"/>
+    <col min="16145" max="16145" width="6.453125" customWidth="1"/>
+    <col min="16146" max="16146" width="7.81640625" customWidth="1"/>
+    <col min="16147" max="16147" width="3" customWidth="1"/>
+    <col min="16148" max="16148" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="297" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
+      <c r="S1"/>
+    </row>
+    <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2"/>
+    </row>
+    <row r="3" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="298" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="306" t="s">
+        <v>99</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="I3" s="129" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="305" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="299" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="26"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="307" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" s="308"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="301" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="302"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="29"/>
+    </row>
+    <row r="4" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="298"/>
+      <c r="E4" s="258" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" s="306"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="305"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="299"/>
+      <c r="O4" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" s="291" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" s="292" t="s">
+        <v>71</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" s="287" t="s">
+        <v>70</v>
+      </c>
+      <c r="U4" s="288" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="260" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="37"/>
+      <c r="E5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="306" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="298" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="38"/>
+      <c r="O5" s="39">
+        <v>31</v>
+      </c>
+      <c r="P5" s="40">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="41">
+        <v>19</v>
+      </c>
+      <c r="R5" s="42">
+        <v>11</v>
+      </c>
+      <c r="S5" s="40">
+        <v>31</v>
+      </c>
+      <c r="T5" s="41">
+        <v>19</v>
+      </c>
+      <c r="U5" s="42">
+        <v>11</v>
+      </c>
+      <c r="V5" s="43">
+        <f t="shared" ref="V5:V17" si="0">-SUM(S5-P5)*-1</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="44"/>
+    </row>
+    <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="45"/>
+      <c r="C6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F6" s="306"/>
+      <c r="G6" s="278"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="129" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="298"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="N6" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" s="47">
+        <v>49</v>
+      </c>
+      <c r="P6" s="48">
+        <f t="shared" ref="P6:P17" si="1">SUM(Q6:R6)</f>
+        <v>12</v>
+      </c>
+      <c r="Q6" s="49">
+        <v>7</v>
+      </c>
+      <c r="R6" s="50">
+        <v>5</v>
+      </c>
+      <c r="S6" s="48">
+        <f t="shared" ref="S6:S17" si="2">SUM(T6:U6)</f>
+        <v>12</v>
+      </c>
+      <c r="T6" s="49">
+        <v>7</v>
+      </c>
+      <c r="U6" s="50">
+        <v>5</v>
+      </c>
+      <c r="V6" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="52"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="53"/>
+      <c r="C7" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="306" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" s="278"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="299" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" s="54"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="47">
+        <v>22</v>
+      </c>
+      <c r="P7" s="48">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Q7" s="49">
+        <v>11</v>
+      </c>
+      <c r="R7" s="50">
+        <v>4</v>
+      </c>
+      <c r="S7" s="48">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="T7" s="49">
+        <v>11</v>
+      </c>
+      <c r="U7" s="50">
+        <v>4</v>
+      </c>
+      <c r="V7" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W7" s="52"/>
+    </row>
+    <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="45"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="260" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F8" s="306"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="299"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="56">
+        <v>46316</v>
+      </c>
+      <c r="O8" s="47">
+        <v>24</v>
+      </c>
+      <c r="P8" s="48">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Q8" s="49">
+        <v>3</v>
+      </c>
+      <c r="R8" s="50">
+        <v>3</v>
+      </c>
+      <c r="S8" s="48">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="T8" s="49">
+        <v>2</v>
+      </c>
+      <c r="U8" s="50">
+        <v>2</v>
+      </c>
+      <c r="V8" s="51">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="W8" s="52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="45"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="58"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="296" t="s">
+        <v>258</v>
+      </c>
+      <c r="G9" s="62"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9" s="47"/>
+      <c r="P9" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="49"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W9" s="52"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="45"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="129" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="61"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="296"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="49"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="52"/>
+    </row>
+    <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="64"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="D11" s="61"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="G11" s="64"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="66"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="68"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="70"/>
+    </row>
+    <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="71"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="258" t="s">
+        <v>262</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="L12" s="73" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" s="74"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="68"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W12" s="70"/>
+    </row>
+    <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="61"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="293" t="s">
+        <v>150</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="299" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="30"/>
+      <c r="J13" s="127" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="128"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="60"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="68"/>
+      <c r="U13" s="69"/>
+      <c r="V13" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="70"/>
+    </row>
+    <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="8"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="293" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="299"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="60"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="68"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="70"/>
+    </row>
+    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="129"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="290"/>
+      <c r="F15" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="107"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="68"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="70"/>
+    </row>
+    <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="296" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="296" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="299" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="61"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="294" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="107"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="68"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="68"/>
+      <c r="U16" s="69"/>
+      <c r="V16" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="70"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="296"/>
+      <c r="B17" s="296"/>
+      <c r="C17" s="299"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="59"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="80"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="82">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="83"/>
+    </row>
+    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="77"/>
+      <c r="M18" s="77"/>
+      <c r="R18" s="84"/>
+      <c r="S18"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="290"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="77"/>
+      <c r="R19" s="84"/>
+      <c r="S19"/>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="129" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="85" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="290"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="158"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="R20" s="84"/>
+      <c r="S20"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="128" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="D21" s="61"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="R21" s="84"/>
+      <c r="S21"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="6"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="290"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="R22" s="84"/>
+      <c r="S22"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="R23" s="84"/>
+      <c r="S23"/>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="R24" s="84"/>
+      <c r="S24"/>
+    </row>
+    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="30"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="R25" s="84"/>
+      <c r="S25"/>
+    </row>
+    <row r="26" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="290"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="R26" s="84"/>
+      <c r="S26"/>
+    </row>
+    <row r="27" spans="1:23" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="R27" s="84"/>
+      <c r="S27"/>
+    </row>
+    <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="300" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="R28" s="84"/>
+      <c r="S28"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="30"/>
+      <c r="I29" s="290"/>
+      <c r="J29" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K29" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="92" t="s">
+        <v>25</v>
+      </c>
+      <c r="R29" s="84"/>
+      <c r="S29"/>
+    </row>
+    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="93" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="94"/>
+      <c r="C30" s="93" t="s">
+        <v>249</v>
+      </c>
+      <c r="D30" s="93" t="s">
+        <v>251</v>
+      </c>
+      <c r="E30" s="304" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="8"/>
+      <c r="G30" s="289" t="s">
+        <v>269</v>
+      </c>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="159" t="s">
+        <v>150</v>
+      </c>
+      <c r="K30" s="124" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="218" t="s">
+        <v>119</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="R30" s="84"/>
+      <c r="S30"/>
+    </row>
+    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C31" s="93" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" s="93" t="s">
+        <v>252</v>
+      </c>
+      <c r="E31" s="304"/>
+      <c r="F31" s="8"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="159" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="L31" s="218" t="s">
+        <v>122</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" s="84"/>
+      <c r="S31"/>
+    </row>
+    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="B32" s="94"/>
+      <c r="C32" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="93" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="304" t="s">
+        <v>259</v>
+      </c>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="159"/>
+      <c r="K32" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="L32" s="218" t="s">
+        <v>243</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="R32" s="84"/>
+      <c r="S32"/>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="8"/>
+      <c r="C33" s="93" t="s">
+        <v>267</v>
+      </c>
+      <c r="D33" s="93" t="s">
+        <v>253</v>
+      </c>
+      <c r="E33" s="304"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="110" t="s">
+        <v>16</v>
+      </c>
+      <c r="L33" s="218" t="s">
+        <v>38</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="R33" s="84"/>
+      <c r="S33"/>
+    </row>
+    <row r="34" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="94"/>
+      <c r="B34" s="95"/>
+      <c r="D34" s="93" t="s">
+        <v>254</v>
+      </c>
+      <c r="E34" s="304" t="s">
+        <v>260</v>
+      </c>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="K34" s="110" t="s">
+        <v>203</v>
+      </c>
+      <c r="M34" s="8"/>
+      <c r="R34" s="84"/>
+      <c r="S34"/>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="94"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="93" t="s">
+        <v>255</v>
+      </c>
+      <c r="E35" s="304"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="224" t="s">
+        <v>58</v>
+      </c>
+      <c r="L35" s="8"/>
+      <c r="M35" s="13"/>
+      <c r="R35" s="84"/>
+      <c r="S35"/>
+    </row>
+    <row r="36" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="94"/>
+      <c r="B36" s="94"/>
+      <c r="D36" s="93" t="s">
+        <v>256</v>
+      </c>
+      <c r="E36" s="304" t="s">
+        <v>261</v>
+      </c>
+      <c r="F36" s="53"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="97"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="124" t="s">
+        <v>211</v>
+      </c>
+      <c r="L36" s="8"/>
+      <c r="M36" s="94"/>
+      <c r="R36" s="84"/>
+      <c r="S36"/>
+    </row>
+    <row r="37" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="E37" s="304"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="100"/>
+      <c r="K37" s="124" t="s">
+        <v>212</v>
+      </c>
+      <c r="L37" s="8"/>
+      <c r="M37" s="94"/>
+      <c r="R37" s="84"/>
+      <c r="S37"/>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="77"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="289" t="s">
+        <v>270</v>
+      </c>
+      <c r="F38" s="77"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="2"/>
+      <c r="R38" s="84"/>
+      <c r="S38"/>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="74"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="289" t="s">
+        <v>271</v>
+      </c>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="2"/>
+      <c r="S39"/>
+    </row>
+    <row r="40" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="131" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="105"/>
+      <c r="S40"/>
+    </row>
+    <row r="41" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="104"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="104"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="93" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="8"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="101"/>
+      <c r="M41" s="106"/>
+      <c r="S41"/>
+    </row>
+    <row r="42" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="104"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="104"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="289" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42" s="104"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="106"/>
+      <c r="S42"/>
+    </row>
+    <row r="43" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="104"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="289" t="s">
+        <v>268</v>
+      </c>
+      <c r="F43" s="107"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="106"/>
+      <c r="S43"/>
+    </row>
+    <row r="44" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="104"/>
+      <c r="B44" s="104"/>
+      <c r="C44" s="104"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="109"/>
+      <c r="S44"/>
+    </row>
+    <row r="45" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="104"/>
+      <c r="B45" s="104"/>
+      <c r="C45" s="104"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="110"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="111"/>
+      <c r="S45"/>
+    </row>
+    <row r="46" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="104"/>
+      <c r="B46" s="104"/>
+      <c r="C46" s="104"/>
+      <c r="D46" s="104"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="104"/>
+      <c r="J46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="111"/>
+      <c r="S46"/>
+    </row>
+    <row r="47" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="104"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="104"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="104"/>
+      <c r="H47" s="104"/>
+      <c r="I47" s="290"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="112"/>
+      <c r="S47"/>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="84"/>
+      <c r="S48"/>
+    </row>
+    <row r="49" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="77"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="113"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="104"/>
+      <c r="I49" s="290"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="84"/>
+      <c r="S49"/>
+    </row>
+    <row r="50" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="77"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="84"/>
+      <c r="S50"/>
+    </row>
+    <row r="51" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="77"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="77"/>
+      <c r="D51" s="113"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="77"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="84"/>
+      <c r="S51"/>
+    </row>
+    <row r="52" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="77"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="113"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="77"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="77"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+    </row>
+    <row r="53" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="77"/>
+      <c r="B53" s="77"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="113"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="77"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="114"/>
+      <c r="M53" s="8"/>
+    </row>
+    <row r="54" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="77"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="113"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="77"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="77"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="114"/>
+      <c r="M54" s="8"/>
+    </row>
+    <row r="55" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="77"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="113"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="77"/>
+      <c r="G55" s="77"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="104"/>
+      <c r="J55" s="77"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="114"/>
+      <c r="M55" s="8"/>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="77"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="113"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="77"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="77"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="114"/>
+      <c r="M56" s="8"/>
+    </row>
+    <row r="57" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="77"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="77"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="114"/>
+      <c r="M57" s="8"/>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="77"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="113"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="77"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="115"/>
+      <c r="L58" s="114"/>
+      <c r="M58" s="8"/>
+    </row>
+    <row r="59" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="77"/>
+      <c r="B59" s="77"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="113"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="77"/>
+      <c r="G59" s="77"/>
+      <c r="H59" s="104"/>
+      <c r="I59" s="104"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="115"/>
+      <c r="L59" s="114"/>
+      <c r="M59" s="8"/>
+    </row>
+    <row r="60" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="77"/>
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="77"/>
+      <c r="G60" s="77"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="115"/>
+      <c r="L60" s="114"/>
+      <c r="M60" s="8"/>
+    </row>
+    <row r="61" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="77"/>
+      <c r="B61" s="77"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="113"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="114"/>
+      <c r="M61" s="8"/>
+    </row>
+    <row r="62" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="77"/>
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="77"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="114"/>
+      <c r="M62" s="8"/>
+    </row>
+    <row r="63" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="77"/>
+      <c r="B63" s="77"/>
+      <c r="C63" s="77"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="104"/>
+      <c r="I63" s="104"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="77"/>
+      <c r="M63" s="8"/>
+    </row>
+    <row r="64" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="77"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="77"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="77"/>
+      <c r="H64" s="104"/>
+      <c r="I64" s="104"/>
+      <c r="J64" s="77"/>
+      <c r="K64" s="116">
+        <v>22</v>
+      </c>
+      <c r="L64" s="117">
+        <v>6</v>
+      </c>
+      <c r="M64" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="61"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
+      <c r="S65"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L66" s="119" t="s">
+        <v>94</v>
+      </c>
+      <c r="M66" s="25">
+        <v>97</v>
+      </c>
+      <c r="S66"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L67" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="M67" s="25">
+        <f>SUM(M66-(M68+M69+M70))</f>
+        <v>69</v>
+      </c>
+      <c r="S67"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L68" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" s="25">
+        <v>15</v>
+      </c>
+      <c r="S68"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L69" s="121" t="s">
+        <v>24</v>
+      </c>
+      <c r="M69" s="25">
+        <v>9</v>
+      </c>
+      <c r="S69"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L70" s="122" t="s">
+        <v>25</v>
+      </c>
+      <c r="M70" s="25">
+        <v>4</v>
+      </c>
+      <c r="S70"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="L71" t="s">
+        <v>96</v>
+      </c>
+      <c r="M71" s="25">
+        <v>13</v>
+      </c>
+      <c r="S71"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="M72" s="25"/>
+      <c r="S72"/>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="Q3:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -25809,21 +28506,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -25878,13 +28575,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="290" t="s">
+      <c r="D3" s="298" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="298" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -25897,20 +28594,20 @@
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="299" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -25922,11 +28619,11 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="290"/>
+      <c r="D4" s="298"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="290"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
@@ -25935,7 +28632,7 @@
       <c r="J4" s="296"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="299"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -25974,7 +28671,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -25982,7 +28679,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -26027,13 +28724,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -26088,7 +28785,7 @@
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="292" t="s">
+      <c r="J7" s="305" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -26140,7 +28837,7 @@
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="292"/>
+      <c r="J8" s="305"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -26184,7 +28881,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="293" t="s">
+      <c r="F9" s="306" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -26224,7 +28921,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="293"/>
+      <c r="F10" s="306"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -26350,7 +29047,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="297" t="s">
+      <c r="I13" s="299" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -26391,7 +29088,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="297"/>
+      <c r="I14" s="299"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -26457,7 +29154,7 @@
       <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="298" t="s">
+      <c r="C16" s="309" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -26494,7 +29191,7 @@
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="296"/>
       <c r="B17" s="296"/>
-      <c r="C17" s="299"/>
+      <c r="C17" s="310"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -26527,7 +29224,7 @@
     <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="297" t="s">
+      <c r="C18" s="299" t="s">
         <v>82</v>
       </c>
       <c r="D18" s="61"/>
@@ -26545,7 +29242,7 @@
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="147"/>
-      <c r="C19" s="297"/>
+      <c r="C19" s="299"/>
       <c r="D19" s="125"/>
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
@@ -26704,13 +29401,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -26770,7 +29467,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -26804,7 +29501,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -26834,7 +29531,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -26864,7 +29561,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -26888,7 +29585,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="289" t="s">
+      <c r="E34" s="303" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -26913,7 +29610,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="289"/>
+      <c r="E35" s="303"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -26932,7 +29629,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -26952,7 +29649,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -27480,28 +30177,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="C18:C19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -28422,21 +31119,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -28491,13 +31188,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="290" t="s">
+      <c r="D3" s="298" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="298" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -28510,20 +31207,20 @@
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="299" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -28535,11 +31232,11 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="290"/>
+      <c r="D4" s="298"/>
       <c r="E4" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="290"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
@@ -28548,7 +31245,7 @@
       <c r="J4" s="296"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="299"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -28587,7 +31284,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -28595,7 +31292,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -28640,13 +31337,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -28696,7 +31393,7 @@
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="292" t="s">
+      <c r="J7" s="305" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -28748,7 +31445,7 @@
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="292"/>
+      <c r="J8" s="305"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -28792,7 +31489,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="293" t="s">
+      <c r="F9" s="306" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -28832,7 +31529,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="293"/>
+      <c r="F10" s="306"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -28958,7 +31655,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="297" t="s">
+      <c r="I13" s="299" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -28999,7 +31696,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="297"/>
+      <c r="I14" s="299"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -29034,7 +31731,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="297" t="s">
+      <c r="I15" s="299" t="s">
         <v>82</v>
       </c>
       <c r="J15" s="60"/>
@@ -29067,7 +31764,7 @@
       <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="298" t="s">
+      <c r="C16" s="309" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -29077,7 +31774,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="297"/>
+      <c r="I16" s="299"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -29104,13 +31801,13 @@
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="296"/>
       <c r="B17" s="296"/>
-      <c r="C17" s="299"/>
+      <c r="C17" s="310"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="293" t="s">
+      <c r="I17" s="306" t="s">
         <v>139</v>
       </c>
       <c r="J17" s="71"/>
@@ -29145,7 +31842,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="293"/>
+      <c r="I18" s="306"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -29317,13 +32014,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -29383,7 +32080,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -29417,7 +32114,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -29447,7 +32144,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -29477,7 +32174,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -29503,7 +32200,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="289" t="s">
+      <c r="E34" s="303" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -29526,7 +32223,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="289"/>
+      <c r="E35" s="303"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -29546,7 +32243,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -29563,7 +32260,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -30091,29 +32788,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="I13:I14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -31031,21 +33728,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -31098,13 +33795,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="290" t="s">
+      <c r="D3" s="298" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="298" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -31117,20 +33814,20 @@
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="299" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -31142,11 +33839,11 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="290"/>
+      <c r="D4" s="298"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="290"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
@@ -31155,7 +33852,7 @@
       <c r="J4" s="296"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="299"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -31194,7 +33891,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -31202,7 +33899,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -31247,13 +33944,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -31303,7 +34000,7 @@
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="292" t="s">
+      <c r="J7" s="305" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -31357,7 +34054,7 @@
       <c r="I8" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="J8" s="292"/>
+      <c r="J8" s="305"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -31401,13 +34098,13 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="293" t="s">
+      <c r="F9" s="306" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
       <c r="H9" s="30"/>
       <c r="I9" s="134"/>
-      <c r="J9" s="297" t="s">
+      <c r="J9" s="299" t="s">
         <v>82</v>
       </c>
       <c r="K9" s="54"/>
@@ -31443,11 +34140,11 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="293"/>
+      <c r="F10" s="306"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
-      <c r="J10" s="297"/>
+      <c r="J10" s="299"/>
       <c r="K10" s="6"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
@@ -31570,7 +34267,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="297" t="s">
+      <c r="I13" s="299" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -31611,7 +34308,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="297"/>
+      <c r="I14" s="299"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -31646,7 +34343,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="303" t="s">
+      <c r="I15" s="311" t="s">
         <v>139</v>
       </c>
       <c r="J15" s="60"/>
@@ -31679,7 +34376,7 @@
       <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="298" t="s">
+      <c r="C16" s="309" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="61"/>
@@ -31689,7 +34386,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="303"/>
+      <c r="I16" s="311"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -31716,7 +34413,7 @@
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="296"/>
       <c r="B17" s="296"/>
-      <c r="C17" s="299"/>
+      <c r="C17" s="310"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -31927,13 +34624,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -31993,7 +34690,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -32027,7 +34724,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -32057,7 +34754,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -32082,7 +34779,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -32103,7 +34800,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="289" t="s">
+      <c r="E34" s="303" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -32126,7 +34823,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="289"/>
+      <c r="E35" s="303"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -32146,7 +34843,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -32166,7 +34863,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -32694,17 +35391,11 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="A16:A17"/>
@@ -32712,11 +35403,17 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -33633,21 +36330,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -33702,13 +36399,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="290" t="s">
+      <c r="D3" s="298" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="298" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -33721,20 +36418,20 @@
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="299" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -33746,11 +36443,11 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="290"/>
+      <c r="D4" s="298"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="290"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
@@ -33759,7 +36456,7 @@
       <c r="J4" s="296"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="299"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -33798,7 +36495,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -33806,7 +36503,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -33851,13 +36548,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -33912,7 +36609,7 @@
       <c r="I7" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="292" t="s">
+      <c r="J7" s="305" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -33963,7 +36660,7 @@
       <c r="F8" s="296"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
-      <c r="J8" s="292"/>
+      <c r="J8" s="305"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -34007,7 +36704,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="293" t="s">
+      <c r="F9" s="306" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -34047,7 +36744,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="293"/>
+      <c r="F10" s="306"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -34174,7 +36871,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="297" t="s">
+      <c r="I13" s="299" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -34212,7 +36909,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="297"/>
+      <c r="I14" s="299"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -34247,7 +36944,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="297" t="s">
+      <c r="I15" s="299" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -34280,7 +36977,7 @@
       <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="293" t="s">
+      <c r="C16" s="306" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -34290,7 +36987,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="297"/>
+      <c r="I16" s="299"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -34317,13 +37014,13 @@
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="296"/>
       <c r="B17" s="296"/>
-      <c r="C17" s="293"/>
+      <c r="C17" s="306"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="297" t="s">
+      <c r="I17" s="299" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -34358,7 +37055,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="297"/>
+      <c r="I18" s="299"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -34528,13 +37225,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -34594,7 +37291,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -34628,7 +37325,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -34658,7 +37355,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -34684,7 +37381,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -34706,7 +37403,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="289" t="s">
+      <c r="E34" s="303" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -34729,7 +37426,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="289"/>
+      <c r="E35" s="303"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -34749,7 +37446,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -34766,7 +37463,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -35294,17 +37991,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="I17:I18"/>
     <mergeCell ref="A1:M1"/>
@@ -35317,6 +38003,17 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="I13:I14"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -36236,21 +38933,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -36305,13 +39002,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="290" t="s">
+      <c r="D3" s="298" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="298" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -36324,20 +39021,20 @@
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="297" t="s">
+      <c r="M3" s="299" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -36349,11 +39046,11 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="290"/>
+      <c r="D4" s="298"/>
       <c r="E4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="290"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
@@ -36362,7 +39059,7 @@
       <c r="J4" s="296"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="297"/>
+      <c r="M4" s="299"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -36401,7 +39098,7 @@
       <c r="E5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -36409,7 +39106,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -36454,13 +39151,13 @@
       <c r="E6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -36513,7 +39210,7 @@
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="292" t="s">
+      <c r="J7" s="305" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -36563,7 +39260,7 @@
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="292"/>
+      <c r="J8" s="305"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -36608,7 +39305,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="293" t="s">
+      <c r="F9" s="306" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -36648,7 +39345,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="293"/>
+      <c r="F10" s="306"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -36775,7 +39472,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="297" t="s">
+      <c r="I13" s="299" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -36816,7 +39513,7 @@
         <v>150</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="297"/>
+      <c r="I14" s="299"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -36851,7 +39548,7 @@
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="30"/>
-      <c r="I15" s="297" t="s">
+      <c r="I15" s="299" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="60"/>
@@ -36884,7 +39581,7 @@
       <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="293" t="s">
+      <c r="C16" s="306" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="61"/>
@@ -36894,7 +39591,7 @@
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="30"/>
-      <c r="I16" s="297"/>
+      <c r="I16" s="299"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -36921,13 +39618,13 @@
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="296"/>
       <c r="B17" s="296"/>
-      <c r="C17" s="293"/>
+      <c r="C17" s="306"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
       <c r="H17" s="30"/>
-      <c r="I17" s="297" t="s">
+      <c r="I17" s="299" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="71"/>
@@ -36962,7 +39659,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
       <c r="H18" s="30"/>
-      <c r="I18" s="297"/>
+      <c r="I18" s="299"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
       <c r="L18" s="77"/>
@@ -37133,13 +39830,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -37199,7 +39896,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -37233,7 +39930,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -37261,7 +39958,7 @@
       <c r="D32" s="93" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -37287,7 +39984,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -37309,7 +40006,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="289" t="s">
+      <c r="E34" s="303" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -37332,7 +40029,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="289"/>
+      <c r="E35" s="303"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -37352,7 +40049,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -37372,7 +40069,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -37902,29 +40599,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -37956,18 +40653,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="193" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="311" t="s">
+      <c r="A1" s="312" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="312"/>
-      <c r="C1" s="312"/>
-      <c r="D1" s="312"/>
-      <c r="E1" s="312"/>
-      <c r="F1" s="312"/>
-      <c r="G1" s="312"/>
-      <c r="H1" s="312"/>
-      <c r="I1" s="313"/>
-      <c r="J1" s="313"/>
+      <c r="B1" s="313"/>
+      <c r="C1" s="313"/>
+      <c r="D1" s="313"/>
+      <c r="E1" s="313"/>
+      <c r="F1" s="313"/>
+      <c r="G1" s="313"/>
+      <c r="H1" s="313"/>
+      <c r="I1" s="314"/>
+      <c r="J1" s="314"/>
       <c r="K1" s="190"/>
       <c r="L1" s="190"/>
       <c r="M1" s="191"/>
@@ -38073,22 +40770,22 @@
       <c r="C3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="290" t="s">
+      <c r="D3" s="298" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="201" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="304" t="s">
+      <c r="F3" s="315" t="s">
         <v>160</v>
       </c>
       <c r="H3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="292" t="s">
+      <c r="I3" s="305" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="305" t="s">
+      <c r="K3" s="316" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="2"/>
@@ -38104,16 +40801,16 @@
       <c r="C4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="290"/>
+      <c r="D4" s="298"/>
       <c r="E4" s="201" t="s">
         <v>162</v>
       </c>
-      <c r="F4" s="304"/>
+      <c r="F4" s="315"/>
       <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="292"/>
-      <c r="K4" s="306"/>
+      <c r="I4" s="305"/>
+      <c r="K4" s="317"/>
       <c r="L4" s="203" t="s">
         <v>163</v>
       </c>
@@ -38126,13 +40823,13 @@
       <c r="E5" s="129" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="304" t="s">
+      <c r="F5" s="315" t="s">
         <v>165</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="290" t="s">
+      <c r="I5" s="298" t="s">
         <v>166</v>
       </c>
       <c r="K5" s="2"/>
@@ -38146,11 +40843,11 @@
       <c r="E6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="304"/>
+      <c r="F6" s="315"/>
       <c r="H6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="290"/>
+      <c r="I6" s="298"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -38165,10 +40862,10 @@
       <c r="E7" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F7" s="290" t="s">
+      <c r="F7" s="298" t="s">
         <v>168</v>
       </c>
-      <c r="I7" s="290" t="s">
+      <c r="I7" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K7" s="2"/>
@@ -38182,17 +40879,17 @@
       <c r="E8" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="290"/>
-      <c r="I8" s="290"/>
+      <c r="F8" s="298"/>
+      <c r="I8" s="298"/>
       <c r="K8" s="2"/>
       <c r="L8" s="206"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="298" t="s">
+      <c r="A9" s="309" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="290" t="s">
+      <c r="B9" s="298" t="s">
         <v>171</v>
       </c>
       <c r="C9" s="207" t="s">
@@ -38201,7 +40898,7 @@
       <c r="E9" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="304" t="s">
+      <c r="F9" s="315" t="s">
         <v>173</v>
       </c>
       <c r="K9" s="2"/>
@@ -38211,15 +40908,15 @@
       <c r="P9"/>
     </row>
     <row r="10" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="299"/>
-      <c r="B10" s="290"/>
+      <c r="A10" s="310"/>
+      <c r="B10" s="298"/>
       <c r="C10" s="208" t="s">
         <v>174</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>175</v>
       </c>
-      <c r="F10" s="304"/>
+      <c r="F10" s="315"/>
       <c r="K10" s="209"/>
       <c r="L10" s="2"/>
       <c r="M10" s="206"/>
@@ -38314,10 +41011,10 @@
       <c r="E13" s="183" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="307" t="s">
+      <c r="F13" s="318" t="s">
         <v>184</v>
       </c>
-      <c r="H13" s="298" t="s">
+      <c r="H13" s="309" t="s">
         <v>185</v>
       </c>
       <c r="K13" s="2"/>
@@ -38347,8 +41044,8 @@
       <c r="E14" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="F14" s="308"/>
-      <c r="H14" s="299"/>
+      <c r="F14" s="319"/>
+      <c r="H14" s="310"/>
       <c r="K14" s="2"/>
       <c r="L14" s="6"/>
       <c r="M14" s="2"/>
@@ -38375,10 +41072,10 @@
       <c r="E15" s="183" t="s">
         <v>189</v>
       </c>
-      <c r="F15" s="290" t="s">
+      <c r="F15" s="298" t="s">
         <v>190</v>
       </c>
-      <c r="H15" s="305" t="s">
+      <c r="H15" s="316" t="s">
         <v>45</v>
       </c>
       <c r="K15" s="2"/>
@@ -38403,8 +41100,8 @@
       <c r="C16" s="183" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="290"/>
-      <c r="H16" s="306"/>
+      <c r="F16" s="298"/>
+      <c r="H16" s="317"/>
       <c r="K16" s="2"/>
       <c r="L16" s="209"/>
       <c r="M16" s="8"/>
@@ -38431,7 +41128,7 @@
       </c>
       <c r="D17" s="206"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="309" t="s">
+      <c r="F17" s="320" t="s">
         <v>193</v>
       </c>
       <c r="G17" s="2"/>
@@ -38448,7 +41145,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="310"/>
+      <c r="F18" s="321"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="209"/>
@@ -38499,7 +41196,7 @@
       <c r="B20" s="133" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="290" t="s">
+      <c r="C20" s="298" t="s">
         <v>197</v>
       </c>
       <c r="D20" s="2"/>
@@ -38531,7 +41228,7 @@
         <v>199</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="290"/>
+      <c r="C21" s="298"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="219" t="s">
@@ -38539,7 +41236,7 @@
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="305" t="s">
+      <c r="I21" s="316" t="s">
         <v>82</v>
       </c>
       <c r="J21" s="209"/>
@@ -38573,7 +41270,7 @@
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="306"/>
+      <c r="I22" s="317"/>
       <c r="J22" s="209"/>
       <c r="K22" s="101" t="s">
         <v>40</v>
@@ -39303,11 +42000,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="F9:F10"/>
@@ -39318,11 +42015,11 @@
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="F17:F18"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -40242,21 +42939,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -40311,13 +43008,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="297" t="s">
+      <c r="D3" s="299" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="298" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -40326,24 +43023,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="297" t="s">
+      <c r="J3" s="299" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="314" t="s">
+      <c r="M3" s="322" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -40357,20 +43054,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="297"/>
+      <c r="D4" s="299"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="290"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="297"/>
+      <c r="J4" s="299"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="314"/>
+      <c r="M4" s="322"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -40409,7 +43106,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -40417,7 +43114,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -40462,13 +43159,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -40518,7 +43215,7 @@
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="292" t="s">
+      <c r="J7" s="305" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -40570,7 +43267,7 @@
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="292"/>
+      <c r="J8" s="305"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -40615,7 +43312,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="293" t="s">
+      <c r="F9" s="306" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -40655,7 +43352,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="293"/>
+      <c r="F10" s="306"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -40883,7 +43580,7 @@
       <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="297" t="s">
+      <c r="C16" s="299" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -40920,7 +43617,7 @@
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="296"/>
       <c r="B17" s="296"/>
-      <c r="C17" s="297"/>
+      <c r="C17" s="299"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -41130,13 +43827,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -41196,7 +43893,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -41228,7 +43925,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -41256,7 +43953,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -41284,7 +43981,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -41308,7 +44005,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="289" t="s">
+      <c r="E34" s="303" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -41331,7 +44028,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="289"/>
+      <c r="E35" s="303"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -41351,7 +44048,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -41371,7 +44068,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -41899,6 +44596,18 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="J5:J6"/>
@@ -41907,18 +44616,6 @@
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="J7:J8"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -42836,21 +45533,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="301"/>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="301"/>
-      <c r="J1" s="301"/>
-      <c r="K1" s="301"/>
-      <c r="L1" s="301"/>
-      <c r="M1" s="301"/>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="297"/>
+      <c r="G1" s="297"/>
+      <c r="H1" s="297"/>
+      <c r="I1" s="297"/>
+      <c r="J1" s="297"/>
+      <c r="K1" s="297"/>
+      <c r="L1" s="297"/>
+      <c r="M1" s="297"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -42905,13 +45602,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="297" t="s">
+      <c r="D3" s="299" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="290" t="s">
+      <c r="F3" s="298" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -42920,24 +45617,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="297" t="s">
+      <c r="J3" s="299" t="s">
         <v>82</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="314" t="s">
+      <c r="M3" s="322" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="294" t="s">
+      <c r="Q3" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="295"/>
+      <c r="R3" s="308"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="287" t="s">
+      <c r="T3" s="301" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="288"/>
+      <c r="U3" s="302"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -42951,20 +45648,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="297"/>
+      <c r="D4" s="299"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="290"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="297"/>
+      <c r="J4" s="299"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="314"/>
+      <c r="M4" s="322"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -43003,7 +45700,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="306" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -43011,7 +45708,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="290" t="s">
+      <c r="J5" s="298" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -43056,13 +45753,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="293"/>
+      <c r="F6" s="306"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="290"/>
+      <c r="J6" s="298"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -43112,7 +45809,7 @@
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="292" t="s">
+      <c r="J7" s="305" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -43164,7 +45861,7 @@
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="292"/>
+      <c r="J8" s="305"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -43209,7 +45906,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="293" t="s">
+      <c r="F9" s="306" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -43249,7 +45946,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="293"/>
+      <c r="F10" s="306"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -43477,7 +46174,7 @@
       <c r="B16" s="296" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="297" t="s">
+      <c r="C16" s="299" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -43514,7 +46211,7 @@
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="296"/>
       <c r="B17" s="296"/>
-      <c r="C17" s="297"/>
+      <c r="C17" s="299"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -43724,13 +46421,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="300" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="302"/>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
+      <c r="B28" s="300"/>
+      <c r="C28" s="300"/>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -43790,7 +46487,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="291" t="s">
+      <c r="E30" s="304" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -43824,7 +46521,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="291"/>
+      <c r="E31" s="304"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -43852,7 +46549,7 @@
       <c r="D32" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="291" t="s">
+      <c r="E32" s="304" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -43880,7 +46577,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="291"/>
+      <c r="E33" s="304"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -43904,7 +46601,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="289" t="s">
+      <c r="E34" s="303" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -43929,7 +46626,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="289"/>
+      <c r="E35" s="303"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -43951,7 +46648,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="291" t="s">
+      <c r="E36" s="304" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -43973,7 +46670,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="291"/>
+      <c r="E37" s="304"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -44501,6 +47198,18 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="A16:A17"/>
@@ -44509,18 +47218,6 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/raw/D3.xlsx
+++ b/raw/D3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="4" activeTab="16"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="4" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="30-2" sheetId="34" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="20-2" sheetId="48" r:id="rId15"/>
     <sheet name="21" sheetId="49" r:id="rId16"/>
     <sheet name="22" sheetId="50" r:id="rId17"/>
+    <sheet name="23" sheetId="51" r:id="rId18"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -579,6 +580,94 @@
       </text>
     </comment>
     <comment ref="K35" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Сандыбай Берды
+87759316709</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments18.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="J7" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Алібек
+87012894507</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I13" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Аслан
+87014988298</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I15" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Сандыбай Берды
+87759316709</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Даулет
+87025167087</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1294,7 +1383,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="275">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -2113,6 +2202,12 @@
   </si>
   <si>
     <t>31-H2994/12</t>
+  </si>
+  <si>
+    <t>44-Н1434/12н</t>
+  </si>
+  <si>
+    <t>31-H0004/12</t>
   </si>
 </sst>
 </file>
@@ -2933,7 +3028,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="324">
+  <cellXfs count="332">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3787,22 +3882,25 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3813,6 +3911,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3829,22 +3930,28 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3868,11 +3975,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5067,21 +5186,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="297" t="s">
+      <c r="A1" s="316" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="297"/>
-      <c r="C1" s="297"/>
-      <c r="D1" s="297"/>
-      <c r="E1" s="297"/>
-      <c r="F1" s="297"/>
-      <c r="G1" s="297"/>
-      <c r="H1" s="297"/>
-      <c r="I1" s="297"/>
-      <c r="J1" s="297"/>
-      <c r="K1" s="297"/>
-      <c r="L1" s="297"/>
-      <c r="M1" s="297"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="316"/>
+      <c r="M1" s="316"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -5136,13 +5255,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="298" t="s">
+      <c r="D3" s="305" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="298" t="s">
+      <c r="F3" s="305" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -5154,24 +5273,24 @@
       <c r="I3" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="296" t="s">
+      <c r="J3" s="311" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="299" t="s">
+      <c r="M3" s="312" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="307" t="s">
+      <c r="Q3" s="309" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="308"/>
+      <c r="R3" s="310"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="301" t="s">
+      <c r="T3" s="302" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="302"/>
+      <c r="U3" s="303"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -5183,20 +5302,20 @@
       <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="298"/>
+      <c r="D4" s="305"/>
       <c r="E4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="298"/>
+      <c r="F4" s="305"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="296"/>
+      <c r="J4" s="311"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="299"/>
+      <c r="M4" s="312"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -5235,7 +5354,7 @@
       <c r="E5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="306" t="s">
+      <c r="F5" s="308" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -5243,7 +5362,7 @@
       <c r="I5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="298" t="s">
+      <c r="J5" s="305" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -5288,13 +5407,13 @@
       <c r="E6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="306"/>
+      <c r="F6" s="308"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="298"/>
+      <c r="J6" s="305"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -5340,13 +5459,13 @@
       <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="296" t="s">
+      <c r="F7" s="311" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="305" t="s">
+      <c r="J7" s="307" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="54"/>
@@ -5394,11 +5513,11 @@
       <c r="E8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="296"/>
+      <c r="F8" s="311"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="305"/>
+      <c r="J8" s="307"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -5442,7 +5561,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="58"/>
-      <c r="F9" s="306" t="s">
+      <c r="F9" s="308" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="64"/>
@@ -5482,7 +5601,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="306"/>
+      <c r="F10" s="308"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="59"/>
@@ -5607,7 +5726,7 @@
         <v>115</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="299" t="s">
+      <c r="H13" s="312" t="s">
         <v>82</v>
       </c>
       <c r="I13" s="30"/>
@@ -5646,7 +5765,7 @@
       <c r="F14" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="299"/>
+      <c r="H14" s="312"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -5681,7 +5800,7 @@
         <v>83</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="299" t="s">
+      <c r="H15" s="312" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="30"/>
@@ -5718,7 +5837,7 @@
         <v>81</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="299"/>
+      <c r="H16" s="312"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
@@ -5750,7 +5869,7 @@
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="309" t="s">
+      <c r="H17" s="313" t="s">
         <v>45</v>
       </c>
       <c r="I17" s="30"/>
@@ -5785,7 +5904,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="310"/>
+      <c r="H18" s="314"/>
       <c r="I18" s="30"/>
       <c r="J18" s="123"/>
       <c r="K18" s="8"/>
@@ -5802,7 +5921,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="296" t="s">
+      <c r="H19" s="311" t="s">
         <v>85</v>
       </c>
       <c r="I19" s="30"/>
@@ -5827,7 +5946,7 @@
       <c r="E20" s="137"/>
       <c r="F20" s="8"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="296"/>
+      <c r="H20" s="311"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -5846,7 +5965,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="296" t="s">
+      <c r="H21" s="311" t="s">
         <v>84</v>
       </c>
       <c r="I21" s="30"/>
@@ -5863,7 +5982,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="137"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="296"/>
+      <c r="H22" s="311"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -5960,13 +6079,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="300" t="s">
+      <c r="A28" s="317" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="300"/>
-      <c r="C28" s="300"/>
-      <c r="D28" s="300"/>
-      <c r="E28" s="300"/>
+      <c r="B28" s="317"/>
+      <c r="C28" s="317"/>
+      <c r="D28" s="317"/>
+      <c r="E28" s="317"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -6026,7 +6145,7 @@
       <c r="D30" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="304" t="s">
+      <c r="E30" s="306" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -6060,7 +6179,7 @@
       <c r="D31" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="304"/>
+      <c r="E31" s="306"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -6090,7 +6209,7 @@
       <c r="D32" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="304" t="s">
+      <c r="E32" s="306" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="8"/>
@@ -6116,7 +6235,7 @@
       <c r="D33" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="304"/>
+      <c r="E33" s="306"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
       <c r="I33" s="30"/>
@@ -6139,7 +6258,7 @@
       <c r="D34" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="303" t="s">
+      <c r="E34" s="304" t="s">
         <v>133</v>
       </c>
       <c r="G34" s="8"/>
@@ -6160,7 +6279,7 @@
       <c r="D35" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="303"/>
+      <c r="E35" s="304"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
       <c r="I35" s="30"/>
@@ -6179,7 +6298,7 @@
       <c r="D36" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="304" t="s">
+      <c r="E36" s="306" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -6199,7 +6318,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="304"/>
+      <c r="E37" s="306"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -6666,7 +6785,7 @@
       <c r="S65"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A66" s="295" t="s">
+      <c r="A66" s="315" t="s">
         <v>139</v>
       </c>
       <c r="L66" s="119" t="s">
@@ -6678,7 +6797,7 @@
       <c r="S66"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A67" s="295"/>
+      <c r="A67" s="315"/>
       <c r="L67" s="119" t="s">
         <v>95</v>
       </c>
@@ -6730,6 +6849,14 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="J5:J6"/>
@@ -6745,14 +6872,6 @@
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="H17:H18"/>
     <mergeCell ref="H19:H20"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A28:E28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -7669,21 +7788,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="297" t="s">
+      <c r="A1" s="316" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="297"/>
-      <c r="C1" s="297"/>
-      <c r="D1" s="297"/>
-      <c r="E1" s="297"/>
-      <c r="F1" s="297"/>
-      <c r="G1" s="297"/>
-      <c r="H1" s="297"/>
-      <c r="I1" s="297"/>
-      <c r="J1" s="297"/>
-      <c r="K1" s="297"/>
-      <c r="L1" s="297"/>
-      <c r="M1" s="297"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="316"/>
+      <c r="M1" s="316"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -7742,7 +7861,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="298" t="s">
+      <c r="F3" s="305" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -7751,24 +7870,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="305" t="s">
+      <c r="J3" s="307" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="322" t="s">
+      <c r="M3" s="329" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="307" t="s">
+      <c r="Q3" s="309" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="308"/>
+      <c r="R3" s="310"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="301" t="s">
+      <c r="T3" s="302" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="302"/>
+      <c r="U3" s="303"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -7786,16 +7905,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="298"/>
+      <c r="F4" s="305"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="305"/>
+      <c r="J4" s="307"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="322"/>
+      <c r="M4" s="329"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -7834,7 +7953,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="306" t="s">
+      <c r="F5" s="308" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -7842,7 +7961,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="298" t="s">
+      <c r="J5" s="305" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -7887,13 +8006,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="306"/>
+      <c r="F6" s="308"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="298"/>
+      <c r="J6" s="305"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -7940,7 +8059,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="306" t="s">
+      <c r="F7" s="308" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -7992,7 +8111,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="306"/>
+      <c r="F8" s="308"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -8208,7 +8327,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="296" t="s">
+      <c r="H13" s="311" t="s">
         <v>121</v>
       </c>
       <c r="I13" s="30"/>
@@ -8244,7 +8363,7 @@
       <c r="F14" s="240" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="296"/>
+      <c r="H14" s="311"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -8277,7 +8396,7 @@
       <c r="E15" s="240"/>
       <c r="F15" s="8"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="296" t="s">
+      <c r="H15" s="311" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="30"/>
@@ -8306,7 +8425,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="296" t="s">
+      <c r="B16" s="311" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="8"/>
@@ -8314,7 +8433,7 @@
       <c r="E16" s="59"/>
       <c r="F16" s="8"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="296"/>
+      <c r="H16" s="311"/>
       <c r="I16" s="30"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
@@ -8341,13 +8460,13 @@
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
-      <c r="B17" s="296"/>
+      <c r="B17" s="311"/>
       <c r="C17" s="8"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="299" t="s">
+      <c r="H17" s="312" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -8382,7 +8501,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="299"/>
+      <c r="H18" s="312"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -8399,7 +8518,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="299" t="s">
+      <c r="H19" s="312" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -8424,7 +8543,7 @@
       <c r="E20" s="240"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="299"/>
+      <c r="H20" s="312"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -8443,7 +8562,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="299" t="s">
+      <c r="H21" s="312" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -8461,7 +8580,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="240"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="299"/>
+      <c r="H22" s="312"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -8558,13 +8677,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="300" t="s">
+      <c r="A28" s="317" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="300"/>
-      <c r="C28" s="300"/>
-      <c r="D28" s="300"/>
-      <c r="E28" s="300"/>
+      <c r="B28" s="317"/>
+      <c r="C28" s="317"/>
+      <c r="D28" s="317"/>
+      <c r="E28" s="317"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -8624,7 +8743,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="304" t="s">
+      <c r="E30" s="306" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -8658,7 +8777,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="304"/>
+      <c r="E31" s="306"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -8685,7 +8804,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="304" t="s">
+      <c r="E32" s="306" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -8713,7 +8832,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="304"/>
+      <c r="E33" s="306"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -8737,7 +8856,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="303" t="s">
+      <c r="E34" s="304" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -8762,7 +8881,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="303"/>
+      <c r="E35" s="304"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -8784,7 +8903,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="304" t="s">
+      <c r="E36" s="306" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -8806,7 +8925,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="304"/>
+      <c r="E37" s="306"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -9338,6 +9457,18 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="H15:H16"/>
@@ -9346,18 +9477,6 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -10274,21 +10393,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="297" t="s">
+      <c r="A1" s="316" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="297"/>
-      <c r="C1" s="297"/>
-      <c r="D1" s="297"/>
-      <c r="E1" s="297"/>
-      <c r="F1" s="297"/>
-      <c r="G1" s="297"/>
-      <c r="H1" s="297"/>
-      <c r="I1" s="297"/>
-      <c r="J1" s="297"/>
-      <c r="K1" s="297"/>
-      <c r="L1" s="297"/>
-      <c r="M1" s="297"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="316"/>
+      <c r="M1" s="316"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -10347,7 +10466,7 @@
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="298" t="s">
+      <c r="F3" s="305" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -10356,24 +10475,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="305" t="s">
+      <c r="J3" s="307" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="299" t="s">
+      <c r="M3" s="312" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="307" t="s">
+      <c r="Q3" s="309" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="308"/>
+      <c r="R3" s="310"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="301" t="s">
+      <c r="T3" s="302" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="302"/>
+      <c r="U3" s="303"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -10391,16 +10510,16 @@
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="298"/>
+      <c r="F4" s="305"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="305"/>
+      <c r="J4" s="307"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="299"/>
+      <c r="M4" s="312"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -10439,7 +10558,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="306" t="s">
+      <c r="F5" s="308" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -10447,7 +10566,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="298" t="s">
+      <c r="J5" s="305" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -10492,13 +10611,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="306"/>
+      <c r="F6" s="308"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="298"/>
+      <c r="J6" s="305"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -10545,7 +10664,7 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="306" t="s">
+      <c r="F7" s="308" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
@@ -10597,7 +10716,7 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="306"/>
+      <c r="F8" s="308"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
@@ -10813,7 +10932,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="296" t="s">
+      <c r="H13" s="311" t="s">
         <v>121</v>
       </c>
       <c r="I13" s="30"/>
@@ -10849,7 +10968,7 @@
       <c r="F14" s="248" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="296"/>
+      <c r="H14" s="311"/>
       <c r="I14" s="30"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
@@ -10882,7 +11001,7 @@
       <c r="E15" s="248"/>
       <c r="F15" s="8"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="296" t="s">
+      <c r="H15" s="311" t="s">
         <v>84</v>
       </c>
       <c r="I15" s="30"/>
@@ -10911,7 +11030,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8"/>
-      <c r="B16" s="296" t="s">
+      <c r="B16" s="311" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="8"/>
@@ -10919,7 +11038,7 @@
       <c r="E16" s="59"/>
       <c r="F16" s="8"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="296"/>
+      <c r="H16" s="311"/>
       <c r="I16" s="30"/>
       <c r="J16" s="60"/>
       <c r="K16" s="8"/>
@@ -10946,13 +11065,13 @@
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
-      <c r="B17" s="296"/>
+      <c r="B17" s="311"/>
       <c r="C17" s="8"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="299" t="s">
+      <c r="H17" s="312" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="30"/>
@@ -10987,7 +11106,7 @@
       <c r="E18" s="59"/>
       <c r="F18" s="8"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="299"/>
+      <c r="H18" s="312"/>
       <c r="I18" s="30"/>
       <c r="J18" s="71"/>
       <c r="K18" s="8"/>
@@ -11004,7 +11123,7 @@
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
       <c r="G19" s="158"/>
-      <c r="H19" s="299" t="s">
+      <c r="H19" s="312" t="s">
         <v>45</v>
       </c>
       <c r="I19" s="30"/>
@@ -11029,7 +11148,7 @@
       <c r="E20" s="248"/>
       <c r="F20" s="8"/>
       <c r="G20" s="158"/>
-      <c r="H20" s="299"/>
+      <c r="H20" s="312"/>
       <c r="I20" s="30"/>
       <c r="J20" s="60"/>
       <c r="K20" s="8"/>
@@ -11048,7 +11167,7 @@
       <c r="D21" s="61"/>
       <c r="F21" s="87"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="299" t="s">
+      <c r="H21" s="312" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="30"/>
@@ -11066,7 +11185,7 @@
       <c r="E22" s="30"/>
       <c r="F22" s="248"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="299"/>
+      <c r="H22" s="312"/>
       <c r="I22" s="30"/>
       <c r="J22" s="60"/>
       <c r="K22" s="8"/>
@@ -11163,13 +11282,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="300" t="s">
+      <c r="A28" s="317" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="300"/>
-      <c r="C28" s="300"/>
-      <c r="D28" s="300"/>
-      <c r="E28" s="300"/>
+      <c r="B28" s="317"/>
+      <c r="C28" s="317"/>
+      <c r="D28" s="317"/>
+      <c r="E28" s="317"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -11229,7 +11348,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="304" t="s">
+      <c r="E30" s="306" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -11263,7 +11382,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="304"/>
+      <c r="E31" s="306"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -11293,7 +11412,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="304" t="s">
+      <c r="E32" s="306" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -11321,7 +11440,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="304"/>
+      <c r="E33" s="306"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -11345,7 +11464,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="303" t="s">
+      <c r="E34" s="304" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -11369,7 +11488,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="303"/>
+      <c r="E35" s="304"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -11391,7 +11510,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="304" t="s">
+      <c r="E36" s="306" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -11411,7 +11530,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="304"/>
+      <c r="E37" s="306"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -11943,6 +12062,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="B16:B17"/>
@@ -11956,13 +12082,6 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="H15:H16"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -12879,21 +12998,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="297" t="s">
+      <c r="A1" s="316" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="297"/>
-      <c r="C1" s="297"/>
-      <c r="D1" s="297"/>
-      <c r="E1" s="297"/>
-      <c r="F1" s="297"/>
-      <c r="G1" s="297"/>
-      <c r="H1" s="297"/>
-      <c r="I1" s="297"/>
-      <c r="J1" s="297"/>
-      <c r="K1" s="297"/>
-      <c r="L1" s="297"/>
-      <c r="M1" s="297"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="316"/>
+      <c r="M1" s="316"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -12948,13 +13067,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="299" t="s">
+      <c r="D3" s="312" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="298" t="s">
+      <c r="F3" s="305" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -12963,24 +13082,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="305" t="s">
+      <c r="J3" s="307" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="299" t="s">
+      <c r="M3" s="312" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="307" t="s">
+      <c r="Q3" s="309" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="308"/>
+      <c r="R3" s="310"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="301" t="s">
+      <c r="T3" s="302" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="302"/>
+      <c r="U3" s="303"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -12994,20 +13113,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="299"/>
+      <c r="D4" s="312"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="298"/>
+      <c r="F4" s="305"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="305"/>
+      <c r="J4" s="307"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="299"/>
+      <c r="M4" s="312"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -13046,7 +13165,7 @@
       <c r="E5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="306" t="s">
+      <c r="F5" s="308" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -13054,7 +13173,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="298" t="s">
+      <c r="J5" s="305" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -13099,13 +13218,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="306"/>
+      <c r="F6" s="308"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="298"/>
+      <c r="J6" s="305"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -13152,13 +13271,13 @@
       <c r="E7" s="260" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="323" t="s">
+      <c r="F7" s="330" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="299" t="s">
+      <c r="J7" s="312" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -13206,11 +13325,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="323"/>
+      <c r="F8" s="330"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="299"/>
+      <c r="J8" s="312"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -13255,7 +13374,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="296" t="s">
+      <c r="F9" s="311" t="s">
         <v>121</v>
       </c>
       <c r="G9" s="64"/>
@@ -13295,7 +13414,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="296"/>
+      <c r="F10" s="311"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -13515,13 +13634,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="296" t="s">
+      <c r="A16" s="311" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="296" t="s">
+      <c r="B16" s="311" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="299" t="s">
+      <c r="C16" s="312" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -13556,9 +13675,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="296"/>
-      <c r="B17" s="296"/>
-      <c r="C17" s="299"/>
+      <c r="A17" s="311"/>
+      <c r="B17" s="311"/>
+      <c r="C17" s="312"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="259" t="s">
@@ -13769,13 +13888,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="300" t="s">
+      <c r="A28" s="317" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="300"/>
-      <c r="C28" s="300"/>
-      <c r="D28" s="300"/>
-      <c r="E28" s="300"/>
+      <c r="B28" s="317"/>
+      <c r="C28" s="317"/>
+      <c r="D28" s="317"/>
+      <c r="E28" s="317"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -13835,7 +13954,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="304" t="s">
+      <c r="E30" s="306" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -13869,7 +13988,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="304"/>
+      <c r="E31" s="306"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -13899,7 +14018,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="304" t="s">
+      <c r="E32" s="306" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -13929,7 +14048,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="304"/>
+      <c r="E33" s="306"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -13953,7 +14072,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="303" t="s">
+      <c r="E34" s="304" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -13977,7 +14096,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="303"/>
+      <c r="E35" s="304"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -13996,7 +14115,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="304" t="s">
+      <c r="E36" s="306" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -14016,7 +14135,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="304"/>
+      <c r="E37" s="306"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -14546,6 +14665,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="J7:J8"/>
@@ -14560,12 +14685,6 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="Q3:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -15482,21 +15601,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="297" t="s">
+      <c r="A1" s="316" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="297"/>
-      <c r="C1" s="297"/>
-      <c r="D1" s="297"/>
-      <c r="E1" s="297"/>
-      <c r="F1" s="297"/>
-      <c r="G1" s="297"/>
-      <c r="H1" s="297"/>
-      <c r="I1" s="297"/>
-      <c r="J1" s="297"/>
-      <c r="K1" s="297"/>
-      <c r="L1" s="297"/>
-      <c r="M1" s="297"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="316"/>
+      <c r="M1" s="316"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -15551,13 +15670,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="298" t="s">
+      <c r="D3" s="305" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="298" t="s">
+      <c r="F3" s="305" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -15566,24 +15685,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="305" t="s">
+      <c r="J3" s="307" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="299" t="s">
+      <c r="M3" s="312" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="307" t="s">
+      <c r="Q3" s="309" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="308"/>
+      <c r="R3" s="310"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="301" t="s">
+      <c r="T3" s="302" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="302"/>
+      <c r="U3" s="303"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -15597,20 +15716,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="298"/>
+      <c r="D4" s="305"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="298"/>
+      <c r="F4" s="305"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="305"/>
+      <c r="J4" s="307"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="299"/>
+      <c r="M4" s="312"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -15649,7 +15768,7 @@
       <c r="E5" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="F5" s="306" t="s">
+      <c r="F5" s="308" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -15657,7 +15776,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="298" t="s">
+      <c r="J5" s="305" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -15702,13 +15821,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="306"/>
+      <c r="F6" s="308"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="298"/>
+      <c r="J6" s="305"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -15755,13 +15874,13 @@
       <c r="E7" s="260" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="323" t="s">
+      <c r="F7" s="330" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="299" t="s">
+      <c r="J7" s="312" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -15809,11 +15928,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="323"/>
+      <c r="F8" s="330"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="299"/>
+      <c r="J8" s="312"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -15858,7 +15977,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="296" t="s">
+      <c r="F9" s="311" t="s">
         <v>121</v>
       </c>
       <c r="G9" s="64"/>
@@ -15898,7 +16017,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="296"/>
+      <c r="F10" s="311"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -16025,7 +16144,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="299" t="s">
+      <c r="I13" s="312" t="s">
         <v>45</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -16061,7 +16180,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="299"/>
+      <c r="I14" s="312"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -16121,13 +16240,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="296" t="s">
+      <c r="A16" s="311" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="296" t="s">
+      <c r="B16" s="311" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="299" t="s">
+      <c r="C16" s="312" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -16162,9 +16281,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="296"/>
-      <c r="B17" s="296"/>
-      <c r="C17" s="299"/>
+      <c r="A17" s="311"/>
+      <c r="B17" s="311"/>
+      <c r="C17" s="312"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="269" t="s">
@@ -16375,13 +16494,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="300" t="s">
+      <c r="A28" s="317" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="300"/>
-      <c r="C28" s="300"/>
-      <c r="D28" s="300"/>
-      <c r="E28" s="300"/>
+      <c r="B28" s="317"/>
+      <c r="C28" s="317"/>
+      <c r="D28" s="317"/>
+      <c r="E28" s="317"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -16441,7 +16560,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="304" t="s">
+      <c r="E30" s="306" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -16475,7 +16594,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="304"/>
+      <c r="E31" s="306"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -16503,7 +16622,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="304" t="s">
+      <c r="E32" s="306" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -16531,7 +16650,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="304"/>
+      <c r="E33" s="306"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -16555,7 +16674,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="303" t="s">
+      <c r="E34" s="304" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -16577,7 +16696,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="303"/>
+      <c r="E35" s="304"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -16597,7 +16716,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="304" t="s">
+      <c r="E36" s="306" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -16617,7 +16736,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="304"/>
+      <c r="E37" s="306"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -17151,6 +17270,18 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="D3:D4"/>
@@ -17160,18 +17291,6 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="E32:E33"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18088,21 +18207,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="297" t="s">
+      <c r="A1" s="316" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="297"/>
-      <c r="C1" s="297"/>
-      <c r="D1" s="297"/>
-      <c r="E1" s="297"/>
-      <c r="F1" s="297"/>
-      <c r="G1" s="297"/>
-      <c r="H1" s="297"/>
-      <c r="I1" s="297"/>
-      <c r="J1" s="297"/>
-      <c r="K1" s="297"/>
-      <c r="L1" s="297"/>
-      <c r="M1" s="297"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="316"/>
+      <c r="M1" s="316"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -18157,13 +18276,13 @@
       <c r="C3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="298" t="s">
+      <c r="D3" s="305" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="298" t="s">
+      <c r="F3" s="305" t="s">
         <v>138</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -18172,24 +18291,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="305" t="s">
+      <c r="J3" s="307" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="299" t="s">
+      <c r="M3" s="312" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="307" t="s">
+      <c r="Q3" s="309" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="308"/>
+      <c r="R3" s="310"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="301" t="s">
+      <c r="T3" s="302" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="302"/>
+      <c r="U3" s="303"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -18203,20 +18322,20 @@
       <c r="C4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="298"/>
+      <c r="D4" s="305"/>
       <c r="E4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="298"/>
+      <c r="F4" s="305"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="305"/>
+      <c r="J4" s="307"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="299"/>
+      <c r="M4" s="312"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -18255,7 +18374,7 @@
       <c r="E5" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="F5" s="306" t="s">
+      <c r="F5" s="308" t="s">
         <v>99</v>
       </c>
       <c r="G5" s="8"/>
@@ -18263,7 +18382,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="298" t="s">
+      <c r="J5" s="305" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -18308,13 +18427,13 @@
       <c r="E6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="306"/>
+      <c r="F6" s="308"/>
       <c r="G6" s="62"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="298"/>
+      <c r="J6" s="305"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -18361,13 +18480,13 @@
       <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="306" t="s">
+      <c r="F7" s="308" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="299" t="s">
+      <c r="J7" s="312" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -18415,11 +18534,11 @@
       <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="306"/>
+      <c r="F8" s="308"/>
       <c r="G8" s="64"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="299"/>
+      <c r="J8" s="312"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -18464,7 +18583,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="296" t="s">
+      <c r="F9" s="311" t="s">
         <v>121</v>
       </c>
       <c r="G9" s="64"/>
@@ -18504,7 +18623,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="296"/>
+      <c r="F10" s="311"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -18725,13 +18844,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="296" t="s">
+      <c r="A16" s="311" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="296" t="s">
+      <c r="B16" s="311" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="299" t="s">
+      <c r="C16" s="312" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -18766,9 +18885,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="296"/>
-      <c r="B17" s="296"/>
-      <c r="C17" s="299"/>
+      <c r="A17" s="311"/>
+      <c r="B17" s="311"/>
+      <c r="C17" s="312"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="8"/>
@@ -18801,7 +18920,7 @@
     <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="299" t="s">
+      <c r="C18" s="312" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="61"/>
@@ -18820,7 +18939,7 @@
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="B19" s="273"/>
-      <c r="C19" s="299"/>
+      <c r="C19" s="312"/>
       <c r="D19" s="125"/>
       <c r="E19" s="59"/>
       <c r="F19" s="8"/>
@@ -18980,13 +19099,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="300" t="s">
+      <c r="A28" s="317" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="300"/>
-      <c r="C28" s="300"/>
-      <c r="D28" s="300"/>
-      <c r="E28" s="300"/>
+      <c r="B28" s="317"/>
+      <c r="C28" s="317"/>
+      <c r="D28" s="317"/>
+      <c r="E28" s="317"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -19046,7 +19165,7 @@
       <c r="D30" s="93" t="s">
         <v>234</v>
       </c>
-      <c r="E30" s="304" t="s">
+      <c r="E30" s="306" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -19080,7 +19199,7 @@
       <c r="D31" s="93" t="s">
         <v>233</v>
       </c>
-      <c r="E31" s="304"/>
+      <c r="E31" s="306"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -19108,7 +19227,7 @@
       <c r="D32" s="93" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="304" t="s">
+      <c r="E32" s="306" t="s">
         <v>103</v>
       </c>
       <c r="F32" s="8"/>
@@ -19136,7 +19255,7 @@
       <c r="D33" s="93" t="s">
         <v>236</v>
       </c>
-      <c r="E33" s="304"/>
+      <c r="E33" s="306"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -19160,7 +19279,7 @@
       <c r="D34" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="E34" s="303" t="s">
+      <c r="E34" s="304" t="s">
         <v>133</v>
       </c>
       <c r="F34" s="8"/>
@@ -19184,7 +19303,7 @@
       <c r="D35" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="E35" s="303"/>
+      <c r="E35" s="304"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -19204,7 +19323,7 @@
       <c r="D36" s="93" t="s">
         <v>239</v>
       </c>
-      <c r="E36" s="304" t="s">
+      <c r="E36" s="306" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="53"/>
@@ -19224,7 +19343,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="304"/>
+      <c r="E37" s="306"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -19756,6 +19875,18 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
@@ -19765,18 +19896,6 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="E30:E31"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20697,21 +20816,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="297" t="s">
+      <c r="A1" s="316" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="297"/>
-      <c r="C1" s="297"/>
-      <c r="D1" s="297"/>
-      <c r="E1" s="297"/>
-      <c r="F1" s="297"/>
-      <c r="G1" s="297"/>
-      <c r="H1" s="297"/>
-      <c r="I1" s="297"/>
-      <c r="J1" s="297"/>
-      <c r="K1" s="297"/>
-      <c r="L1" s="297"/>
-      <c r="M1" s="297"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="316"/>
+      <c r="M1" s="316"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -20766,13 +20885,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="298" t="s">
+      <c r="D3" s="305" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="306" t="s">
+      <c r="F3" s="308" t="s">
         <v>99</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -20781,24 +20900,24 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="305" t="s">
+      <c r="J3" s="307" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="8"/>
-      <c r="M3" s="299" t="s">
+      <c r="M3" s="312" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="307" t="s">
+      <c r="Q3" s="309" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="308"/>
+      <c r="R3" s="310"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="301" t="s">
+      <c r="T3" s="302" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="302"/>
+      <c r="U3" s="303"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -20809,20 +20928,20 @@
       <c r="C4" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="298"/>
+      <c r="D4" s="305"/>
       <c r="E4" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="F4" s="306"/>
+      <c r="F4" s="308"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="305"/>
+      <c r="J4" s="307"/>
       <c r="K4" s="54"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="299"/>
+      <c r="M4" s="312"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -20863,7 +20982,7 @@
       <c r="E5" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F5" s="306" t="s">
+      <c r="F5" s="308" t="s">
         <v>257</v>
       </c>
       <c r="G5" s="8"/>
@@ -20871,7 +20990,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="298" t="s">
+      <c r="J5" s="305" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="54"/>
@@ -20916,13 +21035,13 @@
       <c r="E6" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F6" s="306"/>
+      <c r="F6" s="308"/>
       <c r="G6" s="278"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="298"/>
+      <c r="J6" s="305"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="N6" s="46" t="s">
@@ -20966,13 +21085,13 @@
       <c r="E7" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="306" t="s">
+      <c r="F7" s="308" t="s">
         <v>110</v>
       </c>
       <c r="G7" s="278"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="299" t="s">
+      <c r="J7" s="312" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -21020,11 +21139,11 @@
       <c r="E8" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F8" s="306"/>
+      <c r="F8" s="308"/>
       <c r="G8" s="62"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="299"/>
+      <c r="J8" s="312"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="56">
@@ -21069,7 +21188,7 @@
       </c>
       <c r="D9" s="58"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="296" t="s">
+      <c r="F9" s="311" t="s">
         <v>258</v>
       </c>
       <c r="G9" s="62"/>
@@ -21109,7 +21228,7 @@
       </c>
       <c r="D10" s="61"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="296"/>
+      <c r="F10" s="311"/>
       <c r="G10" s="64"/>
       <c r="H10" s="62"/>
       <c r="I10" s="134"/>
@@ -21236,7 +21355,7 @@
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="30"/>
-      <c r="I13" s="299" t="s">
+      <c r="I13" s="312" t="s">
         <v>45</v>
       </c>
       <c r="J13" s="127" t="s">
@@ -21272,7 +21391,7 @@
         <v>59</v>
       </c>
       <c r="H14" s="30"/>
-      <c r="I14" s="299"/>
+      <c r="I14" s="312"/>
       <c r="J14" s="60"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -21334,13 +21453,13 @@
       <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="296" t="s">
+      <c r="A16" s="311" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="296" t="s">
+      <c r="B16" s="311" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="299" t="s">
+      <c r="C16" s="312" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="61"/>
@@ -21375,9 +21494,9 @@
       <c r="W16" s="70"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="296"/>
-      <c r="B17" s="296"/>
-      <c r="C17" s="299"/>
+      <c r="A17" s="311"/>
+      <c r="B17" s="311"/>
+      <c r="C17" s="312"/>
       <c r="D17" s="61"/>
       <c r="E17" s="59"/>
       <c r="F17" s="128" t="s">
@@ -21589,13 +21708,13 @@
       <c r="S27"/>
     </row>
     <row r="28" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="300" t="s">
+      <c r="A28" s="317" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="300"/>
-      <c r="C28" s="300"/>
-      <c r="D28" s="300"/>
-      <c r="E28" s="300"/>
+      <c r="B28" s="317"/>
+      <c r="C28" s="317"/>
+      <c r="D28" s="317"/>
+      <c r="E28" s="317"/>
       <c r="F28" s="91"/>
       <c r="G28" s="8"/>
       <c r="H28" s="30"/>
@@ -21655,7 +21774,7 @@
       <c r="D30" s="93" t="s">
         <v>251</v>
       </c>
-      <c r="E30" s="304" t="s">
+      <c r="E30" s="306" t="s">
         <v>90</v>
       </c>
       <c r="F30" s="8"/>
@@ -21689,7 +21808,7 @@
       <c r="D31" s="93" t="s">
         <v>252</v>
       </c>
-      <c r="E31" s="304"/>
+      <c r="E31" s="306"/>
       <c r="F31" s="8"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30"/>
@@ -21717,7 +21836,7 @@
       <c r="D32" s="93" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="304" t="s">
+      <c r="E32" s="306" t="s">
         <v>259</v>
       </c>
       <c r="F32" s="8"/>
@@ -21745,7 +21864,7 @@
       <c r="D33" s="93" t="s">
         <v>253</v>
       </c>
-      <c r="E33" s="304"/>
+      <c r="E33" s="306"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="30"/>
@@ -21769,7 +21888,7 @@
       <c r="D34" s="93" t="s">
         <v>254</v>
       </c>
-      <c r="E34" s="304" t="s">
+      <c r="E34" s="306" t="s">
         <v>260</v>
       </c>
       <c r="F34" s="8"/>
@@ -21791,7 +21910,7 @@
       <c r="D35" s="93" t="s">
         <v>255</v>
       </c>
-      <c r="E35" s="304"/>
+      <c r="E35" s="306"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="96"/>
@@ -21811,7 +21930,7 @@
       <c r="D36" s="93" t="s">
         <v>256</v>
       </c>
-      <c r="E36" s="304" t="s">
+      <c r="E36" s="306" t="s">
         <v>261</v>
       </c>
       <c r="F36" s="53"/>
@@ -21831,7 +21950,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="E37" s="304"/>
+      <c r="E37" s="306"/>
       <c r="F37" s="77"/>
       <c r="G37" s="8"/>
       <c r="H37" s="99"/>
@@ -22363,27 +22482,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="E30:E31"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="Q3:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -23301,21 +23420,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="297" t="s">
+      <c r="A1" s="316" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="297"/>
-      <c r="C1" s="297"/>
-      <c r="D1" s="297"/>
-      <c r="E1" s="297"/>
-      <c r="F1" s="297"/>
-      <c r="G1" s="297"/>
-      <c r="H1" s="297"/>
-      <c r="I1" s="297"/>
-      <c r="J1" s="297"/>
-      <c r="K1" s="297"/>
-      <c r="L1" s="297"/>
-      <c r="M1" s="297"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="316"/>
+      <c r="M1" s="316"/>
       <c r="S1"/>
     </row>
     <row r="2" spans="1:23" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -23370,13 +23489,13 @@
       <c r="C3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="298" t="s">
+      <c r="D3" s="305" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="306" t="s">
+      <c r="F3" s="308" t="s">
         <v>99</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -23385,25 +23504,25 @@
       <c r="I3" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="305" t="s">
+      <c r="J3" s="307" t="s">
         <v>10</v>
       </c>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
-      <c r="M3" s="299" t="s">
+      <c r="M3" s="312" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="307" t="s">
+      <c r="Q3" s="309" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="308"/>
+      <c r="R3" s="310"/>
       <c r="S3" s="27"/>
-      <c r="T3" s="301" t="s">
+      <c r="T3" s="302" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="302"/>
+      <c r="U3" s="303"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29"/>
     </row>
@@ -23414,20 +23533,20 @@
       <c r="C4" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="298"/>
+      <c r="D4" s="305"/>
       <c r="E4" s="258" t="s">
         <v>182</v>
       </c>
-      <c r="F4" s="306"/>
+      <c r="F4" s="308"/>
       <c r="G4" s="8"/>
       <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="305"/>
+      <c r="J4" s="307"/>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="299"/>
+      <c r="M4" s="312"/>
       <c r="O4" s="31" t="s">
         <v>68</v>
       </c>
@@ -23468,7 +23587,7 @@
       <c r="E5" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F5" s="306" t="s">
+      <c r="F5" s="308" t="s">
         <v>257</v>
       </c>
       <c r="G5" s="8"/>
@@ -23476,7 +23595,7 @@
       <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="298" t="s">
+      <c r="J5" s="305" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="8"/>
@@ -23520,13 +23639,13 @@
       <c r="E6" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F6" s="306"/>
+      <c r="F6" s="308"/>
       <c r="G6" s="278"/>
       <c r="H6" s="30"/>
       <c r="I6" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="298"/>
+      <c r="J6" s="305"/>
       <c r="K6" s="54"/>
       <c r="L6" s="8"/>
       <c r="M6" s="126" t="s">
@@ -23573,13 +23692,13 @@
       <c r="E7" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="306" t="s">
+      <c r="F7" s="308" t="s">
         <v>110</v>
       </c>
       <c r="G7" s="278"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="299" t="s">
+      <c r="J7" s="312" t="s">
         <v>82</v>
       </c>
       <c r="K7" s="54"/>
@@ -23627,11 +23746,11 @@
       <c r="E8" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F8" s